--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B369E781-21F2-46FC-BE83-EE81FA312749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF9AA86-8710-405B-8891-B3AC9E78BCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21030" yWindow="16620" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22740" yWindow="16470" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7581" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7582" uniqueCount="995">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -4801,6 +4801,17 @@
   </si>
   <si>
     <t>04:30-10定期メンテナンス中</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩の海岸</t>
+    <rPh sb="3" eb="5">
+      <t>カイガン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:21</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7895,12 +7906,14 @@
         <v>55</v>
       </c>
       <c r="C60" s="29" t="s">
-        <v>441</v>
+        <v>994</v>
       </c>
       <c r="D60" s="28" t="s">
         <v>989</v>
       </c>
-      <c r="E60" s="28"/>
+      <c r="E60" s="28" t="s">
+        <v>993</v>
+      </c>
       <c r="F60" s="29" t="s">
         <v>441</v>
       </c>
@@ -7920,7 +7933,7 @@
       </c>
       <c r="N60" s="67" t="str">
         <f t="shared" si="0"/>
-        <v>10:00</v>
+        <v>10:21</v>
       </c>
       <c r="O60" s="67" t="str">
         <f t="shared" si="1"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF9AA86-8710-405B-8891-B3AC9E78BCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38352E7-E1BC-4EE5-948D-E5464371A87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22740" yWindow="16470" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21285" yWindow="16950" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7582" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7598" uniqueCount="1012">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -4812,6 +4812,100 @@
   </si>
   <si>
     <t>10:21</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新緑</t>
+    <rPh sb="0" eb="2">
+      <t>シンリョク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナマズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>万年キョンシー</t>
+    <rPh sb="0" eb="2">
+      <t>マンネン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:26</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:35_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:24</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武運村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>鬼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>蛮</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14：53</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:50_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>鬼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>蛮</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>オオウスバ</t>
+  </si>
+  <si>
+    <t>オオウスバ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風之平原</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7915,19 +8009,23 @@
         <v>993</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>441</v>
+        <v>1000</v>
       </c>
       <c r="G60" s="28" t="s">
         <v>989</v>
       </c>
-      <c r="H60" s="28"/>
+      <c r="H60" s="28" t="s">
+        <v>996</v>
+      </c>
       <c r="I60" s="29" t="s">
-        <v>441</v>
+        <v>543</v>
       </c>
       <c r="J60" s="28" t="s">
         <v>989</v>
       </c>
-      <c r="K60" s="28"/>
+      <c r="K60" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="L60" s="130" t="s">
         <v>25</v>
       </c>
@@ -7937,11 +8035,11 @@
       </c>
       <c r="O60" s="67" t="str">
         <f t="shared" si="1"/>
-        <v>10:00</v>
+        <v>10:35_?</v>
       </c>
       <c r="P60" s="67" t="str">
         <f t="shared" si="2"/>
-        <v>10:00</v>
+        <v>10:30</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="18" customHeight="1">
@@ -7957,8 +8055,12 @@
       <c r="F61" s="29"/>
       <c r="G61" s="28"/>
       <c r="H61" s="28"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="28"/>
+      <c r="I61" s="139" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J61" s="28" t="s">
+        <v>1010</v>
+      </c>
       <c r="K61" s="28"/>
       <c r="L61" s="130" t="s">
         <v>23</v>
@@ -7973,7 +8075,7 @@
       </c>
       <c r="P61" s="67" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:00</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1">
@@ -7988,10 +8090,18 @@
       <c r="E62" s="28"/>
       <c r="F62" s="29"/>
       <c r="G62" s="28"/>
-      <c r="H62" s="28"/>
-      <c r="I62" s="29"/>
-      <c r="J62" s="28"/>
-      <c r="K62" s="28"/>
+      <c r="H62" s="28" t="s">
+        <v>998</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>997</v>
+      </c>
+      <c r="J62" s="28" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K62" s="28" t="s">
+        <v>1008</v>
+      </c>
       <c r="L62" s="130" t="s">
         <v>22</v>
       </c>
@@ -8005,7 +8115,7 @@
       </c>
       <c r="P62" s="67" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>12:00</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="18" customHeight="1">
@@ -8021,9 +8131,13 @@
       <c r="F63" s="29"/>
       <c r="G63" s="28"/>
       <c r="H63" s="28"/>
-      <c r="I63" s="29"/>
+      <c r="I63" s="29" t="s">
+        <v>999</v>
+      </c>
       <c r="J63" s="28"/>
-      <c r="K63" s="28"/>
+      <c r="K63" s="28" t="s">
+        <v>1007</v>
+      </c>
       <c r="L63" s="130" t="s">
         <v>21</v>
       </c>
@@ -8037,7 +8151,7 @@
       </c>
       <c r="P63" s="67" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:26</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="18" customHeight="1">
@@ -8047,29 +8161,41 @@
       <c r="B64" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C64" s="29"/>
+      <c r="C64" s="29" t="s">
+        <v>1001</v>
+      </c>
       <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="29"/>
+      <c r="E64" s="28" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F64" s="29" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G64" s="29"/>
+      <c r="H64" s="28" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>1005</v>
+      </c>
       <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
+      <c r="K64" s="28" t="s">
+        <v>1007</v>
+      </c>
       <c r="L64" s="130" t="s">
         <v>20</v>
       </c>
       <c r="N64" s="67" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14:24</v>
       </c>
       <c r="O64" s="67" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>14:53</v>
       </c>
       <c r="P64" s="67" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:50_?</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="18" customHeight="1">
@@ -8239,7 +8365,7 @@
       <c r="B70" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="139"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="28"/>
       <c r="E70" s="28"/>
       <c r="F70" s="29"/>
@@ -8271,7 +8397,7 @@
       <c r="B71" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="139"/>
+      <c r="C71" s="29"/>
       <c r="D71" s="28"/>
       <c r="E71" s="28"/>
       <c r="F71" s="29"/>
@@ -17283,7 +17409,7 @@
         <v>528</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>701</v>
+        <v>1003</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="5"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38352E7-E1BC-4EE5-948D-E5464371A87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D9F24E-FD98-4138-8E4A-C9FCC8E773DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21285" yWindow="16950" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28710" yWindow="16965" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7598" uniqueCount="1012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7610" uniqueCount="1018">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -4867,14 +4867,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>14：53</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>14:50_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <r>
       <t>鬼</t>
     </r>
@@ -4906,6 +4898,75 @@
   </si>
   <si>
     <t>風之平原</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:53</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>14:5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16:30前</t>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16:27</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>17:40</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤村 / 鬼都</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>孤独の村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>悪鬼都市</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>18:06前</t>
+    <rPh sb="5" eb="6">
+      <t>マエ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8056,10 +8117,10 @@
       <c r="G61" s="28"/>
       <c r="H61" s="28"/>
       <c r="I61" s="139" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="J61" s="28" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="K61" s="28"/>
       <c r="L61" s="130" t="s">
@@ -8097,10 +8158,10 @@
         <v>997</v>
       </c>
       <c r="J62" s="28" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="K62" s="28" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="L62" s="130" t="s">
         <v>22</v>
@@ -8134,9 +8195,11 @@
       <c r="I63" s="29" t="s">
         <v>999</v>
       </c>
-      <c r="J63" s="28"/>
+      <c r="J63" s="28" t="s">
+        <v>4</v>
+      </c>
       <c r="K63" s="28" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="L63" s="130" t="s">
         <v>21</v>
@@ -8169,18 +8232,20 @@
         <v>1002</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="G64" s="29"/>
       <c r="H64" s="28" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I64" s="29" t="s">
+        <v>1011</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K64" s="28" t="s">
         <v>1006</v>
-      </c>
-      <c r="I64" s="29" t="s">
-        <v>1005</v>
-      </c>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28" t="s">
-        <v>1007</v>
       </c>
       <c r="L64" s="130" t="s">
         <v>20</v>
@@ -8195,7 +8260,7 @@
       </c>
       <c r="P64" s="67" t="str">
         <f t="shared" si="2"/>
-        <v>14:50_?</v>
+        <v>14:54</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="18" customHeight="1">
@@ -8240,12 +8305,20 @@
       <c r="C66" s="29"/>
       <c r="D66" s="28"/>
       <c r="E66" s="28"/>
-      <c r="F66" s="29"/>
+      <c r="F66" s="139" t="s">
+        <v>1012</v>
+      </c>
       <c r="G66" s="28"/>
-      <c r="H66" s="28"/>
-      <c r="I66" s="29"/>
+      <c r="H66" s="28" t="s">
+        <v>998</v>
+      </c>
+      <c r="I66" s="29" t="s">
+        <v>1013</v>
+      </c>
       <c r="J66" s="28"/>
-      <c r="K66" s="28"/>
+      <c r="K66" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="L66" s="130" t="s">
         <v>16</v>
       </c>
@@ -8255,11 +8328,11 @@
       </c>
       <c r="O66" s="67" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16:30前</v>
       </c>
       <c r="P66" s="67" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:27</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="18" customHeight="1">
@@ -8269,9 +8342,15 @@
       <c r="B67" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="25"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
+      <c r="C67" s="30" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>1016</v>
+      </c>
       <c r="F67" s="29"/>
       <c r="G67" s="28"/>
       <c r="H67" s="28"/>
@@ -8283,7 +8362,7 @@
       </c>
       <c r="N67" s="67" t="str">
         <f t="shared" ref="N67:N130" si="3">IF($C67&lt;&gt;"",TEXT($C67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:40</v>
       </c>
       <c r="O67" s="67" t="str">
         <f t="shared" ref="O67:O130" si="4">IF($F67&lt;&gt;"",TEXT($F67,"HH:MM"),"")</f>
@@ -8307,9 +8386,15 @@
       <c r="F68" s="29"/>
       <c r="G68" s="28"/>
       <c r="H68" s="28"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
+      <c r="I68" s="139" t="s">
+        <v>1017</v>
+      </c>
+      <c r="J68" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K68" s="28" t="s">
+        <v>1005</v>
+      </c>
       <c r="L68" s="130" t="s">
         <v>12</v>
       </c>
@@ -8323,7 +8408,7 @@
       </c>
       <c r="P68" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>18:06前</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="18" customHeight="1">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D9F24E-FD98-4138-8E4A-C9FCC8E773DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC9BE3D4-B5ED-4656-B197-E145BB1CD1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28710" yWindow="16965" windowWidth="21135" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21165" yWindow="16185" windowWidth="21195" windowHeight="14595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7610" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7702" uniqueCount="1040">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -4822,10 +4822,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ナマズ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>12:00</t>
   </si>
   <si>
@@ -4833,10 +4829,6 @@
     <rPh sb="0" eb="2">
       <t>マンネン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>13:26</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4889,67 +4881,103 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>11:00</t>
+    <t>17:40</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>白樺林</t>
+    <t>孤村 / 鬼都</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>風之平原</t>
+    <t>20:15</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>14:53</t>
+    <t>黑森林 / 孤村</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>14:5</t>
-    </r>
+    <t>黒影林 / 孤独の村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>00:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>02:59</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07:01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>土門客棧 / 灰狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑森林 / 雪原</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡門旅館 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">孤独の村 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 北方警戒所</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>20:51</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>23:53</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>鬼蛮</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>4</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>16:30前</t>
-    <rPh sb="5" eb="6">
-      <t>マエ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>16:27</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>17:40</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>孤村 / 鬼都</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>孤独の村</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
+      <t>黒獣</t>
     </r>
     <r>
       <rPr>
@@ -4958,15 +4986,62 @@
         <family val="2"/>
         <charset val="136"/>
       </rPr>
-      <t>悪鬼都市</t>
+      <t>神</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>18:06前</t>
-    <rPh sb="5" eb="6">
-      <t>マエ</t>
+    <t>黒獣神</t>
+  </si>
+  <si>
+    <t>ナマズ王</t>
+    <rPh sb="3" eb="4">
+      <t>オウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>黒獣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>神</t>
+    </r>
+  </si>
+  <si>
+    <t>孤独の村 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>08:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>09:50</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:23</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>09:59</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:07</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -4977,7 +5052,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="\'hh:mm"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5065,6 +5140,18 @@
       <sz val="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -5188,7 +5275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5605,11 +5692,27 @@
     <xf numFmtId="176" fontId="12" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5740,13 +5843,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8070,13 +8166,13 @@
         <v>993</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="G60" s="28" t="s">
         <v>989</v>
       </c>
       <c r="H60" s="28" t="s">
-        <v>996</v>
+        <v>1032</v>
       </c>
       <c r="I60" s="29" t="s">
         <v>543</v>
@@ -8116,11 +8212,11 @@
       <c r="F61" s="29"/>
       <c r="G61" s="28"/>
       <c r="H61" s="28"/>
-      <c r="I61" s="139" t="s">
-        <v>1007</v>
+      <c r="I61" s="29" t="s">
+        <v>217</v>
       </c>
       <c r="J61" s="28" t="s">
-        <v>1008</v>
+        <v>13</v>
       </c>
       <c r="K61" s="28"/>
       <c r="L61" s="130" t="s">
@@ -8149,19 +8245,23 @@
       <c r="C62" s="28"/>
       <c r="D62" s="28"/>
       <c r="E62" s="28"/>
-      <c r="F62" s="29"/>
-      <c r="G62" s="28"/>
+      <c r="F62" s="29" t="s">
+        <v>996</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>27</v>
+      </c>
       <c r="H62" s="28" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="I62" s="29" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J62" s="28" t="s">
-        <v>1009</v>
+        <v>4</v>
       </c>
       <c r="K62" s="28" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="L62" s="130" t="s">
         <v>22</v>
@@ -8172,7 +8272,7 @@
       </c>
       <c r="O62" s="67" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>12:00</v>
       </c>
       <c r="P62" s="67" t="str">
         <f t="shared" si="2"/>
@@ -8189,17 +8289,23 @@
       <c r="C63" s="29"/>
       <c r="D63" s="28"/>
       <c r="E63" s="28"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="28"/>
+      <c r="F63" s="29" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="28" t="s">
+        <v>1033</v>
+      </c>
       <c r="I63" s="29" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="J63" s="28" t="s">
         <v>4</v>
       </c>
       <c r="K63" s="28" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="L63" s="130" t="s">
         <v>21</v>
@@ -8210,7 +8316,7 @@
       </c>
       <c r="O63" s="67" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>13:27</v>
       </c>
       <c r="P63" s="67" t="str">
         <f t="shared" si="2"/>
@@ -8225,27 +8331,29 @@
         <v>55</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D64" s="28"/>
       <c r="E64" s="28" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F64" s="29" t="s">
+        <v>959</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H64" s="28" t="s">
         <v>1002</v>
       </c>
-      <c r="F64" s="29" t="s">
-        <v>1010</v>
-      </c>
-      <c r="G64" s="29"/>
-      <c r="H64" s="28" t="s">
-        <v>1004</v>
-      </c>
       <c r="I64" s="29" t="s">
-        <v>1011</v>
+        <v>959</v>
       </c>
       <c r="J64" s="28" t="s">
         <v>4</v>
       </c>
       <c r="K64" s="28" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="L64" s="130" t="s">
         <v>20</v>
@@ -8256,7 +8364,7 @@
       </c>
       <c r="O64" s="67" t="str">
         <f t="shared" si="1"/>
-        <v>14:53</v>
+        <v>14:54</v>
       </c>
       <c r="P64" s="67" t="str">
         <f t="shared" si="2"/>
@@ -8305,17 +8413,21 @@
       <c r="C66" s="29"/>
       <c r="D66" s="28"/>
       <c r="E66" s="28"/>
-      <c r="F66" s="139" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G66" s="28"/>
+      <c r="F66" s="29" t="s">
+        <v>594</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>27</v>
+      </c>
       <c r="H66" s="28" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="I66" s="29" t="s">
-        <v>1013</v>
-      </c>
-      <c r="J66" s="28"/>
+        <v>594</v>
+      </c>
+      <c r="J66" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="K66" s="28" t="s">
         <v>995</v>
       </c>
@@ -8328,11 +8440,11 @@
       </c>
       <c r="O66" s="67" t="str">
         <f t="shared" si="1"/>
-        <v>16:30前</v>
+        <v>16:24</v>
       </c>
       <c r="P66" s="67" t="str">
         <f t="shared" si="2"/>
-        <v>16:27</v>
+        <v>16:24</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="18" customHeight="1">
@@ -8343,20 +8455,32 @@
         <v>55</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F67" s="29"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
+        <v>1034</v>
+      </c>
+      <c r="F67" s="29" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G67" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H67" s="28" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I67" s="30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="J67" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K67" s="28" t="s">
+        <v>1003</v>
+      </c>
       <c r="L67" s="130" t="s">
         <v>15</v>
       </c>
@@ -8366,11 +8490,11 @@
       </c>
       <c r="O67" s="67" t="str">
         <f t="shared" ref="O67:O130" si="4">IF($F67&lt;&gt;"",TEXT($F67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:50</v>
       </c>
       <c r="P67" s="67" t="str">
         <f t="shared" ref="P67:P130" si="5">IF($I67&lt;&gt;"",TEXT($I67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:55</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="18" customHeight="1">
@@ -8386,14 +8510,10 @@
       <c r="F68" s="29"/>
       <c r="G68" s="28"/>
       <c r="H68" s="28"/>
-      <c r="I68" s="139" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J68" s="28" t="s">
-        <v>4</v>
-      </c>
+      <c r="I68" s="29"/>
+      <c r="J68" s="28"/>
       <c r="K68" s="28" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="L68" s="130" t="s">
         <v>12</v>
@@ -8408,7 +8528,7 @@
       </c>
       <c r="P68" s="67" t="str">
         <f t="shared" si="5"/>
-        <v>18:06前</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="1:16" ht="18" customHeight="1">
@@ -8421,12 +8541,24 @@
       <c r="C69" s="29"/>
       <c r="D69" s="28"/>
       <c r="E69" s="28"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
+      <c r="F69" s="29" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I69" s="29" t="s">
+        <v>960</v>
+      </c>
+      <c r="J69" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="K69" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="L69" s="130" t="s">
         <v>10</v>
       </c>
@@ -8436,11 +8568,11 @@
       </c>
       <c r="O69" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>19:18</v>
       </c>
       <c r="P69" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>19:28</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1">
@@ -8450,29 +8582,47 @@
       <c r="B70" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="29"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
+      <c r="C70" s="29" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D70" s="28" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F70" s="29" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="28" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I70" s="30" t="s">
+        <v>1025</v>
+      </c>
+      <c r="J70" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="K70" s="28" t="s">
+        <v>995</v>
+      </c>
       <c r="L70" s="130" t="s">
         <v>9</v>
       </c>
       <c r="N70" s="67" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>20:15</v>
       </c>
       <c r="O70" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20:51</v>
       </c>
       <c r="P70" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:55</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="18" customHeight="1">
@@ -8517,12 +8667,24 @@
       <c r="C72" s="29"/>
       <c r="D72" s="28"/>
       <c r="E72" s="28"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="29"/>
-      <c r="J72" s="28"/>
-      <c r="K72" s="28"/>
+      <c r="F72" s="29" t="s">
+        <v>791</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H72" s="28" t="s">
+        <v>997</v>
+      </c>
+      <c r="I72" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="J72" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="28" t="s">
+        <v>1003</v>
+      </c>
       <c r="L72" s="130" t="s">
         <v>5</v>
       </c>
@@ -8532,11 +8694,11 @@
       </c>
       <c r="O72" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>22:24</v>
       </c>
       <c r="P72" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>22:28</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -8549,12 +8711,24 @@
       <c r="C73" s="33"/>
       <c r="D73" s="32"/>
       <c r="E73" s="32"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
+      <c r="F73" s="33" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G73" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="H73" s="32" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I73" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="J73" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="K73" s="32" t="s">
+        <v>1003</v>
+      </c>
       <c r="L73" s="131" t="s">
         <v>3</v>
       </c>
@@ -8564,11 +8738,11 @@
       </c>
       <c r="O73" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23:53</v>
       </c>
       <c r="P73" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:56</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="18" customHeight="1">
@@ -8578,9 +8752,15 @@
       <c r="B74" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C74" s="36"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
+      <c r="C74" s="36" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D74" s="35" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E74" s="35" t="s">
+        <v>1016</v>
+      </c>
       <c r="F74" s="36"/>
       <c r="G74" s="35"/>
       <c r="H74" s="35"/>
@@ -8592,7 +8772,7 @@
       </c>
       <c r="N74" s="67" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="O74" s="67" t="str">
         <f t="shared" si="4"/>
@@ -8613,12 +8793,24 @@
       <c r="C75" s="38"/>
       <c r="D75" s="37"/>
       <c r="E75" s="37"/>
-      <c r="F75" s="38"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
+      <c r="F75" s="38" t="s">
+        <v>917</v>
+      </c>
+      <c r="G75" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="37" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I75" s="38" t="s">
+        <v>623</v>
+      </c>
+      <c r="J75" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K75" s="37" t="s">
+        <v>1003</v>
+      </c>
       <c r="L75" s="132" t="s">
         <v>36</v>
       </c>
@@ -8628,11 +8820,11 @@
       </c>
       <c r="O75" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>01:04</v>
       </c>
       <c r="P75" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:01</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="18" customHeight="1">
@@ -8642,29 +8834,47 @@
       <c r="B76" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C76" s="38"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="38"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
+      <c r="C76" s="38" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D76" s="37" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E76" s="37" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F76" s="38" t="s">
+        <v>297</v>
+      </c>
+      <c r="G76" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H76" s="37" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I76" s="39" t="s">
+        <v>806</v>
+      </c>
+      <c r="J76" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K76" s="37" t="s">
+        <v>995</v>
+      </c>
       <c r="L76" s="132" t="s">
         <v>35</v>
       </c>
       <c r="N76" s="67" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>02:59</v>
       </c>
       <c r="O76" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>02:30</v>
       </c>
       <c r="P76" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:29</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="18" customHeight="1">
@@ -8680,9 +8890,15 @@
       <c r="F77" s="38"/>
       <c r="G77" s="37"/>
       <c r="H77" s="37"/>
-      <c r="I77" s="38"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
+      <c r="I77" s="38" t="s">
+        <v>1027</v>
+      </c>
+      <c r="J77" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" s="37" t="s">
+        <v>995</v>
+      </c>
       <c r="L77" s="132" t="s">
         <v>33</v>
       </c>
@@ -8696,7 +8912,7 @@
       </c>
       <c r="P77" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>03:57</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1">
@@ -8709,9 +8925,15 @@
       <c r="C78" s="38"/>
       <c r="D78" s="37"/>
       <c r="E78" s="37"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
+      <c r="F78" s="38" t="s">
+        <v>951</v>
+      </c>
+      <c r="G78" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H78" s="37" t="s">
+        <v>1029</v>
+      </c>
       <c r="I78" s="38"/>
       <c r="J78" s="37"/>
       <c r="K78" s="37"/>
@@ -8724,7 +8946,7 @@
       </c>
       <c r="O78" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:04</v>
       </c>
       <c r="P78" s="67" t="str">
         <f t="shared" si="5"/>
@@ -8741,12 +8963,22 @@
       <c r="C79" s="38"/>
       <c r="D79" s="37"/>
       <c r="E79" s="37"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="37"/>
+      <c r="F79" s="38" t="s">
+        <v>826</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>17</v>
+      </c>
       <c r="H79" s="37"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="37"/>
-      <c r="K79" s="37"/>
+      <c r="I79" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="J79" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K79" s="37" t="s">
+        <v>1003</v>
+      </c>
       <c r="L79" s="132" t="s">
         <v>31</v>
       </c>
@@ -8756,11 +8988,11 @@
       </c>
       <c r="O79" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:32</v>
       </c>
       <c r="P79" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:28</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1">
@@ -8773,12 +9005,24 @@
       <c r="C80" s="38"/>
       <c r="D80" s="37"/>
       <c r="E80" s="37"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="37"/>
-      <c r="K80" s="37"/>
+      <c r="F80" s="38" t="s">
+        <v>851</v>
+      </c>
+      <c r="G80" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H80" s="37" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I80" s="39" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J80" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K80" s="37" t="s">
+        <v>995</v>
+      </c>
       <c r="L80" s="132" t="s">
         <v>30</v>
       </c>
@@ -8788,11 +9032,11 @@
       </c>
       <c r="O80" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>06:59</v>
       </c>
       <c r="P80" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>06:54</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="18" customHeight="1">
@@ -8802,9 +9046,15 @@
       <c r="B81" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C81" s="38"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
+      <c r="C81" s="38" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D81" s="37" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E81" s="37" t="s">
+        <v>1018</v>
+      </c>
       <c r="F81" s="38"/>
       <c r="G81" s="37"/>
       <c r="H81" s="37"/>
@@ -8816,7 +9066,7 @@
       </c>
       <c r="N81" s="67" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>07:01</v>
       </c>
       <c r="O81" s="67" t="str">
         <f t="shared" si="4"/>
@@ -8840,9 +9090,15 @@
       <c r="F82" s="38"/>
       <c r="G82" s="37"/>
       <c r="H82" s="37"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="37"/>
-      <c r="K82" s="37"/>
+      <c r="I82" s="38" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J82" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="K82" s="37" t="s">
+        <v>995</v>
+      </c>
       <c r="L82" s="132" t="s">
         <v>28</v>
       </c>
@@ -8856,7 +9112,7 @@
       </c>
       <c r="P82" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:25</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="18" customHeight="1">
@@ -8869,12 +9125,24 @@
       <c r="C83" s="37"/>
       <c r="D83" s="37"/>
       <c r="E83" s="37"/>
-      <c r="F83" s="38"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="39"/>
-      <c r="J83" s="37"/>
-      <c r="K83" s="37"/>
+      <c r="F83" s="38" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G83" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H83" s="37" t="s">
+        <v>997</v>
+      </c>
+      <c r="I83" s="39" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J83" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="37" t="s">
+        <v>1003</v>
+      </c>
       <c r="L83" s="132" t="s">
         <v>26</v>
       </c>
@@ -8884,11 +9152,11 @@
       </c>
       <c r="O83" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>09:59</v>
       </c>
       <c r="P83" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>09:50</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1">
@@ -8936,9 +9204,15 @@
       <c r="F85" s="38"/>
       <c r="G85" s="37"/>
       <c r="H85" s="37"/>
-      <c r="I85" s="38"/>
-      <c r="J85" s="37"/>
-      <c r="K85" s="37"/>
+      <c r="I85" s="38" t="s">
+        <v>1037</v>
+      </c>
+      <c r="J85" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="K85" s="37" t="s">
+        <v>1003</v>
+      </c>
       <c r="L85" s="132" t="s">
         <v>23</v>
       </c>
@@ -8952,7 +9226,7 @@
       </c>
       <c r="P85" s="67" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>11:23</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1">
@@ -8997,9 +9271,15 @@
       <c r="C87" s="37"/>
       <c r="D87" s="37"/>
       <c r="E87" s="37"/>
-      <c r="F87" s="38"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
+      <c r="F87" s="38" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G87" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="37" t="s">
+        <v>1031</v>
+      </c>
       <c r="I87" s="38"/>
       <c r="J87" s="37"/>
       <c r="K87" s="37"/>
@@ -9012,7 +9292,7 @@
       </c>
       <c r="O87" s="67" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13:07</v>
       </c>
       <c r="P87" s="67" t="str">
         <f t="shared" si="5"/>
@@ -11656,8 +11936,8 @@
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 H1:H1048576 K1:K1048576">
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="定期メンテナンス中">
+  <conditionalFormatting sqref="E1:E1048576 K1:K1048576 H1:H1048576">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16644,12 +16924,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="18" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17494,7 +17774,7 @@
         <v>528</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="5"/>
@@ -18123,8 +18403,8 @@
       <c r="E42" s="18" t="s">
         <v>551</v>
       </c>
-      <c r="F42" s="17" t="s">
-        <v>703</v>
+      <c r="F42" s="142" t="s">
+        <v>1030</v>
       </c>
       <c r="G42" s="19" t="s">
         <v>549</v>
@@ -18915,7 +19195,7 @@
       <c r="C64" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="140" t="s">
         <v>710</v>
       </c>
       <c r="E64" s="29" t="s">
@@ -20253,7 +20533,7 @@
       <c r="C102" s="47" t="s">
         <v>400</v>
       </c>
-      <c r="D102" s="46" t="s">
+      <c r="D102" s="141" t="s">
         <v>717</v>
       </c>
       <c r="E102" s="47" t="s">
@@ -22637,12 +22917,12 @@
   <autoFilter ref="A1:I169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27973,12 +28253,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33966,12 +34246,12 @@
   <autoFilter ref="A1:I169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40050,22 +40330,22 @@
   <autoFilter ref="A1:I169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46032,22 +46312,22 @@
   <autoFilter ref="A1:I169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53611,17 +53891,17 @@
   <autoFilter ref="A1:L169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394CD2A7-7B8A-4D93-9FCC-D90E57BA869E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FCEDBF-4B42-4085-8B06-1EB4B20CC7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25875" yWindow="16065" windowWidth="25980" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16635" yWindow="16380" windowWidth="18570" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10063" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10069" uniqueCount="1439">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6291,58 +6291,92 @@
     <t xml:space="preserve">黒影林 / 海岸旅館 </t>
   </si>
   <si>
+    <t>孤独の村 / 悪鬼都市</t>
+  </si>
+  <si>
+    <t>黒影林 / 孤独の村</t>
+  </si>
+  <si>
+    <t>孤独の村</t>
+  </si>
+  <si>
+    <t>孤独の村 / 染色工房</t>
+  </si>
+  <si>
+    <t>戒狼村 / 染色工房</t>
+  </si>
+  <si>
+    <t>海岸旅館  / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>戒狼村 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>悪鬼都市 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>染色工房 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巨岩の海岸 / 海岸旅館 </t>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 戒狼村</t>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 悪鬼都市</t>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 渡門旅館</t>
+  </si>
+  <si>
+    <t>武運村 / 戒狼村</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武運村 / 海岸旅館 </t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 北方警戒崗哨</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>18:06</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩海岸 / 豬豬農場</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>21:04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豬豬農場 / 染坊</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t xml:space="preserve">戒狼村 / 海岸旅館 </t>
-  </si>
-  <si>
-    <t>孤独の村 / 悪鬼都市</t>
-  </si>
-  <si>
-    <t>黒影林 / 孤独の村</t>
-  </si>
-  <si>
-    <t>孤独の村</t>
-  </si>
-  <si>
-    <t>孤独の村 / 染色工房</t>
-  </si>
-  <si>
-    <t>戒狼村 / 染色工房</t>
-  </si>
-  <si>
-    <t>海岸旅館  / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t>戒狼村 / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t>悪鬼都市 / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t>染色工房 / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t>巨岩の海岸 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">巨岩の海岸 / 海岸旅館 </t>
-  </si>
-  <si>
-    <t>巨岩の海岸 / 戒狼村</t>
-  </si>
-  <si>
-    <t>巨岩の海岸 / 悪鬼都市</t>
-  </si>
-  <si>
-    <t>巨岩の海岸 / 渡門旅館</t>
-  </si>
-  <si>
-    <t>武運村 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>武運村 / 染色工房</t>
-  </si>
-  <si>
-    <t xml:space="preserve">武運村 / 海岸旅館 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海岸旅館 / 染色工房</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -6605,7 +6639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7475,67 +7509,14 @@
     <xf numFmtId="176" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <fill>
         <patternFill>
@@ -7554,20 +7535,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFA3A3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7665,6 +7632,69 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
@@ -7693,7 +7723,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF9999"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8120,7 +8150,7 @@
         <v>1360</v>
       </c>
       <c r="E3" s="149" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F3" s="150" t="s">
         <v>1277</v>
@@ -8246,7 +8276,7 @@
         <v>1361</v>
       </c>
       <c r="E6" s="149" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F6" s="150" t="s">
         <v>977</v>
@@ -8448,7 +8478,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F11" s="150" t="s">
         <v>275</v>
@@ -8612,7 +8642,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="149" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F15" s="150" t="s">
         <v>1075</v>
@@ -8782,7 +8812,7 @@
         <v>1363</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F19" s="150"/>
       <c r="G19" s="149"/>
@@ -8908,7 +8938,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F22" s="150"/>
       <c r="G22" s="149"/>
@@ -9072,7 +9102,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F26" s="159" t="s">
         <v>636</v>
@@ -9242,7 +9272,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>589</v>
@@ -9476,7 +9506,7 @@
         <v>48</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F36" s="162"/>
       <c r="G36" s="160"/>
@@ -9728,7 +9758,7 @@
         <v>1365</v>
       </c>
       <c r="E42" s="160" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F42" s="162"/>
       <c r="G42" s="160"/>
@@ -10566,7 +10596,7 @@
         <v>1367</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F62" s="172" t="s">
         <v>1306</v>
@@ -10862,7 +10892,7 @@
         <v>904</v>
       </c>
       <c r="E69" s="171" t="s">
-        <v>1413</v>
+        <v>1435</v>
       </c>
       <c r="F69" s="172" t="s">
         <v>1312</v>
@@ -11032,7 +11062,7 @@
         <v>1365</v>
       </c>
       <c r="E73" s="175" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F73" s="176"/>
       <c r="G73" s="175"/>
@@ -11158,7 +11188,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F76" s="181"/>
       <c r="G76" s="180"/>
@@ -11705,9 +11735,15 @@
       <c r="B92" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C92" s="181"/>
-      <c r="D92" s="180"/>
-      <c r="E92" s="180"/>
+      <c r="C92" s="291" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D92" s="180" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E92" s="180" t="s">
+        <v>1436</v>
+      </c>
       <c r="F92" s="181"/>
       <c r="G92" s="180"/>
       <c r="H92" s="180"/>
@@ -11719,7 +11755,7 @@
       </c>
       <c r="N92" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>18:06</v>
       </c>
       <c r="O92" s="143" t="str">
         <f t="shared" si="4"/>
@@ -11825,9 +11861,15 @@
       <c r="B95" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C95" s="181"/>
-      <c r="D95" s="180"/>
-      <c r="E95" s="180"/>
+      <c r="C95" s="181" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D95" s="180" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E95" s="180" t="s">
+        <v>1438</v>
+      </c>
       <c r="F95" s="181"/>
       <c r="G95" s="180"/>
       <c r="H95" s="180"/>
@@ -11839,7 +11881,7 @@
       </c>
       <c r="N95" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>21:04</v>
       </c>
       <c r="O95" s="143" t="str">
         <f t="shared" si="4"/>
@@ -11946,7 +11988,7 @@
         <v>1363</v>
       </c>
       <c r="E98" s="279" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F98" s="188"/>
       <c r="G98" s="187"/>
@@ -12075,10 +12117,10 @@
         <v>284</v>
       </c>
       <c r="D101" s="189" t="s">
-        <v>1360</v>
+        <v>1429</v>
       </c>
       <c r="E101" s="189" t="s">
-        <v>1423</v>
+        <v>1434</v>
       </c>
       <c r="F101" s="190"/>
       <c r="G101" s="189"/>
@@ -12242,7 +12284,7 @@
         <v>1367</v>
       </c>
       <c r="E105" s="189" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F105" s="190"/>
       <c r="G105" s="189"/>
@@ -12406,7 +12448,7 @@
         <v>1367</v>
       </c>
       <c r="E109" s="189" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F109" s="190" t="s">
         <v>919</v>
@@ -12532,7 +12574,7 @@
         <v>1361</v>
       </c>
       <c r="E112" s="189" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F112" s="190" t="s">
         <v>838</v>
@@ -12696,7 +12738,7 @@
         <v>1139</v>
       </c>
       <c r="E116" s="189" t="s">
-        <v>1429</v>
+        <v>1437</v>
       </c>
       <c r="F116" s="190" t="s">
         <v>1331</v>
@@ -12822,7 +12864,7 @@
         <v>48</v>
       </c>
       <c r="E119" s="189" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F119" s="190" t="s">
         <v>1333</v>
@@ -12948,7 +12990,7 @@
         <v>1231</v>
       </c>
       <c r="E122" s="196" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F122" s="197" t="s">
         <v>141</v>
@@ -13118,7 +13160,7 @@
         <v>1363</v>
       </c>
       <c r="E126" s="198" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F126" s="199" t="s">
         <v>886</v>
@@ -13370,7 +13412,7 @@
         <v>1369</v>
       </c>
       <c r="E132" s="198" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F132" s="199" t="s">
         <v>1340</v>
@@ -13496,7 +13538,7 @@
         <v>1370</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>1341</v>
@@ -13710,7 +13752,7 @@
         <v>42</v>
       </c>
       <c r="E140" s="198" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F140" s="199"/>
       <c r="G140" s="198"/>
@@ -14038,7 +14080,7 @@
         <v>48</v>
       </c>
       <c r="E148" s="208" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F148" s="209" t="s">
         <v>1349</v>
@@ -14328,7 +14370,7 @@
         <v>1365</v>
       </c>
       <c r="E155" s="208" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F155" s="209" t="s">
         <v>1352</v>
@@ -14454,7 +14496,7 @@
         <v>1363</v>
       </c>
       <c r="E158" s="208" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F158" s="209" t="s">
         <v>1354</v>
@@ -14580,7 +14622,7 @@
         <v>1370</v>
       </c>
       <c r="E161" s="208" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F161" s="209" t="s">
         <v>665</v>
@@ -14744,7 +14786,7 @@
         <v>1371</v>
       </c>
       <c r="E165" s="208" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="F165" s="209"/>
       <c r="G165" s="208"/>
@@ -14864,7 +14906,7 @@
         <v>45</v>
       </c>
       <c r="E168" s="208" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F168" s="209"/>
       <c r="G168" s="208"/>
@@ -14942,43 +14984,43 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="32" priority="7" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K101:K1048576 K54:K99">
-    <cfRule type="containsText" dxfId="29" priority="8" operator="containsText" text="定期メンテナンス中">
-      <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="28" priority="9" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="30" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="25" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
+    <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="定期メンテナンス中">
+      <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K100">
+    <cfRule type="containsText" dxfId="25" priority="9" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20915,34 +20957,29 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C1:C59 E1:E59 G1:G59 G61:G1048576 C61:C1048576 E61:E1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="'">
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D104 F1:F1048576 D106:D1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="例行維護中">
+  <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
+    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G60">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",G60)))</formula>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="'">
+      <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E60">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",E60)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C60">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",C60)))</formula>
+  <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="'">
+      <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26956,18 +26993,18 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="E1:E1048576 C1:C1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="33" priority="2" operator="containsText" text="'">
+  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="32" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32957,12 +32994,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -38853,12 +38890,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44846,12 +44883,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50930,22 +50967,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="19" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56912,22 +56949,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="15" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="14" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -64490,17 +64527,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FCEDBF-4B42-4085-8B06-1EB4B20CC7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DEE665-F484-4E7A-ABBA-5BF2931D8253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16635" yWindow="16380" windowWidth="18570" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18480" yWindow="16455" windowWidth="18450" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10069" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10099" uniqueCount="1452">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6225,10 +6225,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>万霊キョンシー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ナマズ王</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6376,6 +6372,62 @@
   </si>
   <si>
     <t>海岸旅館 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:19_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:38_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07:45</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>01:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05:49</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>04:25_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07:23_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:48_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:49</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">灰狼村 / </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戒狼村 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">戒狼村 / </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12:07</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6639,7 +6691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7464,18 +7516,6 @@
     <xf numFmtId="176" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7507,9 +7547,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8059,38 +8096,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="142" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="276" t="s">
+      <c r="A1" s="145"/>
+      <c r="B1" s="146" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="276" t="s">
+      <c r="C1" s="146" t="s">
         <v>92</v>
       </c>
       <c r="D1" s="146" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="276" t="s">
+      <c r="E1" s="146" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="276" t="s">
+      <c r="F1" s="146" t="s">
         <v>140</v>
       </c>
       <c r="G1" s="146" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="276" t="s">
+      <c r="H1" s="146" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="276" t="s">
+      <c r="I1" s="146" t="s">
         <v>68</v>
       </c>
       <c r="J1" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="276" t="s">
+      <c r="K1" s="146" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="3"/>
+      <c r="L1" s="145"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
       <c r="A2" s="148" t="s">
@@ -8150,7 +8187,7 @@
         <v>1360</v>
       </c>
       <c r="E3" s="149" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F3" s="150" t="s">
         <v>1277</v>
@@ -8165,7 +8202,7 @@
         <v>1041</v>
       </c>
       <c r="J3" s="149" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="K3" s="149" t="s">
         <v>1015</v>
@@ -8276,7 +8313,7 @@
         <v>1361</v>
       </c>
       <c r="E6" s="149" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F6" s="150" t="s">
         <v>977</v>
@@ -8408,7 +8445,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="149" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L9" s="148" t="s">
         <v>29</v>
@@ -8478,7 +8515,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="F11" s="150" t="s">
         <v>275</v>
@@ -8569,10 +8606,10 @@
         <v>1283</v>
       </c>
       <c r="J13" s="149" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K13" s="149" t="s">
         <v>1408</v>
-      </c>
-      <c r="K13" s="149" t="s">
-        <v>1409</v>
       </c>
       <c r="L13" s="148" t="s">
         <v>23</v>
@@ -8642,7 +8679,7 @@
         <v>63</v>
       </c>
       <c r="E15" s="149" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F15" s="150" t="s">
         <v>1075</v>
@@ -8812,7 +8849,7 @@
         <v>1363</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F19" s="150"/>
       <c r="G19" s="149"/>
@@ -8906,7 +8943,7 @@
         <v>13</v>
       </c>
       <c r="K21" s="149" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L21" s="148" t="s">
         <v>10</v>
@@ -8938,7 +8975,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F22" s="150"/>
       <c r="G22" s="149"/>
@@ -8950,7 +8987,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="149" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L22" s="148" t="s">
         <v>9</v>
@@ -9032,7 +9069,7 @@
         <v>13</v>
       </c>
       <c r="K24" s="149" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L24" s="148" t="s">
         <v>5</v>
@@ -9102,7 +9139,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F26" s="159" t="s">
         <v>636</v>
@@ -9158,7 +9195,7 @@
         <v>13</v>
       </c>
       <c r="K27" s="160" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L27" s="157" t="s">
         <v>36</v>
@@ -9272,7 +9309,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>589</v>
@@ -9474,7 +9511,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="160" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L35" s="157" t="s">
         <v>26</v>
@@ -9506,7 +9543,7 @@
         <v>48</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F36" s="162"/>
       <c r="G36" s="160"/>
@@ -9632,7 +9669,7 @@
         <v>41</v>
       </c>
       <c r="E39" s="160" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F39" s="162"/>
       <c r="G39" s="160"/>
@@ -9682,7 +9719,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="160" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L40" s="157" t="s">
         <v>20</v>
@@ -9758,7 +9795,7 @@
         <v>1365</v>
       </c>
       <c r="E42" s="160" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F42" s="162"/>
       <c r="G42" s="160"/>
@@ -9852,7 +9889,7 @@
         <v>13</v>
       </c>
       <c r="K44" s="160" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L44" s="157" t="s">
         <v>12</v>
@@ -9928,7 +9965,7 @@
         <v>13</v>
       </c>
       <c r="K46" s="160" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L46" s="157" t="s">
         <v>9</v>
@@ -10004,7 +10041,7 @@
         <v>902</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="F48" s="162" t="s">
         <v>1303</v>
@@ -10098,7 +10135,7 @@
         <v>13</v>
       </c>
       <c r="K50" s="169" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L50" s="168" t="s">
         <v>37</v>
@@ -10142,7 +10179,7 @@
         <v>13</v>
       </c>
       <c r="K51" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L51" s="168" t="s">
         <v>36</v>
@@ -10218,7 +10255,7 @@
         <v>13</v>
       </c>
       <c r="K53" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L53" s="168" t="s">
         <v>33</v>
@@ -10555,7 +10592,7 @@
         <v>27</v>
       </c>
       <c r="H61" s="171" t="s">
-        <v>1401</v>
+        <v>940</v>
       </c>
       <c r="I61" s="172" t="s">
         <v>217</v>
@@ -10596,7 +10633,7 @@
         <v>1367</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F62" s="172" t="s">
         <v>1306</v>
@@ -10614,7 +10651,7 @@
         <v>13</v>
       </c>
       <c r="K62" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L62" s="168" t="s">
         <v>22</v>
@@ -10658,7 +10695,7 @@
         <v>13</v>
       </c>
       <c r="K63" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L63" s="168" t="s">
         <v>21</v>
@@ -10725,7 +10762,7 @@
         <v>1395</v>
       </c>
       <c r="H65" s="171" t="s">
-        <v>1401</v>
+        <v>940</v>
       </c>
       <c r="I65" s="173" t="s">
         <v>1033</v>
@@ -10734,7 +10771,7 @@
         <v>13</v>
       </c>
       <c r="K65" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L65" s="168" t="s">
         <v>18</v>
@@ -10860,7 +10897,7 @@
         <v>13</v>
       </c>
       <c r="K68" s="171" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L68" s="168" t="s">
         <v>12</v>
@@ -10892,7 +10929,7 @@
         <v>904</v>
       </c>
       <c r="E69" s="171" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F69" s="172" t="s">
         <v>1312</v>
@@ -10901,7 +10938,7 @@
         <v>1398</v>
       </c>
       <c r="H69" s="171" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="I69" s="172" t="s">
         <v>1313</v>
@@ -11062,7 +11099,7 @@
         <v>1365</v>
       </c>
       <c r="E73" s="175" t="s">
-        <v>1419</v>
+        <v>1449</v>
       </c>
       <c r="F73" s="176"/>
       <c r="G73" s="175"/>
@@ -11112,7 +11149,7 @@
         <v>13</v>
       </c>
       <c r="K74" s="178" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L74" s="177" t="s">
         <v>37</v>
@@ -11141,10 +11178,10 @@
       <c r="D75" s="180"/>
       <c r="E75" s="180"/>
       <c r="F75" s="181" t="s">
-        <v>1317</v>
+        <v>1442</v>
       </c>
       <c r="G75" s="180" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H75" s="180" t="s">
         <v>1018</v>
@@ -11167,7 +11204,7 @@
       </c>
       <c r="O75" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>01:30_?</v>
+        <v>01:25</v>
       </c>
       <c r="P75" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11188,7 +11225,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F76" s="181"/>
       <c r="G76" s="180"/>
@@ -11254,9 +11291,15 @@
       <c r="C78" s="181"/>
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
-      <c r="F78" s="181"/>
-      <c r="G78" s="180"/>
-      <c r="H78" s="180"/>
+      <c r="F78" s="181" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G78" s="180" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="180" t="s">
+        <v>1016</v>
+      </c>
       <c r="I78" s="181"/>
       <c r="J78" s="180"/>
       <c r="K78" s="180"/>
@@ -11269,7 +11312,7 @@
       </c>
       <c r="O78" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:25_?</v>
       </c>
       <c r="P78" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11286,9 +11329,15 @@
       <c r="C79" s="181"/>
       <c r="D79" s="180"/>
       <c r="E79" s="180"/>
-      <c r="F79" s="181"/>
-      <c r="G79" s="180"/>
-      <c r="H79" s="180"/>
+      <c r="F79" s="181" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G79" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="180" t="s">
+        <v>1017</v>
+      </c>
       <c r="I79" s="181"/>
       <c r="J79" s="180"/>
       <c r="K79" s="180"/>
@@ -11301,7 +11350,7 @@
       </c>
       <c r="O79" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:49</v>
       </c>
       <c r="P79" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11321,9 +11370,15 @@
       <c r="F80" s="181"/>
       <c r="G80" s="180"/>
       <c r="H80" s="180"/>
-      <c r="I80" s="182"/>
-      <c r="J80" s="180"/>
-      <c r="K80" s="180"/>
+      <c r="I80" s="182" t="s">
+        <v>1441</v>
+      </c>
+      <c r="J80" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K80" s="180" t="s">
+        <v>1408</v>
+      </c>
       <c r="L80" s="177" t="s">
         <v>30</v>
       </c>
@@ -11337,7 +11392,7 @@
       </c>
       <c r="P80" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>06:11</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="18" customHeight="1">
@@ -11349,13 +11404,25 @@
       </c>
       <c r="C81" s="181"/>
       <c r="D81" s="180"/>
-      <c r="E81" s="278"/>
-      <c r="F81" s="181"/>
-      <c r="G81" s="180"/>
-      <c r="H81" s="180"/>
-      <c r="I81" s="181"/>
-      <c r="J81" s="180"/>
-      <c r="K81" s="180"/>
+      <c r="E81" s="180"/>
+      <c r="F81" s="181" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G81" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="180" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I81" s="181" t="s">
+        <v>1440</v>
+      </c>
+      <c r="J81" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K81" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L81" s="177" t="s">
         <v>29</v>
       </c>
@@ -11365,11 +11432,11 @@
       </c>
       <c r="O81" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:23_?</v>
       </c>
       <c r="P81" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:45</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="18" customHeight="1">
@@ -11458,12 +11525,24 @@
       <c r="C84" s="180"/>
       <c r="D84" s="180"/>
       <c r="E84" s="180"/>
-      <c r="F84" s="181"/>
-      <c r="G84" s="180"/>
-      <c r="H84" s="180"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="180"/>
-      <c r="K84" s="180"/>
+      <c r="F84" s="181" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G84" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="H84" s="180" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I84" s="181" t="s">
+        <v>1439</v>
+      </c>
+      <c r="J84" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K84" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
       </c>
@@ -11473,11 +11552,11 @@
       </c>
       <c r="O84" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10:19_?</v>
       </c>
       <c r="P84" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>10:38_?</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1">
@@ -11487,12 +11566,24 @@
       <c r="B85" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="181"/>
-      <c r="D85" s="180"/>
-      <c r="E85" s="180"/>
-      <c r="F85" s="181"/>
-      <c r="G85" s="180"/>
-      <c r="H85" s="180"/>
+      <c r="C85" s="181" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D85" s="180" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E85" s="180" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F85" s="181" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G85" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="180" t="s">
+        <v>1017</v>
+      </c>
       <c r="I85" s="181"/>
       <c r="J85" s="180"/>
       <c r="K85" s="180"/>
@@ -11501,11 +11592,11 @@
       </c>
       <c r="N85" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11:49</v>
       </c>
       <c r="O85" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>11:48_?</v>
       </c>
       <c r="P85" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11525,9 +11616,15 @@
       <c r="F86" s="181"/>
       <c r="G86" s="180"/>
       <c r="H86" s="180"/>
-      <c r="I86" s="182"/>
-      <c r="J86" s="180"/>
-      <c r="K86" s="180"/>
+      <c r="I86" s="182" t="s">
+        <v>1451</v>
+      </c>
+      <c r="J86" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K86" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L86" s="177" t="s">
         <v>22</v>
       </c>
@@ -11541,7 +11638,7 @@
       </c>
       <c r="P86" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>12:07</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="18" customHeight="1">
@@ -11666,7 +11763,7 @@
         <v>13</v>
       </c>
       <c r="K90" s="180" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L90" s="177" t="s">
         <v>16</v>
@@ -11710,7 +11807,7 @@
         <v>13</v>
       </c>
       <c r="K91" s="180" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L91" s="177" t="s">
         <v>15</v>
@@ -11735,14 +11832,14 @@
       <c r="B92" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C92" s="291" t="s">
+      <c r="C92" s="181" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D92" s="180" t="s">
         <v>1430</v>
       </c>
-      <c r="D92" s="180" t="s">
-        <v>1431</v>
-      </c>
       <c r="E92" s="180" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="180"/>
@@ -11792,7 +11889,7 @@
         <v>13</v>
       </c>
       <c r="K93" s="180" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L93" s="177" t="s">
         <v>10</v>
@@ -11862,13 +11959,13 @@
         <v>52</v>
       </c>
       <c r="C95" s="181" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D95" s="180" t="s">
         <v>1432</v>
       </c>
-      <c r="D95" s="180" t="s">
-        <v>1433</v>
-      </c>
       <c r="E95" s="180" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F95" s="181"/>
       <c r="G95" s="180"/>
@@ -11918,7 +12015,7 @@
         <v>13</v>
       </c>
       <c r="K96" s="180" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L96" s="177" t="s">
         <v>5</v>
@@ -11987,8 +12084,8 @@
       <c r="D98" s="187" t="s">
         <v>1363</v>
       </c>
-      <c r="E98" s="279" t="s">
-        <v>1427</v>
+      <c r="E98" s="187" t="s">
+        <v>1426</v>
       </c>
       <c r="F98" s="188"/>
       <c r="G98" s="187"/>
@@ -12117,10 +12214,10 @@
         <v>284</v>
       </c>
       <c r="D101" s="189" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E101" s="189" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F101" s="190"/>
       <c r="G101" s="189"/>
@@ -12284,7 +12381,7 @@
         <v>1367</v>
       </c>
       <c r="E105" s="189" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F105" s="190"/>
       <c r="G105" s="189"/>
@@ -12296,7 +12393,7 @@
         <v>13</v>
       </c>
       <c r="K105" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L105" s="186" t="s">
         <v>29</v>
@@ -12378,7 +12475,7 @@
         <v>13</v>
       </c>
       <c r="K107" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L107" s="186" t="s">
         <v>26</v>
@@ -12416,7 +12513,7 @@
         <v>13</v>
       </c>
       <c r="K108" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L108" s="186" t="s">
         <v>25</v>
@@ -12448,7 +12545,7 @@
         <v>1367</v>
       </c>
       <c r="E109" s="189" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F109" s="190" t="s">
         <v>919</v>
@@ -12504,7 +12601,7 @@
         <v>13</v>
       </c>
       <c r="K110" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L110" s="186" t="s">
         <v>22</v>
@@ -12567,14 +12664,14 @@
       <c r="B112" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C112" s="277" t="s">
+      <c r="C112" s="190" t="s">
         <v>608</v>
       </c>
       <c r="D112" s="189" t="s">
         <v>1361</v>
       </c>
       <c r="E112" s="189" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="F112" s="190" t="s">
         <v>838</v>
@@ -12693,7 +12790,7 @@
       <c r="B115" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C115" s="277"/>
+      <c r="C115" s="190"/>
       <c r="D115" s="189"/>
       <c r="E115" s="189"/>
       <c r="F115" s="190" t="s">
@@ -12738,7 +12835,7 @@
         <v>1139</v>
       </c>
       <c r="E116" s="189" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F116" s="190" t="s">
         <v>1331</v>
@@ -12756,7 +12853,7 @@
         <v>13</v>
       </c>
       <c r="K116" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L116" s="186" t="s">
         <v>12</v>
@@ -12864,7 +12961,7 @@
         <v>48</v>
       </c>
       <c r="E119" s="189" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F119" s="190" t="s">
         <v>1333</v>
@@ -12882,7 +12979,7 @@
         <v>13</v>
       </c>
       <c r="K119" s="189" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L119" s="186" t="s">
         <v>6</v>
@@ -12990,7 +13087,7 @@
         <v>1231</v>
       </c>
       <c r="E122" s="196" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F122" s="197" t="s">
         <v>141</v>
@@ -13160,7 +13257,7 @@
         <v>1363</v>
       </c>
       <c r="E126" s="198" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F126" s="199" t="s">
         <v>886</v>
@@ -13178,7 +13275,7 @@
         <v>13</v>
       </c>
       <c r="K126" s="198" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L126" s="195" t="s">
         <v>32</v>
@@ -13222,7 +13319,7 @@
         <v>13</v>
       </c>
       <c r="K127" s="198" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L127" s="195" t="s">
         <v>31</v>
@@ -13286,7 +13383,7 @@
         <v>34</v>
       </c>
       <c r="E129" s="198" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F129" s="199" t="s">
         <v>1119</v>
@@ -13304,7 +13401,7 @@
         <v>13</v>
       </c>
       <c r="K129" s="198" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L129" s="195" t="s">
         <v>29</v>
@@ -13348,7 +13445,7 @@
         <v>13</v>
       </c>
       <c r="K130" s="198" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L130" s="195" t="s">
         <v>28</v>
@@ -13412,7 +13509,7 @@
         <v>1369</v>
       </c>
       <c r="E132" s="198" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F132" s="199" t="s">
         <v>1340</v>
@@ -13538,7 +13635,7 @@
         <v>1370</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>1341</v>
@@ -13600,7 +13697,7 @@
         <v>13</v>
       </c>
       <c r="K136" s="198" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L136" s="195" t="s">
         <v>20</v>
@@ -13752,7 +13849,7 @@
         <v>42</v>
       </c>
       <c r="E140" s="198" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F140" s="199"/>
       <c r="G140" s="198"/>
@@ -13910,7 +14007,7 @@
         <v>34</v>
       </c>
       <c r="E144" s="198" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F144" s="199" t="s">
         <v>1322</v>
@@ -13972,7 +14069,7 @@
         <v>13</v>
       </c>
       <c r="K145" s="203" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L145" s="202" t="s">
         <v>3</v>
@@ -14048,7 +14145,7 @@
         <v>13</v>
       </c>
       <c r="K147" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L147" s="205" t="s">
         <v>36</v>
@@ -14080,7 +14177,7 @@
         <v>48</v>
       </c>
       <c r="E148" s="208" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F148" s="209" t="s">
         <v>1349</v>
@@ -14174,7 +14271,7 @@
         <v>13</v>
       </c>
       <c r="K150" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L150" s="205" t="s">
         <v>32</v>
@@ -14370,7 +14467,7 @@
         <v>1365</v>
       </c>
       <c r="E155" s="208" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F155" s="209" t="s">
         <v>1352</v>
@@ -14496,7 +14593,7 @@
         <v>1363</v>
       </c>
       <c r="E158" s="208" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="F158" s="209" t="s">
         <v>1354</v>
@@ -14590,7 +14687,7 @@
         <v>13</v>
       </c>
       <c r="K160" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L160" s="205" t="s">
         <v>20</v>
@@ -14622,7 +14719,7 @@
         <v>1370</v>
       </c>
       <c r="E161" s="208" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F161" s="209" t="s">
         <v>665</v>
@@ -14786,7 +14883,7 @@
         <v>1371</v>
       </c>
       <c r="E165" s="208" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F165" s="209"/>
       <c r="G165" s="208"/>
@@ -14836,7 +14933,7 @@
         <v>13</v>
       </c>
       <c r="K166" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L166" s="205" t="s">
         <v>9</v>
@@ -14906,7 +15003,7 @@
         <v>45</v>
       </c>
       <c r="E168" s="208" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="F168" s="209"/>
       <c r="G168" s="208"/>
@@ -14918,7 +15015,7 @@
         <v>13</v>
       </c>
       <c r="K168" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L168" s="205" t="s">
         <v>5</v>
@@ -14962,7 +15059,7 @@
         <v>13</v>
       </c>
       <c r="K169" s="208" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="L169" s="205" t="s">
         <v>3</v>
@@ -15008,7 +15105,7 @@
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
+  <conditionalFormatting sqref="K1 E1:E1048576 K54:K99 K101:K1048576 H1:H1048576">
     <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
@@ -15682,7 +15779,7 @@
       <c r="B19" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="281" t="s">
+      <c r="C19" s="277" t="s">
         <v>1373</v>
       </c>
       <c r="D19" s="149" t="s">
@@ -15929,7 +16026,7 @@
       <c r="B26" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="282" t="s">
+      <c r="C26" s="278" t="s">
         <v>530</v>
       </c>
       <c r="D26" s="158" t="s">
@@ -16044,7 +16141,7 @@
       <c r="F29" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="284" t="s">
+      <c r="G29" s="280" t="s">
         <v>1378</v>
       </c>
       <c r="H29" s="160" t="s">
@@ -16073,7 +16170,7 @@
       <c r="B30" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="283" t="s">
+      <c r="C30" s="279" t="s">
         <v>1374</v>
       </c>
       <c r="D30" s="160" t="s">
@@ -16151,7 +16248,7 @@
       <c r="F32" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="284" t="s">
+      <c r="G32" s="280" t="s">
         <v>1377</v>
       </c>
       <c r="H32" s="160" t="s">
@@ -16240,13 +16337,13 @@
       </c>
       <c r="C35" s="162"/>
       <c r="D35" s="160"/>
-      <c r="E35" s="283" t="s">
+      <c r="E35" s="279" t="s">
         <v>1376</v>
       </c>
       <c r="F35" s="160" t="s">
         <v>0</v>
       </c>
-      <c r="G35" s="284" t="s">
+      <c r="G35" s="280" t="s">
         <v>543</v>
       </c>
       <c r="H35" s="160" t="s">
@@ -16561,13 +16658,13 @@
       </c>
       <c r="C44" s="162"/>
       <c r="D44" s="160"/>
-      <c r="E44" s="283" t="s">
+      <c r="E44" s="279" t="s">
         <v>1380</v>
       </c>
       <c r="F44" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="G44" s="284" t="s">
+      <c r="G44" s="280" t="s">
         <v>1383</v>
       </c>
       <c r="H44" s="160" t="s">
@@ -16664,7 +16761,7 @@
       </c>
       <c r="C47" s="162"/>
       <c r="D47" s="160"/>
-      <c r="E47" s="283" t="s">
+      <c r="E47" s="279" t="s">
         <v>1382</v>
       </c>
       <c r="F47" s="160" t="s">
@@ -17209,7 +17306,7 @@
       <c r="B62" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C62" s="285" t="s">
+      <c r="C62" s="281" t="s">
         <v>1385</v>
       </c>
       <c r="D62" s="171" t="s">
@@ -17926,7 +18023,7 @@
       <c r="F83" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="G83" s="280" t="s">
+      <c r="G83" s="276" t="s">
         <v>1275</v>
       </c>
       <c r="H83" s="180" t="s">
@@ -18728,7 +18825,7 @@
       </c>
       <c r="C107" s="190"/>
       <c r="D107" s="189"/>
-      <c r="E107" s="286" t="s">
+      <c r="E107" s="282" t="s">
         <v>478</v>
       </c>
       <c r="F107" s="189" t="s">
@@ -18903,7 +19000,7 @@
       <c r="B112" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C112" s="286" t="s">
+      <c r="C112" s="282" t="s">
         <v>1386</v>
       </c>
       <c r="D112" s="189" t="s">
@@ -19043,7 +19140,7 @@
       <c r="B116" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C116" s="286" t="s">
+      <c r="C116" s="282" t="s">
         <v>1388</v>
       </c>
       <c r="D116" s="189" t="s">
@@ -19150,7 +19247,7 @@
       <c r="B119" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C119" s="286" t="s">
+      <c r="C119" s="282" t="s">
         <v>1390</v>
       </c>
       <c r="D119" s="189" t="s">
@@ -19508,7 +19605,7 @@
       <c r="B129" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C129" s="287" t="s">
+      <c r="C129" s="283" t="s">
         <v>1393</v>
       </c>
       <c r="D129" s="198" t="s">
@@ -19722,7 +19819,7 @@
       <c r="B135" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="287" t="s">
+      <c r="C135" s="283" t="s">
         <v>1394</v>
       </c>
       <c r="D135" s="198" t="s">
@@ -27149,7 +27246,7 @@
         <v>506</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="I4" s="125" t="s">
         <v>35</v>
@@ -27222,8 +27319,8 @@
       <c r="G6" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="H6" s="289" t="s">
-        <v>1407</v>
+      <c r="H6" s="285" t="s">
+        <v>1406</v>
       </c>
       <c r="I6" s="125" t="s">
         <v>32</v>
@@ -27326,7 +27423,7 @@
         <v>508</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="I9" s="125" t="s">
         <v>29</v>
@@ -27423,7 +27520,7 @@
         <v>519</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>512</v>
@@ -27529,7 +27626,7 @@
       <c r="E15" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="F15" s="288" t="s">
+      <c r="F15" s="284" t="s">
         <v>1399</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -27603,7 +27700,7 @@
       <c r="E17" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="F17" s="288" t="s">
+      <c r="F17" s="284" t="s">
         <v>1400</v>
       </c>
       <c r="G17" s="6"/>
@@ -32572,7 +32669,7 @@
       <c r="C158" s="65" t="s">
         <v>685</v>
       </c>
-      <c r="D158" s="290" t="s">
+      <c r="D158" s="286" t="s">
         <v>719</v>
       </c>
       <c r="E158" s="65"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DEE665-F484-4E7A-ABBA-5BF2931D8253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0997EFA-0926-402D-90C8-2404CE3AD3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18480" yWindow="16455" windowWidth="18450" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="16065" windowWidth="14610" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10099" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10150" uniqueCount="1495">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6284,18 +6284,12 @@
     <t>黒影林 / 悪鬼都市</t>
   </si>
   <si>
-    <t xml:space="preserve">黒影林 / 海岸旅館 </t>
-  </si>
-  <si>
     <t>孤独の村 / 悪鬼都市</t>
   </si>
   <si>
     <t>黒影林 / 孤独の村</t>
   </si>
   <si>
-    <t>孤独の村</t>
-  </si>
-  <si>
     <t>孤独の村 / 染色工房</t>
   </si>
   <si>
@@ -6324,9 +6318,6 @@
   </si>
   <si>
     <t>巨岩の海岸 / 悪鬼都市</t>
-  </si>
-  <si>
-    <t>巨岩の海岸 / 渡門旅館</t>
   </si>
   <si>
     <t>武運村 / 戒狼村</t>
@@ -6375,14 +6366,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>10:19_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10:38_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>07:45</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6399,18 +6382,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>04:25_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>07:23_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>11:48_?</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>11:49</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6428,6 +6399,309 @@
   </si>
   <si>
     <t>12:07</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:34</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:30</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤村 / 豬豬農場</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 孤独の村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">孤独の村 / 海岸旅館 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>08:42_?</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>灰狼村 / 染坊</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戒狼村 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>悲鳴村 / 灰狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>孤村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> / 灰狼村</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武運村 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>孤独の村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> /  戒狼村</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:46</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩海岸 / 土門客棧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑森林 / 土門客棧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07:32</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑森林 / 豬豬農場</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩海岸 / 豬豬農場</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">黒影林 / 海岸旅館 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">巨岩の海岸 / 海岸旅館 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>18:57</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>悲鳴村 / 灰狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩海岸 / 悲鳴村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武運村 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 武運村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>02:40</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑森林 / 孤村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 孤独の村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豬豬農場 / 土門客棧</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海岸旅館 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:09</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>00:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>07:12</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>09:02</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>04:40</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>04:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>07:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>08:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>49</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>10:1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>11:4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>06:5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20:16</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>09:04</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:38</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>04:34</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>04:41</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:38</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>05:5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6691,7 +6965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="287">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7549,6 +7823,30 @@
     <xf numFmtId="176" fontId="13" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="19" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -8139,14 +8437,14 @@
       <c r="C2" s="150"/>
       <c r="D2" s="149"/>
       <c r="E2" s="149"/>
-      <c r="F2" s="150" t="s">
-        <v>269</v>
+      <c r="F2" s="287" t="s">
+        <v>1478</v>
       </c>
       <c r="G2" s="149" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H2" s="149" t="s">
-        <v>1397</v>
+        <v>1017</v>
       </c>
       <c r="I2" s="150" t="s">
         <v>623</v>
@@ -8166,7 +8464,7 @@
       </c>
       <c r="O2" s="143" t="str">
         <f>IF($F2&lt;&gt;"",TEXT($F2,"HH:MM"),"")</f>
-        <v>01:25</v>
+        <v>00:00</v>
       </c>
       <c r="P2" s="143" t="str">
         <f>IF($I2&lt;&gt;"",TEXT($I2,"HH:MM"),"")</f>
@@ -8187,16 +8485,16 @@
         <v>1360</v>
       </c>
       <c r="E3" s="149" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="F3" s="150" t="s">
-        <v>1277</v>
+        <v>269</v>
       </c>
       <c r="G3" s="149" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H3" s="149" t="s">
-        <v>1018</v>
+        <v>1397</v>
       </c>
       <c r="I3" s="150" t="s">
         <v>1041</v>
@@ -8216,7 +8514,7 @@
       </c>
       <c r="O3" s="143" t="str">
         <f t="shared" ref="O3:O66" si="1">IF($F3&lt;&gt;"",TEXT($F3,"HH:MM"),"")</f>
-        <v>02:50</v>
+        <v>01:25</v>
       </c>
       <c r="P3" s="143" t="str">
         <f t="shared" ref="P3:P66" si="2">IF($I3&lt;&gt;"",TEXT($I3,"HH:MM"),"")</f>
@@ -8233,9 +8531,15 @@
       <c r="C4" s="150"/>
       <c r="D4" s="152"/>
       <c r="E4" s="152"/>
-      <c r="F4" s="150"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
+      <c r="F4" s="150" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G4" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="149" t="s">
+        <v>1018</v>
+      </c>
       <c r="I4" s="150" t="s">
         <v>998</v>
       </c>
@@ -8254,7 +8558,7 @@
       </c>
       <c r="O4" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>02:50</v>
       </c>
       <c r="P4" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8271,15 +8575,9 @@
       <c r="C5" s="149"/>
       <c r="D5" s="149"/>
       <c r="E5" s="149"/>
-      <c r="F5" s="150" t="s">
-        <v>1278</v>
-      </c>
-      <c r="G5" s="149" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="149" t="s">
-        <v>1017</v>
-      </c>
+      <c r="F5" s="150"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
       <c r="I5" s="150"/>
       <c r="J5" s="149"/>
       <c r="K5" s="149"/>
@@ -8292,7 +8590,7 @@
       </c>
       <c r="O5" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>04:15</v>
+        <v/>
       </c>
       <c r="P5" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8313,16 +8611,16 @@
         <v>1361</v>
       </c>
       <c r="E6" s="149" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="F6" s="150" t="s">
-        <v>977</v>
+        <v>1278</v>
       </c>
       <c r="G6" s="149" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H6" s="149" t="s">
-        <v>1397</v>
+        <v>1017</v>
       </c>
       <c r="I6" s="148" t="s">
         <v>931</v>
@@ -8342,7 +8640,7 @@
       </c>
       <c r="O6" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>05:44</v>
+        <v>04:15</v>
       </c>
       <c r="P6" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8359,9 +8657,15 @@
       <c r="C7" s="149"/>
       <c r="D7" s="149"/>
       <c r="E7" s="149"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="149"/>
+      <c r="F7" s="150" t="s">
+        <v>977</v>
+      </c>
+      <c r="G7" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="149" t="s">
+        <v>1397</v>
+      </c>
       <c r="I7" s="150" t="s">
         <v>299</v>
       </c>
@@ -8380,7 +8684,7 @@
       </c>
       <c r="O7" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>05:44</v>
       </c>
       <c r="P7" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8394,9 +8698,15 @@
       <c r="B8" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="150"/>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
+      <c r="C8" s="287" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D8" s="149" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E8" s="149" t="s">
+        <v>1460</v>
+      </c>
       <c r="F8" s="153"/>
       <c r="G8" s="149"/>
       <c r="H8" s="149"/>
@@ -8408,7 +8718,7 @@
       </c>
       <c r="N8" s="143" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>06:46</v>
       </c>
       <c r="O8" s="143" t="str">
         <f t="shared" si="1"/>
@@ -8429,14 +8739,14 @@
       <c r="C9" s="150"/>
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
-      <c r="F9" s="150" t="s">
-        <v>650</v>
+      <c r="F9" s="287" t="s">
+        <v>1479</v>
       </c>
       <c r="G9" s="149" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H9" s="149" t="s">
-        <v>1397</v>
+        <v>1017</v>
       </c>
       <c r="I9" s="150" t="s">
         <v>1280</v>
@@ -8456,7 +8766,7 @@
       </c>
       <c r="O9" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>08:40</v>
+        <v>07:12</v>
       </c>
       <c r="P9" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8473,9 +8783,15 @@
       <c r="C10" s="150"/>
       <c r="D10" s="149"/>
       <c r="E10" s="149"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
+      <c r="F10" s="150" t="s">
+        <v>650</v>
+      </c>
+      <c r="G10" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="149" t="s">
+        <v>1397</v>
+      </c>
       <c r="I10" s="148" t="s">
         <v>1281</v>
       </c>
@@ -8494,7 +8810,7 @@
       </c>
       <c r="O10" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>08:40</v>
       </c>
       <c r="P10" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8515,17 +8831,11 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1422</v>
-      </c>
-      <c r="F11" s="150" t="s">
-        <v>275</v>
-      </c>
-      <c r="G11" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="H11" s="149" t="s">
-        <v>1018</v>
-      </c>
+        <v>1420</v>
+      </c>
+      <c r="F11" s="150"/>
+      <c r="G11" s="149"/>
+      <c r="H11" s="149"/>
       <c r="I11" s="150"/>
       <c r="J11" s="149"/>
       <c r="K11" s="149"/>
@@ -8538,7 +8848,7 @@
       </c>
       <c r="O11" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>10:07</v>
+        <v/>
       </c>
       <c r="P11" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8556,13 +8866,13 @@
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
       <c r="F12" s="150" t="s">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="G12" s="149" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H12" s="149" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="I12" s="150" t="s">
         <v>1282</v>
@@ -8582,7 +8892,7 @@
       </c>
       <c r="O12" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>11:42</v>
+        <v>10:07</v>
       </c>
       <c r="P12" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8599,9 +8909,15 @@
       <c r="C13" s="150"/>
       <c r="D13" s="149"/>
       <c r="E13" s="149"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
+      <c r="F13" s="150" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="149" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="149" t="s">
+        <v>1016</v>
+      </c>
       <c r="I13" s="148" t="s">
         <v>1283</v>
       </c>
@@ -8620,7 +8936,7 @@
       </c>
       <c r="O13" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>11:42</v>
       </c>
       <c r="P13" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8637,15 +8953,9 @@
       <c r="C14" s="149"/>
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
-      <c r="F14" s="150" t="s">
-        <v>809</v>
-      </c>
-      <c r="G14" s="149" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="149" t="s">
-        <v>1017</v>
-      </c>
+      <c r="F14" s="150"/>
+      <c r="G14" s="149"/>
+      <c r="H14" s="149"/>
       <c r="I14" s="150"/>
       <c r="J14" s="149"/>
       <c r="K14" s="149"/>
@@ -8658,7 +8968,7 @@
       </c>
       <c r="O14" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>13:10</v>
+        <v/>
       </c>
       <c r="P14" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8676,13 +8986,13 @@
         <v>1284</v>
       </c>
       <c r="D15" s="149" t="s">
-        <v>63</v>
+        <v>1457</v>
       </c>
       <c r="E15" s="149" t="s">
-        <v>1425</v>
+        <v>1459</v>
       </c>
       <c r="F15" s="150" t="s">
-        <v>1075</v>
+        <v>809</v>
       </c>
       <c r="G15" s="149" t="s">
         <v>17</v>
@@ -8708,7 +9018,7 @@
       </c>
       <c r="O15" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>14:35</v>
+        <v>13:10</v>
       </c>
       <c r="P15" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8725,9 +9035,15 @@
       <c r="C16" s="149"/>
       <c r="D16" s="149"/>
       <c r="E16" s="149"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
+      <c r="F16" s="150" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G16" s="149" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="149" t="s">
+        <v>1017</v>
+      </c>
       <c r="I16" s="148" t="s">
         <v>1286</v>
       </c>
@@ -8746,7 +9062,7 @@
       </c>
       <c r="O16" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>14:35</v>
       </c>
       <c r="P16" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8763,15 +9079,9 @@
       <c r="C17" s="150"/>
       <c r="D17" s="149"/>
       <c r="E17" s="149"/>
-      <c r="F17" s="150" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G17" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="149" t="s">
-        <v>1397</v>
-      </c>
+      <c r="F17" s="150"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
       <c r="I17" s="150"/>
       <c r="J17" s="149"/>
       <c r="K17" s="149"/>
@@ -8784,7 +9094,7 @@
       </c>
       <c r="O17" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>16:08</v>
+        <v/>
       </c>
       <c r="P17" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8802,13 +9112,13 @@
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
       <c r="F18" s="150" t="s">
-        <v>216</v>
+        <v>1204</v>
       </c>
       <c r="G18" s="149" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H18" s="149" t="s">
-        <v>1017</v>
+        <v>1397</v>
       </c>
       <c r="I18" s="148" t="s">
         <v>1287</v>
@@ -8828,7 +9138,7 @@
       </c>
       <c r="O18" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>17:34</v>
+        <v>16:08</v>
       </c>
       <c r="P18" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8846,14 +9156,20 @@
         <v>1372</v>
       </c>
       <c r="D19" s="149" t="s">
-        <v>1363</v>
+        <v>1467</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1426</v>
-      </c>
-      <c r="F19" s="150"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
+        <v>1469</v>
+      </c>
+      <c r="F19" s="150" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="149" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="149" t="s">
+        <v>1017</v>
+      </c>
       <c r="I19" s="150" t="s">
         <v>1079</v>
       </c>
@@ -8872,7 +9188,7 @@
       </c>
       <c r="O19" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>17:34</v>
       </c>
       <c r="P19" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8889,15 +9205,9 @@
       <c r="C20" s="149"/>
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
-      <c r="F20" s="150" t="s">
-        <v>818</v>
-      </c>
-      <c r="G20" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="H20" s="149" t="s">
-        <v>1397</v>
-      </c>
+      <c r="F20" s="150"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
       <c r="I20" s="150"/>
       <c r="J20" s="149"/>
       <c r="K20" s="149"/>
@@ -8910,7 +9220,7 @@
       </c>
       <c r="O20" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>19:06</v>
+        <v/>
       </c>
       <c r="P20" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8928,7 +9238,7 @@
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
       <c r="F21" s="150" t="s">
-        <v>1288</v>
+        <v>818</v>
       </c>
       <c r="G21" s="149" t="s">
         <v>27</v>
@@ -8954,7 +9264,7 @@
       </c>
       <c r="O21" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>20:29</v>
+        <v>19:06</v>
       </c>
       <c r="P21" s="143" t="str">
         <f t="shared" si="2"/>
@@ -8975,11 +9285,17 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1412</v>
-      </c>
-      <c r="F22" s="150"/>
-      <c r="G22" s="149"/>
-      <c r="H22" s="149"/>
+        <v>1411</v>
+      </c>
+      <c r="F22" s="150" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G22" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="149" t="s">
+        <v>1397</v>
+      </c>
       <c r="I22" s="150" t="s">
         <v>1290</v>
       </c>
@@ -8998,7 +9314,7 @@
       </c>
       <c r="O22" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20:29</v>
       </c>
       <c r="P22" s="143" t="str">
         <f t="shared" si="2"/>
@@ -9015,15 +9331,9 @@
       <c r="C23" s="149"/>
       <c r="D23" s="149"/>
       <c r="E23" s="149"/>
-      <c r="F23" s="150" t="s">
-        <v>1022</v>
-      </c>
-      <c r="G23" s="149" t="s">
-        <v>27</v>
-      </c>
-      <c r="H23" s="149" t="s">
-        <v>1397</v>
-      </c>
+      <c r="F23" s="150"/>
+      <c r="G23" s="149"/>
+      <c r="H23" s="149"/>
       <c r="I23" s="150"/>
       <c r="J23" s="149"/>
       <c r="K23" s="149"/>
@@ -9036,7 +9346,7 @@
       </c>
       <c r="O23" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>22:02</v>
+        <v/>
       </c>
       <c r="P23" s="143" t="str">
         <f t="shared" si="2"/>
@@ -9054,13 +9364,13 @@
       <c r="D24" s="149"/>
       <c r="E24" s="149"/>
       <c r="F24" s="150" t="s">
-        <v>1291</v>
+        <v>1022</v>
       </c>
       <c r="G24" s="149" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H24" s="149" t="s">
-        <v>1018</v>
+        <v>1397</v>
       </c>
       <c r="I24" s="148" t="s">
         <v>1081</v>
@@ -9080,7 +9390,7 @@
       </c>
       <c r="O24" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>23:34</v>
+        <v>22:02</v>
       </c>
       <c r="P24" s="143" t="str">
         <f t="shared" si="2"/>
@@ -9098,7 +9408,7 @@
       <c r="D25" s="155"/>
       <c r="E25" s="155"/>
       <c r="F25" s="156" t="s">
-        <v>141</v>
+        <v>1291</v>
       </c>
       <c r="G25" s="155" t="s">
         <v>0</v>
@@ -9118,7 +9428,7 @@
       </c>
       <c r="O25" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>00:00</v>
+        <v>23:34</v>
       </c>
       <c r="P25" s="143" t="str">
         <f t="shared" si="2"/>
@@ -9139,25 +9449,25 @@
         <v>45</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="F26" s="159" t="s">
-        <v>636</v>
+        <v>141</v>
       </c>
       <c r="G26" s="158" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H26" s="158" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I26" s="159" t="s">
-        <v>269</v>
+        <v>1018</v>
+      </c>
+      <c r="I26" s="293" t="s">
+        <v>1478</v>
       </c>
       <c r="J26" s="158" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K26" s="158" t="s">
-        <v>1015</v>
+        <v>1408</v>
       </c>
       <c r="L26" s="157" t="s">
         <v>37</v>
@@ -9168,11 +9478,11 @@
       </c>
       <c r="O26" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>01:32</v>
+        <v>00:00</v>
       </c>
       <c r="P26" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>01:25</v>
+        <v>00:00</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1">
@@ -9185,17 +9495,23 @@
       <c r="C27" s="161"/>
       <c r="D27" s="160"/>
       <c r="E27" s="160"/>
-      <c r="F27" s="162"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="160"/>
+      <c r="F27" s="162" t="s">
+        <v>636</v>
+      </c>
+      <c r="G27" s="160" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="160" t="s">
+        <v>1016</v>
+      </c>
       <c r="I27" s="162" t="s">
-        <v>1292</v>
+        <v>269</v>
       </c>
       <c r="J27" s="160" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K27" s="160" t="s">
-        <v>1408</v>
+        <v>1015</v>
       </c>
       <c r="L27" s="157" t="s">
         <v>36</v>
@@ -9206,11 +9522,11 @@
       </c>
       <c r="O27" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>01:32</v>
       </c>
       <c r="P27" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>02:58</v>
+        <v>01:25</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1">
@@ -9223,18 +9539,18 @@
       <c r="C28" s="162"/>
       <c r="D28" s="160"/>
       <c r="E28" s="160"/>
-      <c r="F28" s="162" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="160" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="160" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I28" s="162"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="160"/>
+      <c r="F28" s="162"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="160"/>
+      <c r="I28" s="162" t="s">
+        <v>1292</v>
+      </c>
+      <c r="J28" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="160" t="s">
+        <v>1408</v>
+      </c>
       <c r="L28" s="157" t="s">
         <v>35</v>
       </c>
@@ -9244,11 +9560,11 @@
       </c>
       <c r="O28" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>03:00</v>
+        <v/>
       </c>
       <c r="P28" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>02:58</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="18" customHeight="1">
@@ -9262,23 +9578,17 @@
       <c r="D29" s="160"/>
       <c r="E29" s="160"/>
       <c r="F29" s="162" t="s">
-        <v>1195</v>
+        <v>143</v>
       </c>
       <c r="G29" s="160" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H29" s="160" t="s">
-        <v>1397</v>
-      </c>
-      <c r="I29" s="157" t="s">
-        <v>950</v>
-      </c>
-      <c r="J29" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="K29" s="160" t="s">
-        <v>1015</v>
-      </c>
+        <v>1017</v>
+      </c>
+      <c r="I29" s="157"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="160"/>
       <c r="L29" s="157" t="s">
         <v>33</v>
       </c>
@@ -9288,11 +9598,11 @@
       </c>
       <c r="O29" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>04:25</v>
+        <v>03:00</v>
       </c>
       <c r="P29" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>04:29</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:16" ht="18" customHeight="1">
@@ -9309,10 +9619,10 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="F30" s="162" t="s">
-        <v>589</v>
+        <v>1195</v>
       </c>
       <c r="G30" s="160" t="s">
         <v>27</v>
@@ -9320,9 +9630,15 @@
       <c r="H30" s="160" t="s">
         <v>1397</v>
       </c>
-      <c r="I30" s="162"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
+      <c r="I30" s="162" t="s">
+        <v>950</v>
+      </c>
+      <c r="J30" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K30" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L30" s="157" t="s">
         <v>32</v>
       </c>
@@ -9332,11 +9648,11 @@
       </c>
       <c r="O30" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>05:55</v>
+        <v>04:25</v>
       </c>
       <c r="P30" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:29</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="18" customHeight="1">
@@ -9349,18 +9665,18 @@
       <c r="C31" s="162"/>
       <c r="D31" s="160"/>
       <c r="E31" s="160"/>
-      <c r="F31" s="162"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="162" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J31" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="K31" s="160" t="s">
-        <v>1015</v>
-      </c>
+      <c r="F31" s="162" t="s">
+        <v>589</v>
+      </c>
+      <c r="G31" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H31" s="160" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I31" s="162"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="160"/>
       <c r="L31" s="157" t="s">
         <v>31</v>
       </c>
@@ -9370,11 +9686,11 @@
       </c>
       <c r="O31" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>05:55</v>
       </c>
       <c r="P31" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>06:03</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:16" ht="18" customHeight="1">
@@ -9387,17 +9703,11 @@
       <c r="C32" s="162"/>
       <c r="D32" s="160"/>
       <c r="E32" s="160"/>
-      <c r="F32" s="162" t="s">
-        <v>887</v>
-      </c>
-      <c r="G32" s="160" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="160" t="s">
-        <v>1397</v>
-      </c>
+      <c r="F32" s="162"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="160"/>
       <c r="I32" s="157" t="s">
-        <v>541</v>
+        <v>1293</v>
       </c>
       <c r="J32" s="160" t="s">
         <v>4</v>
@@ -9414,11 +9724,11 @@
       </c>
       <c r="O32" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>07:29</v>
+        <v/>
       </c>
       <c r="P32" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>07:34</v>
+        <v>06:03</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1">
@@ -9428,29 +9738,47 @@
       <c r="B33" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="161"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="160"/>
-      <c r="F33" s="162"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="162"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
+      <c r="C33" s="288" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D33" s="160" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E33" s="160" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F33" s="162" t="s">
+        <v>887</v>
+      </c>
+      <c r="G33" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="160" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I33" s="162" t="s">
+        <v>541</v>
+      </c>
+      <c r="J33" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L33" s="157" t="s">
         <v>29</v>
       </c>
       <c r="N33" s="143" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>07:32</v>
       </c>
       <c r="O33" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>07:29</v>
       </c>
       <c r="P33" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>07:34</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="18" customHeight="1">
@@ -9495,17 +9823,17 @@
       <c r="C35" s="162"/>
       <c r="D35" s="160"/>
       <c r="E35" s="160"/>
-      <c r="F35" s="160" t="s">
-        <v>1375</v>
+      <c r="F35" s="289" t="s">
+        <v>1480</v>
       </c>
       <c r="G35" s="160" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H35" s="160" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I35" s="157" t="s">
-        <v>1121</v>
+        <v>1016</v>
+      </c>
+      <c r="I35" s="294" t="s">
+        <v>1489</v>
       </c>
       <c r="J35" s="160" t="s">
         <v>13</v>
@@ -9522,11 +9850,11 @@
       </c>
       <c r="O35" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>10:35</v>
+        <v>09:02</v>
       </c>
       <c r="P35" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>10:30</v>
+        <v>09:04</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="18" customHeight="1">
@@ -9540,17 +9868,29 @@
         <v>1294</v>
       </c>
       <c r="D36" s="160" t="s">
-        <v>48</v>
+        <v>1472</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1413</v>
-      </c>
-      <c r="F36" s="162"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="160"/>
+        <v>1473</v>
+      </c>
+      <c r="F36" s="162" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G36" s="160" t="s">
+        <v>0</v>
+      </c>
+      <c r="H36" s="160" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I36" s="162" t="s">
+        <v>1121</v>
+      </c>
+      <c r="J36" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" s="160" t="s">
+        <v>1408</v>
+      </c>
       <c r="L36" s="157" t="s">
         <v>25</v>
       </c>
@@ -9560,11 +9900,11 @@
       </c>
       <c r="O36" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>10:35</v>
       </c>
       <c r="P36" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10:30</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1">
@@ -9577,24 +9917,12 @@
       <c r="C37" s="160"/>
       <c r="D37" s="160"/>
       <c r="E37" s="160"/>
-      <c r="F37" s="162" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G37" s="160" t="s">
-        <v>17</v>
-      </c>
-      <c r="H37" s="160" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I37" s="162" t="s">
-        <v>1296</v>
-      </c>
-      <c r="J37" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="K37" s="160" t="s">
-        <v>1015</v>
-      </c>
+      <c r="F37" s="162"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="160"/>
+      <c r="I37" s="162"/>
+      <c r="J37" s="160"/>
+      <c r="K37" s="160"/>
       <c r="L37" s="157" t="s">
         <v>23</v>
       </c>
@@ -9604,11 +9932,11 @@
       </c>
       <c r="O37" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>12:10</v>
+        <v/>
       </c>
       <c r="P37" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>12:05</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:16" ht="18" customHeight="1">
@@ -9622,7 +9950,7 @@
       <c r="D38" s="160"/>
       <c r="E38" s="160"/>
       <c r="F38" s="162" t="s">
-        <v>189</v>
+        <v>1295</v>
       </c>
       <c r="G38" s="160" t="s">
         <v>17</v>
@@ -9630,8 +9958,8 @@
       <c r="H38" s="160" t="s">
         <v>1017</v>
       </c>
-      <c r="I38" s="163">
-        <v>0.56805555555555554</v>
+      <c r="I38" s="163" t="s">
+        <v>1296</v>
       </c>
       <c r="J38" s="160" t="s">
         <v>4</v>
@@ -9648,11 +9976,11 @@
       </c>
       <c r="O38" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>13:43</v>
+        <v>12:10</v>
       </c>
       <c r="P38" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>13:38</v>
+        <v>12:05</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="18" customHeight="1">
@@ -9671,12 +9999,24 @@
       <c r="E39" s="160" t="s">
         <v>1410</v>
       </c>
-      <c r="F39" s="162"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="162"/>
-      <c r="J39" s="160"/>
-      <c r="K39" s="160"/>
+      <c r="F39" s="162" t="s">
+        <v>189</v>
+      </c>
+      <c r="G39" s="160" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I39" s="289" t="s">
+        <v>1490</v>
+      </c>
+      <c r="J39" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K39" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L39" s="157" t="s">
         <v>21</v>
       </c>
@@ -9686,11 +10026,11 @@
       </c>
       <c r="O39" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>13:43</v>
       </c>
       <c r="P39" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:38</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1">
@@ -9703,24 +10043,12 @@
       <c r="C40" s="161"/>
       <c r="D40" s="160"/>
       <c r="E40" s="160"/>
-      <c r="F40" s="162" t="s">
-        <v>1297</v>
-      </c>
-      <c r="G40" s="160" t="s">
-        <v>0</v>
-      </c>
-      <c r="H40" s="160" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I40" s="162" t="s">
-        <v>1298</v>
-      </c>
-      <c r="J40" s="160" t="s">
-        <v>13</v>
-      </c>
-      <c r="K40" s="160" t="s">
-        <v>1408</v>
-      </c>
+      <c r="F40" s="162"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="160"/>
+      <c r="I40" s="162"/>
+      <c r="J40" s="160"/>
+      <c r="K40" s="160"/>
       <c r="L40" s="157" t="s">
         <v>20</v>
       </c>
@@ -9730,11 +10058,11 @@
       </c>
       <c r="O40" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>15:13</v>
+        <v/>
       </c>
       <c r="P40" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>15:07</v>
+        <v/>
       </c>
     </row>
     <row r="41" spans="1:16" ht="18" customHeight="1">
@@ -9748,22 +10076,22 @@
       <c r="D41" s="160"/>
       <c r="E41" s="160"/>
       <c r="F41" s="162" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G41" s="160" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H41" s="160" t="s">
-        <v>1397</v>
+        <v>1018</v>
       </c>
       <c r="I41" s="162" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="J41" s="160" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K41" s="160" t="s">
-        <v>1015</v>
+        <v>1408</v>
       </c>
       <c r="L41" s="157" t="s">
         <v>18</v>
@@ -9774,11 +10102,11 @@
       </c>
       <c r="O41" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>16:39</v>
+        <v>15:13</v>
       </c>
       <c r="P41" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>16:38</v>
+        <v>15:07</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1">
@@ -9795,14 +10123,26 @@
         <v>1365</v>
       </c>
       <c r="E42" s="160" t="s">
-        <v>1418</v>
-      </c>
-      <c r="F42" s="162"/>
-      <c r="G42" s="160"/>
-      <c r="H42" s="160"/>
-      <c r="I42" s="164"/>
-      <c r="J42" s="160"/>
-      <c r="K42" s="160"/>
+        <v>1416</v>
+      </c>
+      <c r="F42" s="162" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G42" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="160" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I42" s="164" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J42" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K42" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L42" s="157" t="s">
         <v>16</v>
       </c>
@@ -9812,11 +10152,11 @@
       </c>
       <c r="O42" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16:39</v>
       </c>
       <c r="P42" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:38</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="18" customHeight="1">
@@ -9829,24 +10169,12 @@
       <c r="C43" s="162"/>
       <c r="D43" s="160"/>
       <c r="E43" s="160"/>
-      <c r="F43" s="162" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G43" s="160" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="160" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I43" s="162" t="s">
-        <v>230</v>
-      </c>
-      <c r="J43" s="160" t="s">
-        <v>4</v>
-      </c>
-      <c r="K43" s="160" t="s">
-        <v>1015</v>
-      </c>
+      <c r="F43" s="162"/>
+      <c r="G43" s="160"/>
+      <c r="H43" s="160"/>
+      <c r="I43" s="162"/>
+      <c r="J43" s="160"/>
+      <c r="K43" s="160"/>
       <c r="L43" s="157" t="s">
         <v>15</v>
       </c>
@@ -9856,11 +10184,11 @@
       </c>
       <c r="O43" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>18:12_?</v>
+        <v/>
       </c>
       <c r="P43" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>18:03</v>
+        <v/>
       </c>
     </row>
     <row r="44" spans="1:16" ht="18" customHeight="1">
@@ -9870,41 +10198,47 @@
       <c r="B44" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="162"/>
-      <c r="D44" s="160"/>
-      <c r="E44" s="160"/>
-      <c r="F44" s="160" t="s">
-        <v>1379</v>
+      <c r="C44" s="289" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D44" s="160" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E44" s="160" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F44" s="161">
+        <v>0.75277777777777777</v>
       </c>
       <c r="G44" s="160" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H44" s="160" t="s">
-        <v>1397</v>
+        <v>1016</v>
       </c>
       <c r="I44" s="163" t="s">
-        <v>953</v>
+        <v>230</v>
       </c>
       <c r="J44" s="160" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K44" s="160" t="s">
-        <v>1408</v>
+        <v>1015</v>
       </c>
       <c r="L44" s="157" t="s">
         <v>12</v>
       </c>
       <c r="N44" s="143" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18:57</v>
       </c>
       <c r="O44" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>19:36</v>
+        <v>18:04</v>
       </c>
       <c r="P44" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>19:28</v>
+        <v>18:03</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18" customHeight="1">
@@ -9917,12 +10251,24 @@
       <c r="C45" s="162"/>
       <c r="D45" s="160"/>
       <c r="E45" s="160"/>
-      <c r="F45" s="162"/>
-      <c r="G45" s="160"/>
-      <c r="H45" s="160"/>
-      <c r="I45" s="162"/>
-      <c r="J45" s="160"/>
-      <c r="K45" s="160"/>
+      <c r="F45" s="162" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G45" s="160" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="160" t="s">
+        <v>1397</v>
+      </c>
+      <c r="I45" s="162" t="s">
+        <v>953</v>
+      </c>
+      <c r="J45" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K45" s="160" t="s">
+        <v>1408</v>
+      </c>
       <c r="L45" s="157" t="s">
         <v>10</v>
       </c>
@@ -9932,11 +10278,11 @@
       </c>
       <c r="O45" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>19:36</v>
       </c>
       <c r="P45" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>19:28</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="18" customHeight="1">
@@ -9949,24 +10295,12 @@
       <c r="C46" s="162"/>
       <c r="D46" s="160"/>
       <c r="E46" s="160"/>
-      <c r="F46" s="162" t="s">
-        <v>166</v>
-      </c>
-      <c r="G46" s="160" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" s="160" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I46" s="162" t="s">
-        <v>1038</v>
-      </c>
-      <c r="J46" s="160" t="s">
-        <v>13</v>
-      </c>
-      <c r="K46" s="160" t="s">
-        <v>1408</v>
-      </c>
+      <c r="F46" s="162"/>
+      <c r="G46" s="160"/>
+      <c r="H46" s="160"/>
+      <c r="I46" s="162"/>
+      <c r="J46" s="160"/>
+      <c r="K46" s="160"/>
       <c r="L46" s="157" t="s">
         <v>9</v>
       </c>
@@ -9976,11 +10310,11 @@
       </c>
       <c r="O46" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>21:04</v>
+        <v/>
       </c>
       <c r="P46" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>21:02</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:16" ht="18" customHeight="1">
@@ -9994,22 +10328,22 @@
       <c r="D47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160" t="s">
-        <v>1381</v>
+        <v>166</v>
       </c>
       <c r="G47" s="160" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H47" s="160" t="s">
-        <v>1397</v>
+        <v>1017</v>
       </c>
       <c r="I47" s="162" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="J47" s="160" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K47" s="160" t="s">
-        <v>1015</v>
+        <v>1408</v>
       </c>
       <c r="L47" s="157" t="s">
         <v>6</v>
@@ -10020,11 +10354,11 @@
       </c>
       <c r="O47" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>22:31</v>
+        <v>21:04</v>
       </c>
       <c r="P47" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>22:35</v>
+        <v>21:02</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="18" customHeight="1">
@@ -10038,22 +10372,22 @@
         <v>1302</v>
       </c>
       <c r="D48" s="160" t="s">
-        <v>902</v>
+        <v>1462</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>1411</v>
+        <v>1464</v>
       </c>
       <c r="F48" s="162" t="s">
-        <v>1303</v>
+        <v>1381</v>
       </c>
       <c r="G48" s="160" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H48" s="160" t="s">
-        <v>1017</v>
+        <v>1397</v>
       </c>
       <c r="I48" s="164" t="s">
-        <v>1291</v>
+        <v>1039</v>
       </c>
       <c r="J48" s="160" t="s">
         <v>4</v>
@@ -10070,11 +10404,11 @@
       </c>
       <c r="O48" s="143" t="str">
         <f t="shared" si="1"/>
-        <v>23:59</v>
+        <v>22:31</v>
       </c>
       <c r="P48" s="143" t="str">
         <f t="shared" si="2"/>
-        <v>23:34</v>
+        <v>22:35</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -10087,9 +10421,15 @@
       <c r="C49" s="166"/>
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
-      <c r="F49" s="167"/>
-      <c r="G49" s="166"/>
-      <c r="H49" s="166"/>
+      <c r="F49" s="167" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G49" s="166" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="166" t="s">
+        <v>1017</v>
+      </c>
       <c r="I49" s="167"/>
       <c r="J49" s="166"/>
       <c r="K49" s="166"/>
@@ -10102,7 +10442,7 @@
       </c>
       <c r="O49" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>23:59</v>
       </c>
       <c r="P49" s="143" t="str">
         <f t="shared" si="2"/>
@@ -10204,9 +10544,15 @@
       <c r="B52" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="173"/>
-      <c r="D52" s="171"/>
-      <c r="E52" s="171"/>
+      <c r="C52" s="173" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D52" s="290" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E52" s="171" t="s">
+        <v>1473</v>
+      </c>
       <c r="F52" s="173"/>
       <c r="G52" s="171"/>
       <c r="H52" s="171"/>
@@ -10218,7 +10564,7 @@
       </c>
       <c r="N52" s="143" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>02:40</v>
       </c>
       <c r="O52" s="143" t="str">
         <f t="shared" si="1"/>
@@ -10283,12 +10629,24 @@
       <c r="C54" s="172"/>
       <c r="D54" s="171"/>
       <c r="E54" s="171"/>
-      <c r="F54" s="172"/>
-      <c r="G54" s="171"/>
-      <c r="H54" s="171"/>
-      <c r="I54" s="172"/>
-      <c r="J54" s="171"/>
-      <c r="K54" s="171"/>
+      <c r="F54" s="290" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G54" s="171" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="171" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I54" s="290" t="s">
+        <v>1491</v>
+      </c>
+      <c r="J54" s="171" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L54" s="168" t="s">
         <v>32</v>
       </c>
@@ -10298,11 +10656,11 @@
       </c>
       <c r="O54" s="143" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>04:40</v>
       </c>
       <c r="P54" s="143" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:34</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1">
@@ -10633,7 +10991,7 @@
         <v>1367</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="F62" s="172" t="s">
         <v>1306</v>
@@ -10929,7 +11287,7 @@
         <v>904</v>
       </c>
       <c r="E69" s="171" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="F69" s="172" t="s">
         <v>1312</v>
@@ -11099,7 +11457,7 @@
         <v>1365</v>
       </c>
       <c r="E73" s="175" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="F73" s="176"/>
       <c r="G73" s="175"/>
@@ -11178,7 +11536,7 @@
       <c r="D75" s="180"/>
       <c r="E75" s="180"/>
       <c r="F75" s="181" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="G75" s="180" t="s">
         <v>1402</v>
@@ -11225,7 +11583,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1413</v>
+        <v>1447</v>
       </c>
       <c r="F76" s="181"/>
       <c r="G76" s="180"/>
@@ -11292,7 +11650,7 @@
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
       <c r="F78" s="181" t="s">
-        <v>1444</v>
+        <v>1482</v>
       </c>
       <c r="G78" s="180" t="s">
         <v>11</v>
@@ -11300,9 +11658,15 @@
       <c r="H78" s="180" t="s">
         <v>1016</v>
       </c>
-      <c r="I78" s="181"/>
-      <c r="J78" s="180"/>
-      <c r="K78" s="180"/>
+      <c r="I78" s="291" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J78" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K78" s="180" t="s">
+        <v>1408</v>
+      </c>
       <c r="L78" s="177" t="s">
         <v>32</v>
       </c>
@@ -11312,11 +11676,11 @@
       </c>
       <c r="O78" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>04:25_?</v>
+        <v>04:16</v>
       </c>
       <c r="P78" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>04:41</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1">
@@ -11330,7 +11694,7 @@
       <c r="D79" s="180"/>
       <c r="E79" s="180"/>
       <c r="F79" s="181" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="G79" s="180" t="s">
         <v>17</v>
@@ -11364,14 +11728,20 @@
       <c r="B80" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C80" s="181"/>
-      <c r="D80" s="180"/>
-      <c r="E80" s="180"/>
+      <c r="C80" s="291" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D80" s="180" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E80" s="180" t="s">
+        <v>1476</v>
+      </c>
       <c r="F80" s="181"/>
       <c r="G80" s="180"/>
       <c r="H80" s="180"/>
       <c r="I80" s="182" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="J80" s="180" t="s">
         <v>13</v>
@@ -11384,7 +11754,7 @@
       </c>
       <c r="N80" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>06:03</v>
       </c>
       <c r="O80" s="143" t="str">
         <f t="shared" si="4"/>
@@ -11406,7 +11776,7 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1445</v>
+        <v>1483</v>
       </c>
       <c r="G81" s="180" t="s">
         <v>17</v>
@@ -11415,7 +11785,7 @@
         <v>1017</v>
       </c>
       <c r="I81" s="181" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="J81" s="180" t="s">
         <v>4</v>
@@ -11432,7 +11802,7 @@
       </c>
       <c r="O81" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>07:23_?</v>
+        <v>07:18</v>
       </c>
       <c r="P81" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11446,12 +11816,24 @@
       <c r="B82" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C82" s="181"/>
-      <c r="D82" s="180"/>
-      <c r="E82" s="180"/>
-      <c r="F82" s="181"/>
-      <c r="G82" s="180"/>
-      <c r="H82" s="180"/>
+      <c r="C82" s="181" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D82" s="180" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E82" s="180" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F82" s="181" t="s">
+        <v>1484</v>
+      </c>
+      <c r="G82" s="180" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="180" t="s">
+        <v>1017</v>
+      </c>
       <c r="I82" s="181"/>
       <c r="J82" s="180"/>
       <c r="K82" s="180"/>
@@ -11460,11 +11842,11 @@
       </c>
       <c r="N82" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>08:42_?</v>
       </c>
       <c r="O82" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>08:49</v>
       </c>
       <c r="P82" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11481,15 +11863,9 @@
       <c r="C83" s="180"/>
       <c r="D83" s="180"/>
       <c r="E83" s="180"/>
-      <c r="F83" s="181" t="s">
-        <v>1318</v>
-      </c>
-      <c r="G83" s="180" t="s">
-        <v>17</v>
-      </c>
-      <c r="H83" s="180" t="s">
-        <v>1017</v>
-      </c>
+      <c r="F83" s="181"/>
+      <c r="G83" s="180"/>
+      <c r="H83" s="180"/>
       <c r="I83" s="182" t="s">
         <v>240</v>
       </c>
@@ -11508,7 +11884,7 @@
       </c>
       <c r="O83" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>09:08_?</v>
+        <v/>
       </c>
       <c r="P83" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11526,7 +11902,7 @@
       <c r="D84" s="180"/>
       <c r="E84" s="180"/>
       <c r="F84" s="181" t="s">
-        <v>1438</v>
+        <v>1485</v>
       </c>
       <c r="G84" s="180" t="s">
         <v>0</v>
@@ -11535,7 +11911,7 @@
         <v>1018</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>1439</v>
+        <v>1493</v>
       </c>
       <c r="J84" s="180" t="s">
         <v>4</v>
@@ -11552,11 +11928,11 @@
       </c>
       <c r="O84" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>10:19_?</v>
+        <v>10:18</v>
       </c>
       <c r="P84" s="143" t="str">
         <f t="shared" si="5"/>
-        <v>10:38_?</v>
+        <v>10:38</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1">
@@ -11567,16 +11943,16 @@
         <v>52</v>
       </c>
       <c r="C85" s="181" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="D85" s="180" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="E85" s="180" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="F85" s="181" t="s">
-        <v>1446</v>
+        <v>1486</v>
       </c>
       <c r="G85" s="180" t="s">
         <v>17</v>
@@ -11596,7 +11972,7 @@
       </c>
       <c r="O85" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>11:48_?</v>
+        <v>11:49</v>
       </c>
       <c r="P85" s="143" t="str">
         <f t="shared" si="5"/>
@@ -11617,7 +11993,7 @@
       <c r="G86" s="180"/>
       <c r="H86" s="180"/>
       <c r="I86" s="182" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="J86" s="180" t="s">
         <v>4</v>
@@ -11654,9 +12030,15 @@
       <c r="F87" s="181"/>
       <c r="G87" s="180"/>
       <c r="H87" s="180"/>
-      <c r="I87" s="181"/>
-      <c r="J87" s="180"/>
-      <c r="K87" s="180"/>
+      <c r="I87" s="181" t="s">
+        <v>1444</v>
+      </c>
+      <c r="J87" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" s="180" t="s">
+        <v>1408</v>
+      </c>
       <c r="L87" s="177" t="s">
         <v>21</v>
       </c>
@@ -11670,7 +12052,7 @@
       </c>
       <c r="P87" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>13:34</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="18" customHeight="1">
@@ -11680,9 +12062,15 @@
       <c r="B88" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C88" s="181"/>
-      <c r="D88" s="180"/>
-      <c r="E88" s="180"/>
+      <c r="C88" s="181" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D88" s="180" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E88" s="180" t="s">
+        <v>1448</v>
+      </c>
       <c r="F88" s="181"/>
       <c r="G88" s="180"/>
       <c r="H88" s="180"/>
@@ -11694,7 +12082,7 @@
       </c>
       <c r="N88" s="143" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>14:30</v>
       </c>
       <c r="O88" s="143" t="str">
         <f t="shared" si="4"/>
@@ -11833,13 +12221,13 @@
         <v>52</v>
       </c>
       <c r="C92" s="181" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="D92" s="180" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="E92" s="180" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="180"/>
@@ -11959,13 +12347,13 @@
         <v>52</v>
       </c>
       <c r="C95" s="181" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D95" s="180" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="E95" s="180" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="F95" s="181"/>
       <c r="G95" s="180"/>
@@ -12082,10 +12470,10 @@
         <v>1323</v>
       </c>
       <c r="D98" s="187" t="s">
-        <v>1363</v>
+        <v>1452</v>
       </c>
       <c r="E98" s="187" t="s">
-        <v>1426</v>
+        <v>1454</v>
       </c>
       <c r="F98" s="188"/>
       <c r="G98" s="187"/>
@@ -12214,10 +12602,10 @@
         <v>284</v>
       </c>
       <c r="D101" s="189" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="E101" s="189" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="F101" s="190"/>
       <c r="G101" s="189"/>
@@ -12334,7 +12722,7 @@
       <c r="D104" s="189"/>
       <c r="E104" s="189"/>
       <c r="F104" s="190" t="s">
-        <v>999</v>
+        <v>1487</v>
       </c>
       <c r="G104" s="189" t="s">
         <v>0</v>
@@ -12360,7 +12748,7 @@
       </c>
       <c r="O104" s="143" t="str">
         <f t="shared" si="4"/>
-        <v>06:54</v>
+        <v>06:53</v>
       </c>
       <c r="P104" s="143" t="str">
         <f t="shared" si="5"/>
@@ -12381,7 +12769,7 @@
         <v>1367</v>
       </c>
       <c r="E105" s="189" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="F105" s="190"/>
       <c r="G105" s="189"/>
@@ -12545,7 +12933,7 @@
         <v>1367</v>
       </c>
       <c r="E109" s="189" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="F109" s="190" t="s">
         <v>919</v>
@@ -12671,7 +13059,7 @@
         <v>1361</v>
       </c>
       <c r="E112" s="189" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="F112" s="190" t="s">
         <v>838</v>
@@ -12835,7 +13223,7 @@
         <v>1139</v>
       </c>
       <c r="E116" s="189" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="F116" s="190" t="s">
         <v>1331</v>
@@ -12961,7 +13349,7 @@
         <v>48</v>
       </c>
       <c r="E119" s="189" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F119" s="190" t="s">
         <v>1333</v>
@@ -13084,10 +13472,10 @@
         <v>1336</v>
       </c>
       <c r="D122" s="196" t="s">
-        <v>1231</v>
+        <v>1453</v>
       </c>
       <c r="E122" s="196" t="s">
-        <v>1414</v>
+        <v>1455</v>
       </c>
       <c r="F122" s="197" t="s">
         <v>141</v>
@@ -13257,7 +13645,7 @@
         <v>1363</v>
       </c>
       <c r="E126" s="198" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F126" s="199" t="s">
         <v>886</v>
@@ -13313,7 +13701,7 @@
         <v>1018</v>
       </c>
       <c r="I127" s="199" t="s">
-        <v>272</v>
+        <v>1494</v>
       </c>
       <c r="J127" s="198" t="s">
         <v>13</v>
@@ -13334,7 +13722,7 @@
       </c>
       <c r="P127" s="143" t="str">
         <f t="shared" si="5"/>
-        <v>05:53</v>
+        <v>05:51</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="18" customHeight="1">
@@ -13509,7 +13897,7 @@
         <v>1369</v>
       </c>
       <c r="E132" s="198" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="F132" s="199" t="s">
         <v>1340</v>
@@ -13635,7 +14023,7 @@
         <v>1370</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>1341</v>
@@ -13849,7 +14237,7 @@
         <v>42</v>
       </c>
       <c r="E140" s="198" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="F140" s="199"/>
       <c r="G140" s="198"/>
@@ -14177,7 +14565,7 @@
         <v>48</v>
       </c>
       <c r="E148" s="208" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F148" s="209" t="s">
         <v>1349</v>
@@ -14340,9 +14728,15 @@
       <c r="B152" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="209"/>
-      <c r="D152" s="208"/>
-      <c r="E152" s="208"/>
+      <c r="C152" s="292" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D152" s="208" t="s">
+        <v>45</v>
+      </c>
+      <c r="E152" s="208" t="s">
+        <v>1421</v>
+      </c>
       <c r="F152" s="209" t="s">
         <v>941</v>
       </c>
@@ -14360,7 +14754,7 @@
       </c>
       <c r="N152" s="143" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>06:09</v>
       </c>
       <c r="O152" s="143" t="str">
         <f t="shared" si="7"/>
@@ -14467,7 +14861,7 @@
         <v>1365</v>
       </c>
       <c r="E155" s="208" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="F155" s="209" t="s">
         <v>1352</v>
@@ -14593,7 +14987,7 @@
         <v>1363</v>
       </c>
       <c r="E158" s="208" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F158" s="209" t="s">
         <v>1354</v>
@@ -14719,7 +15113,7 @@
         <v>1370</v>
       </c>
       <c r="E161" s="208" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="F161" s="209" t="s">
         <v>665</v>
@@ -14883,7 +15277,7 @@
         <v>1371</v>
       </c>
       <c r="E165" s="208" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F165" s="209"/>
       <c r="G165" s="208"/>
@@ -14923,9 +15317,15 @@
       <c r="C166" s="211"/>
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
-      <c r="F166" s="209"/>
-      <c r="G166" s="208"/>
-      <c r="H166" s="208"/>
+      <c r="F166" s="292" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G166" s="208" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166" s="208" t="s">
+        <v>1017</v>
+      </c>
       <c r="I166" s="209" t="s">
         <v>1359</v>
       </c>
@@ -14944,7 +15344,7 @@
       </c>
       <c r="O166" s="143" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20:16</v>
       </c>
       <c r="P166" s="143" t="str">
         <f t="shared" si="8"/>
@@ -15003,7 +15403,7 @@
         <v>45</v>
       </c>
       <c r="E168" s="208" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="F168" s="209"/>
       <c r="G168" s="208"/>
@@ -15105,7 +15505,7 @@
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1 E1:E1048576 K54:K99 K101:K1048576 H1:H1048576">
+  <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
     <cfRule type="containsText" dxfId="27" priority="8" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0997EFA-0926-402D-90C8-2404CE3AD3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49254C08-AB97-4150-B2DC-9AB957391877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="16065" windowWidth="14610" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-12960" yWindow="16290" windowWidth="12750" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10150" uniqueCount="1495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10328" uniqueCount="1501">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6386,15 +6386,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t xml:space="preserve">灰狼村 / </t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>戒狼村 / 北方(北方警戒所)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">戒狼村 / </t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -6704,6 +6696,98 @@
     </r>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <r>
+      <t>09:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>47</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">??? / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>染色工房</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">戒狼村 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>???</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">灰狼村 / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>???</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:54</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>03:08</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>15:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>07:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -6712,7 +6796,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="\'hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6844,6 +6928,12 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -6965,7 +7055,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7847,6 +7937,9 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -8386,7 +8479,7 @@
     <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="144" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="143"/>
+    <col min="13" max="13" width="13.25" style="144" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.625" style="143" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.375" style="143" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="6.625" style="143" bestFit="1" customWidth="1"/>
@@ -8426,6 +8519,7 @@
         <v>66</v>
       </c>
       <c r="L1" s="145"/>
+      <c r="M1" s="146"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
       <c r="A2" s="148" t="s">
@@ -8438,7 +8532,7 @@
       <c r="D2" s="149"/>
       <c r="E2" s="149"/>
       <c r="F2" s="287" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="G2" s="149" t="s">
         <v>17</v>
@@ -8457,6 +8551,9 @@
       </c>
       <c r="L2" s="148" t="s">
         <v>65</v>
+      </c>
+      <c r="M2" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N2" s="143" t="str">
         <f>IF($C2&lt;&gt;"",TEXT($C2,"HH:MM"),"")</f>
@@ -8507,6 +8604,9 @@
       </c>
       <c r="L3" s="148" t="s">
         <v>36</v>
+      </c>
+      <c r="M3" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N3" s="143" t="str">
         <f t="shared" ref="N3:N66" si="0">IF($C3&lt;&gt;"",TEXT($C3,"HH:MM"),"")</f>
@@ -8551,6 +8651,9 @@
       </c>
       <c r="L4" s="148" t="s">
         <v>35</v>
+      </c>
+      <c r="M4" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N4" s="143" t="str">
         <f t="shared" si="0"/>
@@ -8584,6 +8687,9 @@
       <c r="L5" s="148" t="s">
         <v>33</v>
       </c>
+      <c r="M5" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N5" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8633,6 +8739,9 @@
       </c>
       <c r="L6" s="148" t="s">
         <v>32</v>
+      </c>
+      <c r="M6" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N6" s="143" t="str">
         <f t="shared" si="0"/>
@@ -8678,6 +8787,9 @@
       <c r="L7" s="148" t="s">
         <v>31</v>
       </c>
+      <c r="M7" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N7" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8699,13 +8811,13 @@
         <v>60</v>
       </c>
       <c r="C8" s="287" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D8" s="149" t="s">
         <v>1456</v>
       </c>
-      <c r="D8" s="149" t="s">
+      <c r="E8" s="149" t="s">
         <v>1458</v>
-      </c>
-      <c r="E8" s="149" t="s">
-        <v>1460</v>
       </c>
       <c r="F8" s="153"/>
       <c r="G8" s="149"/>
@@ -8716,6 +8828,9 @@
       <c r="L8" s="148" t="s">
         <v>30</v>
       </c>
+      <c r="M8" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N8" s="143" t="str">
         <f t="shared" si="0"/>
         <v>06:46</v>
@@ -8740,7 +8855,7 @@
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
       <c r="F9" s="287" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G9" s="149" t="s">
         <v>17</v>
@@ -8759,6 +8874,9 @@
       </c>
       <c r="L9" s="148" t="s">
         <v>29</v>
+      </c>
+      <c r="M9" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N9" s="143" t="str">
         <f t="shared" si="0"/>
@@ -8803,6 +8921,9 @@
       </c>
       <c r="L10" s="148" t="s">
         <v>28</v>
+      </c>
+      <c r="M10" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N10" s="143" t="str">
         <f t="shared" si="0"/>
@@ -8842,6 +8963,9 @@
       <c r="L11" s="148" t="s">
         <v>26</v>
       </c>
+      <c r="M11" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N11" s="143" t="str">
         <f t="shared" si="0"/>
         <v>09:56</v>
@@ -8886,6 +9010,9 @@
       <c r="L12" s="148" t="s">
         <v>25</v>
       </c>
+      <c r="M12" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N12" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8929,6 +9056,9 @@
       </c>
       <c r="L13" s="148" t="s">
         <v>23</v>
+      </c>
+      <c r="M13" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N13" s="143" t="str">
         <f t="shared" si="0"/>
@@ -8962,6 +9092,9 @@
       <c r="L14" s="148" t="s">
         <v>22</v>
       </c>
+      <c r="M14" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N14" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -8986,10 +9119,10 @@
         <v>1284</v>
       </c>
       <c r="D15" s="149" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E15" s="149" t="s">
         <v>1457</v>
-      </c>
-      <c r="E15" s="149" t="s">
-        <v>1459</v>
       </c>
       <c r="F15" s="150" t="s">
         <v>809</v>
@@ -9011,6 +9144,9 @@
       </c>
       <c r="L15" s="148" t="s">
         <v>21</v>
+      </c>
+      <c r="M15" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N15" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9055,6 +9191,9 @@
       </c>
       <c r="L16" s="148" t="s">
         <v>20</v>
+      </c>
+      <c r="M16" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N16" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9088,6 +9227,9 @@
       <c r="L17" s="148" t="s">
         <v>18</v>
       </c>
+      <c r="M17" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N17" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9132,6 +9274,9 @@
       <c r="L18" s="148" t="s">
         <v>16</v>
       </c>
+      <c r="M18" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N18" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9156,10 +9301,10 @@
         <v>1372</v>
       </c>
       <c r="D19" s="149" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E19" s="149" t="s">
         <v>1467</v>
-      </c>
-      <c r="E19" s="149" t="s">
-        <v>1469</v>
       </c>
       <c r="F19" s="150" t="s">
         <v>216</v>
@@ -9181,6 +9326,9 @@
       </c>
       <c r="L19" s="148" t="s">
         <v>15</v>
+      </c>
+      <c r="M19" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N19" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9214,6 +9362,9 @@
       <c r="L20" s="148" t="s">
         <v>12</v>
       </c>
+      <c r="M20" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N20" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9258,6 +9409,9 @@
       <c r="L21" s="148" t="s">
         <v>10</v>
       </c>
+      <c r="M21" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N21" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9307,6 +9461,9 @@
       </c>
       <c r="L22" s="148" t="s">
         <v>9</v>
+      </c>
+      <c r="M22" s="149" t="s">
+        <v>60</v>
       </c>
       <c r="N22" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9340,6 +9497,9 @@
       <c r="L23" s="148" t="s">
         <v>6</v>
       </c>
+      <c r="M23" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N23" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9384,6 +9544,9 @@
       <c r="L24" s="148" t="s">
         <v>5</v>
       </c>
+      <c r="M24" s="149" t="s">
+        <v>60</v>
+      </c>
       <c r="N24" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9422,6 +9585,9 @@
       <c r="L25" s="154" t="s">
         <v>3</v>
       </c>
+      <c r="M25" s="155" t="s">
+        <v>60</v>
+      </c>
       <c r="N25" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9461,7 +9627,7 @@
         <v>1018</v>
       </c>
       <c r="I26" s="293" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="J26" s="158" t="s">
         <v>13</v>
@@ -9471,6 +9637,9 @@
       </c>
       <c r="L26" s="157" t="s">
         <v>37</v>
+      </c>
+      <c r="M26" s="158" t="s">
+        <v>58</v>
       </c>
       <c r="N26" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9515,6 +9684,9 @@
       </c>
       <c r="L27" s="157" t="s">
         <v>36</v>
+      </c>
+      <c r="M27" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N27" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9554,6 +9726,9 @@
       <c r="L28" s="157" t="s">
         <v>35</v>
       </c>
+      <c r="M28" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N28" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9592,6 +9767,9 @@
       <c r="L29" s="157" t="s">
         <v>33</v>
       </c>
+      <c r="M29" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N29" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9641,6 +9819,9 @@
       </c>
       <c r="L30" s="157" t="s">
         <v>32</v>
+      </c>
+      <c r="M30" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N30" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9679,6 +9860,9 @@
       <c r="K31" s="160"/>
       <c r="L31" s="157" t="s">
         <v>31</v>
+      </c>
+      <c r="M31" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N31" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9718,6 +9902,9 @@
       <c r="L32" s="157" t="s">
         <v>30</v>
       </c>
+      <c r="M32" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N32" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9739,13 +9926,13 @@
         <v>58</v>
       </c>
       <c r="C33" s="288" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D33" s="160" t="s">
         <v>1461</v>
       </c>
-      <c r="D33" s="160" t="s">
+      <c r="E33" s="160" t="s">
         <v>1463</v>
-      </c>
-      <c r="E33" s="160" t="s">
-        <v>1465</v>
       </c>
       <c r="F33" s="162" t="s">
         <v>887</v>
@@ -9767,6 +9954,9 @@
       </c>
       <c r="L33" s="157" t="s">
         <v>29</v>
+      </c>
+      <c r="M33" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N33" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9800,6 +9990,9 @@
       <c r="L34" s="157" t="s">
         <v>28</v>
       </c>
+      <c r="M34" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N34" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9824,7 +10017,7 @@
       <c r="D35" s="160"/>
       <c r="E35" s="160"/>
       <c r="F35" s="289" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="G35" s="160" t="s">
         <v>11</v>
@@ -9833,7 +10026,7 @@
         <v>1016</v>
       </c>
       <c r="I35" s="294" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="J35" s="160" t="s">
         <v>13</v>
@@ -9843,6 +10036,9 @@
       </c>
       <c r="L35" s="157" t="s">
         <v>26</v>
+      </c>
+      <c r="M35" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N35" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9868,10 +10064,10 @@
         <v>1294</v>
       </c>
       <c r="D36" s="160" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="F36" s="162" t="s">
         <v>1375</v>
@@ -9893,6 +10089,9 @@
       </c>
       <c r="L36" s="157" t="s">
         <v>25</v>
+      </c>
+      <c r="M36" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N36" s="143" t="str">
         <f t="shared" si="0"/>
@@ -9926,6 +10125,9 @@
       <c r="L37" s="157" t="s">
         <v>23</v>
       </c>
+      <c r="M37" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N37" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -9970,6 +10172,9 @@
       <c r="L38" s="157" t="s">
         <v>22</v>
       </c>
+      <c r="M38" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N38" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10009,7 +10214,7 @@
         <v>1017</v>
       </c>
       <c r="I39" s="289" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="J39" s="160" t="s">
         <v>4</v>
@@ -10019,6 +10224,9 @@
       </c>
       <c r="L39" s="157" t="s">
         <v>21</v>
+      </c>
+      <c r="M39" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N39" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10052,6 +10260,9 @@
       <c r="L40" s="157" t="s">
         <v>20</v>
       </c>
+      <c r="M40" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N40" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10096,6 +10307,9 @@
       <c r="L41" s="157" t="s">
         <v>18</v>
       </c>
+      <c r="M41" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N41" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10145,6 +10359,9 @@
       </c>
       <c r="L42" s="157" t="s">
         <v>16</v>
+      </c>
+      <c r="M42" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N42" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10178,6 +10395,9 @@
       <c r="L43" s="157" t="s">
         <v>15</v>
       </c>
+      <c r="M43" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N43" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10199,13 +10419,13 @@
         <v>58</v>
       </c>
       <c r="C44" s="289" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D44" s="160" t="s">
         <v>1466</v>
       </c>
-      <c r="D44" s="160" t="s">
+      <c r="E44" s="160" t="s">
         <v>1468</v>
-      </c>
-      <c r="E44" s="160" t="s">
-        <v>1470</v>
       </c>
       <c r="F44" s="161">
         <v>0.75277777777777777</v>
@@ -10227,6 +10447,9 @@
       </c>
       <c r="L44" s="157" t="s">
         <v>12</v>
+      </c>
+      <c r="M44" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N44" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10271,6 +10494,9 @@
       </c>
       <c r="L45" s="157" t="s">
         <v>10</v>
+      </c>
+      <c r="M45" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N45" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10304,6 +10530,9 @@
       <c r="L46" s="157" t="s">
         <v>9</v>
       </c>
+      <c r="M46" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N46" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10348,6 +10577,9 @@
       <c r="L47" s="157" t="s">
         <v>6</v>
       </c>
+      <c r="M47" s="160" t="s">
+        <v>58</v>
+      </c>
       <c r="N47" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10372,10 +10604,10 @@
         <v>1302</v>
       </c>
       <c r="D48" s="160" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E48" s="160" t="s">
         <v>1462</v>
-      </c>
-      <c r="E48" s="160" t="s">
-        <v>1464</v>
       </c>
       <c r="F48" s="162" t="s">
         <v>1381</v>
@@ -10397,6 +10629,9 @@
       </c>
       <c r="L48" s="157" t="s">
         <v>5</v>
+      </c>
+      <c r="M48" s="160" t="s">
+        <v>58</v>
       </c>
       <c r="N48" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10436,6 +10671,9 @@
       <c r="L49" s="165" t="s">
         <v>3</v>
       </c>
+      <c r="M49" s="166" t="s">
+        <v>58</v>
+      </c>
       <c r="N49" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10480,6 +10718,9 @@
       <c r="L50" s="168" t="s">
         <v>37</v>
       </c>
+      <c r="M50" s="169" t="s">
+        <v>55</v>
+      </c>
       <c r="N50" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10524,6 +10765,9 @@
       <c r="L51" s="168" t="s">
         <v>36</v>
       </c>
+      <c r="M51" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N51" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10545,13 +10789,13 @@
         <v>55</v>
       </c>
       <c r="C52" s="173" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D52" s="290" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E52" s="171" t="s">
         <v>1471</v>
-      </c>
-      <c r="D52" s="290" t="s">
-        <v>1472</v>
-      </c>
-      <c r="E52" s="171" t="s">
-        <v>1473</v>
       </c>
       <c r="F52" s="173"/>
       <c r="G52" s="171"/>
@@ -10562,6 +10806,9 @@
       <c r="L52" s="168" t="s">
         <v>35</v>
       </c>
+      <c r="M52" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N52" s="143" t="str">
         <f t="shared" si="0"/>
         <v>02:40</v>
@@ -10606,6 +10853,9 @@
       <c r="L53" s="168" t="s">
         <v>33</v>
       </c>
+      <c r="M53" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N53" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10630,7 +10880,7 @@
       <c r="D54" s="171"/>
       <c r="E54" s="171"/>
       <c r="F54" s="290" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="G54" s="171" t="s">
         <v>17</v>
@@ -10639,7 +10889,7 @@
         <v>1017</v>
       </c>
       <c r="I54" s="290" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="J54" s="171" t="s">
         <v>4</v>
@@ -10649,6 +10899,9 @@
       </c>
       <c r="L54" s="168" t="s">
         <v>32</v>
+      </c>
+      <c r="M54" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N54" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10682,6 +10935,9 @@
       <c r="L55" s="168" t="s">
         <v>31</v>
       </c>
+      <c r="M55" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N55" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -10732,6 +10988,9 @@
       <c r="L56" s="168" t="s">
         <v>30</v>
       </c>
+      <c r="M56" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N56" s="143" t="str">
         <f t="shared" si="0"/>
         <v>06:00</v>
@@ -10782,6 +11041,9 @@
       <c r="L57" s="168" t="s">
         <v>29</v>
       </c>
+      <c r="M57" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N57" s="143" t="str">
         <f t="shared" si="0"/>
         <v>07:00</v>
@@ -10832,6 +11094,9 @@
       <c r="L58" s="168" t="s">
         <v>28</v>
       </c>
+      <c r="M58" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N58" s="143" t="str">
         <f t="shared" si="0"/>
         <v>08:00</v>
@@ -10853,12 +11118,14 @@
         <v>55</v>
       </c>
       <c r="C59" s="172" t="s">
-        <v>79</v>
+        <v>1493</v>
       </c>
       <c r="D59" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="E59" s="171"/>
+      <c r="E59" s="295" t="s">
+        <v>1494</v>
+      </c>
       <c r="F59" s="171" t="s">
         <v>79</v>
       </c>
@@ -10876,9 +11143,12 @@
       <c r="L59" s="168" t="s">
         <v>26</v>
       </c>
+      <c r="M59" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N59" s="143" t="str">
         <f t="shared" si="0"/>
-        <v>09:00</v>
+        <v>09:47</v>
       </c>
       <c r="O59" s="143" t="str">
         <f t="shared" si="1"/>
@@ -10919,6 +11189,9 @@
       <c r="K60" s="171"/>
       <c r="L60" s="168" t="s">
         <v>25</v>
+      </c>
+      <c r="M60" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N60" s="143" t="str">
         <f t="shared" si="0"/>
@@ -10964,6 +11237,9 @@
       <c r="L61" s="168" t="s">
         <v>23</v>
       </c>
+      <c r="M61" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N61" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -11013,6 +11289,9 @@
       </c>
       <c r="L62" s="168" t="s">
         <v>22</v>
+      </c>
+      <c r="M62" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N62" s="143" t="str">
         <f t="shared" si="0"/>
@@ -11057,6 +11336,9 @@
       </c>
       <c r="L63" s="168" t="s">
         <v>21</v>
+      </c>
+      <c r="M63" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N63" s="143" t="str">
         <f t="shared" si="0"/>
@@ -11090,6 +11372,9 @@
       <c r="L64" s="168" t="s">
         <v>20</v>
       </c>
+      <c r="M64" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N64" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -11134,6 +11419,9 @@
       <c r="L65" s="168" t="s">
         <v>18</v>
       </c>
+      <c r="M65" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N65" s="143" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -11183,6 +11471,9 @@
       </c>
       <c r="L66" s="168" t="s">
         <v>16</v>
+      </c>
+      <c r="M66" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N66" s="143" t="str">
         <f t="shared" si="0"/>
@@ -11216,6 +11507,9 @@
       <c r="L67" s="168" t="s">
         <v>15</v>
       </c>
+      <c r="M67" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N67" s="143" t="str">
         <f t="shared" ref="N67:N130" si="3">IF($C67&lt;&gt;"",TEXT($C67,"HH:MM"),"")</f>
         <v/>
@@ -11260,6 +11554,9 @@
       <c r="L68" s="168" t="s">
         <v>12</v>
       </c>
+      <c r="M68" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N68" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11309,6 +11606,9 @@
       </c>
       <c r="L69" s="168" t="s">
         <v>10</v>
+      </c>
+      <c r="M69" s="171" t="s">
+        <v>55</v>
       </c>
       <c r="N69" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11342,6 +11642,9 @@
       <c r="L70" s="168" t="s">
         <v>9</v>
       </c>
+      <c r="M70" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N70" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11386,6 +11689,9 @@
       <c r="L71" s="168" t="s">
         <v>6</v>
       </c>
+      <c r="M71" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N71" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11430,6 +11736,9 @@
       <c r="L72" s="168" t="s">
         <v>5</v>
       </c>
+      <c r="M72" s="171" t="s">
+        <v>55</v>
+      </c>
       <c r="N72" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11457,7 +11766,7 @@
         <v>1365</v>
       </c>
       <c r="E73" s="175" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F73" s="176"/>
       <c r="G73" s="175"/>
@@ -11468,6 +11777,9 @@
       <c r="L73" s="174" t="s">
         <v>3</v>
       </c>
+      <c r="M73" s="175" t="s">
+        <v>55</v>
+      </c>
       <c r="N73" s="143" t="str">
         <f t="shared" si="3"/>
         <v>23:32</v>
@@ -11512,6 +11824,9 @@
       <c r="L74" s="177" t="s">
         <v>37</v>
       </c>
+      <c r="M74" s="178" t="s">
+        <v>52</v>
+      </c>
       <c r="N74" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11556,6 +11871,9 @@
       <c r="L75" s="177" t="s">
         <v>36</v>
       </c>
+      <c r="M75" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N75" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11583,7 +11901,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F76" s="181"/>
       <c r="G76" s="180"/>
@@ -11594,6 +11912,9 @@
       <c r="L76" s="177" t="s">
         <v>35</v>
       </c>
+      <c r="M76" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N76" s="143" t="str">
         <f t="shared" si="3"/>
         <v>02:40</v>
@@ -11620,12 +11941,21 @@
       <c r="F77" s="181"/>
       <c r="G77" s="180"/>
       <c r="H77" s="180"/>
-      <c r="I77" s="181"/>
-      <c r="J77" s="180"/>
-      <c r="K77" s="180"/>
+      <c r="I77" s="291" t="s">
+        <v>1498</v>
+      </c>
+      <c r="J77" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K77" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L77" s="177" t="s">
         <v>33</v>
       </c>
+      <c r="M77" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N77" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11636,7 +11966,7 @@
       </c>
       <c r="P77" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>03:08</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1">
@@ -11650,7 +11980,7 @@
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
       <c r="F78" s="181" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="G78" s="180" t="s">
         <v>11</v>
@@ -11659,7 +11989,7 @@
         <v>1016</v>
       </c>
       <c r="I78" s="291" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="J78" s="180" t="s">
         <v>13</v>
@@ -11669,6 +11999,9 @@
       </c>
       <c r="L78" s="177" t="s">
         <v>32</v>
+      </c>
+      <c r="M78" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N78" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11708,6 +12041,9 @@
       <c r="L79" s="177" t="s">
         <v>31</v>
       </c>
+      <c r="M79" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N79" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11729,13 +12065,13 @@
         <v>52</v>
       </c>
       <c r="C80" s="291" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D80" s="180" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E80" s="180" t="s">
         <v>1474</v>
-      </c>
-      <c r="D80" s="180" t="s">
-        <v>1475</v>
-      </c>
-      <c r="E80" s="180" t="s">
-        <v>1476</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="180"/>
@@ -11752,6 +12088,9 @@
       <c r="L80" s="177" t="s">
         <v>30</v>
       </c>
+      <c r="M80" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N80" s="143" t="str">
         <f t="shared" si="3"/>
         <v>06:03</v>
@@ -11776,7 +12115,7 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="G81" s="180" t="s">
         <v>17</v>
@@ -11795,6 +12134,9 @@
       </c>
       <c r="L81" s="177" t="s">
         <v>29</v>
+      </c>
+      <c r="M81" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N81" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11817,16 +12159,16 @@
         <v>52</v>
       </c>
       <c r="C82" s="181" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D82" s="180" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E82" s="180" t="s">
         <v>1449</v>
       </c>
-      <c r="D82" s="180" t="s">
-        <v>1450</v>
-      </c>
-      <c r="E82" s="180" t="s">
-        <v>1451</v>
-      </c>
       <c r="F82" s="181" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="G82" s="180" t="s">
         <v>17</v>
@@ -11839,6 +12181,9 @@
       <c r="K82" s="180"/>
       <c r="L82" s="177" t="s">
         <v>28</v>
+      </c>
+      <c r="M82" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N82" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11878,6 +12223,9 @@
       <c r="L83" s="177" t="s">
         <v>26</v>
       </c>
+      <c r="M83" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N83" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -11902,7 +12250,7 @@
       <c r="D84" s="180"/>
       <c r="E84" s="180"/>
       <c r="F84" s="181" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="G84" s="180" t="s">
         <v>0</v>
@@ -11911,7 +12259,7 @@
         <v>1018</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="J84" s="180" t="s">
         <v>4</v>
@@ -11921,6 +12269,9 @@
       </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
+      </c>
+      <c r="M84" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N84" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11946,13 +12297,13 @@
         <v>1439</v>
       </c>
       <c r="D85" s="180" t="s">
-        <v>1440</v>
+        <v>1496</v>
       </c>
       <c r="E85" s="180" t="s">
-        <v>1442</v>
+        <v>1495</v>
       </c>
       <c r="F85" s="181" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="G85" s="180" t="s">
         <v>17</v>
@@ -11965,6 +12316,9 @@
       <c r="K85" s="180"/>
       <c r="L85" s="177" t="s">
         <v>23</v>
+      </c>
+      <c r="M85" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N85" s="143" t="str">
         <f t="shared" si="3"/>
@@ -11993,7 +12347,7 @@
       <c r="G86" s="180"/>
       <c r="H86" s="180"/>
       <c r="I86" s="182" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="J86" s="180" t="s">
         <v>4</v>
@@ -12003,6 +12357,9 @@
       </c>
       <c r="L86" s="177" t="s">
         <v>22</v>
+      </c>
+      <c r="M86" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N86" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12031,7 +12388,7 @@
       <c r="G87" s="180"/>
       <c r="H87" s="180"/>
       <c r="I87" s="181" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -12041,6 +12398,9 @@
       </c>
       <c r="L87" s="177" t="s">
         <v>21</v>
+      </c>
+      <c r="M87" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N87" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12063,30 +12423,39 @@
         <v>52</v>
       </c>
       <c r="C88" s="181" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="D88" s="180" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E88" s="180" t="s">
         <v>1446</v>
       </c>
-      <c r="E88" s="180" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F88" s="181"/>
-      <c r="G88" s="180"/>
-      <c r="H88" s="180"/>
+      <c r="F88" s="291" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G88" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="H88" s="180" t="s">
+        <v>1018</v>
+      </c>
       <c r="I88" s="181"/>
       <c r="J88" s="180"/>
       <c r="K88" s="180"/>
       <c r="L88" s="177" t="s">
         <v>20</v>
       </c>
+      <c r="M88" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N88" s="143" t="str">
         <f t="shared" si="3"/>
         <v>14:30</v>
       </c>
       <c r="O88" s="143" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14:54</v>
       </c>
       <c r="P88" s="143" t="str">
         <f t="shared" si="5"/>
@@ -12106,12 +12475,21 @@
       <c r="F89" s="181"/>
       <c r="G89" s="180"/>
       <c r="H89" s="180"/>
-      <c r="I89" s="182"/>
-      <c r="J89" s="180"/>
-      <c r="K89" s="180"/>
+      <c r="I89" s="276" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J89" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L89" s="177" t="s">
         <v>18</v>
       </c>
+      <c r="M89" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N89" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12122,7 +12500,7 @@
       </c>
       <c r="P89" s="143" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>15:00</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="18" customHeight="1">
@@ -12156,6 +12534,9 @@
       <c r="L90" s="177" t="s">
         <v>16</v>
       </c>
+      <c r="M90" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N90" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12199,6 +12580,9 @@
       </c>
       <c r="L91" s="177" t="s">
         <v>15</v>
+      </c>
+      <c r="M91" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N91" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12238,6 +12622,9 @@
       <c r="L92" s="177" t="s">
         <v>12</v>
       </c>
+      <c r="M92" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N92" s="143" t="str">
         <f t="shared" si="3"/>
         <v>18:06</v>
@@ -12282,6 +12669,9 @@
       <c r="L93" s="177" t="s">
         <v>10</v>
       </c>
+      <c r="M93" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N93" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12325,6 +12715,9 @@
       </c>
       <c r="L94" s="177" t="s">
         <v>9</v>
+      </c>
+      <c r="M94" s="180" t="s">
+        <v>52</v>
       </c>
       <c r="N94" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12364,6 +12757,9 @@
       <c r="L95" s="177" t="s">
         <v>6</v>
       </c>
+      <c r="M95" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N95" s="143" t="str">
         <f t="shared" si="3"/>
         <v>21:04</v>
@@ -12408,6 +12804,9 @@
       <c r="L96" s="177" t="s">
         <v>5</v>
       </c>
+      <c r="M96" s="180" t="s">
+        <v>52</v>
+      </c>
       <c r="N96" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12446,6 +12845,9 @@
       <c r="L97" s="183" t="s">
         <v>3</v>
       </c>
+      <c r="M97" s="184" t="s">
+        <v>52</v>
+      </c>
       <c r="N97" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12470,10 +12872,10 @@
         <v>1323</v>
       </c>
       <c r="D98" s="187" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E98" s="187" t="s">
         <v>1452</v>
-      </c>
-      <c r="E98" s="187" t="s">
-        <v>1454</v>
       </c>
       <c r="F98" s="188"/>
       <c r="G98" s="187"/>
@@ -12490,6 +12892,9 @@
       <c r="L98" s="186" t="s">
         <v>37</v>
       </c>
+      <c r="M98" s="187" t="s">
+        <v>44</v>
+      </c>
       <c r="N98" s="143" t="str">
         <f t="shared" si="3"/>
         <v>00:26</v>
@@ -12534,6 +12939,9 @@
       <c r="L99" s="186" t="s">
         <v>36</v>
       </c>
+      <c r="M99" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N99" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12577,6 +12985,9 @@
       </c>
       <c r="L100" s="186" t="s">
         <v>35</v>
+      </c>
+      <c r="M100" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N100" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12616,6 +13027,9 @@
       <c r="L101" s="186" t="s">
         <v>33</v>
       </c>
+      <c r="M101" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N101" s="143" t="str">
         <f t="shared" si="3"/>
         <v>03:06</v>
@@ -12660,6 +13074,9 @@
       <c r="L102" s="186" t="s">
         <v>32</v>
       </c>
+      <c r="M102" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N102" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12698,6 +13115,9 @@
       <c r="L103" s="186" t="s">
         <v>31</v>
       </c>
+      <c r="M103" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N103" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12722,7 +13142,7 @@
       <c r="D104" s="189"/>
       <c r="E104" s="189"/>
       <c r="F104" s="190" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="G104" s="189" t="s">
         <v>0</v>
@@ -12741,6 +13161,9 @@
       </c>
       <c r="L104" s="186" t="s">
         <v>30</v>
+      </c>
+      <c r="M104" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N104" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12786,6 +13209,9 @@
       <c r="L105" s="186" t="s">
         <v>29</v>
       </c>
+      <c r="M105" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N105" s="143" t="str">
         <f t="shared" si="3"/>
         <v>07:15</v>
@@ -12824,6 +13250,9 @@
       <c r="L106" s="186" t="s">
         <v>28</v>
       </c>
+      <c r="M106" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N106" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12867,6 +13296,9 @@
       </c>
       <c r="L107" s="186" t="s">
         <v>26</v>
+      </c>
+      <c r="M107" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N107" s="143" t="str">
         <f t="shared" si="3"/>
@@ -12906,6 +13338,9 @@
       <c r="L108" s="186" t="s">
         <v>25</v>
       </c>
+      <c r="M108" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N108" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -12950,6 +13385,9 @@
       <c r="L109" s="186" t="s">
         <v>23</v>
       </c>
+      <c r="M109" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N109" s="143" t="str">
         <f t="shared" si="3"/>
         <v>11:42</v>
@@ -12993,6 +13431,9 @@
       </c>
       <c r="L110" s="186" t="s">
         <v>22</v>
+      </c>
+      <c r="M110" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N110" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13032,6 +13473,9 @@
       <c r="L111" s="186" t="s">
         <v>21</v>
       </c>
+      <c r="M111" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N111" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13076,6 +13520,9 @@
       <c r="L112" s="186" t="s">
         <v>20</v>
       </c>
+      <c r="M112" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N112" s="143" t="str">
         <f t="shared" si="3"/>
         <v>14:40</v>
@@ -13119,6 +13566,9 @@
       </c>
       <c r="L113" s="186" t="s">
         <v>18</v>
+      </c>
+      <c r="M113" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N113" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13158,6 +13608,9 @@
       <c r="L114" s="186" t="s">
         <v>16</v>
       </c>
+      <c r="M114" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N114" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13196,6 +13649,9 @@
       <c r="L115" s="186" t="s">
         <v>15</v>
       </c>
+      <c r="M115" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N115" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13245,6 +13701,9 @@
       </c>
       <c r="L116" s="186" t="s">
         <v>12</v>
+      </c>
+      <c r="M116" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N116" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13284,6 +13743,9 @@
       <c r="L117" s="186" t="s">
         <v>10</v>
       </c>
+      <c r="M117" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N117" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13322,6 +13784,9 @@
       <c r="L118" s="186" t="s">
         <v>9</v>
       </c>
+      <c r="M118" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N118" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13371,6 +13836,9 @@
       </c>
       <c r="L119" s="186" t="s">
         <v>6</v>
+      </c>
+      <c r="M119" s="189" t="s">
+        <v>44</v>
       </c>
       <c r="N119" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13410,6 +13878,9 @@
       <c r="L120" s="186" t="s">
         <v>5</v>
       </c>
+      <c r="M120" s="189" t="s">
+        <v>44</v>
+      </c>
       <c r="N120" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13448,6 +13919,9 @@
       <c r="L121" s="192" t="s">
         <v>3</v>
       </c>
+      <c r="M121" s="193" t="s">
+        <v>44</v>
+      </c>
       <c r="N121" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13472,10 +13946,10 @@
         <v>1336</v>
       </c>
       <c r="D122" s="196" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E122" s="196" t="s">
         <v>1453</v>
-      </c>
-      <c r="E122" s="196" t="s">
-        <v>1455</v>
       </c>
       <c r="F122" s="197" t="s">
         <v>141</v>
@@ -13497,6 +13971,9 @@
       </c>
       <c r="L122" s="195" t="s">
         <v>37</v>
+      </c>
+      <c r="M122" s="196" t="s">
+        <v>38</v>
       </c>
       <c r="N122" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13542,6 +14019,9 @@
       <c r="L123" s="195" t="s">
         <v>36</v>
       </c>
+      <c r="M123" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N123" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13585,6 +14065,9 @@
       </c>
       <c r="L124" s="195" t="s">
         <v>35</v>
+      </c>
+      <c r="M124" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N124" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13618,6 +14101,9 @@
       <c r="L125" s="195" t="s">
         <v>33</v>
       </c>
+      <c r="M125" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N125" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13667,6 +14153,9 @@
       </c>
       <c r="L126" s="195" t="s">
         <v>32</v>
+      </c>
+      <c r="M126" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N126" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13701,7 +14190,7 @@
         <v>1018</v>
       </c>
       <c r="I127" s="199" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="J127" s="198" t="s">
         <v>13</v>
@@ -13711,6 +14200,9 @@
       </c>
       <c r="L127" s="195" t="s">
         <v>31</v>
+      </c>
+      <c r="M127" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N127" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13744,6 +14236,9 @@
       <c r="L128" s="195" t="s">
         <v>30</v>
       </c>
+      <c r="M128" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N128" s="143" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -13783,7 +14278,7 @@
         <v>1017</v>
       </c>
       <c r="I129" s="200" t="s">
-        <v>1338</v>
+        <v>1500</v>
       </c>
       <c r="J129" s="198" t="s">
         <v>13</v>
@@ -13793,6 +14288,9 @@
       </c>
       <c r="L129" s="195" t="s">
         <v>29</v>
+      </c>
+      <c r="M129" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N129" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13804,7 +14302,7 @@
       </c>
       <c r="P129" s="143" t="str">
         <f t="shared" si="5"/>
-        <v>07:19</v>
+        <v>07:20</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="18" customHeight="1">
@@ -13837,6 +14335,9 @@
       </c>
       <c r="L130" s="195" t="s">
         <v>28</v>
+      </c>
+      <c r="M130" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N130" s="143" t="str">
         <f t="shared" si="3"/>
@@ -13870,6 +14371,9 @@
       <c r="L131" s="195" t="s">
         <v>26</v>
       </c>
+      <c r="M131" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N131" s="143" t="str">
         <f t="shared" ref="N131:N169" si="6">IF($C131&lt;&gt;"",TEXT($C131,"HH:MM"),"")</f>
         <v/>
@@ -13919,6 +14423,9 @@
       </c>
       <c r="L132" s="195" t="s">
         <v>25</v>
+      </c>
+      <c r="M132" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N132" s="143" t="str">
         <f t="shared" si="6"/>
@@ -13958,6 +14465,9 @@
       <c r="L133" s="195" t="s">
         <v>23</v>
       </c>
+      <c r="M133" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N133" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -13996,6 +14506,9 @@
       <c r="L134" s="195" t="s">
         <v>22</v>
       </c>
+      <c r="M134" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N134" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14045,6 +14558,9 @@
       </c>
       <c r="L135" s="195" t="s">
         <v>21</v>
+      </c>
+      <c r="M135" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N135" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14089,6 +14605,9 @@
       </c>
       <c r="L136" s="195" t="s">
         <v>20</v>
+      </c>
+      <c r="M136" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N136" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14122,6 +14641,9 @@
       <c r="L137" s="195" t="s">
         <v>18</v>
       </c>
+      <c r="M137" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N137" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14166,6 +14688,9 @@
       <c r="L138" s="195">
         <v>16</v>
       </c>
+      <c r="M138" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N138" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14209,6 +14734,9 @@
       </c>
       <c r="L139" s="195" t="s">
         <v>15</v>
+      </c>
+      <c r="M139" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N139" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14248,6 +14776,9 @@
       <c r="L140" s="195" t="s">
         <v>12</v>
       </c>
+      <c r="M140" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N140" s="143" t="str">
         <f t="shared" si="6"/>
         <v>18:03</v>
@@ -14292,6 +14823,9 @@
       <c r="L141" s="195" t="s">
         <v>10</v>
       </c>
+      <c r="M141" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N141" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14335,6 +14869,9 @@
       </c>
       <c r="L142" s="195" t="s">
         <v>9</v>
+      </c>
+      <c r="M142" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N142" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14368,6 +14905,9 @@
       <c r="L143" s="195" t="s">
         <v>6</v>
       </c>
+      <c r="M143" s="198" t="s">
+        <v>38</v>
+      </c>
       <c r="N143" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14417,6 +14957,9 @@
       </c>
       <c r="L144" s="195" t="s">
         <v>5</v>
+      </c>
+      <c r="M144" s="198" t="s">
+        <v>38</v>
       </c>
       <c r="N144" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14462,6 +15005,9 @@
       <c r="L145" s="202" t="s">
         <v>3</v>
       </c>
+      <c r="M145" s="203" t="s">
+        <v>38</v>
+      </c>
       <c r="N145" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14499,6 +15045,9 @@
       <c r="K146" s="206"/>
       <c r="L146" s="205" t="s">
         <v>37</v>
+      </c>
+      <c r="M146" s="206" t="s">
+        <v>2</v>
       </c>
       <c r="N146" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14538,6 +15087,9 @@
       <c r="L147" s="205" t="s">
         <v>36</v>
       </c>
+      <c r="M147" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N147" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14587,6 +15139,9 @@
       </c>
       <c r="L148" s="205" t="s">
         <v>35</v>
+      </c>
+      <c r="M148" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N148" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14625,6 +15180,9 @@
       <c r="K149" s="208"/>
       <c r="L149" s="205" t="s">
         <v>33</v>
+      </c>
+      <c r="M149" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N149" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14664,6 +15222,9 @@
       <c r="L150" s="205" t="s">
         <v>32</v>
       </c>
+      <c r="M150" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N150" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14708,6 +15269,9 @@
       <c r="L151" s="205" t="s">
         <v>31</v>
       </c>
+      <c r="M151" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N151" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14729,7 +15293,7 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="D152" s="208" t="s">
         <v>45</v>
@@ -14751,6 +15315,9 @@
       <c r="K152" s="208"/>
       <c r="L152" s="205" t="s">
         <v>30</v>
+      </c>
+      <c r="M152" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N152" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14790,6 +15357,9 @@
       <c r="L153" s="205" t="s">
         <v>29</v>
       </c>
+      <c r="M153" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N153" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14834,6 +15404,9 @@
       <c r="L154" s="205" t="s">
         <v>28</v>
       </c>
+      <c r="M154" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N154" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14877,6 +15450,9 @@
       <c r="K155" s="208"/>
       <c r="L155" s="205" t="s">
         <v>26</v>
+      </c>
+      <c r="M155" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N155" s="143" t="str">
         <f t="shared" si="6"/>
@@ -14916,6 +15492,9 @@
       <c r="L156" s="205" t="s">
         <v>25</v>
       </c>
+      <c r="M156" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N156" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -14960,6 +15539,9 @@
       <c r="L157" s="205" t="s">
         <v>23</v>
       </c>
+      <c r="M157" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N157" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15003,6 +15585,9 @@
       <c r="K158" s="208"/>
       <c r="L158" s="205" t="s">
         <v>22</v>
+      </c>
+      <c r="M158" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N158" s="143" t="str">
         <f t="shared" si="6"/>
@@ -15042,6 +15627,9 @@
       <c r="L159" s="205" t="s">
         <v>21</v>
       </c>
+      <c r="M159" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N159" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15086,6 +15674,9 @@
       <c r="L160" s="205" t="s">
         <v>20</v>
       </c>
+      <c r="M160" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N160" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15129,6 +15720,9 @@
       <c r="K161" s="208"/>
       <c r="L161" s="205" t="s">
         <v>18</v>
+      </c>
+      <c r="M161" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N161" s="143" t="str">
         <f t="shared" si="6"/>
@@ -15168,6 +15762,9 @@
       <c r="L162" s="205" t="s">
         <v>16</v>
       </c>
+      <c r="M162" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N162" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15212,6 +15809,9 @@
       <c r="L163" s="205" t="s">
         <v>15</v>
       </c>
+      <c r="M163" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N163" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15250,6 +15850,9 @@
       <c r="L164" s="205" t="s">
         <v>12</v>
       </c>
+      <c r="M164" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N164" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15294,6 +15897,9 @@
       <c r="L165" s="205" t="s">
         <v>10</v>
       </c>
+      <c r="M165" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N165" s="143" t="str">
         <f t="shared" si="6"/>
         <v>19:16</v>
@@ -15318,7 +15924,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="292" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="G166" s="208" t="s">
         <v>17</v>
@@ -15337,6 +15943,9 @@
       </c>
       <c r="L166" s="205" t="s">
         <v>9</v>
+      </c>
+      <c r="M166" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N166" s="143" t="str">
         <f t="shared" si="6"/>
@@ -15376,6 +15985,9 @@
       <c r="L167" s="205" t="s">
         <v>6</v>
       </c>
+      <c r="M167" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N167" s="143" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -15420,6 +16032,9 @@
       <c r="L168" s="205" t="s">
         <v>5</v>
       </c>
+      <c r="M168" s="208" t="s">
+        <v>2</v>
+      </c>
       <c r="N168" s="143" t="str">
         <f t="shared" si="6"/>
         <v>22:10</v>
@@ -15463,6 +16078,9 @@
       </c>
       <c r="L169" s="205" t="s">
         <v>3</v>
+      </c>
+      <c r="M169" s="208" t="s">
+        <v>2</v>
       </c>
       <c r="N169" s="143" t="str">
         <f t="shared" si="6"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC16BCD7-3A1A-454F-BE87-A5F6A348050F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C1AE0D-FFD0-428D-BC52-6A2592E0741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20220" yWindow="16290" windowWidth="20010" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22245" yWindow="16230" windowWidth="22275" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
     <sheet name="S3_三四週" sheetId="10" r:id="rId2"/>
-    <sheet name="S3_zh第二週" sheetId="9" r:id="rId3"/>
-    <sheet name="S3_zh_jp_第一週" sheetId="7" r:id="rId4"/>
-    <sheet name="S2_jp_20251015-20251112" sheetId="1" r:id="rId5"/>
-    <sheet name="S2_zh第四週" sheetId="6" r:id="rId6"/>
-    <sheet name="S2_zh第三週" sheetId="3" r:id="rId7"/>
-    <sheet name="S2_zh第二週" sheetId="5" r:id="rId8"/>
-    <sheet name="S2_zh第一週" sheetId="4" r:id="rId9"/>
-    <sheet name="S1_20250903-1015" sheetId="2" r:id="rId10"/>
+    <sheet name="S3_zh第二週" sheetId="9" state="hidden" r:id="rId3"/>
+    <sheet name="S3_zh_jp_第一週" sheetId="7" state="hidden" r:id="rId4"/>
+    <sheet name="S2_jp_20251015-20251112" sheetId="1" state="hidden" r:id="rId5"/>
+    <sheet name="S2_zh第四週" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="S2_zh第三週" sheetId="3" state="hidden" r:id="rId7"/>
+    <sheet name="S2_zh第二週" sheetId="5" state="hidden" r:id="rId8"/>
+    <sheet name="S2_zh第一週" sheetId="4" state="hidden" r:id="rId9"/>
+    <sheet name="S1_20250903-1015" sheetId="2" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'S1_20250903-1015'!$B$1:$K$169</definedName>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11094" uniqueCount="1489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11690" uniqueCount="1610">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6458,14 +6458,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>黑森林 / 孤村</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>黒影林 / 孤独の村</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>06:03</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6715,53 +6707,157 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>05:00</t>
+    <t>05 - 11 例行維護中</t>
+  </si>
+  <si>
+    <t>06-10 定期メンテナンス中</t>
+  </si>
+  <si>
+    <t>11:40</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>13:14</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:43</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16:16</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>14:04</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>18:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:10</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20:23</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16:51</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12:23</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:13</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20:22</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:56</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 渡門旅館</t>
+  </si>
+  <si>
+    <t>黒影林 / 染色工房</t>
+  </si>
+  <si>
+    <t>戒狼村 / ？？？</t>
+  </si>
+  <si>
+    <t>黒影林 / ？？？</t>
+  </si>
+  <si>
+    <t>？？？ / 染色工房</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>18:32</t>
+  </si>
+  <si>
+    <t>19:57</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>20:49</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>07:26</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>新緑</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑神戾</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑鯰王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05 - 11 例行維護中</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06-10 定期メンテナンス中</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>5</t>
+      <t>06-10 定期</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Microsoft JhengHei UI"/>
         <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
         <charset val="128"/>
-      </rPr>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 定期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-        <charset val="136"/>
       </rPr>
       <t>メンテナンス</t>
     </r>
@@ -6773,24 +6869,318 @@
       </rPr>
       <t>中</t>
     </r>
+  </si>
+  <si>
+    <t>黒影林 / ？？？</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>05-10 定期メンテナンス中</t>
-  </si>
-  <si>
-    <t>03:30</t>
+    <t>敵萬夫</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>04:00</t>
+    <t>鬼蛮</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>0330 - 11 例行維護中</t>
-  </si>
-  <si>
-    <t>0330 - 11 例行維護中</t>
+    <t>黒獣神</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>万</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>霊キョンシー</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:54</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>11:15</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>18:01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>？？？ / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>11:40</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戒狼村 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:18</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:24</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>17:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>？？？ / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤独の村 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05:54</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>12:01</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>16:32</t>
+  </si>
+  <si>
+    <t>18:02</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>07:28</t>
+  </si>
+  <si>
+    <t>13:31</t>
+  </si>
+  <si>
+    <t>13:01</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>17:56</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>19:03</t>
+  </si>
+  <si>
+    <t>20:47</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:16</t>
+  </si>
+  <si>
+    <t>05:29</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>14:43</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>17:26</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>22:29</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>11:58</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>17:38</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>22:01</t>
+  </si>
+  <si>
+    <t>23:28</t>
+  </si>
+  <si>
+    <t>04:01</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>15:42</t>
+  </si>
+  <si>
+    <t>15:58</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>18:53</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>20:27</t>
+  </si>
+  <si>
+    <t>21:36</t>
+  </si>
+  <si>
+    <t>23:08</t>
+  </si>
+  <si>
+    <t>敵萬夫</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鬼蛮</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑神戾</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒獣神</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑鯰王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナマズ王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>萬年殭屍</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>万霊キョンシー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>14:48</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新緑</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風之風之平原</t>
+  </si>
+  <si>
+    <t>オオウスバ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>22:01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / ？？？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>21:47</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海岸旅館</t>
+    <rPh sb="0" eb="2">
+      <t>カイガン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リョカン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7060,7 +7450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7945,11 +8335,105 @@
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8101,62 +8585,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8528,57 +8956,57 @@
   <dimension ref="A1:P169"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="144" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="144" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="144" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="212" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="144" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.375" style="144" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="6.625" style="143" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.25" style="143"/>
+    <col min="11" max="11" width="22.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.375" style="212" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="6.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.25" style="151"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="142" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="145"/>
-      <c r="B1" s="146" t="s">
+    <row r="1" spans="1:16" s="147" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="296" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="146" t="s">
+      <c r="C1" s="296" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="146" t="s">
+      <c r="D1" s="296" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="146" t="s">
+      <c r="E1" s="296" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="146" t="s">
+      <c r="F1" s="296" t="s">
         <v>140</v>
       </c>
-      <c r="G1" s="146" t="s">
+      <c r="G1" s="296" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="146" t="s">
+      <c r="H1" s="296" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="146" t="s">
+      <c r="I1" s="296" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="146" t="s">
+      <c r="J1" s="296" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="146" t="s">
+      <c r="K1" s="296" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="146"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="296"/>
     </row>
     <row r="2" spans="1:16" ht="18" customHeight="1">
       <c r="A2" s="148" t="s">
@@ -8590,29 +9018,41 @@
       <c r="C2" s="150"/>
       <c r="D2" s="149"/>
       <c r="E2" s="149"/>
-      <c r="F2" s="287"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="150"/>
-      <c r="J2" s="149"/>
-      <c r="K2" s="149"/>
+      <c r="F2" s="150" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I2" s="150" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L2" s="148" t="s">
         <v>65</v>
       </c>
       <c r="M2" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="143" t="str">
+      <c r="N2" s="151" t="str">
         <f>IF($C2&lt;&gt;"",TEXT($C2,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="O2" s="143" t="str">
+      <c r="O2" s="151" t="str">
         <f>IF($F2&lt;&gt;"",TEXT($F2,"HH:MM"),"")</f>
-        <v/>
-      </c>
-      <c r="P2" s="143" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="P2" s="151" t="str">
         <f>IF($I2&lt;&gt;"",TEXT($I2,"HH:MM"),"")</f>
-        <v/>
+        <v>00:00</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="18" customHeight="1">
@@ -8625,29 +9065,41 @@
       <c r="C3" s="150"/>
       <c r="D3" s="149"/>
       <c r="E3" s="149"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="150"/>
-      <c r="J3" s="149"/>
-      <c r="K3" s="149"/>
+      <c r="F3" s="150" t="s">
+        <v>885</v>
+      </c>
+      <c r="G3" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="149" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I3" s="150" t="s">
+        <v>782</v>
+      </c>
+      <c r="J3" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L3" s="148" t="s">
         <v>36</v>
       </c>
       <c r="M3" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N3" s="143" t="str">
+      <c r="N3" s="151" t="str">
         <f t="shared" ref="N3:N66" si="0">IF($C3&lt;&gt;"",TEXT($C3,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="O3" s="143" t="str">
+      <c r="O3" s="151" t="str">
         <f t="shared" ref="O3:O66" si="1">IF($F3&lt;&gt;"",TEXT($F3,"HH:MM"),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="143" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="P3" s="151" t="str">
         <f t="shared" ref="P3:P66" si="2">IF($I3&lt;&gt;"",TEXT($I3,"HH:MM"),"")</f>
-        <v/>
+        <v>01:27</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1">
@@ -8661,28 +9113,34 @@
       <c r="D4" s="152"/>
       <c r="E4" s="152"/>
       <c r="F4" s="150"/>
-      <c r="G4" s="149"/>
+      <c r="G4" s="213"/>
       <c r="H4" s="149"/>
-      <c r="I4" s="150"/>
-      <c r="J4" s="149"/>
-      <c r="K4" s="149"/>
+      <c r="I4" s="150" t="s">
+        <v>648</v>
+      </c>
+      <c r="J4" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L4" s="148" t="s">
         <v>35</v>
       </c>
       <c r="M4" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="143" t="str">
+      <c r="N4" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O4" s="143" t="str">
+      <c r="O4" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P4" s="143" t="str">
+      <c r="P4" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>02:53</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="18" customHeight="1">
@@ -8696,7 +9154,7 @@
       <c r="D5" s="149"/>
       <c r="E5" s="149"/>
       <c r="F5" s="150"/>
-      <c r="G5" s="149"/>
+      <c r="G5" s="213"/>
       <c r="H5" s="149"/>
       <c r="I5" s="150"/>
       <c r="J5" s="149"/>
@@ -8707,15 +9165,15 @@
       <c r="M5" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N5" s="143" t="str">
+      <c r="N5" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O5" s="143" t="str">
+      <c r="O5" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="143" t="str">
+      <c r="P5" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8730,29 +9188,41 @@
       <c r="C6" s="150"/>
       <c r="D6" s="149"/>
       <c r="E6" s="149"/>
-      <c r="F6" s="150"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="149"/>
+      <c r="F6" s="150" t="s">
+        <v>588</v>
+      </c>
+      <c r="G6" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I6" s="148" t="s">
+        <v>649</v>
+      </c>
+      <c r="J6" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L6" s="148" t="s">
         <v>32</v>
       </c>
       <c r="M6" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N6" s="143" t="str">
+      <c r="N6" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O6" s="143" t="str">
+      <c r="O6" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P6" s="143" t="str">
+        <v>04:28</v>
+      </c>
+      <c r="P6" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:19</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="18" customHeight="1">
@@ -8765,29 +9235,41 @@
       <c r="C7" s="149"/>
       <c r="D7" s="149"/>
       <c r="E7" s="149"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="149"/>
-      <c r="K7" s="149"/>
+      <c r="F7" s="150" t="s">
+        <v>1540</v>
+      </c>
+      <c r="G7" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="149" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I7" s="150" t="s">
+        <v>1597</v>
+      </c>
+      <c r="J7" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L7" s="148" t="s">
         <v>31</v>
       </c>
       <c r="M7" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N7" s="143" t="str">
+      <c r="N7" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O7" s="143" t="str">
+      <c r="O7" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P7" s="143" t="str">
+        <v>05:54</v>
+      </c>
+      <c r="P7" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>05:45</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="18" customHeight="1">
@@ -8797,11 +9279,11 @@
       <c r="B8" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="287"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="149"/>
       <c r="E8" s="149"/>
       <c r="F8" s="153"/>
-      <c r="G8" s="149"/>
+      <c r="G8" s="213"/>
       <c r="H8" s="149"/>
       <c r="I8" s="150"/>
       <c r="J8" s="149"/>
@@ -8812,15 +9294,15 @@
       <c r="M8" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="143" t="str">
+      <c r="N8" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O8" s="143" t="str">
+      <c r="O8" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P8" s="143" t="str">
+      <c r="P8" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8835,29 +9317,41 @@
       <c r="C9" s="150"/>
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
-      <c r="F9" s="287"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="149"/>
+      <c r="F9" s="150" t="s">
+        <v>590</v>
+      </c>
+      <c r="G9" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I9" s="150" t="s">
+        <v>1338</v>
+      </c>
+      <c r="J9" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L9" s="148" t="s">
         <v>29</v>
       </c>
       <c r="M9" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="143" t="str">
+      <c r="N9" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O9" s="143" t="str">
+      <c r="O9" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P9" s="143" t="str">
+        <v>07:21</v>
+      </c>
+      <c r="P9" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>07:19</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="18" customHeight="1">
@@ -8870,29 +9364,41 @@
       <c r="C10" s="150"/>
       <c r="D10" s="149"/>
       <c r="E10" s="149"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
-      <c r="I10" s="148"/>
-      <c r="J10" s="149"/>
-      <c r="K10" s="149"/>
+      <c r="F10" s="150" t="s">
+        <v>274</v>
+      </c>
+      <c r="G10" s="213" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="149" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I10" s="148" t="s">
+        <v>206</v>
+      </c>
+      <c r="J10" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L10" s="148" t="s">
         <v>28</v>
       </c>
       <c r="M10" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N10" s="143" t="str">
+      <c r="N10" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O10" s="143" t="str">
+      <c r="O10" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P10" s="143" t="str">
+        <v>08:52</v>
+      </c>
+      <c r="P10" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>08:49</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="18" customHeight="1">
@@ -8906,7 +9412,7 @@
       <c r="D11" s="149"/>
       <c r="E11" s="149"/>
       <c r="F11" s="150"/>
-      <c r="G11" s="149"/>
+      <c r="G11" s="213"/>
       <c r="H11" s="149"/>
       <c r="I11" s="150"/>
       <c r="J11" s="149"/>
@@ -8917,15 +9423,15 @@
       <c r="M11" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N11" s="143" t="str">
+      <c r="N11" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O11" s="143" t="str">
+      <c r="O11" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P11" s="143" t="str">
+      <c r="P11" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8940,29 +9446,41 @@
       <c r="C12" s="150"/>
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="149"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="149"/>
+      <c r="F12" s="150" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G12" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="149" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I12" s="150" t="s">
+        <v>979</v>
+      </c>
+      <c r="J12" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L12" s="148" t="s">
         <v>25</v>
       </c>
       <c r="M12" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="143" t="str">
+      <c r="N12" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O12" s="143" t="str">
+      <c r="O12" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P12" s="143" t="str">
+        <v>10:26</v>
+      </c>
+      <c r="P12" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10:15</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="18" customHeight="1">
@@ -8972,32 +9490,42 @@
       <c r="B13" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="150"/>
+      <c r="C13" s="150" t="s">
+        <v>1531</v>
+      </c>
       <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
+      <c r="E13" s="149" t="s">
+        <v>1532</v>
+      </c>
       <c r="F13" s="150"/>
-      <c r="G13" s="149"/>
+      <c r="G13" s="213"/>
       <c r="H13" s="149"/>
-      <c r="I13" s="148"/>
-      <c r="J13" s="149"/>
-      <c r="K13" s="149"/>
+      <c r="I13" s="148" t="s">
+        <v>1598</v>
+      </c>
+      <c r="J13" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K13" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L13" s="148" t="s">
         <v>23</v>
       </c>
       <c r="M13" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N13" s="143" t="str">
+      <c r="N13" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O13" s="143" t="str">
+        <v>11:40</v>
+      </c>
+      <c r="O13" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P13" s="143" t="str">
+      <c r="P13" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:48</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="18" customHeight="1">
@@ -9010,9 +9538,15 @@
       <c r="C14" s="149"/>
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="149"/>
-      <c r="H14" s="149"/>
+      <c r="F14" s="150" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G14" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="149" t="s">
+        <v>1396</v>
+      </c>
       <c r="I14" s="150"/>
       <c r="J14" s="149"/>
       <c r="K14" s="149"/>
@@ -9022,15 +9556,15 @@
       <c r="M14" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N14" s="143" t="str">
+      <c r="N14" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O14" s="143" t="str">
+      <c r="O14" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P14" s="143" t="str">
+        <v>12:01</v>
+      </c>
+      <c r="P14" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9045,29 +9579,41 @@
       <c r="C15" s="150"/>
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
+      <c r="F15" s="150" t="s">
+        <v>1543</v>
+      </c>
+      <c r="G15" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="149" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I15" s="150" t="s">
+        <v>910</v>
+      </c>
+      <c r="J15" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L15" s="148" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N15" s="143" t="str">
+      <c r="N15" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O15" s="143" t="str">
+      <c r="O15" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P15" s="143" t="str">
+        <v>13:30</v>
+      </c>
+      <c r="P15" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:15</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="18" customHeight="1">
@@ -9081,28 +9627,34 @@
       <c r="D16" s="149"/>
       <c r="E16" s="149"/>
       <c r="F16" s="150"/>
-      <c r="G16" s="149"/>
+      <c r="G16" s="213"/>
       <c r="H16" s="149"/>
-      <c r="I16" s="148"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
+      <c r="I16" s="148" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J16" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L16" s="148" t="s">
         <v>20</v>
       </c>
       <c r="M16" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N16" s="143" t="str">
+      <c r="N16" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O16" s="143" t="str">
+      <c r="O16" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P16" s="143" t="str">
+      <c r="P16" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:48</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="18" customHeight="1">
@@ -9115,9 +9667,15 @@
       <c r="C17" s="150"/>
       <c r="D17" s="149"/>
       <c r="E17" s="149"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
+      <c r="F17" s="150" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G17" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="149" t="s">
+        <v>1016</v>
+      </c>
       <c r="I17" s="150"/>
       <c r="J17" s="149"/>
       <c r="K17" s="149"/>
@@ -9127,15 +9685,15 @@
       <c r="M17" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N17" s="143" t="str">
+      <c r="N17" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O17" s="143" t="str">
+      <c r="O17" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P17" s="143" t="str">
+        <v>15:03</v>
+      </c>
+      <c r="P17" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9150,29 +9708,41 @@
       <c r="C18" s="150"/>
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="149"/>
+      <c r="F18" s="150" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G18" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="149" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I18" s="148" t="s">
+        <v>278</v>
+      </c>
+      <c r="J18" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L18" s="148" t="s">
         <v>16</v>
       </c>
       <c r="M18" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N18" s="143" t="str">
+      <c r="N18" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O18" s="143" t="str">
+      <c r="O18" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P18" s="143" t="str">
+        <v>16:32</v>
+      </c>
+      <c r="P18" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:22</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="18" customHeight="1">
@@ -9186,28 +9756,34 @@
       <c r="D19" s="149"/>
       <c r="E19" s="149"/>
       <c r="F19" s="150"/>
-      <c r="G19" s="149"/>
+      <c r="G19" s="213"/>
       <c r="H19" s="149"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="149"/>
-      <c r="K19" s="149"/>
+      <c r="I19" s="150" t="s">
+        <v>291</v>
+      </c>
+      <c r="J19" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K19" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L19" s="148" t="s">
         <v>15</v>
       </c>
       <c r="M19" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N19" s="143" t="str">
+      <c r="N19" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O19" s="143" t="str">
+      <c r="O19" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P19" s="143" t="str">
+      <c r="P19" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>17:57</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="18" customHeight="1">
@@ -9220,9 +9796,15 @@
       <c r="C20" s="149"/>
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
+      <c r="F20" s="150" t="s">
+        <v>1545</v>
+      </c>
+      <c r="G20" s="213" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="149" t="s">
+        <v>1017</v>
+      </c>
       <c r="I20" s="150"/>
       <c r="J20" s="149"/>
       <c r="K20" s="149"/>
@@ -9232,15 +9814,15 @@
       <c r="M20" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N20" s="143" t="str">
+      <c r="N20" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O20" s="143" t="str">
+      <c r="O20" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P20" s="143" t="str">
+        <v>18:02</v>
+      </c>
+      <c r="P20" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9255,29 +9837,41 @@
       <c r="C21" s="150"/>
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="149"/>
-      <c r="K21" s="149"/>
+      <c r="F21" s="150" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G21" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I21" s="148" t="s">
+        <v>596</v>
+      </c>
+      <c r="J21" s="149" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="149" t="s">
+        <v>1403</v>
+      </c>
       <c r="L21" s="148" t="s">
         <v>10</v>
       </c>
       <c r="M21" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N21" s="143" t="str">
+      <c r="N21" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O21" s="143" t="str">
+      <c r="O21" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P21" s="143" t="str">
+        <v>19:33</v>
+      </c>
+      <c r="P21" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>19:26</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="18" customHeight="1">
@@ -9291,28 +9885,34 @@
       <c r="D22" s="149"/>
       <c r="E22" s="149"/>
       <c r="F22" s="150"/>
-      <c r="G22" s="149"/>
+      <c r="G22" s="213"/>
       <c r="H22" s="149"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="149"/>
-      <c r="K22" s="149"/>
+      <c r="I22" s="150" t="s">
+        <v>1346</v>
+      </c>
+      <c r="J22" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L22" s="148" t="s">
         <v>9</v>
       </c>
       <c r="M22" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N22" s="143" t="str">
+      <c r="N22" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O22" s="143" t="str">
+      <c r="O22" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P22" s="143" t="str">
+      <c r="P22" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>20:50</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1">
@@ -9325,9 +9925,15 @@
       <c r="C23" s="149"/>
       <c r="D23" s="149"/>
       <c r="E23" s="149"/>
-      <c r="F23" s="150"/>
-      <c r="G23" s="149"/>
-      <c r="H23" s="149"/>
+      <c r="F23" s="150" t="s">
+        <v>166</v>
+      </c>
+      <c r="G23" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="H23" s="149" t="s">
+        <v>1018</v>
+      </c>
       <c r="I23" s="150"/>
       <c r="J23" s="149"/>
       <c r="K23" s="149"/>
@@ -9337,15 +9943,15 @@
       <c r="M23" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N23" s="143" t="str">
+      <c r="N23" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O23" s="143" t="str">
+      <c r="O23" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P23" s="143" t="str">
+        <v>21:04</v>
+      </c>
+      <c r="P23" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9360,29 +9966,41 @@
       <c r="C24" s="150"/>
       <c r="D24" s="149"/>
       <c r="E24" s="149"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="149"/>
-      <c r="H24" s="149"/>
-      <c r="I24" s="148"/>
-      <c r="J24" s="149"/>
-      <c r="K24" s="149"/>
+      <c r="F24" s="150" t="s">
+        <v>647</v>
+      </c>
+      <c r="G24" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I24" s="148" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J24" s="149" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="149" t="s">
+        <v>1015</v>
+      </c>
       <c r="L24" s="148" t="s">
         <v>5</v>
       </c>
       <c r="M24" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="N24" s="143" t="str">
+      <c r="N24" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O24" s="143" t="str">
+      <c r="O24" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P24" s="143" t="str">
+        <v>22:39</v>
+      </c>
+      <c r="P24" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>22:25</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -9396,28 +10014,34 @@
       <c r="D25" s="155"/>
       <c r="E25" s="155"/>
       <c r="F25" s="156"/>
-      <c r="G25" s="155"/>
+      <c r="G25" s="217"/>
       <c r="H25" s="155"/>
-      <c r="I25" s="156"/>
-      <c r="J25" s="155"/>
-      <c r="K25" s="155"/>
+      <c r="I25" s="156" t="s">
+        <v>955</v>
+      </c>
+      <c r="J25" s="155" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="155" t="s">
+        <v>1403</v>
+      </c>
       <c r="L25" s="154" t="s">
         <v>3</v>
       </c>
       <c r="M25" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="N25" s="143" t="str">
+      <c r="N25" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O25" s="143" t="str">
+      <c r="O25" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P25" s="143" t="str">
+      <c r="P25" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>23:58</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="18" customHeight="1">
@@ -9430,10 +10054,16 @@
       <c r="C26" s="158"/>
       <c r="D26" s="158"/>
       <c r="E26" s="158"/>
-      <c r="F26" s="159"/>
-      <c r="G26" s="158"/>
-      <c r="H26" s="158"/>
-      <c r="I26" s="293"/>
+      <c r="F26" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="219" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="158" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I26" s="159"/>
       <c r="J26" s="158"/>
       <c r="K26" s="158"/>
       <c r="L26" s="157" t="s">
@@ -9442,15 +10072,15 @@
       <c r="M26" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="143" t="str">
+      <c r="N26" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O26" s="143" t="str">
+      <c r="O26" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P26" s="143" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="P26" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9465,29 +10095,41 @@
       <c r="C27" s="161"/>
       <c r="D27" s="160"/>
       <c r="E27" s="160"/>
-      <c r="F27" s="162"/>
-      <c r="G27" s="160"/>
-      <c r="H27" s="160"/>
-      <c r="I27" s="162"/>
-      <c r="J27" s="160"/>
-      <c r="K27" s="160"/>
+      <c r="F27" s="162" t="s">
+        <v>885</v>
+      </c>
+      <c r="G27" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="160" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I27" s="162" t="s">
+        <v>623</v>
+      </c>
+      <c r="J27" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L27" s="157" t="s">
         <v>36</v>
       </c>
       <c r="M27" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N27" s="143" t="str">
+      <c r="N27" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O27" s="143" t="str">
+      <c r="O27" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P27" s="143" t="str">
+        <v>01:30</v>
+      </c>
+      <c r="P27" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>01:01</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1">
@@ -9501,28 +10143,34 @@
       <c r="D28" s="160"/>
       <c r="E28" s="160"/>
       <c r="F28" s="162"/>
-      <c r="G28" s="160"/>
+      <c r="G28" s="221"/>
       <c r="H28" s="160"/>
-      <c r="I28" s="162"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="160"/>
+      <c r="I28" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J28" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L28" s="157" t="s">
         <v>35</v>
       </c>
       <c r="M28" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N28" s="143" t="str">
+      <c r="N28" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O28" s="143" t="str">
+      <c r="O28" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P28" s="143" t="str">
+      <c r="P28" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>02:29</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="18" customHeight="1">
@@ -9535,9 +10183,15 @@
       <c r="C29" s="161"/>
       <c r="D29" s="160"/>
       <c r="E29" s="160"/>
-      <c r="F29" s="162"/>
-      <c r="G29" s="160"/>
-      <c r="H29" s="160"/>
+      <c r="F29" s="162" t="s">
+        <v>259</v>
+      </c>
+      <c r="G29" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" s="160" t="s">
+        <v>1396</v>
+      </c>
       <c r="I29" s="157"/>
       <c r="J29" s="160"/>
       <c r="K29" s="160"/>
@@ -9547,15 +10201,15 @@
       <c r="M29" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N29" s="143" t="str">
+      <c r="N29" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O29" s="143" t="str">
+      <c r="O29" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P29" s="143" t="str">
+        <v>03:02</v>
+      </c>
+      <c r="P29" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9570,9 +10224,15 @@
       <c r="C30" s="160"/>
       <c r="D30" s="160"/>
       <c r="E30" s="160"/>
-      <c r="F30" s="162"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="160"/>
+      <c r="F30" s="162" t="s">
+        <v>1546</v>
+      </c>
+      <c r="G30" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="160" t="s">
+        <v>1396</v>
+      </c>
       <c r="I30" s="162"/>
       <c r="J30" s="160"/>
       <c r="K30" s="160"/>
@@ -9582,15 +10242,15 @@
       <c r="M30" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N30" s="143" t="str">
+      <c r="N30" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O30" s="143" t="str">
+      <c r="O30" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P30" s="143" t="str">
+        <v>04:34</v>
+      </c>
+      <c r="P30" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9606,28 +10266,34 @@
       <c r="D31" s="160"/>
       <c r="E31" s="160"/>
       <c r="F31" s="162"/>
-      <c r="G31" s="160"/>
+      <c r="G31" s="221"/>
       <c r="H31" s="160"/>
-      <c r="I31" s="162"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="160"/>
+      <c r="I31" s="162" t="s">
+        <v>849</v>
+      </c>
+      <c r="J31" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K31" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L31" s="157" t="s">
         <v>31</v>
       </c>
       <c r="M31" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N31" s="143" t="str">
+      <c r="N31" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O31" s="143" t="str">
+      <c r="O31" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P31" s="143" t="str">
+      <c r="P31" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>05:38</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="18" customHeight="1">
@@ -9640,9 +10306,15 @@
       <c r="C32" s="162"/>
       <c r="D32" s="160"/>
       <c r="E32" s="160"/>
-      <c r="F32" s="162"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="160"/>
+      <c r="F32" s="162" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="H32" s="160" t="s">
+        <v>1018</v>
+      </c>
       <c r="I32" s="157"/>
       <c r="J32" s="160"/>
       <c r="K32" s="160"/>
@@ -9652,15 +10324,15 @@
       <c r="M32" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N32" s="143" t="str">
+      <c r="N32" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O32" s="143" t="str">
+      <c r="O32" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P32" s="143" t="str">
+        <v>06:00</v>
+      </c>
+      <c r="P32" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9672,32 +10344,44 @@
       <c r="B33" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="288"/>
+      <c r="C33" s="279"/>
       <c r="D33" s="160"/>
       <c r="E33" s="160"/>
-      <c r="F33" s="162"/>
-      <c r="G33" s="160"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="162"/>
-      <c r="J33" s="160"/>
-      <c r="K33" s="160"/>
+      <c r="F33" s="162" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G33" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I33" s="162" t="s">
+        <v>829</v>
+      </c>
+      <c r="J33" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L33" s="157" t="s">
         <v>29</v>
       </c>
       <c r="M33" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N33" s="143" t="str">
+      <c r="N33" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O33" s="143" t="str">
+      <c r="O33" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P33" s="143" t="str">
+        <v>07:28</v>
+      </c>
+      <c r="P33" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>07:03</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="18" customHeight="1">
@@ -9710,29 +10394,41 @@
       <c r="C34" s="160"/>
       <c r="D34" s="160"/>
       <c r="E34" s="160"/>
-      <c r="F34" s="162"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="162"/>
-      <c r="J34" s="160"/>
-      <c r="K34" s="160"/>
+      <c r="F34" s="162" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G34" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I34" s="162" t="s">
+        <v>661</v>
+      </c>
+      <c r="J34" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K34" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L34" s="157" t="s">
         <v>28</v>
       </c>
       <c r="M34" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N34" s="143" t="str">
+      <c r="N34" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O34" s="143" t="str">
+      <c r="O34" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P34" s="143" t="str">
+        <v>08:57</v>
+      </c>
+      <c r="P34" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>08:33</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="18" customHeight="1">
@@ -9745,10 +10441,10 @@
       <c r="C35" s="162"/>
       <c r="D35" s="160"/>
       <c r="E35" s="160"/>
-      <c r="F35" s="289"/>
-      <c r="G35" s="160"/>
+      <c r="F35" s="162"/>
+      <c r="G35" s="221"/>
       <c r="H35" s="160"/>
-      <c r="I35" s="294"/>
+      <c r="I35" s="164"/>
       <c r="J35" s="160"/>
       <c r="K35" s="160"/>
       <c r="L35" s="157" t="s">
@@ -9757,15 +10453,15 @@
       <c r="M35" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N35" s="143" t="str">
+      <c r="N35" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O35" s="143" t="str">
+      <c r="O35" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P35" s="143" t="str">
+      <c r="P35" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9777,32 +10473,48 @@
       <c r="B36" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="162"/>
+      <c r="C36" s="162" t="s">
+        <v>1533</v>
+      </c>
       <c r="D36" s="160"/>
-      <c r="E36" s="160"/>
-      <c r="F36" s="162"/>
-      <c r="G36" s="160"/>
-      <c r="H36" s="160"/>
-      <c r="I36" s="162"/>
-      <c r="J36" s="160"/>
-      <c r="K36" s="160"/>
+      <c r="E36" s="160" t="s">
+        <v>1539</v>
+      </c>
+      <c r="F36" s="162" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G36" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I36" s="162" t="s">
+        <v>833</v>
+      </c>
+      <c r="J36" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L36" s="157" t="s">
         <v>25</v>
       </c>
       <c r="M36" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N36" s="143" t="str">
+      <c r="N36" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O36" s="143" t="str">
+        <v>10:18</v>
+      </c>
+      <c r="O36" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P36" s="143" t="str">
+        <v>10:26</v>
+      </c>
+      <c r="P36" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10:03</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1">
@@ -9815,29 +10527,41 @@
       <c r="C37" s="160"/>
       <c r="D37" s="160"/>
       <c r="E37" s="160"/>
-      <c r="F37" s="162"/>
-      <c r="G37" s="160"/>
-      <c r="H37" s="160"/>
-      <c r="I37" s="162"/>
-      <c r="J37" s="160"/>
-      <c r="K37" s="160"/>
+      <c r="F37" s="162" t="s">
+        <v>592</v>
+      </c>
+      <c r="G37" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I37" s="162" t="s">
+        <v>652</v>
+      </c>
+      <c r="J37" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K37" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L37" s="157" t="s">
         <v>23</v>
       </c>
       <c r="M37" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N37" s="143" t="str">
+      <c r="N37" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O37" s="143" t="str">
+      <c r="O37" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P37" s="143" t="str">
+        <v>11:59</v>
+      </c>
+      <c r="P37" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:37</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="18" customHeight="1">
@@ -9851,7 +10575,7 @@
       <c r="D38" s="160"/>
       <c r="E38" s="160"/>
       <c r="F38" s="162"/>
-      <c r="G38" s="160"/>
+      <c r="G38" s="221"/>
       <c r="H38" s="160"/>
       <c r="I38" s="163"/>
       <c r="J38" s="160"/>
@@ -9862,15 +10586,15 @@
       <c r="M38" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N38" s="143" t="str">
+      <c r="N38" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O38" s="143" t="str">
+      <c r="O38" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P38" s="143" t="str">
+      <c r="P38" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9882,32 +10606,48 @@
       <c r="B39" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="162"/>
+      <c r="C39" s="162" t="s">
+        <v>1534</v>
+      </c>
       <c r="D39" s="160"/>
-      <c r="E39" s="160"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="160"/>
-      <c r="H39" s="160"/>
-      <c r="I39" s="289"/>
-      <c r="J39" s="160"/>
-      <c r="K39" s="160"/>
+      <c r="E39" s="160" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F39" s="162" t="s">
+        <v>991</v>
+      </c>
+      <c r="G39" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="H39" s="160" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I39" s="162" t="s">
+        <v>920</v>
+      </c>
+      <c r="J39" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K39" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L39" s="157" t="s">
         <v>21</v>
       </c>
       <c r="M39" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N39" s="143" t="str">
+      <c r="N39" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O39" s="143" t="str">
+        <v>13:24</v>
+      </c>
+      <c r="O39" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P39" s="143" t="str">
+        <v>13:26</v>
+      </c>
+      <c r="P39" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:02</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1">
@@ -9920,29 +10660,41 @@
       <c r="C40" s="161"/>
       <c r="D40" s="160"/>
       <c r="E40" s="160"/>
-      <c r="F40" s="162"/>
-      <c r="G40" s="160"/>
-      <c r="H40" s="160"/>
-      <c r="I40" s="162"/>
-      <c r="J40" s="160"/>
-      <c r="K40" s="160"/>
+      <c r="F40" s="162" t="s">
+        <v>787</v>
+      </c>
+      <c r="G40" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I40" s="162" t="s">
+        <v>1601</v>
+      </c>
+      <c r="J40" s="160" t="s">
+        <v>13</v>
+      </c>
+      <c r="K40" s="160" t="s">
+        <v>1403</v>
+      </c>
       <c r="L40" s="157" t="s">
         <v>20</v>
       </c>
       <c r="M40" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N40" s="143" t="str">
+      <c r="N40" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O40" s="143" t="str">
+      <c r="O40" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P40" s="143" t="str">
+        <v>14:52</v>
+      </c>
+      <c r="P40" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:31</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="18" customHeight="1">
@@ -9956,7 +10708,7 @@
       <c r="D41" s="160"/>
       <c r="E41" s="160"/>
       <c r="F41" s="162"/>
-      <c r="G41" s="160"/>
+      <c r="G41" s="221"/>
       <c r="H41" s="160"/>
       <c r="I41" s="162"/>
       <c r="J41" s="160"/>
@@ -9967,15 +10719,15 @@
       <c r="M41" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N41" s="143" t="str">
+      <c r="N41" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O41" s="143" t="str">
+      <c r="O41" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P41" s="143" t="str">
+      <c r="P41" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -9991,7 +10743,7 @@
       <c r="D42" s="160"/>
       <c r="E42" s="160"/>
       <c r="F42" s="162"/>
-      <c r="G42" s="160"/>
+      <c r="G42" s="221"/>
       <c r="H42" s="160"/>
       <c r="I42" s="164"/>
       <c r="J42" s="160"/>
@@ -10002,15 +10754,15 @@
       <c r="M42" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N42" s="143" t="str">
+      <c r="N42" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O42" s="143" t="str">
+      <c r="O42" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P42" s="143" t="str">
+      <c r="P42" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10022,11 +10774,15 @@
       <c r="B43" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="162"/>
+      <c r="C43" s="162" t="s">
+        <v>1535</v>
+      </c>
       <c r="D43" s="160"/>
-      <c r="E43" s="160"/>
+      <c r="E43" s="160" t="s">
+        <v>1607</v>
+      </c>
       <c r="F43" s="162"/>
-      <c r="G43" s="160"/>
+      <c r="G43" s="221"/>
       <c r="H43" s="160"/>
       <c r="I43" s="162"/>
       <c r="J43" s="160"/>
@@ -10037,15 +10793,15 @@
       <c r="M43" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N43" s="143" t="str">
+      <c r="N43" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O43" s="143" t="str">
+        <v>17:25</v>
+      </c>
+      <c r="O43" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P43" s="143" t="str">
+      <c r="P43" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10057,11 +10813,11 @@
       <c r="B44" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="289"/>
+      <c r="C44" s="162"/>
       <c r="D44" s="160"/>
       <c r="E44" s="160"/>
       <c r="F44" s="161"/>
-      <c r="G44" s="160"/>
+      <c r="G44" s="221"/>
       <c r="H44" s="160"/>
       <c r="I44" s="163"/>
       <c r="J44" s="160"/>
@@ -10072,15 +10828,15 @@
       <c r="M44" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N44" s="143" t="str">
+      <c r="N44" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O44" s="143" t="str">
+      <c r="O44" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P44" s="143" t="str">
+      <c r="P44" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10096,7 +10852,7 @@
       <c r="D45" s="160"/>
       <c r="E45" s="160"/>
       <c r="F45" s="162"/>
-      <c r="G45" s="160"/>
+      <c r="G45" s="221"/>
       <c r="H45" s="160"/>
       <c r="I45" s="162"/>
       <c r="J45" s="160"/>
@@ -10107,15 +10863,15 @@
       <c r="M45" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N45" s="143" t="str">
+      <c r="N45" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O45" s="143" t="str">
+      <c r="O45" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P45" s="143" t="str">
+      <c r="P45" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10131,7 +10887,7 @@
       <c r="D46" s="160"/>
       <c r="E46" s="160"/>
       <c r="F46" s="162"/>
-      <c r="G46" s="160"/>
+      <c r="G46" s="221"/>
       <c r="H46" s="160"/>
       <c r="I46" s="162"/>
       <c r="J46" s="160"/>
@@ -10142,15 +10898,15 @@
       <c r="M46" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N46" s="143" t="str">
+      <c r="N46" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O46" s="143" t="str">
+      <c r="O46" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P46" s="143" t="str">
+      <c r="P46" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10162,11 +10918,15 @@
       <c r="B47" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="162"/>
+      <c r="C47" s="162" t="s">
+        <v>1608</v>
+      </c>
       <c r="D47" s="160"/>
-      <c r="E47" s="160"/>
+      <c r="E47" s="160" t="s">
+        <v>1609</v>
+      </c>
       <c r="F47" s="160"/>
-      <c r="G47" s="160"/>
+      <c r="G47" s="221"/>
       <c r="H47" s="160"/>
       <c r="I47" s="162"/>
       <c r="J47" s="160"/>
@@ -10177,15 +10937,15 @@
       <c r="M47" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="143" t="str">
+      <c r="N47" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O47" s="143" t="str">
+        <v>21:47</v>
+      </c>
+      <c r="O47" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P47" s="143" t="str">
+      <c r="P47" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10201,28 +10961,32 @@
       <c r="D48" s="160"/>
       <c r="E48" s="160"/>
       <c r="F48" s="162"/>
-      <c r="G48" s="160"/>
+      <c r="G48" s="221"/>
       <c r="H48" s="160"/>
-      <c r="I48" s="164"/>
+      <c r="I48" s="164" t="s">
+        <v>1606</v>
+      </c>
       <c r="J48" s="160"/>
-      <c r="K48" s="160"/>
+      <c r="K48" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L48" s="157" t="s">
         <v>5</v>
       </c>
       <c r="M48" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="N48" s="143" t="str">
+      <c r="N48" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O48" s="143" t="str">
+      <c r="O48" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P48" s="143" t="str">
+      <c r="P48" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>22:01</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -10235,15 +10999,9 @@
       <c r="C49" s="166"/>
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
-      <c r="F49" s="167" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G49" s="166" t="s">
-        <v>17</v>
-      </c>
-      <c r="H49" s="166" t="s">
-        <v>1017</v>
-      </c>
+      <c r="F49" s="167"/>
+      <c r="G49" s="225"/>
+      <c r="H49" s="166"/>
       <c r="I49" s="167"/>
       <c r="J49" s="166"/>
       <c r="K49" s="166"/>
@@ -10253,15 +11011,15 @@
       <c r="M49" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="N49" s="143" t="str">
+      <c r="N49" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O49" s="143" t="str">
+      <c r="O49" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>23:59</v>
-      </c>
-      <c r="P49" s="143" t="str">
+        <v/>
+      </c>
+      <c r="P49" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10276,41 +11034,29 @@
       <c r="C50" s="170"/>
       <c r="D50" s="169"/>
       <c r="E50" s="169"/>
-      <c r="F50" s="170" t="s">
-        <v>1304</v>
-      </c>
-      <c r="G50" s="169" t="s">
-        <v>0</v>
-      </c>
-      <c r="H50" s="169" t="s">
-        <v>1018</v>
-      </c>
-      <c r="I50" s="170" t="s">
-        <v>1116</v>
-      </c>
-      <c r="J50" s="169" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" s="169" t="s">
-        <v>1403</v>
-      </c>
+      <c r="F50" s="170"/>
+      <c r="G50" s="227"/>
+      <c r="H50" s="169"/>
+      <c r="I50" s="170"/>
+      <c r="J50" s="169"/>
+      <c r="K50" s="169"/>
       <c r="L50" s="168" t="s">
         <v>37</v>
       </c>
       <c r="M50" s="169" t="s">
         <v>55</v>
       </c>
-      <c r="N50" s="143" t="str">
+      <c r="N50" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O50" s="143" t="str">
+      <c r="O50" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>00:04</v>
-      </c>
-      <c r="P50" s="143" t="str">
+        <v/>
+      </c>
+      <c r="P50" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>00:01</v>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:16" ht="18" customHeight="1">
@@ -10323,41 +11069,29 @@
       <c r="C51" s="172"/>
       <c r="D51" s="171"/>
       <c r="E51" s="171"/>
-      <c r="F51" s="172" t="s">
-        <v>258</v>
-      </c>
-      <c r="G51" s="171" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="171" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I51" s="172" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J51" s="171" t="s">
-        <v>13</v>
-      </c>
-      <c r="K51" s="171" t="s">
-        <v>1403</v>
-      </c>
+      <c r="F51" s="172"/>
+      <c r="G51" s="229"/>
+      <c r="H51" s="171"/>
+      <c r="I51" s="172"/>
+      <c r="J51" s="171"/>
+      <c r="K51" s="171"/>
       <c r="L51" s="168" t="s">
         <v>36</v>
       </c>
       <c r="M51" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N51" s="143" t="str">
+      <c r="N51" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O51" s="143" t="str">
+      <c r="O51" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>01:36</v>
-      </c>
-      <c r="P51" s="143" t="str">
+        <v/>
+      </c>
+      <c r="P51" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>01:34</v>
+        <v/>
       </c>
     </row>
     <row r="52" spans="1:16" ht="18" customHeight="1">
@@ -10367,17 +11101,11 @@
       <c r="B52" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="173" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D52" s="290" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E52" s="171" t="s">
-        <v>1453</v>
-      </c>
+      <c r="C52" s="173"/>
+      <c r="D52" s="172"/>
+      <c r="E52" s="171"/>
       <c r="F52" s="173"/>
-      <c r="G52" s="171"/>
+      <c r="G52" s="229"/>
       <c r="H52" s="171"/>
       <c r="I52" s="173"/>
       <c r="J52" s="171"/>
@@ -10388,15 +11116,15 @@
       <c r="M52" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N52" s="143" t="str">
+      <c r="N52" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>02:40</v>
-      </c>
-      <c r="O52" s="143" t="str">
+        <v/>
+      </c>
+      <c r="O52" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P52" s="143" t="str">
+      <c r="P52" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10408,48 +11136,32 @@
       <c r="B53" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C53" s="172" t="s">
-        <v>1485</v>
-      </c>
-      <c r="D53" s="171" t="s">
-        <v>1487</v>
-      </c>
+      <c r="C53" s="172"/>
+      <c r="D53" s="171"/>
       <c r="E53" s="171"/>
-      <c r="F53" s="172" t="s">
-        <v>1305</v>
-      </c>
-      <c r="G53" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="H53" s="171" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I53" s="172" t="s">
-        <v>259</v>
-      </c>
-      <c r="J53" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="K53" s="171" t="s">
-        <v>1403</v>
-      </c>
+      <c r="F53" s="172"/>
+      <c r="G53" s="229"/>
+      <c r="H53" s="171"/>
+      <c r="I53" s="172"/>
+      <c r="J53" s="171"/>
+      <c r="K53" s="171"/>
       <c r="L53" s="168" t="s">
         <v>33</v>
       </c>
       <c r="M53" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N53" s="143" t="str">
+      <c r="N53" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>03:30</v>
-      </c>
-      <c r="O53" s="143" t="str">
+        <v/>
+      </c>
+      <c r="O53" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>03:10</v>
-      </c>
-      <c r="P53" s="143" t="str">
+        <v/>
+      </c>
+      <c r="P53" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>03:02</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="1:16" ht="18" customHeight="1">
@@ -10459,48 +11171,32 @@
       <c r="B54" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="172" t="s">
-        <v>1486</v>
-      </c>
-      <c r="D54" s="171" t="s">
-        <v>1487</v>
-      </c>
+      <c r="C54" s="172"/>
+      <c r="D54" s="171"/>
       <c r="E54" s="171"/>
-      <c r="F54" s="290" t="s">
-        <v>1460</v>
-      </c>
-      <c r="G54" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="H54" s="171" t="s">
-        <v>1017</v>
-      </c>
-      <c r="I54" s="290" t="s">
-        <v>1470</v>
-      </c>
-      <c r="J54" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="K54" s="171" t="s">
-        <v>1015</v>
-      </c>
+      <c r="F54" s="172"/>
+      <c r="G54" s="229"/>
+      <c r="H54" s="171"/>
+      <c r="I54" s="172"/>
+      <c r="J54" s="171"/>
+      <c r="K54" s="171"/>
       <c r="L54" s="168" t="s">
         <v>32</v>
       </c>
       <c r="M54" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N54" s="143" t="str">
+      <c r="N54" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>04:00</v>
-      </c>
-      <c r="O54" s="143" t="str">
+        <v/>
+      </c>
+      <c r="O54" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>04:40</v>
-      </c>
-      <c r="P54" s="143" t="str">
+        <v/>
+      </c>
+      <c r="P54" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>04:34</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1">
@@ -10510,48 +11206,42 @@
       <c r="B55" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="290" t="s">
-        <v>1482</v>
+      <c r="C55" s="172" t="s">
+        <v>199</v>
       </c>
       <c r="D55" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="E55" s="171" t="s">
-        <v>1484</v>
-      </c>
+        <v>1480</v>
+      </c>
+      <c r="E55" s="171"/>
       <c r="F55" s="172" t="s">
         <v>199</v>
       </c>
-      <c r="G55" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="H55" s="171" t="s">
-        <v>1484</v>
-      </c>
+      <c r="G55" s="229" t="s">
+        <v>1519</v>
+      </c>
+      <c r="H55" s="171"/>
       <c r="I55" s="172" t="s">
         <v>199</v>
       </c>
       <c r="J55" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="K55" s="171" t="s">
-        <v>1484</v>
-      </c>
+        <v>1480</v>
+      </c>
+      <c r="K55" s="171"/>
       <c r="L55" s="168" t="s">
         <v>31</v>
       </c>
       <c r="M55" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N55" s="143" t="str">
+      <c r="N55" s="151" t="str">
         <f t="shared" si="0"/>
         <v>05:00</v>
       </c>
-      <c r="O55" s="143" t="str">
+      <c r="O55" s="151" t="str">
         <f t="shared" si="1"/>
         <v>05:00</v>
       </c>
-      <c r="P55" s="143" t="str">
+      <c r="P55" s="151" t="str">
         <f t="shared" si="2"/>
         <v>05:00</v>
       </c>
@@ -10567,28 +11257,28 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
       <c r="E56" s="171" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="F56" s="172" t="s">
         <v>77</v>
       </c>
-      <c r="G56" s="171" t="s">
-        <v>1487</v>
+      <c r="G56" s="229" t="s">
+        <v>1480</v>
       </c>
       <c r="H56" s="171" t="s">
-        <v>1484</v>
+        <v>1520</v>
       </c>
       <c r="I56" s="171" t="s">
         <v>77</v>
       </c>
       <c r="J56" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K56" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L56" s="168" t="s">
         <v>30</v>
@@ -10596,15 +11286,15 @@
       <c r="M56" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N56" s="143" t="str">
+      <c r="N56" s="151" t="str">
         <f t="shared" si="0"/>
         <v>06:00</v>
       </c>
-      <c r="O56" s="143" t="str">
+      <c r="O56" s="151" t="str">
         <f t="shared" si="1"/>
         <v>06:00</v>
       </c>
-      <c r="P56" s="143" t="str">
+      <c r="P56" s="151" t="str">
         <f t="shared" si="2"/>
         <v>06:00</v>
       </c>
@@ -10620,28 +11310,28 @@
         <v>81</v>
       </c>
       <c r="D57" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="E57" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="F57" s="171" t="s">
         <v>81</v>
       </c>
-      <c r="G57" s="171" t="s">
-        <v>1487</v>
+      <c r="G57" s="229" t="s">
+        <v>1480</v>
       </c>
       <c r="H57" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="I57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="J57" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K57" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L57" s="168" t="s">
         <v>29</v>
@@ -10649,15 +11339,15 @@
       <c r="M57" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N57" s="143" t="str">
+      <c r="N57" s="151" t="str">
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="O57" s="143" t="str">
+      <c r="O57" s="151" t="str">
         <f t="shared" si="1"/>
         <v>07:00</v>
       </c>
-      <c r="P57" s="143" t="str">
+      <c r="P57" s="151" t="str">
         <f t="shared" si="2"/>
         <v>07:00</v>
       </c>
@@ -10673,28 +11363,28 @@
         <v>78</v>
       </c>
       <c r="D58" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="E58" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="F58" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="G58" s="171" t="s">
-        <v>1487</v>
+      <c r="G58" s="229" t="s">
+        <v>1480</v>
       </c>
       <c r="H58" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="I58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="J58" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K58" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L58" s="168" t="s">
         <v>28</v>
@@ -10702,15 +11392,15 @@
       <c r="M58" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N58" s="143" t="str">
+      <c r="N58" s="151" t="str">
         <f t="shared" si="0"/>
         <v>08:00</v>
       </c>
-      <c r="O58" s="143" t="str">
+      <c r="O58" s="151" t="str">
         <f t="shared" si="1"/>
         <v>08:00</v>
       </c>
-      <c r="P58" s="143" t="str">
+      <c r="P58" s="151" t="str">
         <f t="shared" si="2"/>
         <v>08:00</v>
       </c>
@@ -10726,28 +11416,28 @@
         <v>79</v>
       </c>
       <c r="D59" s="171" t="s">
-        <v>1487</v>
-      </c>
-      <c r="E59" s="295" t="s">
-        <v>1484</v>
+        <v>1480</v>
+      </c>
+      <c r="E59" s="171" t="s">
+        <v>1521</v>
       </c>
       <c r="F59" s="171" t="s">
         <v>79</v>
       </c>
-      <c r="G59" s="171" t="s">
-        <v>1487</v>
+      <c r="G59" s="229" t="s">
+        <v>1480</v>
       </c>
       <c r="H59" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="I59" s="172" t="s">
-        <v>681</v>
+        <v>79</v>
       </c>
       <c r="J59" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K59" s="171" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="L59" s="168" t="s">
         <v>26</v>
@@ -10755,15 +11445,15 @@
       <c r="M59" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N59" s="143" t="str">
+      <c r="N59" s="151" t="str">
         <f t="shared" si="0"/>
         <v>09:00</v>
       </c>
-      <c r="O59" s="143" t="str">
+      <c r="O59" s="151" t="str">
         <f t="shared" si="1"/>
         <v>09:00</v>
       </c>
-      <c r="P59" s="143" t="str">
+      <c r="P59" s="151" t="str">
         <f t="shared" si="2"/>
         <v>09:00</v>
       </c>
@@ -10776,24 +11466,24 @@
         <v>55</v>
       </c>
       <c r="C60" s="172" t="s">
-        <v>441</v>
+        <v>80</v>
       </c>
       <c r="D60" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="E60" s="171"/>
       <c r="F60" s="172" t="s">
         <v>441</v>
       </c>
-      <c r="G60" s="171" t="s">
-        <v>1487</v>
+      <c r="G60" s="229" t="s">
+        <v>1480</v>
       </c>
       <c r="H60" s="171"/>
       <c r="I60" s="172" t="s">
-        <v>441</v>
+        <v>80</v>
       </c>
       <c r="J60" s="171" t="s">
-        <v>1487</v>
+        <v>1480</v>
       </c>
       <c r="K60" s="171"/>
       <c r="L60" s="168" t="s">
@@ -10802,15 +11492,15 @@
       <c r="M60" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N60" s="143" t="str">
+      <c r="N60" s="151" t="str">
         <f t="shared" si="0"/>
         <v>10:00</v>
       </c>
-      <c r="O60" s="143" t="str">
+      <c r="O60" s="151" t="str">
         <f t="shared" si="1"/>
         <v>10:00</v>
       </c>
-      <c r="P60" s="143" t="str">
+      <c r="P60" s="151" t="str">
         <f t="shared" si="2"/>
         <v>10:00</v>
       </c>
@@ -10825,29 +11515,41 @@
       <c r="C61" s="172"/>
       <c r="D61" s="171"/>
       <c r="E61" s="171"/>
-      <c r="F61" s="172"/>
-      <c r="G61" s="171"/>
-      <c r="H61" s="171"/>
-      <c r="I61" s="172"/>
-      <c r="J61" s="171"/>
-      <c r="K61" s="171"/>
+      <c r="F61" s="172" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G61" s="229" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H61" s="171" t="s">
+        <v>1399</v>
+      </c>
+      <c r="I61" s="172" t="s">
+        <v>1482</v>
+      </c>
+      <c r="J61" s="171" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K61" s="171" t="s">
+        <v>1402</v>
+      </c>
       <c r="L61" s="168" t="s">
         <v>23</v>
       </c>
       <c r="M61" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N61" s="143" t="str">
+      <c r="N61" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O61" s="143" t="str">
+      <c r="O61" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P61" s="143" t="str">
+        <v>11:05</v>
+      </c>
+      <c r="P61" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:40</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1">
@@ -10857,12 +11559,22 @@
       <c r="B62" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C62" s="171"/>
+      <c r="C62" s="172" t="s">
+        <v>1495</v>
+      </c>
       <c r="D62" s="171"/>
-      <c r="E62" s="171"/>
-      <c r="F62" s="172"/>
-      <c r="G62" s="171"/>
-      <c r="H62" s="171"/>
+      <c r="E62" s="171" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F62" s="172" t="s">
+        <v>1487</v>
+      </c>
+      <c r="G62" s="229" t="s">
+        <v>1517</v>
+      </c>
+      <c r="H62" s="171" t="s">
+        <v>1525</v>
+      </c>
       <c r="I62" s="172"/>
       <c r="J62" s="171"/>
       <c r="K62" s="171"/>
@@ -10872,15 +11584,15 @@
       <c r="M62" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N62" s="143" t="str">
+      <c r="N62" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O62" s="143" t="str">
+        <v>12:23</v>
+      </c>
+      <c r="O62" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P62" s="143" t="str">
+        <v>12:34</v>
+      </c>
+      <c r="P62" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10896,28 +11608,34 @@
       <c r="D63" s="171"/>
       <c r="E63" s="171"/>
       <c r="F63" s="172"/>
-      <c r="G63" s="171"/>
+      <c r="G63" s="229"/>
       <c r="H63" s="171"/>
-      <c r="I63" s="172"/>
-      <c r="J63" s="171"/>
-      <c r="K63" s="171"/>
+      <c r="I63" s="172" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J63" s="171" t="s">
+        <v>13</v>
+      </c>
+      <c r="K63" s="171" t="s">
+        <v>1403</v>
+      </c>
       <c r="L63" s="168" t="s">
         <v>21</v>
       </c>
       <c r="M63" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N63" s="143" t="str">
+      <c r="N63" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O63" s="143" t="str">
+      <c r="O63" s="151" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P63" s="143" t="str">
+      <c r="P63" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:14</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="18" customHeight="1">
@@ -10930,29 +11648,41 @@
       <c r="C64" s="172"/>
       <c r="D64" s="171"/>
       <c r="E64" s="171"/>
-      <c r="F64" s="172"/>
-      <c r="G64" s="172"/>
-      <c r="H64" s="171"/>
-      <c r="I64" s="172"/>
-      <c r="J64" s="171"/>
-      <c r="K64" s="171"/>
+      <c r="F64" s="172" t="s">
+        <v>1488</v>
+      </c>
+      <c r="G64" s="229" t="s">
+        <v>0</v>
+      </c>
+      <c r="H64" s="171" t="s">
+        <v>1524</v>
+      </c>
+      <c r="I64" s="172" t="s">
+        <v>1484</v>
+      </c>
+      <c r="J64" s="171" t="s">
+        <v>13</v>
+      </c>
+      <c r="K64" s="171" t="s">
+        <v>1515</v>
+      </c>
       <c r="L64" s="168" t="s">
         <v>20</v>
       </c>
       <c r="M64" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N64" s="143" t="str">
+      <c r="N64" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O64" s="143" t="str">
+      <c r="O64" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P64" s="143" t="str">
+        <v>14:04</v>
+      </c>
+      <c r="P64" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:43</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="18" customHeight="1">
@@ -10965,9 +11695,15 @@
       <c r="C65" s="168"/>
       <c r="D65" s="171"/>
       <c r="E65" s="171"/>
-      <c r="F65" s="172"/>
-      <c r="G65" s="171"/>
-      <c r="H65" s="171"/>
+      <c r="F65" s="172" t="s">
+        <v>695</v>
+      </c>
+      <c r="G65" s="229" t="s">
+        <v>1523</v>
+      </c>
+      <c r="H65" s="171" t="s">
+        <v>1018</v>
+      </c>
       <c r="I65" s="173"/>
       <c r="J65" s="171"/>
       <c r="K65" s="171"/>
@@ -10977,15 +11713,15 @@
       <c r="M65" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N65" s="143" t="str">
+      <c r="N65" s="151" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="O65" s="143" t="str">
+      <c r="O65" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P65" s="143" t="str">
+        <v>15:31</v>
+      </c>
+      <c r="P65" s="151" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10997,32 +11733,48 @@
       <c r="B66" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C66" s="172"/>
+      <c r="C66" s="172" t="s">
+        <v>1494</v>
+      </c>
       <c r="D66" s="171"/>
-      <c r="E66" s="171"/>
-      <c r="F66" s="172"/>
-      <c r="G66" s="171"/>
-      <c r="H66" s="171"/>
-      <c r="I66" s="172"/>
-      <c r="J66" s="171"/>
-      <c r="K66" s="171"/>
+      <c r="E66" s="171" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F66" s="172" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G66" s="229" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="171" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I66" s="172" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J66" s="171" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K66" s="171" t="s">
+        <v>1403</v>
+      </c>
       <c r="L66" s="168" t="s">
         <v>16</v>
       </c>
       <c r="M66" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N66" s="143" t="str">
+      <c r="N66" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="O66" s="143" t="str">
+        <v>16:51</v>
+      </c>
+      <c r="O66" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="P66" s="143" t="str">
+        <v>16:59</v>
+      </c>
+      <c r="P66" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:16</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="18" customHeight="1">
@@ -11036,28 +11788,34 @@
       <c r="D67" s="171"/>
       <c r="E67" s="171"/>
       <c r="F67" s="172"/>
-      <c r="G67" s="171"/>
+      <c r="G67" s="229"/>
       <c r="H67" s="171"/>
-      <c r="I67" s="173"/>
-      <c r="J67" s="171"/>
-      <c r="K67" s="171"/>
+      <c r="I67" s="173" t="s">
+        <v>595</v>
+      </c>
+      <c r="J67" s="171" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K67" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L67" s="168" t="s">
         <v>15</v>
       </c>
       <c r="M67" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N67" s="143" t="str">
+      <c r="N67" s="151" t="str">
         <f t="shared" ref="N67:N130" si="3">IF($C67&lt;&gt;"",TEXT($C67,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="O67" s="143" t="str">
+      <c r="O67" s="151" t="str">
         <f t="shared" ref="O67:O130" si="4">IF($F67&lt;&gt;"",TEXT($F67,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="P67" s="143" t="str">
+      <c r="P67" s="151" t="str">
         <f t="shared" ref="P67:P130" si="5">IF($I67&lt;&gt;"",TEXT($I67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:52</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="18" customHeight="1">
@@ -11070,9 +11828,15 @@
       <c r="C68" s="172"/>
       <c r="D68" s="171"/>
       <c r="E68" s="171"/>
-      <c r="F68" s="172"/>
-      <c r="G68" s="171"/>
-      <c r="H68" s="171"/>
+      <c r="F68" s="172" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G68" s="229" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="171" t="s">
+        <v>1016</v>
+      </c>
       <c r="I68" s="172"/>
       <c r="J68" s="171"/>
       <c r="K68" s="171"/>
@@ -11082,15 +11846,15 @@
       <c r="M68" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N68" s="143" t="str">
+      <c r="N68" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O68" s="143" t="str">
+      <c r="O68" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P68" s="143" t="str">
+        <v>18:32</v>
+      </c>
+      <c r="P68" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11105,29 +11869,41 @@
       <c r="C69" s="172"/>
       <c r="D69" s="171"/>
       <c r="E69" s="171"/>
-      <c r="F69" s="172"/>
-      <c r="G69" s="171"/>
-      <c r="H69" s="171"/>
-      <c r="I69" s="172"/>
-      <c r="J69" s="171"/>
-      <c r="K69" s="171"/>
+      <c r="F69" s="172" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G69" s="229" t="s">
+        <v>0</v>
+      </c>
+      <c r="H69" s="171" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I69" s="172" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J69" s="171" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K69" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L69" s="168" t="s">
         <v>10</v>
       </c>
       <c r="M69" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N69" s="143" t="str">
+      <c r="N69" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O69" s="143" t="str">
+      <c r="O69" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P69" s="143" t="str">
+        <v>19:57</v>
+      </c>
+      <c r="P69" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>19:21</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1">
@@ -11137,32 +11913,42 @@
       <c r="B70" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="172"/>
+      <c r="C70" s="172" t="s">
+        <v>1493</v>
+      </c>
       <c r="D70" s="171"/>
-      <c r="E70" s="171"/>
+      <c r="E70" s="171" t="s">
+        <v>71</v>
+      </c>
       <c r="F70" s="172"/>
-      <c r="G70" s="171"/>
+      <c r="G70" s="229"/>
       <c r="H70" s="171"/>
-      <c r="I70" s="173"/>
-      <c r="J70" s="171"/>
-      <c r="K70" s="171"/>
+      <c r="I70" s="173" t="s">
+        <v>1508</v>
+      </c>
+      <c r="J70" s="171" t="s">
+        <v>13</v>
+      </c>
+      <c r="K70" s="171" t="s">
+        <v>1403</v>
+      </c>
       <c r="L70" s="168" t="s">
         <v>9</v>
       </c>
       <c r="M70" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N70" s="143" t="str">
+      <c r="N70" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O70" s="143" t="str">
+        <v>20:23</v>
+      </c>
+      <c r="O70" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P70" s="143" t="str">
+      <c r="P70" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:49</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="18" customHeight="1">
@@ -11175,9 +11961,15 @@
       <c r="C71" s="172"/>
       <c r="D71" s="171"/>
       <c r="E71" s="171"/>
-      <c r="F71" s="172"/>
-      <c r="G71" s="171"/>
-      <c r="H71" s="171"/>
+      <c r="F71" s="172" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G71" s="229" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="171" t="s">
+        <v>1016</v>
+      </c>
       <c r="I71" s="172"/>
       <c r="J71" s="171"/>
       <c r="K71" s="171"/>
@@ -11187,15 +11979,15 @@
       <c r="M71" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N71" s="143" t="str">
+      <c r="N71" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O71" s="143" t="str">
+      <c r="O71" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P71" s="143" t="str">
+        <v>21:25</v>
+      </c>
+      <c r="P71" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11211,28 +12003,34 @@
       <c r="D72" s="171"/>
       <c r="E72" s="171"/>
       <c r="F72" s="172"/>
-      <c r="G72" s="171"/>
+      <c r="G72" s="229"/>
       <c r="H72" s="171"/>
-      <c r="I72" s="172"/>
-      <c r="J72" s="171"/>
-      <c r="K72" s="171"/>
+      <c r="I72" s="172" t="s">
+        <v>791</v>
+      </c>
+      <c r="J72" s="171" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K72" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L72" s="168" t="s">
         <v>5</v>
       </c>
       <c r="M72" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="N72" s="143" t="str">
+      <c r="N72" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O72" s="143" t="str">
+      <c r="O72" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P72" s="143" t="str">
+      <c r="P72" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>22:24</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -11245,29 +12043,41 @@
       <c r="C73" s="176"/>
       <c r="D73" s="175"/>
       <c r="E73" s="175"/>
-      <c r="F73" s="176"/>
-      <c r="G73" s="175"/>
-      <c r="H73" s="175"/>
-      <c r="I73" s="176"/>
-      <c r="J73" s="175"/>
-      <c r="K73" s="175"/>
+      <c r="F73" s="176" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G73" s="233" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="175" t="s">
+        <v>1596</v>
+      </c>
+      <c r="I73" s="176" t="s">
+        <v>150</v>
+      </c>
+      <c r="J73" s="175" t="s">
+        <v>13</v>
+      </c>
+      <c r="K73" s="175" t="s">
+        <v>1403</v>
+      </c>
       <c r="L73" s="174" t="s">
         <v>3</v>
       </c>
       <c r="M73" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="N73" s="143" t="str">
+      <c r="N73" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O73" s="143" t="str">
+      <c r="O73" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P73" s="143" t="str">
+        <v>23:00</v>
+      </c>
+      <c r="P73" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:54</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="18" customHeight="1">
@@ -11280,9 +12090,15 @@
       <c r="C74" s="179"/>
       <c r="D74" s="178"/>
       <c r="E74" s="178"/>
-      <c r="F74" s="179"/>
-      <c r="G74" s="178"/>
-      <c r="H74" s="178"/>
+      <c r="F74" s="179" t="s">
+        <v>141</v>
+      </c>
+      <c r="G74" s="235" t="s">
+        <v>27</v>
+      </c>
+      <c r="H74" s="178" t="s">
+        <v>1396</v>
+      </c>
       <c r="I74" s="179"/>
       <c r="J74" s="178"/>
       <c r="K74" s="178"/>
@@ -11292,15 +12108,15 @@
       <c r="M74" s="178" t="s">
         <v>52</v>
       </c>
-      <c r="N74" s="143" t="str">
+      <c r="N74" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O74" s="143" t="str">
+      <c r="O74" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P74" s="143" t="str">
+        <v>00:00</v>
+      </c>
+      <c r="P74" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11315,29 +12131,41 @@
       <c r="C75" s="181"/>
       <c r="D75" s="180"/>
       <c r="E75" s="180"/>
-      <c r="F75" s="181"/>
-      <c r="G75" s="180"/>
-      <c r="H75" s="180"/>
-      <c r="I75" s="181"/>
-      <c r="J75" s="180"/>
-      <c r="K75" s="180"/>
+      <c r="F75" s="181" t="s">
+        <v>127</v>
+      </c>
+      <c r="G75" s="237" t="s">
+        <v>1595</v>
+      </c>
+      <c r="H75" s="180" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I75" s="181" t="s">
+        <v>600</v>
+      </c>
+      <c r="J75" s="180" t="s">
+        <v>1602</v>
+      </c>
+      <c r="K75" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L75" s="177" t="s">
         <v>36</v>
       </c>
       <c r="M75" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N75" s="143" t="str">
+      <c r="N75" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O75" s="143" t="str">
+      <c r="O75" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P75" s="143" t="str">
+        <v>01:26</v>
+      </c>
+      <c r="P75" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:02</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="18" customHeight="1">
@@ -11350,29 +12178,41 @@
       <c r="C76" s="181"/>
       <c r="D76" s="180"/>
       <c r="E76" s="180"/>
-      <c r="F76" s="181"/>
-      <c r="G76" s="180"/>
-      <c r="H76" s="180"/>
-      <c r="I76" s="182"/>
-      <c r="J76" s="180"/>
-      <c r="K76" s="180"/>
+      <c r="F76" s="181" t="s">
+        <v>783</v>
+      </c>
+      <c r="G76" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="180" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I76" s="182" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J76" s="180" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K76" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L76" s="177" t="s">
         <v>35</v>
       </c>
       <c r="M76" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N76" s="143" t="str">
+      <c r="N76" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O76" s="143" t="str">
+      <c r="O76" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P76" s="143" t="str">
+        <v>02:55</v>
+      </c>
+      <c r="P76" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:27</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="18" customHeight="1">
@@ -11386,28 +12226,34 @@
       <c r="D77" s="180"/>
       <c r="E77" s="180"/>
       <c r="F77" s="181"/>
-      <c r="G77" s="180"/>
+      <c r="G77" s="237"/>
       <c r="H77" s="180"/>
-      <c r="I77" s="291"/>
-      <c r="J77" s="180"/>
-      <c r="K77" s="180"/>
+      <c r="I77" s="181" t="s">
+        <v>998</v>
+      </c>
+      <c r="J77" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L77" s="177" t="s">
         <v>33</v>
       </c>
       <c r="M77" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N77" s="143" t="str">
+      <c r="N77" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O77" s="143" t="str">
+      <c r="O77" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P77" s="143" t="str">
+      <c r="P77" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>03:57</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1">
@@ -11420,10 +12266,16 @@
       <c r="C78" s="181"/>
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
-      <c r="F78" s="181"/>
-      <c r="G78" s="180"/>
-      <c r="H78" s="180"/>
-      <c r="I78" s="291"/>
+      <c r="F78" s="181" t="s">
+        <v>784</v>
+      </c>
+      <c r="G78" s="237" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="180" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I78" s="181"/>
       <c r="J78" s="180"/>
       <c r="K78" s="180"/>
       <c r="L78" s="177" t="s">
@@ -11432,15 +12284,15 @@
       <c r="M78" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N78" s="143" t="str">
+      <c r="N78" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O78" s="143" t="str">
+      <c r="O78" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P78" s="143" t="str">
+        <v>04:24</v>
+      </c>
+      <c r="P78" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11455,29 +12307,41 @@
       <c r="C79" s="181"/>
       <c r="D79" s="180"/>
       <c r="E79" s="180"/>
-      <c r="F79" s="181"/>
-      <c r="G79" s="180"/>
-      <c r="H79" s="180"/>
-      <c r="I79" s="181"/>
-      <c r="J79" s="180"/>
-      <c r="K79" s="180"/>
+      <c r="F79" s="181" t="s">
+        <v>272</v>
+      </c>
+      <c r="G79" s="237" t="s">
+        <v>0</v>
+      </c>
+      <c r="H79" s="180" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I79" s="181" t="s">
+        <v>108</v>
+      </c>
+      <c r="J79" s="180" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K79" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L79" s="177" t="s">
         <v>31</v>
       </c>
       <c r="M79" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N79" s="143" t="str">
+      <c r="N79" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O79" s="143" t="str">
+      <c r="O79" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P79" s="143" t="str">
+        <v>05:53</v>
+      </c>
+      <c r="P79" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:31</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1">
@@ -11487,11 +12351,11 @@
       <c r="B80" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C80" s="291"/>
+      <c r="C80" s="181"/>
       <c r="D80" s="180"/>
       <c r="E80" s="180"/>
       <c r="F80" s="181"/>
-      <c r="G80" s="180"/>
+      <c r="G80" s="237"/>
       <c r="H80" s="180"/>
       <c r="I80" s="182"/>
       <c r="J80" s="180"/>
@@ -11502,15 +12366,15 @@
       <c r="M80" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N80" s="143" t="str">
+      <c r="N80" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O80" s="143" t="str">
+      <c r="O80" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P80" s="143" t="str">
+      <c r="P80" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11525,29 +12389,41 @@
       <c r="C81" s="181"/>
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
-      <c r="F81" s="181"/>
-      <c r="G81" s="180"/>
-      <c r="H81" s="180"/>
-      <c r="I81" s="181"/>
-      <c r="J81" s="180"/>
-      <c r="K81" s="180"/>
+      <c r="F81" s="181" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G81" s="237" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H81" s="180" t="s">
+        <v>1590</v>
+      </c>
+      <c r="I81" s="181" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J81" s="180" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K81" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L81" s="177" t="s">
         <v>29</v>
       </c>
       <c r="M81" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N81" s="143" t="str">
+      <c r="N81" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O81" s="143" t="str">
+      <c r="O81" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P81" s="143" t="str">
+        <v>07:26</v>
+      </c>
+      <c r="P81" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:05</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="18" customHeight="1">
@@ -11560,29 +12436,41 @@
       <c r="C82" s="181"/>
       <c r="D82" s="180"/>
       <c r="E82" s="180"/>
-      <c r="F82" s="181"/>
-      <c r="G82" s="180"/>
-      <c r="H82" s="180"/>
-      <c r="I82" s="181"/>
-      <c r="J82" s="180"/>
-      <c r="K82" s="180"/>
+      <c r="F82" s="181" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G82" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="180" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I82" s="181" t="s">
+        <v>808</v>
+      </c>
+      <c r="J82" s="180" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K82" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L82" s="177" t="s">
         <v>28</v>
       </c>
       <c r="M82" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N82" s="143" t="str">
+      <c r="N82" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O82" s="143" t="str">
+      <c r="O82" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P82" s="143" t="str">
+        <v>08:57</v>
+      </c>
+      <c r="P82" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:38</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="18" customHeight="1">
@@ -11596,7 +12484,7 @@
       <c r="D83" s="180"/>
       <c r="E83" s="180"/>
       <c r="F83" s="181"/>
-      <c r="G83" s="180"/>
+      <c r="G83" s="237"/>
       <c r="H83" s="180"/>
       <c r="I83" s="182"/>
       <c r="J83" s="180"/>
@@ -11607,15 +12495,15 @@
       <c r="M83" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N83" s="143" t="str">
+      <c r="N83" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O83" s="143" t="str">
+      <c r="O83" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P83" s="143" t="str">
+      <c r="P83" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11627,32 +12515,48 @@
       <c r="B84" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C84" s="180"/>
+      <c r="C84" s="181" t="s">
+        <v>1492</v>
+      </c>
       <c r="D84" s="180"/>
-      <c r="E84" s="180"/>
-      <c r="F84" s="181"/>
-      <c r="G84" s="180"/>
-      <c r="H84" s="180"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="180"/>
-      <c r="K84" s="180"/>
+      <c r="E84" s="180" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F84" s="181" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G84" s="237" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H84" s="180" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I84" s="181" t="s">
+        <v>651</v>
+      </c>
+      <c r="J84" s="180" t="s">
+        <v>1602</v>
+      </c>
+      <c r="K84" s="180" t="s">
+        <v>1603</v>
+      </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
       </c>
       <c r="M84" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N84" s="143" t="str">
+      <c r="N84" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O84" s="143" t="str">
+        <v>10:11</v>
+      </c>
+      <c r="O84" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P84" s="143" t="str">
+        <v>10:31</v>
+      </c>
+      <c r="P84" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>10:05</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1">
@@ -11666,28 +12570,34 @@
       <c r="D85" s="180"/>
       <c r="E85" s="180"/>
       <c r="F85" s="181"/>
-      <c r="G85" s="180"/>
+      <c r="G85" s="237"/>
       <c r="H85" s="180"/>
-      <c r="I85" s="181"/>
-      <c r="J85" s="180"/>
-      <c r="K85" s="180"/>
+      <c r="I85" s="181" t="s">
+        <v>835</v>
+      </c>
+      <c r="J85" s="180" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K85" s="180" t="s">
+        <v>1605</v>
+      </c>
       <c r="L85" s="177" t="s">
         <v>23</v>
       </c>
       <c r="M85" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N85" s="143" t="str">
+      <c r="N85" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O85" s="143" t="str">
+      <c r="O85" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P85" s="143" t="str">
+      <c r="P85" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>11:34</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1">
@@ -11700,9 +12610,15 @@
       <c r="C86" s="180"/>
       <c r="D86" s="180"/>
       <c r="E86" s="180"/>
-      <c r="F86" s="181"/>
-      <c r="G86" s="180"/>
-      <c r="H86" s="180"/>
+      <c r="F86" s="181" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G86" s="237" t="s">
+        <v>1593</v>
+      </c>
+      <c r="H86" s="180" t="s">
+        <v>1594</v>
+      </c>
       <c r="I86" s="182"/>
       <c r="J86" s="180"/>
       <c r="K86" s="180"/>
@@ -11712,15 +12628,15 @@
       <c r="M86" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N86" s="143" t="str">
+      <c r="N86" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O86" s="143" t="str">
+      <c r="O86" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P86" s="143" t="str">
+        <v>12:02</v>
+      </c>
+      <c r="P86" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11735,29 +12651,41 @@
       <c r="C87" s="181"/>
       <c r="D87" s="180"/>
       <c r="E87" s="180"/>
-      <c r="F87" s="181"/>
-      <c r="G87" s="180"/>
-      <c r="H87" s="180"/>
-      <c r="I87" s="181"/>
-      <c r="J87" s="180"/>
-      <c r="K87" s="180"/>
+      <c r="F87" s="181" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G87" s="237" t="s">
+        <v>0</v>
+      </c>
+      <c r="H87" s="237" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I87" s="181" t="s">
+        <v>1549</v>
+      </c>
+      <c r="J87" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K87" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L87" s="177" t="s">
         <v>21</v>
       </c>
       <c r="M87" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N87" s="143" t="str">
+      <c r="N87" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O87" s="143" t="str">
+      <c r="O87" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P87" s="143" t="str">
+        <v>13:31</v>
+      </c>
+      <c r="P87" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>13:01</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="18" customHeight="1">
@@ -11767,32 +12695,48 @@
       <c r="B88" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C88" s="181"/>
+      <c r="C88" s="181" t="s">
+        <v>1491</v>
+      </c>
       <c r="D88" s="180"/>
-      <c r="E88" s="180"/>
-      <c r="F88" s="291"/>
-      <c r="G88" s="180"/>
-      <c r="H88" s="180"/>
-      <c r="I88" s="181"/>
-      <c r="J88" s="180"/>
-      <c r="K88" s="180"/>
+      <c r="E88" s="180" t="s">
+        <v>1537</v>
+      </c>
+      <c r="F88" s="181" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G88" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="180" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I88" s="181" t="s">
+        <v>1075</v>
+      </c>
+      <c r="J88" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K88" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L88" s="177" t="s">
         <v>20</v>
       </c>
       <c r="M88" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N88" s="143" t="str">
+      <c r="N88" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O88" s="143" t="str">
+        <v>14:10</v>
+      </c>
+      <c r="O88" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P88" s="143" t="str">
+        <v>14:58</v>
+      </c>
+      <c r="P88" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>14:35</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="18" customHeight="1">
@@ -11806,9 +12750,9 @@
       <c r="D89" s="180"/>
       <c r="E89" s="180"/>
       <c r="F89" s="181"/>
-      <c r="G89" s="180"/>
+      <c r="G89" s="237"/>
       <c r="H89" s="180"/>
-      <c r="I89" s="276"/>
+      <c r="I89" s="182"/>
       <c r="J89" s="180"/>
       <c r="K89" s="180"/>
       <c r="L89" s="177" t="s">
@@ -11817,15 +12761,15 @@
       <c r="M89" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N89" s="143" t="str">
+      <c r="N89" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O89" s="143" t="str">
+      <c r="O89" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P89" s="143" t="str">
+      <c r="P89" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11840,29 +12784,41 @@
       <c r="C90" s="181"/>
       <c r="D90" s="180"/>
       <c r="E90" s="180"/>
-      <c r="F90" s="181"/>
-      <c r="G90" s="180"/>
-      <c r="H90" s="180"/>
-      <c r="I90" s="181"/>
-      <c r="J90" s="180"/>
-      <c r="K90" s="180"/>
+      <c r="F90" s="181" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G90" s="237" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="180" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I90" s="181" t="s">
+        <v>124</v>
+      </c>
+      <c r="J90" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L90" s="177" t="s">
         <v>16</v>
       </c>
       <c r="M90" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N90" s="143" t="str">
+      <c r="N90" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O90" s="143" t="str">
+      <c r="O90" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P90" s="143" t="str">
+        <v>16:27</v>
+      </c>
+      <c r="P90" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>16:09</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="18" customHeight="1">
@@ -11875,29 +12831,41 @@
       <c r="C91" s="181"/>
       <c r="D91" s="180"/>
       <c r="E91" s="180"/>
-      <c r="F91" s="181"/>
-      <c r="G91" s="180"/>
-      <c r="H91" s="180"/>
-      <c r="I91" s="181"/>
-      <c r="J91" s="180"/>
-      <c r="K91" s="180"/>
+      <c r="F91" s="181" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G91" s="237" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" s="180" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I91" s="181" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J91" s="180" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="180" t="s">
+        <v>1015</v>
+      </c>
       <c r="L91" s="177" t="s">
         <v>15</v>
       </c>
       <c r="M91" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N91" s="143" t="str">
+      <c r="N91" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O91" s="143" t="str">
+      <c r="O91" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P91" s="143" t="str">
+        <v>17:56</v>
+      </c>
+      <c r="P91" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>17:35</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1">
@@ -11907,11 +12875,15 @@
       <c r="B92" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C92" s="181"/>
+      <c r="C92" s="181" t="s">
+        <v>1490</v>
+      </c>
       <c r="D92" s="180"/>
-      <c r="E92" s="180"/>
+      <c r="E92" s="180" t="s">
+        <v>1501</v>
+      </c>
       <c r="F92" s="181"/>
-      <c r="G92" s="180"/>
+      <c r="G92" s="237"/>
       <c r="H92" s="180"/>
       <c r="I92" s="182"/>
       <c r="J92" s="180"/>
@@ -11922,15 +12894,15 @@
       <c r="M92" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N92" s="143" t="str">
+      <c r="N92" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O92" s="143" t="str">
+        <v>18:25</v>
+      </c>
+      <c r="O92" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P92" s="143" t="str">
+      <c r="P92" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -11945,29 +12917,41 @@
       <c r="C93" s="180"/>
       <c r="D93" s="180"/>
       <c r="E93" s="180"/>
-      <c r="F93" s="181"/>
-      <c r="G93" s="180"/>
-      <c r="H93" s="180"/>
-      <c r="I93" s="181"/>
-      <c r="J93" s="180"/>
-      <c r="K93" s="180"/>
+      <c r="F93" s="181" t="s">
+        <v>789</v>
+      </c>
+      <c r="G93" s="237" t="s">
+        <v>27</v>
+      </c>
+      <c r="H93" s="180" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I93" s="181" t="s">
+        <v>1553</v>
+      </c>
+      <c r="J93" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K93" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L93" s="177" t="s">
         <v>10</v>
       </c>
       <c r="M93" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N93" s="143" t="str">
+      <c r="N93" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O93" s="143" t="str">
+      <c r="O93" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P93" s="143" t="str">
+        <v>19:22</v>
+      </c>
+      <c r="P93" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>19:03</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="18" customHeight="1">
@@ -11980,29 +12964,41 @@
       <c r="C94" s="181"/>
       <c r="D94" s="180"/>
       <c r="E94" s="180"/>
-      <c r="F94" s="181"/>
-      <c r="G94" s="180"/>
-      <c r="H94" s="180"/>
-      <c r="I94" s="181"/>
-      <c r="J94" s="180"/>
-      <c r="K94" s="180"/>
+      <c r="F94" s="181" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G94" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="180" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I94" s="181" t="s">
+        <v>1555</v>
+      </c>
+      <c r="J94" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K94" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L94" s="177" t="s">
         <v>9</v>
       </c>
       <c r="M94" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N94" s="143" t="str">
+      <c r="N94" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O94" s="143" t="str">
+      <c r="O94" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P94" s="143" t="str">
+        <v>20:47</v>
+      </c>
+      <c r="P94" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:35</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1">
@@ -12016,7 +13012,7 @@
       <c r="D95" s="180"/>
       <c r="E95" s="180"/>
       <c r="F95" s="181"/>
-      <c r="G95" s="180"/>
+      <c r="G95" s="237"/>
       <c r="H95" s="180"/>
       <c r="I95" s="181"/>
       <c r="J95" s="180"/>
@@ -12027,15 +13023,15 @@
       <c r="M95" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N95" s="143" t="str">
+      <c r="N95" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O95" s="143" t="str">
+      <c r="O95" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P95" s="143" t="str">
+      <c r="P95" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12050,29 +13046,41 @@
       <c r="C96" s="181"/>
       <c r="D96" s="180"/>
       <c r="E96" s="180"/>
-      <c r="F96" s="181"/>
-      <c r="G96" s="180"/>
-      <c r="H96" s="180"/>
-      <c r="I96" s="182"/>
-      <c r="J96" s="180"/>
-      <c r="K96" s="180"/>
+      <c r="F96" s="181" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G96" s="237" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="180" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I96" s="182" t="s">
+        <v>126</v>
+      </c>
+      <c r="J96" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="K96" s="180" t="s">
+        <v>1403</v>
+      </c>
       <c r="L96" s="177" t="s">
         <v>5</v>
       </c>
       <c r="M96" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="N96" s="143" t="str">
+      <c r="N96" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O96" s="143" t="str">
+      <c r="O96" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P96" s="143" t="str">
+        <v>22:16</v>
+      </c>
+      <c r="P96" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>22:04</v>
       </c>
     </row>
     <row r="97" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -12085,29 +13093,41 @@
       <c r="C97" s="185"/>
       <c r="D97" s="184"/>
       <c r="E97" s="184"/>
-      <c r="F97" s="185"/>
-      <c r="G97" s="184"/>
-      <c r="H97" s="184"/>
-      <c r="I97" s="185"/>
-      <c r="J97" s="184"/>
-      <c r="K97" s="184"/>
+      <c r="F97" s="185" t="s">
+        <v>295</v>
+      </c>
+      <c r="G97" s="240" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="184" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I97" s="185" t="s">
+        <v>1291</v>
+      </c>
+      <c r="J97" s="184" t="s">
+        <v>13</v>
+      </c>
+      <c r="K97" s="184" t="s">
+        <v>1403</v>
+      </c>
       <c r="L97" s="183" t="s">
         <v>3</v>
       </c>
       <c r="M97" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="N97" s="143" t="str">
+      <c r="N97" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O97" s="143" t="str">
+      <c r="O97" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P97" s="143" t="str">
+        <v>23:50</v>
+      </c>
+      <c r="P97" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:34</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1">
@@ -12121,7 +13141,7 @@
       <c r="D98" s="187"/>
       <c r="E98" s="187"/>
       <c r="F98" s="188"/>
-      <c r="G98" s="187"/>
+      <c r="G98" s="242"/>
       <c r="H98" s="187"/>
       <c r="I98" s="188"/>
       <c r="J98" s="187"/>
@@ -12132,15 +13152,15 @@
       <c r="M98" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="N98" s="143" t="str">
+      <c r="N98" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O98" s="143" t="str">
+      <c r="O98" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P98" s="143" t="str">
+      <c r="P98" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12155,29 +13175,41 @@
       <c r="C99" s="188"/>
       <c r="D99" s="187"/>
       <c r="E99" s="189"/>
-      <c r="F99" s="190"/>
-      <c r="G99" s="189"/>
-      <c r="H99" s="189"/>
-      <c r="I99" s="190"/>
-      <c r="J99" s="189"/>
-      <c r="K99" s="189"/>
+      <c r="F99" s="190" t="s">
+        <v>623</v>
+      </c>
+      <c r="G99" s="244" t="s">
+        <v>0</v>
+      </c>
+      <c r="H99" s="189" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I99" s="190" t="s">
+        <v>792</v>
+      </c>
+      <c r="J99" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K99" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L99" s="186" t="s">
         <v>36</v>
       </c>
       <c r="M99" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N99" s="143" t="str">
+      <c r="N99" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O99" s="143" t="str">
+      <c r="O99" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P99" s="143" t="str">
+        <v>01:01</v>
+      </c>
+      <c r="P99" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:05</v>
       </c>
     </row>
     <row r="100" spans="1:16" ht="18" customHeight="1">
@@ -12190,29 +13222,41 @@
       <c r="C100" s="190"/>
       <c r="D100" s="189"/>
       <c r="E100" s="189"/>
-      <c r="F100" s="190"/>
-      <c r="G100" s="189"/>
-      <c r="H100" s="189"/>
-      <c r="I100" s="190"/>
-      <c r="J100" s="189"/>
-      <c r="K100" s="189"/>
+      <c r="F100" s="190" t="s">
+        <v>793</v>
+      </c>
+      <c r="G100" s="244" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="189" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I100" s="190" t="s">
+        <v>793</v>
+      </c>
+      <c r="J100" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K100" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L100" s="186" t="s">
         <v>35</v>
       </c>
       <c r="M100" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N100" s="143" t="str">
+      <c r="N100" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O100" s="143" t="str">
+      <c r="O100" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P100" s="143" t="str">
+        <v>02:31</v>
+      </c>
+      <c r="P100" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:31</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1">
@@ -12226,7 +13270,7 @@
       <c r="D101" s="189"/>
       <c r="E101" s="189"/>
       <c r="F101" s="190"/>
-      <c r="G101" s="189"/>
+      <c r="G101" s="244"/>
       <c r="H101" s="189"/>
       <c r="I101" s="190"/>
       <c r="J101" s="189"/>
@@ -12237,15 +13281,15 @@
       <c r="M101" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N101" s="143" t="str">
+      <c r="N101" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O101" s="143" t="str">
+      <c r="O101" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P101" s="143" t="str">
+      <c r="P101" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12260,29 +13304,41 @@
       <c r="C102" s="190"/>
       <c r="D102" s="189"/>
       <c r="E102" s="189"/>
-      <c r="F102" s="190"/>
-      <c r="G102" s="189"/>
-      <c r="H102" s="189"/>
-      <c r="I102" s="190"/>
-      <c r="J102" s="189"/>
-      <c r="K102" s="189"/>
+      <c r="F102" s="190" t="s">
+        <v>794</v>
+      </c>
+      <c r="G102" s="244" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" s="189" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I102" s="190" t="s">
+        <v>794</v>
+      </c>
+      <c r="J102" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K102" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L102" s="186" t="s">
         <v>32</v>
       </c>
       <c r="M102" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N102" s="143" t="str">
+      <c r="N102" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O102" s="143" t="str">
+      <c r="O102" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P102" s="143" t="str">
+        <v>04:02</v>
+      </c>
+      <c r="P102" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>04:02</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="18" customHeight="1">
@@ -12295,29 +13351,41 @@
       <c r="C103" s="189"/>
       <c r="D103" s="189"/>
       <c r="E103" s="189"/>
-      <c r="F103" s="190"/>
-      <c r="G103" s="189"/>
-      <c r="H103" s="189"/>
-      <c r="I103" s="190"/>
-      <c r="J103" s="189"/>
-      <c r="K103" s="189"/>
+      <c r="F103" s="190" t="s">
+        <v>616</v>
+      </c>
+      <c r="G103" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="189" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I103" s="190" t="s">
+        <v>1557</v>
+      </c>
+      <c r="J103" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K103" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L103" s="186" t="s">
         <v>31</v>
       </c>
       <c r="M103" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N103" s="143" t="str">
+      <c r="N103" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O103" s="143" t="str">
+      <c r="O103" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P103" s="143" t="str">
+        <v>05:35</v>
+      </c>
+      <c r="P103" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:29</v>
       </c>
     </row>
     <row r="104" spans="1:16" ht="18" customHeight="1">
@@ -12331,7 +13399,7 @@
       <c r="D104" s="189"/>
       <c r="E104" s="189"/>
       <c r="F104" s="190"/>
-      <c r="G104" s="189"/>
+      <c r="G104" s="244"/>
       <c r="H104" s="189"/>
       <c r="I104" s="190"/>
       <c r="J104" s="189"/>
@@ -12342,15 +13410,15 @@
       <c r="M104" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N104" s="143" t="str">
+      <c r="N104" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O104" s="143" t="str">
+      <c r="O104" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P104" s="143" t="str">
+      <c r="P104" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12365,29 +13433,41 @@
       <c r="C105" s="190"/>
       <c r="D105" s="189"/>
       <c r="E105" s="189"/>
-      <c r="F105" s="190"/>
-      <c r="G105" s="189"/>
-      <c r="H105" s="189"/>
-      <c r="I105" s="190"/>
-      <c r="J105" s="189"/>
-      <c r="K105" s="189"/>
+      <c r="F105" s="190" t="s">
+        <v>205</v>
+      </c>
+      <c r="G105" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H105" s="189" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I105" s="190" t="s">
+        <v>81</v>
+      </c>
+      <c r="J105" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K105" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L105" s="186" t="s">
         <v>29</v>
       </c>
       <c r="M105" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N105" s="143" t="str">
+      <c r="N105" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O105" s="143" t="str">
+      <c r="O105" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P105" s="143" t="str">
+        <v>07:06</v>
+      </c>
+      <c r="P105" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:00</v>
       </c>
     </row>
     <row r="106" spans="1:16" ht="18" customHeight="1">
@@ -12400,29 +13480,41 @@
       <c r="C106" s="190"/>
       <c r="D106" s="189"/>
       <c r="E106" s="189"/>
-      <c r="F106" s="190"/>
-      <c r="G106" s="189"/>
-      <c r="H106" s="189"/>
-      <c r="I106" s="190"/>
-      <c r="J106" s="189"/>
-      <c r="K106" s="189"/>
+      <c r="F106" s="190" t="s">
+        <v>661</v>
+      </c>
+      <c r="G106" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H106" s="189" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I106" s="190" t="s">
+        <v>1558</v>
+      </c>
+      <c r="J106" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K106" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L106" s="186" t="s">
         <v>28</v>
       </c>
       <c r="M106" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N106" s="143" t="str">
+      <c r="N106" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O106" s="143" t="str">
+      <c r="O106" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P106" s="143" t="str">
+        <v>08:33</v>
+      </c>
+      <c r="P106" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:35</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="18" customHeight="1">
@@ -12436,7 +13528,7 @@
       <c r="D107" s="189"/>
       <c r="E107" s="189"/>
       <c r="F107" s="189"/>
-      <c r="G107" s="189"/>
+      <c r="G107" s="244"/>
       <c r="H107" s="189"/>
       <c r="I107" s="190"/>
       <c r="J107" s="189"/>
@@ -12447,15 +13539,15 @@
       <c r="M107" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N107" s="143" t="str">
+      <c r="N107" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O107" s="143" t="str">
+      <c r="O107" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P107" s="143" t="str">
+      <c r="P107" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12467,32 +13559,48 @@
       <c r="B108" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C108" s="190"/>
+      <c r="C108" s="190" t="s">
+        <v>1496</v>
+      </c>
       <c r="D108" s="189"/>
-      <c r="E108" s="189"/>
-      <c r="F108" s="190"/>
-      <c r="G108" s="189"/>
-      <c r="H108" s="189"/>
-      <c r="I108" s="190"/>
-      <c r="J108" s="189"/>
-      <c r="K108" s="189"/>
+      <c r="E108" s="189" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F108" s="190" t="s">
+        <v>207</v>
+      </c>
+      <c r="G108" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="189" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I108" s="190" t="s">
+        <v>918</v>
+      </c>
+      <c r="J108" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K108" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L108" s="186" t="s">
         <v>25</v>
       </c>
       <c r="M108" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N108" s="143" t="str">
+      <c r="N108" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O108" s="143" t="str">
+        <v>10:13</v>
+      </c>
+      <c r="O108" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P108" s="143" t="str">
+        <v>10:04</v>
+      </c>
+      <c r="P108" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>10:02</v>
       </c>
     </row>
     <row r="109" spans="1:16" ht="18" customHeight="1">
@@ -12505,29 +13613,41 @@
       <c r="C109" s="190"/>
       <c r="D109" s="189"/>
       <c r="E109" s="189"/>
-      <c r="F109" s="190"/>
-      <c r="G109" s="189"/>
-      <c r="H109" s="189"/>
-      <c r="I109" s="190"/>
-      <c r="J109" s="189"/>
-      <c r="K109" s="189"/>
+      <c r="F109" s="190" t="s">
+        <v>957</v>
+      </c>
+      <c r="G109" s="244" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="189" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I109" s="190" t="s">
+        <v>1559</v>
+      </c>
+      <c r="J109" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K109" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L109" s="186" t="s">
         <v>23</v>
       </c>
       <c r="M109" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N109" s="143" t="str">
+      <c r="N109" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O109" s="143" t="str">
+      <c r="O109" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P109" s="143" t="str">
+        <v>11:38</v>
+      </c>
+      <c r="P109" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>11:33</v>
       </c>
     </row>
     <row r="110" spans="1:16" ht="18" customHeight="1">
@@ -12541,7 +13661,7 @@
       <c r="D110" s="189"/>
       <c r="E110" s="189"/>
       <c r="F110" s="190"/>
-      <c r="G110" s="189"/>
+      <c r="G110" s="244"/>
       <c r="H110" s="189"/>
       <c r="I110" s="190"/>
       <c r="J110" s="189"/>
@@ -12552,15 +13672,15 @@
       <c r="M110" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N110" s="143" t="str">
+      <c r="N110" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O110" s="143" t="str">
+      <c r="O110" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P110" s="143" t="str">
+      <c r="P110" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12575,29 +13695,41 @@
       <c r="C111" s="190"/>
       <c r="D111" s="189"/>
       <c r="E111" s="189"/>
-      <c r="F111" s="190"/>
-      <c r="G111" s="189"/>
-      <c r="H111" s="189"/>
-      <c r="I111" s="190"/>
-      <c r="J111" s="189"/>
-      <c r="K111" s="189"/>
+      <c r="F111" s="190" t="s">
+        <v>109</v>
+      </c>
+      <c r="G111" s="244" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="189" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I111" s="190" t="s">
+        <v>155</v>
+      </c>
+      <c r="J111" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K111" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L111" s="186" t="s">
         <v>21</v>
       </c>
       <c r="M111" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N111" s="143" t="str">
+      <c r="N111" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O111" s="143" t="str">
+      <c r="O111" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P111" s="143" t="str">
+        <v>13:11</v>
+      </c>
+      <c r="P111" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>13:05</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1">
@@ -12610,29 +13742,41 @@
       <c r="C112" s="190"/>
       <c r="D112" s="189"/>
       <c r="E112" s="189"/>
-      <c r="F112" s="190"/>
-      <c r="G112" s="189"/>
-      <c r="H112" s="189"/>
-      <c r="I112" s="190"/>
-      <c r="J112" s="189"/>
-      <c r="K112" s="189"/>
+      <c r="F112" s="190" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G112" s="244" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="189" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I112" s="190" t="s">
+        <v>1561</v>
+      </c>
+      <c r="J112" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K112" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L112" s="186" t="s">
         <v>20</v>
       </c>
       <c r="M112" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N112" s="143" t="str">
+      <c r="N112" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O112" s="143" t="str">
+      <c r="O112" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P112" s="143" t="str">
+        <v>14:43</v>
+      </c>
+      <c r="P112" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>14:30</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="18" customHeight="1">
@@ -12646,28 +13790,34 @@
       <c r="D113" s="189"/>
       <c r="E113" s="189"/>
       <c r="F113" s="190"/>
-      <c r="G113" s="189"/>
+      <c r="G113" s="244"/>
       <c r="H113" s="189"/>
-      <c r="I113" s="191"/>
-      <c r="J113" s="189"/>
-      <c r="K113" s="189"/>
+      <c r="I113" s="191" t="s">
+        <v>858</v>
+      </c>
+      <c r="J113" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K113" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L113" s="186" t="s">
         <v>18</v>
       </c>
       <c r="M113" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N113" s="143" t="str">
+      <c r="N113" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O113" s="143" t="str">
+      <c r="O113" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P113" s="143" t="str">
+      <c r="P113" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>15:57</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="18" customHeight="1">
@@ -12680,9 +13830,15 @@
       <c r="C114" s="190"/>
       <c r="D114" s="189"/>
       <c r="E114" s="189"/>
-      <c r="F114" s="190"/>
-      <c r="G114" s="189"/>
-      <c r="H114" s="189"/>
+      <c r="F114" s="190" t="s">
+        <v>215</v>
+      </c>
+      <c r="G114" s="244" t="s">
+        <v>17</v>
+      </c>
+      <c r="H114" s="189" t="s">
+        <v>1017</v>
+      </c>
       <c r="I114" s="190"/>
       <c r="J114" s="189"/>
       <c r="K114" s="189"/>
@@ -12692,15 +13848,15 @@
       <c r="M114" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N114" s="143" t="str">
+      <c r="N114" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O114" s="143" t="str">
+      <c r="O114" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P114" s="143" t="str">
+        <v>16:14</v>
+      </c>
+      <c r="P114" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12715,29 +13871,41 @@
       <c r="C115" s="190"/>
       <c r="D115" s="189"/>
       <c r="E115" s="189"/>
-      <c r="F115" s="190"/>
-      <c r="G115" s="189"/>
-      <c r="H115" s="189"/>
-      <c r="I115" s="190"/>
-      <c r="J115" s="189"/>
-      <c r="K115" s="189"/>
+      <c r="F115" s="190" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G115" s="244" t="s">
+        <v>0</v>
+      </c>
+      <c r="H115" s="189" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I115" s="190" t="s">
+        <v>1562</v>
+      </c>
+      <c r="J115" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K115" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L115" s="186" t="s">
         <v>15</v>
       </c>
       <c r="M115" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N115" s="143" t="str">
+      <c r="N115" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O115" s="143" t="str">
+      <c r="O115" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P115" s="143" t="str">
+        <v>17:46</v>
+      </c>
+      <c r="P115" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>17:26</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="18" customHeight="1">
@@ -12751,28 +13919,34 @@
       <c r="D116" s="189"/>
       <c r="E116" s="189"/>
       <c r="F116" s="190"/>
-      <c r="G116" s="189"/>
+      <c r="G116" s="244"/>
       <c r="H116" s="189"/>
-      <c r="I116" s="190"/>
-      <c r="J116" s="189"/>
-      <c r="K116" s="189"/>
+      <c r="I116" s="190" t="s">
+        <v>945</v>
+      </c>
+      <c r="J116" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K116" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L116" s="186" t="s">
         <v>12</v>
       </c>
       <c r="M116" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N116" s="143" t="str">
+      <c r="N116" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O116" s="143" t="str">
+      <c r="O116" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P116" s="143" t="str">
+      <c r="P116" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>18:56</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="18" customHeight="1">
@@ -12785,9 +13959,15 @@
       <c r="C117" s="190"/>
       <c r="D117" s="189"/>
       <c r="E117" s="189"/>
-      <c r="F117" s="190"/>
-      <c r="G117" s="189"/>
-      <c r="H117" s="189"/>
+      <c r="F117" s="190" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G117" s="244" t="s">
+        <v>27</v>
+      </c>
+      <c r="H117" s="189" t="s">
+        <v>1396</v>
+      </c>
       <c r="I117" s="190"/>
       <c r="J117" s="189"/>
       <c r="K117" s="189"/>
@@ -12797,15 +13977,15 @@
       <c r="M117" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N117" s="143" t="str">
+      <c r="N117" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O117" s="143" t="str">
+      <c r="O117" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P117" s="143" t="str">
+        <v>19:20</v>
+      </c>
+      <c r="P117" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12817,32 +13997,48 @@
       <c r="B118" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C118" s="190"/>
+      <c r="C118" s="190" t="s">
+        <v>1497</v>
+      </c>
       <c r="D118" s="189"/>
-      <c r="E118" s="189"/>
-      <c r="F118" s="190"/>
-      <c r="G118" s="189"/>
-      <c r="H118" s="189"/>
-      <c r="I118" s="190"/>
-      <c r="J118" s="189"/>
-      <c r="K118" s="189"/>
+      <c r="E118" s="189" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F118" s="190" t="s">
+        <v>790</v>
+      </c>
+      <c r="G118" s="244" t="s">
+        <v>0</v>
+      </c>
+      <c r="H118" s="189" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I118" s="190" t="s">
+        <v>118</v>
+      </c>
+      <c r="J118" s="189" t="s">
+        <v>13</v>
+      </c>
+      <c r="K118" s="189" t="s">
+        <v>1403</v>
+      </c>
       <c r="L118" s="186" t="s">
         <v>9</v>
       </c>
       <c r="M118" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N118" s="143" t="str">
+      <c r="N118" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O118" s="143" t="str">
+        <v>20:22</v>
+      </c>
+      <c r="O118" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P118" s="143" t="str">
+        <v>20:54</v>
+      </c>
+      <c r="P118" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:25</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1">
@@ -12856,28 +14052,34 @@
       <c r="D119" s="189"/>
       <c r="E119" s="189"/>
       <c r="F119" s="190"/>
-      <c r="G119" s="189"/>
+      <c r="G119" s="244"/>
       <c r="H119" s="189"/>
-      <c r="I119" s="190"/>
-      <c r="J119" s="189"/>
-      <c r="K119" s="189"/>
+      <c r="I119" s="190" t="s">
+        <v>930</v>
+      </c>
+      <c r="J119" s="189" t="s">
+        <v>4</v>
+      </c>
+      <c r="K119" s="189" t="s">
+        <v>1015</v>
+      </c>
       <c r="L119" s="186" t="s">
         <v>6</v>
       </c>
       <c r="M119" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N119" s="143" t="str">
+      <c r="N119" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O119" s="143" t="str">
+      <c r="O119" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P119" s="143" t="str">
+      <c r="P119" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>21:54</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1">
@@ -12890,9 +14092,15 @@
       <c r="C120" s="190"/>
       <c r="D120" s="189"/>
       <c r="E120" s="189"/>
-      <c r="F120" s="190"/>
-      <c r="G120" s="190"/>
-      <c r="H120" s="189"/>
+      <c r="F120" s="190" t="s">
+        <v>1564</v>
+      </c>
+      <c r="G120" s="244" t="s">
+        <v>17</v>
+      </c>
+      <c r="H120" s="189" t="s">
+        <v>1017</v>
+      </c>
       <c r="I120" s="190"/>
       <c r="J120" s="189"/>
       <c r="K120" s="189"/>
@@ -12902,15 +14110,15 @@
       <c r="M120" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="N120" s="143" t="str">
+      <c r="N120" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O120" s="143" t="str">
+      <c r="O120" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P120" s="143" t="str">
+        <v>22:29</v>
+      </c>
+      <c r="P120" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -12925,29 +14133,41 @@
       <c r="C121" s="194"/>
       <c r="D121" s="193"/>
       <c r="E121" s="193"/>
-      <c r="F121" s="194"/>
-      <c r="G121" s="193"/>
-      <c r="H121" s="193"/>
-      <c r="I121" s="194"/>
-      <c r="J121" s="193"/>
-      <c r="K121" s="193"/>
+      <c r="F121" s="194" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G121" s="247" t="s">
+        <v>0</v>
+      </c>
+      <c r="H121" s="193" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I121" s="194" t="s">
+        <v>884</v>
+      </c>
+      <c r="J121" s="193" t="s">
+        <v>13</v>
+      </c>
+      <c r="K121" s="193" t="s">
+        <v>1403</v>
+      </c>
       <c r="L121" s="192" t="s">
         <v>3</v>
       </c>
       <c r="M121" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="N121" s="143" t="str">
+      <c r="N121" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O121" s="143" t="str">
+      <c r="O121" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P121" s="143" t="str">
+        <v>23:55</v>
+      </c>
+      <c r="P121" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:26</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1">
@@ -12961,28 +14181,34 @@
       <c r="D122" s="196"/>
       <c r="E122" s="196"/>
       <c r="F122" s="197"/>
-      <c r="G122" s="196"/>
+      <c r="G122" s="249"/>
       <c r="H122" s="196"/>
-      <c r="I122" s="197"/>
-      <c r="J122" s="196"/>
-      <c r="K122" s="196"/>
+      <c r="I122" s="197" t="s">
+        <v>141</v>
+      </c>
+      <c r="J122" s="196" t="s">
+        <v>13</v>
+      </c>
+      <c r="K122" s="196" t="s">
+        <v>1403</v>
+      </c>
       <c r="L122" s="195" t="s">
         <v>37</v>
       </c>
       <c r="M122" s="196" t="s">
         <v>38</v>
       </c>
-      <c r="N122" s="143" t="str">
+      <c r="N122" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O122" s="143" t="str">
+      <c r="O122" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P122" s="143" t="str">
+      <c r="P122" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>00:00</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="18" customHeight="1">
@@ -12995,29 +14221,41 @@
       <c r="C123" s="199"/>
       <c r="D123" s="198"/>
       <c r="E123" s="198"/>
-      <c r="F123" s="199"/>
-      <c r="G123" s="198"/>
-      <c r="H123" s="198"/>
-      <c r="I123" s="200"/>
-      <c r="J123" s="198"/>
-      <c r="K123" s="198"/>
+      <c r="F123" s="199" t="s">
+        <v>623</v>
+      </c>
+      <c r="G123" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H123" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I123" s="200" t="s">
+        <v>1157</v>
+      </c>
+      <c r="J123" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K123" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L123" s="195" t="s">
         <v>36</v>
       </c>
       <c r="M123" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N123" s="143" t="str">
+      <c r="N123" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O123" s="143" t="str">
+      <c r="O123" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P123" s="143" t="str">
+        <v>01:01</v>
+      </c>
+      <c r="P123" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:29</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1">
@@ -13030,29 +14268,41 @@
       <c r="C124" s="199"/>
       <c r="D124" s="198"/>
       <c r="E124" s="198"/>
-      <c r="F124" s="199"/>
-      <c r="G124" s="198"/>
-      <c r="H124" s="198"/>
-      <c r="I124" s="199"/>
-      <c r="J124" s="198"/>
-      <c r="K124" s="198"/>
+      <c r="F124" s="199" t="s">
+        <v>297</v>
+      </c>
+      <c r="G124" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H124" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I124" s="199" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J124" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K124" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L124" s="195" t="s">
         <v>35</v>
       </c>
       <c r="M124" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N124" s="143" t="str">
+      <c r="N124" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O124" s="143" t="str">
+      <c r="O124" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P124" s="143" t="str">
+        <v>02:30</v>
+      </c>
+      <c r="P124" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:56</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="18" customHeight="1">
@@ -13066,7 +14316,7 @@
       <c r="D125" s="198"/>
       <c r="E125" s="198"/>
       <c r="F125" s="199"/>
-      <c r="G125" s="198"/>
+      <c r="G125" s="251"/>
       <c r="H125" s="198"/>
       <c r="I125" s="199"/>
       <c r="J125" s="198"/>
@@ -13077,15 +14327,15 @@
       <c r="M125" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N125" s="143" t="str">
+      <c r="N125" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O125" s="143" t="str">
+      <c r="O125" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P125" s="143" t="str">
+      <c r="P125" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13100,29 +14350,41 @@
       <c r="C126" s="199"/>
       <c r="D126" s="198"/>
       <c r="E126" s="198"/>
-      <c r="F126" s="199"/>
-      <c r="G126" s="198"/>
-      <c r="H126" s="198"/>
-      <c r="I126" s="200"/>
-      <c r="J126" s="198"/>
-      <c r="K126" s="198"/>
+      <c r="F126" s="199" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G126" s="251" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" s="198" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I126" s="200" t="s">
+        <v>260</v>
+      </c>
+      <c r="J126" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K126" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L126" s="195" t="s">
         <v>32</v>
       </c>
       <c r="M126" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N126" s="143" t="str">
+      <c r="N126" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O126" s="143" t="str">
+      <c r="O126" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P126" s="143" t="str">
+        <v>04:03</v>
+      </c>
+      <c r="P126" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>04:30</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="18" customHeight="1">
@@ -13135,29 +14397,41 @@
       <c r="C127" s="199"/>
       <c r="D127" s="198"/>
       <c r="E127" s="198"/>
-      <c r="F127" s="199"/>
-      <c r="G127" s="198"/>
-      <c r="H127" s="198"/>
-      <c r="I127" s="199"/>
-      <c r="J127" s="198"/>
-      <c r="K127" s="198"/>
+      <c r="F127" s="199" t="s">
+        <v>616</v>
+      </c>
+      <c r="G127" s="251" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" s="198" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I127" s="199" t="s">
+        <v>589</v>
+      </c>
+      <c r="J127" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K127" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L127" s="195" t="s">
         <v>31</v>
       </c>
       <c r="M127" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N127" s="143" t="str">
+      <c r="N127" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O127" s="143" t="str">
+      <c r="O127" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P127" s="143" t="str">
+        <v>05:35</v>
+      </c>
+      <c r="P127" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:55</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="18" customHeight="1">
@@ -13171,7 +14445,7 @@
       <c r="D128" s="198"/>
       <c r="E128" s="198"/>
       <c r="F128" s="199"/>
-      <c r="G128" s="198"/>
+      <c r="G128" s="251"/>
       <c r="H128" s="198"/>
       <c r="I128" s="199"/>
       <c r="J128" s="198"/>
@@ -13182,15 +14456,15 @@
       <c r="M128" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N128" s="143" t="str">
+      <c r="N128" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O128" s="143" t="str">
+      <c r="O128" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P128" s="143" t="str">
+      <c r="P128" s="151" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -13205,29 +14479,41 @@
       <c r="C129" s="198"/>
       <c r="D129" s="198"/>
       <c r="E129" s="198"/>
-      <c r="F129" s="199"/>
-      <c r="G129" s="198"/>
-      <c r="H129" s="198"/>
-      <c r="I129" s="200"/>
-      <c r="J129" s="198"/>
-      <c r="K129" s="198"/>
+      <c r="F129" s="199" t="s">
+        <v>852</v>
+      </c>
+      <c r="G129" s="251" t="s">
+        <v>11</v>
+      </c>
+      <c r="H129" s="198" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I129" s="200" t="s">
+        <v>887</v>
+      </c>
+      <c r="J129" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K129" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L129" s="195" t="s">
         <v>29</v>
       </c>
       <c r="M129" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N129" s="143" t="str">
+      <c r="N129" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O129" s="143" t="str">
+      <c r="O129" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P129" s="143" t="str">
+        <v>07:09</v>
+      </c>
+      <c r="P129" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:29</v>
       </c>
     </row>
     <row r="130" spans="1:16" ht="18" customHeight="1">
@@ -13240,29 +14526,41 @@
       <c r="C130" s="199"/>
       <c r="D130" s="198"/>
       <c r="E130" s="198"/>
-      <c r="F130" s="199"/>
-      <c r="G130" s="198"/>
-      <c r="H130" s="198"/>
-      <c r="I130" s="199"/>
-      <c r="J130" s="198"/>
-      <c r="K130" s="198"/>
+      <c r="F130" s="199" t="s">
+        <v>978</v>
+      </c>
+      <c r="G130" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H130" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I130" s="199" t="s">
+        <v>1566</v>
+      </c>
+      <c r="J130" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K130" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L130" s="195" t="s">
         <v>28</v>
       </c>
       <c r="M130" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N130" s="143" t="str">
+      <c r="N130" s="151" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O130" s="143" t="str">
+      <c r="O130" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="P130" s="143" t="str">
+        <v>08:41</v>
+      </c>
+      <c r="P130" s="151" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:55</v>
       </c>
     </row>
     <row r="131" spans="1:16" ht="18" customHeight="1">
@@ -13276,7 +14574,7 @@
       <c r="D131" s="198"/>
       <c r="E131" s="198"/>
       <c r="F131" s="199"/>
-      <c r="G131" s="198"/>
+      <c r="G131" s="251"/>
       <c r="H131" s="198"/>
       <c r="I131" s="199"/>
       <c r="J131" s="198"/>
@@ -13287,15 +14585,15 @@
       <c r="M131" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N131" s="143" t="str">
+      <c r="N131" s="151" t="str">
         <f t="shared" ref="N131:N169" si="6">IF($C131&lt;&gt;"",TEXT($C131,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="O131" s="143" t="str">
+      <c r="O131" s="151" t="str">
         <f t="shared" ref="O131:O169" si="7">IF($F131&lt;&gt;"",TEXT($F131,"HH:MM"),"")</f>
         <v/>
       </c>
-      <c r="P131" s="143" t="str">
+      <c r="P131" s="151" t="str">
         <f t="shared" ref="P131:P169" si="8">IF($I131&lt;&gt;"",TEXT($I131,"HH:MM"),"")</f>
         <v/>
       </c>
@@ -13310,29 +14608,41 @@
       <c r="C132" s="199"/>
       <c r="D132" s="198"/>
       <c r="E132" s="198"/>
-      <c r="F132" s="199"/>
-      <c r="G132" s="198"/>
-      <c r="H132" s="198"/>
-      <c r="I132" s="200"/>
-      <c r="J132" s="198"/>
-      <c r="K132" s="198"/>
+      <c r="F132" s="199" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G132" s="251" t="s">
+        <v>27</v>
+      </c>
+      <c r="H132" s="198" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I132" s="200" t="s">
+        <v>1541</v>
+      </c>
+      <c r="J132" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K132" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L132" s="195" t="s">
         <v>25</v>
       </c>
       <c r="M132" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N132" s="143" t="str">
+      <c r="N132" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O132" s="143" t="str">
+      <c r="O132" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P132" s="143" t="str">
+        <v>10:14</v>
+      </c>
+      <c r="P132" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>10:26</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1">
@@ -13345,29 +14655,41 @@
       <c r="C133" s="198"/>
       <c r="D133" s="198"/>
       <c r="E133" s="198"/>
-      <c r="F133" s="199"/>
-      <c r="G133" s="198"/>
-      <c r="H133" s="198"/>
-      <c r="I133" s="199"/>
-      <c r="J133" s="198"/>
-      <c r="K133" s="198"/>
+      <c r="F133" s="199" t="s">
+        <v>115</v>
+      </c>
+      <c r="G133" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H133" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I133" s="199" t="s">
+        <v>1568</v>
+      </c>
+      <c r="J133" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K133" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L133" s="195" t="s">
         <v>23</v>
       </c>
       <c r="M133" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N133" s="143" t="str">
+      <c r="N133" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O133" s="143" t="str">
+      <c r="O133" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P133" s="143" t="str">
+        <v>11:39</v>
+      </c>
+      <c r="P133" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>11:58</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="18" customHeight="1">
@@ -13381,7 +14703,7 @@
       <c r="D134" s="198"/>
       <c r="E134" s="198"/>
       <c r="F134" s="201"/>
-      <c r="G134" s="198"/>
+      <c r="G134" s="251"/>
       <c r="H134" s="198"/>
       <c r="I134" s="199"/>
       <c r="J134" s="198"/>
@@ -13392,15 +14714,15 @@
       <c r="M134" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N134" s="143" t="str">
+      <c r="N134" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O134" s="143" t="str">
+      <c r="O134" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P134" s="143" t="str">
+      <c r="P134" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13412,32 +14734,48 @@
       <c r="B135" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="198"/>
+      <c r="C135" s="201">
+        <v>0.54652777777777772</v>
+      </c>
       <c r="D135" s="198"/>
-      <c r="E135" s="198"/>
-      <c r="F135" s="199"/>
-      <c r="G135" s="198"/>
-      <c r="H135" s="198"/>
-      <c r="I135" s="200"/>
-      <c r="J135" s="198"/>
-      <c r="K135" s="198"/>
+      <c r="E135" s="198" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F135" s="199" t="s">
+        <v>607</v>
+      </c>
+      <c r="G135" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H135" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I135" s="200" t="s">
+        <v>990</v>
+      </c>
+      <c r="J135" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K135" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L135" s="195" t="s">
         <v>21</v>
       </c>
       <c r="M135" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N135" s="143" t="str">
+      <c r="N135" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O135" s="143" t="str">
+        <v>13:07</v>
+      </c>
+      <c r="O135" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P135" s="143" t="str">
+        <v>13:12</v>
+      </c>
+      <c r="P135" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>13:27</v>
       </c>
     </row>
     <row r="136" spans="1:16" ht="18" customHeight="1">
@@ -13450,29 +14788,41 @@
       <c r="C136" s="199"/>
       <c r="D136" s="198"/>
       <c r="E136" s="198"/>
-      <c r="F136" s="199"/>
-      <c r="G136" s="198"/>
-      <c r="H136" s="198"/>
-      <c r="I136" s="199"/>
-      <c r="J136" s="198"/>
-      <c r="K136" s="198"/>
+      <c r="F136" s="199" t="s">
+        <v>608</v>
+      </c>
+      <c r="G136" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H136" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I136" s="199" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J136" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K136" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L136" s="195" t="s">
         <v>20</v>
       </c>
       <c r="M136" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N136" s="143" t="str">
+      <c r="N136" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O136" s="143" t="str">
+      <c r="O136" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P136" s="143" t="str">
+        <v>14:40</v>
+      </c>
+      <c r="P136" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>14:58</v>
       </c>
     </row>
     <row r="137" spans="1:16" ht="18" customHeight="1">
@@ -13486,7 +14836,7 @@
       <c r="D137" s="198"/>
       <c r="E137" s="198"/>
       <c r="F137" s="199"/>
-      <c r="G137" s="198"/>
+      <c r="G137" s="251"/>
       <c r="H137" s="198"/>
       <c r="I137" s="200"/>
       <c r="J137" s="198"/>
@@ -13497,15 +14847,15 @@
       <c r="M137" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N137" s="143" t="str">
+      <c r="N137" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O137" s="143" t="str">
+      <c r="O137" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P137" s="143" t="str">
+      <c r="P137" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13520,29 +14870,41 @@
       <c r="C138" s="198"/>
       <c r="D138" s="198"/>
       <c r="E138" s="198"/>
-      <c r="F138" s="199"/>
-      <c r="G138" s="198"/>
-      <c r="H138" s="198"/>
-      <c r="I138" s="199"/>
-      <c r="J138" s="198"/>
-      <c r="K138" s="198"/>
+      <c r="F138" s="199" t="s">
+        <v>124</v>
+      </c>
+      <c r="G138" s="251" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" s="198" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I138" s="199" t="s">
+        <v>1569</v>
+      </c>
+      <c r="J138" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K138" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L138" s="195">
         <v>16</v>
       </c>
       <c r="M138" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N138" s="143" t="str">
+      <c r="N138" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O138" s="143" t="str">
+      <c r="O138" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P138" s="143" t="str">
+        <v>16:09</v>
+      </c>
+      <c r="P138" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>16:25</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1">
@@ -13552,12 +14914,20 @@
       <c r="B139" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C139" s="199"/>
+      <c r="C139" s="199" t="s">
+        <v>1489</v>
+      </c>
       <c r="D139" s="198"/>
       <c r="E139" s="198"/>
-      <c r="F139" s="199"/>
-      <c r="G139" s="198"/>
-      <c r="H139" s="198"/>
+      <c r="F139" s="199" t="s">
+        <v>1570</v>
+      </c>
+      <c r="G139" s="251" t="s">
+        <v>17</v>
+      </c>
+      <c r="H139" s="198" t="s">
+        <v>1017</v>
+      </c>
       <c r="I139" s="199"/>
       <c r="J139" s="198"/>
       <c r="K139" s="198"/>
@@ -13567,15 +14937,15 @@
       <c r="M139" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N139" s="143" t="str">
+      <c r="N139" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O139" s="143" t="str">
+        <v>17:02</v>
+      </c>
+      <c r="O139" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P139" s="143" t="str">
+        <v>17:38</v>
+      </c>
+      <c r="P139" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13591,28 +14961,34 @@
       <c r="D140" s="198"/>
       <c r="E140" s="198"/>
       <c r="F140" s="199"/>
-      <c r="G140" s="198"/>
+      <c r="G140" s="251"/>
       <c r="H140" s="198"/>
-      <c r="I140" s="199"/>
-      <c r="J140" s="198"/>
-      <c r="K140" s="198"/>
+      <c r="I140" s="199" t="s">
+        <v>1571</v>
+      </c>
+      <c r="J140" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K140" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L140" s="195" t="s">
         <v>12</v>
       </c>
       <c r="M140" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N140" s="143" t="str">
+      <c r="N140" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O140" s="143" t="str">
+      <c r="O140" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P140" s="143" t="str">
+      <c r="P140" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18:00</v>
       </c>
     </row>
     <row r="141" spans="1:16" ht="18" customHeight="1">
@@ -13625,29 +15001,41 @@
       <c r="C141" s="199"/>
       <c r="D141" s="198"/>
       <c r="E141" s="198"/>
-      <c r="F141" s="199"/>
-      <c r="G141" s="198"/>
-      <c r="H141" s="198"/>
-      <c r="I141" s="199"/>
-      <c r="J141" s="198"/>
-      <c r="K141" s="198"/>
+      <c r="F141" s="199" t="s">
+        <v>132</v>
+      </c>
+      <c r="G141" s="251" t="s">
+        <v>11</v>
+      </c>
+      <c r="H141" s="198" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I141" s="199" t="s">
+        <v>953</v>
+      </c>
+      <c r="J141" s="198" t="s">
+        <v>4</v>
+      </c>
+      <c r="K141" s="198" t="s">
+        <v>1015</v>
+      </c>
       <c r="L141" s="195" t="s">
         <v>10</v>
       </c>
       <c r="M141" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N141" s="143" t="str">
+      <c r="N141" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O141" s="143" t="str">
+      <c r="O141" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P141" s="143" t="str">
+        <v>19:04</v>
+      </c>
+      <c r="P141" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>19:28</v>
       </c>
     </row>
     <row r="142" spans="1:16" ht="18" customHeight="1">
@@ -13657,32 +15045,48 @@
       <c r="B142" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C142" s="199"/>
+      <c r="C142" s="199" t="s">
+        <v>293</v>
+      </c>
       <c r="D142" s="198"/>
-      <c r="E142" s="198"/>
-      <c r="F142" s="199"/>
-      <c r="G142" s="198"/>
-      <c r="H142" s="198"/>
-      <c r="I142" s="199"/>
-      <c r="J142" s="198"/>
-      <c r="K142" s="198"/>
+      <c r="E142" s="198" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F142" s="199" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G142" s="251" t="s">
+        <v>17</v>
+      </c>
+      <c r="H142" s="198" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I142" s="199" t="s">
+        <v>790</v>
+      </c>
+      <c r="J142" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K142" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L142" s="195" t="s">
         <v>9</v>
       </c>
       <c r="M142" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N142" s="143" t="str">
+      <c r="N142" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O142" s="143" t="str">
+        <v>20:59</v>
+      </c>
+      <c r="O142" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P142" s="143" t="str">
+        <v>20:29</v>
+      </c>
+      <c r="P142" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20:54</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="18" customHeight="1">
@@ -13696,7 +15100,7 @@
       <c r="D143" s="198"/>
       <c r="E143" s="198"/>
       <c r="F143" s="199"/>
-      <c r="G143" s="198"/>
+      <c r="G143" s="251"/>
       <c r="H143" s="198"/>
       <c r="I143" s="199"/>
       <c r="J143" s="198"/>
@@ -13707,15 +15111,15 @@
       <c r="M143" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N143" s="143" t="str">
+      <c r="N143" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O143" s="143" t="str">
+      <c r="O143" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P143" s="143" t="str">
+      <c r="P143" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13730,29 +15134,41 @@
       <c r="C144" s="199"/>
       <c r="D144" s="198"/>
       <c r="E144" s="198"/>
-      <c r="F144" s="199"/>
-      <c r="G144" s="198"/>
-      <c r="H144" s="198"/>
-      <c r="I144" s="199"/>
-      <c r="J144" s="198"/>
-      <c r="K144" s="198"/>
+      <c r="F144" s="199" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G144" s="251" t="s">
+        <v>0</v>
+      </c>
+      <c r="H144" s="198" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I144" s="199" t="s">
+        <v>133</v>
+      </c>
+      <c r="J144" s="198" t="s">
+        <v>13</v>
+      </c>
+      <c r="K144" s="198" t="s">
+        <v>1403</v>
+      </c>
       <c r="L144" s="195" t="s">
         <v>5</v>
       </c>
       <c r="M144" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="N144" s="143" t="str">
+      <c r="N144" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O144" s="143" t="str">
+      <c r="O144" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P144" s="143" t="str">
+        <v>22:01</v>
+      </c>
+      <c r="P144" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22:18</v>
       </c>
     </row>
     <row r="145" spans="1:16" ht="18" customHeight="1" thickBot="1">
@@ -13765,29 +15181,41 @@
       <c r="C145" s="204"/>
       <c r="D145" s="203"/>
       <c r="E145" s="203"/>
-      <c r="F145" s="204"/>
-      <c r="G145" s="203"/>
-      <c r="H145" s="203"/>
-      <c r="I145" s="204"/>
-      <c r="J145" s="203"/>
-      <c r="K145" s="203"/>
+      <c r="F145" s="204" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G145" s="255" t="s">
+        <v>27</v>
+      </c>
+      <c r="H145" s="203" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I145" s="204" t="s">
+        <v>915</v>
+      </c>
+      <c r="J145" s="203" t="s">
+        <v>4</v>
+      </c>
+      <c r="K145" s="203" t="s">
+        <v>1015</v>
+      </c>
       <c r="L145" s="202" t="s">
         <v>3</v>
       </c>
       <c r="M145" s="203" t="s">
         <v>38</v>
       </c>
-      <c r="N145" s="143" t="str">
+      <c r="N145" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O145" s="143" t="str">
+      <c r="O145" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P145" s="143" t="str">
+        <v>23:28</v>
+      </c>
+      <c r="P145" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23:48</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1">
@@ -13800,9 +15228,15 @@
       <c r="C146" s="206"/>
       <c r="D146" s="206"/>
       <c r="E146" s="206"/>
-      <c r="F146" s="207"/>
-      <c r="G146" s="206"/>
-      <c r="H146" s="206"/>
+      <c r="F146" s="207" t="s">
+        <v>112</v>
+      </c>
+      <c r="G146" s="257" t="s">
+        <v>27</v>
+      </c>
+      <c r="H146" s="206" t="s">
+        <v>1396</v>
+      </c>
       <c r="I146" s="207"/>
       <c r="J146" s="206"/>
       <c r="K146" s="206"/>
@@ -13812,15 +15246,15 @@
       <c r="M146" s="206" t="s">
         <v>2</v>
       </c>
-      <c r="N146" s="143" t="str">
+      <c r="N146" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O146" s="143" t="str">
+      <c r="O146" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P146" s="143" t="str">
+        <v>00:56</v>
+      </c>
+      <c r="P146" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13836,28 +15270,34 @@
       <c r="D147" s="208"/>
       <c r="E147" s="208"/>
       <c r="F147" s="209"/>
-      <c r="G147" s="208"/>
+      <c r="G147" s="259"/>
       <c r="H147" s="208"/>
-      <c r="I147" s="209"/>
-      <c r="J147" s="208"/>
-      <c r="K147" s="208"/>
+      <c r="I147" s="209" t="s">
+        <v>600</v>
+      </c>
+      <c r="J147" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K147" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L147" s="205" t="s">
         <v>36</v>
       </c>
       <c r="M147" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N147" s="143" t="str">
+      <c r="N147" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O147" s="143" t="str">
+      <c r="O147" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P147" s="143" t="str">
+      <c r="P147" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>01:02</v>
       </c>
     </row>
     <row r="148" spans="1:16" ht="18" customHeight="1">
@@ -13870,29 +15310,41 @@
       <c r="C148" s="209"/>
       <c r="D148" s="208"/>
       <c r="E148" s="208"/>
-      <c r="F148" s="209"/>
-      <c r="G148" s="208"/>
-      <c r="H148" s="208"/>
-      <c r="I148" s="209"/>
-      <c r="J148" s="208"/>
-      <c r="K148" s="208"/>
+      <c r="F148" s="209" t="s">
+        <v>624</v>
+      </c>
+      <c r="G148" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H148" s="208" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I148" s="209" t="s">
+        <v>800</v>
+      </c>
+      <c r="J148" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K148" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L148" s="205" t="s">
         <v>35</v>
       </c>
       <c r="M148" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N148" s="143" t="str">
+      <c r="N148" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O148" s="143" t="str">
+      <c r="O148" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P148" s="143" t="str">
+        <v>02:26</v>
+      </c>
+      <c r="P148" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>02:32</v>
       </c>
     </row>
     <row r="149" spans="1:16" ht="18" customHeight="1">
@@ -13905,9 +15357,15 @@
       <c r="C149" s="209"/>
       <c r="D149" s="208"/>
       <c r="E149" s="208"/>
-      <c r="F149" s="209"/>
-      <c r="G149" s="208"/>
-      <c r="H149" s="208"/>
+      <c r="F149" s="209" t="s">
+        <v>236</v>
+      </c>
+      <c r="G149" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H149" s="208" t="s">
+        <v>1017</v>
+      </c>
       <c r="I149" s="210"/>
       <c r="J149" s="208"/>
       <c r="K149" s="208"/>
@@ -13917,15 +15375,15 @@
       <c r="M149" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N149" s="143" t="str">
+      <c r="N149" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O149" s="143" t="str">
+      <c r="O149" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P149" s="143" t="str">
+        <v>03:55</v>
+      </c>
+      <c r="P149" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -13941,28 +15399,34 @@
       <c r="D150" s="208"/>
       <c r="E150" s="208"/>
       <c r="F150" s="209"/>
-      <c r="G150" s="208"/>
+      <c r="G150" s="259"/>
       <c r="H150" s="208"/>
-      <c r="I150" s="209"/>
-      <c r="J150" s="208"/>
-      <c r="K150" s="208"/>
+      <c r="I150" s="209" t="s">
+        <v>1574</v>
+      </c>
+      <c r="J150" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K150" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L150" s="205" t="s">
         <v>32</v>
       </c>
       <c r="M150" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N150" s="143" t="str">
+      <c r="N150" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O150" s="143" t="str">
+      <c r="O150" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P150" s="143" t="str">
+      <c r="P150" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>04:01</v>
       </c>
     </row>
     <row r="151" spans="1:16" ht="18" customHeight="1">
@@ -13976,28 +15440,34 @@
       <c r="D151" s="208"/>
       <c r="E151" s="208"/>
       <c r="F151" s="209"/>
-      <c r="G151" s="208"/>
+      <c r="G151" s="259"/>
       <c r="H151" s="208"/>
-      <c r="I151" s="209"/>
-      <c r="J151" s="208"/>
-      <c r="K151" s="208"/>
+      <c r="I151" s="209" t="s">
+        <v>603</v>
+      </c>
+      <c r="J151" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K151" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L151" s="205" t="s">
         <v>31</v>
       </c>
       <c r="M151" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N151" s="143" t="str">
+      <c r="N151" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O151" s="143" t="str">
+      <c r="O151" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P151" s="143" t="str">
+      <c r="P151" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>05:36</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1">
@@ -14007,11 +15477,15 @@
       <c r="B152" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="292"/>
+      <c r="C152" s="209" t="s">
+        <v>1498</v>
+      </c>
       <c r="D152" s="208"/>
-      <c r="E152" s="208"/>
+      <c r="E152" s="208" t="s">
+        <v>1522</v>
+      </c>
       <c r="F152" s="209"/>
-      <c r="G152" s="208"/>
+      <c r="G152" s="259"/>
       <c r="H152" s="208"/>
       <c r="I152" s="209"/>
       <c r="J152" s="208"/>
@@ -14022,15 +15496,15 @@
       <c r="M152" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N152" s="143" t="str">
+      <c r="N152" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O152" s="143" t="str">
+        <v>06:56</v>
+      </c>
+      <c r="O152" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P152" s="143" t="str">
+      <c r="P152" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14046,28 +15520,34 @@
       <c r="D153" s="208"/>
       <c r="E153" s="208"/>
       <c r="F153" s="209"/>
-      <c r="G153" s="208"/>
+      <c r="G153" s="259"/>
       <c r="H153" s="208"/>
-      <c r="I153" s="210"/>
-      <c r="J153" s="208"/>
-      <c r="K153" s="208"/>
+      <c r="I153" s="210" t="s">
+        <v>829</v>
+      </c>
+      <c r="J153" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K153" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L153" s="205" t="s">
         <v>29</v>
       </c>
       <c r="M153" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N153" s="143" t="str">
+      <c r="N153" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O153" s="143" t="str">
+      <c r="O153" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P153" s="143" t="str">
+      <c r="P153" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>07:03</v>
       </c>
     </row>
     <row r="154" spans="1:16" ht="18" customHeight="1">
@@ -14080,29 +15560,41 @@
       <c r="C154" s="209"/>
       <c r="D154" s="208"/>
       <c r="E154" s="208"/>
-      <c r="F154" s="209"/>
-      <c r="G154" s="208"/>
-      <c r="H154" s="208"/>
-      <c r="I154" s="209"/>
-      <c r="J154" s="208"/>
-      <c r="K154" s="208"/>
+      <c r="F154" s="209" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G154" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H154" s="208" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I154" s="209" t="s">
+        <v>661</v>
+      </c>
+      <c r="J154" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K154" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L154" s="205" t="s">
         <v>28</v>
       </c>
       <c r="M154" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N154" s="143" t="str">
+      <c r="N154" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O154" s="143" t="str">
+      <c r="O154" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P154" s="143" t="str">
+        <v>08:23</v>
+      </c>
+      <c r="P154" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>08:33</v>
       </c>
     </row>
     <row r="155" spans="1:16" ht="18" customHeight="1">
@@ -14115,29 +15607,41 @@
       <c r="C155" s="209"/>
       <c r="D155" s="208"/>
       <c r="E155" s="208"/>
-      <c r="F155" s="209"/>
-      <c r="G155" s="208"/>
-      <c r="H155" s="208"/>
-      <c r="I155" s="210"/>
-      <c r="J155" s="208"/>
-      <c r="K155" s="208"/>
+      <c r="F155" s="209" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G155" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="H155" s="208" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I155" s="210" t="s">
+        <v>854</v>
+      </c>
+      <c r="J155" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K155" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L155" s="205" t="s">
         <v>26</v>
       </c>
       <c r="M155" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N155" s="143" t="str">
+      <c r="N155" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O155" s="143" t="str">
+      <c r="O155" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P155" s="143" t="str">
+        <v>09:51</v>
+      </c>
+      <c r="P155" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>09:59</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1">
@@ -14147,11 +15651,15 @@
       <c r="B156" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C156" s="209"/>
+      <c r="C156" s="209" t="s">
+        <v>1528</v>
+      </c>
       <c r="D156" s="208"/>
-      <c r="E156" s="208"/>
+      <c r="E156" s="208" t="s">
+        <v>1536</v>
+      </c>
       <c r="F156" s="209"/>
-      <c r="G156" s="208"/>
+      <c r="G156" s="259"/>
       <c r="H156" s="208"/>
       <c r="I156" s="209"/>
       <c r="J156" s="208"/>
@@ -14162,15 +15670,15 @@
       <c r="M156" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N156" s="143" t="str">
+      <c r="N156" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O156" s="143" t="str">
+        <v>11:15</v>
+      </c>
+      <c r="O156" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P156" s="143" t="str">
+      <c r="P156" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14185,29 +15693,41 @@
       <c r="C157" s="209"/>
       <c r="D157" s="208"/>
       <c r="E157" s="208"/>
-      <c r="F157" s="209"/>
-      <c r="G157" s="208"/>
-      <c r="H157" s="208"/>
-      <c r="I157" s="209"/>
-      <c r="J157" s="208"/>
-      <c r="K157" s="208"/>
+      <c r="F157" s="209" t="s">
+        <v>1576</v>
+      </c>
+      <c r="G157" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="H157" s="208" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I157" s="209" t="s">
+        <v>1559</v>
+      </c>
+      <c r="J157" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K157" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L157" s="205" t="s">
         <v>23</v>
       </c>
       <c r="M157" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N157" s="143" t="str">
+      <c r="N157" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O157" s="143" t="str">
+      <c r="O157" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P157" s="143" t="str">
+        <v>11:17</v>
+      </c>
+      <c r="P157" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>11:33</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1">
@@ -14220,9 +15740,15 @@
       <c r="C158" s="209"/>
       <c r="D158" s="208"/>
       <c r="E158" s="208"/>
-      <c r="F158" s="209"/>
-      <c r="G158" s="208"/>
-      <c r="H158" s="208"/>
+      <c r="F158" s="209" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G158" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H158" s="208" t="s">
+        <v>1017</v>
+      </c>
       <c r="I158" s="209"/>
       <c r="J158" s="208"/>
       <c r="K158" s="208"/>
@@ -14232,15 +15758,15 @@
       <c r="M158" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N158" s="143" t="str">
+      <c r="N158" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O158" s="143" t="str">
+      <c r="O158" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P158" s="143" t="str">
+        <v>12:46</v>
+      </c>
+      <c r="P158" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14252,32 +15778,42 @@
       <c r="B159" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C159" s="209"/>
+      <c r="C159" s="209" t="s">
+        <v>1527</v>
+      </c>
       <c r="D159" s="208"/>
-      <c r="E159" s="208"/>
+      <c r="E159" s="208" t="s">
+        <v>1530</v>
+      </c>
       <c r="F159" s="209"/>
-      <c r="G159" s="208"/>
+      <c r="G159" s="259"/>
       <c r="H159" s="208"/>
-      <c r="I159" s="209"/>
-      <c r="J159" s="208"/>
-      <c r="K159" s="208"/>
+      <c r="I159" s="209" t="s">
+        <v>857</v>
+      </c>
+      <c r="J159" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K159" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L159" s="205" t="s">
         <v>21</v>
       </c>
       <c r="M159" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N159" s="143" t="str">
+      <c r="N159" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O159" s="143" t="str">
+        <v>13:54</v>
+      </c>
+      <c r="O159" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P159" s="143" t="str">
+      <c r="P159" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>13:07</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1">
@@ -14290,29 +15826,41 @@
       <c r="C160" s="209"/>
       <c r="D160" s="208"/>
       <c r="E160" s="208"/>
-      <c r="F160" s="209"/>
-      <c r="G160" s="208"/>
-      <c r="H160" s="208"/>
-      <c r="I160" s="209"/>
-      <c r="J160" s="208"/>
-      <c r="K160" s="208"/>
+      <c r="F160" s="209" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G160" s="259" t="s">
+        <v>27</v>
+      </c>
+      <c r="H160" s="208" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I160" s="209" t="s">
+        <v>1579</v>
+      </c>
+      <c r="J160" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K160" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L160" s="205" t="s">
         <v>20</v>
       </c>
       <c r="M160" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N160" s="143" t="str">
+      <c r="N160" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O160" s="143" t="str">
+      <c r="O160" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P160" s="143" t="str">
+        <v>14:15</v>
+      </c>
+      <c r="P160" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>14:32</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="18" customHeight="1">
@@ -14325,29 +15873,41 @@
       <c r="C161" s="209"/>
       <c r="D161" s="208"/>
       <c r="E161" s="208"/>
-      <c r="F161" s="209"/>
-      <c r="G161" s="208"/>
-      <c r="H161" s="208"/>
-      <c r="I161" s="210"/>
-      <c r="J161" s="208"/>
-      <c r="K161" s="208"/>
+      <c r="F161" s="209" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G161" s="259" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" s="208" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I161" s="210" t="s">
+        <v>1581</v>
+      </c>
+      <c r="J161" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K161" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L161" s="205" t="s">
         <v>18</v>
       </c>
       <c r="M161" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N161" s="143" t="str">
+      <c r="N161" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O161" s="143" t="str">
+      <c r="O161" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P161" s="143" t="str">
+        <v>15:42</v>
+      </c>
+      <c r="P161" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15:58</v>
       </c>
     </row>
     <row r="162" spans="1:16" ht="18" customHeight="1">
@@ -14361,7 +15921,7 @@
       <c r="D162" s="208"/>
       <c r="E162" s="208"/>
       <c r="F162" s="209"/>
-      <c r="G162" s="208"/>
+      <c r="G162" s="259"/>
       <c r="H162" s="208"/>
       <c r="I162" s="209"/>
       <c r="J162" s="208"/>
@@ -14372,15 +15932,15 @@
       <c r="M162" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N162" s="143" t="str">
+      <c r="N162" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O162" s="143" t="str">
+      <c r="O162" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P162" s="143" t="str">
+      <c r="P162" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14395,29 +15955,41 @@
       <c r="C163" s="209"/>
       <c r="D163" s="208"/>
       <c r="E163" s="208"/>
-      <c r="F163" s="209"/>
-      <c r="G163" s="208"/>
-      <c r="H163" s="208"/>
-      <c r="I163" s="209"/>
-      <c r="J163" s="208"/>
-      <c r="K163" s="208"/>
+      <c r="F163" s="209" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G163" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="H163" s="208" t="s">
+        <v>1018</v>
+      </c>
+      <c r="I163" s="209" t="s">
+        <v>1582</v>
+      </c>
+      <c r="J163" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K163" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L163" s="205" t="s">
         <v>15</v>
       </c>
       <c r="M163" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N163" s="143" t="str">
+      <c r="N163" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O163" s="143" t="str">
+      <c r="O163" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P163" s="143" t="str">
+        <v>17:10</v>
+      </c>
+      <c r="P163" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>17:24</v>
       </c>
     </row>
     <row r="164" spans="1:16" ht="18" customHeight="1">
@@ -14427,32 +15999,46 @@
       <c r="B164" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C164" s="209"/>
+      <c r="C164" s="209" t="s">
+        <v>1529</v>
+      </c>
       <c r="D164" s="208"/>
       <c r="E164" s="208"/>
-      <c r="F164" s="209"/>
-      <c r="G164" s="208"/>
-      <c r="H164" s="208"/>
-      <c r="I164" s="209"/>
-      <c r="J164" s="208"/>
-      <c r="K164" s="208"/>
+      <c r="F164" s="209" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G164" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H164" s="208" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I164" s="209" t="s">
+        <v>1584</v>
+      </c>
+      <c r="J164" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K164" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L164" s="205" t="s">
         <v>12</v>
       </c>
       <c r="M164" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N164" s="143" t="str">
+      <c r="N164" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O164" s="143" t="str">
+        <v>18:01</v>
+      </c>
+      <c r="O164" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P164" s="143" t="str">
+        <v>18:35</v>
+      </c>
+      <c r="P164" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18:53</v>
       </c>
     </row>
     <row r="165" spans="1:16" ht="18" customHeight="1">
@@ -14466,7 +16052,7 @@
       <c r="D165" s="208"/>
       <c r="E165" s="208"/>
       <c r="F165" s="209"/>
-      <c r="G165" s="208"/>
+      <c r="G165" s="259"/>
       <c r="H165" s="208"/>
       <c r="I165" s="209"/>
       <c r="J165" s="208"/>
@@ -14477,15 +16063,15 @@
       <c r="M165" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N165" s="143" t="str">
+      <c r="N165" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O165" s="143" t="str">
+      <c r="O165" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P165" s="143" t="str">
+      <c r="P165" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14500,29 +16086,41 @@
       <c r="C166" s="211"/>
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
-      <c r="F166" s="292"/>
-      <c r="G166" s="208"/>
-      <c r="H166" s="208"/>
-      <c r="I166" s="209"/>
-      <c r="J166" s="208"/>
-      <c r="K166" s="208"/>
+      <c r="F166" s="209" t="s">
+        <v>1585</v>
+      </c>
+      <c r="G166" s="259" t="s">
+        <v>27</v>
+      </c>
+      <c r="H166" s="208" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I166" s="209" t="s">
+        <v>1586</v>
+      </c>
+      <c r="J166" s="208" t="s">
+        <v>4</v>
+      </c>
+      <c r="K166" s="208" t="s">
+        <v>1015</v>
+      </c>
       <c r="L166" s="205" t="s">
         <v>9</v>
       </c>
       <c r="M166" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N166" s="143" t="str">
+      <c r="N166" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O166" s="143" t="str">
+      <c r="O166" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P166" s="143" t="str">
+        <v>20:10</v>
+      </c>
+      <c r="P166" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20:27</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="18" customHeight="1">
@@ -14535,29 +16133,41 @@
       <c r="C167" s="209"/>
       <c r="D167" s="208"/>
       <c r="E167" s="208"/>
-      <c r="F167" s="209"/>
-      <c r="G167" s="208"/>
-      <c r="H167" s="208"/>
-      <c r="I167" s="209"/>
-      <c r="J167" s="208"/>
-      <c r="K167" s="208"/>
+      <c r="F167" s="209" t="s">
+        <v>1587</v>
+      </c>
+      <c r="G167" s="259" t="s">
+        <v>17</v>
+      </c>
+      <c r="H167" s="208" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I167" s="209" t="s">
+        <v>1064</v>
+      </c>
+      <c r="J167" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K167" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L167" s="205" t="s">
         <v>6</v>
       </c>
       <c r="M167" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N167" s="143" t="str">
+      <c r="N167" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O167" s="143" t="str">
+      <c r="O167" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P167" s="143" t="str">
+        <v>21:36</v>
+      </c>
+      <c r="P167" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21:53</v>
       </c>
     </row>
     <row r="168" spans="1:16" ht="18" customHeight="1">
@@ -14571,7 +16181,7 @@
       <c r="D168" s="208"/>
       <c r="E168" s="208"/>
       <c r="F168" s="209"/>
-      <c r="G168" s="208"/>
+      <c r="G168" s="259"/>
       <c r="H168" s="208"/>
       <c r="I168" s="209"/>
       <c r="J168" s="208"/>
@@ -14582,15 +16192,15 @@
       <c r="M168" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N168" s="143" t="str">
+      <c r="N168" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O168" s="143" t="str">
+      <c r="O168" s="151" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P168" s="143" t="str">
+      <c r="P168" s="151" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -14605,72 +16215,59 @@
       <c r="C169" s="209"/>
       <c r="D169" s="208"/>
       <c r="E169" s="208"/>
-      <c r="F169" s="209"/>
-      <c r="G169" s="208"/>
-      <c r="H169" s="208"/>
-      <c r="I169" s="209"/>
-      <c r="J169" s="208"/>
-      <c r="K169" s="208"/>
+      <c r="F169" s="209" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G169" s="259" t="s">
+        <v>27</v>
+      </c>
+      <c r="H169" s="208" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I169" s="209" t="s">
+        <v>847</v>
+      </c>
+      <c r="J169" s="208" t="s">
+        <v>13</v>
+      </c>
+      <c r="K169" s="208" t="s">
+        <v>1403</v>
+      </c>
       <c r="L169" s="205" t="s">
         <v>3</v>
       </c>
       <c r="M169" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="N169" s="143" t="str">
+      <c r="N169" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O169" s="143" t="str">
+      <c r="O169" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P169" s="143" t="str">
+        <v>23:08</v>
+      </c>
+      <c r="P169" s="151" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>23:27</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="'">
+  <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="39" priority="5" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="38" priority="4" operator="containsText" text="定期メンテナンス中">
-      <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="36" priority="2" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="35" priority="8" operator="containsText" text="定期メンテナンス中">
+  <conditionalFormatting sqref="E1:E1048576 H1:H1048576 K1:K1048576">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="33" priority="9" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
+  <conditionalFormatting sqref="D1:D1048576 G1:G1048576 J1:J11 J13:J1048576">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22233,17 +23830,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22644,7 +24241,7 @@
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
       <c r="F9" s="287" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="G9" s="149" t="s">
         <v>17</v>
@@ -23806,7 +25403,7 @@
       <c r="D35" s="160"/>
       <c r="E35" s="160"/>
       <c r="F35" s="289" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G35" s="160" t="s">
         <v>11</v>
@@ -23815,7 +25412,7 @@
         <v>1016</v>
       </c>
       <c r="I35" s="294" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="J35" s="160" t="s">
         <v>13</v>
@@ -24003,7 +25600,7 @@
         <v>1017</v>
       </c>
       <c r="I39" s="289" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="J39" s="160" t="s">
         <v>4</v>
@@ -24669,7 +26266,7 @@
       <c r="D54" s="171"/>
       <c r="E54" s="171"/>
       <c r="F54" s="290" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="G54" s="171" t="s">
         <v>17</v>
@@ -24678,7 +26275,7 @@
         <v>1017</v>
       </c>
       <c r="I54" s="290" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="J54" s="171" t="s">
         <v>4</v>
@@ -24907,13 +26504,13 @@
         <v>55</v>
       </c>
       <c r="C59" s="172" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D59" s="171" t="s">
         <v>335</v>
       </c>
       <c r="E59" s="295" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="F59" s="171" t="s">
         <v>79</v>
@@ -25731,7 +27328,7 @@
       <c r="G77" s="180"/>
       <c r="H77" s="180"/>
       <c r="I77" s="291" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="J77" s="180" t="s">
         <v>4</v>
@@ -25769,7 +27366,7 @@
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
       <c r="F78" s="181" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G78" s="180" t="s">
         <v>11</v>
@@ -25778,7 +27375,7 @@
         <v>1016</v>
       </c>
       <c r="I78" s="291" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="J78" s="180" t="s">
         <v>13</v>
@@ -25854,13 +27451,13 @@
         <v>52</v>
       </c>
       <c r="C80" s="291" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D80" s="180" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E80" s="180" t="s">
         <v>1454</v>
-      </c>
-      <c r="D80" s="180" t="s">
-        <v>1455</v>
-      </c>
-      <c r="E80" s="180" t="s">
-        <v>1456</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="180"/>
@@ -25904,7 +27501,7 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="G81" s="180" t="s">
         <v>17</v>
@@ -25957,7 +27554,7 @@
         <v>1439</v>
       </c>
       <c r="F82" s="181" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G82" s="180" t="s">
         <v>17</v>
@@ -26039,7 +27636,7 @@
       <c r="D84" s="180"/>
       <c r="E84" s="180"/>
       <c r="F84" s="181" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="G84" s="180" t="s">
         <v>0</v>
@@ -26048,7 +27645,7 @@
         <v>1018</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="J84" s="180" t="s">
         <v>4</v>
@@ -26086,13 +27683,13 @@
         <v>1432</v>
       </c>
       <c r="D85" s="180" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="E85" s="180" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F85" s="181" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G85" s="180" t="s">
         <v>17</v>
@@ -26221,7 +27818,7 @@
         <v>1436</v>
       </c>
       <c r="F88" s="291" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="G88" s="180" t="s">
         <v>0</v>
@@ -26265,7 +27862,7 @@
       <c r="G89" s="180"/>
       <c r="H89" s="180"/>
       <c r="I89" s="276" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="J89" s="180" t="s">
         <v>4</v>
@@ -26931,7 +28528,7 @@
       <c r="D104" s="189"/>
       <c r="E104" s="189"/>
       <c r="F104" s="190" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="G104" s="189" t="s">
         <v>0</v>
@@ -27979,7 +29576,7 @@
         <v>1018</v>
       </c>
       <c r="I127" s="199" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="J127" s="198" t="s">
         <v>13</v>
@@ -28067,7 +29664,7 @@
         <v>1017</v>
       </c>
       <c r="I129" s="200" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="J129" s="198" t="s">
         <v>13</v>
@@ -29082,7 +30679,7 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="D152" s="208" t="s">
         <v>45</v>
@@ -29713,7 +31310,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="292" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G166" s="208" t="s">
         <v>17</v>
@@ -29888,42 +31485,42 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="45" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="30" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="43" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="38" priority="8" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35862,27 +37459,27 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="36" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41898,17 +43495,17 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="32" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -46565,7 +48162,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="55" t="s">
-        <v>698</v>
+        <v>1526</v>
       </c>
       <c r="G132" s="57"/>
       <c r="H132" s="55"/>
@@ -47898,12 +49495,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="28" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -53794,12 +55391,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -59787,12 +61384,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -65871,22 +67468,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -71853,22 +73450,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C1AE0D-FFD0-428D-BC52-6A2592E0741F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D2BEA6-0B37-4B5E-A674-5594103BF370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22245" yWindow="16230" windowWidth="22275" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11690" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11681" uniqueCount="1607">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6707,12 +6707,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>05 - 11 例行維護中</t>
-  </si>
-  <si>
-    <t>06-10 定期メンテナンス中</t>
-  </si>
-  <si>
     <t>11:40</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6839,36 +6833,6 @@
   <si>
     <t>黑鯰王</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>05 - 11 例行維護中</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>06-10 定期メンテナンス中</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>06-10 定期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>メンテナンス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>中</t>
-    </r>
   </si>
   <si>
     <t>黒影林 / ？？？</t>
@@ -7155,9 +7119,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>風之風之平原</t>
-  </si>
-  <si>
     <t>オオウスバ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7181,6 +7142,56 @@
     <rPh sb="2" eb="4">
       <t>リョカン</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>06-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 定期メンテナンス中</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風之平原</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - 11 例行維護中</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8342,95 +8353,11 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="46">
+  <dxfs count="36">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8648,6 +8575,20 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9236,7 +9177,7 @@
       <c r="D7" s="149"/>
       <c r="E7" s="149"/>
       <c r="F7" s="150" t="s">
-        <v>1540</v>
+        <v>1535</v>
       </c>
       <c r="G7" s="213" t="s">
         <v>11</v>
@@ -9245,7 +9186,7 @@
         <v>1016</v>
       </c>
       <c r="I7" s="150" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="J7" s="149" t="s">
         <v>4</v>
@@ -9447,7 +9388,7 @@
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
       <c r="F12" s="150" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G12" s="213" t="s">
         <v>0</v>
@@ -9491,17 +9432,17 @@
         <v>60</v>
       </c>
       <c r="C13" s="150" t="s">
-        <v>1531</v>
+        <v>1526</v>
       </c>
       <c r="D13" s="149"/>
       <c r="E13" s="149" t="s">
-        <v>1532</v>
+        <v>1527</v>
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="213"/>
       <c r="H13" s="149"/>
       <c r="I13" s="148" t="s">
-        <v>1598</v>
+        <v>1593</v>
       </c>
       <c r="J13" s="149" t="s">
         <v>4</v>
@@ -9539,7 +9480,7 @@
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
       <c r="F14" s="150" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="G14" s="213" t="s">
         <v>27</v>
@@ -9580,7 +9521,7 @@
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
       <c r="F15" s="150" t="s">
-        <v>1543</v>
+        <v>1538</v>
       </c>
       <c r="G15" s="213" t="s">
         <v>11</v>
@@ -9630,7 +9571,7 @@
       <c r="G16" s="213"/>
       <c r="H16" s="149"/>
       <c r="I16" s="148" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="J16" s="149" t="s">
         <v>13</v>
@@ -9709,7 +9650,7 @@
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
       <c r="F18" s="150" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="G18" s="213" t="s">
         <v>11</v>
@@ -9797,7 +9738,7 @@
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
       <c r="F20" s="150" t="s">
-        <v>1545</v>
+        <v>1540</v>
       </c>
       <c r="G20" s="213" t="s">
         <v>17</v>
@@ -9976,7 +9917,7 @@
         <v>1396</v>
       </c>
       <c r="I24" s="148" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="J24" s="149" t="s">
         <v>4</v>
@@ -10225,7 +10166,7 @@
       <c r="D30" s="160"/>
       <c r="E30" s="160"/>
       <c r="F30" s="162" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="G30" s="221" t="s">
         <v>27</v>
@@ -10348,7 +10289,7 @@
       <c r="D33" s="160"/>
       <c r="E33" s="160"/>
       <c r="F33" s="162" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="G33" s="221" t="s">
         <v>17</v>
@@ -10474,14 +10415,14 @@
         <v>58</v>
       </c>
       <c r="C36" s="162" t="s">
-        <v>1533</v>
+        <v>1528</v>
       </c>
       <c r="D36" s="160"/>
       <c r="E36" s="160" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="F36" s="162" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="G36" s="221" t="s">
         <v>17</v>
@@ -10607,11 +10548,11 @@
         <v>58</v>
       </c>
       <c r="C39" s="162" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="D39" s="160"/>
       <c r="E39" s="160" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="F39" s="162" t="s">
         <v>991</v>
@@ -10670,7 +10611,7 @@
         <v>1017</v>
       </c>
       <c r="I40" s="162" t="s">
-        <v>1601</v>
+        <v>1596</v>
       </c>
       <c r="J40" s="160" t="s">
         <v>13</v>
@@ -10775,11 +10716,11 @@
         <v>58</v>
       </c>
       <c r="C43" s="162" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="D43" s="160"/>
       <c r="E43" s="160" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="F43" s="162"/>
       <c r="G43" s="221"/>
@@ -10919,11 +10860,11 @@
         <v>58</v>
       </c>
       <c r="C47" s="162" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="D47" s="160"/>
       <c r="E47" s="160" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="F47" s="160"/>
       <c r="G47" s="221"/>
@@ -10964,7 +10905,7 @@
       <c r="G48" s="221"/>
       <c r="H48" s="160"/>
       <c r="I48" s="164" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="J48" s="160"/>
       <c r="K48" s="160" t="s">
@@ -11206,26 +11147,14 @@
       <c r="B55" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="172" t="s">
-        <v>199</v>
-      </c>
-      <c r="D55" s="171" t="s">
-        <v>1480</v>
-      </c>
+      <c r="C55" s="172"/>
+      <c r="D55" s="171"/>
       <c r="E55" s="171"/>
-      <c r="F55" s="172" t="s">
-        <v>199</v>
-      </c>
-      <c r="G55" s="229" t="s">
-        <v>1519</v>
-      </c>
+      <c r="F55" s="172"/>
+      <c r="G55" s="229"/>
       <c r="H55" s="171"/>
-      <c r="I55" s="172" t="s">
-        <v>199</v>
-      </c>
-      <c r="J55" s="171" t="s">
-        <v>1480</v>
-      </c>
+      <c r="I55" s="172"/>
+      <c r="J55" s="171"/>
       <c r="K55" s="171"/>
       <c r="L55" s="168" t="s">
         <v>31</v>
@@ -11235,15 +11164,15 @@
       </c>
       <c r="N55" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>05:00</v>
+        <v/>
       </c>
       <c r="O55" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>05:00</v>
+        <v/>
       </c>
       <c r="P55" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>05:00</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1">
@@ -11257,28 +11186,28 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1480</v>
+        <v>1606</v>
       </c>
       <c r="E56" s="171" t="s">
-        <v>1481</v>
+        <v>1604</v>
       </c>
       <c r="F56" s="172" t="s">
         <v>77</v>
       </c>
       <c r="G56" s="229" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="H56" s="171" t="s">
-        <v>1520</v>
+        <v>1096</v>
       </c>
       <c r="I56" s="171" t="s">
         <v>77</v>
       </c>
       <c r="J56" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="K56" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="L56" s="168" t="s">
         <v>30</v>
@@ -11310,28 +11239,28 @@
         <v>81</v>
       </c>
       <c r="D57" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="E57" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="F57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="G57" s="229" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="H57" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="I57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="J57" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="K57" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="L57" s="168" t="s">
         <v>29</v>
@@ -11363,28 +11292,28 @@
         <v>78</v>
       </c>
       <c r="D58" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="E58" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="F58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="G58" s="229" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="H58" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="I58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="J58" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="K58" s="171" t="s">
-        <v>1481</v>
+        <v>1096</v>
       </c>
       <c r="L58" s="168" t="s">
         <v>28</v>
@@ -11416,29 +11345,23 @@
         <v>79</v>
       </c>
       <c r="D59" s="171" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E59" s="171" t="s">
-        <v>1521</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="E59" s="171"/>
       <c r="F59" s="171" t="s">
         <v>79</v>
       </c>
       <c r="G59" s="229" t="s">
-        <v>1480</v>
-      </c>
-      <c r="H59" s="171" t="s">
-        <v>1481</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="H59" s="171"/>
       <c r="I59" s="172" t="s">
         <v>79</v>
       </c>
       <c r="J59" s="171" t="s">
-        <v>1480</v>
-      </c>
-      <c r="K59" s="171" t="s">
-        <v>1481</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="K59" s="171"/>
       <c r="L59" s="168" t="s">
         <v>26</v>
       </c>
@@ -11469,21 +11392,21 @@
         <v>80</v>
       </c>
       <c r="D60" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="E60" s="171"/>
       <c r="F60" s="172" t="s">
         <v>441</v>
       </c>
       <c r="G60" s="229" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="H60" s="171"/>
       <c r="I60" s="172" t="s">
         <v>80</v>
       </c>
       <c r="J60" s="171" t="s">
-        <v>1480</v>
+        <v>335</v>
       </c>
       <c r="K60" s="171"/>
       <c r="L60" s="168" t="s">
@@ -11516,19 +11439,19 @@
       <c r="D61" s="171"/>
       <c r="E61" s="171"/>
       <c r="F61" s="172" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="G61" s="229" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="H61" s="171" t="s">
         <v>1399</v>
       </c>
       <c r="I61" s="172" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="J61" s="171" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="K61" s="171" t="s">
         <v>1402</v>
@@ -11560,20 +11483,20 @@
         <v>55</v>
       </c>
       <c r="C62" s="172" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D62" s="171"/>
       <c r="E62" s="171" t="s">
         <v>1418</v>
       </c>
       <c r="F62" s="172" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="G62" s="229" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="H62" s="171" t="s">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="I62" s="172"/>
       <c r="J62" s="171"/>
@@ -11611,7 +11534,7 @@
       <c r="G63" s="229"/>
       <c r="H63" s="171"/>
       <c r="I63" s="172" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="J63" s="171" t="s">
         <v>13</v>
@@ -11649,22 +11572,22 @@
       <c r="D64" s="171"/>
       <c r="E64" s="171"/>
       <c r="F64" s="172" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="G64" s="229" t="s">
         <v>0</v>
       </c>
       <c r="H64" s="171" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="I64" s="172" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="J64" s="171" t="s">
         <v>13</v>
       </c>
       <c r="K64" s="171" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="L64" s="168" t="s">
         <v>20</v>
@@ -11699,7 +11622,7 @@
         <v>695</v>
       </c>
       <c r="G65" s="229" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="H65" s="171" t="s">
         <v>1018</v>
@@ -11734,14 +11657,14 @@
         <v>55</v>
       </c>
       <c r="C66" s="172" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D66" s="171"/>
       <c r="E66" s="171" t="s">
         <v>1445</v>
       </c>
       <c r="F66" s="172" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="G66" s="229" t="s">
         <v>17</v>
@@ -11750,10 +11673,10 @@
         <v>1017</v>
       </c>
       <c r="I66" s="172" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="J66" s="171" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="K66" s="171" t="s">
         <v>1403</v>
@@ -11794,7 +11717,7 @@
         <v>595</v>
       </c>
       <c r="J67" s="171" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K67" s="171" t="s">
         <v>1015</v>
@@ -11829,7 +11752,7 @@
       <c r="D68" s="171"/>
       <c r="E68" s="171"/>
       <c r="F68" s="172" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="G68" s="229" t="s">
         <v>11</v>
@@ -11870,7 +11793,7 @@
       <c r="D69" s="171"/>
       <c r="E69" s="171"/>
       <c r="F69" s="172" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="G69" s="229" t="s">
         <v>0</v>
@@ -11879,10 +11802,10 @@
         <v>1018</v>
       </c>
       <c r="I69" s="172" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="J69" s="171" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K69" s="171" t="s">
         <v>1015</v>
@@ -11914,7 +11837,7 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D70" s="171"/>
       <c r="E70" s="171" t="s">
@@ -11924,7 +11847,7 @@
       <c r="G70" s="229"/>
       <c r="H70" s="171"/>
       <c r="I70" s="173" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="J70" s="171" t="s">
         <v>13</v>
@@ -11962,7 +11885,7 @@
       <c r="D71" s="171"/>
       <c r="E71" s="171"/>
       <c r="F71" s="172" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="G71" s="229" t="s">
         <v>11</v>
@@ -12009,7 +11932,7 @@
         <v>791</v>
       </c>
       <c r="J72" s="171" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K72" s="171" t="s">
         <v>1015</v>
@@ -12044,13 +11967,13 @@
       <c r="D73" s="175"/>
       <c r="E73" s="175"/>
       <c r="F73" s="176" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="G73" s="233" t="s">
         <v>27</v>
       </c>
       <c r="H73" s="175" t="s">
-        <v>1596</v>
+        <v>1591</v>
       </c>
       <c r="I73" s="176" t="s">
         <v>150</v>
@@ -12135,7 +12058,7 @@
         <v>127</v>
       </c>
       <c r="G75" s="237" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="H75" s="180" t="s">
         <v>1396</v>
@@ -12144,7 +12067,7 @@
         <v>600</v>
       </c>
       <c r="J75" s="180" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="K75" s="180" t="s">
         <v>1403</v>
@@ -12191,7 +12114,7 @@
         <v>1041</v>
       </c>
       <c r="J76" s="180" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K76" s="180" t="s">
         <v>1015</v>
@@ -12320,7 +12243,7 @@
         <v>108</v>
       </c>
       <c r="J79" s="180" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K79" s="180" t="s">
         <v>1015</v>
@@ -12390,19 +12313,19 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="G81" s="237" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="H81" s="180" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="I81" s="181" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="J81" s="180" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K81" s="180" t="s">
         <v>1015</v>
@@ -12449,7 +12372,7 @@
         <v>808</v>
       </c>
       <c r="J82" s="180" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K82" s="180" t="s">
         <v>1015</v>
@@ -12516,29 +12439,29 @@
         <v>52</v>
       </c>
       <c r="C84" s="181" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="D84" s="180"/>
       <c r="E84" s="180" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="F84" s="181" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="G84" s="237" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="H84" s="180" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="I84" s="181" t="s">
         <v>651</v>
       </c>
       <c r="J84" s="180" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="K84" s="180" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
@@ -12576,10 +12499,10 @@
         <v>835</v>
       </c>
       <c r="J85" s="180" t="s">
-        <v>1604</v>
+        <v>4</v>
       </c>
       <c r="K85" s="180" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="L85" s="177" t="s">
         <v>23</v>
@@ -12611,13 +12534,13 @@
       <c r="D86" s="180"/>
       <c r="E86" s="180"/>
       <c r="F86" s="181" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="G86" s="237" t="s">
-        <v>1593</v>
+        <v>1588</v>
       </c>
       <c r="H86" s="180" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="I86" s="182"/>
       <c r="J86" s="180"/>
@@ -12652,7 +12575,7 @@
       <c r="D87" s="180"/>
       <c r="E87" s="180"/>
       <c r="F87" s="181" t="s">
-        <v>1548</v>
+        <v>1543</v>
       </c>
       <c r="G87" s="237" t="s">
         <v>0</v>
@@ -12661,7 +12584,7 @@
         <v>1018</v>
       </c>
       <c r="I87" s="181" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -12696,11 +12619,11 @@
         <v>52</v>
       </c>
       <c r="C88" s="181" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D88" s="180"/>
       <c r="E88" s="180" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="F88" s="181" t="s">
         <v>1342</v>
@@ -12785,7 +12708,7 @@
       <c r="D90" s="180"/>
       <c r="E90" s="180"/>
       <c r="F90" s="181" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="G90" s="237" t="s">
         <v>17</v>
@@ -12832,7 +12755,7 @@
       <c r="D91" s="180"/>
       <c r="E91" s="180"/>
       <c r="F91" s="181" t="s">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="G91" s="237" t="s">
         <v>27</v>
@@ -12841,7 +12764,7 @@
         <v>1396</v>
       </c>
       <c r="I91" s="181" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="J91" s="180" t="s">
         <v>4</v>
@@ -12876,11 +12799,11 @@
         <v>52</v>
       </c>
       <c r="C92" s="181" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="D92" s="180"/>
       <c r="E92" s="180" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="237"/>
@@ -12927,7 +12850,7 @@
         <v>1396</v>
       </c>
       <c r="I93" s="181" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="J93" s="180" t="s">
         <v>13</v>
@@ -12965,7 +12888,7 @@
       <c r="D94" s="180"/>
       <c r="E94" s="180"/>
       <c r="F94" s="181" t="s">
-        <v>1554</v>
+        <v>1549</v>
       </c>
       <c r="G94" s="237" t="s">
         <v>11</v>
@@ -12974,7 +12897,7 @@
         <v>1016</v>
       </c>
       <c r="I94" s="181" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="J94" s="180" t="s">
         <v>13</v>
@@ -13047,7 +12970,7 @@
       <c r="D96" s="180"/>
       <c r="E96" s="180"/>
       <c r="F96" s="181" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="G96" s="237" t="s">
         <v>11</v>
@@ -13361,7 +13284,7 @@
         <v>1016</v>
       </c>
       <c r="I103" s="190" t="s">
-        <v>1557</v>
+        <v>1552</v>
       </c>
       <c r="J103" s="189" t="s">
         <v>13</v>
@@ -13490,7 +13413,7 @@
         <v>1016</v>
       </c>
       <c r="I106" s="190" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="J106" s="189" t="s">
         <v>13</v>
@@ -13560,11 +13483,11 @@
         <v>44</v>
       </c>
       <c r="C108" s="190" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="D108" s="189"/>
       <c r="E108" s="189" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="F108" s="190" t="s">
         <v>207</v>
@@ -13623,7 +13546,7 @@
         <v>1016</v>
       </c>
       <c r="I109" s="190" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="J109" s="189" t="s">
         <v>4</v>
@@ -13743,7 +13666,7 @@
       <c r="D112" s="189"/>
       <c r="E112" s="189"/>
       <c r="F112" s="190" t="s">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="G112" s="244" t="s">
         <v>27</v>
@@ -13752,7 +13675,7 @@
         <v>1396</v>
       </c>
       <c r="I112" s="190" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="J112" s="189" t="s">
         <v>4</v>
@@ -13881,7 +13804,7 @@
         <v>1018</v>
       </c>
       <c r="I115" s="190" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="J115" s="189" t="s">
         <v>13</v>
@@ -13960,7 +13883,7 @@
       <c r="D117" s="189"/>
       <c r="E117" s="189"/>
       <c r="F117" s="190" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="G117" s="244" t="s">
         <v>27</v>
@@ -13998,7 +13921,7 @@
         <v>44</v>
       </c>
       <c r="C118" s="190" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="D118" s="189"/>
       <c r="E118" s="189" t="s">
@@ -14093,7 +14016,7 @@
       <c r="D120" s="189"/>
       <c r="E120" s="189"/>
       <c r="F120" s="190" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="G120" s="244" t="s">
         <v>17</v>
@@ -14134,7 +14057,7 @@
       <c r="D121" s="193"/>
       <c r="E121" s="193"/>
       <c r="F121" s="194" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="G121" s="247" t="s">
         <v>0</v>
@@ -14536,7 +14459,7 @@
         <v>1018</v>
       </c>
       <c r="I130" s="199" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="J130" s="198" t="s">
         <v>13</v>
@@ -14609,7 +14532,7 @@
       <c r="D132" s="198"/>
       <c r="E132" s="198"/>
       <c r="F132" s="199" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="G132" s="251" t="s">
         <v>27</v>
@@ -14618,7 +14541,7 @@
         <v>1396</v>
       </c>
       <c r="I132" s="200" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="J132" s="198" t="s">
         <v>4</v>
@@ -14665,7 +14588,7 @@
         <v>1018</v>
       </c>
       <c r="I133" s="199" t="s">
-        <v>1568</v>
+        <v>1563</v>
       </c>
       <c r="J133" s="198" t="s">
         <v>13</v>
@@ -14739,7 +14662,7 @@
       </c>
       <c r="D135" s="198"/>
       <c r="E135" s="198" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>607</v>
@@ -14880,7 +14803,7 @@
         <v>1016</v>
       </c>
       <c r="I138" s="199" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="J138" s="198" t="s">
         <v>4</v>
@@ -14915,12 +14838,12 @@
         <v>38</v>
       </c>
       <c r="C139" s="199" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D139" s="198"/>
       <c r="E139" s="198"/>
       <c r="F139" s="199" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="G139" s="251" t="s">
         <v>17</v>
@@ -14964,7 +14887,7 @@
       <c r="G140" s="251"/>
       <c r="H140" s="198"/>
       <c r="I140" s="199" t="s">
-        <v>1571</v>
+        <v>1566</v>
       </c>
       <c r="J140" s="198" t="s">
         <v>4</v>
@@ -15050,7 +14973,7 @@
       </c>
       <c r="D142" s="198"/>
       <c r="E142" s="198" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="F142" s="199" t="s">
         <v>1288</v>
@@ -15135,7 +15058,7 @@
       <c r="D144" s="198"/>
       <c r="E144" s="198"/>
       <c r="F144" s="199" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="G144" s="251" t="s">
         <v>0</v>
@@ -15182,7 +15105,7 @@
       <c r="D145" s="203"/>
       <c r="E145" s="203"/>
       <c r="F145" s="204" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="G145" s="255" t="s">
         <v>27</v>
@@ -15402,7 +15325,7 @@
       <c r="G150" s="259"/>
       <c r="H150" s="208"/>
       <c r="I150" s="209" t="s">
-        <v>1574</v>
+        <v>1569</v>
       </c>
       <c r="J150" s="208" t="s">
         <v>13</v>
@@ -15478,11 +15401,11 @@
         <v>2</v>
       </c>
       <c r="C152" s="209" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="D152" s="208"/>
       <c r="E152" s="208" t="s">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="F152" s="209"/>
       <c r="G152" s="259"/>
@@ -15608,7 +15531,7 @@
       <c r="D155" s="208"/>
       <c r="E155" s="208"/>
       <c r="F155" s="209" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="G155" s="259" t="s">
         <v>0</v>
@@ -15652,11 +15575,11 @@
         <v>2</v>
       </c>
       <c r="C156" s="209" t="s">
-        <v>1528</v>
+        <v>1523</v>
       </c>
       <c r="D156" s="208"/>
       <c r="E156" s="208" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F156" s="209"/>
       <c r="G156" s="259"/>
@@ -15694,7 +15617,7 @@
       <c r="D157" s="208"/>
       <c r="E157" s="208"/>
       <c r="F157" s="209" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="G157" s="259" t="s">
         <v>0</v>
@@ -15703,7 +15626,7 @@
         <v>1018</v>
       </c>
       <c r="I157" s="209" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="J157" s="208" t="s">
         <v>4</v>
@@ -15741,7 +15664,7 @@
       <c r="D158" s="208"/>
       <c r="E158" s="208"/>
       <c r="F158" s="209" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="G158" s="259" t="s">
         <v>17</v>
@@ -15779,11 +15702,11 @@
         <v>2</v>
       </c>
       <c r="C159" s="209" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="D159" s="208"/>
       <c r="E159" s="208" t="s">
-        <v>1530</v>
+        <v>1525</v>
       </c>
       <c r="F159" s="209"/>
       <c r="G159" s="259"/>
@@ -15827,7 +15750,7 @@
       <c r="D160" s="208"/>
       <c r="E160" s="208"/>
       <c r="F160" s="209" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="G160" s="259" t="s">
         <v>27</v>
@@ -15836,7 +15759,7 @@
         <v>1396</v>
       </c>
       <c r="I160" s="209" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
       <c r="J160" s="208" t="s">
         <v>4</v>
@@ -15874,7 +15797,7 @@
       <c r="D161" s="208"/>
       <c r="E161" s="208"/>
       <c r="F161" s="209" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="G161" s="259" t="s">
         <v>11</v>
@@ -15883,7 +15806,7 @@
         <v>1016</v>
       </c>
       <c r="I161" s="210" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="J161" s="208" t="s">
         <v>13</v>
@@ -15965,7 +15888,7 @@
         <v>1018</v>
       </c>
       <c r="I163" s="209" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="J163" s="208" t="s">
         <v>4</v>
@@ -16000,12 +15923,12 @@
         <v>2</v>
       </c>
       <c r="C164" s="209" t="s">
-        <v>1529</v>
+        <v>1524</v>
       </c>
       <c r="D164" s="208"/>
       <c r="E164" s="208"/>
       <c r="F164" s="209" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="G164" s="259" t="s">
         <v>17</v>
@@ -16014,7 +15937,7 @@
         <v>1017</v>
       </c>
       <c r="I164" s="209" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="J164" s="208" t="s">
         <v>4</v>
@@ -16087,7 +16010,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="209" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="G166" s="259" t="s">
         <v>27</v>
@@ -16096,7 +16019,7 @@
         <v>1396</v>
       </c>
       <c r="I166" s="209" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="J166" s="208" t="s">
         <v>4</v>
@@ -16134,7 +16057,7 @@
       <c r="D167" s="208"/>
       <c r="E167" s="208"/>
       <c r="F167" s="209" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="G167" s="259" t="s">
         <v>17</v>
@@ -16216,7 +16139,7 @@
       <c r="D169" s="208"/>
       <c r="E169" s="208"/>
       <c r="F169" s="209" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="G169" s="259" t="s">
         <v>27</v>
@@ -16256,17 +16179,17 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="35" priority="8" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576 H1:H1048576 K1:K1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576 G1:G1048576 J1:J11 J13:J1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="例行維護中">
+  <conditionalFormatting sqref="J1:J11 D1:D1048576 G1:G1048576 J13:J1048576">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23830,17 +23753,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31485,42 +31408,42 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="45" priority="6" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="44" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="43" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="42" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="41" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="40" priority="7" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="38" priority="8" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37459,27 +37382,27 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="37" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="36" priority="6" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="35" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="23" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="34" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43495,17 +43418,17 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="32" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="30" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48162,7 +48085,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="55" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="G132" s="57"/>
       <c r="H132" s="55"/>
@@ -49495,12 +49418,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="28" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55391,12 +55314,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61384,12 +61307,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67468,22 +67391,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="22" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73450,22 +73373,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="17" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D2BEA6-0B37-4B5E-A674-5594103BF370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13954829-02E7-476A-8DA0-0BFEF76A566D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22245" yWindow="16230" windowWidth="22275" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22560" yWindow="16305" windowWidth="22275" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11681" uniqueCount="1607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11819" uniqueCount="1641">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6266,15 +6266,9 @@
     <t>黒影林 / 悪鬼都市</t>
   </si>
   <si>
-    <t>孤独の村 / 悪鬼都市</t>
-  </si>
-  <si>
     <t>黒影林 / 孤独の村</t>
   </si>
   <si>
-    <t>孤独の村 / 染色工房</t>
-  </si>
-  <si>
     <t>戒狼村 / 染色工房</t>
   </si>
   <si>
@@ -6291,9 +6285,6 @@
   </si>
   <si>
     <t>巨岩の海岸 / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">巨岩の海岸 / 海岸旅館 </t>
   </si>
   <si>
     <t>巨岩の海岸 / 戒狼村</t>
@@ -6732,58 +6723,7 @@
     <t>14:04</t>
   </si>
   <si>
-    <t>17:02</t>
-  </si>
-  <si>
-    <t>18:25</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>14:10</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10:11</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>20:23</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>16:51</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>12:23</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10:13</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>20:22</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>06:56</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>黒影林 / 渡門旅館</t>
-  </si>
-  <si>
     <t>黒影林 / 染色工房</t>
-  </si>
-  <si>
-    <t>戒狼村 / ？？？</t>
-  </si>
-  <si>
-    <t>黒影林 / ？？？</t>
-  </si>
-  <si>
-    <t>？？？ / 染色工房</t>
   </si>
   <si>
     <t>16:59</t>
@@ -6866,45 +6806,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>13:54</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>11:15</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>18:01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>？？？ / 北方(北方警戒所)</t>
-  </si>
-  <si>
-    <t>11:40</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>戒狼村 / 悪鬼都市</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10:18</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>13:24</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>17:25</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>？？？ / 北方(北方警戒所)</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>黒影林 / 染色工房</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -7120,28 +7021,6 @@
   </si>
   <si>
     <t>オオウスバ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>22:01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>黒影林 / ？？？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>21:47</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>海岸旅館</t>
-    <rPh sb="0" eb="2">
-      <t>カイガン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>リョカン</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -7193,6 +7072,227 @@
       <t xml:space="preserve"> - 11 例行維護中</t>
     </r>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>鬼都 / 染坊</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>17:23</t>
+  </si>
+  <si>
+    <t>01:43</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>06:07</t>
+  </si>
+  <si>
+    <t>18:23</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>09:22</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>20:57</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>13:52</t>
+  </si>
+  <si>
+    <t>17:59</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>灰狼村 / 土門客棧</t>
+  </si>
+  <si>
+    <t>土門客棧 / 叛軍駐地</t>
+  </si>
+  <si>
+    <t>染坊 / 叛軍駐地</t>
+  </si>
+  <si>
+    <t>黑森林 / 叛軍駐地</t>
+  </si>
+  <si>
+    <t>豬豬農場 / 叛軍駐地</t>
+  </si>
+  <si>
+    <t>孤村 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 叛軍駐地</t>
+  </si>
+  <si>
+    <t>土門客棧 / 悲鳴村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>21:47</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤独の村 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戒狼村 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:54</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>土門客棧 / 叛軍駐地</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>孤独の村 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 戒狼村</t>
+  </si>
+  <si>
+    <t xml:space="preserve">巨岩の海岸 / 海岸旅館 </t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黒影林 / 海岸旅館</t>
+  </si>
+  <si>
+    <t>黒影林 / 巨岩の海岸</t>
+  </si>
+  <si>
+    <t>渡門旅館/ 海岸旅館</t>
+  </si>
+  <si>
+    <t>孤独の村 / 戒狼村</t>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 孤独の村</t>
+  </si>
+  <si>
+    <t>孤独の村 / 海岸旅館</t>
+  </si>
+  <si>
+    <t>渡門旅館 / 海岸旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>巨岩の海岸 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>染色工房 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海岸旅館 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>戒狼村 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>悪鬼都市 / 染色工房</t>
+  </si>
+  <si>
+    <t>悪鬼都市 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡門旅館 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>戒狼村 / 渡門旅館</t>
+  </si>
+  <si>
+    <t>渡門旅館 / 北方(北方警戒所)</t>
+  </si>
+  <si>
+    <t>海岸旅館 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武運村 / 戒狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>悲鳴村 / 灰狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>武運村 / 海岸旅館</t>
+  </si>
+  <si>
+    <t>染坊 / 叛軍駐地</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡門旅館 / 悪鬼都市</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>渡門旅館 / 北方(北方警戒所)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風之平原</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新緑</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ナマズ王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>22:17</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>05:15</t>
   </si>
 </sst>
 </file>
@@ -7461,7 +7561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8349,11 +8449,28 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="17" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="38">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8900,17 +9017,17 @@
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="212" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.875" style="212" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.375" style="212" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="212" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="6.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.875" style="151" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="14.25" style="151"/>
   </cols>
   <sheetData>
@@ -9003,9 +9120,15 @@
       <c r="B3" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="150"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
+      <c r="C3" s="150" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D3" s="149" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E3" s="149" t="s">
+        <v>1484</v>
+      </c>
       <c r="F3" s="150" t="s">
         <v>885</v>
       </c>
@@ -9032,7 +9155,7 @@
       </c>
       <c r="N3" s="151" t="str">
         <f t="shared" ref="N3:N66" si="0">IF($C3&lt;&gt;"",TEXT($C3,"HH:MM"),"")</f>
-        <v/>
+        <v>01:35</v>
       </c>
       <c r="O3" s="151" t="str">
         <f t="shared" ref="O3:O66" si="1">IF($F3&lt;&gt;"",TEXT($F3,"HH:MM"),"")</f>
@@ -9173,11 +9296,17 @@
       <c r="B7" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="149"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
+      <c r="C7" s="153">
+        <v>0.22013888888888888</v>
+      </c>
+      <c r="D7" s="149" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="149" t="s">
+        <v>1413</v>
+      </c>
       <c r="F7" s="150" t="s">
-        <v>1535</v>
+        <v>1508</v>
       </c>
       <c r="G7" s="213" t="s">
         <v>11</v>
@@ -9186,7 +9315,7 @@
         <v>1016</v>
       </c>
       <c r="I7" s="150" t="s">
-        <v>1592</v>
+        <v>1565</v>
       </c>
       <c r="J7" s="149" t="s">
         <v>4</v>
@@ -9202,7 +9331,7 @@
       </c>
       <c r="N7" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>05:17</v>
       </c>
       <c r="O7" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9302,9 +9431,15 @@
       <c r="B10" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="150"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
+      <c r="C10" s="150" t="s">
+        <v>627</v>
+      </c>
+      <c r="D10" s="149" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E10" s="149" t="s">
+        <v>1613</v>
+      </c>
       <c r="F10" s="150" t="s">
         <v>274</v>
       </c>
@@ -9331,7 +9466,7 @@
       </c>
       <c r="N10" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>08:24</v>
       </c>
       <c r="O10" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9388,7 +9523,7 @@
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
       <c r="F12" s="150" t="s">
-        <v>1536</v>
+        <v>1509</v>
       </c>
       <c r="G12" s="213" t="s">
         <v>0</v>
@@ -9432,17 +9567,19 @@
         <v>60</v>
       </c>
       <c r="C13" s="150" t="s">
-        <v>1526</v>
-      </c>
-      <c r="D13" s="149"/>
+        <v>957</v>
+      </c>
+      <c r="D13" s="149" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="149" t="s">
-        <v>1527</v>
+        <v>1604</v>
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="213"/>
       <c r="H13" s="149"/>
       <c r="I13" s="148" t="s">
-        <v>1593</v>
+        <v>1566</v>
       </c>
       <c r="J13" s="149" t="s">
         <v>4</v>
@@ -9458,7 +9595,7 @@
       </c>
       <c r="N13" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>11:40</v>
+        <v>11:38</v>
       </c>
       <c r="O13" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9480,7 +9617,7 @@
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
       <c r="F14" s="150" t="s">
-        <v>1537</v>
+        <v>1510</v>
       </c>
       <c r="G14" s="213" t="s">
         <v>27</v>
@@ -9521,7 +9658,7 @@
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
       <c r="F15" s="150" t="s">
-        <v>1538</v>
+        <v>1511</v>
       </c>
       <c r="G15" s="213" t="s">
         <v>11</v>
@@ -9564,14 +9701,20 @@
       <c r="B16" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
+      <c r="C16" s="153">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="D16" s="149" t="s">
+        <v>899</v>
+      </c>
+      <c r="E16" s="149" t="s">
+        <v>1627</v>
+      </c>
       <c r="F16" s="150"/>
       <c r="G16" s="213"/>
       <c r="H16" s="149"/>
       <c r="I16" s="148" t="s">
-        <v>1594</v>
+        <v>1567</v>
       </c>
       <c r="J16" s="149" t="s">
         <v>13</v>
@@ -9587,7 +9730,7 @@
       </c>
       <c r="N16" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14:14</v>
       </c>
       <c r="O16" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9650,7 +9793,7 @@
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
       <c r="F18" s="150" t="s">
-        <v>1539</v>
+        <v>1512</v>
       </c>
       <c r="G18" s="213" t="s">
         <v>11</v>
@@ -9693,9 +9836,15 @@
       <c r="B19" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
+      <c r="C19" s="153">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="D19" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="149" t="s">
+        <v>1612</v>
+      </c>
       <c r="F19" s="150"/>
       <c r="G19" s="213"/>
       <c r="H19" s="149"/>
@@ -9716,7 +9865,7 @@
       </c>
       <c r="N19" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>17:50</v>
       </c>
       <c r="O19" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9738,7 +9887,7 @@
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
       <c r="F20" s="150" t="s">
-        <v>1540</v>
+        <v>1513</v>
       </c>
       <c r="G20" s="213" t="s">
         <v>17</v>
@@ -9822,9 +9971,15 @@
       <c r="B22" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
+      <c r="C22" s="150" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D22" s="149" t="s">
+        <v>898</v>
+      </c>
+      <c r="E22" s="149" t="s">
+        <v>1603</v>
+      </c>
       <c r="F22" s="150"/>
       <c r="G22" s="213"/>
       <c r="H22" s="149"/>
@@ -9845,7 +10000,7 @@
       </c>
       <c r="N22" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>20:42</v>
       </c>
       <c r="O22" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9917,7 +10072,7 @@
         <v>1396</v>
       </c>
       <c r="I24" s="148" t="s">
-        <v>1595</v>
+        <v>1568</v>
       </c>
       <c r="J24" s="149" t="s">
         <v>4</v>
@@ -10121,9 +10276,15 @@
       <c r="B29" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="161"/>
-      <c r="D29" s="160"/>
-      <c r="E29" s="160"/>
+      <c r="C29" s="161">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="D29" s="160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="160" t="s">
+        <v>1614</v>
+      </c>
       <c r="F29" s="162" t="s">
         <v>259</v>
       </c>
@@ -10144,7 +10305,7 @@
       </c>
       <c r="N29" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>03:18</v>
       </c>
       <c r="O29" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10166,7 +10327,7 @@
       <c r="D30" s="160"/>
       <c r="E30" s="160"/>
       <c r="F30" s="162" t="s">
-        <v>1541</v>
+        <v>1514</v>
       </c>
       <c r="G30" s="221" t="s">
         <v>27</v>
@@ -10285,11 +10446,17 @@
       <c r="B33" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="279"/>
-      <c r="D33" s="160"/>
-      <c r="E33" s="160"/>
+      <c r="C33" s="279" t="s">
+        <v>273</v>
+      </c>
+      <c r="D33" s="160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="160" t="s">
+        <v>1632</v>
+      </c>
       <c r="F33" s="162" t="s">
-        <v>1542</v>
+        <v>1515</v>
       </c>
       <c r="G33" s="221" t="s">
         <v>17</v>
@@ -10314,7 +10481,7 @@
       </c>
       <c r="N33" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>07:17</v>
       </c>
       <c r="O33" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10415,14 +10582,16 @@
         <v>58</v>
       </c>
       <c r="C36" s="162" t="s">
-        <v>1528</v>
-      </c>
-      <c r="D36" s="160"/>
+        <v>252</v>
+      </c>
+      <c r="D36" s="160" t="s">
+        <v>1364</v>
+      </c>
       <c r="E36" s="160" t="s">
-        <v>1534</v>
+        <v>1507</v>
       </c>
       <c r="F36" s="162" t="s">
-        <v>1536</v>
+        <v>1509</v>
       </c>
       <c r="G36" s="221" t="s">
         <v>17</v>
@@ -10434,7 +10603,7 @@
         <v>833</v>
       </c>
       <c r="J36" s="160" t="s">
-        <v>4</v>
+        <v>1634</v>
       </c>
       <c r="K36" s="160" t="s">
         <v>1015</v>
@@ -10447,7 +10616,7 @@
       </c>
       <c r="N36" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>10:18</v>
+        <v>10:16</v>
       </c>
       <c r="O36" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10484,7 +10653,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="160" t="s">
-        <v>1403</v>
+        <v>1636</v>
       </c>
       <c r="L37" s="157" t="s">
         <v>23</v>
@@ -10548,11 +10717,13 @@
         <v>58</v>
       </c>
       <c r="C39" s="162" t="s">
-        <v>1529</v>
-      </c>
-      <c r="D39" s="160"/>
+        <v>1577</v>
+      </c>
+      <c r="D39" s="160" t="s">
+        <v>1596</v>
+      </c>
       <c r="E39" s="160" t="s">
-        <v>1533</v>
+        <v>1506</v>
       </c>
       <c r="F39" s="162" t="s">
         <v>991</v>
@@ -10580,7 +10751,7 @@
       </c>
       <c r="N39" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>13:24</v>
+        <v>13:19</v>
       </c>
       <c r="O39" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10608,10 +10779,10 @@
         <v>17</v>
       </c>
       <c r="H40" s="160" t="s">
-        <v>1017</v>
+        <v>1637</v>
       </c>
       <c r="I40" s="162" t="s">
-        <v>1596</v>
+        <v>1569</v>
       </c>
       <c r="J40" s="160" t="s">
         <v>13</v>
@@ -10651,9 +10822,15 @@
       <c r="F41" s="162"/>
       <c r="G41" s="221"/>
       <c r="H41" s="160"/>
-      <c r="I41" s="162"/>
-      <c r="J41" s="160"/>
-      <c r="K41" s="160"/>
+      <c r="I41" s="162" t="s">
+        <v>1549</v>
+      </c>
+      <c r="J41" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L41" s="157" t="s">
         <v>18</v>
       </c>
@@ -10670,7 +10847,7 @@
       </c>
       <c r="P41" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>15:58</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1">
@@ -10683,9 +10860,15 @@
       <c r="C42" s="162"/>
       <c r="D42" s="160"/>
       <c r="E42" s="160"/>
-      <c r="F42" s="162"/>
-      <c r="G42" s="221"/>
-      <c r="H42" s="160"/>
+      <c r="F42" s="162" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G42" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="160" t="s">
+        <v>1017</v>
+      </c>
       <c r="I42" s="164"/>
       <c r="J42" s="160"/>
       <c r="K42" s="160"/>
@@ -10701,7 +10884,7 @@
       </c>
       <c r="O42" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16:21</v>
       </c>
       <c r="P42" s="151" t="str">
         <f t="shared" si="2"/>
@@ -10716,18 +10899,32 @@
         <v>58</v>
       </c>
       <c r="C43" s="162" t="s">
-        <v>1530</v>
-      </c>
-      <c r="D43" s="160"/>
+        <v>1578</v>
+      </c>
+      <c r="D43" s="160" t="s">
+        <v>48</v>
+      </c>
       <c r="E43" s="160" t="s">
-        <v>1601</v>
-      </c>
-      <c r="F43" s="162"/>
-      <c r="G43" s="221"/>
-      <c r="H43" s="160"/>
-      <c r="I43" s="162"/>
-      <c r="J43" s="160"/>
-      <c r="K43" s="160"/>
+        <v>1432</v>
+      </c>
+      <c r="F43" s="162" t="s">
+        <v>595</v>
+      </c>
+      <c r="G43" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="160" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I43" s="162" t="s">
+        <v>817</v>
+      </c>
+      <c r="J43" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L43" s="157" t="s">
         <v>15</v>
       </c>
@@ -10736,15 +10933,15 @@
       </c>
       <c r="N43" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>17:25</v>
+        <v>17:23</v>
       </c>
       <c r="O43" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>17:52</v>
       </c>
       <c r="P43" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>17:31</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="18" customHeight="1">
@@ -10760,9 +10957,15 @@
       <c r="F44" s="161"/>
       <c r="G44" s="221"/>
       <c r="H44" s="160"/>
-      <c r="I44" s="163"/>
-      <c r="J44" s="160"/>
-      <c r="K44" s="160"/>
+      <c r="I44" s="163">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="J44" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L44" s="157" t="s">
         <v>12</v>
       </c>
@@ -10779,7 +10982,7 @@
       </c>
       <c r="P44" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18:59</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18" customHeight="1">
@@ -10827,12 +11030,24 @@
       <c r="C46" s="162"/>
       <c r="D46" s="160"/>
       <c r="E46" s="160"/>
-      <c r="F46" s="162"/>
-      <c r="G46" s="221"/>
-      <c r="H46" s="160"/>
-      <c r="I46" s="162"/>
-      <c r="J46" s="160"/>
-      <c r="K46" s="160"/>
+      <c r="F46" s="162" t="s">
+        <v>995</v>
+      </c>
+      <c r="G46" s="221" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="160" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I46" s="162" t="s">
+        <v>1288</v>
+      </c>
+      <c r="J46" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L46" s="157" t="s">
         <v>9</v>
       </c>
@@ -10845,11 +11060,11 @@
       </c>
       <c r="O46" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20:51</v>
       </c>
       <c r="P46" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>20:29</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="18" customHeight="1">
@@ -10859,12 +11074,12 @@
       <c r="B47" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="162" t="s">
-        <v>1602</v>
+      <c r="C47" s="289" t="s">
+        <v>1601</v>
       </c>
       <c r="D47" s="160"/>
       <c r="E47" s="160" t="s">
-        <v>1603</v>
+        <v>453</v>
       </c>
       <c r="F47" s="160"/>
       <c r="G47" s="221"/>
@@ -10901,13 +11116,21 @@
       <c r="C48" s="162"/>
       <c r="D48" s="160"/>
       <c r="E48" s="160"/>
-      <c r="F48" s="162"/>
-      <c r="G48" s="221"/>
-      <c r="H48" s="160"/>
+      <c r="F48" s="162" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G48" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48" s="160" t="s">
+        <v>1396</v>
+      </c>
       <c r="I48" s="164" t="s">
-        <v>1600</v>
-      </c>
-      <c r="J48" s="160"/>
+        <v>1540</v>
+      </c>
+      <c r="J48" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="K48" s="160" t="s">
         <v>1015</v>
       </c>
@@ -10923,7 +11146,7 @@
       </c>
       <c r="O48" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>22:17</v>
       </c>
       <c r="P48" s="151" t="str">
         <f t="shared" si="2"/>
@@ -10940,12 +11163,24 @@
       <c r="C49" s="166"/>
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
-      <c r="F49" s="167"/>
-      <c r="G49" s="225"/>
-      <c r="H49" s="166"/>
-      <c r="I49" s="167"/>
-      <c r="J49" s="166"/>
-      <c r="K49" s="166"/>
+      <c r="F49" s="167" t="s">
+        <v>1533</v>
+      </c>
+      <c r="G49" s="225" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="166" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I49" s="167" t="s">
+        <v>862</v>
+      </c>
+      <c r="J49" s="166" t="s">
+        <v>1635</v>
+      </c>
+      <c r="K49" s="166" t="s">
+        <v>1636</v>
+      </c>
       <c r="L49" s="165" t="s">
         <v>3</v>
       </c>
@@ -10958,11 +11193,11 @@
       </c>
       <c r="O49" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>23:55</v>
       </c>
       <c r="P49" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>23:35</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="18" customHeight="1">
@@ -10975,9 +11210,15 @@
       <c r="C50" s="170"/>
       <c r="D50" s="169"/>
       <c r="E50" s="169"/>
-      <c r="F50" s="170"/>
-      <c r="G50" s="227"/>
-      <c r="H50" s="169"/>
+      <c r="F50" s="170" t="s">
+        <v>658</v>
+      </c>
+      <c r="G50" s="227" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="169" t="s">
+        <v>1016</v>
+      </c>
       <c r="I50" s="170"/>
       <c r="J50" s="169"/>
       <c r="K50" s="169"/>
@@ -10993,7 +11234,7 @@
       </c>
       <c r="O50" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>00:55</v>
       </c>
       <c r="P50" s="151" t="str">
         <f t="shared" si="2"/>
@@ -11007,15 +11248,27 @@
       <c r="B51" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="172"/>
-      <c r="D51" s="171"/>
-      <c r="E51" s="171"/>
+      <c r="C51" s="172" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D51" s="171" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="171" t="s">
+        <v>1615</v>
+      </c>
       <c r="F51" s="172"/>
       <c r="G51" s="229"/>
       <c r="H51" s="171"/>
-      <c r="I51" s="172"/>
-      <c r="J51" s="171"/>
-      <c r="K51" s="171"/>
+      <c r="I51" s="172" t="s">
+        <v>600</v>
+      </c>
+      <c r="J51" s="171" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L51" s="168" t="s">
         <v>36</v>
       </c>
@@ -11024,7 +11277,7 @@
       </c>
       <c r="N51" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>01:43</v>
       </c>
       <c r="O51" s="151" t="str">
         <f t="shared" si="1"/>
@@ -11032,7 +11285,7 @@
       </c>
       <c r="P51" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>01:02</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="18" customHeight="1">
@@ -11045,12 +11298,24 @@
       <c r="C52" s="173"/>
       <c r="D52" s="172"/>
       <c r="E52" s="171"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="229"/>
-      <c r="H52" s="171"/>
-      <c r="I52" s="173"/>
-      <c r="J52" s="171"/>
-      <c r="K52" s="171"/>
+      <c r="F52" s="173" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G52" s="229" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="171" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I52" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J52" s="171" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L52" s="168" t="s">
         <v>35</v>
       </c>
@@ -11063,11 +11328,11 @@
       </c>
       <c r="O52" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>02:21</v>
       </c>
       <c r="P52" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>02:29</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="18" customHeight="1">
@@ -11080,9 +11345,15 @@
       <c r="C53" s="172"/>
       <c r="D53" s="171"/>
       <c r="E53" s="171"/>
-      <c r="F53" s="172"/>
-      <c r="G53" s="229"/>
-      <c r="H53" s="171"/>
+      <c r="F53" s="172" t="s">
+        <v>1639</v>
+      </c>
+      <c r="G53" s="229" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="171" t="s">
+        <v>1016</v>
+      </c>
       <c r="I53" s="172"/>
       <c r="J53" s="171"/>
       <c r="K53" s="171"/>
@@ -11098,7 +11369,7 @@
       </c>
       <c r="O53" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>03:50</v>
       </c>
       <c r="P53" s="151" t="str">
         <f t="shared" si="2"/>
@@ -11118,9 +11389,15 @@
       <c r="F54" s="172"/>
       <c r="G54" s="229"/>
       <c r="H54" s="171"/>
-      <c r="I54" s="172"/>
-      <c r="J54" s="171"/>
-      <c r="K54" s="171"/>
+      <c r="I54" s="172" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J54" s="171" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L54" s="168" t="s">
         <v>32</v>
       </c>
@@ -11137,7 +11414,7 @@
       </c>
       <c r="P54" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:03</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1">
@@ -11147,15 +11424,33 @@
       <c r="B55" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="172"/>
-      <c r="D55" s="171"/>
-      <c r="E55" s="171"/>
-      <c r="F55" s="172"/>
-      <c r="G55" s="229"/>
-      <c r="H55" s="171"/>
-      <c r="I55" s="172"/>
-      <c r="J55" s="171"/>
-      <c r="K55" s="171"/>
+      <c r="C55" s="172" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D55" s="171" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E55" s="171" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F55" s="172" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G55" s="229" t="s">
+        <v>27</v>
+      </c>
+      <c r="H55" s="171" t="s">
+        <v>1396</v>
+      </c>
+      <c r="I55" s="172" t="s">
+        <v>795</v>
+      </c>
+      <c r="J55" s="171" t="s">
+        <v>4</v>
+      </c>
+      <c r="K55" s="171" t="s">
+        <v>1015</v>
+      </c>
       <c r="L55" s="168" t="s">
         <v>31</v>
       </c>
@@ -11164,15 +11459,15 @@
       </c>
       <c r="N55" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>05:10</v>
       </c>
       <c r="O55" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>05:15</v>
       </c>
       <c r="P55" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>05:37</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1">
@@ -11186,10 +11481,10 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1606</v>
+        <v>1575</v>
       </c>
       <c r="E56" s="171" t="s">
-        <v>1604</v>
+        <v>1573</v>
       </c>
       <c r="F56" s="172" t="s">
         <v>77</v>
@@ -11439,19 +11734,19 @@
       <c r="D61" s="171"/>
       <c r="E61" s="171"/>
       <c r="F61" s="172" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="G61" s="229" t="s">
-        <v>1516</v>
+        <v>1499</v>
       </c>
       <c r="H61" s="171" t="s">
         <v>1399</v>
       </c>
       <c r="I61" s="172" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="J61" s="171" t="s">
-        <v>1605</v>
+        <v>1574</v>
       </c>
       <c r="K61" s="171" t="s">
         <v>1402</v>
@@ -11483,20 +11778,22 @@
         <v>55</v>
       </c>
       <c r="C62" s="172" t="s">
-        <v>1493</v>
-      </c>
-      <c r="D62" s="171"/>
+        <v>1581</v>
+      </c>
+      <c r="D62" s="171" t="s">
+        <v>1629</v>
+      </c>
       <c r="E62" s="171" t="s">
-        <v>1418</v>
+        <v>1628</v>
       </c>
       <c r="F62" s="172" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="G62" s="229" t="s">
-        <v>1515</v>
+        <v>1498</v>
       </c>
       <c r="H62" s="171" t="s">
-        <v>1520</v>
+        <v>1503</v>
       </c>
       <c r="I62" s="172"/>
       <c r="J62" s="171"/>
@@ -11509,7 +11806,7 @@
       </c>
       <c r="N62" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>12:23</v>
+        <v>12:21</v>
       </c>
       <c r="O62" s="151" t="str">
         <f t="shared" si="1"/>
@@ -11534,10 +11831,10 @@
       <c r="G63" s="229"/>
       <c r="H63" s="171"/>
       <c r="I63" s="172" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="J63" s="171" t="s">
-        <v>13</v>
+        <v>1635</v>
       </c>
       <c r="K63" s="171" t="s">
         <v>1403</v>
@@ -11572,22 +11869,22 @@
       <c r="D64" s="171"/>
       <c r="E64" s="171"/>
       <c r="F64" s="172" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="G64" s="229" t="s">
         <v>0</v>
       </c>
       <c r="H64" s="171" t="s">
-        <v>1519</v>
+        <v>1502</v>
       </c>
       <c r="I64" s="172" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="J64" s="171" t="s">
         <v>13</v>
       </c>
       <c r="K64" s="171" t="s">
-        <v>1513</v>
+        <v>1496</v>
       </c>
       <c r="L64" s="168" t="s">
         <v>20</v>
@@ -11622,7 +11919,7 @@
         <v>695</v>
       </c>
       <c r="G65" s="229" t="s">
-        <v>1518</v>
+        <v>1501</v>
       </c>
       <c r="H65" s="171" t="s">
         <v>1018</v>
@@ -11657,14 +11954,16 @@
         <v>55</v>
       </c>
       <c r="C66" s="172" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D66" s="171"/>
+        <v>110</v>
+      </c>
+      <c r="D66" s="171" t="s">
+        <v>63</v>
+      </c>
       <c r="E66" s="171" t="s">
-        <v>1445</v>
+        <v>1618</v>
       </c>
       <c r="F66" s="172" t="s">
-        <v>1502</v>
+        <v>1485</v>
       </c>
       <c r="G66" s="229" t="s">
         <v>17</v>
@@ -11673,10 +11972,10 @@
         <v>1017</v>
       </c>
       <c r="I66" s="172" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="J66" s="171" t="s">
-        <v>1514</v>
+        <v>1497</v>
       </c>
       <c r="K66" s="171" t="s">
         <v>1403</v>
@@ -11689,7 +11988,7 @@
       </c>
       <c r="N66" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>16:51</v>
+        <v>16:19</v>
       </c>
       <c r="O66" s="151" t="str">
         <f t="shared" si="1"/>
@@ -11752,7 +12051,7 @@
       <c r="D68" s="171"/>
       <c r="E68" s="171"/>
       <c r="F68" s="172" t="s">
-        <v>1503</v>
+        <v>1486</v>
       </c>
       <c r="G68" s="229" t="s">
         <v>11</v>
@@ -11793,7 +12092,7 @@
       <c r="D69" s="171"/>
       <c r="E69" s="171"/>
       <c r="F69" s="172" t="s">
-        <v>1504</v>
+        <v>1487</v>
       </c>
       <c r="G69" s="229" t="s">
         <v>0</v>
@@ -11802,7 +12101,7 @@
         <v>1018</v>
       </c>
       <c r="I69" s="172" t="s">
-        <v>1505</v>
+        <v>1488</v>
       </c>
       <c r="J69" s="171" t="s">
         <v>4</v>
@@ -11837,9 +12136,11 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D70" s="171"/>
+        <v>202</v>
+      </c>
+      <c r="D70" s="172" t="s">
+        <v>1600</v>
+      </c>
       <c r="E70" s="171" t="s">
         <v>71</v>
       </c>
@@ -11847,7 +12148,7 @@
       <c r="G70" s="229"/>
       <c r="H70" s="171"/>
       <c r="I70" s="173" t="s">
-        <v>1506</v>
+        <v>1489</v>
       </c>
       <c r="J70" s="171" t="s">
         <v>13</v>
@@ -11863,7 +12164,7 @@
       </c>
       <c r="N70" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>20:23</v>
+        <v>20:20</v>
       </c>
       <c r="O70" s="151" t="str">
         <f t="shared" si="4"/>
@@ -11885,7 +12186,7 @@
       <c r="D71" s="171"/>
       <c r="E71" s="171"/>
       <c r="F71" s="172" t="s">
-        <v>1507</v>
+        <v>1490</v>
       </c>
       <c r="G71" s="229" t="s">
         <v>11</v>
@@ -11967,13 +12268,13 @@
       <c r="D73" s="175"/>
       <c r="E73" s="175"/>
       <c r="F73" s="176" t="s">
-        <v>1508</v>
+        <v>1491</v>
       </c>
       <c r="G73" s="233" t="s">
         <v>27</v>
       </c>
       <c r="H73" s="175" t="s">
-        <v>1591</v>
+        <v>1564</v>
       </c>
       <c r="I73" s="176" t="s">
         <v>150</v>
@@ -12010,9 +12311,15 @@
       <c r="B74" s="178" t="s">
         <v>52</v>
       </c>
-      <c r="C74" s="179"/>
-      <c r="D74" s="178"/>
-      <c r="E74" s="178"/>
+      <c r="C74" s="179" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D74" s="178" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E74" s="178" t="s">
+        <v>1633</v>
+      </c>
       <c r="F74" s="179" t="s">
         <v>141</v>
       </c>
@@ -12033,7 +12340,7 @@
       </c>
       <c r="N74" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>00:01</v>
       </c>
       <c r="O74" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12058,7 +12365,7 @@
         <v>127</v>
       </c>
       <c r="G75" s="237" t="s">
-        <v>1590</v>
+        <v>1563</v>
       </c>
       <c r="H75" s="180" t="s">
         <v>1396</v>
@@ -12067,7 +12374,7 @@
         <v>600</v>
       </c>
       <c r="J75" s="180" t="s">
-        <v>1597</v>
+        <v>1570</v>
       </c>
       <c r="K75" s="180" t="s">
         <v>1403</v>
@@ -12098,9 +12405,15 @@
       <c r="B76" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C76" s="181"/>
-      <c r="D76" s="180"/>
-      <c r="E76" s="180"/>
+      <c r="C76" s="181" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D76" s="180" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E76" s="180" t="s">
+        <v>1630</v>
+      </c>
       <c r="F76" s="181" t="s">
         <v>783</v>
       </c>
@@ -12127,7 +12440,7 @@
       </c>
       <c r="N76" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>02:45</v>
       </c>
       <c r="O76" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12274,9 +12587,15 @@
       <c r="B80" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C80" s="181"/>
-      <c r="D80" s="180"/>
-      <c r="E80" s="180"/>
+      <c r="C80" s="181" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D80" s="180" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" s="180" t="s">
+        <v>1612</v>
+      </c>
       <c r="F80" s="181"/>
       <c r="G80" s="237"/>
       <c r="H80" s="180"/>
@@ -12291,7 +12610,7 @@
       </c>
       <c r="N80" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>06:07</v>
       </c>
       <c r="O80" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12313,16 +12632,16 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1509</v>
+        <v>1492</v>
       </c>
       <c r="G81" s="237" t="s">
-        <v>1584</v>
+        <v>1557</v>
       </c>
       <c r="H81" s="180" t="s">
-        <v>1585</v>
+        <v>1558</v>
       </c>
       <c r="I81" s="181" t="s">
-        <v>1510</v>
+        <v>1493</v>
       </c>
       <c r="J81" s="180" t="s">
         <v>4</v>
@@ -12439,29 +12758,31 @@
         <v>52</v>
       </c>
       <c r="C84" s="181" t="s">
-        <v>1490</v>
-      </c>
-      <c r="D84" s="180"/>
+        <v>154</v>
+      </c>
+      <c r="D84" s="180" t="s">
+        <v>64</v>
+      </c>
       <c r="E84" s="180" t="s">
-        <v>1497</v>
+        <v>1602</v>
       </c>
       <c r="F84" s="181" t="s">
-        <v>1511</v>
+        <v>1494</v>
       </c>
       <c r="G84" s="237" t="s">
-        <v>1586</v>
+        <v>1559</v>
       </c>
       <c r="H84" s="180" t="s">
-        <v>1587</v>
+        <v>1560</v>
       </c>
       <c r="I84" s="181" t="s">
         <v>651</v>
       </c>
       <c r="J84" s="180" t="s">
-        <v>1597</v>
+        <v>1570</v>
       </c>
       <c r="K84" s="180" t="s">
-        <v>1598</v>
+        <v>1571</v>
       </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
@@ -12471,7 +12792,7 @@
       </c>
       <c r="N84" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>10:11</v>
+        <v>10:09</v>
       </c>
       <c r="O84" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12502,7 +12823,7 @@
         <v>4</v>
       </c>
       <c r="K85" s="180" t="s">
-        <v>1599</v>
+        <v>1572</v>
       </c>
       <c r="L85" s="177" t="s">
         <v>23</v>
@@ -12534,13 +12855,13 @@
       <c r="D86" s="180"/>
       <c r="E86" s="180"/>
       <c r="F86" s="181" t="s">
-        <v>1512</v>
+        <v>1495</v>
       </c>
       <c r="G86" s="237" t="s">
-        <v>1588</v>
+        <v>1561</v>
       </c>
       <c r="H86" s="180" t="s">
-        <v>1589</v>
+        <v>1562</v>
       </c>
       <c r="I86" s="182"/>
       <c r="J86" s="180"/>
@@ -12575,7 +12896,7 @@
       <c r="D87" s="180"/>
       <c r="E87" s="180"/>
       <c r="F87" s="181" t="s">
-        <v>1543</v>
+        <v>1516</v>
       </c>
       <c r="G87" s="237" t="s">
         <v>0</v>
@@ -12584,7 +12905,7 @@
         <v>1018</v>
       </c>
       <c r="I87" s="181" t="s">
-        <v>1544</v>
+        <v>1517</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -12619,11 +12940,13 @@
         <v>52</v>
       </c>
       <c r="C88" s="181" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D88" s="180"/>
+        <v>177</v>
+      </c>
+      <c r="D88" s="180" t="s">
+        <v>1143</v>
+      </c>
       <c r="E88" s="180" t="s">
-        <v>1532</v>
+        <v>1505</v>
       </c>
       <c r="F88" s="181" t="s">
         <v>1342</v>
@@ -12651,7 +12974,7 @@
       </c>
       <c r="N88" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>14:10</v>
+        <v>14:08</v>
       </c>
       <c r="O88" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12708,7 +13031,7 @@
       <c r="D90" s="180"/>
       <c r="E90" s="180"/>
       <c r="F90" s="181" t="s">
-        <v>1545</v>
+        <v>1518</v>
       </c>
       <c r="G90" s="237" t="s">
         <v>17</v>
@@ -12755,7 +13078,7 @@
       <c r="D91" s="180"/>
       <c r="E91" s="180"/>
       <c r="F91" s="181" t="s">
-        <v>1546</v>
+        <v>1519</v>
       </c>
       <c r="G91" s="237" t="s">
         <v>27</v>
@@ -12764,7 +13087,7 @@
         <v>1396</v>
       </c>
       <c r="I91" s="181" t="s">
-        <v>1547</v>
+        <v>1520</v>
       </c>
       <c r="J91" s="180" t="s">
         <v>4</v>
@@ -12799,11 +13122,13 @@
         <v>52</v>
       </c>
       <c r="C92" s="181" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D92" s="180"/>
+        <v>1584</v>
+      </c>
+      <c r="D92" s="180" t="s">
+        <v>34</v>
+      </c>
       <c r="E92" s="180" t="s">
-        <v>1499</v>
+        <v>1604</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="237"/>
@@ -12819,7 +13144,7 @@
       </c>
       <c r="N92" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>18:25</v>
+        <v>18:23</v>
       </c>
       <c r="O92" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12850,7 +13175,7 @@
         <v>1396</v>
       </c>
       <c r="I93" s="181" t="s">
-        <v>1548</v>
+        <v>1521</v>
       </c>
       <c r="J93" s="180" t="s">
         <v>13</v>
@@ -12888,7 +13213,7 @@
       <c r="D94" s="180"/>
       <c r="E94" s="180"/>
       <c r="F94" s="181" t="s">
-        <v>1549</v>
+        <v>1522</v>
       </c>
       <c r="G94" s="237" t="s">
         <v>11</v>
@@ -12897,7 +13222,7 @@
         <v>1016</v>
       </c>
       <c r="I94" s="181" t="s">
-        <v>1550</v>
+        <v>1523</v>
       </c>
       <c r="J94" s="180" t="s">
         <v>13</v>
@@ -12966,11 +13291,17 @@
       <c r="B96" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C96" s="181"/>
-      <c r="D96" s="180"/>
-      <c r="E96" s="180"/>
+      <c r="C96" s="181" t="s">
+        <v>804</v>
+      </c>
+      <c r="D96" s="180" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="180" t="s">
+        <v>1624</v>
+      </c>
       <c r="F96" s="181" t="s">
-        <v>1551</v>
+        <v>1524</v>
       </c>
       <c r="G96" s="237" t="s">
         <v>11</v>
@@ -12995,7 +13326,7 @@
       </c>
       <c r="N96" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>22:08</v>
       </c>
       <c r="O96" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13095,9 +13426,15 @@
       <c r="B99" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C99" s="188"/>
-      <c r="D99" s="187"/>
-      <c r="E99" s="189"/>
+      <c r="C99" s="188" t="s">
+        <v>234</v>
+      </c>
+      <c r="D99" s="187" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E99" s="189" t="s">
+        <v>1412</v>
+      </c>
       <c r="F99" s="190" t="s">
         <v>623</v>
       </c>
@@ -13124,7 +13461,7 @@
       </c>
       <c r="N99" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>01:22</v>
       </c>
       <c r="O99" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13271,9 +13608,15 @@
       <c r="B103" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="189"/>
-      <c r="D103" s="189"/>
-      <c r="E103" s="189"/>
+      <c r="C103" s="297">
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="D103" s="189" t="s">
+        <v>1</v>
+      </c>
+      <c r="E103" s="189" t="s">
+        <v>1609</v>
+      </c>
       <c r="F103" s="190" t="s">
         <v>616</v>
       </c>
@@ -13284,7 +13627,7 @@
         <v>1016</v>
       </c>
       <c r="I103" s="190" t="s">
-        <v>1552</v>
+        <v>1525</v>
       </c>
       <c r="J103" s="189" t="s">
         <v>13</v>
@@ -13300,7 +13643,7 @@
       </c>
       <c r="N103" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>05:52</v>
       </c>
       <c r="O103" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13413,7 +13756,7 @@
         <v>1016</v>
       </c>
       <c r="I106" s="190" t="s">
-        <v>1553</v>
+        <v>1526</v>
       </c>
       <c r="J106" s="189" t="s">
         <v>13</v>
@@ -13483,11 +13826,13 @@
         <v>44</v>
       </c>
       <c r="C108" s="190" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D108" s="189"/>
+        <v>1585</v>
+      </c>
+      <c r="D108" s="189" t="s">
+        <v>1143</v>
+      </c>
       <c r="E108" s="189" t="s">
-        <v>1500</v>
+        <v>1484</v>
       </c>
       <c r="F108" s="190" t="s">
         <v>207</v>
@@ -13515,7 +13860,7 @@
       </c>
       <c r="N108" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>10:13</v>
+        <v>10:11</v>
       </c>
       <c r="O108" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13546,7 +13891,7 @@
         <v>1016</v>
       </c>
       <c r="I109" s="190" t="s">
-        <v>1554</v>
+        <v>1527</v>
       </c>
       <c r="J109" s="189" t="s">
         <v>4</v>
@@ -13662,11 +14007,17 @@
       <c r="B112" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C112" s="190"/>
-      <c r="D112" s="189"/>
-      <c r="E112" s="189"/>
+      <c r="C112" s="190" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D112" s="189" t="s">
+        <v>903</v>
+      </c>
+      <c r="E112" s="189" t="s">
+        <v>1409</v>
+      </c>
       <c r="F112" s="190" t="s">
-        <v>1555</v>
+        <v>1528</v>
       </c>
       <c r="G112" s="244" t="s">
         <v>27</v>
@@ -13675,7 +14026,7 @@
         <v>1396</v>
       </c>
       <c r="I112" s="190" t="s">
-        <v>1556</v>
+        <v>1529</v>
       </c>
       <c r="J112" s="189" t="s">
         <v>4</v>
@@ -13691,7 +14042,7 @@
       </c>
       <c r="N112" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>14:32</v>
       </c>
       <c r="O112" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13791,9 +14142,15 @@
       <c r="B115" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C115" s="190"/>
-      <c r="D115" s="189"/>
-      <c r="E115" s="189"/>
+      <c r="C115" s="190" t="s">
+        <v>788</v>
+      </c>
+      <c r="D115" s="189" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E115" s="189" t="s">
+        <v>1620</v>
+      </c>
       <c r="F115" s="190" t="s">
         <v>1036</v>
       </c>
@@ -13804,7 +14161,7 @@
         <v>1018</v>
       </c>
       <c r="I115" s="190" t="s">
-        <v>1557</v>
+        <v>1530</v>
       </c>
       <c r="J115" s="189" t="s">
         <v>13</v>
@@ -13820,7 +14177,7 @@
       </c>
       <c r="N115" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>17:54</v>
       </c>
       <c r="O115" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13883,7 +14240,7 @@
       <c r="D117" s="189"/>
       <c r="E117" s="189"/>
       <c r="F117" s="190" t="s">
-        <v>1558</v>
+        <v>1531</v>
       </c>
       <c r="G117" s="244" t="s">
         <v>27</v>
@@ -13920,13 +14277,9 @@
       <c r="B118" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C118" s="190" t="s">
-        <v>1495</v>
-      </c>
+      <c r="C118" s="190"/>
       <c r="D118" s="189"/>
-      <c r="E118" s="189" t="s">
-        <v>1413</v>
-      </c>
+      <c r="E118" s="189"/>
       <c r="F118" s="190" t="s">
         <v>790</v>
       </c>
@@ -13953,7 +14306,7 @@
       </c>
       <c r="N118" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>20:22</v>
+        <v/>
       </c>
       <c r="O118" s="151" t="str">
         <f t="shared" si="4"/>
@@ -14012,11 +14365,17 @@
       <c r="B120" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C120" s="190"/>
-      <c r="D120" s="189"/>
-      <c r="E120" s="189"/>
+      <c r="C120" s="190" t="s">
+        <v>861</v>
+      </c>
+      <c r="D120" s="189" t="s">
+        <v>1631</v>
+      </c>
+      <c r="E120" s="189" t="s">
+        <v>1619</v>
+      </c>
       <c r="F120" s="190" t="s">
-        <v>1559</v>
+        <v>1532</v>
       </c>
       <c r="G120" s="244" t="s">
         <v>17</v>
@@ -14035,7 +14394,7 @@
       </c>
       <c r="N120" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>22:05</v>
       </c>
       <c r="O120" s="151" t="str">
         <f t="shared" si="4"/>
@@ -14057,7 +14416,7 @@
       <c r="D121" s="193"/>
       <c r="E121" s="193"/>
       <c r="F121" s="194" t="s">
-        <v>1560</v>
+        <v>1533</v>
       </c>
       <c r="G121" s="247" t="s">
         <v>0</v>
@@ -14141,9 +14500,15 @@
       <c r="B123" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="199"/>
-      <c r="D123" s="198"/>
-      <c r="E123" s="198"/>
+      <c r="C123" s="199" t="s">
+        <v>269</v>
+      </c>
+      <c r="D123" s="198" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E123" s="198" t="s">
+        <v>1616</v>
+      </c>
       <c r="F123" s="199" t="s">
         <v>623</v>
       </c>
@@ -14170,7 +14535,7 @@
       </c>
       <c r="N123" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>01:25</v>
       </c>
       <c r="O123" s="151" t="str">
         <f t="shared" si="4"/>
@@ -14317,9 +14682,15 @@
       <c r="B127" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C127" s="199"/>
-      <c r="D127" s="198"/>
-      <c r="E127" s="198"/>
+      <c r="C127" s="199" t="s">
+        <v>101</v>
+      </c>
+      <c r="D127" s="198" t="s">
+        <v>45</v>
+      </c>
+      <c r="E127" s="198" t="s">
+        <v>1413</v>
+      </c>
       <c r="F127" s="199" t="s">
         <v>616</v>
       </c>
@@ -14346,7 +14717,7 @@
       </c>
       <c r="N127" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>05:20</v>
       </c>
       <c r="O127" s="151" t="str">
         <f t="shared" si="4"/>
@@ -14459,7 +14830,7 @@
         <v>1018</v>
       </c>
       <c r="I130" s="199" t="s">
-        <v>1561</v>
+        <v>1534</v>
       </c>
       <c r="J130" s="198" t="s">
         <v>13</v>
@@ -14493,9 +14864,15 @@
       <c r="B131" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C131" s="199"/>
-      <c r="D131" s="198"/>
-      <c r="E131" s="198"/>
+      <c r="C131" s="199" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D131" s="198" t="s">
+        <v>908</v>
+      </c>
+      <c r="E131" s="198" t="s">
+        <v>1623</v>
+      </c>
       <c r="F131" s="199"/>
       <c r="G131" s="251"/>
       <c r="H131" s="198"/>
@@ -14510,7 +14887,7 @@
       </c>
       <c r="N131" s="151" t="str">
         <f t="shared" ref="N131:N169" si="6">IF($C131&lt;&gt;"",TEXT($C131,"HH:MM"),"")</f>
-        <v/>
+        <v>09:22</v>
       </c>
       <c r="O131" s="151" t="str">
         <f t="shared" ref="O131:O169" si="7">IF($F131&lt;&gt;"",TEXT($F131,"HH:MM"),"")</f>
@@ -14532,7 +14909,7 @@
       <c r="D132" s="198"/>
       <c r="E132" s="198"/>
       <c r="F132" s="199" t="s">
-        <v>1562</v>
+        <v>1535</v>
       </c>
       <c r="G132" s="251" t="s">
         <v>27</v>
@@ -14541,7 +14918,7 @@
         <v>1396</v>
       </c>
       <c r="I132" s="200" t="s">
-        <v>1536</v>
+        <v>1509</v>
       </c>
       <c r="J132" s="198" t="s">
         <v>4</v>
@@ -14588,7 +14965,7 @@
         <v>1018</v>
       </c>
       <c r="I133" s="199" t="s">
-        <v>1563</v>
+        <v>1536</v>
       </c>
       <c r="J133" s="198" t="s">
         <v>13</v>
@@ -14658,11 +15035,13 @@
         <v>38</v>
       </c>
       <c r="C135" s="201">
-        <v>0.54652777777777772</v>
-      </c>
-      <c r="D135" s="198"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D135" s="198" t="s">
+        <v>1595</v>
+      </c>
       <c r="E135" s="198" t="s">
-        <v>1501</v>
+        <v>1619</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>607</v>
@@ -14690,7 +15069,7 @@
       </c>
       <c r="N135" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>13:07</v>
+        <v>13:12</v>
       </c>
       <c r="O135" s="151" t="str">
         <f t="shared" si="7"/>
@@ -14803,7 +15182,7 @@
         <v>1016</v>
       </c>
       <c r="I138" s="199" t="s">
-        <v>1564</v>
+        <v>1537</v>
       </c>
       <c r="J138" s="198" t="s">
         <v>4</v>
@@ -14838,12 +15217,16 @@
         <v>38</v>
       </c>
       <c r="C139" s="199" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D139" s="198"/>
-      <c r="E139" s="198"/>
+        <v>1587</v>
+      </c>
+      <c r="D139" s="198" t="s">
+        <v>902</v>
+      </c>
+      <c r="E139" s="198" t="s">
+        <v>1611</v>
+      </c>
       <c r="F139" s="199" t="s">
-        <v>1565</v>
+        <v>1538</v>
       </c>
       <c r="G139" s="251" t="s">
         <v>17</v>
@@ -14862,7 +15245,7 @@
       </c>
       <c r="N139" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>17:02</v>
+        <v>17:00</v>
       </c>
       <c r="O139" s="151" t="str">
         <f t="shared" si="7"/>
@@ -14887,7 +15270,7 @@
       <c r="G140" s="251"/>
       <c r="H140" s="198"/>
       <c r="I140" s="199" t="s">
-        <v>1566</v>
+        <v>1539</v>
       </c>
       <c r="J140" s="198" t="s">
         <v>4</v>
@@ -14969,11 +15352,13 @@
         <v>38</v>
       </c>
       <c r="C142" s="199" t="s">
-        <v>293</v>
-      </c>
-      <c r="D142" s="198"/>
+        <v>1588</v>
+      </c>
+      <c r="D142" s="198" t="s">
+        <v>1143</v>
+      </c>
       <c r="E142" s="198" t="s">
-        <v>1498</v>
+        <v>1607</v>
       </c>
       <c r="F142" s="199" t="s">
         <v>1288</v>
@@ -15001,7 +15386,7 @@
       </c>
       <c r="N142" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>20:59</v>
+        <v>20:57</v>
       </c>
       <c r="O142" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15058,7 +15443,7 @@
       <c r="D144" s="198"/>
       <c r="E144" s="198"/>
       <c r="F144" s="199" t="s">
-        <v>1567</v>
+        <v>1540</v>
       </c>
       <c r="G144" s="251" t="s">
         <v>0</v>
@@ -15105,7 +15490,7 @@
       <c r="D145" s="203"/>
       <c r="E145" s="203"/>
       <c r="F145" s="204" t="s">
-        <v>1568</v>
+        <v>1541</v>
       </c>
       <c r="G145" s="255" t="s">
         <v>27</v>
@@ -15277,9 +15662,15 @@
       <c r="B149" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="209"/>
-      <c r="D149" s="208"/>
-      <c r="E149" s="208"/>
+      <c r="C149" s="209" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D149" s="208" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E149" s="208" t="s">
+        <v>1625</v>
+      </c>
       <c r="F149" s="209" t="s">
         <v>236</v>
       </c>
@@ -15300,7 +15691,7 @@
       </c>
       <c r="N149" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>03:30</v>
       </c>
       <c r="O149" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15325,7 +15716,7 @@
       <c r="G150" s="259"/>
       <c r="H150" s="208"/>
       <c r="I150" s="209" t="s">
-        <v>1569</v>
+        <v>1542</v>
       </c>
       <c r="J150" s="208" t="s">
         <v>13</v>
@@ -15400,12 +15791,12 @@
       <c r="B152" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="209" t="s">
-        <v>1496</v>
+      <c r="C152" s="292" t="s">
+        <v>1605</v>
       </c>
       <c r="D152" s="208"/>
       <c r="E152" s="208" t="s">
-        <v>1517</v>
+        <v>1500</v>
       </c>
       <c r="F152" s="209"/>
       <c r="G152" s="259"/>
@@ -15421,7 +15812,7 @@
       </c>
       <c r="N152" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>06:56</v>
+        <v>06:54</v>
       </c>
       <c r="O152" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15531,7 +15922,7 @@
       <c r="D155" s="208"/>
       <c r="E155" s="208"/>
       <c r="F155" s="209" t="s">
-        <v>1570</v>
+        <v>1543</v>
       </c>
       <c r="G155" s="259" t="s">
         <v>0</v>
@@ -15574,13 +15965,9 @@
       <c r="B156" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C156" s="209" t="s">
-        <v>1523</v>
-      </c>
+      <c r="C156" s="209"/>
       <c r="D156" s="208"/>
-      <c r="E156" s="208" t="s">
-        <v>1531</v>
-      </c>
+      <c r="E156" s="208"/>
       <c r="F156" s="209"/>
       <c r="G156" s="259"/>
       <c r="H156" s="208"/>
@@ -15595,7 +15982,7 @@
       </c>
       <c r="N156" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>11:15</v>
+        <v/>
       </c>
       <c r="O156" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15613,11 +16000,17 @@
       <c r="B157" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C157" s="209"/>
-      <c r="D157" s="208"/>
-      <c r="E157" s="208"/>
+      <c r="C157" s="209" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D157" s="208" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E157" s="208" t="s">
+        <v>1626</v>
+      </c>
       <c r="F157" s="209" t="s">
-        <v>1571</v>
+        <v>1544</v>
       </c>
       <c r="G157" s="259" t="s">
         <v>0</v>
@@ -15626,7 +16019,7 @@
         <v>1018</v>
       </c>
       <c r="I157" s="209" t="s">
-        <v>1554</v>
+        <v>1527</v>
       </c>
       <c r="J157" s="208" t="s">
         <v>4</v>
@@ -15642,7 +16035,7 @@
       </c>
       <c r="N157" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>11:13</v>
       </c>
       <c r="O157" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15664,7 +16057,7 @@
       <c r="D158" s="208"/>
       <c r="E158" s="208"/>
       <c r="F158" s="209" t="s">
-        <v>1572</v>
+        <v>1545</v>
       </c>
       <c r="G158" s="259" t="s">
         <v>17</v>
@@ -15702,11 +16095,13 @@
         <v>2</v>
       </c>
       <c r="C159" s="209" t="s">
-        <v>1522</v>
-      </c>
-      <c r="D159" s="208"/>
+        <v>1590</v>
+      </c>
+      <c r="D159" s="208" t="s">
+        <v>908</v>
+      </c>
       <c r="E159" s="208" t="s">
-        <v>1525</v>
+        <v>1410</v>
       </c>
       <c r="F159" s="209"/>
       <c r="G159" s="259"/>
@@ -15728,7 +16123,7 @@
       </c>
       <c r="N159" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>13:54</v>
+        <v>13:52</v>
       </c>
       <c r="O159" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15750,7 +16145,7 @@
       <c r="D160" s="208"/>
       <c r="E160" s="208"/>
       <c r="F160" s="209" t="s">
-        <v>1573</v>
+        <v>1546</v>
       </c>
       <c r="G160" s="259" t="s">
         <v>27</v>
@@ -15759,7 +16154,7 @@
         <v>1396</v>
       </c>
       <c r="I160" s="209" t="s">
-        <v>1574</v>
+        <v>1547</v>
       </c>
       <c r="J160" s="208" t="s">
         <v>4</v>
@@ -15797,7 +16192,7 @@
       <c r="D161" s="208"/>
       <c r="E161" s="208"/>
       <c r="F161" s="209" t="s">
-        <v>1575</v>
+        <v>1548</v>
       </c>
       <c r="G161" s="259" t="s">
         <v>11</v>
@@ -15806,7 +16201,7 @@
         <v>1016</v>
       </c>
       <c r="I161" s="210" t="s">
-        <v>1576</v>
+        <v>1549</v>
       </c>
       <c r="J161" s="208" t="s">
         <v>13</v>
@@ -15875,9 +16270,15 @@
       <c r="B163" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C163" s="209"/>
-      <c r="D163" s="208"/>
-      <c r="E163" s="208"/>
+      <c r="C163" s="209" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D163" s="208" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E163" s="208" t="s">
+        <v>1622</v>
+      </c>
       <c r="F163" s="209" t="s">
         <v>1287</v>
       </c>
@@ -15888,7 +16289,7 @@
         <v>1018</v>
       </c>
       <c r="I163" s="209" t="s">
-        <v>1577</v>
+        <v>1550</v>
       </c>
       <c r="J163" s="208" t="s">
         <v>4</v>
@@ -15904,7 +16305,7 @@
       </c>
       <c r="N163" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>17:59</v>
       </c>
       <c r="O163" s="151" t="str">
         <f t="shared" si="7"/>
@@ -15922,13 +16323,11 @@
       <c r="B164" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C164" s="209" t="s">
-        <v>1524</v>
-      </c>
+      <c r="C164" s="209"/>
       <c r="D164" s="208"/>
       <c r="E164" s="208"/>
       <c r="F164" s="209" t="s">
-        <v>1578</v>
+        <v>1551</v>
       </c>
       <c r="G164" s="259" t="s">
         <v>17</v>
@@ -15937,7 +16336,7 @@
         <v>1017</v>
       </c>
       <c r="I164" s="209" t="s">
-        <v>1579</v>
+        <v>1552</v>
       </c>
       <c r="J164" s="208" t="s">
         <v>4</v>
@@ -15953,7 +16352,7 @@
       </c>
       <c r="N164" s="151" t="str">
         <f t="shared" si="6"/>
-        <v>18:01</v>
+        <v/>
       </c>
       <c r="O164" s="151" t="str">
         <f t="shared" si="7"/>
@@ -16010,7 +16409,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="209" t="s">
-        <v>1580</v>
+        <v>1553</v>
       </c>
       <c r="G166" s="259" t="s">
         <v>27</v>
@@ -16019,7 +16418,7 @@
         <v>1396</v>
       </c>
       <c r="I166" s="209" t="s">
-        <v>1581</v>
+        <v>1554</v>
       </c>
       <c r="J166" s="208" t="s">
         <v>4</v>
@@ -16053,11 +16452,17 @@
       <c r="B167" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C167" s="209"/>
-      <c r="D167" s="208"/>
-      <c r="E167" s="208"/>
+      <c r="C167" s="209" t="s">
+        <v>1592</v>
+      </c>
+      <c r="D167" s="208" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E167" s="208" t="s">
+        <v>1621</v>
+      </c>
       <c r="F167" s="209" t="s">
-        <v>1582</v>
+        <v>1555</v>
       </c>
       <c r="G167" s="259" t="s">
         <v>17</v>
@@ -16082,7 +16487,7 @@
       </c>
       <c r="N167" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>21:55</v>
       </c>
       <c r="O167" s="151" t="str">
         <f t="shared" si="7"/>
@@ -16139,7 +16544,7 @@
       <c r="D169" s="208"/>
       <c r="E169" s="208"/>
       <c r="F169" s="209" t="s">
-        <v>1583</v>
+        <v>1556</v>
       </c>
       <c r="G169" s="259" t="s">
         <v>27</v>
@@ -16178,19 +16583,24 @@
   </sheetData>
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12">
-    <cfRule type="containsText" dxfId="35" priority="8" operator="containsText" text="'">
+  <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12 D70">
+    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E1048576 H1:H1048576 K1:K1048576">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="定期メンテナンス中">
+  <conditionalFormatting sqref="E1:E2 H1:H1048576 K1:K44 E4:E150 E152:E1048576 K46:K1048576">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J11 D1:D1048576 G1:G1048576 J13:J1048576">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="例行維護中">
+  <conditionalFormatting sqref="J1:J11 D1:D69 G1:G1048576 J13:J1048576 D71:D1048576 E151 K45">
+    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23753,17 +24163,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23891,7 +24301,7 @@
         <v>1360</v>
       </c>
       <c r="E3" s="149" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="F3" s="150" t="s">
         <v>269</v>
@@ -24026,7 +24436,7 @@
         <v>1361</v>
       </c>
       <c r="E6" s="149" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="F6" s="150" t="s">
         <v>1278</v>
@@ -24120,13 +24530,13 @@
         <v>60</v>
       </c>
       <c r="C8" s="287" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="D8" s="149" t="s">
         <v>456</v>
       </c>
       <c r="E8" s="149" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F8" s="153"/>
       <c r="G8" s="149"/>
@@ -24164,7 +24574,7 @@
       <c r="D9" s="149"/>
       <c r="E9" s="149"/>
       <c r="F9" s="287" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="G9" s="149" t="s">
         <v>17</v>
@@ -24261,7 +24671,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1415</v>
+        <v>1610</v>
       </c>
       <c r="F11" s="150"/>
       <c r="G11" s="149"/>
@@ -24431,7 +24841,7 @@
         <v>396</v>
       </c>
       <c r="E15" s="149" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="F15" s="150" t="s">
         <v>809</v>
@@ -24610,10 +25020,10 @@
         <v>1372</v>
       </c>
       <c r="D19" s="149" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F19" s="150" t="s">
         <v>216</v>
@@ -24748,7 +25158,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1406</v>
+        <v>1603</v>
       </c>
       <c r="F22" s="150" t="s">
         <v>1288</v>
@@ -24924,7 +25334,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="158" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="F26" s="159" t="s">
         <v>141</v>
@@ -25106,7 +25516,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1408</v>
+        <v>1608</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>1195</v>
@@ -25235,13 +25645,13 @@
         <v>58</v>
       </c>
       <c r="C33" s="288" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="D33" s="160" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="E33" s="160" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="F33" s="162" t="s">
         <v>887</v>
@@ -25326,7 +25736,7 @@
       <c r="D35" s="160"/>
       <c r="E35" s="160"/>
       <c r="F35" s="289" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="G35" s="160" t="s">
         <v>11</v>
@@ -25335,7 +25745,7 @@
         <v>1016</v>
       </c>
       <c r="I35" s="294" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="J35" s="160" t="s">
         <v>13</v>
@@ -25376,7 +25786,7 @@
         <v>986</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F36" s="162" t="s">
         <v>1375</v>
@@ -25523,7 +25933,7 @@
         <v>1017</v>
       </c>
       <c r="I39" s="289" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="J39" s="160" t="s">
         <v>4</v>
@@ -25646,7 +26056,7 @@
         <v>1365</v>
       </c>
       <c r="E42" s="160" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="F42" s="162" t="s">
         <v>1299</v>
@@ -25728,13 +26138,13 @@
         <v>58</v>
       </c>
       <c r="C44" s="289" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="D44" s="160" t="s">
         <v>397</v>
       </c>
       <c r="E44" s="160" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="F44" s="161">
         <v>0.75277777777777777</v>
@@ -25916,7 +26326,7 @@
         <v>359</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F48" s="162" t="s">
         <v>1381</v>
@@ -26098,13 +26508,13 @@
         <v>55</v>
       </c>
       <c r="C52" s="173" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="D52" s="290" t="s">
         <v>986</v>
       </c>
       <c r="E52" s="171" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F52" s="173"/>
       <c r="G52" s="171"/>
@@ -26189,7 +26599,7 @@
       <c r="D54" s="171"/>
       <c r="E54" s="171"/>
       <c r="F54" s="290" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="G54" s="171" t="s">
         <v>17</v>
@@ -26198,7 +26608,7 @@
         <v>1017</v>
       </c>
       <c r="I54" s="290" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="J54" s="171" t="s">
         <v>4</v>
@@ -26427,13 +26837,13 @@
         <v>55</v>
       </c>
       <c r="C59" s="172" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="D59" s="171" t="s">
         <v>335</v>
       </c>
       <c r="E59" s="295" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F59" s="171" t="s">
         <v>79</v>
@@ -26576,7 +26986,7 @@
         <v>1367</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F62" s="172" t="s">
         <v>1306</v>
@@ -26893,7 +27303,7 @@
         <v>904</v>
       </c>
       <c r="E69" s="171" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="F69" s="172" t="s">
         <v>1312</v>
@@ -27075,7 +27485,7 @@
         <v>1365</v>
       </c>
       <c r="E73" s="175" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="F73" s="176"/>
       <c r="G73" s="175"/>
@@ -27160,7 +27570,7 @@
       <c r="D75" s="180"/>
       <c r="E75" s="180"/>
       <c r="F75" s="181" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="G75" s="180" t="s">
         <v>343</v>
@@ -27210,7 +27620,7 @@
         <v>48</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F76" s="181"/>
       <c r="G76" s="180"/>
@@ -27251,7 +27661,7 @@
       <c r="G77" s="180"/>
       <c r="H77" s="180"/>
       <c r="I77" s="291" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="J77" s="180" t="s">
         <v>4</v>
@@ -27289,7 +27699,7 @@
       <c r="D78" s="180"/>
       <c r="E78" s="180"/>
       <c r="F78" s="181" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="G78" s="180" t="s">
         <v>11</v>
@@ -27298,7 +27708,7 @@
         <v>1016</v>
       </c>
       <c r="I78" s="291" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="J78" s="180" t="s">
         <v>13</v>
@@ -27336,7 +27746,7 @@
       <c r="D79" s="180"/>
       <c r="E79" s="180"/>
       <c r="F79" s="181" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="G79" s="180" t="s">
         <v>17</v>
@@ -27374,19 +27784,19 @@
         <v>52</v>
       </c>
       <c r="C80" s="291" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="D80" s="180" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="E80" s="180" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="180"/>
       <c r="H80" s="180"/>
       <c r="I80" s="182" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="J80" s="180" t="s">
         <v>13</v>
@@ -27424,7 +27834,7 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="G81" s="180" t="s">
         <v>17</v>
@@ -27433,7 +27843,7 @@
         <v>1017</v>
       </c>
       <c r="I81" s="181" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
       <c r="J81" s="180" t="s">
         <v>4</v>
@@ -27468,16 +27878,16 @@
         <v>52</v>
       </c>
       <c r="C82" s="181" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="D82" s="180" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="E82" s="180" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="F82" s="181" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="G82" s="180" t="s">
         <v>17</v>
@@ -27559,7 +27969,7 @@
       <c r="D84" s="180"/>
       <c r="E84" s="180"/>
       <c r="F84" s="181" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="G84" s="180" t="s">
         <v>0</v>
@@ -27568,7 +27978,7 @@
         <v>1018</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="J84" s="180" t="s">
         <v>4</v>
@@ -27603,16 +28013,16 @@
         <v>52</v>
       </c>
       <c r="C85" s="181" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="D85" s="180" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="E85" s="180" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="F85" s="181" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="G85" s="180" t="s">
         <v>17</v>
@@ -27697,7 +28107,7 @@
       <c r="G87" s="180"/>
       <c r="H87" s="180"/>
       <c r="I87" s="181" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -27738,10 +28148,10 @@
         <v>454</v>
       </c>
       <c r="E88" s="180" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="F88" s="291" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="G88" s="180" t="s">
         <v>0</v>
@@ -27785,7 +28195,7 @@
       <c r="G89" s="180"/>
       <c r="H89" s="180"/>
       <c r="I89" s="276" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="J89" s="180" t="s">
         <v>4</v>
@@ -27917,10 +28327,10 @@
         <v>350</v>
       </c>
       <c r="D92" s="180" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
       <c r="E92" s="180" t="s">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="180"/>
@@ -28049,13 +28459,13 @@
         <v>52</v>
       </c>
       <c r="C95" s="181" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="D95" s="180" t="s">
         <v>1088</v>
       </c>
       <c r="E95" s="180" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="F95" s="181"/>
       <c r="G95" s="180"/>
@@ -28181,10 +28591,10 @@
         <v>1323</v>
       </c>
       <c r="D98" s="187" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="E98" s="187" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F98" s="188"/>
       <c r="G98" s="187"/>
@@ -28322,10 +28732,10 @@
         <v>284</v>
       </c>
       <c r="D101" s="189" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E101" s="189" t="s">
         <v>1420</v>
-      </c>
-      <c r="E101" s="189" t="s">
-        <v>1423</v>
       </c>
       <c r="F101" s="190"/>
       <c r="G101" s="189"/>
@@ -28451,7 +28861,7 @@
       <c r="D104" s="189"/>
       <c r="E104" s="189"/>
       <c r="F104" s="190" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="G104" s="189" t="s">
         <v>0</v>
@@ -28501,7 +28911,7 @@
         <v>1367</v>
       </c>
       <c r="E105" s="189" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F105" s="190"/>
       <c r="G105" s="189"/>
@@ -28677,7 +29087,7 @@
         <v>1367</v>
       </c>
       <c r="E109" s="189" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F109" s="190" t="s">
         <v>919</v>
@@ -28812,7 +29222,7 @@
         <v>1361</v>
       </c>
       <c r="E112" s="189" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="F112" s="190" t="s">
         <v>838</v>
@@ -28988,7 +29398,7 @@
         <v>1139</v>
       </c>
       <c r="E116" s="189" t="s">
-        <v>1426</v>
+        <v>1423</v>
       </c>
       <c r="F116" s="190" t="s">
         <v>1331</v>
@@ -29123,7 +29533,7 @@
         <v>48</v>
       </c>
       <c r="E119" s="189" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F119" s="190" t="s">
         <v>1333</v>
@@ -29255,10 +29665,10 @@
         <v>1336</v>
       </c>
       <c r="D122" s="196" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="E122" s="196" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="F122" s="197" t="s">
         <v>141</v>
@@ -29440,7 +29850,7 @@
         <v>1363</v>
       </c>
       <c r="E126" s="198" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="F126" s="199" t="s">
         <v>886</v>
@@ -29499,7 +29909,7 @@
         <v>1018</v>
       </c>
       <c r="I127" s="199" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="J127" s="198" t="s">
         <v>13</v>
@@ -29587,7 +29997,7 @@
         <v>1017</v>
       </c>
       <c r="I129" s="200" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="J129" s="198" t="s">
         <v>13</v>
@@ -29710,7 +30120,7 @@
         <v>1369</v>
       </c>
       <c r="E132" s="198" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="F132" s="199" t="s">
         <v>1340</v>
@@ -29845,7 +30255,7 @@
         <v>1370</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>1341</v>
@@ -30074,7 +30484,7 @@
         <v>42</v>
       </c>
       <c r="E140" s="198" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="F140" s="199"/>
       <c r="G140" s="198"/>
@@ -30426,7 +30836,7 @@
         <v>48</v>
       </c>
       <c r="E148" s="208" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="F148" s="209" t="s">
         <v>1349</v>
@@ -30602,13 +31012,13 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="D152" s="208" t="s">
         <v>45</v>
       </c>
       <c r="E152" s="208" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="F152" s="209" t="s">
         <v>941</v>
@@ -30743,7 +31153,7 @@
         <v>1365</v>
       </c>
       <c r="E155" s="208" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="F155" s="209" t="s">
         <v>1352</v>
@@ -30878,7 +31288,7 @@
         <v>1363</v>
       </c>
       <c r="E158" s="208" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="F158" s="209" t="s">
         <v>1354</v>
@@ -31013,7 +31423,7 @@
         <v>1370</v>
       </c>
       <c r="E161" s="208" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="F161" s="209" t="s">
         <v>665</v>
@@ -31189,7 +31599,7 @@
         <v>1371</v>
       </c>
       <c r="E165" s="208" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
       <c r="F165" s="209"/>
       <c r="G165" s="208"/>
@@ -31233,7 +31643,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="292" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="G166" s="208" t="s">
         <v>17</v>
@@ -31324,7 +31734,7 @@
         <v>45</v>
       </c>
       <c r="E168" s="208" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
       <c r="F168" s="209"/>
       <c r="G168" s="208"/>
@@ -31408,42 +31818,42 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="28" priority="8" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37382,27 +37792,27 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="23" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="25" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43418,17 +43828,17 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48085,7 +48495,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="55" t="s">
-        <v>1521</v>
+        <v>1504</v>
       </c>
       <c r="G132" s="57"/>
       <c r="H132" s="55"/>
@@ -49418,12 +49828,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55314,12 +55724,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61307,12 +61717,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67391,22 +67801,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73373,22 +73783,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13954829-02E7-476A-8DA0-0BFEF76A566D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D02ABEC-5518-4906-B8E1-BBE56A99D854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22560" yWindow="16305" windowWidth="22275" windowHeight="15360" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28830" yWindow="16320" windowWidth="11220" windowHeight="13110" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11819" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11826" uniqueCount="1653">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6775,10 +6775,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>黒影林 / ？？？</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>敵萬夫</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -6884,9 +6880,6 @@
     <t>14:30</t>
   </si>
   <si>
-    <t>17:26</t>
-  </si>
-  <si>
     <t>19:20</t>
   </si>
   <si>
@@ -7021,29 +7014,6 @@
   </si>
   <si>
     <t>オオウスバ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>06-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>09</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Microsoft JhengHei UI"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 定期メンテナンス中</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -7237,9 +7207,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>戒狼村 / 渡門旅館</t>
-  </si>
-  <si>
     <t>渡門旅館 / 北方(北方警戒所)</t>
   </si>
   <si>
@@ -7293,6 +7260,81 @@
   </si>
   <si>
     <t>05:15</t>
+  </si>
+  <si>
+    <t>戒狼村 / 渡門旅館</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>黒影林 /</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 戒狼村</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑森林 / 灰狼村</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>23:27</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>10:03</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>17:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>05:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>00:48</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>豬豬農場 / 染坊</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>海岸旅館 / 染色工房</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20:21</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>19:25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>19:36</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>23:49</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>19:23</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>06:51</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -8456,28 +8498,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="37">
     <dxf>
       <fill>
         <patternFill>
@@ -8706,6 +8727,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9012,23 +9047,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}">
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.875" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.8984375" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="212" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.375" style="212" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="5.875" style="151" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.25" style="151"/>
+    <col min="13" max="13" width="3.3984375" style="212" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.19921875" style="151"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="147" customFormat="1" ht="18" customHeight="1">
@@ -9306,7 +9341,7 @@
         <v>1413</v>
       </c>
       <c r="F7" s="150" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G7" s="213" t="s">
         <v>11</v>
@@ -9315,7 +9350,7 @@
         <v>1016</v>
       </c>
       <c r="I7" s="150" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="J7" s="149" t="s">
         <v>4</v>
@@ -9438,7 +9473,7 @@
         <v>1144</v>
       </c>
       <c r="E10" s="149" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="F10" s="150" t="s">
         <v>274</v>
@@ -9523,7 +9558,7 @@
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
       <c r="F12" s="150" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G12" s="213" t="s">
         <v>0</v>
@@ -9573,13 +9608,13 @@
         <v>34</v>
       </c>
       <c r="E13" s="149" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="213"/>
       <c r="H13" s="149"/>
       <c r="I13" s="148" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="J13" s="149" t="s">
         <v>4</v>
@@ -9617,7 +9652,7 @@
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
       <c r="F14" s="150" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="G14" s="213" t="s">
         <v>27</v>
@@ -9658,7 +9693,7 @@
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
       <c r="F15" s="150" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G15" s="213" t="s">
         <v>11</v>
@@ -9708,13 +9743,13 @@
         <v>899</v>
       </c>
       <c r="E16" s="149" t="s">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="F16" s="150"/>
       <c r="G16" s="213"/>
       <c r="H16" s="149"/>
       <c r="I16" s="148" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J16" s="149" t="s">
         <v>13</v>
@@ -9793,7 +9828,7 @@
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
       <c r="F18" s="150" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="G18" s="213" t="s">
         <v>11</v>
@@ -9843,7 +9878,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="F19" s="150"/>
       <c r="G19" s="213"/>
@@ -9887,7 +9922,7 @@
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
       <c r="F20" s="150" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G20" s="213" t="s">
         <v>17</v>
@@ -9928,7 +9963,7 @@
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
       <c r="F21" s="150" t="s">
-        <v>1124</v>
+        <v>1649</v>
       </c>
       <c r="G21" s="213" t="s">
         <v>27</v>
@@ -9937,7 +9972,7 @@
         <v>1396</v>
       </c>
       <c r="I21" s="148" t="s">
-        <v>596</v>
+        <v>1648</v>
       </c>
       <c r="J21" s="149" t="s">
         <v>13</v>
@@ -9957,11 +9992,11 @@
       </c>
       <c r="O21" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>19:33</v>
+        <v>19:36</v>
       </c>
       <c r="P21" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>19:26</v>
+        <v>19:25</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="18" customHeight="1">
@@ -9978,7 +10013,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F22" s="150"/>
       <c r="G22" s="213"/>
@@ -10072,7 +10107,7 @@
         <v>1396</v>
       </c>
       <c r="I24" s="148" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="J24" s="149" t="s">
         <v>4</v>
@@ -10147,9 +10182,15 @@
       <c r="B26" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="158"/>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
+      <c r="C26" s="293" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D26" s="158" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E26" s="158" t="s">
+        <v>1646</v>
+      </c>
       <c r="F26" s="159" t="s">
         <v>141</v>
       </c>
@@ -10170,7 +10211,7 @@
       </c>
       <c r="N26" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>00:48</v>
       </c>
       <c r="O26" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10283,7 +10324,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="160" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="F29" s="162" t="s">
         <v>259</v>
@@ -10327,7 +10368,7 @@
       <c r="D30" s="160"/>
       <c r="E30" s="160"/>
       <c r="F30" s="162" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G30" s="221" t="s">
         <v>27</v>
@@ -10335,9 +10376,15 @@
       <c r="H30" s="160" t="s">
         <v>1396</v>
       </c>
-      <c r="I30" s="162"/>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
+      <c r="I30" s="289" t="s">
+        <v>369</v>
+      </c>
+      <c r="J30" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="K30" s="160" t="s">
+        <v>1015</v>
+      </c>
       <c r="L30" s="157" t="s">
         <v>32</v>
       </c>
@@ -10354,7 +10401,7 @@
       </c>
       <c r="P30" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:04</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="18" customHeight="1">
@@ -10453,10 +10500,10 @@
         <v>24</v>
       </c>
       <c r="E33" s="160" t="s">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="F33" s="162" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G33" s="221" t="s">
         <v>17</v>
@@ -10588,10 +10635,10 @@
         <v>1364</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="F36" s="162" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G36" s="221" t="s">
         <v>17</v>
@@ -10603,7 +10650,7 @@
         <v>833</v>
       </c>
       <c r="J36" s="160" t="s">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="K36" s="160" t="s">
         <v>1015</v>
@@ -10653,7 +10700,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="160" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="L37" s="157" t="s">
         <v>23</v>
@@ -10717,13 +10764,13 @@
         <v>58</v>
       </c>
       <c r="C39" s="162" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="D39" s="160" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="E39" s="160" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F39" s="162" t="s">
         <v>991</v>
@@ -10779,10 +10826,10 @@
         <v>17</v>
       </c>
       <c r="H40" s="160" t="s">
-        <v>1637</v>
+        <v>1633</v>
       </c>
       <c r="I40" s="162" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="J40" s="160" t="s">
         <v>13</v>
@@ -10823,7 +10870,7 @@
       <c r="G41" s="221"/>
       <c r="H41" s="160"/>
       <c r="I41" s="162" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="J41" s="160" t="s">
         <v>4</v>
@@ -10899,7 +10946,7 @@
         <v>58</v>
       </c>
       <c r="C43" s="162" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="D43" s="160" t="s">
         <v>48</v>
@@ -10995,9 +11042,15 @@
       <c r="C45" s="162"/>
       <c r="D45" s="160"/>
       <c r="E45" s="160"/>
-      <c r="F45" s="162"/>
-      <c r="G45" s="221"/>
-      <c r="H45" s="160"/>
+      <c r="F45" s="289" t="s">
+        <v>1651</v>
+      </c>
+      <c r="G45" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="160" t="s">
+        <v>1018</v>
+      </c>
       <c r="I45" s="162"/>
       <c r="J45" s="160"/>
       <c r="K45" s="160"/>
@@ -11013,7 +11066,7 @@
       </c>
       <c r="O45" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>19:23</v>
       </c>
       <c r="P45" s="151" t="str">
         <f t="shared" si="2"/>
@@ -11075,7 +11128,7 @@
         <v>58</v>
       </c>
       <c r="C47" s="289" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="D47" s="160"/>
       <c r="E47" s="160" t="s">
@@ -11117,7 +11170,7 @@
       <c r="D48" s="160"/>
       <c r="E48" s="160"/>
       <c r="F48" s="162" t="s">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="G48" s="221" t="s">
         <v>27</v>
@@ -11126,7 +11179,7 @@
         <v>1396</v>
       </c>
       <c r="I48" s="164" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="J48" s="160" t="s">
         <v>4</v>
@@ -11164,7 +11217,7 @@
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
       <c r="F49" s="167" t="s">
-        <v>1533</v>
+        <v>1650</v>
       </c>
       <c r="G49" s="225" t="s">
         <v>27</v>
@@ -11176,10 +11229,10 @@
         <v>862</v>
       </c>
       <c r="J49" s="166" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="K49" s="166" t="s">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="L49" s="165" t="s">
         <v>3</v>
@@ -11193,7 +11246,7 @@
       </c>
       <c r="O49" s="151" t="str">
         <f t="shared" si="1"/>
-        <v>23:55</v>
+        <v>23:49</v>
       </c>
       <c r="P49" s="151" t="str">
         <f t="shared" si="2"/>
@@ -11249,13 +11302,13 @@
         <v>55</v>
       </c>
       <c r="C51" s="172" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="D51" s="171" t="s">
         <v>40</v>
       </c>
       <c r="E51" s="171" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="F51" s="172"/>
       <c r="G51" s="229"/>
@@ -11346,7 +11399,7 @@
       <c r="D53" s="171"/>
       <c r="E53" s="171"/>
       <c r="F53" s="172" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="G53" s="229" t="s">
         <v>11</v>
@@ -11425,16 +11478,16 @@
         <v>55</v>
       </c>
       <c r="C55" s="172" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="D55" s="171" t="s">
         <v>1144</v>
       </c>
       <c r="E55" s="171" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="F55" s="172" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="G55" s="229" t="s">
         <v>27</v>
@@ -11481,29 +11534,23 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1575</v>
-      </c>
-      <c r="E56" s="171" t="s">
-        <v>1573</v>
-      </c>
+        <v>1572</v>
+      </c>
+      <c r="E56" s="171"/>
       <c r="F56" s="172" t="s">
         <v>77</v>
       </c>
       <c r="G56" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H56" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="H56" s="171"/>
       <c r="I56" s="171" t="s">
         <v>77</v>
       </c>
       <c r="J56" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K56" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="K56" s="171"/>
       <c r="L56" s="168" t="s">
         <v>30</v>
       </c>
@@ -11536,27 +11583,21 @@
       <c r="D57" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="E57" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="E57" s="171"/>
       <c r="F57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="G57" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H57" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="H57" s="171"/>
       <c r="I57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="J57" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K57" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="K57" s="171"/>
       <c r="L57" s="168" t="s">
         <v>29</v>
       </c>
@@ -11589,27 +11630,21 @@
       <c r="D58" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="E58" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="E58" s="171"/>
       <c r="F58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="G58" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H58" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="H58" s="171"/>
       <c r="I58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="J58" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K58" s="171" t="s">
-        <v>1096</v>
-      </c>
+      <c r="K58" s="171"/>
       <c r="L58" s="168" t="s">
         <v>28</v>
       </c>
@@ -11746,7 +11781,7 @@
         <v>1477</v>
       </c>
       <c r="J61" s="171" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="K61" s="171" t="s">
         <v>1402</v>
@@ -11778,13 +11813,13 @@
         <v>55</v>
       </c>
       <c r="C62" s="172" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="D62" s="171" t="s">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="F62" s="172" t="s">
         <v>1482</v>
@@ -11793,7 +11828,7 @@
         <v>1498</v>
       </c>
       <c r="H62" s="171" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="I62" s="172"/>
       <c r="J62" s="171"/>
@@ -11834,7 +11869,7 @@
         <v>1478</v>
       </c>
       <c r="J63" s="171" t="s">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="K63" s="171" t="s">
         <v>1403</v>
@@ -11875,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="171" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="I64" s="172" t="s">
         <v>1479</v>
@@ -11919,7 +11954,7 @@
         <v>695</v>
       </c>
       <c r="G65" s="229" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H65" s="171" t="s">
         <v>1018</v>
@@ -11960,7 +11995,7 @@
         <v>63</v>
       </c>
       <c r="E66" s="171" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="F66" s="172" t="s">
         <v>1485</v>
@@ -12136,10 +12171,10 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>202</v>
+        <v>1647</v>
       </c>
       <c r="D70" s="172" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="E70" s="171" t="s">
         <v>71</v>
@@ -12164,7 +12199,7 @@
       </c>
       <c r="N70" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>20:20</v>
+        <v>20:21</v>
       </c>
       <c r="O70" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12274,7 +12309,7 @@
         <v>27</v>
       </c>
       <c r="H73" s="175" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="I73" s="176" t="s">
         <v>150</v>
@@ -12315,10 +12350,10 @@
         <v>1116</v>
       </c>
       <c r="D74" s="178" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="E74" s="178" t="s">
-        <v>1633</v>
+        <v>1629</v>
       </c>
       <c r="F74" s="179" t="s">
         <v>141</v>
@@ -12365,7 +12400,7 @@
         <v>127</v>
       </c>
       <c r="G75" s="237" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="H75" s="180" t="s">
         <v>1396</v>
@@ -12374,7 +12409,7 @@
         <v>600</v>
       </c>
       <c r="J75" s="180" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="K75" s="180" t="s">
         <v>1403</v>
@@ -12406,13 +12441,13 @@
         <v>52</v>
       </c>
       <c r="C76" s="181" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="D76" s="180" t="s">
         <v>1371</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="F76" s="181" t="s">
         <v>783</v>
@@ -12588,13 +12623,13 @@
         <v>52</v>
       </c>
       <c r="C80" s="181" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="D80" s="180" t="s">
         <v>19</v>
       </c>
       <c r="E80" s="180" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="237"/>
@@ -12635,10 +12670,10 @@
         <v>1492</v>
       </c>
       <c r="G81" s="237" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="H81" s="180" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="I81" s="181" t="s">
         <v>1493</v>
@@ -12764,25 +12799,25 @@
         <v>64</v>
       </c>
       <c r="E84" s="180" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="F84" s="181" t="s">
         <v>1494</v>
       </c>
       <c r="G84" s="237" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="H84" s="180" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>651</v>
+        <v>1641</v>
       </c>
       <c r="J84" s="180" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="K84" s="180" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
@@ -12800,7 +12835,7 @@
       </c>
       <c r="P84" s="151" t="str">
         <f t="shared" si="5"/>
-        <v>10:05</v>
+        <v>10:03</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1">
@@ -12823,7 +12858,7 @@
         <v>4</v>
       </c>
       <c r="K85" s="180" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="L85" s="177" t="s">
         <v>23</v>
@@ -12858,10 +12893,10 @@
         <v>1495</v>
       </c>
       <c r="G86" s="237" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="H86" s="180" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="I86" s="182"/>
       <c r="J86" s="180"/>
@@ -12896,7 +12931,7 @@
       <c r="D87" s="180"/>
       <c r="E87" s="180"/>
       <c r="F87" s="181" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G87" s="237" t="s">
         <v>0</v>
@@ -12905,7 +12940,7 @@
         <v>1018</v>
       </c>
       <c r="I87" s="181" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -12946,7 +12981,7 @@
         <v>1143</v>
       </c>
       <c r="E88" s="180" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F88" s="181" t="s">
         <v>1342</v>
@@ -13031,7 +13066,7 @@
       <c r="D90" s="180"/>
       <c r="E90" s="180"/>
       <c r="F90" s="181" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G90" s="237" t="s">
         <v>17</v>
@@ -13078,7 +13113,7 @@
       <c r="D91" s="180"/>
       <c r="E91" s="180"/>
       <c r="F91" s="181" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="G91" s="237" t="s">
         <v>27</v>
@@ -13087,7 +13122,7 @@
         <v>1396</v>
       </c>
       <c r="I91" s="181" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="J91" s="180" t="s">
         <v>4</v>
@@ -13122,13 +13157,13 @@
         <v>52</v>
       </c>
       <c r="C92" s="181" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="D92" s="180" t="s">
         <v>34</v>
       </c>
       <c r="E92" s="180" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="237"/>
@@ -13175,7 +13210,7 @@
         <v>1396</v>
       </c>
       <c r="I93" s="181" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="J93" s="180" t="s">
         <v>13</v>
@@ -13213,7 +13248,7 @@
       <c r="D94" s="180"/>
       <c r="E94" s="180"/>
       <c r="F94" s="181" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="G94" s="237" t="s">
         <v>11</v>
@@ -13222,7 +13257,7 @@
         <v>1016</v>
       </c>
       <c r="I94" s="181" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="J94" s="180" t="s">
         <v>13</v>
@@ -13298,10 +13333,10 @@
         <v>39</v>
       </c>
       <c r="E96" s="180" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="F96" s="181" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="G96" s="237" t="s">
         <v>11</v>
@@ -13430,7 +13465,7 @@
         <v>234</v>
       </c>
       <c r="D99" s="187" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="E99" s="189" t="s">
         <v>1412</v>
@@ -13615,7 +13650,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="189" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="F103" s="190" t="s">
         <v>616</v>
@@ -13627,7 +13662,7 @@
         <v>1016</v>
       </c>
       <c r="I103" s="190" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="J103" s="189" t="s">
         <v>13</v>
@@ -13756,7 +13791,7 @@
         <v>1016</v>
       </c>
       <c r="I106" s="190" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="J106" s="189" t="s">
         <v>13</v>
@@ -13826,7 +13861,7 @@
         <v>44</v>
       </c>
       <c r="C108" s="190" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="D108" s="189" t="s">
         <v>1143</v>
@@ -13891,7 +13926,7 @@
         <v>1016</v>
       </c>
       <c r="I109" s="190" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="J109" s="189" t="s">
         <v>4</v>
@@ -14008,7 +14043,7 @@
         <v>44</v>
       </c>
       <c r="C112" s="190" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D112" s="189" t="s">
         <v>903</v>
@@ -14017,7 +14052,7 @@
         <v>1409</v>
       </c>
       <c r="F112" s="190" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="G112" s="244" t="s">
         <v>27</v>
@@ -14026,7 +14061,7 @@
         <v>1396</v>
       </c>
       <c r="I112" s="190" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="J112" s="189" t="s">
         <v>4</v>
@@ -14146,10 +14181,10 @@
         <v>788</v>
       </c>
       <c r="D115" s="189" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="E115" s="189" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="F115" s="190" t="s">
         <v>1036</v>
@@ -14161,7 +14196,7 @@
         <v>1018</v>
       </c>
       <c r="I115" s="190" t="s">
-        <v>1530</v>
+        <v>1642</v>
       </c>
       <c r="J115" s="189" t="s">
         <v>13</v>
@@ -14185,7 +14220,7 @@
       </c>
       <c r="P115" s="151" t="str">
         <f t="shared" si="5"/>
-        <v>17:26</v>
+        <v>17:25</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="18" customHeight="1">
@@ -14240,7 +14275,7 @@
       <c r="D117" s="189"/>
       <c r="E117" s="189"/>
       <c r="F117" s="190" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="G117" s="244" t="s">
         <v>27</v>
@@ -14369,13 +14404,13 @@
         <v>861</v>
       </c>
       <c r="D120" s="189" t="s">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="E120" s="189" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="F120" s="190" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="G120" s="244" t="s">
         <v>17</v>
@@ -14416,7 +14451,7 @@
       <c r="D121" s="193"/>
       <c r="E121" s="193"/>
       <c r="F121" s="194" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="G121" s="247" t="s">
         <v>0</v>
@@ -14425,7 +14460,7 @@
         <v>1018</v>
       </c>
       <c r="I121" s="194" t="s">
-        <v>884</v>
+        <v>1640</v>
       </c>
       <c r="J121" s="193" t="s">
         <v>13</v>
@@ -14449,7 +14484,7 @@
       </c>
       <c r="P121" s="151" t="str">
         <f t="shared" si="5"/>
-        <v>23:26</v>
+        <v>23:27</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1">
@@ -14504,10 +14539,10 @@
         <v>269</v>
       </c>
       <c r="D123" s="198" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="E123" s="198" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="F123" s="199" t="s">
         <v>623</v>
@@ -14830,7 +14865,7 @@
         <v>1018</v>
       </c>
       <c r="I130" s="199" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="J130" s="198" t="s">
         <v>13</v>
@@ -14865,13 +14900,13 @@
         <v>38</v>
       </c>
       <c r="C131" s="199" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="D131" s="198" t="s">
         <v>908</v>
       </c>
       <c r="E131" s="198" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="F131" s="199"/>
       <c r="G131" s="251"/>
@@ -14909,7 +14944,7 @@
       <c r="D132" s="198"/>
       <c r="E132" s="198"/>
       <c r="F132" s="199" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="G132" s="251" t="s">
         <v>27</v>
@@ -14918,7 +14953,7 @@
         <v>1396</v>
       </c>
       <c r="I132" s="200" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="J132" s="198" t="s">
         <v>4</v>
@@ -14965,7 +15000,7 @@
         <v>1018</v>
       </c>
       <c r="I133" s="199" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="J133" s="198" t="s">
         <v>13</v>
@@ -15038,10 +15073,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D135" s="198" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>607</v>
@@ -15182,7 +15217,7 @@
         <v>1016</v>
       </c>
       <c r="I138" s="199" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="J138" s="198" t="s">
         <v>4</v>
@@ -15217,16 +15252,16 @@
         <v>38</v>
       </c>
       <c r="C139" s="199" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="D139" s="198" t="s">
         <v>902</v>
       </c>
       <c r="E139" s="198" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="F139" s="199" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G139" s="251" t="s">
         <v>17</v>
@@ -15270,7 +15305,7 @@
       <c r="G140" s="251"/>
       <c r="H140" s="198"/>
       <c r="I140" s="199" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="J140" s="198" t="s">
         <v>4</v>
@@ -15352,13 +15387,13 @@
         <v>38</v>
       </c>
       <c r="C142" s="199" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="D142" s="198" t="s">
         <v>1143</v>
       </c>
       <c r="E142" s="198" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="F142" s="199" t="s">
         <v>1288</v>
@@ -15443,7 +15478,7 @@
       <c r="D144" s="198"/>
       <c r="E144" s="198"/>
       <c r="F144" s="199" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="G144" s="251" t="s">
         <v>0</v>
@@ -15490,7 +15525,7 @@
       <c r="D145" s="203"/>
       <c r="E145" s="203"/>
       <c r="F145" s="204" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="G145" s="255" t="s">
         <v>27</v>
@@ -15663,13 +15698,13 @@
         <v>2</v>
       </c>
       <c r="C149" s="209" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="D149" s="208" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="E149" s="208" t="s">
-        <v>1625</v>
+        <v>1637</v>
       </c>
       <c r="F149" s="209" t="s">
         <v>236</v>
@@ -15716,7 +15751,7 @@
       <c r="G150" s="259"/>
       <c r="H150" s="208"/>
       <c r="I150" s="209" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="J150" s="208" t="s">
         <v>13</v>
@@ -15753,9 +15788,15 @@
       <c r="C151" s="209"/>
       <c r="D151" s="208"/>
       <c r="E151" s="208"/>
-      <c r="F151" s="209"/>
-      <c r="G151" s="259"/>
-      <c r="H151" s="208"/>
+      <c r="F151" s="292" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G151" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="H151" s="208" t="s">
+        <v>1018</v>
+      </c>
       <c r="I151" s="209" t="s">
         <v>603</v>
       </c>
@@ -15777,7 +15818,7 @@
       </c>
       <c r="O151" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>05:25</v>
       </c>
       <c r="P151" s="151" t="str">
         <f t="shared" si="8"/>
@@ -15792,15 +15833,23 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1605</v>
-      </c>
-      <c r="D152" s="208"/>
+        <v>1602</v>
+      </c>
+      <c r="D152" s="208" t="s">
+        <v>1639</v>
+      </c>
       <c r="E152" s="208" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F152" s="209"/>
-      <c r="G152" s="259"/>
-      <c r="H152" s="208"/>
+        <v>1638</v>
+      </c>
+      <c r="F152" s="292" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G152" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="H152" s="208" t="s">
+        <v>1018</v>
+      </c>
       <c r="I152" s="209"/>
       <c r="J152" s="208"/>
       <c r="K152" s="208"/>
@@ -15816,7 +15865,7 @@
       </c>
       <c r="O152" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>06:51</v>
       </c>
       <c r="P152" s="151" t="str">
         <f t="shared" si="8"/>
@@ -15922,7 +15971,7 @@
       <c r="D155" s="208"/>
       <c r="E155" s="208"/>
       <c r="F155" s="209" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="G155" s="259" t="s">
         <v>0</v>
@@ -16004,13 +16053,13 @@
         <v>1282</v>
       </c>
       <c r="D157" s="208" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="E157" s="208" t="s">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="F157" s="209" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G157" s="259" t="s">
         <v>0</v>
@@ -16019,7 +16068,7 @@
         <v>1018</v>
       </c>
       <c r="I157" s="209" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="J157" s="208" t="s">
         <v>4</v>
@@ -16057,7 +16106,7 @@
       <c r="D158" s="208"/>
       <c r="E158" s="208"/>
       <c r="F158" s="209" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="G158" s="259" t="s">
         <v>17</v>
@@ -16095,7 +16144,7 @@
         <v>2</v>
       </c>
       <c r="C159" s="209" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="D159" s="208" t="s">
         <v>908</v>
@@ -16145,7 +16194,7 @@
       <c r="D160" s="208"/>
       <c r="E160" s="208"/>
       <c r="F160" s="209" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G160" s="259" t="s">
         <v>27</v>
@@ -16154,7 +16203,7 @@
         <v>1396</v>
       </c>
       <c r="I160" s="209" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="J160" s="208" t="s">
         <v>4</v>
@@ -16192,7 +16241,7 @@
       <c r="D161" s="208"/>
       <c r="E161" s="208"/>
       <c r="F161" s="209" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G161" s="259" t="s">
         <v>11</v>
@@ -16201,7 +16250,7 @@
         <v>1016</v>
       </c>
       <c r="I161" s="210" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="J161" s="208" t="s">
         <v>13</v>
@@ -16271,13 +16320,13 @@
         <v>2</v>
       </c>
       <c r="C163" s="209" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="D163" s="208" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="E163" s="208" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="F163" s="209" t="s">
         <v>1287</v>
@@ -16289,7 +16338,7 @@
         <v>1018</v>
       </c>
       <c r="I163" s="209" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="J163" s="208" t="s">
         <v>4</v>
@@ -16327,7 +16376,7 @@
       <c r="D164" s="208"/>
       <c r="E164" s="208"/>
       <c r="F164" s="209" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="G164" s="259" t="s">
         <v>17</v>
@@ -16336,7 +16385,7 @@
         <v>1017</v>
       </c>
       <c r="I164" s="209" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="J164" s="208" t="s">
         <v>4</v>
@@ -16409,7 +16458,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="209" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="G166" s="259" t="s">
         <v>27</v>
@@ -16418,7 +16467,7 @@
         <v>1396</v>
       </c>
       <c r="I166" s="209" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="J166" s="208" t="s">
         <v>4</v>
@@ -16453,16 +16502,16 @@
         <v>2</v>
       </c>
       <c r="C167" s="209" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="D167" s="208" t="s">
         <v>1369</v>
       </c>
       <c r="E167" s="208" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="F167" s="209" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="G167" s="259" t="s">
         <v>17</v>
@@ -16544,7 +16593,7 @@
       <c r="D169" s="208"/>
       <c r="E169" s="208"/>
       <c r="F169" s="209" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="G169" s="259" t="s">
         <v>27</v>
@@ -16584,23 +16633,23 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12 D70">
-    <cfRule type="containsText" dxfId="37" priority="9" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="36" priority="9" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E2 H1:H1048576 K1:K44 E4:E150 E152:E1048576 K46:K1048576">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="定期メンテナンス中">
+  <conditionalFormatting sqref="E1:E2 K1:K44 H1:H1048576 E4:E150 K46:K1048576 E152:E1048576">
+    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J11 D1:D69 G1:G1048576 J13:J1048576 D71:D1048576 E151 K45">
-    <cfRule type="containsText" dxfId="36" priority="3" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",E3)))</formula>
+  <conditionalFormatting sqref="J1:J11 D1:D69 G1:G1048576 J13:J1048576 K45 D71:D1048576 E151">
+    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16611,21 +16660,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}">
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="70" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="70" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="70" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="70" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="70" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="70" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.25" style="70" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.875" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.8984375" style="70" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.19921875" style="70" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.8984375" style="70" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="70" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="70"/>
-    <col min="14" max="16" width="5.875" style="70" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.8984375" style="70" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="70"/>
   </cols>
   <sheetData>
@@ -24163,17 +24212,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24184,25 +24233,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C332778B-0E89-49E0-A596-558D2A6CA2E7}">
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="144" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="144" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.625" style="144" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.625" style="144" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="144" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="144" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.59765625" style="144" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.59765625" style="144" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="144" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.19921875" style="144" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="144" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" style="144" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.625" style="143" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.375" style="143" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.625" style="143" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.25" style="143"/>
+    <col min="13" max="13" width="13.19921875" style="144" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.59765625" style="143" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.3984375" style="143" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.59765625" style="143" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.19921875" style="143"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="142" customFormat="1" ht="18" customHeight="1">
@@ -24671,7 +24720,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="F11" s="150"/>
       <c r="G11" s="149"/>
@@ -25158,7 +25207,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="F22" s="150" t="s">
         <v>1288</v>
@@ -25516,7 +25565,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>1195</v>
@@ -31818,42 +31867,42 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="35" priority="6" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="33" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="30" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="31" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="29" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="28" priority="8" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31865,21 +31914,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B7320E-C509-4E9C-A2AC-DAC652C78517}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" style="151" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.875" style="151" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.375" style="151" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -37792,27 +37841,27 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="26" priority="6" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="25" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37823,21 +37872,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" style="151" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.875" style="151" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.375" style="151" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.3984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -43828,17 +43877,17 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="21" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="20" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43850,20 +43899,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.375" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.375" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="67" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="67" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.375" style="67" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.875" style="67" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.3984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.8984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.3984375" style="67" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="67"/>
   </cols>
   <sheetData>
@@ -48495,7 +48544,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="55" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="G132" s="57"/>
       <c r="H132" s="55"/>
@@ -49828,12 +49877,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49845,19 +49894,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="212"/>
-    <col min="11" max="13" width="5.875" style="212" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.8984375" style="212" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="212"/>
   </cols>
   <sheetData>
@@ -55724,12 +55773,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -55740,19 +55789,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="212"/>
-    <col min="11" max="13" width="5.875" style="212" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.8984375" style="212" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="212"/>
   </cols>
   <sheetData>
@@ -61717,12 +61766,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="14" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -61733,19 +61782,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="151" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="151" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="151" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="151"/>
-    <col min="11" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -67801,22 +67850,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -67827,19 +67876,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="151" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="151" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.125" style="151" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="151"/>
-    <col min="11" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -73783,22 +73832,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D02ABEC-5518-4906-B8E1-BBE56A99D854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532B00E4-D9B0-4E6F-86B8-3E71DD4A6592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28830" yWindow="16320" windowWidth="11220" windowHeight="13110" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9660" yWindow="0" windowWidth="9780" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="8" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11826" uniqueCount="1653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11836" uniqueCount="1657">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -6710,10 +6710,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>16:16</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>11:05</t>
   </si>
   <si>
@@ -7334,6 +7330,56 @@
   </si>
   <si>
     <t>06:51</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>灰狼村 / 豬豬海岸</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>20:53</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>16:17</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>16:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>00:0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>0</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9047,23 +9093,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}">
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.8984375" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.875" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="212" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3984375" style="212" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.19921875" style="151"/>
+    <col min="13" max="13" width="3.375" style="212" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.25" style="151"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="147" customFormat="1" ht="18" customHeight="1">
@@ -9162,7 +9208,7 @@
         <v>1143</v>
       </c>
       <c r="E3" s="149" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F3" s="150" t="s">
         <v>885</v>
@@ -9341,7 +9387,7 @@
         <v>1413</v>
       </c>
       <c r="F7" s="150" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="G7" s="213" t="s">
         <v>11</v>
@@ -9350,7 +9396,7 @@
         <v>1016</v>
       </c>
       <c r="I7" s="150" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="J7" s="149" t="s">
         <v>4</v>
@@ -9473,7 +9519,7 @@
         <v>1144</v>
       </c>
       <c r="E10" s="149" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F10" s="150" t="s">
         <v>274</v>
@@ -9558,7 +9604,7 @@
       <c r="D12" s="149"/>
       <c r="E12" s="149"/>
       <c r="F12" s="150" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G12" s="213" t="s">
         <v>0</v>
@@ -9608,13 +9654,13 @@
         <v>34</v>
       </c>
       <c r="E13" s="149" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="213"/>
       <c r="H13" s="149"/>
       <c r="I13" s="148" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="J13" s="149" t="s">
         <v>4</v>
@@ -9652,7 +9698,7 @@
       <c r="D14" s="149"/>
       <c r="E14" s="149"/>
       <c r="F14" s="150" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="G14" s="213" t="s">
         <v>27</v>
@@ -9693,7 +9739,7 @@
       <c r="D15" s="149"/>
       <c r="E15" s="149"/>
       <c r="F15" s="150" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="G15" s="213" t="s">
         <v>11</v>
@@ -9743,13 +9789,13 @@
         <v>899</v>
       </c>
       <c r="E16" s="149" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="F16" s="150"/>
       <c r="G16" s="213"/>
       <c r="H16" s="149"/>
       <c r="I16" s="148" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="J16" s="149" t="s">
         <v>13</v>
@@ -9828,7 +9874,7 @@
       <c r="D18" s="149"/>
       <c r="E18" s="149"/>
       <c r="F18" s="150" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="G18" s="213" t="s">
         <v>11</v>
@@ -9878,7 +9924,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="F19" s="150"/>
       <c r="G19" s="213"/>
@@ -9922,7 +9968,7 @@
       <c r="D20" s="149"/>
       <c r="E20" s="149"/>
       <c r="F20" s="150" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="G20" s="213" t="s">
         <v>17</v>
@@ -9963,7 +10009,7 @@
       <c r="D21" s="149"/>
       <c r="E21" s="149"/>
       <c r="F21" s="150" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="G21" s="213" t="s">
         <v>27</v>
@@ -9972,7 +10018,7 @@
         <v>1396</v>
       </c>
       <c r="I21" s="148" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="J21" s="149" t="s">
         <v>13</v>
@@ -10013,7 +10059,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F22" s="150"/>
       <c r="G22" s="213"/>
@@ -10107,7 +10153,7 @@
         <v>1396</v>
       </c>
       <c r="I24" s="148" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="J24" s="149" t="s">
         <v>4</v>
@@ -10183,13 +10229,13 @@
         <v>58</v>
       </c>
       <c r="C26" s="293" t="s">
+        <v>1643</v>
+      </c>
+      <c r="D26" s="158" t="s">
         <v>1644</v>
       </c>
-      <c r="D26" s="158" t="s">
+      <c r="E26" s="158" t="s">
         <v>1645</v>
-      </c>
-      <c r="E26" s="158" t="s">
-        <v>1646</v>
       </c>
       <c r="F26" s="159" t="s">
         <v>141</v>
@@ -10324,7 +10370,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="160" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="F29" s="162" t="s">
         <v>259</v>
@@ -10368,7 +10414,7 @@
       <c r="D30" s="160"/>
       <c r="E30" s="160"/>
       <c r="F30" s="162" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="G30" s="221" t="s">
         <v>27</v>
@@ -10500,10 +10546,10 @@
         <v>24</v>
       </c>
       <c r="E33" s="160" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F33" s="162" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G33" s="221" t="s">
         <v>17</v>
@@ -10635,10 +10681,10 @@
         <v>1364</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="F36" s="162" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="G36" s="221" t="s">
         <v>17</v>
@@ -10650,7 +10696,7 @@
         <v>833</v>
       </c>
       <c r="J36" s="160" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="K36" s="160" t="s">
         <v>1015</v>
@@ -10700,7 +10746,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="160" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="L37" s="157" t="s">
         <v>23</v>
@@ -10764,13 +10810,13 @@
         <v>58</v>
       </c>
       <c r="C39" s="162" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="D39" s="160" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="E39" s="160" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="F39" s="162" t="s">
         <v>991</v>
@@ -10826,10 +10872,10 @@
         <v>17</v>
       </c>
       <c r="H40" s="160" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="I40" s="162" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="J40" s="160" t="s">
         <v>13</v>
@@ -10870,7 +10916,7 @@
       <c r="G41" s="221"/>
       <c r="H41" s="160"/>
       <c r="I41" s="162" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="J41" s="160" t="s">
         <v>4</v>
@@ -10946,7 +10992,7 @@
         <v>58</v>
       </c>
       <c r="C43" s="162" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="D43" s="160" t="s">
         <v>48</v>
@@ -11043,7 +11089,7 @@
       <c r="D45" s="160"/>
       <c r="E45" s="160"/>
       <c r="F45" s="289" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="G45" s="221" t="s">
         <v>0</v>
@@ -11128,9 +11174,11 @@
         <v>58</v>
       </c>
       <c r="C47" s="289" t="s">
-        <v>1598</v>
-      </c>
-      <c r="D47" s="160"/>
+        <v>1597</v>
+      </c>
+      <c r="D47" s="160" t="s">
+        <v>1652</v>
+      </c>
       <c r="E47" s="160" t="s">
         <v>453</v>
       </c>
@@ -11170,7 +11218,7 @@
       <c r="D48" s="160"/>
       <c r="E48" s="160"/>
       <c r="F48" s="162" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="G48" s="221" t="s">
         <v>27</v>
@@ -11179,7 +11227,7 @@
         <v>1396</v>
       </c>
       <c r="I48" s="164" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="J48" s="160" t="s">
         <v>4</v>
@@ -11217,7 +11265,7 @@
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
       <c r="F49" s="167" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="G49" s="225" t="s">
         <v>27</v>
@@ -11229,10 +11277,10 @@
         <v>862</v>
       </c>
       <c r="J49" s="166" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K49" s="166" t="s">
         <v>1631</v>
-      </c>
-      <c r="K49" s="166" t="s">
-        <v>1632</v>
       </c>
       <c r="L49" s="165" t="s">
         <v>3</v>
@@ -11302,13 +11350,13 @@
         <v>55</v>
       </c>
       <c r="C51" s="172" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="D51" s="171" t="s">
         <v>40</v>
       </c>
       <c r="E51" s="171" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="F51" s="172"/>
       <c r="G51" s="229"/>
@@ -11399,7 +11447,7 @@
       <c r="D53" s="171"/>
       <c r="E53" s="171"/>
       <c r="F53" s="172" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="G53" s="229" t="s">
         <v>11</v>
@@ -11478,16 +11526,16 @@
         <v>55</v>
       </c>
       <c r="C55" s="172" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D55" s="171" t="s">
         <v>1144</v>
       </c>
       <c r="E55" s="171" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F55" s="172" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="G55" s="229" t="s">
         <v>27</v>
@@ -11534,23 +11582,29 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1572</v>
-      </c>
-      <c r="E56" s="171"/>
+        <v>1571</v>
+      </c>
+      <c r="E56" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="F56" s="172" t="s">
         <v>77</v>
       </c>
       <c r="G56" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H56" s="171"/>
+      <c r="H56" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="I56" s="171" t="s">
         <v>77</v>
       </c>
       <c r="J56" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K56" s="171"/>
+      <c r="K56" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="L56" s="168" t="s">
         <v>30</v>
       </c>
@@ -11583,21 +11637,27 @@
       <c r="D57" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="E57" s="171"/>
+      <c r="E57" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="F57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="G57" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H57" s="171"/>
+      <c r="H57" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="I57" s="171" t="s">
         <v>81</v>
       </c>
       <c r="J57" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K57" s="171"/>
+      <c r="K57" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="L57" s="168" t="s">
         <v>29</v>
       </c>
@@ -11630,21 +11690,27 @@
       <c r="D58" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="E58" s="171"/>
+      <c r="E58" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="F58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="G58" s="229" t="s">
         <v>335</v>
       </c>
-      <c r="H58" s="171"/>
+      <c r="H58" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="I58" s="171" t="s">
         <v>78</v>
       </c>
       <c r="J58" s="171" t="s">
         <v>335</v>
       </c>
-      <c r="K58" s="171"/>
+      <c r="K58" s="171" t="s">
+        <v>1096</v>
+      </c>
       <c r="L58" s="168" t="s">
         <v>28</v>
       </c>
@@ -11769,10 +11835,10 @@
       <c r="D61" s="171"/>
       <c r="E61" s="171"/>
       <c r="F61" s="172" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G61" s="229" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H61" s="171" t="s">
         <v>1399</v>
@@ -11781,7 +11847,7 @@
         <v>1477</v>
       </c>
       <c r="J61" s="171" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="K61" s="171" t="s">
         <v>1402</v>
@@ -11813,22 +11879,22 @@
         <v>55</v>
       </c>
       <c r="C62" s="172" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="D62" s="171" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="E62" s="171" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F62" s="172" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="G62" s="229" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H62" s="171" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="I62" s="172"/>
       <c r="J62" s="171"/>
@@ -11869,7 +11935,7 @@
         <v>1478</v>
       </c>
       <c r="J63" s="171" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="K63" s="171" t="s">
         <v>1403</v>
@@ -11904,13 +11970,13 @@
       <c r="D64" s="171"/>
       <c r="E64" s="171"/>
       <c r="F64" s="172" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="G64" s="229" t="s">
         <v>0</v>
       </c>
       <c r="H64" s="171" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="I64" s="172" t="s">
         <v>1479</v>
@@ -11919,7 +11985,7 @@
         <v>13</v>
       </c>
       <c r="K64" s="171" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="L64" s="168" t="s">
         <v>20</v>
@@ -11954,7 +12020,7 @@
         <v>695</v>
       </c>
       <c r="G65" s="229" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H65" s="171" t="s">
         <v>1018</v>
@@ -11989,16 +12055,16 @@
         <v>55</v>
       </c>
       <c r="C66" s="172" t="s">
-        <v>110</v>
+        <v>1655</v>
       </c>
       <c r="D66" s="171" t="s">
         <v>63</v>
       </c>
       <c r="E66" s="171" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F66" s="172" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="G66" s="229" t="s">
         <v>17</v>
@@ -12007,10 +12073,10 @@
         <v>1017</v>
       </c>
       <c r="I66" s="172" t="s">
-        <v>1480</v>
+        <v>1654</v>
       </c>
       <c r="J66" s="171" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="K66" s="171" t="s">
         <v>1403</v>
@@ -12023,7 +12089,7 @@
       </c>
       <c r="N66" s="151" t="str">
         <f t="shared" si="0"/>
-        <v>16:19</v>
+        <v>16:49</v>
       </c>
       <c r="O66" s="151" t="str">
         <f t="shared" si="1"/>
@@ -12031,7 +12097,7 @@
       </c>
       <c r="P66" s="151" t="str">
         <f t="shared" si="2"/>
-        <v>16:16</v>
+        <v>16:17</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="18" customHeight="1">
@@ -12086,7 +12152,7 @@
       <c r="D68" s="171"/>
       <c r="E68" s="171"/>
       <c r="F68" s="172" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="G68" s="229" t="s">
         <v>11</v>
@@ -12127,7 +12193,7 @@
       <c r="D69" s="171"/>
       <c r="E69" s="171"/>
       <c r="F69" s="172" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="G69" s="229" t="s">
         <v>0</v>
@@ -12136,7 +12202,7 @@
         <v>1018</v>
       </c>
       <c r="I69" s="172" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="J69" s="171" t="s">
         <v>4</v>
@@ -12171,10 +12237,10 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="D70" s="172" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="E70" s="171" t="s">
         <v>71</v>
@@ -12183,7 +12249,7 @@
       <c r="G70" s="229"/>
       <c r="H70" s="171"/>
       <c r="I70" s="173" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="J70" s="171" t="s">
         <v>13</v>
@@ -12221,7 +12287,7 @@
       <c r="D71" s="171"/>
       <c r="E71" s="171"/>
       <c r="F71" s="172" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="G71" s="229" t="s">
         <v>11</v>
@@ -12303,13 +12369,13 @@
       <c r="D73" s="175"/>
       <c r="E73" s="175"/>
       <c r="F73" s="176" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="G73" s="233" t="s">
         <v>27</v>
       </c>
       <c r="H73" s="175" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="I73" s="176" t="s">
         <v>150</v>
@@ -12347,13 +12413,13 @@
         <v>52</v>
       </c>
       <c r="C74" s="179" t="s">
-        <v>1116</v>
+        <v>1656</v>
       </c>
       <c r="D74" s="178" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="E74" s="178" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="F74" s="179" t="s">
         <v>141</v>
@@ -12375,7 +12441,7 @@
       </c>
       <c r="N74" s="151" t="str">
         <f t="shared" si="3"/>
-        <v>00:01</v>
+        <v>00:00</v>
       </c>
       <c r="O74" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12400,7 +12466,7 @@
         <v>127</v>
       </c>
       <c r="G75" s="237" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H75" s="180" t="s">
         <v>1396</v>
@@ -12409,7 +12475,7 @@
         <v>600</v>
       </c>
       <c r="J75" s="180" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="K75" s="180" t="s">
         <v>1403</v>
@@ -12441,13 +12507,13 @@
         <v>52</v>
       </c>
       <c r="C76" s="181" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D76" s="180" t="s">
         <v>1371</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="F76" s="181" t="s">
         <v>783</v>
@@ -12623,13 +12689,13 @@
         <v>52</v>
       </c>
       <c r="C80" s="181" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D80" s="180" t="s">
         <v>19</v>
       </c>
       <c r="E80" s="180" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="237"/>
@@ -12667,16 +12733,16 @@
       <c r="D81" s="180"/>
       <c r="E81" s="180"/>
       <c r="F81" s="181" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G81" s="237" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H81" s="180" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I81" s="181" t="s">
         <v>1492</v>
-      </c>
-      <c r="G81" s="237" t="s">
-        <v>1555</v>
-      </c>
-      <c r="H81" s="180" t="s">
-        <v>1556</v>
-      </c>
-      <c r="I81" s="181" t="s">
-        <v>1493</v>
       </c>
       <c r="J81" s="180" t="s">
         <v>4</v>
@@ -12799,25 +12865,25 @@
         <v>64</v>
       </c>
       <c r="E84" s="180" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="F84" s="181" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="G84" s="237" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H84" s="180" t="s">
         <v>1557</v>
       </c>
-      <c r="H84" s="180" t="s">
-        <v>1558</v>
-      </c>
       <c r="I84" s="181" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="J84" s="180" t="s">
+        <v>1567</v>
+      </c>
+      <c r="K84" s="180" t="s">
         <v>1568</v>
-      </c>
-      <c r="K84" s="180" t="s">
-        <v>1569</v>
       </c>
       <c r="L84" s="177" t="s">
         <v>25</v>
@@ -12858,7 +12924,7 @@
         <v>4</v>
       </c>
       <c r="K85" s="180" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="L85" s="177" t="s">
         <v>23</v>
@@ -12890,13 +12956,13 @@
       <c r="D86" s="180"/>
       <c r="E86" s="180"/>
       <c r="F86" s="181" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="G86" s="237" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H86" s="180" t="s">
         <v>1559</v>
-      </c>
-      <c r="H86" s="180" t="s">
-        <v>1560</v>
       </c>
       <c r="I86" s="182"/>
       <c r="J86" s="180"/>
@@ -12931,7 +12997,7 @@
       <c r="D87" s="180"/>
       <c r="E87" s="180"/>
       <c r="F87" s="181" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="G87" s="237" t="s">
         <v>0</v>
@@ -12940,7 +13006,7 @@
         <v>1018</v>
       </c>
       <c r="I87" s="181" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="J87" s="180" t="s">
         <v>13</v>
@@ -12981,7 +13047,7 @@
         <v>1143</v>
       </c>
       <c r="E88" s="180" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="F88" s="181" t="s">
         <v>1342</v>
@@ -13066,7 +13132,7 @@
       <c r="D90" s="180"/>
       <c r="E90" s="180"/>
       <c r="F90" s="181" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="G90" s="237" t="s">
         <v>17</v>
@@ -13113,7 +13179,7 @@
       <c r="D91" s="180"/>
       <c r="E91" s="180"/>
       <c r="F91" s="181" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G91" s="237" t="s">
         <v>27</v>
@@ -13122,7 +13188,7 @@
         <v>1396</v>
       </c>
       <c r="I91" s="181" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="J91" s="180" t="s">
         <v>4</v>
@@ -13157,13 +13223,13 @@
         <v>52</v>
       </c>
       <c r="C92" s="181" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="D92" s="180" t="s">
         <v>34</v>
       </c>
       <c r="E92" s="180" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="237"/>
@@ -13210,7 +13276,7 @@
         <v>1396</v>
       </c>
       <c r="I93" s="181" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="J93" s="180" t="s">
         <v>13</v>
@@ -13248,7 +13314,7 @@
       <c r="D94" s="180"/>
       <c r="E94" s="180"/>
       <c r="F94" s="181" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="G94" s="237" t="s">
         <v>11</v>
@@ -13257,7 +13323,7 @@
         <v>1016</v>
       </c>
       <c r="I94" s="181" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="J94" s="180" t="s">
         <v>13</v>
@@ -13333,10 +13399,10 @@
         <v>39</v>
       </c>
       <c r="E96" s="180" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="F96" s="181" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="G96" s="237" t="s">
         <v>11</v>
@@ -13465,7 +13531,7 @@
         <v>234</v>
       </c>
       <c r="D99" s="187" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E99" s="189" t="s">
         <v>1412</v>
@@ -13650,7 +13716,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="189" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="F103" s="190" t="s">
         <v>616</v>
@@ -13662,7 +13728,7 @@
         <v>1016</v>
       </c>
       <c r="I103" s="190" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="J103" s="189" t="s">
         <v>13</v>
@@ -13791,7 +13857,7 @@
         <v>1016</v>
       </c>
       <c r="I106" s="190" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="J106" s="189" t="s">
         <v>13</v>
@@ -13861,13 +13927,13 @@
         <v>44</v>
       </c>
       <c r="C108" s="190" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D108" s="189" t="s">
         <v>1143</v>
       </c>
       <c r="E108" s="189" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="F108" s="190" t="s">
         <v>207</v>
@@ -13926,7 +13992,7 @@
         <v>1016</v>
       </c>
       <c r="I109" s="190" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="J109" s="189" t="s">
         <v>4</v>
@@ -14043,7 +14109,7 @@
         <v>44</v>
       </c>
       <c r="C112" s="190" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="D112" s="189" t="s">
         <v>903</v>
@@ -14052,7 +14118,7 @@
         <v>1409</v>
       </c>
       <c r="F112" s="190" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="G112" s="244" t="s">
         <v>27</v>
@@ -14061,7 +14127,7 @@
         <v>1396</v>
       </c>
       <c r="I112" s="190" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="J112" s="189" t="s">
         <v>4</v>
@@ -14181,10 +14247,10 @@
         <v>788</v>
       </c>
       <c r="D115" s="189" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="E115" s="189" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="F115" s="190" t="s">
         <v>1036</v>
@@ -14196,7 +14262,7 @@
         <v>1018</v>
       </c>
       <c r="I115" s="190" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="J115" s="189" t="s">
         <v>13</v>
@@ -14275,7 +14341,7 @@
       <c r="D117" s="189"/>
       <c r="E117" s="189"/>
       <c r="F117" s="190" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G117" s="244" t="s">
         <v>27</v>
@@ -14404,13 +14470,13 @@
         <v>861</v>
       </c>
       <c r="D120" s="189" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="E120" s="189" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F120" s="190" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="G120" s="244" t="s">
         <v>17</v>
@@ -14451,7 +14517,7 @@
       <c r="D121" s="193"/>
       <c r="E121" s="193"/>
       <c r="F121" s="194" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="G121" s="247" t="s">
         <v>0</v>
@@ -14460,7 +14526,7 @@
         <v>1018</v>
       </c>
       <c r="I121" s="194" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="J121" s="193" t="s">
         <v>13</v>
@@ -14539,10 +14605,10 @@
         <v>269</v>
       </c>
       <c r="D123" s="198" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E123" s="198" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F123" s="199" t="s">
         <v>623</v>
@@ -14865,7 +14931,7 @@
         <v>1018</v>
       </c>
       <c r="I130" s="199" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="J130" s="198" t="s">
         <v>13</v>
@@ -14900,13 +14966,13 @@
         <v>38</v>
       </c>
       <c r="C131" s="199" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="D131" s="198" t="s">
         <v>908</v>
       </c>
       <c r="E131" s="198" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="F131" s="199"/>
       <c r="G131" s="251"/>
@@ -14944,7 +15010,7 @@
       <c r="D132" s="198"/>
       <c r="E132" s="198"/>
       <c r="F132" s="199" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="G132" s="251" t="s">
         <v>27</v>
@@ -14953,7 +15019,7 @@
         <v>1396</v>
       </c>
       <c r="I132" s="200" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="J132" s="198" t="s">
         <v>4</v>
@@ -15000,7 +15066,7 @@
         <v>1018</v>
       </c>
       <c r="I133" s="199" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="J133" s="198" t="s">
         <v>13</v>
@@ -15073,10 +15139,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D135" s="198" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>607</v>
@@ -15217,7 +15283,7 @@
         <v>1016</v>
       </c>
       <c r="I138" s="199" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="J138" s="198" t="s">
         <v>4</v>
@@ -15252,16 +15318,16 @@
         <v>38</v>
       </c>
       <c r="C139" s="199" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="D139" s="198" t="s">
         <v>902</v>
       </c>
       <c r="E139" s="198" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="F139" s="199" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G139" s="251" t="s">
         <v>17</v>
@@ -15305,7 +15371,7 @@
       <c r="G140" s="251"/>
       <c r="H140" s="198"/>
       <c r="I140" s="199" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="J140" s="198" t="s">
         <v>4</v>
@@ -15387,13 +15453,13 @@
         <v>38</v>
       </c>
       <c r="C142" s="199" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="D142" s="198" t="s">
         <v>1143</v>
       </c>
       <c r="E142" s="198" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F142" s="199" t="s">
         <v>1288</v>
@@ -15405,7 +15471,7 @@
         <v>1017</v>
       </c>
       <c r="I142" s="199" t="s">
-        <v>790</v>
+        <v>1653</v>
       </c>
       <c r="J142" s="198" t="s">
         <v>13</v>
@@ -15429,7 +15495,7 @@
       </c>
       <c r="P142" s="151" t="str">
         <f t="shared" si="8"/>
-        <v>20:54</v>
+        <v>20:53</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="18" customHeight="1">
@@ -15478,7 +15544,7 @@
       <c r="D144" s="198"/>
       <c r="E144" s="198"/>
       <c r="F144" s="199" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G144" s="251" t="s">
         <v>0</v>
@@ -15525,7 +15591,7 @@
       <c r="D145" s="203"/>
       <c r="E145" s="203"/>
       <c r="F145" s="204" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G145" s="255" t="s">
         <v>27</v>
@@ -15698,13 +15764,13 @@
         <v>2</v>
       </c>
       <c r="C149" s="209" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="D149" s="208" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E149" s="208" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="F149" s="209" t="s">
         <v>236</v>
@@ -15751,7 +15817,7 @@
       <c r="G150" s="259"/>
       <c r="H150" s="208"/>
       <c r="I150" s="209" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="J150" s="208" t="s">
         <v>13</v>
@@ -15789,7 +15855,7 @@
       <c r="D151" s="208"/>
       <c r="E151" s="208"/>
       <c r="F151" s="292" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="G151" s="259" t="s">
         <v>0</v>
@@ -15833,16 +15899,16 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="D152" s="208" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="E152" s="208" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="F152" s="292" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="G152" s="259" t="s">
         <v>0</v>
@@ -15971,7 +16037,7 @@
       <c r="D155" s="208"/>
       <c r="E155" s="208"/>
       <c r="F155" s="209" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="G155" s="259" t="s">
         <v>0</v>
@@ -16053,13 +16119,13 @@
         <v>1282</v>
       </c>
       <c r="D157" s="208" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="E157" s="208" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="F157" s="209" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G157" s="259" t="s">
         <v>0</v>
@@ -16068,7 +16134,7 @@
         <v>1018</v>
       </c>
       <c r="I157" s="209" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="J157" s="208" t="s">
         <v>4</v>
@@ -16106,7 +16172,7 @@
       <c r="D158" s="208"/>
       <c r="E158" s="208"/>
       <c r="F158" s="209" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="G158" s="259" t="s">
         <v>17</v>
@@ -16144,7 +16210,7 @@
         <v>2</v>
       </c>
       <c r="C159" s="209" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="D159" s="208" t="s">
         <v>908</v>
@@ -16194,7 +16260,7 @@
       <c r="D160" s="208"/>
       <c r="E160" s="208"/>
       <c r="F160" s="209" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G160" s="259" t="s">
         <v>27</v>
@@ -16203,7 +16269,7 @@
         <v>1396</v>
       </c>
       <c r="I160" s="209" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="J160" s="208" t="s">
         <v>4</v>
@@ -16241,7 +16307,7 @@
       <c r="D161" s="208"/>
       <c r="E161" s="208"/>
       <c r="F161" s="209" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="G161" s="259" t="s">
         <v>11</v>
@@ -16250,7 +16316,7 @@
         <v>1016</v>
       </c>
       <c r="I161" s="210" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="J161" s="208" t="s">
         <v>13</v>
@@ -16320,13 +16386,13 @@
         <v>2</v>
       </c>
       <c r="C163" s="209" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="D163" s="208" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="E163" s="208" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="F163" s="209" t="s">
         <v>1287</v>
@@ -16338,7 +16404,7 @@
         <v>1018</v>
       </c>
       <c r="I163" s="209" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="J163" s="208" t="s">
         <v>4</v>
@@ -16376,7 +16442,7 @@
       <c r="D164" s="208"/>
       <c r="E164" s="208"/>
       <c r="F164" s="209" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="G164" s="259" t="s">
         <v>17</v>
@@ -16385,7 +16451,7 @@
         <v>1017</v>
       </c>
       <c r="I164" s="209" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="J164" s="208" t="s">
         <v>4</v>
@@ -16458,7 +16524,7 @@
       <c r="D166" s="208"/>
       <c r="E166" s="208"/>
       <c r="F166" s="209" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="G166" s="259" t="s">
         <v>27</v>
@@ -16467,7 +16533,7 @@
         <v>1396</v>
       </c>
       <c r="I166" s="209" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="J166" s="208" t="s">
         <v>4</v>
@@ -16502,16 +16568,16 @@
         <v>2</v>
       </c>
       <c r="C167" s="209" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="D167" s="208" t="s">
         <v>1369</v>
       </c>
       <c r="E167" s="208" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F167" s="209" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="G167" s="259" t="s">
         <v>17</v>
@@ -16593,7 +16659,7 @@
       <c r="D169" s="208"/>
       <c r="E169" s="208"/>
       <c r="F169" s="209" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="G169" s="259" t="s">
         <v>27</v>
@@ -16663,18 +16729,18 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="70" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="70" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="70" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="70" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" style="70" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="70" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.8984375" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15.19921875" style="70" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.8984375" style="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="70" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.25" style="70" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.875" style="70" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="70" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="70"/>
-    <col min="14" max="16" width="5.8984375" style="70" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.875" style="70" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="70"/>
   </cols>
   <sheetData>
@@ -24233,25 +24299,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C332778B-0E89-49E0-A596-558D2A6CA2E7}">
   <dimension ref="A1:P169"/>
-  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="144" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="144" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.59765625" style="144" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.59765625" style="144" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="144" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="144" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.625" style="144" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="144" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.19921875" style="144" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="144" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22.5" style="144" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3.5" style="144" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.19921875" style="144" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.59765625" style="143" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.3984375" style="143" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.59765625" style="143" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="14.19921875" style="143"/>
+    <col min="13" max="13" width="13.25" style="144" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.625" style="143" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.375" style="143" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.625" style="143" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="14.25" style="143"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="142" customFormat="1" ht="18" customHeight="1">
@@ -24720,7 +24786,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="F11" s="150"/>
       <c r="G11" s="149"/>
@@ -25207,7 +25273,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F22" s="150" t="s">
         <v>1288</v>
@@ -25565,7 +25631,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>1195</v>
@@ -31914,21 +31980,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B7320E-C509-4E9C-A2AC-DAC652C78517}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.69921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.375" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -37872,21 +37938,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="212" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="212" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3984375" style="151" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="151" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.375" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -43902,17 +43968,17 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.3984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.375" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.3984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.8984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.3984375" style="67" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.875" style="67" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.375" style="67" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="67"/>
   </cols>
   <sheetData>
@@ -48544,7 +48610,7 @@
         <v>441</v>
       </c>
       <c r="F132" s="55" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="G132" s="57"/>
       <c r="H132" s="55"/>
@@ -49894,19 +49960,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="212"/>
-    <col min="11" max="13" width="5.8984375" style="212" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.875" style="212" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="212"/>
   </cols>
   <sheetData>
@@ -55792,16 +55858,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="212" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="212" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="212" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="212" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="212"/>
-    <col min="11" max="13" width="5.8984375" style="212" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.875" style="212" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="212"/>
   </cols>
   <sheetData>
@@ -61785,16 +61851,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="151" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="151" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="151" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="151"/>
-    <col min="11" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>
@@ -67879,16 +67945,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="151" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="151" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="151" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="151" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.09765625" style="151" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="151" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" style="151" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="151" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="151" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="151"/>
-    <col min="11" max="13" width="5.8984375" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.875" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="151"/>
   </cols>
   <sheetData>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB196701-FFFA-4E1A-BB79-309A5639050F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F62CE8-B046-4A3A-907B-4775A74A7F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16515" yWindow="90" windowWidth="16605" windowHeight="15765" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16620" yWindow="0" windowWidth="16605" windowHeight="15690" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList_ZH" sheetId="8" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13927" uniqueCount="1642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14260" uniqueCount="1692">
   <si>
     <t>敵萬夫</t>
   </si>
@@ -7030,9 +7030,6 @@
     <t>灰狼村 / 土門客棧</t>
   </si>
   <si>
-    <t>土門客棧 / 叛軍駐地</t>
-  </si>
-  <si>
     <t>染坊 / 叛軍駐地</t>
   </si>
   <si>
@@ -7247,10 +7244,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>00:00</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>13:40</t>
   </si>
   <si>
@@ -7321,6 +7314,183 @@
   <si>
     <t>09:30_?</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>13:21</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>15:32</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>03:07</t>
+  </si>
+  <si>
+    <t>04:41</t>
+  </si>
+  <si>
+    <t>11:00</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>風之平原</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>12:13</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>18:11</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>04:2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>敵萬夫</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>???</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黑鯰魚</t>
+  </si>
+  <si>
+    <t>土門客棧 / 叛軍駐地</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>土門客棧 / 染坊</t>
+  </si>
+  <si>
+    <t>鬼都 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>悲鳴村 / 灰狼</t>
+  </si>
+  <si>
+    <t>黑森林 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>孤村 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>豬豬農場 / 染坊</t>
+  </si>
+  <si>
+    <t>土門客棧 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>染坊 / (北方)叛軍駐地</t>
+  </si>
+  <si>
+    <t>13:08</t>
+  </si>
+  <si>
+    <t>15:52</t>
+  </si>
+  <si>
+    <t>23:22</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>22:46</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>17:37</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>20:33</t>
+  </si>
+  <si>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>21:46</t>
+  </si>
+  <si>
+    <t>22:56</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>20:43</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>23:30</t>
   </si>
 </sst>
 </file>
@@ -7589,7 +7759,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="300">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8483,11 +8653,21 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="17" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="43">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -8772,13 +8952,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9083,14 +9256,15 @@
     <col min="1" max="1" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.19921875" style="212" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.296875" style="212" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" style="212" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.59765625" style="212" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.296875" style="212" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.19921875" style="212" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.296875" style="212" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="212" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.3984375" style="212" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.796875" style="151" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.19921875" style="151" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.796875" style="151" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="14.19921875" style="151"/>
   </cols>
   <sheetData>
@@ -9127,12 +9301,20 @@
       <c r="B2" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="150"/>
-      <c r="F2" s="213"/>
-      <c r="G2" s="287" t="s">
-        <v>1622</v>
+      <c r="C2" s="150" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="149" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="150" t="s">
+        <v>823</v>
+      </c>
+      <c r="F2" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="150" t="s">
+        <v>141</v>
       </c>
       <c r="H2" s="149" t="s">
         <v>13</v>
@@ -9145,11 +9327,11 @@
       </c>
       <c r="K2" s="151" t="str">
         <f>IF($C2&lt;&gt;"",TEXT($C2,"HH:MM"),"")</f>
-        <v/>
+        <v>00:46</v>
       </c>
       <c r="L2" s="151" t="str">
         <f>IF($E2&lt;&gt;"",TEXT($E2,"HH:MM"),"")</f>
-        <v/>
+        <v>00:57</v>
       </c>
       <c r="M2" s="151" t="str">
         <f>IF($G2&lt;&gt;"",TEXT($G2,"HH:MM"),"")</f>
@@ -9167,8 +9349,12 @@
       <c r="D3" s="149"/>
       <c r="E3" s="150"/>
       <c r="F3" s="213"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="149"/>
+      <c r="G3" s="150" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H3" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I3" s="148" t="s">
         <v>36</v>
       </c>
@@ -9185,7 +9371,7 @@
       </c>
       <c r="M3" s="151" t="str">
         <f t="shared" ref="M3:M66" si="2">IF($G3&lt;&gt;"",TEXT($G3,"HH:MM"),"")</f>
-        <v/>
+        <v>01:29</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" customHeight="1">
@@ -9197,8 +9383,12 @@
       </c>
       <c r="C4" s="150"/>
       <c r="D4" s="152"/>
-      <c r="E4" s="150"/>
-      <c r="F4" s="213"/>
+      <c r="E4" s="150" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F4" s="213" t="s">
+        <v>27</v>
+      </c>
       <c r="G4" s="150"/>
       <c r="H4" s="149"/>
       <c r="I4" s="148" t="s">
@@ -9213,7 +9403,7 @@
       </c>
       <c r="L4" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>02:25</v>
       </c>
       <c r="M4" s="151" t="str">
         <f t="shared" si="2"/>
@@ -9229,10 +9419,18 @@
       </c>
       <c r="C5" s="149"/>
       <c r="D5" s="149"/>
-      <c r="E5" s="150"/>
-      <c r="F5" s="213"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="149"/>
+      <c r="E5" s="150" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="213" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G5" s="150" t="s">
+        <v>143</v>
+      </c>
+      <c r="H5" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I5" s="148" t="s">
         <v>33</v>
       </c>
@@ -9245,11 +9443,11 @@
       </c>
       <c r="L5" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>03:55</v>
       </c>
       <c r="M5" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>03:00</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="18" customHeight="1">
@@ -9263,8 +9461,12 @@
       <c r="D6" s="149"/>
       <c r="E6" s="150"/>
       <c r="F6" s="213"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
+      <c r="G6" s="148" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H6" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I6" s="148" t="s">
         <v>32</v>
       </c>
@@ -9281,7 +9483,7 @@
       </c>
       <c r="M6" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:27</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="18" customHeight="1">
@@ -9293,10 +9495,18 @@
       </c>
       <c r="C7" s="153"/>
       <c r="D7" s="149"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="149"/>
+      <c r="E7" s="150" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F7" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G7" s="150" t="s">
+        <v>272</v>
+      </c>
+      <c r="H7" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I7" s="148" t="s">
         <v>31</v>
       </c>
@@ -9309,11 +9519,11 @@
       </c>
       <c r="L7" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>05:29</v>
       </c>
       <c r="M7" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>05:53</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1">
@@ -9325,8 +9535,12 @@
       </c>
       <c r="C8" s="150"/>
       <c r="D8" s="149"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="213"/>
+      <c r="E8" s="153">
+        <v>0.28749999999999998</v>
+      </c>
+      <c r="F8" s="213" t="s">
+        <v>11</v>
+      </c>
       <c r="G8" s="150"/>
       <c r="H8" s="149"/>
       <c r="I8" s="148" t="s">
@@ -9341,7 +9555,7 @@
       </c>
       <c r="L8" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>06:54</v>
       </c>
       <c r="M8" s="151" t="str">
         <f t="shared" si="2"/>
@@ -9359,8 +9573,12 @@
       <c r="D9" s="149"/>
       <c r="E9" s="150"/>
       <c r="F9" s="213"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="149"/>
+      <c r="G9" s="150" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H9" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I9" s="148" t="s">
         <v>29</v>
       </c>
@@ -9377,7 +9595,7 @@
       </c>
       <c r="M9" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>07:24</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="18" customHeight="1">
@@ -9389,10 +9607,18 @@
       </c>
       <c r="C10" s="150"/>
       <c r="D10" s="149"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="148"/>
-      <c r="H10" s="149"/>
+      <c r="E10" s="150" t="s">
+        <v>830</v>
+      </c>
+      <c r="F10" s="213" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="148" t="s">
+        <v>274</v>
+      </c>
+      <c r="H10" s="149" t="s">
+        <v>1640</v>
+      </c>
       <c r="I10" s="148" t="s">
         <v>28</v>
       </c>
@@ -9405,11 +9631,11 @@
       </c>
       <c r="L10" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>08:29</v>
       </c>
       <c r="M10" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>08:52</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="18" customHeight="1">
@@ -9419,8 +9645,12 @@
       <c r="B11" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="153"/>
-      <c r="D11" s="149"/>
+      <c r="C11" s="153">
+        <v>0.38680555555555557</v>
+      </c>
+      <c r="D11" s="149" t="s">
+        <v>1659</v>
+      </c>
       <c r="E11" s="150"/>
       <c r="F11" s="213"/>
       <c r="G11" s="150"/>
@@ -9433,7 +9663,7 @@
       </c>
       <c r="K11" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>09:17</v>
       </c>
       <c r="L11" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9453,10 +9683,18 @@
       </c>
       <c r="C12" s="150"/>
       <c r="D12" s="149"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
+      <c r="E12" s="150" t="s">
+        <v>833</v>
+      </c>
+      <c r="F12" s="213" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="150" t="s">
+        <v>314</v>
+      </c>
+      <c r="H12" s="150" t="s">
+        <v>4</v>
+      </c>
       <c r="I12" s="148" t="s">
         <v>25</v>
       </c>
@@ -9469,11 +9707,11 @@
       </c>
       <c r="L12" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>10:03</v>
       </c>
       <c r="M12" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10:23</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1">
@@ -9485,10 +9723,18 @@
       </c>
       <c r="C13" s="150"/>
       <c r="D13" s="149"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="213"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="149"/>
+      <c r="E13" s="150" t="s">
+        <v>797</v>
+      </c>
+      <c r="F13" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G13" s="148" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H13" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I13" s="148" t="s">
         <v>23</v>
       </c>
@@ -9501,11 +9747,11 @@
       </c>
       <c r="L13" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>11:35</v>
       </c>
       <c r="M13" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:48</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1">
@@ -9515,8 +9761,12 @@
       <c r="B14" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
+      <c r="C14" s="153">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="D14" s="149" t="s">
+        <v>1660</v>
+      </c>
       <c r="E14" s="150"/>
       <c r="F14" s="213"/>
       <c r="G14" s="150"/>
@@ -9529,7 +9779,7 @@
       </c>
       <c r="K14" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>12:15</v>
       </c>
       <c r="L14" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9549,10 +9799,18 @@
       </c>
       <c r="C15" s="150"/>
       <c r="D15" s="149"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="213"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="149"/>
+      <c r="E15" s="150" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F15" s="213" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="150" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H15" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I15" s="148" t="s">
         <v>21</v>
       </c>
@@ -9565,11 +9823,11 @@
       </c>
       <c r="L15" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>13:08</v>
       </c>
       <c r="M15" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:21</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18" customHeight="1">
@@ -9581,10 +9839,18 @@
       </c>
       <c r="C16" s="153"/>
       <c r="D16" s="149"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="213"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="149"/>
+      <c r="E16" s="150" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F16" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="148" t="s">
+        <v>190</v>
+      </c>
+      <c r="H16" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I16" s="148" t="s">
         <v>20</v>
       </c>
@@ -9597,11 +9863,11 @@
       </c>
       <c r="L16" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>14:36</v>
       </c>
       <c r="M16" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:56</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="18" customHeight="1">
@@ -9611,8 +9877,12 @@
       <c r="B17" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="150"/>
-      <c r="D17" s="149"/>
+      <c r="C17" s="150" t="s">
+        <v>1669</v>
+      </c>
+      <c r="D17" s="149" t="s">
+        <v>1555</v>
+      </c>
       <c r="E17" s="150"/>
       <c r="F17" s="213"/>
       <c r="G17" s="150"/>
@@ -9625,7 +9895,7 @@
       </c>
       <c r="K17" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>15:52</v>
       </c>
       <c r="L17" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9645,10 +9915,18 @@
       </c>
       <c r="C18" s="150"/>
       <c r="D18" s="149"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="149"/>
+      <c r="E18" s="150" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="213" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="148" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H18" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I18" s="148" t="s">
         <v>16</v>
       </c>
@@ -9661,11 +9939,11 @@
       </c>
       <c r="L18" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16:05</v>
       </c>
       <c r="M18" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:28</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="18" customHeight="1">
@@ -9677,10 +9955,18 @@
       </c>
       <c r="C19" s="153"/>
       <c r="D19" s="149"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="149"/>
+      <c r="E19" s="150" t="s">
+        <v>817</v>
+      </c>
+      <c r="F19" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G19" s="150" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I19" s="148" t="s">
         <v>15</v>
       </c>
@@ -9693,11 +9979,11 @@
       </c>
       <c r="L19" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>17:31</v>
       </c>
       <c r="M19" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>17:57</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
@@ -9709,8 +9995,12 @@
       </c>
       <c r="C20" s="149"/>
       <c r="D20" s="149"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="213"/>
+      <c r="E20" s="150" t="s">
+        <v>620</v>
+      </c>
+      <c r="F20" s="213" t="s">
+        <v>27</v>
+      </c>
       <c r="G20" s="150"/>
       <c r="H20" s="149"/>
       <c r="I20" s="148" t="s">
@@ -9725,7 +10015,7 @@
       </c>
       <c r="L20" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>18:59</v>
       </c>
       <c r="M20" s="151" t="str">
         <f t="shared" si="2"/>
@@ -9739,12 +10029,20 @@
       <c r="B21" s="149" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="150"/>
-      <c r="D21" s="149"/>
+      <c r="C21" s="150" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D21" s="149" t="s">
+        <v>1661</v>
+      </c>
       <c r="E21" s="150"/>
       <c r="F21" s="213"/>
-      <c r="G21" s="148"/>
-      <c r="H21" s="149"/>
+      <c r="G21" s="148" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H21" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I21" s="148" t="s">
         <v>10</v>
       </c>
@@ -9753,7 +10051,7 @@
       </c>
       <c r="K21" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>19:33</v>
       </c>
       <c r="L21" s="151" t="str">
         <f t="shared" si="1"/>
@@ -9761,7 +10059,7 @@
       </c>
       <c r="M21" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>19:31</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1">
@@ -9773,10 +10071,18 @@
       </c>
       <c r="C22" s="150"/>
       <c r="D22" s="149"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="213"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="149"/>
+      <c r="E22" s="150" t="s">
+        <v>634</v>
+      </c>
+      <c r="F22" s="213" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" s="150" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H22" s="149" t="s">
+        <v>13</v>
+      </c>
       <c r="I22" s="148" t="s">
         <v>9</v>
       </c>
@@ -9789,11 +10095,11 @@
       </c>
       <c r="L22" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>20:24</v>
       </c>
       <c r="M22" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>20:57</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="18" customHeight="1">
@@ -9805,8 +10111,12 @@
       </c>
       <c r="C23" s="149"/>
       <c r="D23" s="149"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="213"/>
+      <c r="E23" s="150" t="s">
+        <v>930</v>
+      </c>
+      <c r="F23" s="213" t="s">
+        <v>0</v>
+      </c>
       <c r="G23" s="150"/>
       <c r="H23" s="149"/>
       <c r="I23" s="148" t="s">
@@ -9821,7 +10131,7 @@
       </c>
       <c r="L23" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>21:54</v>
       </c>
       <c r="M23" s="151" t="str">
         <f t="shared" si="2"/>
@@ -9839,8 +10149,12 @@
       <c r="D24" s="149"/>
       <c r="E24" s="150"/>
       <c r="F24" s="213"/>
-      <c r="G24" s="148"/>
-      <c r="H24" s="149"/>
+      <c r="G24" s="148" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H24" s="149" t="s">
+        <v>4</v>
+      </c>
       <c r="I24" s="148" t="s">
         <v>5</v>
       </c>
@@ -9857,7 +10171,7 @@
       </c>
       <c r="M24" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>22:31</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="18" customHeight="1" thickBot="1">
@@ -9867,10 +10181,18 @@
       <c r="B25" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="156"/>
-      <c r="D25" s="155"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="217"/>
+      <c r="C25" s="156" t="s">
+        <v>805</v>
+      </c>
+      <c r="D25" s="155" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E25" s="156" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F25" s="217" t="s">
+        <v>27</v>
+      </c>
       <c r="G25" s="156"/>
       <c r="H25" s="155"/>
       <c r="I25" s="154" t="s">
@@ -9881,11 +10203,11 @@
       </c>
       <c r="K25" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>23:40</v>
       </c>
       <c r="L25" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>23:22</v>
       </c>
       <c r="M25" s="151" t="str">
         <f t="shared" si="2"/>
@@ -9899,12 +10221,20 @@
       <c r="B26" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="293"/>
+      <c r="C26" s="159"/>
       <c r="D26" s="158"/>
-      <c r="E26" s="159"/>
-      <c r="F26" s="219"/>
-      <c r="G26" s="159"/>
-      <c r="H26" s="158"/>
+      <c r="E26" s="159" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" s="219" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="159" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H26" s="158" t="s">
+        <v>4</v>
+      </c>
       <c r="I26" s="157" t="s">
         <v>37</v>
       </c>
@@ -9917,11 +10247,11 @@
       </c>
       <c r="L26" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M26" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>00:04</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1">
@@ -9933,10 +10263,18 @@
       </c>
       <c r="C27" s="161"/>
       <c r="D27" s="160"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="162"/>
-      <c r="H27" s="160"/>
+      <c r="E27" s="162" t="s">
+        <v>636</v>
+      </c>
+      <c r="F27" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="162" t="s">
+        <v>222</v>
+      </c>
+      <c r="H27" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="I27" s="157" t="s">
         <v>36</v>
       </c>
@@ -9949,11 +10287,11 @@
       </c>
       <c r="L27" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>01:32</v>
       </c>
       <c r="M27" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>01:39</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="18" customHeight="1">
@@ -9997,10 +10335,18 @@
       </c>
       <c r="C29" s="161"/>
       <c r="D29" s="160"/>
-      <c r="E29" s="162"/>
-      <c r="F29" s="221"/>
-      <c r="G29" s="157"/>
-      <c r="H29" s="160"/>
+      <c r="E29" s="162" t="s">
+        <v>637</v>
+      </c>
+      <c r="F29" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="163">
+        <v>0.13125000000000001</v>
+      </c>
+      <c r="H29" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I29" s="157" t="s">
         <v>33</v>
       </c>
@@ -10013,11 +10359,11 @@
       </c>
       <c r="L29" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>03:04</v>
       </c>
       <c r="M29" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>03:09</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
@@ -10029,10 +10375,18 @@
       </c>
       <c r="C30" s="160"/>
       <c r="D30" s="160"/>
-      <c r="E30" s="162"/>
-      <c r="F30" s="221"/>
-      <c r="G30" s="289"/>
-      <c r="H30" s="160"/>
+      <c r="E30" s="162" t="s">
+        <v>285</v>
+      </c>
+      <c r="F30" s="221" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="162" t="s">
+        <v>927</v>
+      </c>
+      <c r="H30" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I30" s="157" t="s">
         <v>32</v>
       </c>
@@ -10045,11 +10399,11 @@
       </c>
       <c r="L30" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>04:38</v>
       </c>
       <c r="M30" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:39</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="18" customHeight="1">
@@ -10059,8 +10413,12 @@
       <c r="B31" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="162"/>
-      <c r="D31" s="160"/>
+      <c r="C31" s="162" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D31" s="160" t="s">
+        <v>1662</v>
+      </c>
       <c r="E31" s="162"/>
       <c r="F31" s="221"/>
       <c r="G31" s="162"/>
@@ -10073,7 +10431,7 @@
       </c>
       <c r="K31" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>05:29</v>
       </c>
       <c r="L31" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10093,10 +10451,18 @@
       </c>
       <c r="C32" s="162"/>
       <c r="D32" s="160"/>
-      <c r="E32" s="162"/>
-      <c r="F32" s="221"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="160"/>
+      <c r="E32" s="162" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F32" s="221" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="163">
+        <v>0.25763888888888886</v>
+      </c>
+      <c r="H32" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I32" s="157" t="s">
         <v>30</v>
       </c>
@@ -10109,11 +10475,11 @@
       </c>
       <c r="L32" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>06:04</v>
       </c>
       <c r="M32" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>06:11</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
@@ -10125,10 +10491,18 @@
       </c>
       <c r="C33" s="279"/>
       <c r="D33" s="160"/>
-      <c r="E33" s="162"/>
-      <c r="F33" s="221"/>
-      <c r="G33" s="162"/>
-      <c r="H33" s="160"/>
+      <c r="E33" s="162" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F33" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="G33" s="162" t="s">
+        <v>1643</v>
+      </c>
+      <c r="H33" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I33" s="157" t="s">
         <v>29</v>
       </c>
@@ -10141,11 +10515,11 @@
       </c>
       <c r="L33" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>07:30</v>
       </c>
       <c r="M33" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>07:46</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
@@ -10187,12 +10561,24 @@
       <c r="B35" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="162"/>
-      <c r="D35" s="160"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="221"/>
-      <c r="G35" s="164"/>
-      <c r="H35" s="160"/>
+      <c r="C35" s="162" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D35" s="160" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E35" s="162" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F35" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="164" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H35" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I35" s="157" t="s">
         <v>26</v>
       </c>
@@ -10201,15 +10587,15 @@
       </c>
       <c r="K35" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>09:42</v>
       </c>
       <c r="L35" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>09:05</v>
       </c>
       <c r="M35" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>09:16</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="18" customHeight="1">
@@ -10221,10 +10607,18 @@
       </c>
       <c r="C36" s="162"/>
       <c r="D36" s="160"/>
-      <c r="E36" s="162"/>
-      <c r="F36" s="221"/>
-      <c r="G36" s="162"/>
-      <c r="H36" s="160"/>
+      <c r="E36" s="162" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="G36" s="162" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H36" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="I36" s="157" t="s">
         <v>25</v>
       </c>
@@ -10237,11 +10631,11 @@
       </c>
       <c r="L36" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>10:40</v>
       </c>
       <c r="M36" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>10:48</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="18" customHeight="1">
@@ -10285,10 +10679,18 @@
       </c>
       <c r="C38" s="162"/>
       <c r="D38" s="160"/>
-      <c r="E38" s="162"/>
-      <c r="F38" s="221"/>
-      <c r="G38" s="163"/>
-      <c r="H38" s="160"/>
+      <c r="E38" s="162" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F38" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="163">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="H38" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I38" s="157" t="s">
         <v>22</v>
       </c>
@@ -10301,11 +10703,11 @@
       </c>
       <c r="L38" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>12:05</v>
       </c>
       <c r="M38" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>12:23</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="18" customHeight="1">
@@ -10317,10 +10719,18 @@
       </c>
       <c r="C39" s="162"/>
       <c r="D39" s="160"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="221"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="160"/>
+      <c r="E39" s="162" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F39" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="G39" s="162" t="s">
+        <v>164</v>
+      </c>
+      <c r="H39" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="I39" s="157" t="s">
         <v>21</v>
       </c>
@@ -10333,11 +10743,11 @@
       </c>
       <c r="L39" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>13:40</v>
       </c>
       <c r="M39" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>13:58</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="18" customHeight="1">
@@ -10347,8 +10757,12 @@
       <c r="B40" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="161"/>
-      <c r="D40" s="160"/>
+      <c r="C40" s="161">
+        <v>0.59166666666666667</v>
+      </c>
+      <c r="D40" s="160" t="s">
+        <v>1143</v>
+      </c>
       <c r="E40" s="162"/>
       <c r="F40" s="221"/>
       <c r="G40" s="162"/>
@@ -10361,7 +10775,7 @@
       </c>
       <c r="K40" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14:12</v>
       </c>
       <c r="L40" s="151" t="str">
         <f t="shared" si="1"/>
@@ -10381,10 +10795,18 @@
       </c>
       <c r="C41" s="160"/>
       <c r="D41" s="160"/>
-      <c r="E41" s="162"/>
-      <c r="F41" s="221"/>
-      <c r="G41" s="162"/>
-      <c r="H41" s="160"/>
+      <c r="E41" s="162" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F41" s="221" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="162" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H41" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="I41" s="157" t="s">
         <v>18</v>
       </c>
@@ -10397,11 +10819,11 @@
       </c>
       <c r="L41" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>15:09</v>
       </c>
       <c r="M41" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>15:32</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="18" customHeight="1">
@@ -10413,8 +10835,12 @@
       </c>
       <c r="C42" s="162"/>
       <c r="D42" s="160"/>
-      <c r="E42" s="162"/>
-      <c r="F42" s="221"/>
+      <c r="E42" s="162" t="s">
+        <v>191</v>
+      </c>
+      <c r="F42" s="221" t="s">
+        <v>11</v>
+      </c>
       <c r="G42" s="164"/>
       <c r="H42" s="160"/>
       <c r="I42" s="157" t="s">
@@ -10429,7 +10855,7 @@
       </c>
       <c r="L42" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>16:36</v>
       </c>
       <c r="M42" s="151" t="str">
         <f t="shared" si="2"/>
@@ -10447,8 +10873,12 @@
       <c r="D43" s="160"/>
       <c r="E43" s="162"/>
       <c r="F43" s="221"/>
-      <c r="G43" s="162"/>
-      <c r="H43" s="160"/>
+      <c r="G43" s="162" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H43" s="160" t="s">
+        <v>4</v>
+      </c>
       <c r="I43" s="157" t="s">
         <v>15</v>
       </c>
@@ -10465,7 +10895,7 @@
       </c>
       <c r="M43" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>17:00</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="18" customHeight="1">
@@ -10475,12 +10905,24 @@
       <c r="B44" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="162"/>
-      <c r="D44" s="160"/>
-      <c r="E44" s="161"/>
-      <c r="F44" s="221"/>
-      <c r="G44" s="163"/>
-      <c r="H44" s="160"/>
+      <c r="C44" s="162" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D44" s="160" t="s">
+        <v>42</v>
+      </c>
+      <c r="E44" s="161">
+        <v>0.75624999999999998</v>
+      </c>
+      <c r="F44" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="163">
+        <v>0.77013888888888893</v>
+      </c>
+      <c r="H44" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I44" s="157" t="s">
         <v>12</v>
       </c>
@@ -10489,15 +10931,15 @@
       </c>
       <c r="K44" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18:25</v>
       </c>
       <c r="L44" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>18:09</v>
       </c>
       <c r="M44" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18:29</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="18" customHeight="1">
@@ -10509,10 +10951,18 @@
       </c>
       <c r="C45" s="162"/>
       <c r="D45" s="160"/>
-      <c r="E45" s="289"/>
-      <c r="F45" s="221"/>
-      <c r="G45" s="162"/>
-      <c r="H45" s="160"/>
+      <c r="E45" s="162" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" s="162" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H45" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I45" s="157" t="s">
         <v>10</v>
       </c>
@@ -10525,11 +10975,11 @@
       </c>
       <c r="L45" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>19:43</v>
       </c>
       <c r="M45" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>19:55</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="18" customHeight="1">
@@ -10571,12 +11021,24 @@
       <c r="B47" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="289"/>
-      <c r="D47" s="160"/>
-      <c r="E47" s="160"/>
-      <c r="F47" s="221"/>
-      <c r="G47" s="162"/>
-      <c r="H47" s="160"/>
+      <c r="C47" s="162" t="s">
+        <v>281</v>
+      </c>
+      <c r="D47" s="160" t="s">
+        <v>1663</v>
+      </c>
+      <c r="E47" s="161">
+        <v>0.88680555555555551</v>
+      </c>
+      <c r="F47" s="221" t="s">
+        <v>0</v>
+      </c>
+      <c r="G47" s="162" t="s">
+        <v>1488</v>
+      </c>
+      <c r="H47" s="160" t="s">
+        <v>13</v>
+      </c>
       <c r="I47" s="157" t="s">
         <v>6</v>
       </c>
@@ -10585,15 +11047,15 @@
       </c>
       <c r="K47" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>21:56</v>
       </c>
       <c r="L47" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>21:17</v>
       </c>
       <c r="M47" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>21:25</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="18" customHeight="1">
@@ -10605,8 +11067,12 @@
       </c>
       <c r="C48" s="162"/>
       <c r="D48" s="160"/>
-      <c r="E48" s="162"/>
-      <c r="F48" s="221"/>
+      <c r="E48" s="162" t="s">
+        <v>1674</v>
+      </c>
+      <c r="F48" s="221" t="s">
+        <v>0</v>
+      </c>
       <c r="G48" s="164"/>
       <c r="H48" s="160"/>
       <c r="I48" s="157" t="s">
@@ -10621,7 +11087,7 @@
       </c>
       <c r="L48" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>22:46</v>
       </c>
       <c r="M48" s="151" t="str">
         <f t="shared" si="2"/>
@@ -10639,8 +11105,12 @@
       <c r="D49" s="166"/>
       <c r="E49" s="167"/>
       <c r="F49" s="225"/>
-      <c r="G49" s="167"/>
-      <c r="H49" s="166"/>
+      <c r="G49" s="167" t="s">
+        <v>1489</v>
+      </c>
+      <c r="H49" s="166" t="s">
+        <v>13</v>
+      </c>
       <c r="I49" s="165" t="s">
         <v>3</v>
       </c>
@@ -10657,7 +11127,7 @@
       </c>
       <c r="M49" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>23:00</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="18" customHeight="1">
@@ -10669,10 +11139,18 @@
       </c>
       <c r="C50" s="170"/>
       <c r="D50" s="169"/>
-      <c r="E50" s="170"/>
-      <c r="F50" s="227"/>
-      <c r="G50" s="170"/>
-      <c r="H50" s="169"/>
+      <c r="E50" s="170" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="227" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="170" t="s">
+        <v>141</v>
+      </c>
+      <c r="H50" s="169" t="s">
+        <v>13</v>
+      </c>
       <c r="I50" s="168" t="s">
         <v>37</v>
       </c>
@@ -10685,11 +11163,11 @@
       </c>
       <c r="L50" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M50" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>00:00</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="18" customHeight="1">
@@ -10699,12 +11177,24 @@
       <c r="B51" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="172"/>
-      <c r="D51" s="171"/>
-      <c r="E51" s="172"/>
-      <c r="F51" s="229"/>
-      <c r="G51" s="172"/>
-      <c r="H51" s="171"/>
+      <c r="C51" s="172" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D51" s="171" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="172" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F51" s="229" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="172" t="s">
+        <v>636</v>
+      </c>
+      <c r="H51" s="171" t="s">
+        <v>13</v>
+      </c>
       <c r="I51" s="168" t="s">
         <v>36</v>
       </c>
@@ -10713,15 +11203,15 @@
       </c>
       <c r="K51" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>01:34</v>
       </c>
       <c r="L51" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>01:34</v>
       </c>
       <c r="M51" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>01:32</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="18" customHeight="1">
@@ -10765,10 +11255,18 @@
       </c>
       <c r="C53" s="172"/>
       <c r="D53" s="171"/>
-      <c r="E53" s="172"/>
-      <c r="F53" s="229"/>
-      <c r="G53" s="172"/>
-      <c r="H53" s="171"/>
+      <c r="E53" s="172" t="s">
+        <v>270</v>
+      </c>
+      <c r="F53" s="229" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="172" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H53" s="171" t="s">
+        <v>13</v>
+      </c>
       <c r="I53" s="168" t="s">
         <v>33</v>
       </c>
@@ -10781,11 +11279,11 @@
       </c>
       <c r="L53" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>03:08</v>
       </c>
       <c r="M53" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>03:07</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="18" customHeight="1">
@@ -10795,12 +11293,24 @@
       <c r="B54" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C54" s="172"/>
-      <c r="D54" s="171"/>
-      <c r="E54" s="172"/>
-      <c r="F54" s="229"/>
-      <c r="G54" s="172"/>
-      <c r="H54" s="171"/>
+      <c r="C54" s="172" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D54" s="171" t="s">
+        <v>899</v>
+      </c>
+      <c r="E54" s="172" t="s">
+        <v>1648</v>
+      </c>
+      <c r="F54" s="229" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G54" s="172" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H54" s="171" t="s">
+        <v>4</v>
+      </c>
       <c r="I54" s="168" t="s">
         <v>32</v>
       </c>
@@ -10809,15 +11319,15 @@
       </c>
       <c r="K54" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>04:51</v>
       </c>
       <c r="L54" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>04:41</v>
       </c>
       <c r="M54" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>04:41</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="18" customHeight="1">
@@ -10863,7 +11373,7 @@
         <v>77</v>
       </c>
       <c r="D56" s="171" t="s">
-        <v>1554</v>
+        <v>341</v>
       </c>
       <c r="E56" s="172" t="s">
         <v>77</v>
@@ -11079,12 +11589,24 @@
       <c r="B61" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C61" s="172"/>
-      <c r="D61" s="171"/>
-      <c r="E61" s="172"/>
-      <c r="F61" s="229"/>
-      <c r="G61" s="172"/>
-      <c r="H61" s="171"/>
+      <c r="C61" s="172" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D61" s="171" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="172" t="s">
+        <v>217</v>
+      </c>
+      <c r="F61" s="229" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="172" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H61" s="171" t="s">
+        <v>1650</v>
+      </c>
       <c r="I61" s="168" t="s">
         <v>23</v>
       </c>
@@ -11093,15 +11615,15 @@
       </c>
       <c r="K61" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>11:17</v>
       </c>
       <c r="L61" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>11:00</v>
       </c>
       <c r="M61" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>11:00</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="18" customHeight="1">
@@ -11113,10 +11635,18 @@
       </c>
       <c r="C62" s="172"/>
       <c r="D62" s="171"/>
-      <c r="E62" s="172"/>
-      <c r="F62" s="229"/>
-      <c r="G62" s="172"/>
-      <c r="H62" s="171"/>
+      <c r="E62" s="172" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" s="229" t="s">
+        <v>0</v>
+      </c>
+      <c r="G62" s="172" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H62" s="171" t="s">
+        <v>1652</v>
+      </c>
       <c r="I62" s="168" t="s">
         <v>22</v>
       </c>
@@ -11129,11 +11659,11 @@
       </c>
       <c r="L62" s="151" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>12:09</v>
       </c>
       <c r="M62" s="151" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>12:13</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="18" customHeight="1">
@@ -11146,16 +11676,16 @@
       <c r="C63" s="172"/>
       <c r="D63" s="171"/>
       <c r="E63" s="172" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F63" s="229" t="s">
-        <v>17</v>
+        <v>1657</v>
       </c>
       <c r="G63" s="172" t="s">
         <v>644</v>
       </c>
       <c r="H63" s="171" t="s">
-        <v>4</v>
+        <v>1650</v>
       </c>
       <c r="I63" s="168" t="s">
         <v>21</v>
@@ -11183,8 +11713,12 @@
       <c r="B64" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C64" s="172"/>
-      <c r="D64" s="171"/>
+      <c r="C64" s="172" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D64" s="171" t="s">
+        <v>1143</v>
+      </c>
       <c r="E64" s="172"/>
       <c r="F64" s="229"/>
       <c r="G64" s="172"/>
@@ -11197,7 +11731,7 @@
       </c>
       <c r="K64" s="151" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14:35</v>
       </c>
       <c r="L64" s="151" t="str">
         <f t="shared" si="1"/>
@@ -11221,13 +11755,13 @@
         <v>1110</v>
       </c>
       <c r="F65" s="229" t="s">
-        <v>17</v>
+        <v>1657</v>
       </c>
       <c r="G65" s="173" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="H65" s="171" t="s">
-        <v>13</v>
+        <v>1652</v>
       </c>
       <c r="I65" s="168" t="s">
         <v>18</v>
@@ -11261,7 +11795,7 @@
         <v>265</v>
       </c>
       <c r="F66" s="229" t="s">
-        <v>17</v>
+        <v>1657</v>
       </c>
       <c r="G66" s="172" t="s">
         <v>911</v>
@@ -11295,8 +11829,12 @@
       <c r="B67" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C67" s="173"/>
-      <c r="D67" s="171"/>
+      <c r="C67" s="173" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D67" s="171" t="s">
+        <v>1362</v>
+      </c>
       <c r="E67" s="172"/>
       <c r="F67" s="229"/>
       <c r="G67" s="173"/>
@@ -11309,7 +11847,7 @@
       </c>
       <c r="K67" s="151" t="str">
         <f t="shared" ref="K67:K130" si="3">IF($C67&lt;&gt;"",TEXT($C67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:37</v>
       </c>
       <c r="L67" s="151" t="str">
         <f t="shared" ref="L67:L130" si="4">IF($E67&lt;&gt;"",TEXT($E67,"HH:MM"),"")</f>
@@ -11336,7 +11874,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="172" t="s">
-        <v>220</v>
+        <v>1653</v>
       </c>
       <c r="H68" s="171" t="s">
         <v>13</v>
@@ -11357,7 +11895,7 @@
       </c>
       <c r="M68" s="151" t="str">
         <f t="shared" si="5"/>
-        <v>18:10</v>
+        <v>18:11</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="18" customHeight="1">
@@ -11373,7 +11911,7 @@
         <v>193</v>
       </c>
       <c r="F69" s="229" t="s">
-        <v>1097</v>
+        <v>27</v>
       </c>
       <c r="G69" s="172" t="s">
         <v>221</v>
@@ -11407,8 +11945,12 @@
       <c r="B70" s="171" t="s">
         <v>55</v>
       </c>
-      <c r="C70" s="172"/>
-      <c r="D70" s="172"/>
+      <c r="C70" s="172" t="s">
+        <v>913</v>
+      </c>
+      <c r="D70" s="172" t="s">
+        <v>1364</v>
+      </c>
       <c r="E70" s="172"/>
       <c r="F70" s="229"/>
       <c r="G70" s="173"/>
@@ -11421,7 +11963,7 @@
       </c>
       <c r="K70" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>20:38</v>
       </c>
       <c r="L70" s="151" t="str">
         <f t="shared" si="4"/>
@@ -11448,7 +11990,7 @@
         <v>11</v>
       </c>
       <c r="G71" s="172" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="H71" s="171" t="s">
         <v>13</v>
@@ -11482,7 +12024,7 @@
       <c r="C72" s="172"/>
       <c r="D72" s="171"/>
       <c r="E72" s="172" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="F72" s="229" t="s">
         <v>0</v>
@@ -11519,8 +12061,12 @@
       <c r="B73" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="C73" s="176"/>
-      <c r="D73" s="175"/>
+      <c r="C73" s="176" t="s">
+        <v>150</v>
+      </c>
+      <c r="D73" s="175" t="s">
+        <v>1664</v>
+      </c>
       <c r="E73" s="176"/>
       <c r="F73" s="233"/>
       <c r="G73" s="176"/>
@@ -11533,7 +12079,7 @@
       </c>
       <c r="K73" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>23:54</v>
       </c>
       <c r="L73" s="151" t="str">
         <f t="shared" si="4"/>
@@ -11553,8 +12099,12 @@
       </c>
       <c r="C74" s="179"/>
       <c r="D74" s="178"/>
-      <c r="E74" s="178"/>
-      <c r="F74" s="235"/>
+      <c r="E74" s="299">
+        <v>0</v>
+      </c>
+      <c r="F74" s="235" t="s">
+        <v>1657</v>
+      </c>
       <c r="G74" s="179" t="s">
         <v>141</v>
       </c>
@@ -11573,7 +12123,7 @@
       </c>
       <c r="L74" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M74" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11589,8 +12139,12 @@
       </c>
       <c r="C75" s="181"/>
       <c r="D75" s="180"/>
-      <c r="E75" s="181"/>
-      <c r="F75" s="237"/>
+      <c r="E75" s="181" t="s">
+        <v>269</v>
+      </c>
+      <c r="F75" s="237" t="s">
+        <v>27</v>
+      </c>
       <c r="G75" s="181" t="s">
         <v>949</v>
       </c>
@@ -11609,7 +12163,7 @@
       </c>
       <c r="L75" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>01:25</v>
       </c>
       <c r="M75" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11625,8 +12179,12 @@
       </c>
       <c r="C76" s="181"/>
       <c r="D76" s="180"/>
-      <c r="E76" s="181"/>
-      <c r="F76" s="237"/>
+      <c r="E76" s="181" t="s">
+        <v>648</v>
+      </c>
+      <c r="F76" s="237" t="s">
+        <v>27</v>
+      </c>
       <c r="G76" s="182" t="s">
         <v>648</v>
       </c>
@@ -11645,7 +12203,7 @@
       </c>
       <c r="L76" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>02:53</v>
       </c>
       <c r="M76" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11693,10 +12251,14 @@
       </c>
       <c r="C78" s="181"/>
       <c r="D78" s="180"/>
-      <c r="E78" s="181"/>
-      <c r="F78" s="237"/>
+      <c r="E78" s="181" t="s">
+        <v>223</v>
+      </c>
+      <c r="F78" s="237" t="s">
+        <v>0</v>
+      </c>
       <c r="G78" s="181" t="s">
-        <v>223</v>
+        <v>1654</v>
       </c>
       <c r="H78" s="180" t="s">
         <v>1099</v>
@@ -11713,11 +12275,11 @@
       </c>
       <c r="L78" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:20</v>
       </c>
       <c r="M78" s="151" t="str">
         <f t="shared" si="5"/>
-        <v>04:20</v>
+        <v>04:21</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="18" customHeight="1">
@@ -11732,7 +12294,7 @@
       <c r="E79" s="181"/>
       <c r="F79" s="237"/>
       <c r="G79" s="181" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="H79" s="180" t="s">
         <v>4</v>
@@ -11797,8 +12359,12 @@
       </c>
       <c r="C81" s="181"/>
       <c r="D81" s="180"/>
-      <c r="E81" s="181"/>
-      <c r="F81" s="237"/>
+      <c r="E81" s="181" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F81" s="237" t="s">
+        <v>0</v>
+      </c>
       <c r="G81" s="181" t="s">
         <v>250</v>
       </c>
@@ -11817,7 +12383,7 @@
       </c>
       <c r="L81" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:20</v>
       </c>
       <c r="M81" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11833,8 +12399,12 @@
       </c>
       <c r="C82" s="181"/>
       <c r="D82" s="180"/>
-      <c r="E82" s="181"/>
-      <c r="F82" s="237"/>
+      <c r="E82" s="181" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F82" s="237" t="s">
+        <v>27</v>
+      </c>
       <c r="G82" s="181" t="s">
         <v>313</v>
       </c>
@@ -11853,7 +12423,7 @@
       </c>
       <c r="L82" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>08:46</v>
       </c>
       <c r="M82" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11901,8 +12471,12 @@
       </c>
       <c r="C84" s="181"/>
       <c r="D84" s="180"/>
-      <c r="E84" s="181"/>
-      <c r="F84" s="237"/>
+      <c r="E84" s="181" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F84" s="237" t="s">
+        <v>1657</v>
+      </c>
       <c r="G84" s="181" t="s">
         <v>226</v>
       </c>
@@ -11921,7 +12495,7 @@
       </c>
       <c r="L84" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10:11</v>
       </c>
       <c r="M84" s="151" t="str">
         <f t="shared" si="5"/>
@@ -11935,10 +12509,18 @@
       <c r="B85" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="181"/>
-      <c r="D85" s="180"/>
-      <c r="E85" s="181"/>
-      <c r="F85" s="237"/>
+      <c r="C85" s="181" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D85" s="180" t="s">
+        <v>39</v>
+      </c>
+      <c r="E85" s="181" t="s">
+        <v>214</v>
+      </c>
+      <c r="F85" s="237" t="s">
+        <v>27</v>
+      </c>
       <c r="G85" s="181" t="s">
         <v>276</v>
       </c>
@@ -11953,11 +12535,11 @@
       </c>
       <c r="K85" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11:17</v>
       </c>
       <c r="L85" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>11:36</v>
       </c>
       <c r="M85" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12005,8 +12587,12 @@
       </c>
       <c r="C87" s="181"/>
       <c r="D87" s="180"/>
-      <c r="E87" s="181"/>
-      <c r="F87" s="237"/>
+      <c r="E87" s="181" t="s">
+        <v>809</v>
+      </c>
+      <c r="F87" s="237" t="s">
+        <v>1657</v>
+      </c>
       <c r="G87" s="181" t="s">
         <v>802</v>
       </c>
@@ -12025,7 +12611,7 @@
       </c>
       <c r="L87" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13:10</v>
       </c>
       <c r="M87" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12039,10 +12625,18 @@
       <c r="B88" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C88" s="181"/>
-      <c r="D88" s="180"/>
-      <c r="E88" s="181"/>
-      <c r="F88" s="237"/>
+      <c r="C88" s="181" t="s">
+        <v>608</v>
+      </c>
+      <c r="D88" s="180" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E88" s="181" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F88" s="237" t="s">
+        <v>0</v>
+      </c>
       <c r="G88" s="181" t="s">
         <v>156</v>
       </c>
@@ -12057,11 +12651,11 @@
       </c>
       <c r="K88" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>14:40</v>
       </c>
       <c r="L88" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14:45</v>
       </c>
       <c r="M88" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12109,8 +12703,12 @@
       </c>
       <c r="C90" s="181"/>
       <c r="D90" s="180"/>
-      <c r="E90" s="181"/>
-      <c r="F90" s="237"/>
+      <c r="E90" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="F90" s="237" t="s">
+        <v>11</v>
+      </c>
       <c r="G90" s="181" t="s">
         <v>798</v>
       </c>
@@ -12129,7 +12727,7 @@
       </c>
       <c r="L90" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>16:19</v>
       </c>
       <c r="M90" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12145,8 +12743,12 @@
       </c>
       <c r="C91" s="181"/>
       <c r="D91" s="180"/>
-      <c r="E91" s="181"/>
-      <c r="F91" s="237"/>
+      <c r="E91" s="181" t="s">
+        <v>1680</v>
+      </c>
+      <c r="F91" s="237" t="s">
+        <v>11</v>
+      </c>
       <c r="G91" s="181" t="s">
         <v>610</v>
       </c>
@@ -12165,7 +12767,7 @@
       </c>
       <c r="L91" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17:45</v>
       </c>
       <c r="M91" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12179,8 +12781,12 @@
       <c r="B92" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C92" s="181"/>
-      <c r="D92" s="180"/>
+      <c r="C92" s="181" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D92" s="180" t="s">
+        <v>1666</v>
+      </c>
       <c r="E92" s="181"/>
       <c r="F92" s="237"/>
       <c r="G92" s="182"/>
@@ -12193,7 +12799,7 @@
       </c>
       <c r="K92" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>18:02</v>
       </c>
       <c r="L92" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12213,8 +12819,12 @@
       </c>
       <c r="C93" s="180"/>
       <c r="D93" s="180"/>
-      <c r="E93" s="181"/>
-      <c r="F93" s="237"/>
+      <c r="E93" s="181" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F93" s="237" t="s">
+        <v>27</v>
+      </c>
       <c r="G93" s="181" t="s">
         <v>1257</v>
       </c>
@@ -12233,7 +12843,7 @@
       </c>
       <c r="L93" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>19:12</v>
       </c>
       <c r="M93" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12247,10 +12857,18 @@
       <c r="B94" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C94" s="181"/>
-      <c r="D94" s="180"/>
-      <c r="E94" s="181"/>
-      <c r="F94" s="237"/>
+      <c r="C94" s="181" t="s">
+        <v>1681</v>
+      </c>
+      <c r="D94" s="180" t="s">
+        <v>45</v>
+      </c>
+      <c r="E94" s="181" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F94" s="237" t="s">
+        <v>0</v>
+      </c>
       <c r="G94" s="181" t="s">
         <v>158</v>
       </c>
@@ -12265,11 +12883,11 @@
       </c>
       <c r="K94" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>20:33</v>
       </c>
       <c r="L94" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20:42</v>
       </c>
       <c r="M94" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12317,8 +12935,12 @@
       </c>
       <c r="C96" s="181"/>
       <c r="D96" s="180"/>
-      <c r="E96" s="181"/>
-      <c r="F96" s="237"/>
+      <c r="E96" s="181" t="s">
+        <v>961</v>
+      </c>
+      <c r="F96" s="237" t="s">
+        <v>0</v>
+      </c>
       <c r="G96" s="182" t="s">
         <v>961</v>
       </c>
@@ -12337,7 +12959,7 @@
       </c>
       <c r="L96" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>22:06</v>
       </c>
       <c r="M96" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12353,8 +12975,12 @@
       </c>
       <c r="C97" s="185"/>
       <c r="D97" s="184"/>
-      <c r="E97" s="185"/>
-      <c r="F97" s="240"/>
+      <c r="E97" s="185" t="s">
+        <v>139</v>
+      </c>
+      <c r="F97" s="240" t="s">
+        <v>1657</v>
+      </c>
       <c r="G97" s="185" t="s">
         <v>862</v>
       </c>
@@ -12373,7 +12999,7 @@
       </c>
       <c r="L97" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23:33</v>
       </c>
       <c r="M97" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12387,10 +13013,18 @@
       <c r="B98" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="C98" s="188"/>
-      <c r="D98" s="187"/>
-      <c r="E98" s="188"/>
-      <c r="F98" s="242"/>
+      <c r="C98" s="188" t="s">
+        <v>823</v>
+      </c>
+      <c r="D98" s="187" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E98" s="188" t="s">
+        <v>823</v>
+      </c>
+      <c r="F98" s="242" t="s">
+        <v>27</v>
+      </c>
       <c r="G98" s="188" t="s">
         <v>963</v>
       </c>
@@ -12405,11 +13039,11 @@
       </c>
       <c r="K98" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>00:57</v>
       </c>
       <c r="L98" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:57</v>
       </c>
       <c r="M98" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12457,8 +13091,12 @@
       </c>
       <c r="C100" s="190"/>
       <c r="D100" s="189"/>
-      <c r="E100" s="190"/>
-      <c r="F100" s="244"/>
+      <c r="E100" s="190" t="s">
+        <v>624</v>
+      </c>
+      <c r="F100" s="244" t="s">
+        <v>1657</v>
+      </c>
       <c r="G100" s="190" t="s">
         <v>806</v>
       </c>
@@ -12477,7 +13115,7 @@
       </c>
       <c r="L100" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>02:26</v>
       </c>
       <c r="M100" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12493,8 +13131,12 @@
       </c>
       <c r="C101" s="190"/>
       <c r="D101" s="189"/>
-      <c r="E101" s="190"/>
-      <c r="F101" s="244"/>
+      <c r="E101" s="190" t="s">
+        <v>298</v>
+      </c>
+      <c r="F101" s="244" t="s">
+        <v>27</v>
+      </c>
       <c r="G101" s="190" t="s">
         <v>925</v>
       </c>
@@ -12513,7 +13155,7 @@
       </c>
       <c r="L101" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>03:52</v>
       </c>
       <c r="M101" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12559,10 +13201,18 @@
       <c r="B103" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="297"/>
-      <c r="D103" s="189"/>
-      <c r="E103" s="190"/>
-      <c r="F103" s="244"/>
+      <c r="C103" s="297">
+        <v>0.21666666666666667</v>
+      </c>
+      <c r="D103" s="189" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E103" s="190" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F103" s="244" t="s">
+        <v>11</v>
+      </c>
       <c r="G103" s="190" t="s">
         <v>1518</v>
       </c>
@@ -12577,11 +13227,11 @@
       </c>
       <c r="K103" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>05:12</v>
       </c>
       <c r="L103" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:19</v>
       </c>
       <c r="M103" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12597,8 +13247,12 @@
       </c>
       <c r="C104" s="190"/>
       <c r="D104" s="189"/>
-      <c r="E104" s="190"/>
-      <c r="F104" s="244"/>
+      <c r="E104" s="190" t="s">
+        <v>941</v>
+      </c>
+      <c r="F104" s="244" t="s">
+        <v>0</v>
+      </c>
       <c r="G104" s="190"/>
       <c r="H104" s="189"/>
       <c r="I104" s="186" t="s">
@@ -12613,7 +13267,7 @@
       </c>
       <c r="L104" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>06:53</v>
       </c>
       <c r="M104" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12663,10 +13317,18 @@
       <c r="B106" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C106" s="190"/>
-      <c r="D106" s="189"/>
-      <c r="E106" s="190"/>
-      <c r="F106" s="244"/>
+      <c r="C106" s="190" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D106" s="189" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E106" s="190" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F106" s="244" t="s">
+        <v>1657</v>
+      </c>
       <c r="G106" s="190" t="s">
         <v>1174</v>
       </c>
@@ -12681,11 +13343,11 @@
       </c>
       <c r="K106" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>08:04</v>
       </c>
       <c r="L106" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>08:19</v>
       </c>
       <c r="M106" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12701,8 +13363,12 @@
       </c>
       <c r="C107" s="190"/>
       <c r="D107" s="189"/>
-      <c r="E107" s="189"/>
-      <c r="F107" s="244"/>
+      <c r="E107" s="297">
+        <v>0.41041666666666665</v>
+      </c>
+      <c r="F107" s="244" t="s">
+        <v>0</v>
+      </c>
       <c r="G107" s="190"/>
       <c r="H107" s="189"/>
       <c r="I107" s="186" t="s">
@@ -12717,7 +13383,7 @@
       </c>
       <c r="L107" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>09:51</v>
       </c>
       <c r="M107" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12769,10 +13435,14 @@
       </c>
       <c r="C109" s="190"/>
       <c r="D109" s="189"/>
-      <c r="E109" s="190"/>
-      <c r="F109" s="244"/>
+      <c r="E109" s="190" t="s">
+        <v>834</v>
+      </c>
+      <c r="F109" s="244" t="s">
+        <v>27</v>
+      </c>
       <c r="G109" s="190" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="H109" s="189" t="s">
         <v>13</v>
@@ -12789,7 +13459,7 @@
       </c>
       <c r="L109" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>11:23</v>
       </c>
       <c r="M109" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12803,10 +13473,18 @@
       <c r="B110" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C110" s="189"/>
-      <c r="D110" s="189"/>
-      <c r="E110" s="190"/>
-      <c r="F110" s="244"/>
+      <c r="C110" s="297">
+        <v>0.51875000000000004</v>
+      </c>
+      <c r="D110" s="189" t="s">
+        <v>64</v>
+      </c>
+      <c r="E110" s="190" t="s">
+        <v>87</v>
+      </c>
+      <c r="F110" s="244" t="s">
+        <v>11</v>
+      </c>
       <c r="G110" s="190"/>
       <c r="H110" s="189"/>
       <c r="I110" s="186" t="s">
@@ -12817,11 +13495,11 @@
       </c>
       <c r="K110" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12:27</v>
       </c>
       <c r="L110" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12:48</v>
       </c>
       <c r="M110" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12873,8 +13551,12 @@
       </c>
       <c r="C112" s="190"/>
       <c r="D112" s="189"/>
-      <c r="E112" s="190"/>
-      <c r="F112" s="244"/>
+      <c r="E112" s="190" t="s">
+        <v>116</v>
+      </c>
+      <c r="F112" s="244" t="s">
+        <v>0</v>
+      </c>
       <c r="G112" s="190" t="s">
         <v>1203</v>
       </c>
@@ -12893,7 +13575,7 @@
       </c>
       <c r="L112" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14:18</v>
       </c>
       <c r="M112" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12909,8 +13591,12 @@
       </c>
       <c r="C113" s="190"/>
       <c r="D113" s="189"/>
-      <c r="E113" s="190"/>
-      <c r="F113" s="244"/>
+      <c r="E113" s="190" t="s">
+        <v>971</v>
+      </c>
+      <c r="F113" s="244" t="s">
+        <v>27</v>
+      </c>
       <c r="G113" s="191"/>
       <c r="H113" s="189"/>
       <c r="I113" s="186" t="s">
@@ -12925,7 +13611,7 @@
       </c>
       <c r="L113" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15:43</v>
       </c>
       <c r="M113" s="151" t="str">
         <f t="shared" si="5"/>
@@ -12939,8 +13625,12 @@
       <c r="B114" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C114" s="190"/>
-      <c r="D114" s="189"/>
+      <c r="C114" s="190" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D114" s="189" t="s">
+        <v>1369</v>
+      </c>
       <c r="E114" s="190"/>
       <c r="F114" s="244"/>
       <c r="G114" s="190" t="s">
@@ -12957,7 +13647,7 @@
       </c>
       <c r="K114" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>16:10</v>
       </c>
       <c r="L114" s="151" t="str">
         <f t="shared" si="4"/>
@@ -12977,8 +13667,12 @@
       </c>
       <c r="C115" s="190"/>
       <c r="D115" s="189"/>
-      <c r="E115" s="190"/>
-      <c r="F115" s="244"/>
+      <c r="E115" s="190" t="s">
+        <v>666</v>
+      </c>
+      <c r="F115" s="244" t="s">
+        <v>0</v>
+      </c>
       <c r="G115" s="190" t="s">
         <v>1036</v>
       </c>
@@ -12997,7 +13691,7 @@
       </c>
       <c r="L115" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>17:16</v>
       </c>
       <c r="M115" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13013,8 +13707,12 @@
       </c>
       <c r="C116" s="189"/>
       <c r="D116" s="189"/>
-      <c r="E116" s="190"/>
-      <c r="F116" s="244"/>
+      <c r="E116" s="190" t="s">
+        <v>667</v>
+      </c>
+      <c r="F116" s="244" t="s">
+        <v>27</v>
+      </c>
       <c r="G116" s="190"/>
       <c r="H116" s="189"/>
       <c r="I116" s="186" t="s">
@@ -13029,7 +13727,7 @@
       </c>
       <c r="L116" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18:44</v>
       </c>
       <c r="M116" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13043,8 +13741,12 @@
       <c r="B117" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C117" s="190"/>
-      <c r="D117" s="189"/>
+      <c r="C117" s="190" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D117" s="189" t="s">
+        <v>1362</v>
+      </c>
       <c r="E117" s="190"/>
       <c r="F117" s="244"/>
       <c r="G117" s="190" t="s">
@@ -13061,7 +13763,7 @@
       </c>
       <c r="K117" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>19:55</v>
       </c>
       <c r="L117" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13081,10 +13783,14 @@
       </c>
       <c r="C118" s="190"/>
       <c r="D118" s="189"/>
-      <c r="E118" s="190"/>
-      <c r="F118" s="244"/>
+      <c r="E118" s="190" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F118" s="244" t="s">
+        <v>27</v>
+      </c>
       <c r="G118" s="190" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="H118" s="189" t="s">
         <v>13</v>
@@ -13101,7 +13807,7 @@
       </c>
       <c r="L118" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20:13</v>
       </c>
       <c r="M118" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13117,8 +13823,12 @@
       </c>
       <c r="C119" s="189"/>
       <c r="D119" s="189"/>
-      <c r="E119" s="190"/>
-      <c r="F119" s="244"/>
+      <c r="E119" s="190" t="s">
+        <v>1685</v>
+      </c>
+      <c r="F119" s="244" t="s">
+        <v>1657</v>
+      </c>
       <c r="G119" s="190"/>
       <c r="H119" s="189"/>
       <c r="I119" s="186" t="s">
@@ -13133,7 +13843,7 @@
       </c>
       <c r="L119" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>21:46</v>
       </c>
       <c r="M119" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13147,8 +13857,12 @@
       <c r="B120" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="C120" s="190"/>
-      <c r="D120" s="189"/>
+      <c r="C120" s="190" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D120" s="189" t="s">
+        <v>1143</v>
+      </c>
       <c r="E120" s="190"/>
       <c r="F120" s="244"/>
       <c r="G120" s="190" t="s">
@@ -13165,7 +13879,7 @@
       </c>
       <c r="K120" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>22:56</v>
       </c>
       <c r="L120" s="151" t="str">
         <f t="shared" si="4"/>
@@ -13185,10 +13899,14 @@
       </c>
       <c r="C121" s="194"/>
       <c r="D121" s="193"/>
-      <c r="E121" s="194"/>
-      <c r="F121" s="247"/>
+      <c r="E121" s="194" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F121" s="247" t="s">
+        <v>0</v>
+      </c>
       <c r="G121" s="194" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="H121" s="193" t="s">
         <v>4</v>
@@ -13205,7 +13923,7 @@
       </c>
       <c r="L121" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23:15</v>
       </c>
       <c r="M121" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13221,8 +13939,12 @@
       </c>
       <c r="C122" s="197"/>
       <c r="D122" s="196"/>
-      <c r="E122" s="197"/>
-      <c r="F122" s="249"/>
+      <c r="E122" s="197" t="s">
+        <v>141</v>
+      </c>
+      <c r="F122" s="249" t="s">
+        <v>27</v>
+      </c>
       <c r="G122" s="197"/>
       <c r="H122" s="196"/>
       <c r="I122" s="195" t="s">
@@ -13237,7 +13959,7 @@
       </c>
       <c r="L122" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M122" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13361,8 +14083,12 @@
       </c>
       <c r="C126" s="199"/>
       <c r="D126" s="198"/>
-      <c r="E126" s="199"/>
-      <c r="F126" s="251"/>
+      <c r="E126" s="199" t="s">
+        <v>784</v>
+      </c>
+      <c r="F126" s="251" t="s">
+        <v>27</v>
+      </c>
       <c r="G126" s="200"/>
       <c r="H126" s="198"/>
       <c r="I126" s="195" t="s">
@@ -13377,7 +14103,7 @@
       </c>
       <c r="L126" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:24</v>
       </c>
       <c r="M126" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13393,8 +14119,12 @@
       </c>
       <c r="C127" s="199"/>
       <c r="D127" s="198"/>
-      <c r="E127" s="199"/>
-      <c r="F127" s="251"/>
+      <c r="E127" s="199" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F127" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G127" s="199" t="s">
         <v>807</v>
       </c>
@@ -13413,7 +14143,7 @@
       </c>
       <c r="L127" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:54</v>
       </c>
       <c r="M127" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13459,10 +14189,18 @@
       <c r="B129" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C129" s="198"/>
-      <c r="D129" s="198"/>
-      <c r="E129" s="199"/>
-      <c r="F129" s="251"/>
+      <c r="C129" s="201">
+        <v>0.29375000000000001</v>
+      </c>
+      <c r="D129" s="198" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E129" s="199" t="s">
+        <v>590</v>
+      </c>
+      <c r="F129" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G129" s="200" t="s">
         <v>660</v>
       </c>
@@ -13477,11 +14215,11 @@
       </c>
       <c r="K129" s="151" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>07:03</v>
       </c>
       <c r="L129" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:21</v>
       </c>
       <c r="M129" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13497,8 +14235,12 @@
       </c>
       <c r="C130" s="199"/>
       <c r="D130" s="198"/>
-      <c r="E130" s="199"/>
-      <c r="F130" s="251"/>
+      <c r="E130" s="199" t="s">
+        <v>1687</v>
+      </c>
+      <c r="F130" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G130" s="199" t="s">
         <v>1028</v>
       </c>
@@ -13517,7 +14259,7 @@
       </c>
       <c r="L130" s="151" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>08:53</v>
       </c>
       <c r="M130" s="151" t="str">
         <f t="shared" si="5"/>
@@ -13563,10 +14305,18 @@
       <c r="B132" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C132" s="199"/>
-      <c r="D132" s="198"/>
-      <c r="E132" s="199"/>
-      <c r="F132" s="251"/>
+      <c r="C132" s="199" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D132" s="198" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E132" s="199" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F132" s="251" t="s">
+        <v>11</v>
+      </c>
       <c r="G132" s="200" t="s">
         <v>833</v>
       </c>
@@ -13581,11 +14331,11 @@
       </c>
       <c r="K132" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>10:38</v>
       </c>
       <c r="L132" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>10:20</v>
       </c>
       <c r="M132" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13601,10 +14351,14 @@
       </c>
       <c r="C133" s="198"/>
       <c r="D133" s="198"/>
-      <c r="E133" s="199"/>
-      <c r="F133" s="251"/>
+      <c r="E133" s="199" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F133" s="251" t="s">
+        <v>27</v>
+      </c>
       <c r="G133" s="199" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="H133" s="198" t="s">
         <v>13</v>
@@ -13621,7 +14375,7 @@
       </c>
       <c r="L133" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>11:45</v>
       </c>
       <c r="M133" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13669,8 +14423,12 @@
       </c>
       <c r="C135" s="201"/>
       <c r="D135" s="198"/>
-      <c r="E135" s="199"/>
-      <c r="F135" s="251"/>
+      <c r="E135" s="199" t="s">
+        <v>277</v>
+      </c>
+      <c r="F135" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G135" s="200" t="s">
         <v>1510</v>
       </c>
@@ -13689,7 +14447,7 @@
       </c>
       <c r="L135" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13:14</v>
       </c>
       <c r="M135" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13703,10 +14461,18 @@
       <c r="B136" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C136" s="199"/>
-      <c r="D136" s="198"/>
-      <c r="E136" s="199"/>
-      <c r="F136" s="251"/>
+      <c r="C136" s="199" t="s">
+        <v>839</v>
+      </c>
+      <c r="D136" s="198" t="s">
+        <v>41</v>
+      </c>
+      <c r="E136" s="199" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F136" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G136" s="199" t="s">
         <v>1539</v>
       </c>
@@ -13721,11 +14487,11 @@
       </c>
       <c r="K136" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>14:19</v>
       </c>
       <c r="L136" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>14:44</v>
       </c>
       <c r="M136" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13773,8 +14539,12 @@
       </c>
       <c r="C138" s="198"/>
       <c r="D138" s="198"/>
-      <c r="E138" s="199"/>
-      <c r="F138" s="251"/>
+      <c r="E138" s="199" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F138" s="251" t="s">
+        <v>27</v>
+      </c>
       <c r="G138" s="199" t="s">
         <v>304</v>
       </c>
@@ -13793,7 +14563,7 @@
       </c>
       <c r="L138" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>16:10</v>
       </c>
       <c r="M138" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13807,10 +14577,18 @@
       <c r="B139" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C139" s="199"/>
-      <c r="D139" s="198"/>
-      <c r="E139" s="199"/>
-      <c r="F139" s="251"/>
+      <c r="C139" s="199" t="s">
+        <v>788</v>
+      </c>
+      <c r="D139" s="198" t="s">
+        <v>46</v>
+      </c>
+      <c r="E139" s="199" t="s">
+        <v>318</v>
+      </c>
+      <c r="F139" s="251" t="s">
+        <v>27</v>
+      </c>
       <c r="G139" s="199" t="s">
         <v>1513</v>
       </c>
@@ -13825,11 +14603,11 @@
       </c>
       <c r="K139" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>17:54</v>
       </c>
       <c r="L139" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>17:44</v>
       </c>
       <c r="M139" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13877,8 +14655,12 @@
       </c>
       <c r="C141" s="199"/>
       <c r="D141" s="198"/>
-      <c r="E141" s="199"/>
-      <c r="F141" s="251"/>
+      <c r="E141" s="199" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F141" s="251" t="s">
+        <v>27</v>
+      </c>
       <c r="G141" s="199" t="s">
         <v>132</v>
       </c>
@@ -13897,7 +14679,7 @@
       </c>
       <c r="L141" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>19:11</v>
       </c>
       <c r="M141" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13911,10 +14693,18 @@
       <c r="B142" s="198" t="s">
         <v>38</v>
       </c>
-      <c r="C142" s="199"/>
-      <c r="D142" s="198"/>
-      <c r="E142" s="199"/>
-      <c r="F142" s="251"/>
+      <c r="C142" s="199" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D142" s="198" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E142" s="199" t="s">
+        <v>913</v>
+      </c>
+      <c r="F142" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G142" s="199" t="s">
         <v>111</v>
       </c>
@@ -13929,11 +14719,11 @@
       </c>
       <c r="K142" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>20:43</v>
       </c>
       <c r="L142" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20:38</v>
       </c>
       <c r="M142" s="151" t="str">
         <f t="shared" si="8"/>
@@ -13981,8 +14771,12 @@
       </c>
       <c r="C144" s="199"/>
       <c r="D144" s="198"/>
-      <c r="E144" s="199"/>
-      <c r="F144" s="251"/>
+      <c r="E144" s="199" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F144" s="251" t="s">
+        <v>1657</v>
+      </c>
       <c r="G144" s="199" t="s">
         <v>804</v>
       </c>
@@ -14001,7 +14795,7 @@
       </c>
       <c r="L144" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>22:12</v>
       </c>
       <c r="M144" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14017,8 +14811,12 @@
       </c>
       <c r="C145" s="204"/>
       <c r="D145" s="203"/>
-      <c r="E145" s="204"/>
-      <c r="F145" s="255"/>
+      <c r="E145" s="204" t="s">
+        <v>805</v>
+      </c>
+      <c r="F145" s="255" t="s">
+        <v>11</v>
+      </c>
       <c r="G145" s="204" t="s">
         <v>981</v>
       </c>
@@ -14037,7 +14835,7 @@
       </c>
       <c r="L145" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23:40</v>
       </c>
       <c r="M145" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14053,8 +14851,12 @@
       </c>
       <c r="C146" s="206"/>
       <c r="D146" s="206"/>
-      <c r="E146" s="207"/>
-      <c r="F146" s="257"/>
+      <c r="E146" s="207" t="s">
+        <v>799</v>
+      </c>
+      <c r="F146" s="257" t="s">
+        <v>27</v>
+      </c>
       <c r="G146" s="207"/>
       <c r="H146" s="206"/>
       <c r="I146" s="205" t="s">
@@ -14069,7 +14871,7 @@
       </c>
       <c r="L146" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>00:59</v>
       </c>
       <c r="M146" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14121,10 +14923,14 @@
       </c>
       <c r="C148" s="209"/>
       <c r="D148" s="208"/>
-      <c r="E148" s="209"/>
-      <c r="F148" s="259"/>
+      <c r="E148" s="209" t="s">
+        <v>624</v>
+      </c>
+      <c r="F148" s="259" t="s">
+        <v>27</v>
+      </c>
       <c r="G148" s="209" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="H148" s="208" t="s">
         <v>4</v>
@@ -14141,7 +14947,7 @@
       </c>
       <c r="L148" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>02:26</v>
       </c>
       <c r="M148" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14155,8 +14961,12 @@
       <c r="B149" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C149" s="209"/>
-      <c r="D149" s="208"/>
+      <c r="C149" s="209" t="s">
+        <v>120</v>
+      </c>
+      <c r="D149" s="208" t="s">
+        <v>34</v>
+      </c>
       <c r="E149" s="209"/>
       <c r="F149" s="259"/>
       <c r="G149" s="210"/>
@@ -14169,7 +14979,7 @@
       </c>
       <c r="K149" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>03:26</v>
       </c>
       <c r="L149" s="151" t="str">
         <f t="shared" si="7"/>
@@ -14225,7 +15035,7 @@
       </c>
       <c r="C151" s="209"/>
       <c r="D151" s="208"/>
-      <c r="E151" s="292"/>
+      <c r="E151" s="209"/>
       <c r="F151" s="259"/>
       <c r="G151" s="209" t="s">
         <v>616</v>
@@ -14259,9 +15069,9 @@
       <c r="B152" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C152" s="292"/>
+      <c r="C152" s="209"/>
       <c r="D152" s="208"/>
-      <c r="E152" s="292"/>
+      <c r="E152" s="209"/>
       <c r="F152" s="259"/>
       <c r="G152" s="209" t="s">
         <v>828</v>
@@ -14297,8 +15107,12 @@
       </c>
       <c r="C153" s="209"/>
       <c r="D153" s="208"/>
-      <c r="E153" s="209"/>
-      <c r="F153" s="259"/>
+      <c r="E153" s="209" t="s">
+        <v>205</v>
+      </c>
+      <c r="F153" s="259" t="s">
+        <v>0</v>
+      </c>
       <c r="G153" s="210"/>
       <c r="H153" s="208"/>
       <c r="I153" s="205" t="s">
@@ -14313,7 +15127,7 @@
       </c>
       <c r="L153" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>07:06</v>
       </c>
       <c r="M153" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14329,8 +15143,12 @@
       </c>
       <c r="C154" s="209"/>
       <c r="D154" s="208"/>
-      <c r="E154" s="209"/>
-      <c r="F154" s="259"/>
+      <c r="E154" s="209" t="s">
+        <v>808</v>
+      </c>
+      <c r="F154" s="259" t="s">
+        <v>1657</v>
+      </c>
       <c r="G154" s="209" t="s">
         <v>1189</v>
       </c>
@@ -14349,7 +15167,7 @@
       </c>
       <c r="L154" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>08:38</v>
       </c>
       <c r="M154" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14363,12 +15181,16 @@
       <c r="B155" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C155" s="209"/>
-      <c r="D155" s="208"/>
+      <c r="C155" s="209" t="s">
+        <v>967</v>
+      </c>
+      <c r="D155" s="208" t="s">
+        <v>1660</v>
+      </c>
       <c r="E155" s="209"/>
       <c r="F155" s="259"/>
       <c r="G155" s="210" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="H155" s="208" t="s">
         <v>13</v>
@@ -14381,7 +15203,7 @@
       </c>
       <c r="K155" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>09:43</v>
       </c>
       <c r="L155" s="151" t="str">
         <f t="shared" si="7"/>
@@ -14401,8 +15223,12 @@
       </c>
       <c r="C156" s="209"/>
       <c r="D156" s="208"/>
-      <c r="E156" s="209"/>
-      <c r="F156" s="259"/>
+      <c r="E156" s="209" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F156" s="259" t="s">
+        <v>1657</v>
+      </c>
       <c r="G156" s="209"/>
       <c r="H156" s="208"/>
       <c r="I156" s="205" t="s">
@@ -14417,7 +15243,7 @@
       </c>
       <c r="L156" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>10:13</v>
       </c>
       <c r="M156" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14433,10 +15259,14 @@
       </c>
       <c r="C157" s="209"/>
       <c r="D157" s="208"/>
-      <c r="E157" s="209"/>
-      <c r="F157" s="259"/>
+      <c r="E157" s="209" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F157" s="259" t="s">
+        <v>1657</v>
+      </c>
       <c r="G157" s="209" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="H157" s="208" t="s">
         <v>13</v>
@@ -14453,7 +15283,7 @@
       </c>
       <c r="L157" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>11:40</v>
       </c>
       <c r="M157" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14467,8 +15297,12 @@
       <c r="B158" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C158" s="209"/>
-      <c r="D158" s="208"/>
+      <c r="C158" s="209" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D158" s="208" t="s">
+        <v>64</v>
+      </c>
       <c r="E158" s="209"/>
       <c r="F158" s="259"/>
       <c r="G158" s="209" t="s">
@@ -14485,7 +15319,7 @@
       </c>
       <c r="K158" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>12:44</v>
       </c>
       <c r="L158" s="151" t="str">
         <f t="shared" si="7"/>
@@ -14505,8 +15339,12 @@
       </c>
       <c r="C159" s="209"/>
       <c r="D159" s="208"/>
-      <c r="E159" s="209"/>
-      <c r="F159" s="259"/>
+      <c r="E159" s="209" t="s">
+        <v>607</v>
+      </c>
+      <c r="F159" s="259" t="s">
+        <v>0</v>
+      </c>
       <c r="G159" s="209"/>
       <c r="H159" s="208"/>
       <c r="I159" s="205" t="s">
@@ -14521,7 +15359,7 @@
       </c>
       <c r="L159" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13:12</v>
       </c>
       <c r="M159" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14537,10 +15375,14 @@
       </c>
       <c r="C160" s="209"/>
       <c r="D160" s="208"/>
-      <c r="E160" s="209"/>
-      <c r="F160" s="259"/>
+      <c r="E160" s="209" t="s">
+        <v>608</v>
+      </c>
+      <c r="F160" s="259" t="s">
+        <v>0</v>
+      </c>
       <c r="G160" s="209" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="H160" s="208" t="s">
         <v>4</v>
@@ -14557,7 +15399,7 @@
       </c>
       <c r="L160" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>14:40</v>
       </c>
       <c r="M160" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14607,10 +15449,18 @@
       <c r="B162" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C162" s="209"/>
-      <c r="D162" s="208"/>
-      <c r="E162" s="209"/>
-      <c r="F162" s="259"/>
+      <c r="C162" s="209" t="s">
+        <v>646</v>
+      </c>
+      <c r="D162" s="208" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="209" t="s">
+        <v>798</v>
+      </c>
+      <c r="F162" s="259" t="s">
+        <v>27</v>
+      </c>
       <c r="G162" s="209"/>
       <c r="H162" s="208"/>
       <c r="I162" s="205" t="s">
@@ -14621,11 +15471,11 @@
       </c>
       <c r="K162" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16:33</v>
       </c>
       <c r="L162" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>16:12</v>
       </c>
       <c r="M162" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14641,8 +15491,12 @@
       </c>
       <c r="C163" s="209"/>
       <c r="D163" s="208"/>
-      <c r="E163" s="209"/>
-      <c r="F163" s="259"/>
+      <c r="E163" s="209" t="s">
+        <v>137</v>
+      </c>
+      <c r="F163" s="259" t="s">
+        <v>1657</v>
+      </c>
       <c r="G163" s="209" t="s">
         <v>944</v>
       </c>
@@ -14661,7 +15515,7 @@
       </c>
       <c r="L163" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>17:40</v>
       </c>
       <c r="M163" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14680,7 +15534,7 @@
       <c r="E164" s="209"/>
       <c r="F164" s="259"/>
       <c r="G164" s="209" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="H164" s="208" t="s">
         <v>13</v>
@@ -14713,8 +15567,12 @@
       </c>
       <c r="C165" s="209"/>
       <c r="D165" s="208"/>
-      <c r="E165" s="209"/>
-      <c r="F165" s="259"/>
+      <c r="E165" s="209" t="s">
+        <v>818</v>
+      </c>
+      <c r="F165" s="259" t="s">
+        <v>27</v>
+      </c>
       <c r="G165" s="209"/>
       <c r="H165" s="208"/>
       <c r="I165" s="205" t="s">
@@ -14729,7 +15587,7 @@
       </c>
       <c r="L165" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>19:06</v>
       </c>
       <c r="M165" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14743,10 +15601,18 @@
       <c r="B166" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="C166" s="211"/>
-      <c r="D166" s="208"/>
-      <c r="E166" s="209"/>
-      <c r="F166" s="259"/>
+      <c r="C166" s="211" t="s">
+        <v>320</v>
+      </c>
+      <c r="D166" s="208" t="s">
+        <v>902</v>
+      </c>
+      <c r="E166" s="209" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F166" s="259" t="s">
+        <v>11</v>
+      </c>
       <c r="G166" s="209" t="s">
         <v>634</v>
       </c>
@@ -14761,11 +15627,11 @@
       </c>
       <c r="K166" s="151" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>20:44</v>
       </c>
       <c r="L166" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20:33</v>
       </c>
       <c r="M166" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14851,10 +15717,14 @@
       </c>
       <c r="C169" s="209"/>
       <c r="D169" s="208"/>
-      <c r="E169" s="209"/>
-      <c r="F169" s="259"/>
+      <c r="E169" s="209" t="s">
+        <v>1691</v>
+      </c>
+      <c r="F169" s="259" t="s">
+        <v>11</v>
+      </c>
       <c r="G169" s="209" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="H169" s="208"/>
       <c r="I169" s="205" t="s">
@@ -14869,7 +15739,7 @@
       </c>
       <c r="L169" s="151" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23:30</v>
       </c>
       <c r="M169" s="151" t="str">
         <f t="shared" si="8"/>
@@ -14879,13 +15749,13 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="E1:E73 C1:C1048576 G1:G1048576 H12 D70 E75:E1048576">
+  <conditionalFormatting sqref="E1:E7 C1:C1048576 G1:G1048576 E9:E73 H12 D70 E75:E1048576">
     <cfRule type="containsText" dxfId="42" priority="9" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H1048576 D71:D1048576 E74">
-    <cfRule type="containsText" dxfId="41" priority="3" operator="containsText" text="例行維護中">
+  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 E8 H13:H1048576 D71:D1048576 E74">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20965,22 +21835,22 @@
   <autoFilter ref="B1:H169" xr:uid="{E5721A58-BDCF-4001-9246-B563B75376FD}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26947,22 +27817,22 @@
   <autoFilter ref="B1:H169" xr:uid="{6AC87A79-C922-4D7F-AA03-A940ADDE0DDA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E107">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E107)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F106 D1:D1048576 H1:H1048576 F108:F1048576">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F107">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",F107)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34525,17 +35395,17 @@
   <autoFilter ref="B1:K169" xr:uid="{F2D04C18-0E97-4E28-9FC2-690F31DD96B0}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:L1048576">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:K1048576">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34907,7 +35777,7 @@
         <v>627</v>
       </c>
       <c r="D10" s="149" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="E10" s="150" t="s">
         <v>274</v>
@@ -35023,7 +35893,7 @@
         <v>957</v>
       </c>
       <c r="D13" s="149" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="E13" s="150"/>
       <c r="F13" s="149"/>
@@ -35139,7 +36009,7 @@
         <v>0.59305555555555556</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="E16" s="150"/>
       <c r="F16" s="149"/>
@@ -35255,7 +36125,7 @@
         <v>0.74305555555555558</v>
       </c>
       <c r="D19" s="149" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="E19" s="150"/>
       <c r="F19" s="149"/>
@@ -35336,7 +36206,7 @@
         <v>1396</v>
       </c>
       <c r="G21" s="148" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H21" s="149" t="s">
         <v>1403</v>
@@ -35371,7 +36241,7 @@
         <v>1359</v>
       </c>
       <c r="D22" s="149" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="E22" s="150"/>
       <c r="F22" s="149"/>
@@ -35520,7 +36390,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="293" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D26" s="158" t="s">
         <v>1424</v>
@@ -35639,7 +36509,7 @@
         <v>0.13750000000000001</v>
       </c>
       <c r="D29" s="160" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="E29" s="162" t="s">
         <v>259</v>
@@ -35791,7 +36661,7 @@
         <v>273</v>
       </c>
       <c r="D33" s="160" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="E33" s="162" t="s">
         <v>1508</v>
@@ -36258,7 +37128,7 @@
       <c r="C45" s="162"/>
       <c r="D45" s="160"/>
       <c r="E45" s="289" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="F45" s="160" t="s">
         <v>1018</v>
@@ -36332,7 +37202,7 @@
         <v>58</v>
       </c>
       <c r="C47" s="289" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D47" s="160" t="s">
         <v>453</v>
@@ -36370,7 +37240,7 @@
       <c r="C48" s="162"/>
       <c r="D48" s="160"/>
       <c r="E48" s="162" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="F48" s="160" t="s">
         <v>1396</v>
@@ -36410,7 +37280,7 @@
       <c r="C49" s="166"/>
       <c r="D49" s="166"/>
       <c r="E49" s="167" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="F49" s="166" t="s">
         <v>1396</v>
@@ -36487,7 +37357,7 @@
         <v>1558</v>
       </c>
       <c r="D51" s="171" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E51" s="172"/>
       <c r="F51" s="171"/>
@@ -36566,7 +37436,7 @@
       <c r="C53" s="172"/>
       <c r="D53" s="171"/>
       <c r="E53" s="172" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="F53" s="171" t="s">
         <v>1016</v>
@@ -36642,7 +37512,7 @@
         <v>471</v>
       </c>
       <c r="E55" s="172" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="F55" s="171" t="s">
         <v>1396</v>
@@ -36814,10 +37684,10 @@
       <c r="C59" s="172"/>
       <c r="D59" s="171"/>
       <c r="E59" s="298" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="F59" s="171" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="G59" s="172"/>
       <c r="H59" s="171"/>
@@ -36852,10 +37722,10 @@
       <c r="E60" s="172"/>
       <c r="F60" s="171"/>
       <c r="G60" s="172" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="H60" s="171" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="I60" s="168" t="s">
         <v>25</v>
@@ -36971,7 +37841,7 @@
         <v>1477</v>
       </c>
       <c r="H63" s="171" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="I63" s="168" t="s">
         <v>21</v>
@@ -37076,7 +37946,7 @@
         <v>55</v>
       </c>
       <c r="C66" s="172" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D66" s="171" t="s">
         <v>1442</v>
@@ -37088,7 +37958,7 @@
         <v>1017</v>
       </c>
       <c r="G66" s="172" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H66" s="171" t="s">
         <v>1403</v>
@@ -37232,7 +38102,7 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D70" s="171" t="s">
         <v>71</v>
@@ -37384,10 +38254,10 @@
         <v>52</v>
       </c>
       <c r="C74" s="179" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D74" s="178" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="E74" s="179" t="s">
         <v>141</v>
@@ -37467,7 +38337,7 @@
         <v>1561</v>
       </c>
       <c r="D76" s="180" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="E76" s="181" t="s">
         <v>783</v>
@@ -37623,7 +38493,7 @@
         <v>1562</v>
       </c>
       <c r="D80" s="180" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="E80" s="181"/>
       <c r="F80" s="180"/>
@@ -37780,7 +38650,7 @@
         <v>1496</v>
       </c>
       <c r="G84" s="181" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H84" s="180" t="s">
         <v>1494</v>
@@ -38083,7 +38953,7 @@
         <v>1563</v>
       </c>
       <c r="D92" s="180" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="E92" s="181"/>
       <c r="F92" s="180"/>
@@ -38503,7 +39373,7 @@
         <v>0.24444444444444444</v>
       </c>
       <c r="D103" s="189" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E103" s="190" t="s">
         <v>616</v>
@@ -38963,7 +39833,7 @@
         <v>788</v>
       </c>
       <c r="D115" s="189" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="E115" s="190" t="s">
         <v>1036</v>
@@ -38972,7 +39842,7 @@
         <v>1018</v>
       </c>
       <c r="G115" s="190" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H115" s="189" t="s">
         <v>1403</v>
@@ -39155,7 +40025,7 @@
         <v>861</v>
       </c>
       <c r="D120" s="189" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E120" s="190" t="s">
         <v>1524</v>
@@ -39200,7 +40070,7 @@
         <v>1018</v>
       </c>
       <c r="G121" s="194" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H121" s="193" t="s">
         <v>1403</v>
@@ -39271,7 +40141,7 @@
         <v>269</v>
       </c>
       <c r="D123" s="198" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="E123" s="199" t="s">
         <v>623</v>
@@ -39583,7 +40453,7 @@
         <v>1565</v>
       </c>
       <c r="D131" s="198" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="E131" s="199"/>
       <c r="F131" s="198"/>
@@ -39731,7 +40601,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D135" s="198" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="E135" s="199" t="s">
         <v>607</v>
@@ -39887,7 +40757,7 @@
         <v>1566</v>
       </c>
       <c r="D139" s="198" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="E139" s="199" t="s">
         <v>1530</v>
@@ -40012,7 +40882,7 @@
         <v>1017</v>
       </c>
       <c r="G142" s="199" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H142" s="198" t="s">
         <v>1403</v>
@@ -40271,7 +41141,7 @@
         <v>1568</v>
       </c>
       <c r="D149" s="208" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="E149" s="209" t="s">
         <v>236</v>
@@ -40346,7 +41216,7 @@
       <c r="C151" s="209"/>
       <c r="D151" s="208"/>
       <c r="E151" s="292" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="F151" s="208" t="s">
         <v>1018</v>
@@ -40384,13 +41254,13 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D152" s="208" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E152" s="292" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="F152" s="208" t="s">
         <v>1018</v>
@@ -40575,7 +41445,7 @@
         <v>1282</v>
       </c>
       <c r="D157" s="208" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="E157" s="209" t="s">
         <v>1536</v>
@@ -40807,7 +41677,7 @@
         <v>1570</v>
       </c>
       <c r="D163" s="208" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="E163" s="209" t="s">
         <v>1287</v>
@@ -41072,22 +41942,22 @@
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="40" priority="4" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="41" priority="4" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D2 H1:H44 F1:F1048576 D4:D150 H46:H1048576 D152:D1048576">
-    <cfRule type="containsText" dxfId="39" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="40" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3">
-    <cfRule type="containsText" dxfId="38" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="39" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45 D151">
-    <cfRule type="containsText" dxfId="37" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="38" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D45)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41525,7 +42395,7 @@
         <v>1144</v>
       </c>
       <c r="E10" s="149" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="F10" s="150" t="s">
         <v>274</v>
@@ -41660,7 +42530,7 @@
         <v>34</v>
       </c>
       <c r="E13" s="149" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F13" s="150"/>
       <c r="G13" s="213"/>
@@ -41795,7 +42665,7 @@
         <v>899</v>
       </c>
       <c r="E16" s="149" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F16" s="150"/>
       <c r="G16" s="213"/>
@@ -41930,7 +42800,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="149" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F19" s="150"/>
       <c r="G19" s="213"/>
@@ -42024,7 +42894,7 @@
         <v>1396</v>
       </c>
       <c r="I21" s="148" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="J21" s="149" t="s">
         <v>13</v>
@@ -42065,7 +42935,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F22" s="150"/>
       <c r="G22" s="213"/>
@@ -42235,7 +43105,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="293" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="D26" s="158" t="s">
         <v>1088</v>
@@ -42376,7 +43246,7 @@
         <v>14</v>
       </c>
       <c r="E29" s="160" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="F29" s="162" t="s">
         <v>259</v>
@@ -42552,7 +43422,7 @@
         <v>24</v>
       </c>
       <c r="E33" s="160" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="F33" s="162" t="s">
         <v>1508</v>
@@ -42819,7 +43689,7 @@
         <v>1556</v>
       </c>
       <c r="D39" s="160" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="E39" s="160" t="s">
         <v>1499</v>
@@ -43095,7 +43965,7 @@
       <c r="D45" s="160"/>
       <c r="E45" s="160"/>
       <c r="F45" s="289" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="G45" s="221" t="s">
         <v>0</v>
@@ -43180,10 +44050,10 @@
         <v>58</v>
       </c>
       <c r="C47" s="289" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="D47" s="160" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="E47" s="160" t="s">
         <v>453</v>
@@ -43224,7 +44094,7 @@
       <c r="D48" s="160"/>
       <c r="E48" s="160"/>
       <c r="F48" s="162" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="G48" s="221" t="s">
         <v>27</v>
@@ -43271,7 +44141,7 @@
       <c r="D49" s="166"/>
       <c r="E49" s="166"/>
       <c r="F49" s="167" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="G49" s="225" t="s">
         <v>27</v>
@@ -43362,7 +44232,7 @@
         <v>40</v>
       </c>
       <c r="E51" s="171" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="F51" s="172"/>
       <c r="G51" s="229"/>
@@ -43453,7 +44323,7 @@
       <c r="D53" s="171"/>
       <c r="E53" s="171"/>
       <c r="F53" s="172" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="G53" s="229" t="s">
         <v>11</v>
@@ -43541,7 +44411,7 @@
         <v>471</v>
       </c>
       <c r="F55" s="172" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="G55" s="229" t="s">
         <v>27</v>
@@ -44061,7 +44931,7 @@
         <v>55</v>
       </c>
       <c r="C66" s="172" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="D66" s="171" t="s">
         <v>63</v>
@@ -44079,7 +44949,7 @@
         <v>1017</v>
       </c>
       <c r="I66" s="172" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="J66" s="171" t="s">
         <v>345</v>
@@ -44243,7 +45113,7 @@
         <v>55</v>
       </c>
       <c r="C70" s="172" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="D70" s="172" t="s">
         <v>368</v>
@@ -44419,13 +45289,13 @@
         <v>52</v>
       </c>
       <c r="C74" s="179" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D74" s="178" t="s">
-        <v>1573</v>
+        <v>1658</v>
       </c>
       <c r="E74" s="178" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="F74" s="179" t="s">
         <v>141</v>
@@ -44519,7 +45389,7 @@
         <v>1371</v>
       </c>
       <c r="E76" s="180" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="F76" s="181" t="s">
         <v>783</v>
@@ -44701,7 +45571,7 @@
         <v>19</v>
       </c>
       <c r="E80" s="180" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="F80" s="181"/>
       <c r="G80" s="237"/>
@@ -44883,7 +45753,7 @@
         <v>1496</v>
       </c>
       <c r="I84" s="181" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J84" s="180" t="s">
         <v>345</v>
@@ -45235,7 +46105,7 @@
         <v>34</v>
       </c>
       <c r="E92" s="180" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="F92" s="181"/>
       <c r="G92" s="237"/>
@@ -45537,7 +46407,7 @@
         <v>234</v>
       </c>
       <c r="D99" s="187" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="E99" s="189" t="s">
         <v>1412</v>
@@ -45722,7 +46592,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="189" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="F103" s="190" t="s">
         <v>616</v>
@@ -46253,10 +47123,10 @@
         <v>788</v>
       </c>
       <c r="D115" s="189" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="E115" s="189" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="F115" s="190" t="s">
         <v>1036</v>
@@ -46268,7 +47138,7 @@
         <v>1018</v>
       </c>
       <c r="I115" s="190" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="J115" s="189" t="s">
         <v>13</v>
@@ -46476,10 +47346,10 @@
         <v>861</v>
       </c>
       <c r="D120" s="189" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E120" s="189" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F120" s="190" t="s">
         <v>1524</v>
@@ -46532,7 +47402,7 @@
         <v>1018</v>
       </c>
       <c r="I121" s="194" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="J121" s="193" t="s">
         <v>13</v>
@@ -46611,10 +47481,10 @@
         <v>269</v>
       </c>
       <c r="D123" s="198" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="E123" s="198" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="F123" s="199" t="s">
         <v>623</v>
@@ -46978,7 +47848,7 @@
         <v>908</v>
       </c>
       <c r="E131" s="198" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="F131" s="199"/>
       <c r="G131" s="251"/>
@@ -47145,10 +48015,10 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D135" s="198" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="E135" s="198" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="F135" s="199" t="s">
         <v>607</v>
@@ -47330,7 +48200,7 @@
         <v>902</v>
       </c>
       <c r="E139" s="198" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="F139" s="199" t="s">
         <v>1530</v>
@@ -47477,7 +48347,7 @@
         <v>1017</v>
       </c>
       <c r="I142" s="199" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="J142" s="198" t="s">
         <v>13</v>
@@ -47776,7 +48646,7 @@
         <v>1572</v>
       </c>
       <c r="E149" s="208" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="F149" s="209" t="s">
         <v>236</v>
@@ -47861,7 +48731,7 @@
       <c r="D151" s="208"/>
       <c r="E151" s="208"/>
       <c r="F151" s="292" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="G151" s="259" t="s">
         <v>0</v>
@@ -47905,16 +48775,16 @@
         <v>2</v>
       </c>
       <c r="C152" s="292" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D152" s="208" t="s">
         <v>334</v>
       </c>
       <c r="E152" s="208" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="F152" s="292" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="G152" s="259" t="s">
         <v>0</v>
@@ -48128,7 +48998,7 @@
         <v>452</v>
       </c>
       <c r="E157" s="208" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="F157" s="209" t="s">
         <v>1536</v>
@@ -48398,7 +49268,7 @@
         <v>1555</v>
       </c>
       <c r="E163" s="208" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="F163" s="209" t="s">
         <v>1287</v>
@@ -48705,22 +49575,22 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576 J12 D70">
-    <cfRule type="containsText" dxfId="36" priority="4" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="37" priority="4" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E2 K1:K44 H1:H1048576 E4:E150 K46:K1048576 E152:E1048576">
-    <cfRule type="containsText" dxfId="35" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="36" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="containsText" dxfId="34" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="35" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J11 D1:D69 G1:G1048576 J13:J1048576 K45 D71:D1048576 E151">
-    <cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="34" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49219,7 +50089,7 @@
         <v>1362</v>
       </c>
       <c r="E11" s="149" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="F11" s="150"/>
       <c r="G11" s="149"/>
@@ -49706,7 +50576,7 @@
         <v>898</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F22" s="150" t="s">
         <v>1288</v>
@@ -50064,7 +50934,7 @@
         <v>1364</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="F30" s="162" t="s">
         <v>1195</v>
@@ -56366,42 +57236,42 @@
   <autoFilter ref="B1:K169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 F1:F1048576 I1:I1048576">
-    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 D106:D1048576">
-    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="32" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="30" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="31" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:J1048576">
-    <cfRule type="containsText" dxfId="28" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",J1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1 E1:E1048576 H1:H1048576 K54:K99 K101:K1048576">
-    <cfRule type="containsText" dxfId="27" priority="7" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K53">
-    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K100">
-    <cfRule type="containsText" dxfId="25" priority="8" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="26" priority="8" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",K100)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -62340,27 +63210,27 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="24" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="23" priority="6" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="23" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="containsText" dxfId="21" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="containsText" dxfId="20" priority="3" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",G1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68376,17 +69246,17 @@
   <autoFilter ref="B1:H169" xr:uid="{C9CB8B28-8E90-4DF5-B270-3DF6F6D9E7A4}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="19" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D104 F1:F1048576 H1:H1048576 D106:D1048576">
-    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D105">
-    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="18" priority="1" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D105)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -74376,12 +75246,12 @@
   <autoFilter ref="B1:H169" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="17" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="15" priority="4" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -80272,12 +81142,12 @@
   <autoFilter ref="B1:H169" xr:uid="{D1070A93-2548-46EB-82F4-6BE4CD06B45C}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -86265,12 +87135,12 @@
   <autoFilter ref="B1:H169" xr:uid="{45A0ECB4-19C6-406A-B20A-34EE1DA4D5EF}"/>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 F121">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F120 D1:D1048576 H1:H1048576 F122:F1048576">
-    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A7640F-B5B5-46AB-80C5-7C6B4C6E2B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0FFF68-F683-4936-8B4B-D5722CD6FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28155" yWindow="4125" windowWidth="21600" windowHeight="11235" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="480">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1201,6 +1201,450 @@
       <t xml:space="preserve"> 例行維護中</t>
     </r>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:36</t>
+  </si>
+  <si>
+    <t>11:28</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:11</t>
+  </si>
+  <si>
+    <t>16:44</t>
+  </si>
+  <si>
+    <t>17:27</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>18:13</t>
+  </si>
+  <si>
+    <t>19:42</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>20:26</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>21:11</t>
+  </si>
+  <si>
+    <t>22:42</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:31</t>
+  </si>
+  <si>
+    <t>02:59</t>
+  </si>
+  <si>
+    <t>03:13</t>
+  </si>
+  <si>
+    <t>03:04</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>04:32</t>
+  </si>
+  <si>
+    <t>05:58</t>
+  </si>
+  <si>
+    <t>05:59</t>
+  </si>
+  <si>
+    <t>07:33</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>13:28</t>
+  </si>
+  <si>
+    <t>14:54</t>
+  </si>
+  <si>
+    <t>16:37</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:51</t>
+  </si>
+  <si>
+    <t>18:11</t>
+  </si>
+  <si>
+    <t>19:36</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>20:56</t>
+  </si>
+  <si>
+    <t>21:09</t>
+  </si>
+  <si>
+    <t>22:43</t>
+  </si>
+  <si>
+    <t>23:56</t>
+  </si>
+  <si>
+    <t>00:58</t>
+  </si>
+  <si>
+    <t>02:25</t>
+  </si>
+  <si>
+    <t>03:28</t>
+  </si>
+  <si>
+    <t>03:52</t>
+  </si>
+  <si>
+    <t>05:19</t>
+  </si>
+  <si>
+    <t>06:01</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>08:27</t>
+  </si>
+  <si>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:47</t>
+  </si>
+  <si>
+    <t>15:52</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>16:33</t>
+  </si>
+  <si>
+    <t>17:21</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:24</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>22:27</t>
+  </si>
+  <si>
+    <t>23:12</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>孤村 / 灰狼村</t>
+  </si>
+  <si>
+    <t>黑森林 / 悲鳴村</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 鬼都</t>
+  </si>
+  <si>
+    <t>土門 / 雪原(北方警戒崗哨)</t>
+  </si>
+  <si>
+    <t>悲鳴村 / 染坊</t>
+  </si>
+  <si>
+    <t>豬豬農場 / 雪原(北方警戒崗哨)</t>
+  </si>
+  <si>
+    <t>黑森林 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>悲鳴村 / 鬼都</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>灰狼村 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>孤村 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>染坊 / 雪原(北方警戒崗哨)</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 雪原(北方警戒崗哨)</t>
+  </si>
+  <si>
+    <t>孤村 / 鬼都</t>
+  </si>
+  <si>
+    <t>孤村 / 巨岩海岸</t>
+  </si>
+  <si>
+    <t>白樺林</t>
+  </si>
+  <si>
+    <t>風之平原</t>
+  </si>
+  <si>
+    <t>知性森林</t>
+  </si>
+  <si>
+    <t>知性森林</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>力王山脈</t>
+  </si>
+  <si>
+    <t>武神荒野</t>
+  </si>
+  <si>
+    <t>土門客棧 / 染坊</t>
+  </si>
+  <si>
+    <t>孤村 / 染坊</t>
+  </si>
+  <si>
+    <t>黑森林 / 孤村</t>
+  </si>
+  <si>
+    <t>土門客棧 / 豬豬農場</t>
+  </si>
+  <si>
+    <t>灰狼村 / 雪原(北方警戒崗哨)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>染坊 / 雪原(北方警戒崗哨)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:22</t>
+  </si>
+  <si>
+    <t>01:28</t>
+  </si>
+  <si>
+    <t>02:58</t>
+  </si>
+  <si>
+    <t>05:57</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:22</t>
+  </si>
+  <si>
+    <t>07:37</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>11:54</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>18:09</t>
+  </si>
+  <si>
+    <t>19:18</t>
+  </si>
+  <si>
+    <t>19:41</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>21:14</t>
+  </si>
+  <si>
+    <t>22:21</t>
+  </si>
+  <si>
+    <t>23:52</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:28</t>
+  </si>
+  <si>
+    <t>03:56</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>06:27</t>
+  </si>
+  <si>
+    <t>06:54</t>
+  </si>
+  <si>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>09:53</t>
+  </si>
+  <si>
+    <t>11:18</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>15:56</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>19:48</t>
+  </si>
+  <si>
+    <t>20:21</t>
+  </si>
+  <si>
+    <t>20:19</t>
+  </si>
+  <si>
+    <t>10:00</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1681,6 +2125,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2018,21 +2471,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEAFB3C-24F9-4C3B-92E1-88934B2FA9FC}">
-  <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
+  <dimension ref="A1:R169"/>
+  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="16.25" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="14.19921875" style="6"/>
+    <col min="10" max="10" width="3.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="14.25" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">
@@ -3565,7 +4016,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="18" customHeight="1" thickBot="1">
+    <row r="49" spans="1:18" ht="18" customHeight="1" thickBot="1">
       <c r="A49" s="20" t="s">
         <v>1</v>
       </c>
@@ -3597,7 +4048,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="18" customHeight="1">
+    <row r="50" spans="1:18" ht="18" customHeight="1">
       <c r="A50" s="23" t="s">
         <v>24</v>
       </c>
@@ -3629,7 +4080,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="18" customHeight="1">
+    <row r="51" spans="1:18" ht="18" customHeight="1">
       <c r="A51" s="23" t="s">
         <v>23</v>
       </c>
@@ -3661,7 +4112,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="18" customHeight="1">
+    <row r="52" spans="1:18" ht="18" customHeight="1">
       <c r="A52" s="23" t="s">
         <v>22</v>
       </c>
@@ -3693,7 +4144,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="18" customHeight="1">
+    <row r="53" spans="1:18" ht="18" customHeight="1">
       <c r="A53" s="23" t="s">
         <v>21</v>
       </c>
@@ -3725,7 +4176,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="18" customHeight="1">
+    <row r="54" spans="1:18" ht="18" customHeight="1">
       <c r="A54" s="23" t="s">
         <v>20</v>
       </c>
@@ -3757,7 +4208,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="18" customHeight="1">
+    <row r="55" spans="1:18" ht="18" customHeight="1">
       <c r="A55" s="23" t="s">
         <v>19</v>
       </c>
@@ -3789,7 +4240,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="18" customHeight="1">
+    <row r="56" spans="1:18" ht="18" customHeight="1">
       <c r="A56" s="23" t="s">
         <v>18</v>
       </c>
@@ -3833,7 +4284,7 @@
         <v>06:00</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="18" customHeight="1">
+    <row r="57" spans="1:18" ht="18" customHeight="1">
       <c r="A57" s="23" t="s">
         <v>17</v>
       </c>
@@ -3877,7 +4328,7 @@
         <v>07:00</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="18" customHeight="1">
+    <row r="58" spans="1:18" ht="18" customHeight="1">
       <c r="A58" s="23" t="s">
         <v>16</v>
       </c>
@@ -3921,7 +4372,7 @@
         <v>08:00</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="18" customHeight="1">
+    <row r="59" spans="1:18" ht="18" customHeight="1">
       <c r="A59" s="23" t="s">
         <v>15</v>
       </c>
@@ -3934,7 +4385,7 @@
       <c r="D59" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E59" s="26" t="s">
+      <c r="E59" s="99" t="s">
         <v>42</v>
       </c>
       <c r="F59" s="74" t="s">
@@ -3964,8 +4415,20 @@
         <f t="shared" si="2"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="18" customHeight="1">
+      <c r="O59" s="6">
+        <v>0.41597222222222224</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="18" customHeight="1">
       <c r="A60" s="23" t="s">
         <v>14</v>
       </c>
@@ -3979,13 +4442,13 @@
         <v>80</v>
       </c>
       <c r="E60" s="27" t="s">
-        <v>331</v>
+        <v>479</v>
       </c>
       <c r="F60" s="74" t="s">
         <v>80</v>
       </c>
       <c r="G60" s="27" t="s">
-        <v>331</v>
+        <v>479</v>
       </c>
       <c r="H60" s="26" t="s">
         <v>80</v>
@@ -4008,8 +4471,14 @@
         <f t="shared" si="2"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="61" spans="1:13" ht="18" customHeight="1">
+      <c r="Q60" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="18" customHeight="1">
       <c r="A61" s="23" t="s">
         <v>13</v>
       </c>
@@ -4018,8 +4487,12 @@
       </c>
       <c r="C61" s="27"/>
       <c r="D61" s="26"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="74"/>
+      <c r="E61" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="F61" s="74" t="s">
+        <v>423</v>
+      </c>
       <c r="G61" s="27"/>
       <c r="H61" s="26"/>
       <c r="I61" s="23" t="s">
@@ -4034,26 +4507,38 @@
       </c>
       <c r="L61" s="6" t="str">
         <f>IF($E61&lt;&gt;"",TEXT($E61,"HH:MM"),"")</f>
-        <v/>
+        <v>11:28</v>
       </c>
       <c r="M61" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="18" customHeight="1">
+    <row r="62" spans="1:18" ht="18" customHeight="1">
       <c r="A62" s="23" t="s">
         <v>12</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C62" s="27"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="27"/>
-      <c r="H62" s="26"/>
+      <c r="C62" s="27" t="s">
+        <v>335</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>407</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>336</v>
+      </c>
+      <c r="F62" s="74" t="s">
+        <v>423</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="H62" s="26" t="s">
+        <v>426</v>
+      </c>
       <c r="I62" s="23" t="s">
         <v>12</v>
       </c>
@@ -4062,30 +4547,36 @@
       </c>
       <c r="K62" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>12:33</v>
       </c>
       <c r="L62" s="6" t="str">
         <f>IF($E62&lt;&gt;"",TEXT($E62,"HH:MM"),"")</f>
-        <v/>
+        <v>12:59</v>
       </c>
       <c r="M62" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="18" customHeight="1">
+        <v>12:11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="18" customHeight="1">
       <c r="A63" s="23" t="s">
         <v>11</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="27"/>
+      <c r="C63" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D63" s="26"/>
       <c r="E63" s="27"/>
       <c r="F63" s="74"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="26"/>
+      <c r="G63" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="H63" s="26" t="s">
+        <v>427</v>
+      </c>
       <c r="I63" s="23" t="s">
         <v>11</v>
       </c>
@@ -4102,20 +4593,26 @@
       </c>
       <c r="M63" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="18" customHeight="1">
+        <v>13:45</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="18" customHeight="1">
       <c r="A64" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="27"/>
+      <c r="C64" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D64" s="26"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="74"/>
+      <c r="E64" s="27" t="s">
+        <v>340</v>
+      </c>
+      <c r="F64" s="74" t="s">
+        <v>422</v>
+      </c>
       <c r="G64" s="27"/>
       <c r="H64" s="26"/>
       <c r="I64" s="23" t="s">
@@ -4130,7 +4627,7 @@
       </c>
       <c r="L64" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>14:25</v>
       </c>
       <c r="M64" s="6" t="str">
         <f t="shared" si="2"/>
@@ -4144,12 +4641,24 @@
       <c r="B65" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="23"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="74"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="26"/>
+      <c r="C65" s="100">
+        <v>0.66041666666666665</v>
+      </c>
+      <c r="D65" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="E65" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="F65" s="74" t="s">
+        <v>422</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="H65" s="26" t="s">
+        <v>424</v>
+      </c>
       <c r="I65" s="23" t="s">
         <v>9</v>
       </c>
@@ -4158,15 +4667,15 @@
       </c>
       <c r="K65" s="6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>15:51</v>
       </c>
       <c r="L65" s="6" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>15:58</v>
       </c>
       <c r="M65" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>15:11</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="18" customHeight="1">
@@ -4176,12 +4685,18 @@
       <c r="B66" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C66" s="27"/>
+      <c r="C66" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D66" s="26"/>
       <c r="E66" s="27"/>
       <c r="F66" s="74"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="26"/>
+      <c r="G66" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="H66" s="26" t="s">
+        <v>424</v>
+      </c>
       <c r="I66" s="23" t="s">
         <v>8</v>
       </c>
@@ -4198,7 +4713,7 @@
       </c>
       <c r="M66" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>16:44</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="18" customHeight="1">
@@ -4208,10 +4723,16 @@
       <c r="B67" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C67" s="28"/>
+      <c r="C67" s="28" t="s">
+        <v>338</v>
+      </c>
       <c r="D67" s="26"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="74"/>
+      <c r="E67" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="F67" s="74" t="s">
+        <v>423</v>
+      </c>
       <c r="G67" s="28"/>
       <c r="H67" s="26"/>
       <c r="I67" s="23" t="s">
@@ -4226,7 +4747,7 @@
       </c>
       <c r="L67" s="6" t="str">
         <f t="shared" ref="L67:L130" si="4">IF($E67&lt;&gt;"",TEXT($E67,"HH:MM"),"")</f>
-        <v/>
+        <v>17:27</v>
       </c>
       <c r="M67" s="6" t="str">
         <f t="shared" ref="M67:M130" si="5">IF($G67&lt;&gt;"",TEXT($G67,"HH:MM"),"")</f>
@@ -4240,12 +4761,22 @@
       <c r="B68" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="27"/>
+      <c r="C68" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D68" s="26"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="74"/>
-      <c r="G68" s="27"/>
-      <c r="H68" s="26"/>
+      <c r="E68" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="F68" s="74" t="s">
+        <v>422</v>
+      </c>
+      <c r="G68" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="H68" s="26" t="s">
+        <v>427</v>
+      </c>
       <c r="I68" s="23" t="s">
         <v>6</v>
       </c>
@@ -4258,11 +4789,11 @@
       </c>
       <c r="L68" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18:55</v>
       </c>
       <c r="M68" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>18:13</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="18" customHeight="1">
@@ -4272,12 +4803,20 @@
       <c r="B69" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C69" s="27"/>
-      <c r="D69" s="26"/>
+      <c r="C69" s="27" t="s">
+        <v>346</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>409</v>
+      </c>
       <c r="E69" s="27"/>
       <c r="F69" s="74"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="26"/>
+      <c r="G69" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="H69" s="26" t="s">
+        <v>426</v>
+      </c>
       <c r="I69" s="23" t="s">
         <v>5</v>
       </c>
@@ -4286,7 +4825,7 @@
       </c>
       <c r="K69" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>19:42</v>
       </c>
       <c r="L69" s="6" t="str">
         <f t="shared" si="4"/>
@@ -4294,7 +4833,7 @@
       </c>
       <c r="M69" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>19:40</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="18" customHeight="1">
@@ -4304,10 +4843,16 @@
       <c r="B70" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="27"/>
+      <c r="C70" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="74"/>
+      <c r="E70" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="F70" s="74" t="s">
+        <v>422</v>
+      </c>
       <c r="G70" s="28"/>
       <c r="H70" s="26"/>
       <c r="I70" s="23" t="s">
@@ -4322,7 +4867,7 @@
       </c>
       <c r="L70" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20:26</v>
       </c>
       <c r="M70" s="6" t="str">
         <f t="shared" si="5"/>
@@ -4336,12 +4881,22 @@
       <c r="B71" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="27"/>
+      <c r="C71" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D71" s="26"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="26"/>
+      <c r="E71" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="F71" s="74" t="s">
+        <v>422</v>
+      </c>
+      <c r="G71" s="27" t="s">
+        <v>350</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>426</v>
+      </c>
       <c r="I71" s="23" t="s">
         <v>3</v>
       </c>
@@ -4354,11 +4909,11 @@
       </c>
       <c r="L71" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>21:56</v>
       </c>
       <c r="M71" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>21:11</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1">
@@ -4368,12 +4923,18 @@
       <c r="B72" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="27"/>
+      <c r="C72" s="27" t="s">
+        <v>338</v>
+      </c>
       <c r="D72" s="26"/>
       <c r="E72" s="27"/>
       <c r="F72" s="74"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="26"/>
+      <c r="G72" s="27" t="s">
+        <v>351</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>427</v>
+      </c>
       <c r="I72" s="23" t="s">
         <v>2</v>
       </c>
@@ -4390,7 +4951,7 @@
       </c>
       <c r="M72" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>22:42</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="18" customHeight="1" thickBot="1">
@@ -4400,10 +4961,16 @@
       <c r="B73" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C73" s="31"/>
+      <c r="C73" s="31" t="s">
+        <v>338</v>
+      </c>
       <c r="D73" s="30"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="75"/>
+      <c r="E73" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="F73" s="75" t="s">
+        <v>422</v>
+      </c>
       <c r="G73" s="31"/>
       <c r="H73" s="30"/>
       <c r="I73" s="29" t="s">
@@ -4418,7 +4985,7 @@
       </c>
       <c r="L73" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>23:25</v>
       </c>
       <c r="M73" s="6" t="str">
         <f t="shared" si="5"/>
@@ -4432,12 +4999,24 @@
       <c r="B74" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="34"/>
-      <c r="D74" s="33"/>
-      <c r="E74" s="34"/>
-      <c r="F74" s="76"/>
-      <c r="G74" s="34"/>
-      <c r="H74" s="33"/>
+      <c r="C74" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="33" t="s">
+        <v>410</v>
+      </c>
+      <c r="E74" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="76" t="s">
+        <v>423</v>
+      </c>
+      <c r="G74" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74" s="33" t="s">
+        <v>427</v>
+      </c>
       <c r="I74" s="32" t="s">
         <v>24</v>
       </c>
@@ -4446,15 +5025,15 @@
       </c>
       <c r="K74" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="L74" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M74" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>00:00</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="18" customHeight="1">
@@ -4464,12 +5043,22 @@
       <c r="B75" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C75" s="36"/>
+      <c r="C75" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D75" s="35"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="35"/>
+      <c r="E75" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="F75" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G75" s="36" t="s">
+        <v>353</v>
+      </c>
+      <c r="H75" s="35" t="s">
+        <v>427</v>
+      </c>
       <c r="I75" s="32" t="s">
         <v>23</v>
       </c>
@@ -4482,11 +5071,11 @@
       </c>
       <c r="L75" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>01:30</v>
       </c>
       <c r="M75" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:31</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="18" customHeight="1">
@@ -4496,12 +5085,18 @@
       <c r="B76" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="36"/>
+      <c r="C76" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D76" s="35"/>
       <c r="E76" s="36"/>
       <c r="F76" s="77"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="35"/>
+      <c r="G76" s="37" t="s">
+        <v>354</v>
+      </c>
+      <c r="H76" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I76" s="32" t="s">
         <v>22</v>
       </c>
@@ -4518,7 +5113,7 @@
       </c>
       <c r="M76" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:59</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="18" customHeight="1">
@@ -4528,11 +5123,19 @@
       <c r="B77" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="36"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="36"/>
-      <c r="F77" s="77"/>
-      <c r="G77" s="36"/>
+      <c r="C77" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="D77" s="35" t="s">
+        <v>407</v>
+      </c>
+      <c r="E77" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="F77" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G77" s="77"/>
       <c r="H77" s="35"/>
       <c r="I77" s="32" t="s">
         <v>21</v>
@@ -4542,11 +5145,11 @@
       </c>
       <c r="K77" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>03:13</v>
       </c>
       <c r="L77" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>03:04</v>
       </c>
       <c r="M77" s="6" t="str">
         <f t="shared" si="5"/>
@@ -4560,12 +5163,22 @@
       <c r="B78" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="36"/>
+      <c r="C78" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D78" s="35"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="77"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="35"/>
+      <c r="E78" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="F78" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="G78" s="36" t="s">
+        <v>358</v>
+      </c>
+      <c r="H78" s="35" t="s">
+        <v>424</v>
+      </c>
       <c r="I78" s="32" t="s">
         <v>20</v>
       </c>
@@ -4578,11 +5191,11 @@
       </c>
       <c r="L78" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:31</v>
       </c>
       <c r="M78" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>04:32</v>
       </c>
     </row>
     <row r="79" spans="1:13" ht="18" customHeight="1">
@@ -4592,12 +5205,24 @@
       <c r="B79" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="36"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="77"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="35"/>
+      <c r="C79" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>411</v>
+      </c>
+      <c r="E79" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="F79" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="G79" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="H79" s="35" t="s">
+        <v>427</v>
+      </c>
       <c r="I79" s="32" t="s">
         <v>19</v>
       </c>
@@ -4606,15 +5231,15 @@
       </c>
       <c r="K79" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>05:58</v>
       </c>
       <c r="L79" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:59</v>
       </c>
       <c r="M79" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:59</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="18" customHeight="1">
@@ -4624,7 +5249,9 @@
       <c r="B80" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="36"/>
+      <c r="C80" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D80" s="35"/>
       <c r="E80" s="36"/>
       <c r="F80" s="77"/>
@@ -4656,12 +5283,22 @@
       <c r="B81" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="36"/>
+      <c r="C81" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D81" s="35"/>
-      <c r="E81" s="36"/>
-      <c r="F81" s="77"/>
-      <c r="G81" s="36"/>
-      <c r="H81" s="35"/>
+      <c r="E81" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="F81" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G81" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="H81" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I81" s="32" t="s">
         <v>17</v>
       </c>
@@ -4674,11 +5311,11 @@
       </c>
       <c r="L81" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:33</v>
       </c>
       <c r="M81" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:25</v>
       </c>
     </row>
     <row r="82" spans="1:13" ht="18" customHeight="1">
@@ -4688,12 +5325,20 @@
       <c r="B82" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="36"/>
-      <c r="D82" s="35"/>
+      <c r="C82" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>409</v>
+      </c>
       <c r="E82" s="36"/>
       <c r="F82" s="77"/>
-      <c r="G82" s="36"/>
-      <c r="H82" s="35"/>
+      <c r="G82" s="36" t="s">
+        <v>364</v>
+      </c>
+      <c r="H82" s="35" t="s">
+        <v>425</v>
+      </c>
       <c r="I82" s="32" t="s">
         <v>16</v>
       </c>
@@ -4702,7 +5347,7 @@
       </c>
       <c r="K82" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>08:42</v>
       </c>
       <c r="L82" s="6" t="str">
         <f t="shared" si="4"/>
@@ -4710,7 +5355,7 @@
       </c>
       <c r="M82" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:50</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="18" customHeight="1">
@@ -4722,8 +5367,12 @@
       </c>
       <c r="C83" s="35"/>
       <c r="D83" s="35"/>
-      <c r="E83" s="36"/>
-      <c r="F83" s="77"/>
+      <c r="E83" s="36" t="s">
+        <v>365</v>
+      </c>
+      <c r="F83" s="77" t="s">
+        <v>423</v>
+      </c>
       <c r="G83" s="37"/>
       <c r="H83" s="35"/>
       <c r="I83" s="32" t="s">
@@ -4738,7 +5387,7 @@
       </c>
       <c r="L83" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>09:07</v>
       </c>
       <c r="M83" s="6" t="str">
         <f t="shared" si="5"/>
@@ -4752,12 +5401,22 @@
       <c r="B84" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C84" s="36"/>
+      <c r="C84" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D84" s="35"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="77"/>
-      <c r="G84" s="36"/>
-      <c r="H84" s="35"/>
+      <c r="E84" s="36" t="s">
+        <v>366</v>
+      </c>
+      <c r="F84" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G84" s="36" t="s">
+        <v>367</v>
+      </c>
+      <c r="H84" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I84" s="32" t="s">
         <v>14</v>
       </c>
@@ -4770,11 +5429,11 @@
       </c>
       <c r="L84" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10:37</v>
       </c>
       <c r="M84" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>10:25</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="18" customHeight="1">
@@ -4784,7 +5443,9 @@
       <c r="B85" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="36"/>
+      <c r="C85" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D85" s="35"/>
       <c r="E85" s="36"/>
       <c r="F85" s="77"/>
@@ -4816,12 +5477,24 @@
       <c r="B86" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="77"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="35"/>
+      <c r="C86" s="101">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="D86" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>368</v>
+      </c>
+      <c r="F86" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G86" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="H86" s="35" t="s">
+        <v>427</v>
+      </c>
       <c r="I86" s="32" t="s">
         <v>12</v>
       </c>
@@ -4830,15 +5503,15 @@
       </c>
       <c r="K86" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12:22</v>
       </c>
       <c r="L86" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12:07</v>
       </c>
       <c r="M86" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>12:00</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="18" customHeight="1">
@@ -4848,12 +5521,22 @@
       <c r="B87" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C87" s="36"/>
+      <c r="C87" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D87" s="35"/>
-      <c r="E87" s="36"/>
-      <c r="F87" s="77"/>
-      <c r="G87" s="36"/>
-      <c r="H87" s="35"/>
+      <c r="E87" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="F87" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G87" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="H87" s="35" t="s">
+        <v>427</v>
+      </c>
       <c r="I87" s="32" t="s">
         <v>11</v>
       </c>
@@ -4866,11 +5549,11 @@
       </c>
       <c r="L87" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13:34</v>
       </c>
       <c r="M87" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>13:28</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="18" customHeight="1">
@@ -4880,12 +5563,18 @@
       <c r="B88" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C88" s="36"/>
+      <c r="C88" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D88" s="35"/>
       <c r="E88" s="36"/>
       <c r="F88" s="77"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="35"/>
+      <c r="G88" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="H88" s="35" t="s">
+        <v>427</v>
+      </c>
       <c r="I88" s="32" t="s">
         <v>10</v>
       </c>
@@ -4902,7 +5591,7 @@
       </c>
       <c r="M88" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>14:54</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="18" customHeight="1">
@@ -4912,10 +5601,16 @@
       <c r="B89" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="36"/>
+      <c r="C89" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D89" s="35"/>
-      <c r="E89" s="36"/>
-      <c r="F89" s="77"/>
+      <c r="E89" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="F89" s="77" t="s">
+        <v>422</v>
+      </c>
       <c r="G89" s="37"/>
       <c r="H89" s="35"/>
       <c r="I89" s="32" t="s">
@@ -4930,7 +5625,7 @@
       </c>
       <c r="L89" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>15:03</v>
       </c>
       <c r="M89" s="6" t="str">
         <f t="shared" si="5"/>
@@ -4944,12 +5639,22 @@
       <c r="B90" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C90" s="36"/>
+      <c r="C90" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D90" s="35"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="77"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="35"/>
+      <c r="E90" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="F90" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G90" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="H90" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I90" s="32" t="s">
         <v>8</v>
       </c>
@@ -4962,11 +5667,11 @@
       </c>
       <c r="L90" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>16:37</v>
       </c>
       <c r="M90" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>16:25</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="18" customHeight="1">
@@ -4976,12 +5681,18 @@
       <c r="B91" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="36"/>
+      <c r="C91" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D91" s="35"/>
       <c r="E91" s="36"/>
       <c r="F91" s="77"/>
-      <c r="G91" s="36"/>
-      <c r="H91" s="35"/>
+      <c r="G91" s="36" t="s">
+        <v>374</v>
+      </c>
+      <c r="H91" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I91" s="32" t="s">
         <v>7</v>
       </c>
@@ -4998,7 +5709,7 @@
       </c>
       <c r="M91" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>17:55</v>
       </c>
     </row>
     <row r="92" spans="1:13" ht="18" customHeight="1">
@@ -5008,10 +5719,18 @@
       <c r="B92" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C92" s="36"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="36"/>
-      <c r="F92" s="77"/>
+      <c r="C92" s="36" t="s">
+        <v>375</v>
+      </c>
+      <c r="D92" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="E92" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="F92" s="77" t="s">
+        <v>423</v>
+      </c>
       <c r="G92" s="37"/>
       <c r="H92" s="35"/>
       <c r="I92" s="32" t="s">
@@ -5022,11 +5741,11 @@
       </c>
       <c r="K92" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>19:51</v>
       </c>
       <c r="L92" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18:11</v>
       </c>
       <c r="M92" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5042,10 +5761,18 @@
       </c>
       <c r="C93" s="35"/>
       <c r="D93" s="35"/>
-      <c r="E93" s="36"/>
-      <c r="F93" s="77"/>
-      <c r="G93" s="36"/>
-      <c r="H93" s="35"/>
+      <c r="E93" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G93" s="36" t="s">
+        <v>378</v>
+      </c>
+      <c r="H93" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I93" s="32" t="s">
         <v>5</v>
       </c>
@@ -5058,11 +5785,11 @@
       </c>
       <c r="L93" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>19:36</v>
       </c>
       <c r="M93" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>19:24</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="18" customHeight="1">
@@ -5072,12 +5799,18 @@
       <c r="B94" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="36"/>
+      <c r="C94" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D94" s="35"/>
       <c r="E94" s="36"/>
       <c r="F94" s="77"/>
-      <c r="G94" s="36"/>
-      <c r="H94" s="35"/>
+      <c r="G94" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="H94" s="35" t="s">
+        <v>426</v>
+      </c>
       <c r="I94" s="32" t="s">
         <v>4</v>
       </c>
@@ -5094,7 +5827,7 @@
       </c>
       <c r="M94" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:56</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="18" customHeight="1">
@@ -5104,10 +5837,16 @@
       <c r="B95" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C95" s="36"/>
+      <c r="C95" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D95" s="35"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="77"/>
+      <c r="E95" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="F95" s="77" t="s">
+        <v>422</v>
+      </c>
       <c r="G95" s="36"/>
       <c r="H95" s="35"/>
       <c r="I95" s="32" t="s">
@@ -5122,7 +5861,7 @@
       </c>
       <c r="L95" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>21:09</v>
       </c>
       <c r="M95" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5136,12 +5875,22 @@
       <c r="B96" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C96" s="36"/>
+      <c r="C96" s="36" t="s">
+        <v>338</v>
+      </c>
       <c r="D96" s="35"/>
-      <c r="E96" s="36"/>
-      <c r="F96" s="77"/>
-      <c r="G96" s="37"/>
-      <c r="H96" s="35"/>
+      <c r="E96" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="F96" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="G96" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="H96" s="35" t="s">
+        <v>424</v>
+      </c>
       <c r="I96" s="32" t="s">
         <v>2</v>
       </c>
@@ -5154,11 +5903,11 @@
       </c>
       <c r="L96" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>22:43</v>
       </c>
       <c r="M96" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>22:29</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="18" customHeight="1" thickBot="1">
@@ -5168,12 +5917,20 @@
       <c r="B97" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C97" s="40"/>
-      <c r="D97" s="39"/>
+      <c r="C97" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="39" t="s">
+        <v>407</v>
+      </c>
       <c r="E97" s="40"/>
       <c r="F97" s="78"/>
-      <c r="G97" s="40"/>
-      <c r="H97" s="39"/>
+      <c r="G97" s="40" t="s">
+        <v>382</v>
+      </c>
+      <c r="H97" s="39" t="s">
+        <v>427</v>
+      </c>
       <c r="I97" s="38" t="s">
         <v>1</v>
       </c>
@@ -5182,7 +5939,7 @@
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="L97" s="6" t="str">
         <f t="shared" si="4"/>
@@ -5190,7 +5947,7 @@
       </c>
       <c r="M97" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:56</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="18" customHeight="1">
@@ -5200,12 +5957,22 @@
       <c r="B98" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="43"/>
+      <c r="C98" s="43" t="s">
+        <v>338</v>
+      </c>
       <c r="D98" s="42"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="79"/>
-      <c r="G98" s="43"/>
-      <c r="H98" s="42"/>
+      <c r="E98" s="43" t="s">
+        <v>57</v>
+      </c>
+      <c r="F98" s="79" t="s">
+        <v>423</v>
+      </c>
+      <c r="G98" s="43" t="s">
+        <v>383</v>
+      </c>
+      <c r="H98" s="42" t="s">
+        <v>427</v>
+      </c>
       <c r="I98" s="41" t="s">
         <v>24</v>
       </c>
@@ -5218,11 +5985,11 @@
       </c>
       <c r="L98" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M98" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>00:58</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="18" customHeight="1">
@@ -5232,10 +5999,16 @@
       <c r="B99" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="43"/>
+      <c r="C99" s="43" t="s">
+        <v>338</v>
+      </c>
       <c r="D99" s="42"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="80"/>
+      <c r="E99" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="F99" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G99" s="45"/>
       <c r="H99" s="44"/>
       <c r="I99" s="41" t="s">
@@ -5250,7 +6023,7 @@
       </c>
       <c r="L99" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>01:30</v>
       </c>
       <c r="M99" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5266,10 +6039,18 @@
       </c>
       <c r="C100" s="45"/>
       <c r="D100" s="44"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="80"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="44"/>
+      <c r="E100" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="F100" s="80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G100" s="45" t="s">
+        <v>384</v>
+      </c>
+      <c r="H100" s="44" t="s">
+        <v>426</v>
+      </c>
       <c r="I100" s="41" t="s">
         <v>22</v>
       </c>
@@ -5282,11 +6063,11 @@
       </c>
       <c r="L100" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>02:59</v>
       </c>
       <c r="M100" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:25</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="18" customHeight="1">
@@ -5296,12 +6077,20 @@
       <c r="B101" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="45"/>
-      <c r="D101" s="44"/>
+      <c r="C101" s="45" t="s">
+        <v>385</v>
+      </c>
+      <c r="D101" s="44" t="s">
+        <v>414</v>
+      </c>
       <c r="E101" s="45"/>
       <c r="F101" s="80"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="44"/>
+      <c r="G101" s="45" t="s">
+        <v>386</v>
+      </c>
+      <c r="H101" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I101" s="41" t="s">
         <v>21</v>
       </c>
@@ -5310,7 +6099,7 @@
       </c>
       <c r="K101" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>03:28</v>
       </c>
       <c r="L101" s="6" t="str">
         <f t="shared" si="4"/>
@@ -5318,7 +6107,7 @@
       </c>
       <c r="M101" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>03:52</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="18" customHeight="1">
@@ -5328,10 +6117,16 @@
       <c r="B102" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="45"/>
+      <c r="C102" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D102" s="44"/>
-      <c r="E102" s="45"/>
-      <c r="F102" s="80"/>
+      <c r="E102" s="45" t="s">
+        <v>71</v>
+      </c>
+      <c r="F102" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G102" s="45"/>
       <c r="H102" s="44"/>
       <c r="I102" s="41" t="s">
@@ -5346,7 +6141,7 @@
       </c>
       <c r="L102" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:30</v>
       </c>
       <c r="M102" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5364,8 +6159,12 @@
       <c r="D103" s="44"/>
       <c r="E103" s="45"/>
       <c r="F103" s="80"/>
-      <c r="G103" s="45"/>
-      <c r="H103" s="44"/>
+      <c r="G103" s="45" t="s">
+        <v>387</v>
+      </c>
+      <c r="H103" s="44" t="s">
+        <v>426</v>
+      </c>
       <c r="I103" s="41" t="s">
         <v>19</v>
       </c>
@@ -5382,7 +6181,7 @@
       </c>
       <c r="M103" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>05:19</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="18" customHeight="1">
@@ -5392,12 +6191,22 @@
       <c r="B104" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="45"/>
+      <c r="C104" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D104" s="44"/>
-      <c r="E104" s="45"/>
-      <c r="F104" s="80"/>
-      <c r="G104" s="45"/>
-      <c r="H104" s="44"/>
+      <c r="E104" s="45" t="s">
+        <v>388</v>
+      </c>
+      <c r="F104" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="G104" s="45" t="s">
+        <v>389</v>
+      </c>
+      <c r="H104" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I104" s="41" t="s">
         <v>18</v>
       </c>
@@ -5410,11 +6219,11 @@
       </c>
       <c r="L104" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>06:01</v>
       </c>
       <c r="M104" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>06:53</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="18" customHeight="1">
@@ -5424,10 +6233,18 @@
       <c r="B105" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="45"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="45"/>
-      <c r="F105" s="80"/>
+      <c r="C105" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="D105" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="E105" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="80" t="s">
+        <v>422</v>
+      </c>
       <c r="G105" s="45"/>
       <c r="H105" s="44"/>
       <c r="I105" s="41" t="s">
@@ -5438,11 +6255,11 @@
       </c>
       <c r="K105" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>07:21</v>
       </c>
       <c r="L105" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:26</v>
       </c>
       <c r="M105" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5456,12 +6273,18 @@
       <c r="B106" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C106" s="45"/>
+      <c r="C106" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D106" s="44"/>
       <c r="E106" s="45"/>
       <c r="F106" s="80"/>
-      <c r="G106" s="45"/>
-      <c r="H106" s="44"/>
+      <c r="G106" s="45" t="s">
+        <v>390</v>
+      </c>
+      <c r="H106" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I106" s="41" t="s">
         <v>16</v>
       </c>
@@ -5478,7 +6301,7 @@
       </c>
       <c r="M106" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>08:27</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="18" customHeight="1">
@@ -5488,12 +6311,22 @@
       <c r="B107" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="45"/>
+      <c r="C107" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D107" s="44"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="80"/>
-      <c r="G107" s="45"/>
-      <c r="H107" s="44"/>
+      <c r="E107" s="93">
+        <v>0.37569444444444444</v>
+      </c>
+      <c r="F107" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="G107" s="45" t="s">
+        <v>391</v>
+      </c>
+      <c r="H107" s="44" t="s">
+        <v>427</v>
+      </c>
       <c r="I107" s="41" t="s">
         <v>15</v>
       </c>
@@ -5506,11 +6339,11 @@
       </c>
       <c r="L107" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>09:01</v>
       </c>
       <c r="M107" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>09:52</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="18" customHeight="1">
@@ -5520,10 +6353,16 @@
       <c r="B108" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C108" s="45"/>
+      <c r="C108" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D108" s="44"/>
-      <c r="E108" s="45"/>
-      <c r="F108" s="80"/>
+      <c r="E108" s="45" t="s">
+        <v>392</v>
+      </c>
+      <c r="F108" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G108" s="45"/>
       <c r="H108" s="44"/>
       <c r="I108" s="41" t="s">
@@ -5538,7 +6377,7 @@
       </c>
       <c r="L108" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>10:35</v>
       </c>
       <c r="M108" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5552,12 +6391,20 @@
       <c r="B109" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C109" s="45"/>
-      <c r="D109" s="44"/>
+      <c r="C109" s="45" t="s">
+        <v>393</v>
+      </c>
+      <c r="D109" s="44" t="s">
+        <v>416</v>
+      </c>
       <c r="E109" s="45"/>
       <c r="F109" s="80"/>
-      <c r="G109" s="45"/>
-      <c r="H109" s="44"/>
+      <c r="G109" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="H109" s="44" t="s">
+        <v>427</v>
+      </c>
       <c r="I109" s="41" t="s">
         <v>13</v>
       </c>
@@ -5566,7 +6413,7 @@
       </c>
       <c r="K109" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11:45</v>
       </c>
       <c r="L109" s="6" t="str">
         <f t="shared" si="4"/>
@@ -5574,7 +6421,7 @@
       </c>
       <c r="M109" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>11:17</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="18" customHeight="1">
@@ -5586,10 +6433,18 @@
       </c>
       <c r="C110" s="44"/>
       <c r="D110" s="44"/>
-      <c r="E110" s="45"/>
-      <c r="F110" s="80"/>
-      <c r="G110" s="45"/>
-      <c r="H110" s="44"/>
+      <c r="E110" s="45" t="s">
+        <v>369</v>
+      </c>
+      <c r="F110" s="80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G110" s="45" t="s">
+        <v>394</v>
+      </c>
+      <c r="H110" s="44" t="s">
+        <v>426</v>
+      </c>
       <c r="I110" s="41" t="s">
         <v>12</v>
       </c>
@@ -5602,11 +6457,11 @@
       </c>
       <c r="L110" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>12:00</v>
       </c>
       <c r="M110" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>12:47</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="18" customHeight="1">
@@ -5616,10 +6471,16 @@
       <c r="B111" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="45"/>
+      <c r="C111" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D111" s="44"/>
-      <c r="E111" s="45"/>
-      <c r="F111" s="80"/>
+      <c r="E111" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="F111" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G111" s="45"/>
       <c r="H111" s="44"/>
       <c r="I111" s="41" t="s">
@@ -5634,7 +6495,7 @@
       </c>
       <c r="L111" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>13:30</v>
       </c>
       <c r="M111" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5648,12 +6509,22 @@
       <c r="B112" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="45"/>
+      <c r="C112" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D112" s="44"/>
-      <c r="E112" s="45"/>
-      <c r="F112" s="80"/>
-      <c r="G112" s="45"/>
-      <c r="H112" s="44"/>
+      <c r="E112" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F112" s="80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G112" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="H112" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I112" s="41" t="s">
         <v>10</v>
       </c>
@@ -5666,11 +6537,11 @@
       </c>
       <c r="L112" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>14:58</v>
       </c>
       <c r="M112" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>14:15</v>
       </c>
     </row>
     <row r="113" spans="1:13" ht="18" customHeight="1">
@@ -5680,12 +6551,20 @@
       <c r="B113" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C113" s="45"/>
-      <c r="D113" s="44"/>
+      <c r="C113" s="45" t="s">
+        <v>395</v>
+      </c>
+      <c r="D113" s="44" t="s">
+        <v>417</v>
+      </c>
       <c r="E113" s="45"/>
       <c r="F113" s="80"/>
-      <c r="G113" s="98"/>
-      <c r="H113" s="44"/>
+      <c r="G113" s="98" t="s">
+        <v>396</v>
+      </c>
+      <c r="H113" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I113" s="97" t="s">
         <v>9</v>
       </c>
@@ -5694,7 +6573,7 @@
       </c>
       <c r="K113" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>15:52</v>
       </c>
       <c r="L113" s="6" t="str">
         <f t="shared" si="4"/>
@@ -5702,7 +6581,7 @@
       </c>
       <c r="M113" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>15:49</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="18" customHeight="1">
@@ -5712,10 +6591,16 @@
       <c r="B114" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C114" s="43"/>
+      <c r="C114" s="43" t="s">
+        <v>338</v>
+      </c>
       <c r="D114" s="42"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="79"/>
+      <c r="E114" s="43" t="s">
+        <v>397</v>
+      </c>
+      <c r="F114" s="79" t="s">
+        <v>423</v>
+      </c>
       <c r="G114" s="43"/>
       <c r="H114" s="42"/>
       <c r="I114" s="41" t="s">
@@ -5730,7 +6615,7 @@
       </c>
       <c r="L114" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>16:33</v>
       </c>
       <c r="M114" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5744,12 +6629,18 @@
       <c r="B115" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C115" s="45"/>
+      <c r="C115" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D115" s="44"/>
       <c r="E115" s="45"/>
       <c r="F115" s="80"/>
-      <c r="G115" s="45"/>
-      <c r="H115" s="44"/>
+      <c r="G115" s="45" t="s">
+        <v>398</v>
+      </c>
+      <c r="H115" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I115" s="41" t="s">
         <v>7</v>
       </c>
@@ -5766,7 +6657,7 @@
       </c>
       <c r="M115" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>17:21</v>
       </c>
     </row>
     <row r="116" spans="1:13" ht="18" customHeight="1">
@@ -5776,12 +6667,24 @@
       <c r="B116" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C116" s="44"/>
-      <c r="D116" s="44"/>
-      <c r="E116" s="45"/>
-      <c r="F116" s="80"/>
-      <c r="G116" s="45"/>
-      <c r="H116" s="44"/>
+      <c r="C116" s="93">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="D116" s="44" t="s">
+        <v>418</v>
+      </c>
+      <c r="E116" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="F116" s="80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G116" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="H116" s="44" t="s">
+        <v>424</v>
+      </c>
       <c r="I116" s="41" t="s">
         <v>6</v>
       </c>
@@ -5790,15 +6693,15 @@
       </c>
       <c r="K116" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>18:42</v>
       </c>
       <c r="L116" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>18:00</v>
       </c>
       <c r="M116" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>18:56</v>
       </c>
     </row>
     <row r="117" spans="1:13" ht="18" customHeight="1">
@@ -5808,10 +6711,16 @@
       <c r="B117" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C117" s="45"/>
+      <c r="C117" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D117" s="44"/>
-      <c r="E117" s="45"/>
-      <c r="F117" s="80"/>
+      <c r="E117" s="45" t="s">
+        <v>399</v>
+      </c>
+      <c r="F117" s="80" t="s">
+        <v>422</v>
+      </c>
       <c r="G117" s="45"/>
       <c r="H117" s="44"/>
       <c r="I117" s="41" t="s">
@@ -5826,7 +6735,7 @@
       </c>
       <c r="L117" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>19:30</v>
       </c>
       <c r="M117" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5840,12 +6749,18 @@
       <c r="B118" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="45"/>
+      <c r="C118" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D118" s="44"/>
       <c r="E118" s="45"/>
       <c r="F118" s="80"/>
-      <c r="G118" s="45"/>
-      <c r="H118" s="44"/>
+      <c r="G118" s="45" t="s">
+        <v>400</v>
+      </c>
+      <c r="H118" s="44" t="s">
+        <v>426</v>
+      </c>
       <c r="I118" s="41" t="s">
         <v>4</v>
       </c>
@@ -5862,7 +6777,7 @@
       </c>
       <c r="M118" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>20:24</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="18" customHeight="1">
@@ -5874,8 +6789,12 @@
       </c>
       <c r="C119" s="44"/>
       <c r="D119" s="44"/>
-      <c r="E119" s="45"/>
-      <c r="F119" s="80"/>
+      <c r="E119" s="45" t="s">
+        <v>401</v>
+      </c>
+      <c r="F119" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G119" s="45"/>
       <c r="H119" s="44"/>
       <c r="I119" s="41" t="s">
@@ -5890,7 +6809,7 @@
       </c>
       <c r="L119" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>21:00</v>
       </c>
       <c r="M119" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5904,10 +6823,16 @@
       <c r="B120" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C120" s="45"/>
+      <c r="C120" s="45" t="s">
+        <v>338</v>
+      </c>
       <c r="D120" s="44"/>
-      <c r="E120" s="45"/>
-      <c r="F120" s="80"/>
+      <c r="E120" s="45" t="s">
+        <v>402</v>
+      </c>
+      <c r="F120" s="80" t="s">
+        <v>423</v>
+      </c>
       <c r="G120" s="45"/>
       <c r="H120" s="45"/>
       <c r="I120" s="41" t="s">
@@ -5922,7 +6847,7 @@
       </c>
       <c r="L120" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>22:27</v>
       </c>
       <c r="M120" s="6" t="str">
         <f t="shared" si="5"/>
@@ -5936,12 +6861,20 @@
       <c r="B121" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C121" s="49"/>
-      <c r="D121" s="48"/>
+      <c r="C121" s="49" t="s">
+        <v>403</v>
+      </c>
+      <c r="D121" s="48" t="s">
+        <v>412</v>
+      </c>
       <c r="E121" s="49"/>
       <c r="F121" s="81"/>
-      <c r="G121" s="49"/>
-      <c r="H121" s="48"/>
+      <c r="G121" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="H121" s="48" t="s">
+        <v>426</v>
+      </c>
       <c r="I121" s="47" t="s">
         <v>1</v>
       </c>
@@ -5950,7 +6883,7 @@
       </c>
       <c r="K121" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>23:12</v>
       </c>
       <c r="L121" s="6" t="str">
         <f t="shared" si="4"/>
@@ -5958,7 +6891,7 @@
       </c>
       <c r="M121" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>23:22</v>
       </c>
     </row>
     <row r="122" spans="1:13" ht="18" customHeight="1">
@@ -5968,12 +6901,22 @@
       <c r="B122" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C122" s="52"/>
+      <c r="C122" s="52" t="s">
+        <v>338</v>
+      </c>
       <c r="D122" s="51"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="82"/>
-      <c r="G122" s="52"/>
-      <c r="H122" s="51"/>
+      <c r="E122" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="F122" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="G122" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H122" s="51" t="s">
+        <v>424</v>
+      </c>
       <c r="I122" s="50" t="s">
         <v>24</v>
       </c>
@@ -5986,11 +6929,11 @@
       </c>
       <c r="L122" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>00:00</v>
       </c>
       <c r="M122" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>00:00</v>
       </c>
     </row>
     <row r="123" spans="1:13" ht="18" customHeight="1">
@@ -6000,12 +6943,22 @@
       <c r="B123" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C123" s="54"/>
+      <c r="C123" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D123" s="53"/>
-      <c r="E123" s="54"/>
-      <c r="F123" s="83"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="53"/>
+      <c r="E123" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="F123" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G123" s="55" t="s">
+        <v>435</v>
+      </c>
+      <c r="H123" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I123" s="50" t="s">
         <v>23</v>
       </c>
@@ -6018,11 +6971,11 @@
       </c>
       <c r="L123" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>01:25</v>
       </c>
       <c r="M123" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>01:28</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="18" customHeight="1">
@@ -6032,12 +6985,22 @@
       <c r="B124" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C124" s="54"/>
+      <c r="C124" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D124" s="53"/>
-      <c r="E124" s="54"/>
-      <c r="F124" s="83"/>
-      <c r="G124" s="54"/>
-      <c r="H124" s="53"/>
+      <c r="E124" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="F124" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G124" s="54" t="s">
+        <v>436</v>
+      </c>
+      <c r="H124" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I124" s="50" t="s">
         <v>22</v>
       </c>
@@ -6050,11 +7013,11 @@
       </c>
       <c r="L124" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>02:53</v>
       </c>
       <c r="M124" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>02:58</v>
       </c>
     </row>
     <row r="125" spans="1:13" ht="18" customHeight="1">
@@ -6064,7 +7027,9 @@
       <c r="B125" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C125" s="54"/>
+      <c r="C125" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D125" s="53"/>
       <c r="E125" s="54"/>
       <c r="F125" s="83"/>
@@ -6096,12 +7061,22 @@
       <c r="B126" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C126" s="54"/>
+      <c r="C126" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D126" s="53"/>
-      <c r="E126" s="54"/>
-      <c r="F126" s="83"/>
-      <c r="G126" s="55"/>
-      <c r="H126" s="53"/>
+      <c r="E126" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="F126" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G126" s="55" t="s">
+        <v>357</v>
+      </c>
+      <c r="H126" s="53" t="s">
+        <v>426</v>
+      </c>
       <c r="I126" s="50" t="s">
         <v>20</v>
       </c>
@@ -6114,11 +7089,11 @@
       </c>
       <c r="L126" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>04:28</v>
       </c>
       <c r="M126" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>04:31</v>
       </c>
     </row>
     <row r="127" spans="1:13" ht="18" customHeight="1">
@@ -6128,10 +7103,16 @@
       <c r="B127" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="54"/>
+      <c r="C127" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D127" s="53"/>
-      <c r="E127" s="54"/>
-      <c r="F127" s="83"/>
+      <c r="E127" s="54" t="s">
+        <v>437</v>
+      </c>
+      <c r="F127" s="83" t="s">
+        <v>422</v>
+      </c>
       <c r="G127" s="54"/>
       <c r="H127" s="53"/>
       <c r="I127" s="50" t="s">
@@ -6146,7 +7127,7 @@
       </c>
       <c r="L127" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>05:57</v>
       </c>
       <c r="M127" s="6" t="str">
         <f t="shared" si="5"/>
@@ -6160,12 +7141,20 @@
       <c r="B128" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C128" s="55"/>
-      <c r="D128" s="53"/>
+      <c r="C128" s="55" t="s">
+        <v>404</v>
+      </c>
+      <c r="D128" s="53" t="s">
+        <v>419</v>
+      </c>
       <c r="E128" s="54"/>
       <c r="F128" s="83"/>
-      <c r="G128" s="54"/>
-      <c r="H128" s="53"/>
+      <c r="G128" s="54" t="s">
+        <v>438</v>
+      </c>
+      <c r="H128" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I128" s="50" t="s">
         <v>18</v>
       </c>
@@ -6174,7 +7163,7 @@
       </c>
       <c r="K128" s="6" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>06:48</v>
       </c>
       <c r="L128" s="6" t="str">
         <f t="shared" si="4"/>
@@ -6182,7 +7171,7 @@
       </c>
       <c r="M128" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>06:05</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="18" customHeight="1">
@@ -6194,10 +7183,18 @@
       </c>
       <c r="C129" s="53"/>
       <c r="D129" s="53"/>
-      <c r="E129" s="54"/>
-      <c r="F129" s="83"/>
-      <c r="G129" s="55"/>
-      <c r="H129" s="53"/>
+      <c r="E129" s="54" t="s">
+        <v>439</v>
+      </c>
+      <c r="F129" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G129" s="55" t="s">
+        <v>440</v>
+      </c>
+      <c r="H129" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I129" s="50" t="s">
         <v>17</v>
       </c>
@@ -6210,11 +7207,11 @@
       </c>
       <c r="L129" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>07:22</v>
       </c>
       <c r="M129" s="6" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>07:37</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="18" customHeight="1">
@@ -6224,10 +7221,16 @@
       <c r="B130" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C130" s="54"/>
+      <c r="C130" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D130" s="53"/>
-      <c r="E130" s="54"/>
-      <c r="F130" s="83"/>
+      <c r="E130" s="54" t="s">
+        <v>441</v>
+      </c>
+      <c r="F130" s="83" t="s">
+        <v>423</v>
+      </c>
       <c r="G130" s="54"/>
       <c r="H130" s="53"/>
       <c r="I130" s="50" t="s">
@@ -6242,7 +7245,7 @@
       </c>
       <c r="L130" s="6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>08:56</v>
       </c>
       <c r="M130" s="6" t="str">
         <f t="shared" si="5"/>
@@ -6256,12 +7259,18 @@
       <c r="B131" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C131" s="54"/>
+      <c r="C131" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D131" s="53"/>
       <c r="E131" s="54"/>
       <c r="F131" s="83"/>
-      <c r="G131" s="54"/>
-      <c r="H131" s="53"/>
+      <c r="G131" s="54" t="s">
+        <v>442</v>
+      </c>
+      <c r="H131" s="53" t="s">
+        <v>427</v>
+      </c>
       <c r="I131" s="50" t="s">
         <v>15</v>
       </c>
@@ -6278,7 +7287,7 @@
       </c>
       <c r="M131" s="6" t="str">
         <f t="shared" ref="M131:M169" si="8">IF($G131&lt;&gt;"",TEXT($G131,"HH:MM"),"")</f>
-        <v/>
+        <v>09:10</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="18" customHeight="1">
@@ -6288,12 +7297,22 @@
       <c r="B132" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C132" s="54"/>
+      <c r="C132" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D132" s="53"/>
-      <c r="E132" s="54"/>
-      <c r="F132" s="83"/>
-      <c r="G132" s="55"/>
-      <c r="H132" s="53"/>
+      <c r="E132" s="54" t="s">
+        <v>443</v>
+      </c>
+      <c r="F132" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G132" s="55" t="s">
+        <v>366</v>
+      </c>
+      <c r="H132" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I132" s="50" t="s">
         <v>14</v>
       </c>
@@ -6306,11 +7325,11 @@
       </c>
       <c r="L132" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>10:27</v>
       </c>
       <c r="M132" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>10:37</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="18" customHeight="1">
@@ -6320,10 +7339,18 @@
       <c r="B133" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C133" s="53"/>
-      <c r="D133" s="53"/>
-      <c r="E133" s="54"/>
-      <c r="F133" s="83"/>
+      <c r="C133" s="56">
+        <v>0.46458333333333335</v>
+      </c>
+      <c r="D133" s="53" t="s">
+        <v>414</v>
+      </c>
+      <c r="E133" s="54" t="s">
+        <v>444</v>
+      </c>
+      <c r="F133" s="83" t="s">
+        <v>422</v>
+      </c>
       <c r="G133" s="54"/>
       <c r="H133" s="53"/>
       <c r="I133" s="50" t="s">
@@ -6334,11 +7361,11 @@
       </c>
       <c r="K133" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>11:09</v>
       </c>
       <c r="L133" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>11:54</v>
       </c>
       <c r="M133" s="6" t="str">
         <f t="shared" si="8"/>
@@ -6352,12 +7379,18 @@
       <c r="B134" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C134" s="54"/>
+      <c r="C134" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D134" s="53"/>
       <c r="E134" s="56"/>
       <c r="F134" s="83"/>
-      <c r="G134" s="54"/>
-      <c r="H134" s="53"/>
+      <c r="G134" s="54" t="s">
+        <v>445</v>
+      </c>
+      <c r="H134" s="53" t="s">
+        <v>427</v>
+      </c>
       <c r="I134" s="50" t="s">
         <v>12</v>
       </c>
@@ -6374,7 +7407,7 @@
       </c>
       <c r="M134" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>12:08</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="18" customHeight="1">
@@ -6386,10 +7419,18 @@
       </c>
       <c r="C135" s="56"/>
       <c r="D135" s="53"/>
-      <c r="E135" s="54"/>
-      <c r="F135" s="83"/>
-      <c r="G135" s="55"/>
-      <c r="H135" s="53"/>
+      <c r="E135" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="F135" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G135" s="55" t="s">
+        <v>446</v>
+      </c>
+      <c r="H135" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I135" s="50" t="s">
         <v>11</v>
       </c>
@@ -6402,11 +7443,11 @@
       </c>
       <c r="L135" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>13:19</v>
       </c>
       <c r="M135" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>13:38</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="18" customHeight="1">
@@ -6416,10 +7457,18 @@
       <c r="B136" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C136" s="54"/>
-      <c r="D136" s="53"/>
-      <c r="E136" s="54"/>
-      <c r="F136" s="83"/>
+      <c r="C136" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="D136" s="53" t="s">
+        <v>420</v>
+      </c>
+      <c r="E136" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="F136" s="83" t="s">
+        <v>423</v>
+      </c>
       <c r="G136" s="54"/>
       <c r="H136" s="53"/>
       <c r="I136" s="50" t="s">
@@ -6430,11 +7479,11 @@
       </c>
       <c r="K136" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>14:00</v>
       </c>
       <c r="L136" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>14:48</v>
       </c>
       <c r="M136" s="6" t="str">
         <f t="shared" si="8"/>
@@ -6448,12 +7497,18 @@
       <c r="B137" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C137" s="54"/>
+      <c r="C137" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D137" s="53"/>
       <c r="E137" s="54"/>
       <c r="F137" s="83"/>
-      <c r="G137" s="55"/>
-      <c r="H137" s="53"/>
+      <c r="G137" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="H137" s="53" t="s">
+        <v>426</v>
+      </c>
       <c r="I137" s="50" t="s">
         <v>9</v>
       </c>
@@ -6470,7 +7525,7 @@
       </c>
       <c r="M137" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15:03</v>
       </c>
     </row>
     <row r="138" spans="1:13" ht="18" customHeight="1">
@@ -6480,12 +7535,24 @@
       <c r="B138" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C138" s="53"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="54"/>
-      <c r="F138" s="83"/>
-      <c r="G138" s="54"/>
-      <c r="H138" s="53"/>
+      <c r="C138" s="56">
+        <v>0.68819444444444444</v>
+      </c>
+      <c r="D138" s="53" t="s">
+        <v>421</v>
+      </c>
+      <c r="E138" s="54" t="s">
+        <v>447</v>
+      </c>
+      <c r="F138" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G138" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="H138" s="53" t="s">
+        <v>424</v>
+      </c>
       <c r="I138" s="50">
         <v>16</v>
       </c>
@@ -6494,15 +7561,15 @@
       </c>
       <c r="K138" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16:31</v>
       </c>
       <c r="L138" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>16:23</v>
       </c>
       <c r="M138" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>16:37</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="18" customHeight="1">
@@ -6512,10 +7579,16 @@
       <c r="B139" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C139" s="54"/>
+      <c r="C139" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D139" s="53"/>
-      <c r="E139" s="54"/>
-      <c r="F139" s="83"/>
+      <c r="E139" s="54" t="s">
+        <v>88</v>
+      </c>
+      <c r="F139" s="83" t="s">
+        <v>423</v>
+      </c>
       <c r="G139" s="54"/>
       <c r="H139" s="53"/>
       <c r="I139" s="50" t="s">
@@ -6530,7 +7603,7 @@
       </c>
       <c r="L139" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>17:52</v>
       </c>
       <c r="M139" s="6" t="str">
         <f t="shared" si="8"/>
@@ -6544,12 +7617,18 @@
       <c r="B140" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C140" s="54"/>
+      <c r="C140" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D140" s="53"/>
       <c r="E140" s="54"/>
       <c r="F140" s="83"/>
-      <c r="G140" s="54"/>
-      <c r="H140" s="53"/>
+      <c r="G140" s="54" t="s">
+        <v>448</v>
+      </c>
+      <c r="H140" s="53" t="s">
+        <v>426</v>
+      </c>
       <c r="I140" s="50" t="s">
         <v>6</v>
       </c>
@@ -6566,7 +7645,7 @@
       </c>
       <c r="M140" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18:09</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="18" customHeight="1">
@@ -6576,12 +7655,24 @@
       <c r="B141" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C141" s="54"/>
-      <c r="D141" s="53"/>
-      <c r="E141" s="54"/>
-      <c r="F141" s="83"/>
-      <c r="G141" s="54"/>
-      <c r="H141" s="53"/>
+      <c r="C141" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="D141" s="53" t="s">
+        <v>416</v>
+      </c>
+      <c r="E141" s="54" t="s">
+        <v>449</v>
+      </c>
+      <c r="F141" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G141" s="54" t="s">
+        <v>450</v>
+      </c>
+      <c r="H141" s="53" t="s">
+        <v>427</v>
+      </c>
       <c r="I141" s="50" t="s">
         <v>5</v>
       </c>
@@ -6590,15 +7681,15 @@
       </c>
       <c r="K141" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>19:38</v>
       </c>
       <c r="L141" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>19:18</v>
       </c>
       <c r="M141" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>19:41</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="18" customHeight="1">
@@ -6608,10 +7699,16 @@
       <c r="B142" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C142" s="54"/>
+      <c r="C142" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D142" s="53"/>
-      <c r="E142" s="54"/>
-      <c r="F142" s="83"/>
+      <c r="E142" s="54" t="s">
+        <v>451</v>
+      </c>
+      <c r="F142" s="83" t="s">
+        <v>422</v>
+      </c>
       <c r="G142" s="54"/>
       <c r="H142" s="53"/>
       <c r="I142" s="50" t="s">
@@ -6626,7 +7723,7 @@
       </c>
       <c r="L142" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20:53</v>
       </c>
       <c r="M142" s="6" t="str">
         <f t="shared" si="8"/>
@@ -6640,12 +7737,18 @@
       <c r="B143" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="54"/>
+      <c r="C143" s="54" t="s">
+        <v>338</v>
+      </c>
       <c r="D143" s="53"/>
       <c r="E143" s="54"/>
       <c r="F143" s="83"/>
-      <c r="G143" s="54"/>
-      <c r="H143" s="53"/>
+      <c r="G143" s="54" t="s">
+        <v>452</v>
+      </c>
+      <c r="H143" s="53" t="s">
+        <v>427</v>
+      </c>
       <c r="I143" s="50" t="s">
         <v>3</v>
       </c>
@@ -6662,7 +7765,7 @@
       </c>
       <c r="M143" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>21:14</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="18" customHeight="1">
@@ -6672,12 +7775,24 @@
       <c r="B144" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C144" s="54"/>
-      <c r="D144" s="53"/>
-      <c r="E144" s="54"/>
-      <c r="F144" s="83"/>
-      <c r="G144" s="54"/>
-      <c r="H144" s="53"/>
+      <c r="C144" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="D144" s="53" t="s">
+        <v>432</v>
+      </c>
+      <c r="E144" s="54" t="s">
+        <v>453</v>
+      </c>
+      <c r="F144" s="83" t="s">
+        <v>423</v>
+      </c>
+      <c r="G144" s="54" t="s">
+        <v>381</v>
+      </c>
+      <c r="H144" s="53" t="s">
+        <v>427</v>
+      </c>
       <c r="I144" s="50" t="s">
         <v>2</v>
       </c>
@@ -6686,15 +7801,15 @@
       </c>
       <c r="K144" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>22:29</v>
       </c>
       <c r="L144" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>22:21</v>
       </c>
       <c r="M144" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>22:43</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="18" customHeight="1" thickBot="1">
@@ -6706,8 +7821,12 @@
       </c>
       <c r="C145" s="59"/>
       <c r="D145" s="58"/>
-      <c r="E145" s="59"/>
-      <c r="F145" s="84"/>
+      <c r="E145" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="F145" s="84" t="s">
+        <v>422</v>
+      </c>
       <c r="G145" s="59"/>
       <c r="H145" s="58"/>
       <c r="I145" s="57" t="s">
@@ -6722,7 +7841,7 @@
       </c>
       <c r="L145" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23:52</v>
       </c>
       <c r="M145" s="6" t="str">
         <f t="shared" si="8"/>
@@ -6770,10 +7889,18 @@
       </c>
       <c r="C147" s="63"/>
       <c r="D147" s="63"/>
-      <c r="E147" s="64"/>
-      <c r="F147" s="86"/>
-      <c r="G147" s="64"/>
-      <c r="H147" s="63"/>
+      <c r="E147" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F147" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G147" s="64" t="s">
+        <v>455</v>
+      </c>
+      <c r="H147" s="63" t="s">
+        <v>424</v>
+      </c>
       <c r="I147" s="60" t="s">
         <v>23</v>
       </c>
@@ -6786,11 +7913,11 @@
       </c>
       <c r="L147" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>01:01</v>
       </c>
       <c r="M147" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>01:00</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="18" customHeight="1">
@@ -6800,12 +7927,24 @@
       <c r="B148" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C148" s="64"/>
-      <c r="D148" s="63"/>
-      <c r="E148" s="64"/>
-      <c r="F148" s="86"/>
-      <c r="G148" s="64"/>
-      <c r="H148" s="63"/>
+      <c r="C148" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148" s="63" t="s">
+        <v>428</v>
+      </c>
+      <c r="E148" s="64" t="s">
+        <v>456</v>
+      </c>
+      <c r="F148" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G148" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="H148" s="63" t="s">
+        <v>424</v>
+      </c>
       <c r="I148" s="60" t="s">
         <v>22</v>
       </c>
@@ -6814,15 +7953,15 @@
       </c>
       <c r="K148" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>02:56</v>
       </c>
       <c r="L148" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>02:28</v>
       </c>
       <c r="M148" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>02:29</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="18" customHeight="1">
@@ -6836,8 +7975,12 @@
       <c r="D149" s="63"/>
       <c r="E149" s="64"/>
       <c r="F149" s="86"/>
-      <c r="G149" s="65"/>
-      <c r="H149" s="63"/>
+      <c r="G149" s="65" t="s">
+        <v>457</v>
+      </c>
+      <c r="H149" s="63" t="s">
+        <v>424</v>
+      </c>
       <c r="I149" s="60" t="s">
         <v>21</v>
       </c>
@@ -6854,7 +7997,7 @@
       </c>
       <c r="M149" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>03:56</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="18" customHeight="1">
@@ -6898,10 +8041,18 @@
       </c>
       <c r="C151" s="64"/>
       <c r="D151" s="63"/>
-      <c r="E151" s="90"/>
-      <c r="F151" s="86"/>
-      <c r="G151" s="64"/>
-      <c r="H151" s="63"/>
+      <c r="E151" s="90" t="s">
+        <v>458</v>
+      </c>
+      <c r="F151" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G151" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="H151" s="63" t="s">
+        <v>427</v>
+      </c>
       <c r="I151" s="60" t="s">
         <v>19</v>
       </c>
@@ -6914,11 +8065,11 @@
       </c>
       <c r="L151" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>05:25</v>
       </c>
       <c r="M151" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>05:26</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="18" customHeight="1">
@@ -6928,12 +8079,24 @@
       <c r="B152" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C152" s="90"/>
-      <c r="D152" s="63"/>
-      <c r="E152" s="90"/>
-      <c r="F152" s="86"/>
-      <c r="G152" s="64"/>
-      <c r="H152" s="63"/>
+      <c r="C152" s="90" t="s">
+        <v>460</v>
+      </c>
+      <c r="D152" s="63" t="s">
+        <v>429</v>
+      </c>
+      <c r="E152" s="90" t="s">
+        <v>389</v>
+      </c>
+      <c r="F152" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G152" s="64" t="s">
+        <v>461</v>
+      </c>
+      <c r="H152" s="63" t="s">
+        <v>427</v>
+      </c>
       <c r="I152" s="60" t="s">
         <v>18</v>
       </c>
@@ -6942,15 +8105,15 @@
       </c>
       <c r="K152" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>06:27</v>
       </c>
       <c r="L152" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>06:53</v>
       </c>
       <c r="M152" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>06:54</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="18" customHeight="1">
@@ -6994,10 +8157,18 @@
       </c>
       <c r="C154" s="64"/>
       <c r="D154" s="63"/>
-      <c r="E154" s="64"/>
-      <c r="F154" s="86"/>
-      <c r="G154" s="64"/>
-      <c r="H154" s="63"/>
+      <c r="E154" s="64" t="s">
+        <v>390</v>
+      </c>
+      <c r="F154" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G154" s="64" t="s">
+        <v>96</v>
+      </c>
+      <c r="H154" s="63" t="s">
+        <v>426</v>
+      </c>
       <c r="I154" s="60" t="s">
         <v>16</v>
       </c>
@@ -7010,11 +8181,11 @@
       </c>
       <c r="L154" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>08:27</v>
       </c>
       <c r="M154" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>08:24</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="18" customHeight="1">
@@ -7024,12 +8195,24 @@
       <c r="B155" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C155" s="64"/>
-      <c r="D155" s="63"/>
-      <c r="E155" s="64"/>
-      <c r="F155" s="86"/>
-      <c r="G155" s="65"/>
-      <c r="H155" s="63"/>
+      <c r="C155" s="64" t="s">
+        <v>462</v>
+      </c>
+      <c r="D155" s="63" t="s">
+        <v>433</v>
+      </c>
+      <c r="E155" s="64" t="s">
+        <v>463</v>
+      </c>
+      <c r="F155" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G155" s="65" t="s">
+        <v>463</v>
+      </c>
+      <c r="H155" s="63" t="s">
+        <v>426</v>
+      </c>
       <c r="I155" s="60" t="s">
         <v>15</v>
       </c>
@@ -7038,15 +8221,15 @@
       </c>
       <c r="K155" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>09:38</v>
       </c>
       <c r="L155" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>09:53</v>
       </c>
       <c r="M155" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>09:53</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="18" customHeight="1">
@@ -7090,10 +8273,18 @@
       </c>
       <c r="C157" s="64"/>
       <c r="D157" s="63"/>
-      <c r="E157" s="64"/>
-      <c r="F157" s="86"/>
-      <c r="G157" s="64"/>
-      <c r="H157" s="63"/>
+      <c r="E157" s="64" t="s">
+        <v>464</v>
+      </c>
+      <c r="F157" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G157" s="64" t="s">
+        <v>465</v>
+      </c>
+      <c r="H157" s="63" t="s">
+        <v>427</v>
+      </c>
       <c r="I157" s="60" t="s">
         <v>13</v>
       </c>
@@ -7106,11 +8297,11 @@
       </c>
       <c r="L157" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>11:18</v>
       </c>
       <c r="M157" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>11:20</v>
       </c>
     </row>
     <row r="158" spans="1:13" ht="18" customHeight="1">
@@ -7122,10 +8313,18 @@
       </c>
       <c r="C158" s="64"/>
       <c r="D158" s="63"/>
-      <c r="E158" s="64"/>
-      <c r="F158" s="86"/>
-      <c r="G158" s="64"/>
-      <c r="H158" s="63"/>
+      <c r="E158" s="64" t="s">
+        <v>466</v>
+      </c>
+      <c r="F158" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G158" s="64" t="s">
+        <v>394</v>
+      </c>
+      <c r="H158" s="63" t="s">
+        <v>427</v>
+      </c>
       <c r="I158" s="60" t="s">
         <v>12</v>
       </c>
@@ -7138,11 +8337,11 @@
       </c>
       <c r="L158" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>12:48</v>
       </c>
       <c r="M158" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>12:47</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="18" customHeight="1">
@@ -7152,9 +8351,13 @@
       <c r="B159" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C159" s="64"/>
-      <c r="D159" s="63"/>
-      <c r="E159" s="64"/>
+      <c r="C159" s="64" t="s">
+        <v>467</v>
+      </c>
+      <c r="D159" s="63" t="s">
+        <v>430</v>
+      </c>
+      <c r="E159" s="63"/>
       <c r="F159" s="86"/>
       <c r="G159" s="64"/>
       <c r="H159" s="63"/>
@@ -7166,7 +8369,7 @@
       </c>
       <c r="K159" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>13:16</v>
       </c>
       <c r="L159" s="6" t="str">
         <f t="shared" si="7"/>
@@ -7186,10 +8389,18 @@
       </c>
       <c r="C160" s="64"/>
       <c r="D160" s="63"/>
-      <c r="E160" s="64"/>
-      <c r="F160" s="86"/>
-      <c r="G160" s="64"/>
-      <c r="H160" s="63"/>
+      <c r="E160" s="64" t="s">
+        <v>468</v>
+      </c>
+      <c r="F160" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G160" s="64" t="s">
+        <v>469</v>
+      </c>
+      <c r="H160" s="63" t="s">
+        <v>426</v>
+      </c>
       <c r="I160" s="60" t="s">
         <v>10</v>
       </c>
@@ -7202,11 +8413,11 @@
       </c>
       <c r="L160" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>14:23</v>
       </c>
       <c r="M160" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>14:16</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="18" customHeight="1">
@@ -7218,10 +8429,18 @@
       </c>
       <c r="C161" s="64"/>
       <c r="D161" s="63"/>
-      <c r="E161" s="64"/>
-      <c r="F161" s="86"/>
-      <c r="G161" s="65"/>
-      <c r="H161" s="63"/>
+      <c r="E161" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="F161" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G161" s="65" t="s">
+        <v>471</v>
+      </c>
+      <c r="H161" s="63" t="s">
+        <v>427</v>
+      </c>
       <c r="I161" s="60" t="s">
         <v>9</v>
       </c>
@@ -7234,11 +8453,11 @@
       </c>
       <c r="L161" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>15:56</v>
       </c>
       <c r="M161" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>15:44</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="18" customHeight="1">
@@ -7248,8 +8467,12 @@
       <c r="B162" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C162" s="64"/>
-      <c r="D162" s="63"/>
+      <c r="C162" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="D162" s="63" t="s">
+        <v>415</v>
+      </c>
       <c r="E162" s="64"/>
       <c r="F162" s="86"/>
       <c r="G162" s="64"/>
@@ -7262,7 +8485,7 @@
       </c>
       <c r="K162" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>16:36</v>
       </c>
       <c r="L162" s="6" t="str">
         <f t="shared" si="7"/>
@@ -7282,10 +8505,18 @@
       </c>
       <c r="C163" s="64"/>
       <c r="D163" s="63"/>
-      <c r="E163" s="64"/>
-      <c r="F163" s="86"/>
-      <c r="G163" s="64"/>
-      <c r="H163" s="63"/>
+      <c r="E163" s="64" t="s">
+        <v>473</v>
+      </c>
+      <c r="F163" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G163" s="64" t="s">
+        <v>474</v>
+      </c>
+      <c r="H163" s="63" t="s">
+        <v>424</v>
+      </c>
       <c r="I163" s="60" t="s">
         <v>7</v>
       </c>
@@ -7298,11 +8529,11 @@
       </c>
       <c r="L163" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>17:22</v>
       </c>
       <c r="M163" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>17:12</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="18" customHeight="1">
@@ -7314,10 +8545,18 @@
       </c>
       <c r="C164" s="64"/>
       <c r="D164" s="63"/>
-      <c r="E164" s="64"/>
-      <c r="F164" s="86"/>
-      <c r="G164" s="64"/>
-      <c r="H164" s="63"/>
+      <c r="E164" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="F164" s="86" t="s">
+        <v>423</v>
+      </c>
+      <c r="G164" s="64" t="s">
+        <v>475</v>
+      </c>
+      <c r="H164" s="63" t="s">
+        <v>426</v>
+      </c>
       <c r="I164" s="60" t="s">
         <v>6</v>
       </c>
@@ -7330,11 +8569,11 @@
       </c>
       <c r="L164" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>18:55</v>
       </c>
       <c r="M164" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>18:44</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="18" customHeight="1">
@@ -7344,8 +8583,12 @@
       <c r="B165" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C165" s="64"/>
-      <c r="D165" s="63"/>
+      <c r="C165" s="64" t="s">
+        <v>476</v>
+      </c>
+      <c r="D165" s="63" t="s">
+        <v>431</v>
+      </c>
       <c r="E165" s="64"/>
       <c r="F165" s="86"/>
       <c r="G165" s="64"/>
@@ -7358,7 +8601,7 @@
       </c>
       <c r="K165" s="6" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>19:48</v>
       </c>
       <c r="L165" s="6" t="str">
         <f t="shared" si="7"/>
@@ -7378,10 +8621,18 @@
       </c>
       <c r="C166" s="66"/>
       <c r="D166" s="63"/>
-      <c r="E166" s="64"/>
-      <c r="F166" s="86"/>
-      <c r="G166" s="64"/>
-      <c r="H166" s="63"/>
+      <c r="E166" s="64" t="s">
+        <v>477</v>
+      </c>
+      <c r="F166" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G166" s="64" t="s">
+        <v>478</v>
+      </c>
+      <c r="H166" s="63" t="s">
+        <v>426</v>
+      </c>
       <c r="I166" s="60" t="s">
         <v>4</v>
       </c>
@@ -7394,11 +8645,11 @@
       </c>
       <c r="L166" s="6" t="str">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20:21</v>
       </c>
       <c r="M166" s="6" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>20:19</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="18" customHeight="1">
@@ -7500,12 +8751,12 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 H12 D70 H120">
+  <conditionalFormatting sqref="G1:G76 E1:E158 C1:C1048576 H12 D70 G78:G1048576 H120 E160:E1048576">
     <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H119 D71:D1048576 H121:H1048576">
+  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H119 D71:D1048576 G77 H121:H1048576 E159">
     <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
@@ -7518,20 +8769,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717295CC-0D64-4C6E-BF3A-41575595C9E1}">
   <dimension ref="A1:M169"/>
-  <sheetFormatPr defaultColWidth="14.19921875" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.19921875" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.8984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.59765625" style="67" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.875" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="67" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.19921875" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="67" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="67" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.3984375" style="67" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.8984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="14.19921875" style="6"/>
+    <col min="10" max="10" width="3.375" style="67" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="14.25" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0FFF68-F683-4936-8B4B-D5722CD6FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF91ACA4-C5AD-4F64-B6FE-E4EC3DA5727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10815" yWindow="0" windowWidth="16140" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="485">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1218,9 +1218,6 @@
     <t>12:11</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>13:45</t>
   </si>
   <si>
@@ -1645,6 +1642,72 @@
   </si>
   <si>
     <t>10:00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>15:51</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>12:22</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>18:42</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>11:09</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>16:31</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>09:01</t>
+    </r>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1831,7 +1894,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2097,9 +2160,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2124,17 +2184,170 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="6" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="7" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2476,10 +2689,12 @@
   <cols>
     <col min="1" max="1" width="3.5" style="67" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="67" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="67" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="138" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.625" style="67" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="67" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="16.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="138" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="67" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="138" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="67" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="3.5" style="67" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.375" style="67" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.75" style="6" bestFit="1" customWidth="1"/>
@@ -2488,29 +2703,29 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="92" t="s">
+      <c r="G1" s="97" t="s">
         <v>324</v>
       </c>
-      <c r="H1" s="92" t="s">
+      <c r="H1" s="91" t="s">
         <v>325</v>
       </c>
       <c r="I1" s="1"/>
-      <c r="J1" s="95"/>
+      <c r="J1" s="94"/>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -2519,11 +2734,11 @@
       <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="98"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="98"/>
       <c r="F2" s="68"/>
-      <c r="G2" s="5"/>
+      <c r="G2" s="98"/>
       <c r="H2" s="4"/>
       <c r="I2" s="3" t="s">
         <v>31</v>
@@ -2551,11 +2766,11 @@
       <c r="B3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="98"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
+      <c r="E3" s="98"/>
       <c r="F3" s="68"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="98"/>
       <c r="H3" s="4"/>
       <c r="I3" s="3" t="s">
         <v>23</v>
@@ -2583,11 +2798,11 @@
       <c r="B4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="98"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="5"/>
+      <c r="E4" s="98"/>
       <c r="F4" s="68"/>
-      <c r="G4" s="5"/>
+      <c r="G4" s="98"/>
       <c r="H4" s="4"/>
       <c r="I4" s="3" t="s">
         <v>22</v>
@@ -2615,11 +2830,11 @@
       <c r="B5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="98"/>
       <c r="F5" s="68"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="98"/>
       <c r="H5" s="4"/>
       <c r="I5" s="3" t="s">
         <v>21</v>
@@ -2647,11 +2862,11 @@
       <c r="B6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="98"/>
       <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="98"/>
       <c r="F6" s="68"/>
-      <c r="G6" s="3"/>
+      <c r="G6" s="144"/>
       <c r="H6" s="4"/>
       <c r="I6" s="3" t="s">
         <v>20</v>
@@ -2679,11 +2894,11 @@
       <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="8"/>
+      <c r="C7" s="100"/>
       <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="98"/>
       <c r="F7" s="68"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="98"/>
       <c r="H7" s="4"/>
       <c r="I7" s="3" t="s">
         <v>19</v>
@@ -2711,11 +2926,11 @@
       <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="8"/>
+      <c r="E8" s="100"/>
       <c r="F8" s="68"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="98"/>
       <c r="H8" s="4"/>
       <c r="I8" s="3" t="s">
         <v>18</v>
@@ -2743,11 +2958,11 @@
       <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="5"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="98"/>
       <c r="F9" s="68"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="98"/>
       <c r="H9" s="4"/>
       <c r="I9" s="3" t="s">
         <v>17</v>
@@ -2775,11 +2990,11 @@
       <c r="B10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="98"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="98"/>
       <c r="F10" s="68"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="144"/>
       <c r="H10" s="4"/>
       <c r="I10" s="3" t="s">
         <v>16</v>
@@ -2807,11 +3022,11 @@
       <c r="B11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="8"/>
+      <c r="C11" s="100"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="98"/>
       <c r="F11" s="68"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="98"/>
       <c r="H11" s="4"/>
       <c r="I11" s="3" t="s">
         <v>15</v>
@@ -2839,11 +3054,11 @@
       <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="98"/>
       <c r="F12" s="68"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="98"/>
       <c r="H12" s="5"/>
       <c r="I12" s="3" t="s">
         <v>14</v>
@@ -2871,11 +3086,11 @@
       <c r="B13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="98"/>
       <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="98"/>
       <c r="F13" s="68"/>
-      <c r="G13" s="3"/>
+      <c r="G13" s="144"/>
       <c r="H13" s="4"/>
       <c r="I13" s="3" t="s">
         <v>13</v>
@@ -2903,11 +3118,11 @@
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="98"/>
       <c r="F14" s="68"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="98"/>
       <c r="H14" s="4"/>
       <c r="I14" s="3" t="s">
         <v>12</v>
@@ -2935,11 +3150,11 @@
       <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="5"/>
+      <c r="C15" s="98"/>
       <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="98"/>
       <c r="F15" s="68"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="98"/>
       <c r="H15" s="4"/>
       <c r="I15" s="3" t="s">
         <v>11</v>
@@ -2967,11 +3182,11 @@
       <c r="B16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="8"/>
+      <c r="C16" s="100"/>
       <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="98"/>
       <c r="F16" s="68"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="144"/>
       <c r="H16" s="4"/>
       <c r="I16" s="3" t="s">
         <v>10</v>
@@ -2999,11 +3214,11 @@
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="5"/>
+      <c r="C17" s="98"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
+      <c r="E17" s="98"/>
       <c r="F17" s="68"/>
-      <c r="G17" s="5"/>
+      <c r="G17" s="98"/>
       <c r="H17" s="4"/>
       <c r="I17" s="3" t="s">
         <v>9</v>
@@ -3031,11 +3246,11 @@
       <c r="B18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="5"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
+      <c r="E18" s="98"/>
       <c r="F18" s="68"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="144"/>
       <c r="H18" s="4"/>
       <c r="I18" s="3" t="s">
         <v>8</v>
@@ -3063,11 +3278,11 @@
       <c r="B19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="8"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
+      <c r="E19" s="98"/>
       <c r="F19" s="68"/>
-      <c r="G19" s="5"/>
+      <c r="G19" s="98"/>
       <c r="H19" s="4"/>
       <c r="I19" s="3" t="s">
         <v>7</v>
@@ -3095,11 +3310,11 @@
       <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
+      <c r="E20" s="98"/>
       <c r="F20" s="68"/>
-      <c r="G20" s="5"/>
+      <c r="G20" s="98"/>
       <c r="H20" s="4"/>
       <c r="I20" s="3" t="s">
         <v>6</v>
@@ -3127,11 +3342,11 @@
       <c r="B21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="98"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="68"/>
-      <c r="G21" s="3"/>
+      <c r="G21" s="144"/>
       <c r="H21" s="4"/>
       <c r="I21" s="3" t="s">
         <v>5</v>
@@ -3159,11 +3374,11 @@
       <c r="B22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="98"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="98"/>
       <c r="F22" s="68"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="98"/>
       <c r="H22" s="4"/>
       <c r="I22" s="3" t="s">
         <v>4</v>
@@ -3191,11 +3406,11 @@
       <c r="B23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="98"/>
       <c r="F23" s="68"/>
-      <c r="G23" s="5"/>
+      <c r="G23" s="98"/>
       <c r="H23" s="4"/>
       <c r="I23" s="3" t="s">
         <v>3</v>
@@ -3223,11 +3438,11 @@
       <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="5"/>
+      <c r="C24" s="98"/>
       <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="98"/>
       <c r="F24" s="68"/>
-      <c r="G24" s="3"/>
+      <c r="G24" s="144"/>
       <c r="H24" s="4"/>
       <c r="I24" s="3" t="s">
         <v>2</v>
@@ -3255,11 +3470,11 @@
       <c r="B25" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="11"/>
+      <c r="C25" s="101"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="11"/>
+      <c r="E25" s="101"/>
       <c r="F25" s="69"/>
-      <c r="G25" s="11"/>
+      <c r="G25" s="101"/>
       <c r="H25" s="10"/>
       <c r="I25" s="9" t="s">
         <v>1</v>
@@ -3287,11 +3502,11 @@
       <c r="B26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="102"/>
       <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
+      <c r="E26" s="139"/>
       <c r="F26" s="70"/>
-      <c r="G26" s="14"/>
+      <c r="G26" s="139"/>
       <c r="H26" s="13"/>
       <c r="I26" s="12" t="s">
         <v>24</v>
@@ -3319,11 +3534,11 @@
       <c r="B27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="16"/>
+      <c r="C27" s="103"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="17"/>
+      <c r="E27" s="104"/>
       <c r="F27" s="71"/>
-      <c r="G27" s="17"/>
+      <c r="G27" s="104"/>
       <c r="H27" s="15"/>
       <c r="I27" s="12" t="s">
         <v>23</v>
@@ -3351,11 +3566,11 @@
       <c r="B28" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="17"/>
+      <c r="C28" s="104"/>
       <c r="D28" s="15"/>
-      <c r="E28" s="17"/>
+      <c r="E28" s="104"/>
       <c r="F28" s="71"/>
-      <c r="G28" s="17"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="15"/>
       <c r="I28" s="12" t="s">
         <v>22</v>
@@ -3383,11 +3598,11 @@
       <c r="B29" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="16"/>
+      <c r="C29" s="103"/>
       <c r="D29" s="15"/>
-      <c r="E29" s="17"/>
+      <c r="E29" s="104"/>
       <c r="F29" s="71"/>
-      <c r="G29" s="12"/>
+      <c r="G29" s="145"/>
       <c r="H29" s="15"/>
       <c r="I29" s="12" t="s">
         <v>21</v>
@@ -3415,11 +3630,11 @@
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="15"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="104"/>
       <c r="F30" s="71"/>
-      <c r="G30" s="88"/>
+      <c r="G30" s="107"/>
       <c r="H30" s="15"/>
       <c r="I30" s="12" t="s">
         <v>20</v>
@@ -3447,11 +3662,11 @@
       <c r="B31" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="17"/>
+      <c r="C31" s="104"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="104"/>
       <c r="F31" s="71"/>
-      <c r="G31" s="17"/>
+      <c r="G31" s="104"/>
       <c r="H31" s="15"/>
       <c r="I31" s="12" t="s">
         <v>19</v>
@@ -3479,11 +3694,11 @@
       <c r="B32" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="17"/>
+      <c r="C32" s="104"/>
       <c r="D32" s="15"/>
-      <c r="E32" s="17"/>
+      <c r="E32" s="104"/>
       <c r="F32" s="71"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="145"/>
       <c r="H32" s="15"/>
       <c r="I32" s="12" t="s">
         <v>18</v>
@@ -3511,11 +3726,11 @@
       <c r="B33" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="87"/>
+      <c r="C33" s="106"/>
       <c r="D33" s="15"/>
-      <c r="E33" s="17"/>
+      <c r="E33" s="104"/>
       <c r="F33" s="71"/>
-      <c r="G33" s="17"/>
+      <c r="G33" s="104"/>
       <c r="H33" s="15"/>
       <c r="I33" s="12" t="s">
         <v>17</v>
@@ -3543,11 +3758,11 @@
       <c r="B34" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="15"/>
+      <c r="C34" s="105"/>
       <c r="D34" s="15"/>
-      <c r="E34" s="17"/>
+      <c r="E34" s="104"/>
       <c r="F34" s="71"/>
-      <c r="G34" s="17"/>
+      <c r="G34" s="104"/>
       <c r="H34" s="15"/>
       <c r="I34" s="12" t="s">
         <v>16</v>
@@ -3575,11 +3790,11 @@
       <c r="B35" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="17"/>
+      <c r="C35" s="104"/>
       <c r="D35" s="15"/>
-      <c r="E35" s="17"/>
+      <c r="E35" s="104"/>
       <c r="F35" s="71"/>
-      <c r="G35" s="19"/>
+      <c r="G35" s="146"/>
       <c r="H35" s="15"/>
       <c r="I35" s="12" t="s">
         <v>15</v>
@@ -3607,11 +3822,11 @@
       <c r="B36" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="17"/>
+      <c r="C36" s="104"/>
       <c r="D36" s="15"/>
-      <c r="E36" s="17"/>
+      <c r="E36" s="104"/>
       <c r="F36" s="71"/>
-      <c r="G36" s="17"/>
+      <c r="G36" s="104"/>
       <c r="H36" s="15"/>
       <c r="I36" s="12" t="s">
         <v>14</v>
@@ -3639,11 +3854,11 @@
       <c r="B37" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C37" s="15"/>
+      <c r="C37" s="105"/>
       <c r="D37" s="15"/>
-      <c r="E37" s="17"/>
+      <c r="E37" s="104"/>
       <c r="F37" s="71"/>
-      <c r="G37" s="17"/>
+      <c r="G37" s="104"/>
       <c r="H37" s="15"/>
       <c r="I37" s="12" t="s">
         <v>13</v>
@@ -3671,11 +3886,11 @@
       <c r="B38" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="17"/>
+      <c r="C38" s="104"/>
       <c r="D38" s="15"/>
-      <c r="E38" s="17"/>
+      <c r="E38" s="104"/>
       <c r="F38" s="71"/>
-      <c r="G38" s="18"/>
+      <c r="G38" s="147"/>
       <c r="H38" s="15"/>
       <c r="I38" s="12" t="s">
         <v>12</v>
@@ -3703,11 +3918,11 @@
       <c r="B39" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="17"/>
+      <c r="C39" s="104"/>
       <c r="D39" s="15"/>
-      <c r="E39" s="17"/>
+      <c r="E39" s="104"/>
       <c r="F39" s="71"/>
-      <c r="G39" s="17"/>
+      <c r="G39" s="104"/>
       <c r="H39" s="15"/>
       <c r="I39" s="12" t="s">
         <v>11</v>
@@ -3735,11 +3950,11 @@
       <c r="B40" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="16"/>
+      <c r="C40" s="103"/>
       <c r="D40" s="15"/>
-      <c r="E40" s="17"/>
+      <c r="E40" s="104"/>
       <c r="F40" s="71"/>
-      <c r="G40" s="17"/>
+      <c r="G40" s="104"/>
       <c r="H40" s="15"/>
       <c r="I40" s="12" t="s">
         <v>10</v>
@@ -3767,11 +3982,11 @@
       <c r="B41" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C41" s="15"/>
+      <c r="C41" s="105"/>
       <c r="D41" s="15"/>
-      <c r="E41" s="17"/>
+      <c r="E41" s="104"/>
       <c r="F41" s="71"/>
-      <c r="G41" s="17"/>
+      <c r="G41" s="104"/>
       <c r="H41" s="15"/>
       <c r="I41" s="12" t="s">
         <v>9</v>
@@ -3799,11 +4014,11 @@
       <c r="B42" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="17"/>
+      <c r="C42" s="104"/>
       <c r="D42" s="15"/>
-      <c r="E42" s="17"/>
+      <c r="E42" s="104"/>
       <c r="F42" s="71"/>
-      <c r="G42" s="19"/>
+      <c r="G42" s="146"/>
       <c r="H42" s="15"/>
       <c r="I42" s="12" t="s">
         <v>8</v>
@@ -3831,11 +4046,11 @@
       <c r="B43" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C43" s="17"/>
+      <c r="C43" s="104"/>
       <c r="D43" s="15"/>
-      <c r="E43" s="17"/>
+      <c r="E43" s="104"/>
       <c r="F43" s="71"/>
-      <c r="G43" s="17"/>
+      <c r="G43" s="104"/>
       <c r="H43" s="15"/>
       <c r="I43" s="12" t="s">
         <v>7</v>
@@ -3863,11 +4078,11 @@
       <c r="B44" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="17"/>
+      <c r="C44" s="104"/>
       <c r="D44" s="15"/>
-      <c r="E44" s="16"/>
+      <c r="E44" s="103"/>
       <c r="F44" s="71"/>
-      <c r="G44" s="18"/>
+      <c r="G44" s="147"/>
       <c r="H44" s="15"/>
       <c r="I44" s="12" t="s">
         <v>6</v>
@@ -3895,11 +4110,11 @@
       <c r="B45" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C45" s="17"/>
+      <c r="C45" s="104"/>
       <c r="D45" s="15"/>
-      <c r="E45" s="88"/>
+      <c r="E45" s="107"/>
       <c r="F45" s="71"/>
-      <c r="G45" s="17"/>
+      <c r="G45" s="104"/>
       <c r="H45" s="15"/>
       <c r="I45" s="12" t="s">
         <v>5</v>
@@ -3927,11 +4142,11 @@
       <c r="B46" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="17"/>
+      <c r="C46" s="104"/>
       <c r="D46" s="15"/>
-      <c r="E46" s="17"/>
+      <c r="E46" s="104"/>
       <c r="F46" s="71"/>
-      <c r="G46" s="17"/>
+      <c r="G46" s="104"/>
       <c r="H46" s="15"/>
       <c r="I46" s="12" t="s">
         <v>4</v>
@@ -3959,11 +4174,11 @@
       <c r="B47" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="88"/>
+      <c r="C47" s="107"/>
       <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
+      <c r="E47" s="105"/>
       <c r="F47" s="71"/>
-      <c r="G47" s="17"/>
+      <c r="G47" s="104"/>
       <c r="H47" s="15"/>
       <c r="I47" s="12" t="s">
         <v>3</v>
@@ -3991,11 +4206,11 @@
       <c r="B48" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="17"/>
+      <c r="C48" s="104"/>
       <c r="D48" s="15"/>
-      <c r="E48" s="17"/>
+      <c r="E48" s="104"/>
       <c r="F48" s="71"/>
-      <c r="G48" s="19"/>
+      <c r="G48" s="146"/>
       <c r="H48" s="15"/>
       <c r="I48" s="12" t="s">
         <v>2</v>
@@ -4023,11 +4238,11 @@
       <c r="B49" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="21"/>
+      <c r="C49" s="108"/>
       <c r="D49" s="21"/>
-      <c r="E49" s="22"/>
+      <c r="E49" s="140"/>
       <c r="F49" s="72"/>
-      <c r="G49" s="22"/>
+      <c r="G49" s="140"/>
       <c r="H49" s="21"/>
       <c r="I49" s="20" t="s">
         <v>1</v>
@@ -4055,11 +4270,11 @@
       <c r="B50" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C50" s="25"/>
+      <c r="C50" s="109"/>
       <c r="D50" s="24"/>
-      <c r="E50" s="25"/>
+      <c r="E50" s="109"/>
       <c r="F50" s="73"/>
-      <c r="G50" s="25"/>
+      <c r="G50" s="109"/>
       <c r="H50" s="24"/>
       <c r="I50" s="23" t="s">
         <v>24</v>
@@ -4087,11 +4302,11 @@
       <c r="B51" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="27"/>
+      <c r="C51" s="110"/>
       <c r="D51" s="26"/>
-      <c r="E51" s="27"/>
+      <c r="E51" s="110"/>
       <c r="F51" s="74"/>
-      <c r="G51" s="27"/>
+      <c r="G51" s="110"/>
       <c r="H51" s="26"/>
       <c r="I51" s="23" t="s">
         <v>23</v>
@@ -4119,11 +4334,11 @@
       <c r="B52" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="28"/>
+      <c r="C52" s="111"/>
       <c r="D52" s="27"/>
-      <c r="E52" s="28"/>
+      <c r="E52" s="111"/>
       <c r="F52" s="74"/>
-      <c r="G52" s="28"/>
+      <c r="G52" s="111"/>
       <c r="H52" s="26"/>
       <c r="I52" s="23" t="s">
         <v>22</v>
@@ -4151,11 +4366,11 @@
       <c r="B53" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="27"/>
+      <c r="C53" s="110"/>
       <c r="D53" s="26"/>
-      <c r="E53" s="27"/>
+      <c r="E53" s="110"/>
       <c r="F53" s="74"/>
-      <c r="G53" s="27"/>
+      <c r="G53" s="110"/>
       <c r="H53" s="26"/>
       <c r="I53" s="23" t="s">
         <v>21</v>
@@ -4183,11 +4398,11 @@
       <c r="B54" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="89"/>
+      <c r="C54" s="112"/>
       <c r="D54" s="26"/>
-      <c r="E54" s="89"/>
+      <c r="E54" s="112"/>
       <c r="F54" s="74"/>
-      <c r="G54" s="89"/>
+      <c r="G54" s="112"/>
       <c r="H54" s="26"/>
       <c r="I54" s="23" t="s">
         <v>20</v>
@@ -4215,11 +4430,11 @@
       <c r="B55" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C55" s="89"/>
+      <c r="C55" s="112"/>
       <c r="D55" s="26"/>
-      <c r="E55" s="89"/>
+      <c r="E55" s="112"/>
       <c r="F55" s="74"/>
-      <c r="G55" s="89"/>
+      <c r="G55" s="112"/>
       <c r="H55" s="26"/>
       <c r="I55" s="23" t="s">
         <v>19</v>
@@ -4247,19 +4462,19 @@
       <c r="B56" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C56" s="27" t="s">
+      <c r="C56" s="110" t="s">
         <v>40</v>
       </c>
       <c r="D56" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="E56" s="27" t="s">
+      <c r="E56" s="110" t="s">
         <v>40</v>
       </c>
       <c r="F56" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G56" s="26" t="s">
+      <c r="G56" s="141" t="s">
         <v>40</v>
       </c>
       <c r="H56" s="26" t="s">
@@ -4291,19 +4506,19 @@
       <c r="B57" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="110" t="s">
         <v>43</v>
       </c>
       <c r="D57" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E57" s="26" t="s">
+      <c r="E57" s="141" t="s">
         <v>43</v>
       </c>
       <c r="F57" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G57" s="26" t="s">
+      <c r="G57" s="141" t="s">
         <v>43</v>
       </c>
       <c r="H57" s="26" t="s">
@@ -4335,19 +4550,19 @@
       <c r="B58" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="27" t="s">
+      <c r="C58" s="110" t="s">
         <v>41</v>
       </c>
       <c r="D58" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E58" s="26" t="s">
+      <c r="E58" s="141" t="s">
         <v>41</v>
       </c>
       <c r="F58" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G58" s="26" t="s">
+      <c r="G58" s="141" t="s">
         <v>41</v>
       </c>
       <c r="H58" s="26" t="s">
@@ -4379,19 +4594,19 @@
       <c r="B59" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="27" t="s">
+      <c r="C59" s="110" t="s">
         <v>42</v>
       </c>
       <c r="D59" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E59" s="99" t="s">
+      <c r="E59" s="142" t="s">
         <v>42</v>
       </c>
       <c r="F59" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G59" s="27" t="s">
+      <c r="G59" s="110" t="s">
         <v>42</v>
       </c>
       <c r="H59" s="26" t="s">
@@ -4419,7 +4634,7 @@
         <v>0.41597222222222224</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>42</v>
@@ -4435,20 +4650,20 @@
       <c r="B60" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C60" s="89" t="s">
+      <c r="C60" s="112" t="s">
         <v>331</v>
       </c>
       <c r="D60" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="27" t="s">
-        <v>479</v>
+      <c r="E60" s="110" t="s">
+        <v>478</v>
       </c>
       <c r="F60" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="G60" s="27" t="s">
-        <v>479</v>
+      <c r="G60" s="110" t="s">
+        <v>478</v>
       </c>
       <c r="H60" s="26" t="s">
         <v>80</v>
@@ -4475,7 +4690,7 @@
         <v>333</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="18" customHeight="1">
@@ -4485,15 +4700,15 @@
       <c r="B61" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C61" s="27"/>
+      <c r="C61" s="110"/>
       <c r="D61" s="26"/>
-      <c r="E61" s="27" t="s">
+      <c r="E61" s="110" t="s">
         <v>334</v>
       </c>
       <c r="F61" s="74" t="s">
-        <v>423</v>
-      </c>
-      <c r="G61" s="27"/>
+        <v>422</v>
+      </c>
+      <c r="G61" s="110"/>
       <c r="H61" s="26"/>
       <c r="I61" s="23" t="s">
         <v>13</v>
@@ -4521,23 +4736,23 @@
       <c r="B62" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C62" s="110" t="s">
         <v>335</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>407</v>
-      </c>
-      <c r="E62" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="E62" s="110" t="s">
         <v>336</v>
       </c>
       <c r="F62" s="74" t="s">
-        <v>423</v>
-      </c>
-      <c r="G62" s="27" t="s">
+        <v>422</v>
+      </c>
+      <c r="G62" s="110" t="s">
         <v>337</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I62" s="23" t="s">
         <v>12</v>
@@ -4565,17 +4780,15 @@
       <c r="B63" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="27" t="s">
+      <c r="C63" s="110"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="110"/>
+      <c r="F63" s="74"/>
+      <c r="G63" s="110" t="s">
         <v>338</v>
       </c>
-      <c r="D63" s="26"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="74"/>
-      <c r="G63" s="27" t="s">
-        <v>339</v>
-      </c>
       <c r="H63" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I63" s="23" t="s">
         <v>11</v>
@@ -4603,17 +4816,15 @@
       <c r="B64" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C64" s="110"/>
       <c r="D64" s="26"/>
-      <c r="E64" s="27" t="s">
-        <v>340</v>
+      <c r="E64" s="110" t="s">
+        <v>339</v>
       </c>
       <c r="F64" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G64" s="27"/>
+        <v>421</v>
+      </c>
+      <c r="G64" s="110"/>
       <c r="H64" s="26"/>
       <c r="I64" s="23" t="s">
         <v>10</v>
@@ -4641,23 +4852,23 @@
       <c r="B65" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="100">
-        <v>0.66041666666666665</v>
+      <c r="C65" s="113" t="s">
+        <v>479</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="E65" s="27" t="s">
+        <v>407</v>
+      </c>
+      <c r="E65" s="110" t="s">
         <v>254</v>
       </c>
       <c r="F65" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G65" s="28" t="s">
-        <v>341</v>
+        <v>421</v>
+      </c>
+      <c r="G65" s="111" t="s">
+        <v>340</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I65" s="23" t="s">
         <v>9</v>
@@ -4685,17 +4896,15 @@
       <c r="B66" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C66" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C66" s="110"/>
       <c r="D66" s="26"/>
-      <c r="E66" s="27"/>
+      <c r="E66" s="110"/>
       <c r="F66" s="74"/>
-      <c r="G66" s="27" t="s">
-        <v>342</v>
+      <c r="G66" s="110" t="s">
+        <v>341</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I66" s="23" t="s">
         <v>8</v>
@@ -4723,17 +4932,15 @@
       <c r="B67" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C67" s="28" t="s">
-        <v>338</v>
-      </c>
+      <c r="C67" s="111"/>
       <c r="D67" s="26"/>
-      <c r="E67" s="27" t="s">
-        <v>343</v>
+      <c r="E67" s="110" t="s">
+        <v>342</v>
       </c>
       <c r="F67" s="74" t="s">
-        <v>423</v>
-      </c>
-      <c r="G67" s="28"/>
+        <v>422</v>
+      </c>
+      <c r="G67" s="111"/>
       <c r="H67" s="26"/>
       <c r="I67" s="23" t="s">
         <v>7</v>
@@ -4761,21 +4968,19 @@
       <c r="B68" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C68" s="110"/>
       <c r="D68" s="26"/>
-      <c r="E68" s="27" t="s">
+      <c r="E68" s="110" t="s">
+        <v>343</v>
+      </c>
+      <c r="F68" s="74" t="s">
+        <v>421</v>
+      </c>
+      <c r="G68" s="110" t="s">
         <v>344</v>
       </c>
-      <c r="F68" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G68" s="27" t="s">
-        <v>345</v>
-      </c>
       <c r="H68" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I68" s="23" t="s">
         <v>6</v>
@@ -4803,19 +5008,19 @@
       <c r="B69" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C69" s="27" t="s">
+      <c r="C69" s="110" t="s">
+        <v>345</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="E69" s="110"/>
+      <c r="F69" s="74"/>
+      <c r="G69" s="110" t="s">
         <v>346</v>
       </c>
-      <c r="D69" s="26" t="s">
-        <v>409</v>
-      </c>
-      <c r="E69" s="27"/>
-      <c r="F69" s="74"/>
-      <c r="G69" s="27" t="s">
-        <v>347</v>
-      </c>
       <c r="H69" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I69" s="23" t="s">
         <v>5</v>
@@ -4843,17 +5048,15 @@
       <c r="B70" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C70" s="110"/>
       <c r="D70" s="27"/>
-      <c r="E70" s="27" t="s">
-        <v>348</v>
+      <c r="E70" s="110" t="s">
+        <v>347</v>
       </c>
       <c r="F70" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G70" s="28"/>
+        <v>421</v>
+      </c>
+      <c r="G70" s="111"/>
       <c r="H70" s="26"/>
       <c r="I70" s="23" t="s">
         <v>4</v>
@@ -4881,21 +5084,19 @@
       <c r="B71" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C71" s="110"/>
       <c r="D71" s="26"/>
-      <c r="E71" s="27" t="s">
+      <c r="E71" s="110" t="s">
+        <v>348</v>
+      </c>
+      <c r="F71" s="74" t="s">
+        <v>421</v>
+      </c>
+      <c r="G71" s="110" t="s">
         <v>349</v>
       </c>
-      <c r="F71" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="G71" s="27" t="s">
-        <v>350</v>
-      </c>
       <c r="H71" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I71" s="23" t="s">
         <v>3</v>
@@ -4923,17 +5124,15 @@
       <c r="B72" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="27" t="s">
-        <v>338</v>
-      </c>
+      <c r="C72" s="110"/>
       <c r="D72" s="26"/>
-      <c r="E72" s="27"/>
+      <c r="E72" s="110"/>
       <c r="F72" s="74"/>
-      <c r="G72" s="27" t="s">
-        <v>351</v>
+      <c r="G72" s="110" t="s">
+        <v>350</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I72" s="23" t="s">
         <v>2</v>
@@ -4961,17 +5160,15 @@
       <c r="B73" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C73" s="31" t="s">
-        <v>338</v>
-      </c>
+      <c r="C73" s="114"/>
       <c r="D73" s="30"/>
-      <c r="E73" s="31" t="s">
-        <v>352</v>
+      <c r="E73" s="114" t="s">
+        <v>351</v>
       </c>
       <c r="F73" s="75" t="s">
-        <v>422</v>
-      </c>
-      <c r="G73" s="31"/>
+        <v>421</v>
+      </c>
+      <c r="G73" s="114"/>
       <c r="H73" s="30"/>
       <c r="I73" s="29" t="s">
         <v>1</v>
@@ -4999,23 +5196,23 @@
       <c r="B74" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="34" t="s">
+      <c r="C74" s="115" t="s">
         <v>57</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>410</v>
-      </c>
-      <c r="E74" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="E74" s="115" t="s">
         <v>57</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>423</v>
-      </c>
-      <c r="G74" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="G74" s="115" t="s">
         <v>57</v>
       </c>
       <c r="H74" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I74" s="32" t="s">
         <v>24</v>
@@ -5043,21 +5240,19 @@
       <c r="B75" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C75" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C75" s="116"/>
       <c r="D75" s="35"/>
-      <c r="E75" s="36" t="s">
+      <c r="E75" s="116" t="s">
         <v>132</v>
       </c>
       <c r="F75" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G75" s="36" t="s">
-        <v>353</v>
+        <v>421</v>
+      </c>
+      <c r="G75" s="116" t="s">
+        <v>352</v>
       </c>
       <c r="H75" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I75" s="32" t="s">
         <v>23</v>
@@ -5085,17 +5280,15 @@
       <c r="B76" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C76" s="116"/>
       <c r="D76" s="35"/>
-      <c r="E76" s="36"/>
+      <c r="E76" s="116"/>
       <c r="F76" s="77"/>
-      <c r="G76" s="37" t="s">
-        <v>354</v>
+      <c r="G76" s="148" t="s">
+        <v>353</v>
       </c>
       <c r="H76" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I76" s="32" t="s">
         <v>22</v>
@@ -5123,19 +5316,19 @@
       <c r="B77" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="36" t="s">
+      <c r="C77" s="116" t="s">
+        <v>354</v>
+      </c>
+      <c r="D77" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="E77" s="116" t="s">
         <v>355</v>
       </c>
-      <c r="D77" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="E77" s="36" t="s">
-        <v>356</v>
-      </c>
       <c r="F77" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G77" s="77"/>
+        <v>421</v>
+      </c>
+      <c r="G77" s="149"/>
       <c r="H77" s="35"/>
       <c r="I77" s="32" t="s">
         <v>21</v>
@@ -5163,21 +5356,19 @@
       <c r="B78" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C78" s="116"/>
       <c r="D78" s="35"/>
-      <c r="E78" s="36" t="s">
+      <c r="E78" s="116" t="s">
+        <v>356</v>
+      </c>
+      <c r="F78" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G78" s="116" t="s">
         <v>357</v>
       </c>
-      <c r="F78" s="77" t="s">
+      <c r="H78" s="35" t="s">
         <v>423</v>
-      </c>
-      <c r="G78" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="H78" s="35" t="s">
-        <v>424</v>
       </c>
       <c r="I78" s="32" t="s">
         <v>20</v>
@@ -5205,23 +5396,23 @@
       <c r="B79" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="36" t="s">
+      <c r="C79" s="116" t="s">
+        <v>358</v>
+      </c>
+      <c r="D79" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="E79" s="116" t="s">
         <v>359</v>
       </c>
-      <c r="D79" s="35" t="s">
-        <v>411</v>
-      </c>
-      <c r="E79" s="36" t="s">
-        <v>360</v>
-      </c>
       <c r="F79" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="G79" s="36" t="s">
-        <v>360</v>
+        <v>422</v>
+      </c>
+      <c r="G79" s="116" t="s">
+        <v>359</v>
       </c>
       <c r="H79" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I79" s="32" t="s">
         <v>19</v>
@@ -5249,13 +5440,11 @@
       <c r="B80" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C80" s="116"/>
       <c r="D80" s="35"/>
-      <c r="E80" s="36"/>
+      <c r="E80" s="116"/>
       <c r="F80" s="77"/>
-      <c r="G80" s="37"/>
+      <c r="G80" s="148"/>
       <c r="H80" s="35"/>
       <c r="I80" s="32" t="s">
         <v>18</v>
@@ -5283,21 +5472,19 @@
       <c r="B81" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C81" s="116"/>
       <c r="D81" s="35"/>
-      <c r="E81" s="36" t="s">
+      <c r="E81" s="116" t="s">
+        <v>360</v>
+      </c>
+      <c r="F81" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G81" s="116" t="s">
         <v>361</v>
       </c>
-      <c r="F81" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G81" s="36" t="s">
-        <v>362</v>
-      </c>
       <c r="H81" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I81" s="32" t="s">
         <v>17</v>
@@ -5325,19 +5512,19 @@
       <c r="B82" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="36" t="s">
+      <c r="C82" s="116" t="s">
+        <v>362</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>408</v>
+      </c>
+      <c r="E82" s="116"/>
+      <c r="F82" s="77"/>
+      <c r="G82" s="116" t="s">
         <v>363</v>
       </c>
-      <c r="D82" s="35" t="s">
-        <v>409</v>
-      </c>
-      <c r="E82" s="36"/>
-      <c r="F82" s="77"/>
-      <c r="G82" s="36" t="s">
-        <v>364</v>
-      </c>
       <c r="H82" s="35" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I82" s="32" t="s">
         <v>16</v>
@@ -5365,15 +5552,15 @@
       <c r="B83" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="35"/>
+      <c r="C83" s="117"/>
       <c r="D83" s="35"/>
-      <c r="E83" s="36" t="s">
-        <v>365</v>
+      <c r="E83" s="116" t="s">
+        <v>364</v>
       </c>
       <c r="F83" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="G83" s="37"/>
+        <v>422</v>
+      </c>
+      <c r="G83" s="148"/>
       <c r="H83" s="35"/>
       <c r="I83" s="32" t="s">
         <v>15</v>
@@ -5401,21 +5588,19 @@
       <c r="B84" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C84" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C84" s="116"/>
       <c r="D84" s="35"/>
-      <c r="E84" s="36" t="s">
+      <c r="E84" s="116" t="s">
+        <v>365</v>
+      </c>
+      <c r="F84" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G84" s="116" t="s">
         <v>366</v>
       </c>
-      <c r="F84" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G84" s="36" t="s">
-        <v>367</v>
-      </c>
       <c r="H84" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I84" s="32" t="s">
         <v>14</v>
@@ -5443,13 +5628,11 @@
       <c r="B85" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C85" s="116"/>
       <c r="D85" s="35"/>
-      <c r="E85" s="36"/>
+      <c r="E85" s="116"/>
       <c r="F85" s="77"/>
-      <c r="G85" s="36"/>
+      <c r="G85" s="116"/>
       <c r="H85" s="35"/>
       <c r="I85" s="32" t="s">
         <v>13</v>
@@ -5477,23 +5660,23 @@
       <c r="B86" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C86" s="101">
-        <v>0.51527777777777772</v>
+      <c r="C86" s="118" t="s">
+        <v>480</v>
       </c>
       <c r="D86" s="35" t="s">
-        <v>412</v>
-      </c>
-      <c r="E86" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="E86" s="116" t="s">
+        <v>367</v>
+      </c>
+      <c r="F86" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G86" s="148" t="s">
         <v>368</v>
       </c>
-      <c r="F86" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G86" s="37" t="s">
-        <v>369</v>
-      </c>
       <c r="H86" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I86" s="32" t="s">
         <v>12</v>
@@ -5521,21 +5704,19 @@
       <c r="B87" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C87" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C87" s="116"/>
       <c r="D87" s="35"/>
-      <c r="E87" s="36" t="s">
+      <c r="E87" s="116" t="s">
+        <v>369</v>
+      </c>
+      <c r="F87" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G87" s="116" t="s">
         <v>370</v>
       </c>
-      <c r="F87" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G87" s="36" t="s">
-        <v>371</v>
-      </c>
       <c r="H87" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I87" s="32" t="s">
         <v>11</v>
@@ -5563,17 +5744,15 @@
       <c r="B88" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C88" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C88" s="116"/>
       <c r="D88" s="35"/>
-      <c r="E88" s="36"/>
+      <c r="E88" s="116"/>
       <c r="F88" s="77"/>
-      <c r="G88" s="36" t="s">
-        <v>372</v>
+      <c r="G88" s="116" t="s">
+        <v>371</v>
       </c>
       <c r="H88" s="35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I88" s="32" t="s">
         <v>10</v>
@@ -5601,17 +5780,15 @@
       <c r="B89" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C89" s="116"/>
       <c r="D89" s="35"/>
-      <c r="E89" s="36" t="s">
+      <c r="E89" s="116" t="s">
         <v>161</v>
       </c>
       <c r="F89" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G89" s="37"/>
+        <v>421</v>
+      </c>
+      <c r="G89" s="148"/>
       <c r="H89" s="35"/>
       <c r="I89" s="32" t="s">
         <v>9</v>
@@ -5639,21 +5816,19 @@
       <c r="B90" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C90" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C90" s="116"/>
       <c r="D90" s="35"/>
-      <c r="E90" s="36" t="s">
-        <v>373</v>
+      <c r="E90" s="116" t="s">
+        <v>372</v>
       </c>
       <c r="F90" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G90" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="G90" s="116" t="s">
         <v>242</v>
       </c>
       <c r="H90" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I90" s="32" t="s">
         <v>8</v>
@@ -5681,17 +5856,15 @@
       <c r="B91" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C91" s="116"/>
       <c r="D91" s="35"/>
-      <c r="E91" s="36"/>
+      <c r="E91" s="116"/>
       <c r="F91" s="77"/>
-      <c r="G91" s="36" t="s">
-        <v>374</v>
+      <c r="G91" s="116" t="s">
+        <v>373</v>
       </c>
       <c r="H91" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I91" s="32" t="s">
         <v>7</v>
@@ -5719,19 +5892,19 @@
       <c r="B92" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C92" s="36" t="s">
+      <c r="C92" s="116" t="s">
+        <v>374</v>
+      </c>
+      <c r="D92" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="E92" s="116" t="s">
         <v>375</v>
       </c>
-      <c r="D92" s="35" t="s">
-        <v>413</v>
-      </c>
-      <c r="E92" s="36" t="s">
-        <v>376</v>
-      </c>
       <c r="F92" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="G92" s="37"/>
+        <v>422</v>
+      </c>
+      <c r="G92" s="148"/>
       <c r="H92" s="35"/>
       <c r="I92" s="32" t="s">
         <v>6</v>
@@ -5759,19 +5932,19 @@
       <c r="B93" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="35"/>
+      <c r="C93" s="117"/>
       <c r="D93" s="35"/>
-      <c r="E93" s="36" t="s">
+      <c r="E93" s="116" t="s">
+        <v>376</v>
+      </c>
+      <c r="F93" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="G93" s="116" t="s">
         <v>377</v>
       </c>
-      <c r="F93" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G93" s="36" t="s">
-        <v>378</v>
-      </c>
       <c r="H93" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I93" s="32" t="s">
         <v>5</v>
@@ -5799,17 +5972,15 @@
       <c r="B94" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C94" s="116"/>
       <c r="D94" s="35"/>
-      <c r="E94" s="36"/>
+      <c r="E94" s="116"/>
       <c r="F94" s="77"/>
-      <c r="G94" s="36" t="s">
-        <v>379</v>
+      <c r="G94" s="116" t="s">
+        <v>378</v>
       </c>
       <c r="H94" s="35" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I94" s="32" t="s">
         <v>4</v>
@@ -5837,17 +6008,15 @@
       <c r="B95" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C95" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C95" s="116"/>
       <c r="D95" s="35"/>
-      <c r="E95" s="36" t="s">
-        <v>380</v>
+      <c r="E95" s="116" t="s">
+        <v>379</v>
       </c>
       <c r="F95" s="77" t="s">
-        <v>422</v>
-      </c>
-      <c r="G95" s="36"/>
+        <v>421</v>
+      </c>
+      <c r="G95" s="116"/>
       <c r="H95" s="35"/>
       <c r="I95" s="32" t="s">
         <v>3</v>
@@ -5875,21 +6044,19 @@
       <c r="B96" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C96" s="36" t="s">
-        <v>338</v>
-      </c>
+      <c r="C96" s="116"/>
       <c r="D96" s="35"/>
-      <c r="E96" s="36" t="s">
-        <v>381</v>
+      <c r="E96" s="116" t="s">
+        <v>380</v>
       </c>
       <c r="F96" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="G96" s="148" t="s">
+        <v>237</v>
+      </c>
+      <c r="H96" s="35" t="s">
         <v>423</v>
-      </c>
-      <c r="G96" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="H96" s="35" t="s">
-        <v>424</v>
       </c>
       <c r="I96" s="32" t="s">
         <v>2</v>
@@ -5917,19 +6084,19 @@
       <c r="B97" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="C97" s="40" t="s">
+      <c r="C97" s="119" t="s">
         <v>57</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>407</v>
-      </c>
-      <c r="E97" s="40"/>
+        <v>406</v>
+      </c>
+      <c r="E97" s="119"/>
       <c r="F97" s="78"/>
-      <c r="G97" s="40" t="s">
-        <v>382</v>
+      <c r="G97" s="119" t="s">
+        <v>381</v>
       </c>
       <c r="H97" s="39" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I97" s="38" t="s">
         <v>1</v>
@@ -5957,21 +6124,19 @@
       <c r="B98" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="43" t="s">
-        <v>338</v>
-      </c>
+      <c r="C98" s="120"/>
       <c r="D98" s="42"/>
-      <c r="E98" s="43" t="s">
+      <c r="E98" s="120" t="s">
         <v>57</v>
       </c>
       <c r="F98" s="79" t="s">
-        <v>423</v>
-      </c>
-      <c r="G98" s="43" t="s">
-        <v>383</v>
+        <v>422</v>
+      </c>
+      <c r="G98" s="120" t="s">
+        <v>382</v>
       </c>
       <c r="H98" s="42" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I98" s="41" t="s">
         <v>24</v>
@@ -5999,17 +6164,15 @@
       <c r="B99" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="43" t="s">
-        <v>338</v>
-      </c>
+      <c r="C99" s="120"/>
       <c r="D99" s="42"/>
-      <c r="E99" s="45" t="s">
+      <c r="E99" s="121" t="s">
         <v>132</v>
       </c>
       <c r="F99" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G99" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G99" s="121"/>
       <c r="H99" s="44"/>
       <c r="I99" s="41" t="s">
         <v>23</v>
@@ -6037,19 +6200,19 @@
       <c r="B100" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="45"/>
+      <c r="C100" s="121"/>
       <c r="D100" s="44"/>
-      <c r="E100" s="45" t="s">
-        <v>354</v>
+      <c r="E100" s="121" t="s">
+        <v>353</v>
       </c>
       <c r="F100" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G100" s="45" t="s">
-        <v>384</v>
+        <v>422</v>
+      </c>
+      <c r="G100" s="121" t="s">
+        <v>383</v>
       </c>
       <c r="H100" s="44" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I100" s="41" t="s">
         <v>22</v>
@@ -6077,19 +6240,19 @@
       <c r="B101" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="45" t="s">
+      <c r="C101" s="121" t="s">
+        <v>384</v>
+      </c>
+      <c r="D101" s="44" t="s">
+        <v>413</v>
+      </c>
+      <c r="E101" s="121"/>
+      <c r="F101" s="80"/>
+      <c r="G101" s="121" t="s">
         <v>385</v>
       </c>
-      <c r="D101" s="44" t="s">
-        <v>414</v>
-      </c>
-      <c r="E101" s="45"/>
-      <c r="F101" s="80"/>
-      <c r="G101" s="45" t="s">
-        <v>386</v>
-      </c>
       <c r="H101" s="44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I101" s="41" t="s">
         <v>21</v>
@@ -6117,17 +6280,15 @@
       <c r="B102" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C102" s="121"/>
       <c r="D102" s="44"/>
-      <c r="E102" s="45" t="s">
+      <c r="E102" s="121" t="s">
         <v>71</v>
       </c>
       <c r="F102" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G102" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G102" s="121"/>
       <c r="H102" s="44"/>
       <c r="I102" s="41" t="s">
         <v>20</v>
@@ -6155,15 +6316,15 @@
       <c r="B103" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="93"/>
+      <c r="C103" s="122"/>
       <c r="D103" s="44"/>
-      <c r="E103" s="45"/>
+      <c r="E103" s="121"/>
       <c r="F103" s="80"/>
-      <c r="G103" s="45" t="s">
-        <v>387</v>
+      <c r="G103" s="121" t="s">
+        <v>386</v>
       </c>
       <c r="H103" s="44" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I103" s="41" t="s">
         <v>19</v>
@@ -6191,21 +6352,19 @@
       <c r="B104" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C104" s="121"/>
       <c r="D104" s="44"/>
-      <c r="E104" s="45" t="s">
+      <c r="E104" s="121" t="s">
+        <v>387</v>
+      </c>
+      <c r="F104" s="80" t="s">
+        <v>421</v>
+      </c>
+      <c r="G104" s="121" t="s">
         <v>388</v>
       </c>
-      <c r="F104" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="G104" s="45" t="s">
-        <v>389</v>
-      </c>
       <c r="H104" s="44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I104" s="41" t="s">
         <v>18</v>
@@ -6233,19 +6392,19 @@
       <c r="B105" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="45" t="s">
+      <c r="C105" s="121" t="s">
         <v>86</v>
       </c>
       <c r="D105" s="44" t="s">
-        <v>415</v>
-      </c>
-      <c r="E105" s="45" t="s">
+        <v>414</v>
+      </c>
+      <c r="E105" s="121" t="s">
         <v>204</v>
       </c>
       <c r="F105" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="G105" s="45"/>
+        <v>421</v>
+      </c>
+      <c r="G105" s="121"/>
       <c r="H105" s="44"/>
       <c r="I105" s="41" t="s">
         <v>17</v>
@@ -6273,17 +6432,15 @@
       <c r="B106" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C106" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C106" s="121"/>
       <c r="D106" s="44"/>
-      <c r="E106" s="45"/>
+      <c r="E106" s="121"/>
       <c r="F106" s="80"/>
-      <c r="G106" s="45" t="s">
-        <v>390</v>
+      <c r="G106" s="121" t="s">
+        <v>389</v>
       </c>
       <c r="H106" s="44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I106" s="41" t="s">
         <v>16</v>
@@ -6311,21 +6468,19 @@
       <c r="B107" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C107" s="121"/>
       <c r="D107" s="44"/>
-      <c r="E107" s="93">
-        <v>0.37569444444444444</v>
+      <c r="E107" s="124" t="s">
+        <v>484</v>
       </c>
       <c r="F107" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="G107" s="45" t="s">
-        <v>391</v>
+        <v>421</v>
+      </c>
+      <c r="G107" s="121" t="s">
+        <v>390</v>
       </c>
       <c r="H107" s="44" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I107" s="41" t="s">
         <v>15</v>
@@ -6353,17 +6508,15 @@
       <c r="B108" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C108" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C108" s="121"/>
       <c r="D108" s="44"/>
-      <c r="E108" s="45" t="s">
-        <v>392</v>
+      <c r="E108" s="121" t="s">
+        <v>391</v>
       </c>
       <c r="F108" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G108" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G108" s="121"/>
       <c r="H108" s="44"/>
       <c r="I108" s="41" t="s">
         <v>14</v>
@@ -6391,19 +6544,19 @@
       <c r="B109" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C109" s="45" t="s">
-        <v>393</v>
+      <c r="C109" s="121" t="s">
+        <v>392</v>
       </c>
       <c r="D109" s="44" t="s">
-        <v>416</v>
-      </c>
-      <c r="E109" s="45"/>
+        <v>415</v>
+      </c>
+      <c r="E109" s="121"/>
       <c r="F109" s="80"/>
-      <c r="G109" s="45" t="s">
+      <c r="G109" s="121" t="s">
         <v>249</v>
       </c>
       <c r="H109" s="44" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I109" s="41" t="s">
         <v>13</v>
@@ -6431,19 +6584,19 @@
       <c r="B110" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C110" s="44"/>
+      <c r="C110" s="123"/>
       <c r="D110" s="44"/>
-      <c r="E110" s="45" t="s">
-        <v>369</v>
+      <c r="E110" s="121" t="s">
+        <v>368</v>
       </c>
       <c r="F110" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G110" s="45" t="s">
-        <v>394</v>
+        <v>422</v>
+      </c>
+      <c r="G110" s="121" t="s">
+        <v>393</v>
       </c>
       <c r="H110" s="44" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I110" s="41" t="s">
         <v>12</v>
@@ -6471,17 +6624,15 @@
       <c r="B111" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C111" s="121"/>
       <c r="D111" s="44"/>
-      <c r="E111" s="45" t="s">
+      <c r="E111" s="121" t="s">
         <v>217</v>
       </c>
       <c r="F111" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G111" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G111" s="121"/>
       <c r="H111" s="44"/>
       <c r="I111" s="41" t="s">
         <v>11</v>
@@ -6509,21 +6660,19 @@
       <c r="B112" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C112" s="121"/>
       <c r="D112" s="44"/>
-      <c r="E112" s="45" t="s">
+      <c r="E112" s="121" t="s">
         <v>172</v>
       </c>
       <c r="F112" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="G112" s="121" t="s">
+        <v>251</v>
+      </c>
+      <c r="H112" s="44" t="s">
         <v>423</v>
-      </c>
-      <c r="G112" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="H112" s="44" t="s">
-        <v>424</v>
       </c>
       <c r="I112" s="41" t="s">
         <v>10</v>
@@ -6545,27 +6694,27 @@
       </c>
     </row>
     <row r="113" spans="1:13" ht="18" customHeight="1">
-      <c r="A113" s="97" t="s">
+      <c r="A113" s="96" t="s">
         <v>9</v>
       </c>
       <c r="B113" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C113" s="45" t="s">
+      <c r="C113" s="121" t="s">
+        <v>394</v>
+      </c>
+      <c r="D113" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="E113" s="121"/>
+      <c r="F113" s="80"/>
+      <c r="G113" s="150" t="s">
         <v>395</v>
       </c>
-      <c r="D113" s="44" t="s">
-        <v>417</v>
-      </c>
-      <c r="E113" s="45"/>
-      <c r="F113" s="80"/>
-      <c r="G113" s="98" t="s">
-        <v>396</v>
-      </c>
       <c r="H113" s="44" t="s">
-        <v>424</v>
-      </c>
-      <c r="I113" s="97" t="s">
+        <v>423</v>
+      </c>
+      <c r="I113" s="96" t="s">
         <v>9</v>
       </c>
       <c r="J113" s="44" t="s">
@@ -6591,17 +6740,15 @@
       <c r="B114" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C114" s="43" t="s">
-        <v>338</v>
-      </c>
+      <c r="C114" s="120"/>
       <c r="D114" s="42"/>
-      <c r="E114" s="43" t="s">
-        <v>397</v>
+      <c r="E114" s="120" t="s">
+        <v>396</v>
       </c>
       <c r="F114" s="79" t="s">
-        <v>423</v>
-      </c>
-      <c r="G114" s="43"/>
+        <v>422</v>
+      </c>
+      <c r="G114" s="120"/>
       <c r="H114" s="42"/>
       <c r="I114" s="41" t="s">
         <v>8</v>
@@ -6629,17 +6776,15 @@
       <c r="B115" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C115" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C115" s="121"/>
       <c r="D115" s="44"/>
-      <c r="E115" s="45"/>
+      <c r="E115" s="121"/>
       <c r="F115" s="80"/>
-      <c r="G115" s="45" t="s">
-        <v>398</v>
+      <c r="G115" s="121" t="s">
+        <v>397</v>
       </c>
       <c r="H115" s="44" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I115" s="41" t="s">
         <v>7</v>
@@ -6667,23 +6812,23 @@
       <c r="B116" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C116" s="93">
-        <v>0.77916666666666667</v>
+      <c r="C116" s="124" t="s">
+        <v>481</v>
       </c>
       <c r="D116" s="44" t="s">
-        <v>418</v>
-      </c>
-      <c r="E116" s="45" t="s">
+        <v>417</v>
+      </c>
+      <c r="E116" s="121" t="s">
         <v>244</v>
       </c>
       <c r="F116" s="80" t="s">
+        <v>422</v>
+      </c>
+      <c r="G116" s="121" t="s">
+        <v>140</v>
+      </c>
+      <c r="H116" s="44" t="s">
         <v>423</v>
-      </c>
-      <c r="G116" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="H116" s="44" t="s">
-        <v>424</v>
       </c>
       <c r="I116" s="41" t="s">
         <v>6</v>
@@ -6711,17 +6856,15 @@
       <c r="B117" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C117" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C117" s="121"/>
       <c r="D117" s="44"/>
-      <c r="E117" s="45" t="s">
-        <v>399</v>
+      <c r="E117" s="121" t="s">
+        <v>398</v>
       </c>
       <c r="F117" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="G117" s="45"/>
+        <v>421</v>
+      </c>
+      <c r="G117" s="121"/>
       <c r="H117" s="44"/>
       <c r="I117" s="41" t="s">
         <v>5</v>
@@ -6749,17 +6892,15 @@
       <c r="B118" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C118" s="121"/>
       <c r="D118" s="44"/>
-      <c r="E118" s="45"/>
+      <c r="E118" s="121"/>
       <c r="F118" s="80"/>
-      <c r="G118" s="45" t="s">
-        <v>400</v>
+      <c r="G118" s="121" t="s">
+        <v>399</v>
       </c>
       <c r="H118" s="44" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I118" s="41" t="s">
         <v>4</v>
@@ -6787,15 +6928,15 @@
       <c r="B119" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C119" s="44"/>
+      <c r="C119" s="123"/>
       <c r="D119" s="44"/>
-      <c r="E119" s="45" t="s">
-        <v>401</v>
+      <c r="E119" s="121" t="s">
+        <v>400</v>
       </c>
       <c r="F119" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G119" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G119" s="121"/>
       <c r="H119" s="44"/>
       <c r="I119" s="41" t="s">
         <v>3</v>
@@ -6823,17 +6964,15 @@
       <c r="B120" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C120" s="45" t="s">
-        <v>338</v>
-      </c>
+      <c r="C120" s="121"/>
       <c r="D120" s="44"/>
-      <c r="E120" s="45" t="s">
-        <v>402</v>
+      <c r="E120" s="121" t="s">
+        <v>401</v>
       </c>
       <c r="F120" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="G120" s="45"/>
+        <v>422</v>
+      </c>
+      <c r="G120" s="121"/>
       <c r="H120" s="45"/>
       <c r="I120" s="41" t="s">
         <v>2</v>
@@ -6861,19 +7000,19 @@
       <c r="B121" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C121" s="49" t="s">
-        <v>403</v>
+      <c r="C121" s="125" t="s">
+        <v>402</v>
       </c>
       <c r="D121" s="48" t="s">
-        <v>412</v>
-      </c>
-      <c r="E121" s="49"/>
+        <v>411</v>
+      </c>
+      <c r="E121" s="125"/>
       <c r="F121" s="81"/>
-      <c r="G121" s="49" t="s">
-        <v>434</v>
+      <c r="G121" s="125" t="s">
+        <v>433</v>
       </c>
       <c r="H121" s="48" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I121" s="47" t="s">
         <v>1</v>
@@ -6901,21 +7040,19 @@
       <c r="B122" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="C122" s="52" t="s">
-        <v>338</v>
-      </c>
+      <c r="C122" s="126"/>
       <c r="D122" s="51"/>
-      <c r="E122" s="52" t="s">
+      <c r="E122" s="126" t="s">
         <v>57</v>
       </c>
       <c r="F122" s="82" t="s">
+        <v>422</v>
+      </c>
+      <c r="G122" s="126" t="s">
+        <v>57</v>
+      </c>
+      <c r="H122" s="51" t="s">
         <v>423</v>
-      </c>
-      <c r="G122" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="H122" s="51" t="s">
-        <v>424</v>
       </c>
       <c r="I122" s="50" t="s">
         <v>24</v>
@@ -6943,21 +7080,19 @@
       <c r="B123" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C123" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C123" s="127"/>
       <c r="D123" s="53"/>
-      <c r="E123" s="54" t="s">
+      <c r="E123" s="127" t="s">
         <v>72</v>
       </c>
       <c r="F123" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G123" s="55" t="s">
-        <v>435</v>
+        <v>421</v>
+      </c>
+      <c r="G123" s="128" t="s">
+        <v>434</v>
       </c>
       <c r="H123" s="53" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I123" s="50" t="s">
         <v>23</v>
@@ -6985,21 +7120,19 @@
       <c r="B124" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C124" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C124" s="127"/>
       <c r="D124" s="53"/>
-      <c r="E124" s="54" t="s">
+      <c r="E124" s="127" t="s">
         <v>98</v>
       </c>
       <c r="F124" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G124" s="127" t="s">
+        <v>435</v>
+      </c>
+      <c r="H124" s="53" t="s">
         <v>423</v>
-      </c>
-      <c r="G124" s="54" t="s">
-        <v>436</v>
-      </c>
-      <c r="H124" s="53" t="s">
-        <v>424</v>
       </c>
       <c r="I124" s="50" t="s">
         <v>22</v>
@@ -7027,13 +7160,11 @@
       <c r="B125" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C125" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C125" s="127"/>
       <c r="D125" s="53"/>
-      <c r="E125" s="54"/>
+      <c r="E125" s="127"/>
       <c r="F125" s="83"/>
-      <c r="G125" s="54"/>
+      <c r="G125" s="127"/>
       <c r="H125" s="53"/>
       <c r="I125" s="50" t="s">
         <v>21</v>
@@ -7061,21 +7192,19 @@
       <c r="B126" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C126" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C126" s="127"/>
       <c r="D126" s="53"/>
-      <c r="E126" s="54" t="s">
+      <c r="E126" s="127" t="s">
         <v>84</v>
       </c>
       <c r="F126" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G126" s="55" t="s">
-        <v>357</v>
+        <v>421</v>
+      </c>
+      <c r="G126" s="128" t="s">
+        <v>356</v>
       </c>
       <c r="H126" s="53" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I126" s="50" t="s">
         <v>20</v>
@@ -7103,17 +7232,15 @@
       <c r="B127" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C127" s="127"/>
       <c r="D127" s="53"/>
-      <c r="E127" s="54" t="s">
-        <v>437</v>
+      <c r="E127" s="127" t="s">
+        <v>436</v>
       </c>
       <c r="F127" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G127" s="54"/>
+        <v>421</v>
+      </c>
+      <c r="G127" s="127"/>
       <c r="H127" s="53"/>
       <c r="I127" s="50" t="s">
         <v>19</v>
@@ -7141,19 +7268,19 @@
       <c r="B128" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C128" s="55" t="s">
-        <v>404</v>
+      <c r="C128" s="128" t="s">
+        <v>403</v>
       </c>
       <c r="D128" s="53" t="s">
-        <v>419</v>
-      </c>
-      <c r="E128" s="54"/>
+        <v>418</v>
+      </c>
+      <c r="E128" s="127"/>
       <c r="F128" s="83"/>
-      <c r="G128" s="54" t="s">
-        <v>438</v>
+      <c r="G128" s="127" t="s">
+        <v>437</v>
       </c>
       <c r="H128" s="53" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I128" s="50" t="s">
         <v>18</v>
@@ -7181,19 +7308,19 @@
       <c r="B129" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C129" s="53"/>
+      <c r="C129" s="129"/>
       <c r="D129" s="53"/>
-      <c r="E129" s="54" t="s">
+      <c r="E129" s="127" t="s">
+        <v>438</v>
+      </c>
+      <c r="F129" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G129" s="128" t="s">
         <v>439</v>
       </c>
-      <c r="F129" s="83" t="s">
+      <c r="H129" s="53" t="s">
         <v>423</v>
-      </c>
-      <c r="G129" s="55" t="s">
-        <v>440</v>
-      </c>
-      <c r="H129" s="53" t="s">
-        <v>424</v>
       </c>
       <c r="I129" s="50" t="s">
         <v>17</v>
@@ -7221,17 +7348,15 @@
       <c r="B130" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C130" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C130" s="127"/>
       <c r="D130" s="53"/>
-      <c r="E130" s="54" t="s">
-        <v>441</v>
+      <c r="E130" s="127" t="s">
+        <v>440</v>
       </c>
       <c r="F130" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="G130" s="54"/>
+        <v>422</v>
+      </c>
+      <c r="G130" s="127"/>
       <c r="H130" s="53"/>
       <c r="I130" s="50" t="s">
         <v>16</v>
@@ -7259,17 +7384,15 @@
       <c r="B131" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C131" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C131" s="127"/>
       <c r="D131" s="53"/>
-      <c r="E131" s="54"/>
+      <c r="E131" s="127"/>
       <c r="F131" s="83"/>
-      <c r="G131" s="54" t="s">
-        <v>442</v>
+      <c r="G131" s="127" t="s">
+        <v>441</v>
       </c>
       <c r="H131" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I131" s="50" t="s">
         <v>15</v>
@@ -7297,21 +7420,19 @@
       <c r="B132" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C132" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C132" s="127"/>
       <c r="D132" s="53"/>
-      <c r="E132" s="54" t="s">
-        <v>443</v>
+      <c r="E132" s="127" t="s">
+        <v>442</v>
       </c>
       <c r="F132" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G132" s="55" t="s">
-        <v>366</v>
+        <v>421</v>
+      </c>
+      <c r="G132" s="128" t="s">
+        <v>365</v>
       </c>
       <c r="H132" s="53" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I132" s="50" t="s">
         <v>14</v>
@@ -7339,19 +7460,19 @@
       <c r="B133" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C133" s="56">
-        <v>0.46458333333333335</v>
+      <c r="C133" s="130" t="s">
+        <v>482</v>
       </c>
       <c r="D133" s="53" t="s">
-        <v>414</v>
-      </c>
-      <c r="E133" s="54" t="s">
-        <v>444</v>
+        <v>413</v>
+      </c>
+      <c r="E133" s="127" t="s">
+        <v>443</v>
       </c>
       <c r="F133" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G133" s="54"/>
+        <v>421</v>
+      </c>
+      <c r="G133" s="127"/>
       <c r="H133" s="53"/>
       <c r="I133" s="50" t="s">
         <v>13</v>
@@ -7379,17 +7500,15 @@
       <c r="B134" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C134" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C134" s="127"/>
       <c r="D134" s="53"/>
-      <c r="E134" s="56"/>
+      <c r="E134" s="131"/>
       <c r="F134" s="83"/>
-      <c r="G134" s="54" t="s">
-        <v>445</v>
+      <c r="G134" s="127" t="s">
+        <v>444</v>
       </c>
       <c r="H134" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I134" s="50" t="s">
         <v>12</v>
@@ -7417,19 +7536,19 @@
       <c r="B135" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C135" s="56"/>
+      <c r="C135" s="131"/>
       <c r="D135" s="53"/>
-      <c r="E135" s="54" t="s">
+      <c r="E135" s="127" t="s">
         <v>267</v>
       </c>
       <c r="F135" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G135" s="128" t="s">
+        <v>445</v>
+      </c>
+      <c r="H135" s="53" t="s">
         <v>423</v>
-      </c>
-      <c r="G135" s="55" t="s">
-        <v>446</v>
-      </c>
-      <c r="H135" s="53" t="s">
-        <v>424</v>
       </c>
       <c r="I135" s="50" t="s">
         <v>11</v>
@@ -7457,19 +7576,19 @@
       <c r="B136" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C136" s="54" t="s">
-        <v>405</v>
+      <c r="C136" s="127" t="s">
+        <v>404</v>
       </c>
       <c r="D136" s="53" t="s">
-        <v>420</v>
-      </c>
-      <c r="E136" s="54" t="s">
+        <v>419</v>
+      </c>
+      <c r="E136" s="127" t="s">
         <v>264</v>
       </c>
       <c r="F136" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="G136" s="54"/>
+        <v>422</v>
+      </c>
+      <c r="G136" s="127"/>
       <c r="H136" s="53"/>
       <c r="I136" s="50" t="s">
         <v>10</v>
@@ -7497,17 +7616,15 @@
       <c r="B137" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C137" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C137" s="127"/>
       <c r="D137" s="53"/>
-      <c r="E137" s="54"/>
+      <c r="E137" s="127"/>
       <c r="F137" s="83"/>
-      <c r="G137" s="55" t="s">
+      <c r="G137" s="128" t="s">
         <v>161</v>
       </c>
       <c r="H137" s="53" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I137" s="50" t="s">
         <v>9</v>
@@ -7535,23 +7652,23 @@
       <c r="B138" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C138" s="56">
-        <v>0.68819444444444444</v>
+      <c r="C138" s="130" t="s">
+        <v>483</v>
       </c>
       <c r="D138" s="53" t="s">
-        <v>421</v>
-      </c>
-      <c r="E138" s="54" t="s">
-        <v>447</v>
+        <v>420</v>
+      </c>
+      <c r="E138" s="127" t="s">
+        <v>446</v>
       </c>
       <c r="F138" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G138" s="127" t="s">
+        <v>372</v>
+      </c>
+      <c r="H138" s="53" t="s">
         <v>423</v>
-      </c>
-      <c r="G138" s="54" t="s">
-        <v>373</v>
-      </c>
-      <c r="H138" s="53" t="s">
-        <v>424</v>
       </c>
       <c r="I138" s="50">
         <v>16</v>
@@ -7579,17 +7696,15 @@
       <c r="B139" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C139" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C139" s="127"/>
       <c r="D139" s="53"/>
-      <c r="E139" s="54" t="s">
+      <c r="E139" s="127" t="s">
         <v>88</v>
       </c>
       <c r="F139" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="G139" s="54"/>
+        <v>422</v>
+      </c>
+      <c r="G139" s="127"/>
       <c r="H139" s="53"/>
       <c r="I139" s="50" t="s">
         <v>7</v>
@@ -7617,17 +7732,15 @@
       <c r="B140" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C140" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C140" s="127"/>
       <c r="D140" s="53"/>
-      <c r="E140" s="54"/>
+      <c r="E140" s="127"/>
       <c r="F140" s="83"/>
-      <c r="G140" s="54" t="s">
-        <v>448</v>
+      <c r="G140" s="127" t="s">
+        <v>447</v>
       </c>
       <c r="H140" s="53" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I140" s="50" t="s">
         <v>6</v>
@@ -7655,23 +7768,23 @@
       <c r="B141" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C141" s="54" t="s">
-        <v>406</v>
+      <c r="C141" s="127" t="s">
+        <v>405</v>
       </c>
       <c r="D141" s="53" t="s">
-        <v>416</v>
-      </c>
-      <c r="E141" s="54" t="s">
+        <v>415</v>
+      </c>
+      <c r="E141" s="127" t="s">
+        <v>448</v>
+      </c>
+      <c r="F141" s="83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G141" s="127" t="s">
         <v>449</v>
       </c>
-      <c r="F141" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="G141" s="54" t="s">
-        <v>450</v>
-      </c>
       <c r="H141" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I141" s="50" t="s">
         <v>5</v>
@@ -7699,17 +7812,15 @@
       <c r="B142" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C142" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C142" s="127"/>
       <c r="D142" s="53"/>
-      <c r="E142" s="54" t="s">
-        <v>451</v>
+      <c r="E142" s="127" t="s">
+        <v>450</v>
       </c>
       <c r="F142" s="83" t="s">
-        <v>422</v>
-      </c>
-      <c r="G142" s="54"/>
+        <v>421</v>
+      </c>
+      <c r="G142" s="127"/>
       <c r="H142" s="53"/>
       <c r="I142" s="50" t="s">
         <v>4</v>
@@ -7737,17 +7848,15 @@
       <c r="B143" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="54" t="s">
-        <v>338</v>
-      </c>
+      <c r="C143" s="127"/>
       <c r="D143" s="53"/>
-      <c r="E143" s="54"/>
+      <c r="E143" s="127"/>
       <c r="F143" s="83"/>
-      <c r="G143" s="54" t="s">
-        <v>452</v>
+      <c r="G143" s="127" t="s">
+        <v>451</v>
       </c>
       <c r="H143" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I143" s="50" t="s">
         <v>3</v>
@@ -7775,23 +7884,23 @@
       <c r="B144" s="53" t="s">
         <v>25</v>
       </c>
-      <c r="C144" s="54" t="s">
+      <c r="C144" s="127" t="s">
         <v>237</v>
       </c>
       <c r="D144" s="53" t="s">
-        <v>432</v>
-      </c>
-      <c r="E144" s="54" t="s">
-        <v>453</v>
+        <v>431</v>
+      </c>
+      <c r="E144" s="127" t="s">
+        <v>452</v>
       </c>
       <c r="F144" s="83" t="s">
-        <v>423</v>
-      </c>
-      <c r="G144" s="54" t="s">
-        <v>381</v>
+        <v>422</v>
+      </c>
+      <c r="G144" s="127" t="s">
+        <v>380</v>
       </c>
       <c r="H144" s="53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I144" s="50" t="s">
         <v>2</v>
@@ -7819,15 +7928,15 @@
       <c r="B145" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C145" s="59"/>
+      <c r="C145" s="132"/>
       <c r="D145" s="58"/>
-      <c r="E145" s="59" t="s">
-        <v>454</v>
+      <c r="E145" s="132" t="s">
+        <v>453</v>
       </c>
       <c r="F145" s="84" t="s">
-        <v>422</v>
-      </c>
-      <c r="G145" s="59"/>
+        <v>421</v>
+      </c>
+      <c r="G145" s="132"/>
       <c r="H145" s="58"/>
       <c r="I145" s="57" t="s">
         <v>1</v>
@@ -7855,11 +7964,11 @@
       <c r="B146" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C146" s="61"/>
+      <c r="C146" s="133"/>
       <c r="D146" s="61"/>
-      <c r="E146" s="62"/>
+      <c r="E146" s="143"/>
       <c r="F146" s="85"/>
-      <c r="G146" s="62"/>
+      <c r="G146" s="143"/>
       <c r="H146" s="61"/>
       <c r="I146" s="60" t="s">
         <v>24</v>
@@ -7887,19 +7996,19 @@
       <c r="B147" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C147" s="63"/>
+      <c r="C147" s="134"/>
       <c r="D147" s="63"/>
-      <c r="E147" s="64" t="s">
+      <c r="E147" s="135" t="s">
         <v>94</v>
       </c>
       <c r="F147" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G147" s="135" t="s">
+        <v>454</v>
+      </c>
+      <c r="H147" s="63" t="s">
         <v>423</v>
-      </c>
-      <c r="G147" s="64" t="s">
-        <v>455</v>
-      </c>
-      <c r="H147" s="63" t="s">
-        <v>424</v>
       </c>
       <c r="I147" s="60" t="s">
         <v>23</v>
@@ -7927,23 +8036,23 @@
       <c r="B148" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C148" s="64" t="s">
+      <c r="C148" s="135" t="s">
         <v>163</v>
       </c>
       <c r="D148" s="63" t="s">
-        <v>428</v>
-      </c>
-      <c r="E148" s="64" t="s">
-        <v>456</v>
+        <v>427</v>
+      </c>
+      <c r="E148" s="135" t="s">
+        <v>455</v>
       </c>
       <c r="F148" s="86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G148" s="64" t="s">
+        <v>421</v>
+      </c>
+      <c r="G148" s="135" t="s">
         <v>118</v>
       </c>
       <c r="H148" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I148" s="60" t="s">
         <v>22</v>
@@ -7971,15 +8080,15 @@
       <c r="B149" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C149" s="64"/>
+      <c r="C149" s="135"/>
       <c r="D149" s="63"/>
-      <c r="E149" s="64"/>
+      <c r="E149" s="135"/>
       <c r="F149" s="86"/>
-      <c r="G149" s="65" t="s">
-        <v>457</v>
+      <c r="G149" s="151" t="s">
+        <v>456</v>
       </c>
       <c r="H149" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I149" s="60" t="s">
         <v>21</v>
@@ -8007,11 +8116,11 @@
       <c r="B150" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C150" s="64"/>
+      <c r="C150" s="135"/>
       <c r="D150" s="63"/>
-      <c r="E150" s="64"/>
+      <c r="E150" s="135"/>
       <c r="F150" s="86"/>
-      <c r="G150" s="64"/>
+      <c r="G150" s="135"/>
       <c r="H150" s="63"/>
       <c r="I150" s="60" t="s">
         <v>20</v>
@@ -8039,19 +8148,19 @@
       <c r="B151" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C151" s="64"/>
+      <c r="C151" s="135"/>
       <c r="D151" s="63"/>
-      <c r="E151" s="90" t="s">
+      <c r="E151" s="136" t="s">
+        <v>457</v>
+      </c>
+      <c r="F151" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="G151" s="135" t="s">
         <v>458</v>
       </c>
-      <c r="F151" s="86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G151" s="64" t="s">
-        <v>459</v>
-      </c>
       <c r="H151" s="63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I151" s="60" t="s">
         <v>19</v>
@@ -8079,23 +8188,23 @@
       <c r="B152" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C152" s="90" t="s">
+      <c r="C152" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="D152" s="63" t="s">
+        <v>428</v>
+      </c>
+      <c r="E152" s="136" t="s">
+        <v>388</v>
+      </c>
+      <c r="F152" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="G152" s="135" t="s">
         <v>460</v>
       </c>
-      <c r="D152" s="63" t="s">
-        <v>429</v>
-      </c>
-      <c r="E152" s="90" t="s">
-        <v>389</v>
-      </c>
-      <c r="F152" s="86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G152" s="64" t="s">
-        <v>461</v>
-      </c>
       <c r="H152" s="63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I152" s="60" t="s">
         <v>18</v>
@@ -8123,11 +8232,11 @@
       <c r="B153" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="64"/>
+      <c r="C153" s="135"/>
       <c r="D153" s="63"/>
-      <c r="E153" s="64"/>
+      <c r="E153" s="135"/>
       <c r="F153" s="86"/>
-      <c r="G153" s="65"/>
+      <c r="G153" s="151"/>
       <c r="H153" s="63"/>
       <c r="I153" s="60" t="s">
         <v>17</v>
@@ -8155,19 +8264,19 @@
       <c r="B154" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C154" s="64"/>
+      <c r="C154" s="135"/>
       <c r="D154" s="63"/>
-      <c r="E154" s="64" t="s">
-        <v>390</v>
+      <c r="E154" s="135" t="s">
+        <v>389</v>
       </c>
       <c r="F154" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G154" s="64" t="s">
+        <v>422</v>
+      </c>
+      <c r="G154" s="135" t="s">
         <v>96</v>
       </c>
       <c r="H154" s="63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I154" s="60" t="s">
         <v>16</v>
@@ -8195,23 +8304,23 @@
       <c r="B155" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C155" s="64" t="s">
+      <c r="C155" s="135" t="s">
+        <v>461</v>
+      </c>
+      <c r="D155" s="63" t="s">
+        <v>432</v>
+      </c>
+      <c r="E155" s="135" t="s">
         <v>462</v>
       </c>
-      <c r="D155" s="63" t="s">
-        <v>433</v>
-      </c>
-      <c r="E155" s="64" t="s">
-        <v>463</v>
-      </c>
       <c r="F155" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G155" s="65" t="s">
-        <v>463</v>
+        <v>422</v>
+      </c>
+      <c r="G155" s="151" t="s">
+        <v>462</v>
       </c>
       <c r="H155" s="63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I155" s="60" t="s">
         <v>15</v>
@@ -8239,11 +8348,11 @@
       <c r="B156" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C156" s="64"/>
+      <c r="C156" s="135"/>
       <c r="D156" s="63"/>
-      <c r="E156" s="64"/>
+      <c r="E156" s="135"/>
       <c r="F156" s="86"/>
-      <c r="G156" s="64"/>
+      <c r="G156" s="135"/>
       <c r="H156" s="63"/>
       <c r="I156" s="60" t="s">
         <v>14</v>
@@ -8271,19 +8380,19 @@
       <c r="B157" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C157" s="64"/>
+      <c r="C157" s="135"/>
       <c r="D157" s="63"/>
-      <c r="E157" s="64" t="s">
+      <c r="E157" s="135" t="s">
+        <v>463</v>
+      </c>
+      <c r="F157" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G157" s="135" t="s">
         <v>464</v>
       </c>
-      <c r="F157" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G157" s="64" t="s">
-        <v>465</v>
-      </c>
       <c r="H157" s="63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I157" s="60" t="s">
         <v>13</v>
@@ -8311,19 +8420,19 @@
       <c r="B158" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C158" s="64"/>
+      <c r="C158" s="135"/>
       <c r="D158" s="63"/>
-      <c r="E158" s="64" t="s">
-        <v>466</v>
+      <c r="E158" s="135" t="s">
+        <v>465</v>
       </c>
       <c r="F158" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G158" s="64" t="s">
-        <v>394</v>
+        <v>422</v>
+      </c>
+      <c r="G158" s="135" t="s">
+        <v>393</v>
       </c>
       <c r="H158" s="63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I158" s="60" t="s">
         <v>12</v>
@@ -8351,15 +8460,15 @@
       <c r="B159" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C159" s="64" t="s">
-        <v>467</v>
+      <c r="C159" s="135" t="s">
+        <v>466</v>
       </c>
       <c r="D159" s="63" t="s">
-        <v>430</v>
-      </c>
-      <c r="E159" s="63"/>
+        <v>429</v>
+      </c>
+      <c r="E159" s="134"/>
       <c r="F159" s="86"/>
-      <c r="G159" s="64"/>
+      <c r="G159" s="135"/>
       <c r="H159" s="63"/>
       <c r="I159" s="60" t="s">
         <v>11</v>
@@ -8387,19 +8496,19 @@
       <c r="B160" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C160" s="64"/>
+      <c r="C160" s="135"/>
       <c r="D160" s="63"/>
-      <c r="E160" s="64" t="s">
+      <c r="E160" s="135" t="s">
+        <v>467</v>
+      </c>
+      <c r="F160" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G160" s="135" t="s">
         <v>468</v>
       </c>
-      <c r="F160" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G160" s="64" t="s">
-        <v>469</v>
-      </c>
       <c r="H160" s="63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I160" s="60" t="s">
         <v>10</v>
@@ -8427,19 +8536,19 @@
       <c r="B161" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C161" s="64"/>
+      <c r="C161" s="135"/>
       <c r="D161" s="63"/>
-      <c r="E161" s="64" t="s">
+      <c r="E161" s="135" t="s">
+        <v>469</v>
+      </c>
+      <c r="F161" s="86" t="s">
+        <v>422</v>
+      </c>
+      <c r="G161" s="151" t="s">
         <v>470</v>
       </c>
-      <c r="F161" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G161" s="65" t="s">
-        <v>471</v>
-      </c>
       <c r="H161" s="63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I161" s="60" t="s">
         <v>9</v>
@@ -8467,15 +8576,15 @@
       <c r="B162" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C162" s="64" t="s">
-        <v>472</v>
+      <c r="C162" s="135" t="s">
+        <v>471</v>
       </c>
       <c r="D162" s="63" t="s">
-        <v>415</v>
-      </c>
-      <c r="E162" s="64"/>
+        <v>414</v>
+      </c>
+      <c r="E162" s="135"/>
       <c r="F162" s="86"/>
-      <c r="G162" s="64"/>
+      <c r="G162" s="135"/>
       <c r="H162" s="63"/>
       <c r="I162" s="60" t="s">
         <v>8</v>
@@ -8503,19 +8612,19 @@
       <c r="B163" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C163" s="64"/>
+      <c r="C163" s="135"/>
       <c r="D163" s="63"/>
-      <c r="E163" s="64" t="s">
+      <c r="E163" s="135" t="s">
+        <v>472</v>
+      </c>
+      <c r="F163" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="G163" s="135" t="s">
         <v>473</v>
       </c>
-      <c r="F163" s="86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G163" s="64" t="s">
-        <v>474</v>
-      </c>
       <c r="H163" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I163" s="60" t="s">
         <v>7</v>
@@ -8543,19 +8652,19 @@
       <c r="B164" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C164" s="64"/>
+      <c r="C164" s="135"/>
       <c r="D164" s="63"/>
-      <c r="E164" s="64" t="s">
-        <v>344</v>
+      <c r="E164" s="135" t="s">
+        <v>343</v>
       </c>
       <c r="F164" s="86" t="s">
-        <v>423</v>
-      </c>
-      <c r="G164" s="64" t="s">
-        <v>475</v>
+        <v>422</v>
+      </c>
+      <c r="G164" s="135" t="s">
+        <v>474</v>
       </c>
       <c r="H164" s="63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I164" s="60" t="s">
         <v>6</v>
@@ -8583,15 +8692,15 @@
       <c r="B165" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C165" s="64" t="s">
-        <v>476</v>
+      <c r="C165" s="135" t="s">
+        <v>475</v>
       </c>
       <c r="D165" s="63" t="s">
-        <v>431</v>
-      </c>
-      <c r="E165" s="64"/>
+        <v>430</v>
+      </c>
+      <c r="E165" s="135"/>
       <c r="F165" s="86"/>
-      <c r="G165" s="64"/>
+      <c r="G165" s="135"/>
       <c r="H165" s="63"/>
       <c r="I165" s="60" t="s">
         <v>5</v>
@@ -8619,19 +8728,19 @@
       <c r="B166" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C166" s="66"/>
+      <c r="C166" s="137"/>
       <c r="D166" s="63"/>
-      <c r="E166" s="64" t="s">
+      <c r="E166" s="135" t="s">
+        <v>476</v>
+      </c>
+      <c r="F166" s="86" t="s">
+        <v>421</v>
+      </c>
+      <c r="G166" s="135" t="s">
         <v>477</v>
       </c>
-      <c r="F166" s="86" t="s">
-        <v>422</v>
-      </c>
-      <c r="G166" s="64" t="s">
-        <v>478</v>
-      </c>
       <c r="H166" s="63" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I166" s="60" t="s">
         <v>4</v>
@@ -8659,11 +8768,11 @@
       <c r="B167" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="64"/>
+      <c r="C167" s="135"/>
       <c r="D167" s="63"/>
-      <c r="E167" s="64"/>
+      <c r="E167" s="135"/>
       <c r="F167" s="86"/>
-      <c r="G167" s="64"/>
+      <c r="G167" s="135"/>
       <c r="H167" s="63"/>
       <c r="I167" s="60" t="s">
         <v>3</v>
@@ -8691,11 +8800,11 @@
       <c r="B168" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C168" s="64"/>
+      <c r="C168" s="135"/>
       <c r="D168" s="63"/>
-      <c r="E168" s="64"/>
+      <c r="E168" s="135"/>
       <c r="F168" s="86"/>
-      <c r="G168" s="64"/>
+      <c r="G168" s="135"/>
       <c r="H168" s="63"/>
       <c r="I168" s="60" t="s">
         <v>2</v>
@@ -8723,11 +8832,11 @@
       <c r="B169" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C169" s="64"/>
+      <c r="C169" s="135"/>
       <c r="D169" s="63"/>
-      <c r="E169" s="64"/>
+      <c r="E169" s="135"/>
       <c r="F169" s="86"/>
-      <c r="G169" s="64"/>
+      <c r="G169" s="135"/>
       <c r="H169" s="63"/>
       <c r="I169" s="60" t="s">
         <v>1</v>
@@ -8787,29 +8896,29 @@
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="91" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="92" t="s">
+      <c r="F1" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="92" t="s">
+      <c r="G1" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="92" t="s">
+      <c r="H1" s="91" t="s">
         <v>32</v>
       </c>
       <c r="I1" s="1"/>
-      <c r="J1" s="92"/>
+      <c r="J1" s="91"/>
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -9742,7 +9851,7 @@
       <c r="B26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="90" t="s">
         <v>312</v>
       </c>
       <c r="D26" s="13" t="s">
@@ -11034,13 +11143,13 @@
       <c r="B59" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="96" t="s">
+      <c r="C59" s="95" t="s">
         <v>327</v>
       </c>
       <c r="D59" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="E59" s="94" t="s">
+      <c r="E59" s="93" t="s">
         <v>326</v>
       </c>
       <c r="F59" s="26" t="s">
@@ -12726,7 +12835,7 @@
       <c r="B103" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="93">
+      <c r="C103" s="92">
         <v>0.24444444444444444</v>
       </c>
       <c r="D103" s="44" t="s">
@@ -14572,7 +14681,7 @@
       </c>
       <c r="C151" s="64"/>
       <c r="D151" s="63"/>
-      <c r="E151" s="90" t="s">
+      <c r="E151" s="89" t="s">
         <v>311</v>
       </c>
       <c r="F151" s="63" t="s">
@@ -14610,13 +14719,13 @@
       <c r="B152" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C152" s="90" t="s">
+      <c r="C152" s="89" t="s">
         <v>286</v>
       </c>
       <c r="D152" s="63" t="s">
         <v>307</v>
       </c>
-      <c r="E152" s="90" t="s">
+      <c r="E152" s="89" t="s">
         <v>317</v>
       </c>
       <c r="F152" s="63" t="s">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FE450-89CD-4DE0-A2CF-57081E66E329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0730BBCE-3FEB-417B-87B2-62DEBC0753B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12630" yWindow="3885" windowWidth="16140" windowHeight="11235" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="563">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1908,6 +1908,10 @@
   </si>
   <si>
     <t>05:4×_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21:49_?</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -7590,8 +7594,12 @@
       <c r="F119" s="151" t="s">
         <v>420</v>
       </c>
-      <c r="G119" s="150"/>
-      <c r="H119" s="149"/>
+      <c r="G119" s="150" t="s">
+        <v>562</v>
+      </c>
+      <c r="H119" s="149" t="s">
+        <v>424</v>
+      </c>
       <c r="I119" s="145" t="s">
         <v>3</v>
       </c>
@@ -7608,7 +7616,7 @@
       </c>
       <c r="M119" s="85" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>21:49_?</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="18" customHeight="1">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0730BBCE-3FEB-417B-87B2-62DEBC0753B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202B427C-01EE-4F15-A8BF-D4D0780D2530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12630" yWindow="0" windowWidth="16140" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="562">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1644,10 +1644,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>23:52</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>23:54</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1792,13 +1788,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>武神荒野_?</t>
-  </si>
-  <si>
-    <t>力王山脈_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>03:53_?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1911,7 +1900,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>21:49_?</t>
+    <t>21:50</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武神荒野</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風之平原</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1922,7 +1919,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="\'hh:mm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1982,6 +1979,11 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2113,7 +2115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2684,6 +2686,9 @@
     </xf>
     <xf numFmtId="20" fontId="8" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3119,7 +3124,7 @@
       <c r="C3" s="83"/>
       <c r="D3" s="82"/>
       <c r="E3" s="83" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F3" s="84" t="s">
         <v>420</v>
@@ -3165,7 +3170,7 @@
         <v>420</v>
       </c>
       <c r="G4" s="83" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H4" s="82" t="s">
         <v>421</v>
@@ -3197,10 +3202,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="83" t="s">
+        <v>507</v>
+      </c>
+      <c r="D5" s="82" t="s">
         <v>508</v>
-      </c>
-      <c r="D5" s="82" t="s">
-        <v>509</v>
       </c>
       <c r="E5" s="83"/>
       <c r="F5" s="84"/>
@@ -3235,7 +3240,7 @@
       <c r="C6" s="83"/>
       <c r="D6" s="82"/>
       <c r="E6" s="83" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F6" s="84" t="s">
         <v>420</v>
@@ -3309,10 +3314,10 @@
         <v>30</v>
       </c>
       <c r="C8" s="83" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E8" s="88"/>
       <c r="F8" s="84"/>
@@ -3429,10 +3434,10 @@
       <c r="E11" s="83"/>
       <c r="F11" s="84"/>
       <c r="G11" s="83" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H11" s="82" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I11" s="81" t="s">
         <v>15</v>
@@ -3461,22 +3466,22 @@
         <v>30</v>
       </c>
       <c r="C12" s="83" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E12" s="83" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F12" s="84" t="s">
         <v>420</v>
       </c>
       <c r="G12" s="83" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H12" s="89" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="I12" s="81" t="s">
         <v>14</v>
@@ -3507,13 +3512,13 @@
       <c r="C13" s="83"/>
       <c r="D13" s="82"/>
       <c r="E13" s="83" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F13" s="84" t="s">
         <v>419</v>
       </c>
       <c r="G13" s="87" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H13" s="82" t="s">
         <v>421</v>
@@ -3617,19 +3622,19 @@
         <v>30</v>
       </c>
       <c r="C16" s="91" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D16" s="82" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E16" s="83" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F16" s="84" t="s">
         <v>420</v>
       </c>
       <c r="G16" s="87" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H16" s="82" t="s">
         <v>421</v>
@@ -3695,7 +3700,7 @@
       <c r="C18" s="83"/>
       <c r="D18" s="82"/>
       <c r="E18" s="83" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F18" s="84" t="s">
         <v>419</v>
@@ -3737,10 +3742,10 @@
       <c r="E19" s="83"/>
       <c r="F19" s="84"/>
       <c r="G19" s="83" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H19" s="82" t="s">
-        <v>525</v>
+        <v>560</v>
       </c>
       <c r="I19" s="81" t="s">
         <v>7</v>
@@ -3805,7 +3810,7 @@
       <c r="E21" s="83"/>
       <c r="F21" s="84"/>
       <c r="G21" s="87" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H21" s="82" t="s">
         <v>423</v>
@@ -3837,13 +3842,13 @@
         <v>30</v>
       </c>
       <c r="C22" s="83" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D22" s="82" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E22" s="83" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F22" s="84" t="s">
         <v>419</v>
@@ -3993,10 +3998,10 @@
         <v>29</v>
       </c>
       <c r="C26" s="98" t="s">
+        <v>501</v>
+      </c>
+      <c r="D26" s="97" t="s">
         <v>502</v>
-      </c>
-      <c r="D26" s="97" t="s">
-        <v>503</v>
       </c>
       <c r="E26" s="98" t="s">
         <v>57</v>
@@ -4081,10 +4086,10 @@
         <v>420</v>
       </c>
       <c r="G28" s="102" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="H28" s="100" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I28" s="96" t="s">
         <v>22</v>
@@ -4117,10 +4122,10 @@
       <c r="E29" s="102"/>
       <c r="F29" s="103"/>
       <c r="G29" s="107" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H29" s="100" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I29" s="96" t="s">
         <v>21</v>
@@ -4151,7 +4156,7 @@
       <c r="C30" s="105"/>
       <c r="D30" s="100"/>
       <c r="E30" s="102" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F30" s="103" t="s">
         <v>420</v>
@@ -4187,16 +4192,16 @@
       <c r="C31" s="102"/>
       <c r="D31" s="100"/>
       <c r="E31" s="102" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="F31" s="103" t="s">
         <v>420</v>
       </c>
       <c r="G31" s="102" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H31" s="100" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I31" s="96" t="s">
         <v>19</v>
@@ -4259,16 +4264,16 @@
       <c r="C33" s="106"/>
       <c r="D33" s="100"/>
       <c r="E33" s="102" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F33" s="103" t="s">
         <v>419</v>
       </c>
       <c r="G33" s="102" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H33" s="100" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I33" s="96" t="s">
         <v>17</v>
@@ -4299,16 +4304,16 @@
       <c r="C34" s="105"/>
       <c r="D34" s="100"/>
       <c r="E34" s="102" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F34" s="103" t="s">
         <v>420</v>
       </c>
       <c r="G34" s="102" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H34" s="100" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I34" s="96" t="s">
         <v>16</v>
@@ -4409,13 +4414,13 @@
         <v>29</v>
       </c>
       <c r="C37" s="102" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D37" s="100" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E37" s="102" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F37" s="103" t="s">
         <v>420</v>
@@ -4457,7 +4462,7 @@
       <c r="E38" s="102"/>
       <c r="F38" s="103"/>
       <c r="G38" s="190" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H38" s="100" t="s">
         <v>423</v>
@@ -4491,7 +4496,7 @@
       <c r="C39" s="102"/>
       <c r="D39" s="100"/>
       <c r="E39" s="102" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F39" s="103" t="s">
         <v>420</v>
@@ -4527,13 +4532,13 @@
       <c r="C40" s="101"/>
       <c r="D40" s="100"/>
       <c r="E40" s="102" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F40" s="103" t="s">
         <v>420</v>
       </c>
       <c r="G40" s="102" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H40" s="100" t="s">
         <v>421</v>
@@ -4565,18 +4570,18 @@
         <v>29</v>
       </c>
       <c r="C41" s="102" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D41" s="100" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E41" s="102"/>
       <c r="F41" s="103"/>
       <c r="G41" s="102" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H41" s="100" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I41" s="96" t="s">
         <v>9</v>
@@ -4735,13 +4740,13 @@
       <c r="C46" s="102"/>
       <c r="D46" s="100"/>
       <c r="E46" s="102" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="F46" s="103" t="s">
         <v>419</v>
       </c>
       <c r="G46" s="102" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H46" s="100" t="s">
         <v>421</v>
@@ -4777,7 +4782,7 @@
       <c r="E47" s="105"/>
       <c r="F47" s="103"/>
       <c r="G47" s="102" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H47" s="100" t="s">
         <v>423</v>
@@ -4809,10 +4814,10 @@
         <v>29</v>
       </c>
       <c r="C48" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="D48" s="100" t="s">
         <v>495</v>
-      </c>
-      <c r="D48" s="100" t="s">
-        <v>496</v>
       </c>
       <c r="E48" s="102" t="s">
         <v>130</v>
@@ -4851,13 +4856,13 @@
       <c r="C49" s="111"/>
       <c r="D49" s="110"/>
       <c r="E49" s="112" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F49" s="113" t="s">
         <v>419</v>
       </c>
       <c r="G49" s="112" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H49" s="110" t="s">
         <v>423</v>
@@ -4896,7 +4901,7 @@
         <v>479</v>
       </c>
       <c r="H50" s="115" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I50" s="114" t="s">
         <v>24</v>
@@ -4965,10 +4970,10 @@
         <v>28</v>
       </c>
       <c r="C52" s="121" t="s">
+        <v>492</v>
+      </c>
+      <c r="D52" s="122" t="s">
         <v>493</v>
-      </c>
-      <c r="D52" s="122" t="s">
-        <v>494</v>
       </c>
       <c r="E52" s="121" t="s">
         <v>484</v>
@@ -5120,7 +5125,7 @@
         <v>40</v>
       </c>
       <c r="D56" s="118" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E56" s="119" t="s">
         <v>40</v>
@@ -5255,7 +5260,7 @@
         <v>80</v>
       </c>
       <c r="E59" s="124" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F59" s="120" t="s">
         <v>80</v>
@@ -5317,7 +5322,7 @@
         <v>80</v>
       </c>
       <c r="G60" s="119" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H60" s="118" t="s">
         <v>80</v>
@@ -5507,7 +5512,7 @@
         <v>28</v>
       </c>
       <c r="C65" s="125" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D65" s="118" t="s">
         <v>406</v>
@@ -5854,7 +5859,7 @@
         <v>57</v>
       </c>
       <c r="D74" s="131" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E74" s="132" t="s">
         <v>57</v>
@@ -6175,7 +6180,7 @@
       <c r="E82" s="135"/>
       <c r="F82" s="136"/>
       <c r="G82" s="135" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H82" s="134" t="s">
         <v>422</v>
@@ -6315,7 +6320,7 @@
         <v>27</v>
       </c>
       <c r="C86" s="140" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D86" s="134" t="s">
         <v>409</v>
@@ -6471,10 +6476,10 @@
         <v>27</v>
       </c>
       <c r="C90" s="135" t="s">
+        <v>490</v>
+      </c>
+      <c r="D90" s="134" t="s">
         <v>491</v>
-      </c>
-      <c r="D90" s="134" t="s">
-        <v>492</v>
       </c>
       <c r="E90" s="135" t="s">
         <v>371</v>
@@ -7129,7 +7134,7 @@
       <c r="C107" s="150"/>
       <c r="D107" s="149"/>
       <c r="E107" s="153" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F107" s="151" t="s">
         <v>419</v>
@@ -7471,7 +7476,7 @@
         <v>26</v>
       </c>
       <c r="C116" s="153" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D116" s="149" t="s">
         <v>415</v>
@@ -7595,7 +7600,7 @@
         <v>420</v>
       </c>
       <c r="G119" s="150" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H119" s="149" t="s">
         <v>424</v>
@@ -7616,7 +7621,7 @@
       </c>
       <c r="M119" s="85" t="str">
         <f t="shared" si="5"/>
-        <v>21:49_?</v>
+        <v>21:50</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="18" customHeight="1">
@@ -8123,7 +8128,7 @@
         <v>25</v>
       </c>
       <c r="C133" s="171" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D133" s="166" t="s">
         <v>411</v>
@@ -8315,7 +8320,7 @@
         <v>25</v>
       </c>
       <c r="C138" s="171" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D138" s="166" t="s">
         <v>418</v>
@@ -9503,16 +9508,16 @@
         <v>0</v>
       </c>
       <c r="C169" s="184" t="s">
+        <v>488</v>
+      </c>
+      <c r="D169" s="182" t="s">
         <v>489</v>
       </c>
-      <c r="D169" s="182" t="s">
-        <v>490</v>
-      </c>
       <c r="E169" s="184" t="s">
-        <v>488</v>
-      </c>
-      <c r="F169" s="185" t="s">
-        <v>419</v>
+        <v>478</v>
+      </c>
+      <c r="F169" s="191" t="s">
+        <v>561</v>
       </c>
       <c r="G169" s="184" t="s">
         <v>478</v>
@@ -9532,7 +9537,7 @@
       </c>
       <c r="L169" s="85" t="str">
         <f t="shared" si="7"/>
-        <v>23:52</v>
+        <v>23:23</v>
       </c>
       <c r="M169" s="85" t="str">
         <f t="shared" si="8"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202B427C-01EE-4F15-A8BF-D4D0780D2530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A15B871-8536-4022-A909-A6370B3746D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12630" yWindow="0" windowWidth="16140" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2446" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="573">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1370,9 +1370,6 @@
     <t>22:27</t>
   </si>
   <si>
-    <t>23:12</t>
-  </si>
-  <si>
     <t>06:48</t>
   </si>
   <si>
@@ -1788,10 +1785,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>03:53_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>力王山脈</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1808,9 +1801,6 @@
     <t>09:02_?</t>
   </si>
   <si>
-    <t>10:29_?</t>
-  </si>
-  <si>
     <t>11:49</t>
   </si>
   <si>
@@ -1826,9 +1816,6 @@
     <t>16:07</t>
   </si>
   <si>
-    <t>17:57_?</t>
-  </si>
-  <si>
     <t>19:23</t>
   </si>
   <si>
@@ -1838,16 +1825,7 @@
     <t>02:21_?</t>
   </si>
   <si>
-    <t>05:28_?</t>
-  </si>
-  <si>
     <t>07:18</t>
-  </si>
-  <si>
-    <t>07:05_?</t>
-  </si>
-  <si>
-    <t>08:29_?</t>
   </si>
   <si>
     <t>11:42</t>
@@ -1884,10 +1862,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>08:40_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>12:45</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1909,6 +1883,82 @@
   </si>
   <si>
     <t>風之平原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土門客棧 / ???</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:48</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:57</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03:51</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:26</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06_54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:24</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>力王山脈</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>風之平原</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18:42_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18:43</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:08</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2426,9 +2476,6 @@
     <xf numFmtId="176" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2438,9 +2485,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2688,6 +2732,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3028,16 +3078,16 @@
   <dimension ref="A1:R169"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="188" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" style="189" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.25" style="188" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.25" style="189" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.125" style="188" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.375" style="189" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.125" style="188" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.75" style="188" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.375" style="188" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.75" style="186" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="186" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="187" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.25" style="186" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.25" style="187" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.125" style="186" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="187" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.125" style="186" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.75" style="186" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.375" style="186" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.625" style="85" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.75" style="85" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.5" style="85" bestFit="1" customWidth="1"/>
@@ -3087,13 +3137,13 @@
         <v>57</v>
       </c>
       <c r="F2" s="84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G2" s="83" t="s">
         <v>57</v>
       </c>
       <c r="H2" s="82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I2" s="81" t="s">
         <v>31</v>
@@ -3124,16 +3174,16 @@
       <c r="C3" s="83"/>
       <c r="D3" s="82"/>
       <c r="E3" s="83" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F3" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G3" s="83" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I3" s="81" t="s">
         <v>23</v>
@@ -3164,16 +3214,16 @@
       <c r="C4" s="83"/>
       <c r="D4" s="86"/>
       <c r="E4" s="83" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F4" s="84" t="s">
+        <v>419</v>
+      </c>
+      <c r="G4" s="83" t="s">
+        <v>525</v>
+      </c>
+      <c r="H4" s="82" t="s">
         <v>420</v>
-      </c>
-      <c r="G4" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="H4" s="82" t="s">
-        <v>421</v>
       </c>
       <c r="I4" s="81" t="s">
         <v>22</v>
@@ -3202,10 +3252,10 @@
         <v>30</v>
       </c>
       <c r="C5" s="83" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="82" t="s">
         <v>507</v>
-      </c>
-      <c r="D5" s="82" t="s">
-        <v>508</v>
       </c>
       <c r="E5" s="83"/>
       <c r="F5" s="84"/>
@@ -3240,16 +3290,16 @@
       <c r="C6" s="83"/>
       <c r="D6" s="82"/>
       <c r="E6" s="83" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F6" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G6" s="87" t="s">
         <v>356</v>
       </c>
       <c r="H6" s="82" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I6" s="81" t="s">
         <v>20</v>
@@ -3283,7 +3333,7 @@
         <v>73</v>
       </c>
       <c r="F7" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G7" s="83"/>
       <c r="H7" s="82"/>
@@ -3314,10 +3364,10 @@
         <v>30</v>
       </c>
       <c r="C8" s="83" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D8" s="82" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E8" s="88"/>
       <c r="F8" s="84"/>
@@ -3325,7 +3375,7 @@
         <v>40</v>
       </c>
       <c r="H8" s="82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I8" s="81" t="s">
         <v>18</v>
@@ -3356,16 +3406,16 @@
       <c r="C9" s="83"/>
       <c r="D9" s="82"/>
       <c r="E9" s="83" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F9" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G9" s="83" t="s">
         <v>221</v>
       </c>
       <c r="H9" s="82" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I9" s="81" t="s">
         <v>17</v>
@@ -3399,7 +3449,7 @@
         <v>362</v>
       </c>
       <c r="F10" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G10" s="87"/>
       <c r="H10" s="82"/>
@@ -3434,10 +3484,10 @@
       <c r="E11" s="83"/>
       <c r="F11" s="84"/>
       <c r="G11" s="83" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H11" s="82" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I11" s="81" t="s">
         <v>15</v>
@@ -3466,22 +3516,22 @@
         <v>30</v>
       </c>
       <c r="C12" s="83" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D12" s="82" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E12" s="83" t="s">
+        <v>547</v>
+      </c>
+      <c r="F12" s="84" t="s">
+        <v>419</v>
+      </c>
+      <c r="G12" s="83" t="s">
         <v>554</v>
       </c>
-      <c r="F12" s="84" t="s">
-        <v>420</v>
-      </c>
-      <c r="G12" s="83" t="s">
-        <v>530</v>
-      </c>
       <c r="H12" s="89" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="I12" s="81" t="s">
         <v>14</v>
@@ -3499,7 +3549,7 @@
       </c>
       <c r="M12" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>10:29_?</v>
+        <v>10:28</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="18" customHeight="1">
@@ -3512,16 +3562,16 @@
       <c r="C13" s="83"/>
       <c r="D13" s="82"/>
       <c r="E13" s="83" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F13" s="84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G13" s="87" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H13" s="82" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I13" s="81" t="s">
         <v>13</v>
@@ -3584,16 +3634,16 @@
       <c r="C15" s="83"/>
       <c r="D15" s="82"/>
       <c r="E15" s="83" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F15" s="84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G15" s="83" t="s">
         <v>369</v>
       </c>
       <c r="H15" s="82" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I15" s="81" t="s">
         <v>11</v>
@@ -3622,22 +3672,22 @@
         <v>30</v>
       </c>
       <c r="C16" s="91" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D16" s="82" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E16" s="83" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F16" s="84" t="s">
+        <v>419</v>
+      </c>
+      <c r="G16" s="87" t="s">
+        <v>531</v>
+      </c>
+      <c r="H16" s="82" t="s">
         <v>420</v>
-      </c>
-      <c r="G16" s="87" t="s">
-        <v>534</v>
-      </c>
-      <c r="H16" s="82" t="s">
-        <v>421</v>
       </c>
       <c r="I16" s="81" t="s">
         <v>10</v>
@@ -3700,16 +3750,16 @@
       <c r="C18" s="83"/>
       <c r="D18" s="82"/>
       <c r="E18" s="83" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F18" s="84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G18" s="87" t="s">
         <v>242</v>
       </c>
       <c r="H18" s="82" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I18" s="81" t="s">
         <v>8</v>
@@ -3739,13 +3789,17 @@
       </c>
       <c r="C19" s="88"/>
       <c r="D19" s="82"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="84"/>
+      <c r="E19" s="83" t="s">
+        <v>565</v>
+      </c>
+      <c r="F19" s="191" t="s">
+        <v>564</v>
+      </c>
       <c r="G19" s="83" t="s">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="H19" s="82" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="I19" s="81" t="s">
         <v>7</v>
@@ -3759,11 +3813,11 @@
       </c>
       <c r="L19" s="85" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>17:32</v>
       </c>
       <c r="M19" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>17:57_?</v>
+        <v>17:57</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="18" customHeight="1">
@@ -3807,13 +3861,17 @@
       </c>
       <c r="C21" s="83"/>
       <c r="D21" s="82"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="84"/>
+      <c r="E21" s="83" t="s">
+        <v>563</v>
+      </c>
+      <c r="F21" s="191" t="s">
+        <v>564</v>
+      </c>
       <c r="G21" s="87" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H21" s="82" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I21" s="81" t="s">
         <v>5</v>
@@ -3827,7 +3885,7 @@
       </c>
       <c r="L21" s="85" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>19:04</v>
       </c>
       <c r="M21" s="85" t="str">
         <f t="shared" si="2"/>
@@ -3842,22 +3900,22 @@
         <v>30</v>
       </c>
       <c r="C22" s="83" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D22" s="82" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E22" s="83" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F22" s="84" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G22" s="83" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H22" s="82" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I22" s="81" t="s">
         <v>4</v>
@@ -3891,7 +3949,7 @@
         <v>347</v>
       </c>
       <c r="F23" s="84" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G23" s="83"/>
       <c r="H23" s="82"/>
@@ -3929,7 +3987,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="82" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I24" s="81" t="s">
         <v>2</v>
@@ -3963,13 +4021,13 @@
         <v>350</v>
       </c>
       <c r="F25" s="95" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G25" s="94" t="s">
         <v>380</v>
       </c>
       <c r="H25" s="93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I25" s="92" t="s">
         <v>1</v>
@@ -3998,22 +4056,22 @@
         <v>29</v>
       </c>
       <c r="C26" s="98" t="s">
+        <v>500</v>
+      </c>
+      <c r="D26" s="97" t="s">
         <v>501</v>
-      </c>
-      <c r="D26" s="97" t="s">
-        <v>502</v>
       </c>
       <c r="E26" s="98" t="s">
         <v>57</v>
       </c>
       <c r="F26" s="99" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G26" s="98" t="s">
         <v>48</v>
       </c>
       <c r="H26" s="97" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I26" s="96" t="s">
         <v>24</v>
@@ -4047,7 +4105,7 @@
         <v>53</v>
       </c>
       <c r="F27" s="103" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G27" s="102"/>
       <c r="H27" s="100"/>
@@ -4083,13 +4141,13 @@
         <v>105</v>
       </c>
       <c r="F28" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G28" s="102" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H28" s="100" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I28" s="96" t="s">
         <v>22</v>
@@ -4121,11 +4179,11 @@
       <c r="D29" s="100"/>
       <c r="E29" s="102"/>
       <c r="F29" s="103"/>
-      <c r="G29" s="107" t="s">
-        <v>524</v>
+      <c r="G29" s="106" t="s">
+        <v>559</v>
       </c>
       <c r="H29" s="100" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I29" s="96" t="s">
         <v>21</v>
@@ -4143,7 +4201,7 @@
       </c>
       <c r="M29" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>03:53_?</v>
+        <v>03:51</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="18" customHeight="1">
@@ -4153,13 +4211,13 @@
       <c r="B30" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="105"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="100"/>
       <c r="E30" s="102" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="F30" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G30" s="102"/>
       <c r="H30" s="100"/>
@@ -4192,16 +4250,16 @@
       <c r="C31" s="102"/>
       <c r="D31" s="100"/>
       <c r="E31" s="102" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="F31" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G31" s="102" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="H31" s="100" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I31" s="96" t="s">
         <v>19</v>
@@ -4219,7 +4277,7 @@
       </c>
       <c r="M31" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>05:28_?</v>
+        <v>05:26</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="18" customHeight="1">
@@ -4233,8 +4291,12 @@
       <c r="D32" s="100"/>
       <c r="E32" s="102"/>
       <c r="F32" s="103"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="100"/>
+      <c r="G32" s="106" t="s">
+        <v>561</v>
+      </c>
+      <c r="H32" s="100" t="s">
+        <v>523</v>
+      </c>
       <c r="I32" s="96" t="s">
         <v>18</v>
       </c>
@@ -4251,7 +4313,7 @@
       </c>
       <c r="M32" s="85" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>06_54</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1">
@@ -4261,20 +4323,16 @@
       <c r="B33" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="106"/>
+      <c r="C33" s="105"/>
       <c r="D33" s="100"/>
       <c r="E33" s="102" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F33" s="103" t="s">
-        <v>419</v>
-      </c>
-      <c r="G33" s="102" t="s">
-        <v>542</v>
-      </c>
-      <c r="H33" s="100" t="s">
-        <v>525</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="G33" s="102"/>
+      <c r="H33" s="100"/>
       <c r="I33" s="96" t="s">
         <v>17</v>
       </c>
@@ -4291,7 +4349,7 @@
       </c>
       <c r="M33" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>07:05_?</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1">
@@ -4301,19 +4359,23 @@
       <c r="B34" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="105"/>
-      <c r="D34" s="100"/>
+      <c r="C34" s="102" t="s">
+        <v>555</v>
+      </c>
+      <c r="D34" s="190" t="s">
+        <v>556</v>
+      </c>
       <c r="E34" s="102" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F34" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G34" s="102" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="H34" s="100" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I34" s="96" t="s">
         <v>16</v>
@@ -4323,15 +4385,15 @@
       </c>
       <c r="K34" s="85" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>08:05</v>
       </c>
       <c r="L34" s="85" t="str">
         <f t="shared" si="1"/>
-        <v>08:40_?</v>
+        <v>08:48</v>
       </c>
       <c r="M34" s="85" t="str">
         <f t="shared" si="2"/>
-        <v>08:29_?</v>
+        <v>08:24</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="18" customHeight="1">
@@ -4345,11 +4407,11 @@
       <c r="D35" s="100"/>
       <c r="E35" s="102"/>
       <c r="F35" s="103"/>
-      <c r="G35" s="107" t="s">
+      <c r="G35" s="106" t="s">
         <v>389</v>
       </c>
       <c r="H35" s="100" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I35" s="96" t="s">
         <v>15</v>
@@ -4383,7 +4445,7 @@
         <v>240</v>
       </c>
       <c r="F36" s="103" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G36" s="102"/>
       <c r="H36" s="100"/>
@@ -4414,22 +4476,22 @@
         <v>29</v>
       </c>
       <c r="C37" s="102" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D37" s="100" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E37" s="102" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F37" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G37" s="102" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H37" s="100" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I37" s="96" t="s">
         <v>13</v>
@@ -4461,11 +4523,11 @@
       <c r="D38" s="100"/>
       <c r="E38" s="102"/>
       <c r="F38" s="103"/>
-      <c r="G38" s="190" t="s">
-        <v>556</v>
+      <c r="G38" s="188" t="s">
+        <v>548</v>
       </c>
       <c r="H38" s="100" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I38" s="96" t="s">
         <v>12</v>
@@ -4496,10 +4558,10 @@
       <c r="C39" s="102"/>
       <c r="D39" s="100"/>
       <c r="E39" s="102" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F39" s="103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G39" s="102"/>
       <c r="H39" s="100"/>
@@ -4532,16 +4594,16 @@
       <c r="C40" s="101"/>
       <c r="D40" s="100"/>
       <c r="E40" s="102" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F40" s="103" t="s">
-        <v>420</v>
+        <v>568</v>
       </c>
       <c r="G40" s="102" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="H40" s="100" t="s">
-        <v>421</v>
+        <v>567</v>
       </c>
       <c r="I40" s="96" t="s">
         <v>10</v>
@@ -4570,18 +4632,18 @@
         <v>29</v>
       </c>
       <c r="C41" s="102" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D41" s="100" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E41" s="102"/>
       <c r="F41" s="103"/>
       <c r="G41" s="102" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="H41" s="100" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="I41" s="96" t="s">
         <v>9</v>
@@ -4613,7 +4675,7 @@
       <c r="D42" s="100"/>
       <c r="E42" s="102"/>
       <c r="F42" s="103"/>
-      <c r="G42" s="107"/>
+      <c r="G42" s="106"/>
       <c r="H42" s="100"/>
       <c r="I42" s="96" t="s">
         <v>8</v>
@@ -4645,8 +4707,12 @@
       <c r="D43" s="100"/>
       <c r="E43" s="102"/>
       <c r="F43" s="103"/>
-      <c r="G43" s="102"/>
-      <c r="H43" s="100"/>
+      <c r="G43" s="102" t="s">
+        <v>570</v>
+      </c>
+      <c r="H43" s="100" t="s">
+        <v>567</v>
+      </c>
       <c r="I43" s="96" t="s">
         <v>7</v>
       </c>
@@ -4663,7 +4729,7 @@
       </c>
       <c r="M43" s="85" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>17:15</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="18" customHeight="1">
@@ -4675,10 +4741,18 @@
       </c>
       <c r="C44" s="102"/>
       <c r="D44" s="100"/>
-      <c r="E44" s="101"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="100"/>
+      <c r="E44" s="105" t="s">
+        <v>569</v>
+      </c>
+      <c r="F44" s="103" t="s">
+        <v>568</v>
+      </c>
+      <c r="G44" s="188" t="s">
+        <v>571</v>
+      </c>
+      <c r="H44" s="100" t="s">
+        <v>567</v>
+      </c>
       <c r="I44" s="96" t="s">
         <v>6</v>
       </c>
@@ -4691,11 +4765,11 @@
       </c>
       <c r="L44" s="85" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>18:42_?</v>
       </c>
       <c r="M44" s="85" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>18:43</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="18" customHeight="1">
@@ -4707,8 +4781,12 @@
       </c>
       <c r="C45" s="102"/>
       <c r="D45" s="100"/>
-      <c r="E45" s="102"/>
-      <c r="F45" s="103"/>
+      <c r="E45" s="102" t="s">
+        <v>572</v>
+      </c>
+      <c r="F45" s="103" t="s">
+        <v>568</v>
+      </c>
       <c r="G45" s="102"/>
       <c r="H45" s="100"/>
       <c r="I45" s="96" t="s">
@@ -4723,7 +4801,7 @@
       </c>
       <c r="L45" s="85" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>19:08</v>
       </c>
       <c r="M45" s="85" t="str">
         <f t="shared" si="2"/>
@@ -4740,16 +4818,16 @@
       <c r="C46" s="102"/>
       <c r="D46" s="100"/>
       <c r="E46" s="102" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="F46" s="103" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G46" s="102" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="H46" s="100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I46" s="96" t="s">
         <v>4</v>
@@ -4779,13 +4857,13 @@
       </c>
       <c r="C47" s="102"/>
       <c r="D47" s="100"/>
-      <c r="E47" s="105"/>
+      <c r="E47" s="104"/>
       <c r="F47" s="103"/>
       <c r="G47" s="102" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="H47" s="100" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I47" s="96" t="s">
         <v>3</v>
@@ -4814,18 +4892,18 @@
         <v>29</v>
       </c>
       <c r="C48" s="102" t="s">
+        <v>493</v>
+      </c>
+      <c r="D48" s="100" t="s">
         <v>494</v>
-      </c>
-      <c r="D48" s="100" t="s">
-        <v>495</v>
       </c>
       <c r="E48" s="102" t="s">
         <v>130</v>
       </c>
       <c r="F48" s="103" t="s">
-        <v>420</v>
-      </c>
-      <c r="G48" s="107"/>
+        <v>419</v>
+      </c>
+      <c r="G48" s="106"/>
       <c r="H48" s="100"/>
       <c r="I48" s="96" t="s">
         <v>2</v>
@@ -4847,30 +4925,30 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickBot="1">
-      <c r="A49" s="109" t="s">
+      <c r="A49" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="110" t="s">
+      <c r="B49" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C49" s="111"/>
-      <c r="D49" s="110"/>
-      <c r="E49" s="112" t="s">
-        <v>552</v>
-      </c>
-      <c r="F49" s="113" t="s">
-        <v>419</v>
-      </c>
-      <c r="G49" s="112" t="s">
-        <v>553</v>
-      </c>
-      <c r="H49" s="110" t="s">
-        <v>423</v>
-      </c>
-      <c r="I49" s="109" t="s">
+      <c r="C49" s="109"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="110" t="s">
+        <v>545</v>
+      </c>
+      <c r="F49" s="111" t="s">
+        <v>418</v>
+      </c>
+      <c r="G49" s="110" t="s">
+        <v>546</v>
+      </c>
+      <c r="H49" s="108" t="s">
+        <v>422</v>
+      </c>
+      <c r="I49" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="J49" s="110" t="s">
+      <c r="J49" s="108" t="s">
         <v>29</v>
       </c>
       <c r="K49" s="85" t="str">
@@ -4887,26 +4965,26 @@
       </c>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1">
-      <c r="A50" s="114" t="s">
+      <c r="A50" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="B50" s="115" t="s">
+      <c r="B50" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="C50" s="116"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="116"/>
-      <c r="F50" s="117"/>
-      <c r="G50" s="116" t="s">
-        <v>479</v>
-      </c>
-      <c r="H50" s="115" t="s">
-        <v>523</v>
-      </c>
-      <c r="I50" s="114" t="s">
+      <c r="C50" s="114"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="114"/>
+      <c r="F50" s="115"/>
+      <c r="G50" s="114" t="s">
+        <v>478</v>
+      </c>
+      <c r="H50" s="113" t="s">
+        <v>522</v>
+      </c>
+      <c r="I50" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="115" t="s">
+      <c r="J50" s="113" t="s">
         <v>28</v>
       </c>
       <c r="K50" s="85" t="str">
@@ -4923,30 +5001,30 @@
       </c>
     </row>
     <row r="51" spans="1:18" ht="18" customHeight="1">
-      <c r="A51" s="114" t="s">
+      <c r="A51" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="B51" s="118" t="s">
+      <c r="B51" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="119"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="119" t="s">
-        <v>483</v>
-      </c>
-      <c r="F51" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G51" s="119" t="s">
-        <v>480</v>
-      </c>
-      <c r="H51" s="118" t="s">
-        <v>423</v>
-      </c>
-      <c r="I51" s="114" t="s">
+      <c r="C51" s="117"/>
+      <c r="D51" s="116"/>
+      <c r="E51" s="117" t="s">
+        <v>482</v>
+      </c>
+      <c r="F51" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G51" s="117" t="s">
+        <v>479</v>
+      </c>
+      <c r="H51" s="116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I51" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="J51" s="118" t="s">
+      <c r="J51" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K51" s="85" t="str">
@@ -4963,30 +5041,30 @@
       </c>
     </row>
     <row r="52" spans="1:18" ht="18" customHeight="1">
-      <c r="A52" s="114" t="s">
+      <c r="A52" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="B52" s="118" t="s">
+      <c r="B52" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C52" s="121" t="s">
+      <c r="C52" s="119" t="s">
+        <v>491</v>
+      </c>
+      <c r="D52" s="120" t="s">
         <v>492</v>
       </c>
-      <c r="D52" s="122" t="s">
-        <v>493</v>
-      </c>
-      <c r="E52" s="121" t="s">
-        <v>484</v>
-      </c>
-      <c r="F52" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G52" s="121"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="114" t="s">
+      <c r="E52" s="119" t="s">
+        <v>483</v>
+      </c>
+      <c r="F52" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G52" s="119"/>
+      <c r="H52" s="116"/>
+      <c r="I52" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="J52" s="118" t="s">
+      <c r="J52" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="85" t="str">
@@ -5003,26 +5081,26 @@
       </c>
     </row>
     <row r="53" spans="1:18" ht="18" customHeight="1">
-      <c r="A53" s="114" t="s">
+      <c r="A53" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="118" t="s">
+      <c r="B53" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C53" s="119"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="119" t="s">
-        <v>481</v>
-      </c>
-      <c r="H53" s="118" t="s">
-        <v>424</v>
-      </c>
-      <c r="I53" s="114" t="s">
+      <c r="C53" s="117"/>
+      <c r="D53" s="116"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="118"/>
+      <c r="G53" s="117" t="s">
+        <v>480</v>
+      </c>
+      <c r="H53" s="116" t="s">
+        <v>423</v>
+      </c>
+      <c r="I53" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="J53" s="118" t="s">
+      <c r="J53" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K53" s="85" t="str">
@@ -5039,30 +5117,30 @@
       </c>
     </row>
     <row r="54" spans="1:18" ht="18" customHeight="1">
-      <c r="A54" s="114" t="s">
+      <c r="A54" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B54" s="118" t="s">
+      <c r="B54" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="119"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="119" t="s">
-        <v>486</v>
-      </c>
-      <c r="F54" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G54" s="119" t="s">
-        <v>482</v>
-      </c>
-      <c r="H54" s="118" t="s">
-        <v>424</v>
-      </c>
-      <c r="I54" s="114" t="s">
+      <c r="C54" s="117"/>
+      <c r="D54" s="116"/>
+      <c r="E54" s="117" t="s">
+        <v>485</v>
+      </c>
+      <c r="F54" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G54" s="117" t="s">
+        <v>481</v>
+      </c>
+      <c r="H54" s="116" t="s">
+        <v>423</v>
+      </c>
+      <c r="I54" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="J54" s="118" t="s">
+      <c r="J54" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K54" s="85" t="str">
@@ -5079,26 +5157,26 @@
       </c>
     </row>
     <row r="55" spans="1:18" ht="18" customHeight="1">
-      <c r="A55" s="114" t="s">
+      <c r="A55" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="B55" s="118" t="s">
+      <c r="B55" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C55" s="119"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="119" t="s">
-        <v>487</v>
-      </c>
-      <c r="F55" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G55" s="119"/>
-      <c r="H55" s="118"/>
-      <c r="I55" s="114" t="s">
+      <c r="C55" s="117"/>
+      <c r="D55" s="116"/>
+      <c r="E55" s="117" t="s">
+        <v>486</v>
+      </c>
+      <c r="F55" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G55" s="117"/>
+      <c r="H55" s="116"/>
+      <c r="I55" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="J55" s="118" t="s">
+      <c r="J55" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K55" s="85" t="str">
@@ -5115,34 +5193,34 @@
       </c>
     </row>
     <row r="56" spans="1:18" ht="18" customHeight="1">
-      <c r="A56" s="114" t="s">
+      <c r="A56" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="B56" s="118" t="s">
+      <c r="B56" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C56" s="119" t="s">
+      <c r="C56" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D56" s="118" t="s">
-        <v>513</v>
-      </c>
-      <c r="E56" s="119" t="s">
+      <c r="D56" s="116" t="s">
+        <v>512</v>
+      </c>
+      <c r="E56" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F56" s="120" t="s">
+      <c r="F56" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="G56" s="123" t="s">
+      <c r="G56" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="H56" s="118" t="s">
+      <c r="H56" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="I56" s="114" t="s">
+      <c r="I56" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="J56" s="118" t="s">
+      <c r="J56" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K56" s="85" t="str">
@@ -5159,34 +5237,34 @@
       </c>
     </row>
     <row r="57" spans="1:18" ht="18" customHeight="1">
-      <c r="A57" s="114" t="s">
+      <c r="A57" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="118" t="s">
+      <c r="B57" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="119" t="s">
+      <c r="C57" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="D57" s="118" t="s">
+      <c r="D57" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="E57" s="123" t="s">
+      <c r="E57" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="F57" s="120" t="s">
+      <c r="F57" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="G57" s="123" t="s">
+      <c r="G57" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="H57" s="118" t="s">
+      <c r="H57" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="I57" s="114" t="s">
+      <c r="I57" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="J57" s="118" t="s">
+      <c r="J57" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K57" s="85" t="str">
@@ -5203,34 +5281,34 @@
       </c>
     </row>
     <row r="58" spans="1:18" ht="18" customHeight="1">
-      <c r="A58" s="114" t="s">
+      <c r="A58" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="B58" s="118" t="s">
+      <c r="B58" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C58" s="119" t="s">
+      <c r="C58" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="D58" s="118" t="s">
+      <c r="D58" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="E58" s="123" t="s">
+      <c r="E58" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="120" t="s">
+      <c r="F58" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="G58" s="123" t="s">
+      <c r="G58" s="121" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="118" t="s">
+      <c r="H58" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="I58" s="114" t="s">
+      <c r="I58" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="J58" s="118" t="s">
+      <c r="J58" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K58" s="85" t="str">
@@ -5247,34 +5325,34 @@
       </c>
     </row>
     <row r="59" spans="1:18" ht="18" customHeight="1">
-      <c r="A59" s="114" t="s">
+      <c r="A59" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="118" t="s">
+      <c r="B59" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="119" t="s">
+      <c r="C59" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="118" t="s">
+      <c r="D59" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="E59" s="124" t="s">
-        <v>514</v>
-      </c>
-      <c r="F59" s="120" t="s">
+      <c r="E59" s="122" t="s">
+        <v>513</v>
+      </c>
+      <c r="F59" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="G59" s="119" t="s">
+      <c r="G59" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="118" t="s">
+      <c r="H59" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="I59" s="114" t="s">
+      <c r="I59" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="J59" s="118" t="s">
+      <c r="J59" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K59" s="85" t="str">
@@ -5293,7 +5371,7 @@
         <v>0.41597222222222224</v>
       </c>
       <c r="P59" s="85" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q59" s="85" t="s">
         <v>42</v>
@@ -5303,34 +5381,34 @@
       </c>
     </row>
     <row r="60" spans="1:18" ht="18" customHeight="1">
-      <c r="A60" s="114" t="s">
+      <c r="A60" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="B60" s="118" t="s">
+      <c r="B60" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C60" s="119" t="s">
+      <c r="C60" s="117" t="s">
         <v>331</v>
       </c>
-      <c r="D60" s="118" t="s">
+      <c r="D60" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="E60" s="119" t="s">
-        <v>476</v>
-      </c>
-      <c r="F60" s="120" t="s">
+      <c r="E60" s="117" t="s">
+        <v>475</v>
+      </c>
+      <c r="F60" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="G60" s="119" t="s">
-        <v>515</v>
-      </c>
-      <c r="H60" s="118" t="s">
+      <c r="G60" s="117" t="s">
+        <v>514</v>
+      </c>
+      <c r="H60" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="I60" s="114" t="s">
+      <c r="I60" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="J60" s="118" t="s">
+      <c r="J60" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K60" s="85" t="str">
@@ -5349,30 +5427,30 @@
         <v>332</v>
       </c>
       <c r="R60" s="85" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:18" ht="18" customHeight="1">
-      <c r="A61" s="114" t="s">
+      <c r="A61" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="B61" s="118" t="s">
+      <c r="B61" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C61" s="119"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="119" t="s">
+      <c r="C61" s="117"/>
+      <c r="D61" s="116"/>
+      <c r="E61" s="117" t="s">
         <v>333</v>
       </c>
-      <c r="F61" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G61" s="119"/>
-      <c r="H61" s="118"/>
-      <c r="I61" s="114" t="s">
+      <c r="F61" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G61" s="117"/>
+      <c r="H61" s="116"/>
+      <c r="I61" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="J61" s="118" t="s">
+      <c r="J61" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K61" s="85" t="str">
@@ -5389,34 +5467,34 @@
       </c>
     </row>
     <row r="62" spans="1:18" ht="18" customHeight="1">
-      <c r="A62" s="114" t="s">
+      <c r="A62" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="118" t="s">
+      <c r="B62" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C62" s="119" t="s">
+      <c r="C62" s="117" t="s">
         <v>334</v>
       </c>
-      <c r="D62" s="118" t="s">
-        <v>405</v>
-      </c>
-      <c r="E62" s="119" t="s">
+      <c r="D62" s="116" t="s">
+        <v>404</v>
+      </c>
+      <c r="E62" s="117" t="s">
         <v>335</v>
       </c>
-      <c r="F62" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G62" s="119" t="s">
+      <c r="F62" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G62" s="117" t="s">
         <v>336</v>
       </c>
-      <c r="H62" s="118" t="s">
-        <v>423</v>
-      </c>
-      <c r="I62" s="114" t="s">
+      <c r="H62" s="116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I62" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="J62" s="118" t="s">
+      <c r="J62" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K62" s="85" t="str">
@@ -5433,26 +5511,26 @@
       </c>
     </row>
     <row r="63" spans="1:18" ht="18" customHeight="1">
-      <c r="A63" s="114" t="s">
+      <c r="A63" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="B63" s="118" t="s">
+      <c r="B63" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C63" s="119"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="119"/>
-      <c r="F63" s="120"/>
-      <c r="G63" s="119" t="s">
+      <c r="C63" s="117"/>
+      <c r="D63" s="116"/>
+      <c r="E63" s="117"/>
+      <c r="F63" s="118"/>
+      <c r="G63" s="117" t="s">
         <v>337</v>
       </c>
-      <c r="H63" s="118" t="s">
-        <v>424</v>
-      </c>
-      <c r="I63" s="114" t="s">
+      <c r="H63" s="116" t="s">
+        <v>423</v>
+      </c>
+      <c r="I63" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="118" t="s">
+      <c r="J63" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K63" s="85" t="str">
@@ -5469,26 +5547,26 @@
       </c>
     </row>
     <row r="64" spans="1:18" ht="18" customHeight="1">
-      <c r="A64" s="114" t="s">
+      <c r="A64" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="B64" s="118" t="s">
+      <c r="B64" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="119"/>
-      <c r="D64" s="118"/>
-      <c r="E64" s="119" t="s">
+      <c r="C64" s="117"/>
+      <c r="D64" s="116"/>
+      <c r="E64" s="117" t="s">
         <v>338</v>
       </c>
-      <c r="F64" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G64" s="119"/>
-      <c r="H64" s="118"/>
-      <c r="I64" s="114" t="s">
+      <c r="F64" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G64" s="117"/>
+      <c r="H64" s="116"/>
+      <c r="I64" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="J64" s="118" t="s">
+      <c r="J64" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K64" s="85" t="str">
@@ -5505,34 +5583,34 @@
       </c>
     </row>
     <row r="65" spans="1:13" ht="18" customHeight="1">
-      <c r="A65" s="114" t="s">
+      <c r="A65" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="B65" s="118" t="s">
+      <c r="B65" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="125" t="s">
-        <v>516</v>
-      </c>
-      <c r="D65" s="118" t="s">
-        <v>406</v>
-      </c>
-      <c r="E65" s="119" t="s">
+      <c r="C65" s="123" t="s">
+        <v>515</v>
+      </c>
+      <c r="D65" s="116" t="s">
+        <v>405</v>
+      </c>
+      <c r="E65" s="117" t="s">
         <v>254</v>
       </c>
-      <c r="F65" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G65" s="121" t="s">
+      <c r="F65" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G65" s="119" t="s">
         <v>339</v>
       </c>
-      <c r="H65" s="118" t="s">
-        <v>421</v>
-      </c>
-      <c r="I65" s="114" t="s">
+      <c r="H65" s="116" t="s">
+        <v>420</v>
+      </c>
+      <c r="I65" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="J65" s="118" t="s">
+      <c r="J65" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K65" s="85" t="str">
@@ -5549,26 +5627,26 @@
       </c>
     </row>
     <row r="66" spans="1:13" ht="18" customHeight="1">
-      <c r="A66" s="114" t="s">
+      <c r="A66" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="B66" s="118" t="s">
+      <c r="B66" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C66" s="119"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="119"/>
-      <c r="F66" s="120"/>
-      <c r="G66" s="119" t="s">
+      <c r="C66" s="117"/>
+      <c r="D66" s="116"/>
+      <c r="E66" s="117"/>
+      <c r="F66" s="118"/>
+      <c r="G66" s="117" t="s">
         <v>340</v>
       </c>
-      <c r="H66" s="118" t="s">
-        <v>421</v>
-      </c>
-      <c r="I66" s="114" t="s">
+      <c r="H66" s="116" t="s">
+        <v>420</v>
+      </c>
+      <c r="I66" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="118" t="s">
+      <c r="J66" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K66" s="85" t="str">
@@ -5585,26 +5663,26 @@
       </c>
     </row>
     <row r="67" spans="1:13" ht="18" customHeight="1">
-      <c r="A67" s="114" t="s">
+      <c r="A67" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="B67" s="118" t="s">
+      <c r="B67" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C67" s="121"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="119" t="s">
+      <c r="C67" s="119"/>
+      <c r="D67" s="116"/>
+      <c r="E67" s="117" t="s">
         <v>341</v>
       </c>
-      <c r="F67" s="120" t="s">
-        <v>420</v>
-      </c>
-      <c r="G67" s="121"/>
-      <c r="H67" s="118"/>
-      <c r="I67" s="114" t="s">
+      <c r="F67" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="G67" s="119"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="J67" s="118" t="s">
+      <c r="J67" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K67" s="85" t="str">
@@ -5621,30 +5699,30 @@
       </c>
     </row>
     <row r="68" spans="1:13" ht="18" customHeight="1">
-      <c r="A68" s="114" t="s">
+      <c r="A68" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="B68" s="118" t="s">
+      <c r="B68" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="119"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="119" t="s">
+      <c r="C68" s="117"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="117" t="s">
         <v>342</v>
       </c>
-      <c r="F68" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G68" s="119" t="s">
+      <c r="F68" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G68" s="117" t="s">
         <v>343</v>
       </c>
-      <c r="H68" s="118" t="s">
-        <v>424</v>
-      </c>
-      <c r="I68" s="114" t="s">
+      <c r="H68" s="116" t="s">
+        <v>423</v>
+      </c>
+      <c r="I68" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="J68" s="118" t="s">
+      <c r="J68" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K68" s="85" t="str">
@@ -5661,30 +5739,30 @@
       </c>
     </row>
     <row r="69" spans="1:13" ht="18" customHeight="1">
-      <c r="A69" s="114" t="s">
+      <c r="A69" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="B69" s="118" t="s">
+      <c r="B69" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C69" s="119" t="s">
+      <c r="C69" s="117" t="s">
         <v>344</v>
       </c>
-      <c r="D69" s="118" t="s">
-        <v>407</v>
-      </c>
-      <c r="E69" s="119"/>
-      <c r="F69" s="120"/>
-      <c r="G69" s="119" t="s">
+      <c r="D69" s="116" t="s">
+        <v>406</v>
+      </c>
+      <c r="E69" s="117"/>
+      <c r="F69" s="118"/>
+      <c r="G69" s="117" t="s">
         <v>345</v>
       </c>
-      <c r="H69" s="118" t="s">
-        <v>423</v>
-      </c>
-      <c r="I69" s="114" t="s">
+      <c r="H69" s="116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I69" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="J69" s="118" t="s">
+      <c r="J69" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K69" s="85" t="str">
@@ -5701,26 +5779,26 @@
       </c>
     </row>
     <row r="70" spans="1:13" ht="18" customHeight="1">
-      <c r="A70" s="114" t="s">
+      <c r="A70" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="B70" s="118" t="s">
+      <c r="B70" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="119"/>
-      <c r="D70" s="122"/>
-      <c r="E70" s="119" t="s">
+      <c r="C70" s="117"/>
+      <c r="D70" s="120"/>
+      <c r="E70" s="117" t="s">
         <v>346</v>
       </c>
-      <c r="F70" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G70" s="121"/>
-      <c r="H70" s="118"/>
-      <c r="I70" s="114" t="s">
+      <c r="F70" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G70" s="119"/>
+      <c r="H70" s="116"/>
+      <c r="I70" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="J70" s="118" t="s">
+      <c r="J70" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K70" s="85" t="str">
@@ -5737,30 +5815,30 @@
       </c>
     </row>
     <row r="71" spans="1:13" ht="18" customHeight="1">
-      <c r="A71" s="114" t="s">
+      <c r="A71" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="B71" s="118" t="s">
+      <c r="B71" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="119"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="119" t="s">
+      <c r="C71" s="117"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="117" t="s">
         <v>347</v>
       </c>
-      <c r="F71" s="120" t="s">
-        <v>419</v>
-      </c>
-      <c r="G71" s="119" t="s">
+      <c r="F71" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="G71" s="117" t="s">
         <v>348</v>
       </c>
-      <c r="H71" s="118" t="s">
-        <v>423</v>
-      </c>
-      <c r="I71" s="114" t="s">
+      <c r="H71" s="116" t="s">
+        <v>422</v>
+      </c>
+      <c r="I71" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="J71" s="118" t="s">
+      <c r="J71" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K71" s="85" t="str">
@@ -5777,26 +5855,26 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1">
-      <c r="A72" s="114" t="s">
+      <c r="A72" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="B72" s="118" t="s">
+      <c r="B72" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="119"/>
-      <c r="D72" s="118"/>
-      <c r="E72" s="119"/>
-      <c r="F72" s="120"/>
-      <c r="G72" s="119" t="s">
+      <c r="C72" s="117"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="117"/>
+      <c r="F72" s="118"/>
+      <c r="G72" s="117" t="s">
         <v>349</v>
       </c>
-      <c r="H72" s="118" t="s">
-        <v>424</v>
-      </c>
-      <c r="I72" s="114" t="s">
+      <c r="H72" s="116" t="s">
+        <v>423</v>
+      </c>
+      <c r="I72" s="112" t="s">
         <v>2</v>
       </c>
-      <c r="J72" s="118" t="s">
+      <c r="J72" s="116" t="s">
         <v>28</v>
       </c>
       <c r="K72" s="85" t="str">
@@ -5813,26 +5891,26 @@
       </c>
     </row>
     <row r="73" spans="1:13" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="126" t="s">
+      <c r="A73" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="B73" s="127" t="s">
+      <c r="B73" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="C73" s="128"/>
-      <c r="D73" s="127"/>
-      <c r="E73" s="128" t="s">
+      <c r="C73" s="126"/>
+      <c r="D73" s="125"/>
+      <c r="E73" s="126" t="s">
         <v>350</v>
       </c>
-      <c r="F73" s="129" t="s">
-        <v>419</v>
-      </c>
-      <c r="G73" s="128"/>
-      <c r="H73" s="127"/>
-      <c r="I73" s="126" t="s">
+      <c r="F73" s="127" t="s">
+        <v>418</v>
+      </c>
+      <c r="G73" s="126"/>
+      <c r="H73" s="125"/>
+      <c r="I73" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="J73" s="127" t="s">
+      <c r="J73" s="125" t="s">
         <v>28</v>
       </c>
       <c r="K73" s="85" t="str">
@@ -5849,34 +5927,34 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="18" customHeight="1">
-      <c r="A74" s="130" t="s">
+      <c r="A74" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B74" s="131" t="s">
+      <c r="B74" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="132" t="s">
+      <c r="C74" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="D74" s="131" t="s">
-        <v>497</v>
-      </c>
-      <c r="E74" s="132" t="s">
+      <c r="D74" s="129" t="s">
+        <v>496</v>
+      </c>
+      <c r="E74" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F74" s="133" t="s">
-        <v>420</v>
-      </c>
-      <c r="G74" s="132" t="s">
+      <c r="F74" s="131" t="s">
+        <v>419</v>
+      </c>
+      <c r="G74" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="H74" s="131" t="s">
-        <v>424</v>
-      </c>
-      <c r="I74" s="130" t="s">
+      <c r="H74" s="129" t="s">
+        <v>423</v>
+      </c>
+      <c r="I74" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="J74" s="131" t="s">
+      <c r="J74" s="129" t="s">
         <v>27</v>
       </c>
       <c r="K74" s="85" t="str">
@@ -5893,30 +5971,30 @@
       </c>
     </row>
     <row r="75" spans="1:13" ht="18" customHeight="1">
-      <c r="A75" s="130" t="s">
+      <c r="A75" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="B75" s="134" t="s">
+      <c r="B75" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C75" s="135"/>
-      <c r="D75" s="134"/>
-      <c r="E75" s="135" t="s">
+      <c r="C75" s="133"/>
+      <c r="D75" s="132"/>
+      <c r="E75" s="133" t="s">
         <v>132</v>
       </c>
-      <c r="F75" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G75" s="135" t="s">
+      <c r="F75" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G75" s="133" t="s">
         <v>351</v>
       </c>
-      <c r="H75" s="134" t="s">
-        <v>424</v>
-      </c>
-      <c r="I75" s="130" t="s">
+      <c r="H75" s="132" t="s">
+        <v>423</v>
+      </c>
+      <c r="I75" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="J75" s="134" t="s">
+      <c r="J75" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K75" s="85" t="str">
@@ -5933,26 +6011,26 @@
       </c>
     </row>
     <row r="76" spans="1:13" ht="18" customHeight="1">
-      <c r="A76" s="130" t="s">
+      <c r="A76" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="B76" s="134" t="s">
+      <c r="B76" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="135"/>
-      <c r="D76" s="134"/>
-      <c r="E76" s="135"/>
-      <c r="F76" s="136"/>
-      <c r="G76" s="137" t="s">
+      <c r="C76" s="133"/>
+      <c r="D76" s="132"/>
+      <c r="E76" s="133"/>
+      <c r="F76" s="134"/>
+      <c r="G76" s="135" t="s">
         <v>352</v>
       </c>
-      <c r="H76" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I76" s="130" t="s">
+      <c r="H76" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I76" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="J76" s="134" t="s">
+      <c r="J76" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K76" s="85" t="str">
@@ -5969,30 +6047,30 @@
       </c>
     </row>
     <row r="77" spans="1:13" ht="18" customHeight="1">
-      <c r="A77" s="130" t="s">
+      <c r="A77" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="B77" s="134" t="s">
+      <c r="B77" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C77" s="135" t="s">
+      <c r="C77" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="D77" s="134" t="s">
-        <v>405</v>
-      </c>
-      <c r="E77" s="135" t="s">
+      <c r="D77" s="132" t="s">
+        <v>404</v>
+      </c>
+      <c r="E77" s="133" t="s">
         <v>354</v>
       </c>
-      <c r="F77" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G77" s="138"/>
-      <c r="H77" s="134"/>
-      <c r="I77" s="130" t="s">
+      <c r="F77" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G77" s="136"/>
+      <c r="H77" s="132"/>
+      <c r="I77" s="128" t="s">
         <v>21</v>
       </c>
-      <c r="J77" s="134" t="s">
+      <c r="J77" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K77" s="85" t="str">
@@ -6009,30 +6087,30 @@
       </c>
     </row>
     <row r="78" spans="1:13" ht="18" customHeight="1">
-      <c r="A78" s="130" t="s">
+      <c r="A78" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="B78" s="134" t="s">
+      <c r="B78" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C78" s="135"/>
-      <c r="D78" s="134"/>
-      <c r="E78" s="135" t="s">
+      <c r="C78" s="133"/>
+      <c r="D78" s="132"/>
+      <c r="E78" s="133" t="s">
         <v>355</v>
       </c>
-      <c r="F78" s="136" t="s">
+      <c r="F78" s="134" t="s">
+        <v>419</v>
+      </c>
+      <c r="G78" s="133" t="s">
+        <v>356</v>
+      </c>
+      <c r="H78" s="132" t="s">
         <v>420</v>
       </c>
-      <c r="G78" s="135" t="s">
-        <v>356</v>
-      </c>
-      <c r="H78" s="134" t="s">
-        <v>421</v>
-      </c>
-      <c r="I78" s="130" t="s">
+      <c r="I78" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="J78" s="134" t="s">
+      <c r="J78" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K78" s="85" t="str">
@@ -6049,34 +6127,34 @@
       </c>
     </row>
     <row r="79" spans="1:13" ht="18" customHeight="1">
-      <c r="A79" s="130" t="s">
+      <c r="A79" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="B79" s="134" t="s">
+      <c r="B79" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C79" s="135" t="s">
+      <c r="C79" s="133" t="s">
         <v>357</v>
       </c>
-      <c r="D79" s="134" t="s">
-        <v>408</v>
-      </c>
-      <c r="E79" s="135" t="s">
+      <c r="D79" s="132" t="s">
+        <v>407</v>
+      </c>
+      <c r="E79" s="133" t="s">
         <v>358</v>
       </c>
-      <c r="F79" s="136" t="s">
-        <v>420</v>
-      </c>
-      <c r="G79" s="135" t="s">
+      <c r="F79" s="134" t="s">
+        <v>419</v>
+      </c>
+      <c r="G79" s="133" t="s">
         <v>358</v>
       </c>
-      <c r="H79" s="134" t="s">
-        <v>424</v>
-      </c>
-      <c r="I79" s="130" t="s">
+      <c r="H79" s="132" t="s">
+        <v>423</v>
+      </c>
+      <c r="I79" s="128" t="s">
         <v>19</v>
       </c>
-      <c r="J79" s="134" t="s">
+      <c r="J79" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K79" s="85" t="str">
@@ -6093,22 +6171,22 @@
       </c>
     </row>
     <row r="80" spans="1:13" ht="18" customHeight="1">
-      <c r="A80" s="130" t="s">
+      <c r="A80" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="B80" s="134" t="s">
+      <c r="B80" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C80" s="135"/>
-      <c r="D80" s="134"/>
-      <c r="E80" s="135"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="137"/>
-      <c r="H80" s="134"/>
-      <c r="I80" s="130" t="s">
+      <c r="C80" s="133"/>
+      <c r="D80" s="132"/>
+      <c r="E80" s="133"/>
+      <c r="F80" s="134"/>
+      <c r="G80" s="135"/>
+      <c r="H80" s="132"/>
+      <c r="I80" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="J80" s="134" t="s">
+      <c r="J80" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K80" s="85" t="str">
@@ -6125,30 +6203,30 @@
       </c>
     </row>
     <row r="81" spans="1:13" ht="18" customHeight="1">
-      <c r="A81" s="130" t="s">
+      <c r="A81" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="B81" s="134" t="s">
+      <c r="B81" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C81" s="135"/>
-      <c r="D81" s="134"/>
-      <c r="E81" s="135" t="s">
+      <c r="C81" s="133"/>
+      <c r="D81" s="132"/>
+      <c r="E81" s="133" t="s">
         <v>359</v>
       </c>
-      <c r="F81" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G81" s="135" t="s">
+      <c r="F81" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G81" s="133" t="s">
         <v>360</v>
       </c>
-      <c r="H81" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I81" s="130" t="s">
+      <c r="H81" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I81" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="J81" s="134" t="s">
+      <c r="J81" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K81" s="85" t="str">
@@ -6165,30 +6243,30 @@
       </c>
     </row>
     <row r="82" spans="1:13" ht="18" customHeight="1">
-      <c r="A82" s="130" t="s">
+      <c r="A82" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="B82" s="134" t="s">
+      <c r="B82" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C82" s="135" t="s">
+      <c r="C82" s="133" t="s">
         <v>361</v>
       </c>
-      <c r="D82" s="134" t="s">
-        <v>407</v>
-      </c>
-      <c r="E82" s="135"/>
-      <c r="F82" s="136"/>
-      <c r="G82" s="135" t="s">
-        <v>517</v>
-      </c>
-      <c r="H82" s="134" t="s">
-        <v>422</v>
-      </c>
-      <c r="I82" s="130" t="s">
+      <c r="D82" s="132" t="s">
+        <v>406</v>
+      </c>
+      <c r="E82" s="133"/>
+      <c r="F82" s="134"/>
+      <c r="G82" s="133" t="s">
+        <v>516</v>
+      </c>
+      <c r="H82" s="132" t="s">
+        <v>421</v>
+      </c>
+      <c r="I82" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="J82" s="134" t="s">
+      <c r="J82" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K82" s="85" t="str">
@@ -6205,26 +6283,26 @@
       </c>
     </row>
     <row r="83" spans="1:13" ht="18" customHeight="1">
-      <c r="A83" s="130" t="s">
+      <c r="A83" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="B83" s="134" t="s">
+      <c r="B83" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C83" s="139"/>
-      <c r="D83" s="134"/>
-      <c r="E83" s="135" t="s">
+      <c r="C83" s="137"/>
+      <c r="D83" s="132"/>
+      <c r="E83" s="133" t="s">
         <v>363</v>
       </c>
-      <c r="F83" s="136" t="s">
-        <v>420</v>
-      </c>
-      <c r="G83" s="137"/>
-      <c r="H83" s="134"/>
-      <c r="I83" s="130" t="s">
+      <c r="F83" s="134" t="s">
+        <v>419</v>
+      </c>
+      <c r="G83" s="135"/>
+      <c r="H83" s="132"/>
+      <c r="I83" s="128" t="s">
         <v>15</v>
       </c>
-      <c r="J83" s="134" t="s">
+      <c r="J83" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K83" s="85" t="str">
@@ -6241,30 +6319,30 @@
       </c>
     </row>
     <row r="84" spans="1:13" ht="18" customHeight="1">
-      <c r="A84" s="130" t="s">
+      <c r="A84" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="B84" s="134" t="s">
+      <c r="B84" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C84" s="135"/>
-      <c r="D84" s="134"/>
-      <c r="E84" s="135" t="s">
+      <c r="C84" s="133"/>
+      <c r="D84" s="132"/>
+      <c r="E84" s="133" t="s">
         <v>364</v>
       </c>
-      <c r="F84" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G84" s="135" t="s">
+      <c r="F84" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G84" s="133" t="s">
         <v>365</v>
       </c>
-      <c r="H84" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I84" s="130" t="s">
+      <c r="H84" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I84" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="J84" s="134" t="s">
+      <c r="J84" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K84" s="85" t="str">
@@ -6281,22 +6359,22 @@
       </c>
     </row>
     <row r="85" spans="1:13" ht="18" customHeight="1">
-      <c r="A85" s="130" t="s">
+      <c r="A85" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="B85" s="134" t="s">
+      <c r="B85" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C85" s="135"/>
-      <c r="D85" s="134"/>
-      <c r="E85" s="135"/>
-      <c r="F85" s="136"/>
-      <c r="G85" s="135"/>
-      <c r="H85" s="134"/>
-      <c r="I85" s="130" t="s">
+      <c r="C85" s="133"/>
+      <c r="D85" s="132"/>
+      <c r="E85" s="133"/>
+      <c r="F85" s="134"/>
+      <c r="G85" s="133"/>
+      <c r="H85" s="132"/>
+      <c r="I85" s="128" t="s">
         <v>13</v>
       </c>
-      <c r="J85" s="134" t="s">
+      <c r="J85" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K85" s="85" t="str">
@@ -6313,34 +6391,34 @@
       </c>
     </row>
     <row r="86" spans="1:13" ht="18" customHeight="1">
-      <c r="A86" s="130" t="s">
+      <c r="A86" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="B86" s="134" t="s">
+      <c r="B86" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C86" s="140" t="s">
-        <v>518</v>
-      </c>
-      <c r="D86" s="134" t="s">
-        <v>409</v>
-      </c>
-      <c r="E86" s="135" t="s">
+      <c r="C86" s="138" t="s">
+        <v>517</v>
+      </c>
+      <c r="D86" s="132" t="s">
+        <v>408</v>
+      </c>
+      <c r="E86" s="133" t="s">
         <v>366</v>
       </c>
-      <c r="F86" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G86" s="137" t="s">
+      <c r="F86" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G86" s="135" t="s">
         <v>367</v>
       </c>
-      <c r="H86" s="134" t="s">
-        <v>424</v>
-      </c>
-      <c r="I86" s="130" t="s">
+      <c r="H86" s="132" t="s">
+        <v>423</v>
+      </c>
+      <c r="I86" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="J86" s="134" t="s">
+      <c r="J86" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K86" s="85" t="str">
@@ -6357,30 +6435,30 @@
       </c>
     </row>
     <row r="87" spans="1:13" ht="18" customHeight="1">
-      <c r="A87" s="130" t="s">
+      <c r="A87" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="134" t="s">
+      <c r="B87" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C87" s="135"/>
-      <c r="D87" s="134"/>
-      <c r="E87" s="135" t="s">
+      <c r="C87" s="133"/>
+      <c r="D87" s="132"/>
+      <c r="E87" s="133" t="s">
         <v>368</v>
       </c>
-      <c r="F87" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G87" s="135" t="s">
+      <c r="F87" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G87" s="133" t="s">
         <v>369</v>
       </c>
-      <c r="H87" s="134" t="s">
-        <v>424</v>
-      </c>
-      <c r="I87" s="130" t="s">
+      <c r="H87" s="132" t="s">
+        <v>423</v>
+      </c>
+      <c r="I87" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="J87" s="134" t="s">
+      <c r="J87" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K87" s="85" t="str">
@@ -6397,26 +6475,26 @@
       </c>
     </row>
     <row r="88" spans="1:13" ht="18" customHeight="1">
-      <c r="A88" s="130" t="s">
+      <c r="A88" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="B88" s="134" t="s">
+      <c r="B88" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C88" s="135"/>
-      <c r="D88" s="134"/>
-      <c r="E88" s="135"/>
-      <c r="F88" s="136"/>
-      <c r="G88" s="135" t="s">
+      <c r="C88" s="133"/>
+      <c r="D88" s="132"/>
+      <c r="E88" s="133"/>
+      <c r="F88" s="134"/>
+      <c r="G88" s="133" t="s">
         <v>370</v>
       </c>
-      <c r="H88" s="134" t="s">
-        <v>424</v>
-      </c>
-      <c r="I88" s="130" t="s">
+      <c r="H88" s="132" t="s">
+        <v>423</v>
+      </c>
+      <c r="I88" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="J88" s="134" t="s">
+      <c r="J88" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K88" s="85" t="str">
@@ -6433,26 +6511,26 @@
       </c>
     </row>
     <row r="89" spans="1:13" ht="18" customHeight="1">
-      <c r="A89" s="130" t="s">
+      <c r="A89" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="134" t="s">
+      <c r="B89" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="135"/>
-      <c r="D89" s="134"/>
-      <c r="E89" s="135" t="s">
+      <c r="C89" s="133"/>
+      <c r="D89" s="132"/>
+      <c r="E89" s="133" t="s">
         <v>161</v>
       </c>
-      <c r="F89" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G89" s="137"/>
-      <c r="H89" s="134"/>
-      <c r="I89" s="130" t="s">
+      <c r="F89" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G89" s="135"/>
+      <c r="H89" s="132"/>
+      <c r="I89" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="J89" s="134" t="s">
+      <c r="J89" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K89" s="85" t="str">
@@ -6469,34 +6547,34 @@
       </c>
     </row>
     <row r="90" spans="1:13" ht="18" customHeight="1">
-      <c r="A90" s="130" t="s">
+      <c r="A90" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="B90" s="134" t="s">
+      <c r="B90" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C90" s="135" t="s">
+      <c r="C90" s="133" t="s">
+        <v>489</v>
+      </c>
+      <c r="D90" s="132" t="s">
         <v>490</v>
       </c>
-      <c r="D90" s="134" t="s">
-        <v>491</v>
-      </c>
-      <c r="E90" s="135" t="s">
+      <c r="E90" s="133" t="s">
         <v>371</v>
       </c>
-      <c r="F90" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G90" s="135" t="s">
+      <c r="F90" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G90" s="133" t="s">
         <v>242</v>
       </c>
-      <c r="H90" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I90" s="130" t="s">
+      <c r="H90" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I90" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="J90" s="134" t="s">
+      <c r="J90" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K90" s="85" t="str">
@@ -6513,26 +6591,26 @@
       </c>
     </row>
     <row r="91" spans="1:13" ht="18" customHeight="1">
-      <c r="A91" s="130" t="s">
+      <c r="A91" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="134" t="s">
+      <c r="B91" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C91" s="135"/>
-      <c r="D91" s="134"/>
-      <c r="E91" s="135"/>
-      <c r="F91" s="136"/>
-      <c r="G91" s="135" t="s">
+      <c r="C91" s="133"/>
+      <c r="D91" s="132"/>
+      <c r="E91" s="133"/>
+      <c r="F91" s="134"/>
+      <c r="G91" s="133" t="s">
         <v>372</v>
       </c>
-      <c r="H91" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I91" s="130" t="s">
+      <c r="H91" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I91" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="J91" s="134" t="s">
+      <c r="J91" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K91" s="85" t="str">
@@ -6549,26 +6627,26 @@
       </c>
     </row>
     <row r="92" spans="1:13" ht="18" customHeight="1">
-      <c r="A92" s="130" t="s">
+      <c r="A92" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="134" t="s">
+      <c r="B92" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C92" s="135"/>
-      <c r="D92" s="134"/>
-      <c r="E92" s="135" t="s">
+      <c r="C92" s="133"/>
+      <c r="D92" s="132"/>
+      <c r="E92" s="133" t="s">
         <v>374</v>
       </c>
-      <c r="F92" s="136" t="s">
-        <v>420</v>
-      </c>
-      <c r="G92" s="137"/>
-      <c r="H92" s="134"/>
-      <c r="I92" s="130" t="s">
+      <c r="F92" s="134" t="s">
+        <v>419</v>
+      </c>
+      <c r="G92" s="135"/>
+      <c r="H92" s="132"/>
+      <c r="I92" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="J92" s="134" t="s">
+      <c r="J92" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K92" s="85" t="str">
@@ -6585,34 +6663,34 @@
       </c>
     </row>
     <row r="93" spans="1:13" ht="18" customHeight="1">
-      <c r="A93" s="130" t="s">
+      <c r="A93" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="B93" s="134" t="s">
+      <c r="B93" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C93" s="139" t="s">
+      <c r="C93" s="137" t="s">
         <v>373</v>
       </c>
-      <c r="D93" s="134" t="s">
-        <v>410</v>
-      </c>
-      <c r="E93" s="135" t="s">
+      <c r="D93" s="132" t="s">
+        <v>409</v>
+      </c>
+      <c r="E93" s="133" t="s">
         <v>375</v>
       </c>
-      <c r="F93" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G93" s="135" t="s">
+      <c r="F93" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G93" s="133" t="s">
         <v>376</v>
       </c>
-      <c r="H93" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I93" s="130" t="s">
+      <c r="H93" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I93" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J93" s="134" t="s">
+      <c r="J93" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K93" s="85" t="str">
@@ -6629,26 +6707,26 @@
       </c>
     </row>
     <row r="94" spans="1:13" ht="18" customHeight="1">
-      <c r="A94" s="130" t="s">
+      <c r="A94" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B94" s="134" t="s">
+      <c r="B94" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C94" s="135"/>
-      <c r="D94" s="134"/>
-      <c r="E94" s="135"/>
-      <c r="F94" s="136"/>
-      <c r="G94" s="135" t="s">
+      <c r="C94" s="133"/>
+      <c r="D94" s="132"/>
+      <c r="E94" s="133"/>
+      <c r="F94" s="134"/>
+      <c r="G94" s="133" t="s">
         <v>377</v>
       </c>
-      <c r="H94" s="134" t="s">
-        <v>423</v>
-      </c>
-      <c r="I94" s="130" t="s">
+      <c r="H94" s="132" t="s">
+        <v>422</v>
+      </c>
+      <c r="I94" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="134" t="s">
+      <c r="J94" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K94" s="85" t="str">
@@ -6665,26 +6743,26 @@
       </c>
     </row>
     <row r="95" spans="1:13" ht="18" customHeight="1">
-      <c r="A95" s="130" t="s">
+      <c r="A95" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="B95" s="134" t="s">
+      <c r="B95" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C95" s="135"/>
-      <c r="D95" s="134"/>
-      <c r="E95" s="135" t="s">
+      <c r="C95" s="133"/>
+      <c r="D95" s="132"/>
+      <c r="E95" s="133" t="s">
         <v>378</v>
       </c>
-      <c r="F95" s="136" t="s">
-        <v>419</v>
-      </c>
-      <c r="G95" s="135"/>
-      <c r="H95" s="134"/>
-      <c r="I95" s="130" t="s">
+      <c r="F95" s="134" t="s">
+        <v>418</v>
+      </c>
+      <c r="G95" s="133"/>
+      <c r="H95" s="132"/>
+      <c r="I95" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="J95" s="134" t="s">
+      <c r="J95" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K95" s="85" t="str">
@@ -6701,30 +6779,30 @@
       </c>
     </row>
     <row r="96" spans="1:13" ht="18" customHeight="1">
-      <c r="A96" s="130" t="s">
+      <c r="A96" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="B96" s="134" t="s">
+      <c r="B96" s="132" t="s">
         <v>27</v>
       </c>
-      <c r="C96" s="135"/>
-      <c r="D96" s="134"/>
-      <c r="E96" s="135" t="s">
+      <c r="C96" s="133"/>
+      <c r="D96" s="132"/>
+      <c r="E96" s="133" t="s">
         <v>379</v>
       </c>
-      <c r="F96" s="136" t="s">
+      <c r="F96" s="134" t="s">
+        <v>419</v>
+      </c>
+      <c r="G96" s="135" t="s">
+        <v>237</v>
+      </c>
+      <c r="H96" s="132" t="s">
         <v>420</v>
       </c>
-      <c r="G96" s="137" t="s">
-        <v>237</v>
-      </c>
-      <c r="H96" s="134" t="s">
-        <v>421</v>
-      </c>
-      <c r="I96" s="130" t="s">
+      <c r="I96" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="J96" s="134" t="s">
+      <c r="J96" s="132" t="s">
         <v>27</v>
       </c>
       <c r="K96" s="85" t="str">
@@ -6741,26 +6819,26 @@
       </c>
     </row>
     <row r="97" spans="1:13" ht="18" customHeight="1" thickBot="1">
-      <c r="A97" s="141" t="s">
+      <c r="A97" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="B97" s="142" t="s">
+      <c r="B97" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="C97" s="143"/>
-      <c r="D97" s="142"/>
-      <c r="E97" s="143"/>
-      <c r="F97" s="144"/>
-      <c r="G97" s="143" t="s">
+      <c r="C97" s="141"/>
+      <c r="D97" s="140"/>
+      <c r="E97" s="141"/>
+      <c r="F97" s="142"/>
+      <c r="G97" s="141" t="s">
         <v>380</v>
       </c>
-      <c r="H97" s="142" t="s">
-        <v>424</v>
-      </c>
-      <c r="I97" s="141" t="s">
+      <c r="H97" s="140" t="s">
+        <v>423</v>
+      </c>
+      <c r="I97" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="J97" s="142" t="s">
+      <c r="J97" s="140" t="s">
         <v>27</v>
       </c>
       <c r="K97" s="85" t="str">
@@ -6777,34 +6855,34 @@
       </c>
     </row>
     <row r="98" spans="1:13" ht="18" customHeight="1">
-      <c r="A98" s="145" t="s">
+      <c r="A98" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B98" s="146" t="s">
+      <c r="B98" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="147" t="s">
+      <c r="C98" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="D98" s="146" t="s">
-        <v>405</v>
-      </c>
-      <c r="E98" s="147" t="s">
+      <c r="D98" s="144" t="s">
+        <v>404</v>
+      </c>
+      <c r="E98" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="F98" s="148" t="s">
-        <v>420</v>
-      </c>
-      <c r="G98" s="147" t="s">
+      <c r="F98" s="146" t="s">
+        <v>419</v>
+      </c>
+      <c r="G98" s="145" t="s">
         <v>381</v>
       </c>
-      <c r="H98" s="146" t="s">
-        <v>424</v>
-      </c>
-      <c r="I98" s="145" t="s">
+      <c r="H98" s="144" t="s">
+        <v>423</v>
+      </c>
+      <c r="I98" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J98" s="146" t="s">
+      <c r="J98" s="144" t="s">
         <v>26</v>
       </c>
       <c r="K98" s="85" t="str">
@@ -6821,26 +6899,26 @@
       </c>
     </row>
     <row r="99" spans="1:13" ht="18" customHeight="1">
-      <c r="A99" s="145" t="s">
+      <c r="A99" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="B99" s="149" t="s">
+      <c r="B99" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="147"/>
-      <c r="D99" s="146"/>
-      <c r="E99" s="150" t="s">
+      <c r="C99" s="145"/>
+      <c r="D99" s="144"/>
+      <c r="E99" s="148" t="s">
         <v>132</v>
       </c>
-      <c r="F99" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G99" s="150"/>
-      <c r="H99" s="149"/>
-      <c r="I99" s="145" t="s">
+      <c r="F99" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G99" s="148"/>
+      <c r="H99" s="147"/>
+      <c r="I99" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="J99" s="149" t="s">
+      <c r="J99" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K99" s="85" t="str">
@@ -6857,30 +6935,30 @@
       </c>
     </row>
     <row r="100" spans="1:13" ht="18" customHeight="1">
-      <c r="A100" s="145" t="s">
+      <c r="A100" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="B100" s="149" t="s">
+      <c r="B100" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="150"/>
-      <c r="D100" s="149"/>
-      <c r="E100" s="150" t="s">
+      <c r="C100" s="148"/>
+      <c r="D100" s="147"/>
+      <c r="E100" s="148" t="s">
         <v>352</v>
       </c>
-      <c r="F100" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G100" s="150" t="s">
+      <c r="F100" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G100" s="148" t="s">
         <v>382</v>
       </c>
-      <c r="H100" s="149" t="s">
-        <v>423</v>
-      </c>
-      <c r="I100" s="145" t="s">
+      <c r="H100" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="I100" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="J100" s="149" t="s">
+      <c r="J100" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K100" s="85" t="str">
@@ -6897,30 +6975,30 @@
       </c>
     </row>
     <row r="101" spans="1:13" ht="18" customHeight="1">
-      <c r="A101" s="145" t="s">
+      <c r="A101" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="149" t="s">
+      <c r="B101" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="150" t="s">
+      <c r="C101" s="148" t="s">
         <v>383</v>
       </c>
-      <c r="D101" s="149" t="s">
-        <v>411</v>
-      </c>
-      <c r="E101" s="150"/>
-      <c r="F101" s="151"/>
-      <c r="G101" s="150" t="s">
+      <c r="D101" s="147" t="s">
+        <v>410</v>
+      </c>
+      <c r="E101" s="148"/>
+      <c r="F101" s="149"/>
+      <c r="G101" s="148" t="s">
         <v>384</v>
       </c>
-      <c r="H101" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I101" s="145" t="s">
+      <c r="H101" s="147" t="s">
+        <v>420</v>
+      </c>
+      <c r="I101" s="143" t="s">
         <v>21</v>
       </c>
-      <c r="J101" s="149" t="s">
+      <c r="J101" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K101" s="85" t="str">
@@ -6937,26 +7015,26 @@
       </c>
     </row>
     <row r="102" spans="1:13" ht="18" customHeight="1">
-      <c r="A102" s="145" t="s">
+      <c r="A102" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="B102" s="149" t="s">
+      <c r="B102" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="150"/>
-      <c r="D102" s="149"/>
-      <c r="E102" s="150" t="s">
+      <c r="C102" s="148"/>
+      <c r="D102" s="147"/>
+      <c r="E102" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="F102" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G102" s="150"/>
-      <c r="H102" s="149"/>
-      <c r="I102" s="145" t="s">
+      <c r="F102" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G102" s="148"/>
+      <c r="H102" s="147"/>
+      <c r="I102" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="J102" s="149" t="s">
+      <c r="J102" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K102" s="85" t="str">
@@ -6973,26 +7051,26 @@
       </c>
     </row>
     <row r="103" spans="1:13" ht="18" customHeight="1">
-      <c r="A103" s="145" t="s">
+      <c r="A103" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B103" s="149" t="s">
+      <c r="B103" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="152"/>
-      <c r="D103" s="149"/>
-      <c r="E103" s="150"/>
-      <c r="F103" s="151"/>
-      <c r="G103" s="150" t="s">
+      <c r="C103" s="150"/>
+      <c r="D103" s="147"/>
+      <c r="E103" s="148"/>
+      <c r="F103" s="149"/>
+      <c r="G103" s="148" t="s">
         <v>385</v>
       </c>
-      <c r="H103" s="149" t="s">
-        <v>423</v>
-      </c>
-      <c r="I103" s="145" t="s">
+      <c r="H103" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="I103" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="J103" s="149" t="s">
+      <c r="J103" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K103" s="85" t="str">
@@ -7009,30 +7087,30 @@
       </c>
     </row>
     <row r="104" spans="1:13" ht="18" customHeight="1">
-      <c r="A104" s="145" t="s">
+      <c r="A104" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="B104" s="149" t="s">
+      <c r="B104" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="150"/>
-      <c r="D104" s="149"/>
-      <c r="E104" s="150" t="s">
+      <c r="C104" s="148"/>
+      <c r="D104" s="147"/>
+      <c r="E104" s="148" t="s">
         <v>386</v>
       </c>
-      <c r="F104" s="151" t="s">
-        <v>419</v>
-      </c>
-      <c r="G104" s="150" t="s">
+      <c r="F104" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="G104" s="148" t="s">
         <v>387</v>
       </c>
-      <c r="H104" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I104" s="145" t="s">
+      <c r="H104" s="147" t="s">
+        <v>420</v>
+      </c>
+      <c r="I104" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="J104" s="149" t="s">
+      <c r="J104" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K104" s="85" t="str">
@@ -7049,30 +7127,30 @@
       </c>
     </row>
     <row r="105" spans="1:13" ht="18" customHeight="1">
-      <c r="A105" s="145" t="s">
+      <c r="A105" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="B105" s="149" t="s">
+      <c r="B105" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="150" t="s">
+      <c r="C105" s="148" t="s">
         <v>86</v>
       </c>
-      <c r="D105" s="149" t="s">
-        <v>412</v>
-      </c>
-      <c r="E105" s="150" t="s">
+      <c r="D105" s="147" t="s">
+        <v>411</v>
+      </c>
+      <c r="E105" s="148" t="s">
         <v>204</v>
       </c>
-      <c r="F105" s="151" t="s">
-        <v>419</v>
-      </c>
-      <c r="G105" s="150"/>
-      <c r="H105" s="149"/>
-      <c r="I105" s="145" t="s">
+      <c r="F105" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="G105" s="148"/>
+      <c r="H105" s="147"/>
+      <c r="I105" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="J105" s="149" t="s">
+      <c r="J105" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K105" s="85" t="str">
@@ -7089,26 +7167,26 @@
       </c>
     </row>
     <row r="106" spans="1:13" ht="18" customHeight="1">
-      <c r="A106" s="145" t="s">
+      <c r="A106" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B106" s="149" t="s">
+      <c r="B106" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C106" s="150"/>
-      <c r="D106" s="149"/>
-      <c r="E106" s="150"/>
-      <c r="F106" s="151"/>
-      <c r="G106" s="150" t="s">
+      <c r="C106" s="148"/>
+      <c r="D106" s="147"/>
+      <c r="E106" s="148"/>
+      <c r="F106" s="149"/>
+      <c r="G106" s="148" t="s">
         <v>388</v>
       </c>
-      <c r="H106" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I106" s="145" t="s">
+      <c r="H106" s="147" t="s">
+        <v>420</v>
+      </c>
+      <c r="I106" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="J106" s="149" t="s">
+      <c r="J106" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K106" s="85" t="str">
@@ -7125,30 +7203,30 @@
       </c>
     </row>
     <row r="107" spans="1:13" ht="18" customHeight="1">
-      <c r="A107" s="145" t="s">
+      <c r="A107" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="B107" s="149" t="s">
+      <c r="B107" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="150"/>
-      <c r="D107" s="149"/>
-      <c r="E107" s="153" t="s">
-        <v>519</v>
-      </c>
-      <c r="F107" s="151" t="s">
-        <v>419</v>
-      </c>
-      <c r="G107" s="150" t="s">
+      <c r="C107" s="148"/>
+      <c r="D107" s="147"/>
+      <c r="E107" s="151" t="s">
+        <v>518</v>
+      </c>
+      <c r="F107" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="G107" s="148" t="s">
         <v>389</v>
       </c>
-      <c r="H107" s="149" t="s">
-        <v>424</v>
-      </c>
-      <c r="I107" s="145" t="s">
+      <c r="H107" s="147" t="s">
+        <v>423</v>
+      </c>
+      <c r="I107" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="J107" s="149" t="s">
+      <c r="J107" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K107" s="85" t="str">
@@ -7165,26 +7243,26 @@
       </c>
     </row>
     <row r="108" spans="1:13" ht="18" customHeight="1">
-      <c r="A108" s="145" t="s">
+      <c r="A108" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="B108" s="149" t="s">
+      <c r="B108" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C108" s="150"/>
-      <c r="D108" s="149"/>
-      <c r="E108" s="150" t="s">
+      <c r="C108" s="148"/>
+      <c r="D108" s="147"/>
+      <c r="E108" s="148" t="s">
         <v>390</v>
       </c>
-      <c r="F108" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G108" s="150"/>
-      <c r="H108" s="149"/>
-      <c r="I108" s="145" t="s">
+      <c r="F108" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G108" s="148"/>
+      <c r="H108" s="147"/>
+      <c r="I108" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="J108" s="149" t="s">
+      <c r="J108" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K108" s="85" t="str">
@@ -7201,30 +7279,30 @@
       </c>
     </row>
     <row r="109" spans="1:13" ht="18" customHeight="1">
-      <c r="A109" s="145" t="s">
+      <c r="A109" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B109" s="149" t="s">
+      <c r="B109" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C109" s="150" t="s">
+      <c r="C109" s="148" t="s">
         <v>391</v>
       </c>
-      <c r="D109" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="E109" s="150"/>
-      <c r="F109" s="151"/>
-      <c r="G109" s="150" t="s">
+      <c r="D109" s="147" t="s">
+        <v>412</v>
+      </c>
+      <c r="E109" s="148"/>
+      <c r="F109" s="149"/>
+      <c r="G109" s="148" t="s">
         <v>249</v>
       </c>
-      <c r="H109" s="149" t="s">
-        <v>424</v>
-      </c>
-      <c r="I109" s="145" t="s">
+      <c r="H109" s="147" t="s">
+        <v>423</v>
+      </c>
+      <c r="I109" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="J109" s="149" t="s">
+      <c r="J109" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K109" s="85" t="str">
@@ -7241,30 +7319,30 @@
       </c>
     </row>
     <row r="110" spans="1:13" ht="18" customHeight="1">
-      <c r="A110" s="145" t="s">
+      <c r="A110" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="B110" s="149" t="s">
+      <c r="B110" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C110" s="154"/>
-      <c r="D110" s="149"/>
-      <c r="E110" s="150" t="s">
+      <c r="C110" s="152"/>
+      <c r="D110" s="147"/>
+      <c r="E110" s="148" t="s">
         <v>367</v>
       </c>
-      <c r="F110" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G110" s="150" t="s">
+      <c r="F110" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G110" s="148" t="s">
         <v>392</v>
       </c>
-      <c r="H110" s="149" t="s">
-        <v>423</v>
-      </c>
-      <c r="I110" s="145" t="s">
+      <c r="H110" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="I110" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="J110" s="149" t="s">
+      <c r="J110" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K110" s="85" t="str">
@@ -7281,26 +7359,26 @@
       </c>
     </row>
     <row r="111" spans="1:13" ht="18" customHeight="1">
-      <c r="A111" s="145" t="s">
+      <c r="A111" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="B111" s="149" t="s">
+      <c r="B111" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="150"/>
-      <c r="D111" s="149"/>
-      <c r="E111" s="150" t="s">
+      <c r="C111" s="148"/>
+      <c r="D111" s="147"/>
+      <c r="E111" s="148" t="s">
         <v>217</v>
       </c>
-      <c r="F111" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G111" s="150"/>
-      <c r="H111" s="149"/>
-      <c r="I111" s="145" t="s">
+      <c r="F111" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G111" s="148"/>
+      <c r="H111" s="147"/>
+      <c r="I111" s="143" t="s">
         <v>11</v>
       </c>
-      <c r="J111" s="149" t="s">
+      <c r="J111" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K111" s="85" t="str">
@@ -7317,30 +7395,30 @@
       </c>
     </row>
     <row r="112" spans="1:13" ht="18" customHeight="1">
-      <c r="A112" s="145" t="s">
+      <c r="A112" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="B112" s="149" t="s">
+      <c r="B112" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="150"/>
-      <c r="D112" s="149"/>
-      <c r="E112" s="150" t="s">
+      <c r="C112" s="148"/>
+      <c r="D112" s="147"/>
+      <c r="E112" s="148" t="s">
         <v>172</v>
       </c>
-      <c r="F112" s="151" t="s">
+      <c r="F112" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G112" s="148" t="s">
+        <v>251</v>
+      </c>
+      <c r="H112" s="147" t="s">
         <v>420</v>
       </c>
-      <c r="G112" s="150" t="s">
-        <v>251</v>
-      </c>
-      <c r="H112" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I112" s="145" t="s">
+      <c r="I112" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="J112" s="149" t="s">
+      <c r="J112" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K112" s="85" t="str">
@@ -7357,30 +7435,30 @@
       </c>
     </row>
     <row r="113" spans="1:13" ht="18" customHeight="1">
-      <c r="A113" s="155" t="s">
+      <c r="A113" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="149" t="s">
+      <c r="B113" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C113" s="150" t="s">
+      <c r="C113" s="148" t="s">
         <v>393</v>
       </c>
-      <c r="D113" s="149" t="s">
-        <v>414</v>
-      </c>
-      <c r="E113" s="150"/>
-      <c r="F113" s="151"/>
-      <c r="G113" s="156" t="s">
+      <c r="D113" s="147" t="s">
+        <v>413</v>
+      </c>
+      <c r="E113" s="148"/>
+      <c r="F113" s="149"/>
+      <c r="G113" s="154" t="s">
         <v>394</v>
       </c>
-      <c r="H113" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I113" s="155" t="s">
+      <c r="H113" s="147" t="s">
+        <v>420</v>
+      </c>
+      <c r="I113" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="J113" s="149" t="s">
+      <c r="J113" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K113" s="85" t="str">
@@ -7397,26 +7475,26 @@
       </c>
     </row>
     <row r="114" spans="1:13" ht="18" customHeight="1">
-      <c r="A114" s="145" t="s">
+      <c r="A114" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="B114" s="146" t="s">
+      <c r="B114" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="C114" s="147"/>
-      <c r="D114" s="146"/>
-      <c r="E114" s="147" t="s">
+      <c r="C114" s="145"/>
+      <c r="D114" s="144"/>
+      <c r="E114" s="145" t="s">
         <v>395</v>
       </c>
-      <c r="F114" s="148" t="s">
-        <v>420</v>
-      </c>
-      <c r="G114" s="147"/>
-      <c r="H114" s="146"/>
-      <c r="I114" s="145" t="s">
+      <c r="F114" s="146" t="s">
+        <v>419</v>
+      </c>
+      <c r="G114" s="145"/>
+      <c r="H114" s="144"/>
+      <c r="I114" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="J114" s="146" t="s">
+      <c r="J114" s="144" t="s">
         <v>26</v>
       </c>
       <c r="K114" s="85" t="str">
@@ -7433,26 +7511,26 @@
       </c>
     </row>
     <row r="115" spans="1:13" ht="18" customHeight="1">
-      <c r="A115" s="145" t="s">
+      <c r="A115" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="B115" s="149" t="s">
+      <c r="B115" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C115" s="150"/>
-      <c r="D115" s="149"/>
-      <c r="E115" s="150"/>
-      <c r="F115" s="151"/>
-      <c r="G115" s="150" t="s">
+      <c r="C115" s="148"/>
+      <c r="D115" s="147"/>
+      <c r="E115" s="148"/>
+      <c r="F115" s="149"/>
+      <c r="G115" s="148" t="s">
         <v>396</v>
       </c>
-      <c r="H115" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I115" s="145" t="s">
+      <c r="H115" s="147" t="s">
+        <v>420</v>
+      </c>
+      <c r="I115" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="J115" s="149" t="s">
+      <c r="J115" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K115" s="85" t="str">
@@ -7469,34 +7547,34 @@
       </c>
     </row>
     <row r="116" spans="1:13" ht="18" customHeight="1">
-      <c r="A116" s="145" t="s">
+      <c r="A116" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="B116" s="149" t="s">
+      <c r="B116" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C116" s="153" t="s">
-        <v>520</v>
-      </c>
-      <c r="D116" s="149" t="s">
-        <v>415</v>
-      </c>
-      <c r="E116" s="150" t="s">
+      <c r="C116" s="151" t="s">
+        <v>519</v>
+      </c>
+      <c r="D116" s="147" t="s">
+        <v>414</v>
+      </c>
+      <c r="E116" s="148" t="s">
         <v>244</v>
       </c>
-      <c r="F116" s="151" t="s">
+      <c r="F116" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G116" s="148" t="s">
+        <v>140</v>
+      </c>
+      <c r="H116" s="147" t="s">
         <v>420</v>
       </c>
-      <c r="G116" s="150" t="s">
-        <v>140</v>
-      </c>
-      <c r="H116" s="149" t="s">
-        <v>421</v>
-      </c>
-      <c r="I116" s="145" t="s">
+      <c r="I116" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="J116" s="149" t="s">
+      <c r="J116" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K116" s="85" t="str">
@@ -7513,26 +7591,26 @@
       </c>
     </row>
     <row r="117" spans="1:13" ht="18" customHeight="1">
-      <c r="A117" s="145" t="s">
+      <c r="A117" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="B117" s="149" t="s">
+      <c r="B117" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C117" s="150"/>
-      <c r="D117" s="149"/>
-      <c r="E117" s="150" t="s">
+      <c r="C117" s="148"/>
+      <c r="D117" s="147"/>
+      <c r="E117" s="148" t="s">
         <v>397</v>
       </c>
-      <c r="F117" s="151" t="s">
-        <v>419</v>
-      </c>
-      <c r="G117" s="150"/>
-      <c r="H117" s="149"/>
-      <c r="I117" s="145" t="s">
+      <c r="F117" s="149" t="s">
+        <v>418</v>
+      </c>
+      <c r="G117" s="148"/>
+      <c r="H117" s="147"/>
+      <c r="I117" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="J117" s="149" t="s">
+      <c r="J117" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K117" s="85" t="str">
@@ -7549,26 +7627,26 @@
       </c>
     </row>
     <row r="118" spans="1:13" ht="18" customHeight="1">
-      <c r="A118" s="145" t="s">
+      <c r="A118" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="B118" s="149" t="s">
+      <c r="B118" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C118" s="150"/>
-      <c r="D118" s="149"/>
-      <c r="E118" s="150"/>
-      <c r="F118" s="151"/>
-      <c r="G118" s="150" t="s">
+      <c r="C118" s="148"/>
+      <c r="D118" s="147"/>
+      <c r="E118" s="148"/>
+      <c r="F118" s="149"/>
+      <c r="G118" s="148" t="s">
         <v>398</v>
       </c>
-      <c r="H118" s="149" t="s">
-        <v>423</v>
-      </c>
-      <c r="I118" s="145" t="s">
+      <c r="H118" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="I118" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J118" s="149" t="s">
+      <c r="J118" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K118" s="85" t="str">
@@ -7585,30 +7663,30 @@
       </c>
     </row>
     <row r="119" spans="1:13" ht="18" customHeight="1">
-      <c r="A119" s="145" t="s">
+      <c r="A119" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="B119" s="149" t="s">
+      <c r="B119" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C119" s="154"/>
-      <c r="D119" s="149"/>
-      <c r="E119" s="150" t="s">
+      <c r="C119" s="152"/>
+      <c r="D119" s="147"/>
+      <c r="E119" s="148" t="s">
         <v>399</v>
       </c>
-      <c r="F119" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G119" s="150" t="s">
-        <v>559</v>
-      </c>
-      <c r="H119" s="149" t="s">
-        <v>424</v>
-      </c>
-      <c r="I119" s="145" t="s">
+      <c r="F119" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G119" s="148" t="s">
+        <v>551</v>
+      </c>
+      <c r="H119" s="147" t="s">
+        <v>423</v>
+      </c>
+      <c r="I119" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="J119" s="149" t="s">
+      <c r="J119" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K119" s="85" t="str">
@@ -7625,26 +7703,26 @@
       </c>
     </row>
     <row r="120" spans="1:13" ht="18" customHeight="1">
-      <c r="A120" s="145" t="s">
+      <c r="A120" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="B120" s="149" t="s">
+      <c r="B120" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="C120" s="150"/>
-      <c r="D120" s="149"/>
-      <c r="E120" s="150" t="s">
+      <c r="C120" s="148"/>
+      <c r="D120" s="147"/>
+      <c r="E120" s="148" t="s">
         <v>400</v>
       </c>
-      <c r="F120" s="151" t="s">
-        <v>420</v>
-      </c>
-      <c r="G120" s="150"/>
-      <c r="H120" s="157"/>
-      <c r="I120" s="145" t="s">
+      <c r="F120" s="149" t="s">
+        <v>419</v>
+      </c>
+      <c r="G120" s="148"/>
+      <c r="H120" s="155"/>
+      <c r="I120" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="J120" s="149" t="s">
+      <c r="J120" s="147" t="s">
         <v>26</v>
       </c>
       <c r="K120" s="85" t="str">
@@ -7661,35 +7739,35 @@
       </c>
     </row>
     <row r="121" spans="1:13" ht="18" customHeight="1" thickBot="1">
-      <c r="A121" s="158" t="s">
+      <c r="A121" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B121" s="159" t="s">
+      <c r="B121" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="C121" s="160" t="s">
-        <v>401</v>
-      </c>
-      <c r="D121" s="159" t="s">
-        <v>409</v>
-      </c>
-      <c r="E121" s="160"/>
-      <c r="F121" s="161"/>
-      <c r="G121" s="160" t="s">
-        <v>431</v>
-      </c>
-      <c r="H121" s="159" t="s">
-        <v>423</v>
-      </c>
-      <c r="I121" s="158" t="s">
+      <c r="C121" s="158" t="s">
+        <v>566</v>
+      </c>
+      <c r="D121" s="157" t="s">
+        <v>408</v>
+      </c>
+      <c r="E121" s="158"/>
+      <c r="F121" s="159"/>
+      <c r="G121" s="158" t="s">
+        <v>430</v>
+      </c>
+      <c r="H121" s="157" t="s">
+        <v>422</v>
+      </c>
+      <c r="I121" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="J121" s="159" t="s">
+      <c r="J121" s="157" t="s">
         <v>26</v>
       </c>
       <c r="K121" s="85" t="str">
         <f t="shared" si="3"/>
-        <v>23:12</v>
+        <v>23:15</v>
       </c>
       <c r="L121" s="85" t="str">
         <f t="shared" si="4"/>
@@ -7701,30 +7779,30 @@
       </c>
     </row>
     <row r="122" spans="1:13" ht="18" customHeight="1">
-      <c r="A122" s="162" t="s">
+      <c r="A122" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="B122" s="163" t="s">
+      <c r="B122" s="161" t="s">
         <v>25</v>
       </c>
-      <c r="C122" s="164"/>
-      <c r="D122" s="163"/>
-      <c r="E122" s="164" t="s">
+      <c r="C122" s="162"/>
+      <c r="D122" s="161"/>
+      <c r="E122" s="162" t="s">
         <v>57</v>
       </c>
-      <c r="F122" s="165" t="s">
+      <c r="F122" s="163" t="s">
+        <v>419</v>
+      </c>
+      <c r="G122" s="162" t="s">
+        <v>57</v>
+      </c>
+      <c r="H122" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="G122" s="164" t="s">
-        <v>57</v>
-      </c>
-      <c r="H122" s="163" t="s">
-        <v>421</v>
-      </c>
-      <c r="I122" s="162" t="s">
+      <c r="I122" s="160" t="s">
         <v>24</v>
       </c>
-      <c r="J122" s="163" t="s">
+      <c r="J122" s="161" t="s">
         <v>25</v>
       </c>
       <c r="K122" s="85" t="str">
@@ -7741,30 +7819,30 @@
       </c>
     </row>
     <row r="123" spans="1:13" ht="18" customHeight="1">
-      <c r="A123" s="162" t="s">
+      <c r="A123" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="B123" s="166" t="s">
+      <c r="B123" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C123" s="167"/>
-      <c r="D123" s="166"/>
-      <c r="E123" s="167" t="s">
+      <c r="C123" s="165"/>
+      <c r="D123" s="164"/>
+      <c r="E123" s="165" t="s">
         <v>72</v>
       </c>
-      <c r="F123" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G123" s="169" t="s">
-        <v>432</v>
-      </c>
-      <c r="H123" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I123" s="162" t="s">
+      <c r="F123" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G123" s="167" t="s">
+        <v>431</v>
+      </c>
+      <c r="H123" s="164" t="s">
+        <v>420</v>
+      </c>
+      <c r="I123" s="160" t="s">
         <v>23</v>
       </c>
-      <c r="J123" s="166" t="s">
+      <c r="J123" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K123" s="85" t="str">
@@ -7781,30 +7859,30 @@
       </c>
     </row>
     <row r="124" spans="1:13" ht="18" customHeight="1">
-      <c r="A124" s="162" t="s">
+      <c r="A124" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="B124" s="166" t="s">
+      <c r="B124" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C124" s="167"/>
-      <c r="D124" s="166"/>
-      <c r="E124" s="167" t="s">
+      <c r="C124" s="165"/>
+      <c r="D124" s="164"/>
+      <c r="E124" s="165" t="s">
         <v>98</v>
       </c>
-      <c r="F124" s="168" t="s">
+      <c r="F124" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G124" s="165" t="s">
+        <v>432</v>
+      </c>
+      <c r="H124" s="164" t="s">
         <v>420</v>
       </c>
-      <c r="G124" s="167" t="s">
-        <v>433</v>
-      </c>
-      <c r="H124" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I124" s="162" t="s">
+      <c r="I124" s="160" t="s">
         <v>22</v>
       </c>
-      <c r="J124" s="166" t="s">
+      <c r="J124" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K124" s="85" t="str">
@@ -7821,22 +7899,22 @@
       </c>
     </row>
     <row r="125" spans="1:13" ht="18" customHeight="1">
-      <c r="A125" s="162" t="s">
+      <c r="A125" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B125" s="166" t="s">
+      <c r="B125" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C125" s="167"/>
-      <c r="D125" s="166"/>
-      <c r="E125" s="167"/>
-      <c r="F125" s="168"/>
-      <c r="G125" s="167"/>
-      <c r="H125" s="166"/>
-      <c r="I125" s="162" t="s">
+      <c r="C125" s="165"/>
+      <c r="D125" s="164"/>
+      <c r="E125" s="165"/>
+      <c r="F125" s="166"/>
+      <c r="G125" s="165"/>
+      <c r="H125" s="164"/>
+      <c r="I125" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="J125" s="166" t="s">
+      <c r="J125" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K125" s="85" t="str">
@@ -7853,30 +7931,30 @@
       </c>
     </row>
     <row r="126" spans="1:13" ht="18" customHeight="1">
-      <c r="A126" s="162" t="s">
+      <c r="A126" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="B126" s="166" t="s">
+      <c r="B126" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C126" s="167"/>
-      <c r="D126" s="166"/>
-      <c r="E126" s="167" t="s">
+      <c r="C126" s="165"/>
+      <c r="D126" s="164"/>
+      <c r="E126" s="165" t="s">
         <v>84</v>
       </c>
-      <c r="F126" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G126" s="169" t="s">
+      <c r="F126" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G126" s="167" t="s">
         <v>355</v>
       </c>
-      <c r="H126" s="166" t="s">
-        <v>423</v>
-      </c>
-      <c r="I126" s="162" t="s">
+      <c r="H126" s="164" t="s">
+        <v>422</v>
+      </c>
+      <c r="I126" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="J126" s="166" t="s">
+      <c r="J126" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K126" s="85" t="str">
@@ -7893,26 +7971,26 @@
       </c>
     </row>
     <row r="127" spans="1:13" ht="18" customHeight="1">
-      <c r="A127" s="162" t="s">
+      <c r="A127" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B127" s="166" t="s">
+      <c r="B127" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C127" s="167"/>
-      <c r="D127" s="166"/>
-      <c r="E127" s="167" t="s">
-        <v>434</v>
-      </c>
-      <c r="F127" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G127" s="167"/>
-      <c r="H127" s="166"/>
-      <c r="I127" s="162" t="s">
+      <c r="C127" s="165"/>
+      <c r="D127" s="164"/>
+      <c r="E127" s="165" t="s">
+        <v>433</v>
+      </c>
+      <c r="F127" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G127" s="165"/>
+      <c r="H127" s="164"/>
+      <c r="I127" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="J127" s="166" t="s">
+      <c r="J127" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K127" s="85" t="str">
@@ -7929,30 +8007,30 @@
       </c>
     </row>
     <row r="128" spans="1:13" ht="18" customHeight="1">
-      <c r="A128" s="162" t="s">
+      <c r="A128" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="B128" s="166" t="s">
+      <c r="B128" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C128" s="169" t="s">
-        <v>402</v>
-      </c>
-      <c r="D128" s="166" t="s">
-        <v>416</v>
-      </c>
-      <c r="E128" s="167"/>
-      <c r="F128" s="168"/>
-      <c r="G128" s="167" t="s">
-        <v>435</v>
-      </c>
-      <c r="H128" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I128" s="162" t="s">
+      <c r="C128" s="167" t="s">
+        <v>401</v>
+      </c>
+      <c r="D128" s="164" t="s">
+        <v>415</v>
+      </c>
+      <c r="E128" s="165"/>
+      <c r="F128" s="166"/>
+      <c r="G128" s="165" t="s">
+        <v>434</v>
+      </c>
+      <c r="H128" s="164" t="s">
+        <v>420</v>
+      </c>
+      <c r="I128" s="160" t="s">
         <v>18</v>
       </c>
-      <c r="J128" s="166" t="s">
+      <c r="J128" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K128" s="85" t="str">
@@ -7969,30 +8047,30 @@
       </c>
     </row>
     <row r="129" spans="1:13" ht="18" customHeight="1">
-      <c r="A129" s="162" t="s">
+      <c r="A129" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="B129" s="166" t="s">
+      <c r="B129" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C129" s="170"/>
-      <c r="D129" s="166"/>
-      <c r="E129" s="167" t="s">
+      <c r="C129" s="168"/>
+      <c r="D129" s="164"/>
+      <c r="E129" s="165" t="s">
+        <v>435</v>
+      </c>
+      <c r="F129" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G129" s="167" t="s">
         <v>436</v>
       </c>
-      <c r="F129" s="168" t="s">
+      <c r="H129" s="164" t="s">
         <v>420</v>
       </c>
-      <c r="G129" s="169" t="s">
-        <v>437</v>
-      </c>
-      <c r="H129" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I129" s="162" t="s">
+      <c r="I129" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="J129" s="166" t="s">
+      <c r="J129" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K129" s="85" t="str">
@@ -8009,26 +8087,26 @@
       </c>
     </row>
     <row r="130" spans="1:13" ht="18" customHeight="1">
-      <c r="A130" s="162" t="s">
+      <c r="A130" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B130" s="166" t="s">
+      <c r="B130" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C130" s="167"/>
-      <c r="D130" s="166"/>
-      <c r="E130" s="167" t="s">
-        <v>438</v>
-      </c>
-      <c r="F130" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G130" s="167"/>
-      <c r="H130" s="166"/>
-      <c r="I130" s="162" t="s">
+      <c r="C130" s="165"/>
+      <c r="D130" s="164"/>
+      <c r="E130" s="165" t="s">
+        <v>437</v>
+      </c>
+      <c r="F130" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G130" s="165"/>
+      <c r="H130" s="164"/>
+      <c r="I130" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="J130" s="166" t="s">
+      <c r="J130" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K130" s="85" t="str">
@@ -8045,26 +8123,26 @@
       </c>
     </row>
     <row r="131" spans="1:13" ht="18" customHeight="1">
-      <c r="A131" s="162" t="s">
+      <c r="A131" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="B131" s="166" t="s">
+      <c r="B131" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C131" s="167"/>
-      <c r="D131" s="166"/>
-      <c r="E131" s="167"/>
-      <c r="F131" s="168"/>
-      <c r="G131" s="167" t="s">
-        <v>439</v>
-      </c>
-      <c r="H131" s="166" t="s">
-        <v>424</v>
-      </c>
-      <c r="I131" s="162" t="s">
+      <c r="C131" s="165"/>
+      <c r="D131" s="164"/>
+      <c r="E131" s="165"/>
+      <c r="F131" s="166"/>
+      <c r="G131" s="165" t="s">
+        <v>438</v>
+      </c>
+      <c r="H131" s="164" t="s">
+        <v>423</v>
+      </c>
+      <c r="I131" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="J131" s="166" t="s">
+      <c r="J131" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K131" s="85" t="str">
@@ -8081,30 +8159,30 @@
       </c>
     </row>
     <row r="132" spans="1:13" ht="18" customHeight="1">
-      <c r="A132" s="162" t="s">
+      <c r="A132" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="B132" s="166" t="s">
+      <c r="B132" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C132" s="167"/>
-      <c r="D132" s="166"/>
-      <c r="E132" s="167" t="s">
-        <v>440</v>
-      </c>
-      <c r="F132" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G132" s="169" t="s">
+      <c r="C132" s="165"/>
+      <c r="D132" s="164"/>
+      <c r="E132" s="165" t="s">
+        <v>439</v>
+      </c>
+      <c r="F132" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G132" s="167" t="s">
         <v>364</v>
       </c>
-      <c r="H132" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I132" s="162" t="s">
+      <c r="H132" s="164" t="s">
+        <v>420</v>
+      </c>
+      <c r="I132" s="160" t="s">
         <v>14</v>
       </c>
-      <c r="J132" s="166" t="s">
+      <c r="J132" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K132" s="85" t="str">
@@ -8121,30 +8199,30 @@
       </c>
     </row>
     <row r="133" spans="1:13" ht="18" customHeight="1">
-      <c r="A133" s="162" t="s">
+      <c r="A133" s="160" t="s">
         <v>13</v>
       </c>
-      <c r="B133" s="166" t="s">
+      <c r="B133" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C133" s="171" t="s">
-        <v>521</v>
-      </c>
-      <c r="D133" s="166" t="s">
-        <v>411</v>
-      </c>
-      <c r="E133" s="167" t="s">
-        <v>441</v>
-      </c>
-      <c r="F133" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G133" s="167"/>
-      <c r="H133" s="166"/>
-      <c r="I133" s="162" t="s">
+      <c r="C133" s="169" t="s">
+        <v>520</v>
+      </c>
+      <c r="D133" s="164" t="s">
+        <v>410</v>
+      </c>
+      <c r="E133" s="165" t="s">
+        <v>440</v>
+      </c>
+      <c r="F133" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G133" s="165"/>
+      <c r="H133" s="164"/>
+      <c r="I133" s="160" t="s">
         <v>13</v>
       </c>
-      <c r="J133" s="166" t="s">
+      <c r="J133" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K133" s="85" t="str">
@@ -8161,26 +8239,26 @@
       </c>
     </row>
     <row r="134" spans="1:13" ht="18" customHeight="1">
-      <c r="A134" s="162" t="s">
+      <c r="A134" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="B134" s="166" t="s">
+      <c r="B134" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C134" s="167"/>
-      <c r="D134" s="166"/>
-      <c r="E134" s="172"/>
-      <c r="F134" s="168"/>
-      <c r="G134" s="167" t="s">
-        <v>442</v>
-      </c>
-      <c r="H134" s="166" t="s">
-        <v>424</v>
-      </c>
-      <c r="I134" s="162" t="s">
+      <c r="C134" s="165"/>
+      <c r="D134" s="164"/>
+      <c r="E134" s="170"/>
+      <c r="F134" s="166"/>
+      <c r="G134" s="165" t="s">
+        <v>441</v>
+      </c>
+      <c r="H134" s="164" t="s">
+        <v>423</v>
+      </c>
+      <c r="I134" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="J134" s="166" t="s">
+      <c r="J134" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K134" s="85" t="str">
@@ -8197,30 +8275,30 @@
       </c>
     </row>
     <row r="135" spans="1:13" ht="18" customHeight="1">
-      <c r="A135" s="162" t="s">
+      <c r="A135" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="B135" s="166" t="s">
+      <c r="B135" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C135" s="172"/>
-      <c r="D135" s="166"/>
-      <c r="E135" s="167" t="s">
+      <c r="C135" s="170"/>
+      <c r="D135" s="164"/>
+      <c r="E135" s="165" t="s">
         <v>267</v>
       </c>
-      <c r="F135" s="168" t="s">
+      <c r="F135" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G135" s="167" t="s">
+        <v>442</v>
+      </c>
+      <c r="H135" s="164" t="s">
         <v>420</v>
       </c>
-      <c r="G135" s="169" t="s">
-        <v>443</v>
-      </c>
-      <c r="H135" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I135" s="162" t="s">
+      <c r="I135" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="J135" s="166" t="s">
+      <c r="J135" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K135" s="85" t="str">
@@ -8237,30 +8315,30 @@
       </c>
     </row>
     <row r="136" spans="1:13" ht="18" customHeight="1">
-      <c r="A136" s="162" t="s">
+      <c r="A136" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="B136" s="166" t="s">
+      <c r="B136" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C136" s="167" t="s">
-        <v>403</v>
-      </c>
-      <c r="D136" s="166" t="s">
-        <v>417</v>
-      </c>
-      <c r="E136" s="167" t="s">
+      <c r="C136" s="165" t="s">
+        <v>402</v>
+      </c>
+      <c r="D136" s="164" t="s">
+        <v>416</v>
+      </c>
+      <c r="E136" s="165" t="s">
         <v>264</v>
       </c>
-      <c r="F136" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G136" s="167"/>
-      <c r="H136" s="166"/>
-      <c r="I136" s="162" t="s">
+      <c r="F136" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G136" s="165"/>
+      <c r="H136" s="164"/>
+      <c r="I136" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="J136" s="166" t="s">
+      <c r="J136" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K136" s="85" t="str">
@@ -8277,26 +8355,26 @@
       </c>
     </row>
     <row r="137" spans="1:13" ht="18" customHeight="1">
-      <c r="A137" s="162" t="s">
+      <c r="A137" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B137" s="166" t="s">
+      <c r="B137" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C137" s="167"/>
-      <c r="D137" s="166"/>
-      <c r="E137" s="167"/>
-      <c r="F137" s="168"/>
-      <c r="G137" s="169" t="s">
+      <c r="C137" s="165"/>
+      <c r="D137" s="164"/>
+      <c r="E137" s="165"/>
+      <c r="F137" s="166"/>
+      <c r="G137" s="167" t="s">
         <v>161</v>
       </c>
-      <c r="H137" s="166" t="s">
-        <v>423</v>
-      </c>
-      <c r="I137" s="162" t="s">
+      <c r="H137" s="164" t="s">
+        <v>422</v>
+      </c>
+      <c r="I137" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="J137" s="166" t="s">
+      <c r="J137" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K137" s="85" t="str">
@@ -8313,34 +8391,34 @@
       </c>
     </row>
     <row r="138" spans="1:13" ht="18" customHeight="1">
-      <c r="A138" s="162" t="s">
+      <c r="A138" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="B138" s="166" t="s">
+      <c r="B138" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C138" s="171" t="s">
-        <v>522</v>
-      </c>
-      <c r="D138" s="166" t="s">
-        <v>418</v>
-      </c>
-      <c r="E138" s="167" t="s">
-        <v>444</v>
-      </c>
-      <c r="F138" s="168" t="s">
+      <c r="C138" s="169" t="s">
+        <v>521</v>
+      </c>
+      <c r="D138" s="164" t="s">
+        <v>417</v>
+      </c>
+      <c r="E138" s="165" t="s">
+        <v>443</v>
+      </c>
+      <c r="F138" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G138" s="165" t="s">
+        <v>371</v>
+      </c>
+      <c r="H138" s="164" t="s">
         <v>420</v>
       </c>
-      <c r="G138" s="167" t="s">
-        <v>371</v>
-      </c>
-      <c r="H138" s="166" t="s">
-        <v>421</v>
-      </c>
-      <c r="I138" s="162">
+      <c r="I138" s="160">
         <v>16</v>
       </c>
-      <c r="J138" s="166" t="s">
+      <c r="J138" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K138" s="85" t="str">
@@ -8357,26 +8435,26 @@
       </c>
     </row>
     <row r="139" spans="1:13" ht="18" customHeight="1">
-      <c r="A139" s="162" t="s">
+      <c r="A139" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="B139" s="166" t="s">
+      <c r="B139" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C139" s="167"/>
-      <c r="D139" s="166"/>
-      <c r="E139" s="167" t="s">
+      <c r="C139" s="165"/>
+      <c r="D139" s="164"/>
+      <c r="E139" s="165" t="s">
         <v>88</v>
       </c>
-      <c r="F139" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G139" s="167"/>
-      <c r="H139" s="166"/>
-      <c r="I139" s="162" t="s">
+      <c r="F139" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G139" s="165"/>
+      <c r="H139" s="164"/>
+      <c r="I139" s="160" t="s">
         <v>7</v>
       </c>
-      <c r="J139" s="166" t="s">
+      <c r="J139" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K139" s="85" t="str">
@@ -8393,26 +8471,26 @@
       </c>
     </row>
     <row r="140" spans="1:13" ht="18" customHeight="1">
-      <c r="A140" s="162" t="s">
+      <c r="A140" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="B140" s="166" t="s">
+      <c r="B140" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C140" s="167"/>
-      <c r="D140" s="166"/>
-      <c r="E140" s="167"/>
-      <c r="F140" s="168"/>
-      <c r="G140" s="167" t="s">
-        <v>445</v>
-      </c>
-      <c r="H140" s="166" t="s">
-        <v>423</v>
-      </c>
-      <c r="I140" s="162" t="s">
+      <c r="C140" s="165"/>
+      <c r="D140" s="164"/>
+      <c r="E140" s="165"/>
+      <c r="F140" s="166"/>
+      <c r="G140" s="165" t="s">
+        <v>444</v>
+      </c>
+      <c r="H140" s="164" t="s">
+        <v>422</v>
+      </c>
+      <c r="I140" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="J140" s="166" t="s">
+      <c r="J140" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K140" s="85" t="str">
@@ -8429,34 +8507,34 @@
       </c>
     </row>
     <row r="141" spans="1:13" ht="18" customHeight="1">
-      <c r="A141" s="162" t="s">
+      <c r="A141" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="B141" s="166" t="s">
+      <c r="B141" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C141" s="167" t="s">
-        <v>404</v>
-      </c>
-      <c r="D141" s="166" t="s">
-        <v>413</v>
-      </c>
-      <c r="E141" s="167" t="s">
+      <c r="C141" s="165" t="s">
+        <v>403</v>
+      </c>
+      <c r="D141" s="164" t="s">
+        <v>412</v>
+      </c>
+      <c r="E141" s="165" t="s">
+        <v>445</v>
+      </c>
+      <c r="F141" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G141" s="165" t="s">
         <v>446</v>
       </c>
-      <c r="F141" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G141" s="167" t="s">
-        <v>447</v>
-      </c>
-      <c r="H141" s="166" t="s">
-        <v>424</v>
-      </c>
-      <c r="I141" s="162" t="s">
+      <c r="H141" s="164" t="s">
+        <v>423</v>
+      </c>
+      <c r="I141" s="160" t="s">
         <v>5</v>
       </c>
-      <c r="J141" s="166" t="s">
+      <c r="J141" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K141" s="85" t="str">
@@ -8473,26 +8551,26 @@
       </c>
     </row>
     <row r="142" spans="1:13" ht="18" customHeight="1">
-      <c r="A142" s="162" t="s">
+      <c r="A142" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="B142" s="166" t="s">
+      <c r="B142" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C142" s="167"/>
-      <c r="D142" s="166"/>
-      <c r="E142" s="167" t="s">
-        <v>448</v>
-      </c>
-      <c r="F142" s="168" t="s">
-        <v>419</v>
-      </c>
-      <c r="G142" s="167"/>
-      <c r="H142" s="166"/>
-      <c r="I142" s="162" t="s">
+      <c r="C142" s="165"/>
+      <c r="D142" s="164"/>
+      <c r="E142" s="165" t="s">
+        <v>447</v>
+      </c>
+      <c r="F142" s="166" t="s">
+        <v>418</v>
+      </c>
+      <c r="G142" s="165"/>
+      <c r="H142" s="164"/>
+      <c r="I142" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="J142" s="166" t="s">
+      <c r="J142" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K142" s="85" t="str">
@@ -8509,26 +8587,26 @@
       </c>
     </row>
     <row r="143" spans="1:13" ht="18" customHeight="1">
-      <c r="A143" s="162" t="s">
+      <c r="A143" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="B143" s="166" t="s">
+      <c r="B143" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C143" s="167"/>
-      <c r="D143" s="166"/>
-      <c r="E143" s="167"/>
-      <c r="F143" s="168"/>
-      <c r="G143" s="167" t="s">
-        <v>449</v>
-      </c>
-      <c r="H143" s="166" t="s">
-        <v>424</v>
-      </c>
-      <c r="I143" s="162" t="s">
+      <c r="C143" s="165"/>
+      <c r="D143" s="164"/>
+      <c r="E143" s="165"/>
+      <c r="F143" s="166"/>
+      <c r="G143" s="165" t="s">
+        <v>448</v>
+      </c>
+      <c r="H143" s="164" t="s">
+        <v>423</v>
+      </c>
+      <c r="I143" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="J143" s="166" t="s">
+      <c r="J143" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K143" s="85" t="str">
@@ -8545,34 +8623,34 @@
       </c>
     </row>
     <row r="144" spans="1:13" ht="18" customHeight="1">
-      <c r="A144" s="162" t="s">
+      <c r="A144" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="B144" s="166" t="s">
+      <c r="B144" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C144" s="167" t="s">
+      <c r="C144" s="165" t="s">
         <v>237</v>
       </c>
-      <c r="D144" s="166" t="s">
-        <v>429</v>
-      </c>
-      <c r="E144" s="167" t="s">
-        <v>450</v>
-      </c>
-      <c r="F144" s="168" t="s">
-        <v>420</v>
-      </c>
-      <c r="G144" s="167" t="s">
+      <c r="D144" s="164" t="s">
+        <v>428</v>
+      </c>
+      <c r="E144" s="165" t="s">
+        <v>449</v>
+      </c>
+      <c r="F144" s="166" t="s">
+        <v>419</v>
+      </c>
+      <c r="G144" s="165" t="s">
         <v>379</v>
       </c>
-      <c r="H144" s="166" t="s">
-        <v>424</v>
-      </c>
-      <c r="I144" s="162" t="s">
+      <c r="H144" s="164" t="s">
+        <v>423</v>
+      </c>
+      <c r="I144" s="160" t="s">
         <v>2</v>
       </c>
-      <c r="J144" s="166" t="s">
+      <c r="J144" s="164" t="s">
         <v>25</v>
       </c>
       <c r="K144" s="85" t="str">
@@ -8589,26 +8667,26 @@
       </c>
     </row>
     <row r="145" spans="1:13" ht="18" customHeight="1" thickBot="1">
-      <c r="A145" s="173" t="s">
+      <c r="A145" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="B145" s="174" t="s">
+      <c r="B145" s="172" t="s">
         <v>25</v>
       </c>
-      <c r="C145" s="175"/>
-      <c r="D145" s="174"/>
-      <c r="E145" s="175" t="s">
-        <v>451</v>
-      </c>
-      <c r="F145" s="176" t="s">
-        <v>419</v>
-      </c>
-      <c r="G145" s="175"/>
-      <c r="H145" s="174"/>
-      <c r="I145" s="173" t="s">
+      <c r="C145" s="173"/>
+      <c r="D145" s="172"/>
+      <c r="E145" s="173" t="s">
+        <v>450</v>
+      </c>
+      <c r="F145" s="174" t="s">
+        <v>418</v>
+      </c>
+      <c r="G145" s="173"/>
+      <c r="H145" s="172"/>
+      <c r="I145" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="J145" s="174" t="s">
+      <c r="J145" s="172" t="s">
         <v>25</v>
       </c>
       <c r="K145" s="85" t="str">
@@ -8625,22 +8703,22 @@
       </c>
     </row>
     <row r="146" spans="1:13" ht="18" customHeight="1">
-      <c r="A146" s="177" t="s">
+      <c r="A146" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="B146" s="178" t="s">
+      <c r="B146" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="C146" s="179"/>
-      <c r="D146" s="178"/>
-      <c r="E146" s="180"/>
-      <c r="F146" s="181"/>
-      <c r="G146" s="180"/>
-      <c r="H146" s="178"/>
-      <c r="I146" s="177" t="s">
+      <c r="C146" s="177"/>
+      <c r="D146" s="176"/>
+      <c r="E146" s="178"/>
+      <c r="F146" s="179"/>
+      <c r="G146" s="178"/>
+      <c r="H146" s="176"/>
+      <c r="I146" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="J146" s="178" t="s">
+      <c r="J146" s="176" t="s">
         <v>0</v>
       </c>
       <c r="K146" s="85" t="str">
@@ -8657,30 +8735,30 @@
       </c>
     </row>
     <row r="147" spans="1:13" ht="18" customHeight="1">
-      <c r="A147" s="177" t="s">
+      <c r="A147" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="B147" s="182" t="s">
+      <c r="B147" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C147" s="183"/>
-      <c r="D147" s="182"/>
-      <c r="E147" s="184" t="s">
+      <c r="C147" s="181"/>
+      <c r="D147" s="180"/>
+      <c r="E147" s="182" t="s">
         <v>94</v>
       </c>
-      <c r="F147" s="185" t="s">
+      <c r="F147" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G147" s="182" t="s">
+        <v>451</v>
+      </c>
+      <c r="H147" s="180" t="s">
         <v>420</v>
       </c>
-      <c r="G147" s="184" t="s">
-        <v>452</v>
-      </c>
-      <c r="H147" s="182" t="s">
-        <v>421</v>
-      </c>
-      <c r="I147" s="177" t="s">
+      <c r="I147" s="175" t="s">
         <v>23</v>
       </c>
-      <c r="J147" s="182" t="s">
+      <c r="J147" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K147" s="85" t="str">
@@ -8697,34 +8775,34 @@
       </c>
     </row>
     <row r="148" spans="1:13" ht="18" customHeight="1">
-      <c r="A148" s="177" t="s">
+      <c r="A148" s="175" t="s">
         <v>22</v>
       </c>
-      <c r="B148" s="182" t="s">
+      <c r="B148" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C148" s="184" t="s">
+      <c r="C148" s="182" t="s">
         <v>163</v>
       </c>
-      <c r="D148" s="182" t="s">
-        <v>425</v>
-      </c>
-      <c r="E148" s="184" t="s">
-        <v>453</v>
-      </c>
-      <c r="F148" s="185" t="s">
-        <v>419</v>
-      </c>
-      <c r="G148" s="184" t="s">
+      <c r="D148" s="180" t="s">
+        <v>424</v>
+      </c>
+      <c r="E148" s="182" t="s">
+        <v>452</v>
+      </c>
+      <c r="F148" s="183" t="s">
+        <v>418</v>
+      </c>
+      <c r="G148" s="182" t="s">
         <v>118</v>
       </c>
-      <c r="H148" s="182" t="s">
-        <v>421</v>
-      </c>
-      <c r="I148" s="177" t="s">
+      <c r="H148" s="180" t="s">
+        <v>420</v>
+      </c>
+      <c r="I148" s="175" t="s">
         <v>22</v>
       </c>
-      <c r="J148" s="182" t="s">
+      <c r="J148" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K148" s="85" t="str">
@@ -8741,26 +8819,26 @@
       </c>
     </row>
     <row r="149" spans="1:13" ht="18" customHeight="1">
-      <c r="A149" s="177" t="s">
+      <c r="A149" s="175" t="s">
         <v>21</v>
       </c>
-      <c r="B149" s="182" t="s">
+      <c r="B149" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C149" s="184"/>
-      <c r="D149" s="182"/>
-      <c r="E149" s="184"/>
-      <c r="F149" s="185"/>
-      <c r="G149" s="186" t="s">
-        <v>454</v>
-      </c>
-      <c r="H149" s="182" t="s">
-        <v>421</v>
-      </c>
-      <c r="I149" s="177" t="s">
+      <c r="C149" s="182"/>
+      <c r="D149" s="180"/>
+      <c r="E149" s="182"/>
+      <c r="F149" s="183"/>
+      <c r="G149" s="184" t="s">
+        <v>453</v>
+      </c>
+      <c r="H149" s="180" t="s">
+        <v>420</v>
+      </c>
+      <c r="I149" s="175" t="s">
         <v>21</v>
       </c>
-      <c r="J149" s="182" t="s">
+      <c r="J149" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K149" s="85" t="str">
@@ -8777,22 +8855,22 @@
       </c>
     </row>
     <row r="150" spans="1:13" ht="18" customHeight="1">
-      <c r="A150" s="177" t="s">
+      <c r="A150" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="B150" s="182" t="s">
+      <c r="B150" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C150" s="184"/>
-      <c r="D150" s="182"/>
-      <c r="E150" s="184"/>
-      <c r="F150" s="185"/>
-      <c r="G150" s="184"/>
-      <c r="H150" s="182"/>
-      <c r="I150" s="177" t="s">
+      <c r="C150" s="182"/>
+      <c r="D150" s="180"/>
+      <c r="E150" s="182"/>
+      <c r="F150" s="183"/>
+      <c r="G150" s="182"/>
+      <c r="H150" s="180"/>
+      <c r="I150" s="175" t="s">
         <v>20</v>
       </c>
-      <c r="J150" s="182" t="s">
+      <c r="J150" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K150" s="85" t="str">
@@ -8809,30 +8887,30 @@
       </c>
     </row>
     <row r="151" spans="1:13" ht="18" customHeight="1">
-      <c r="A151" s="177" t="s">
+      <c r="A151" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="B151" s="182" t="s">
+      <c r="B151" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C151" s="184"/>
-      <c r="D151" s="182"/>
-      <c r="E151" s="184" t="s">
+      <c r="C151" s="182"/>
+      <c r="D151" s="180"/>
+      <c r="E151" s="182" t="s">
+        <v>454</v>
+      </c>
+      <c r="F151" s="183" t="s">
+        <v>418</v>
+      </c>
+      <c r="G151" s="182" t="s">
         <v>455</v>
       </c>
-      <c r="F151" s="185" t="s">
-        <v>419</v>
-      </c>
-      <c r="G151" s="184" t="s">
-        <v>456</v>
-      </c>
-      <c r="H151" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I151" s="177" t="s">
+      <c r="H151" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I151" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="J151" s="182" t="s">
+      <c r="J151" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K151" s="85" t="str">
@@ -8849,34 +8927,34 @@
       </c>
     </row>
     <row r="152" spans="1:13" ht="18" customHeight="1">
-      <c r="A152" s="177" t="s">
+      <c r="A152" s="175" t="s">
         <v>18</v>
       </c>
-      <c r="B152" s="182" t="s">
+      <c r="B152" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C152" s="184" t="s">
+      <c r="C152" s="182" t="s">
+        <v>456</v>
+      </c>
+      <c r="D152" s="180" t="s">
+        <v>425</v>
+      </c>
+      <c r="E152" s="182" t="s">
+        <v>387</v>
+      </c>
+      <c r="F152" s="183" t="s">
+        <v>418</v>
+      </c>
+      <c r="G152" s="182" t="s">
         <v>457</v>
       </c>
-      <c r="D152" s="182" t="s">
-        <v>426</v>
-      </c>
-      <c r="E152" s="184" t="s">
-        <v>387</v>
-      </c>
-      <c r="F152" s="185" t="s">
-        <v>419</v>
-      </c>
-      <c r="G152" s="184" t="s">
-        <v>458</v>
-      </c>
-      <c r="H152" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I152" s="177" t="s">
+      <c r="H152" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I152" s="175" t="s">
         <v>18</v>
       </c>
-      <c r="J152" s="182" t="s">
+      <c r="J152" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K152" s="85" t="str">
@@ -8893,22 +8971,22 @@
       </c>
     </row>
     <row r="153" spans="1:13" ht="18" customHeight="1">
-      <c r="A153" s="177" t="s">
+      <c r="A153" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="B153" s="182" t="s">
+      <c r="B153" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C153" s="184"/>
-      <c r="D153" s="182"/>
-      <c r="E153" s="184"/>
-      <c r="F153" s="185"/>
-      <c r="G153" s="186"/>
-      <c r="H153" s="182"/>
-      <c r="I153" s="177" t="s">
+      <c r="C153" s="182"/>
+      <c r="D153" s="180"/>
+      <c r="E153" s="182"/>
+      <c r="F153" s="183"/>
+      <c r="G153" s="184"/>
+      <c r="H153" s="180"/>
+      <c r="I153" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="J153" s="182" t="s">
+      <c r="J153" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K153" s="85" t="str">
@@ -8925,30 +9003,30 @@
       </c>
     </row>
     <row r="154" spans="1:13" ht="18" customHeight="1">
-      <c r="A154" s="177" t="s">
+      <c r="A154" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="B154" s="182" t="s">
+      <c r="B154" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C154" s="184"/>
-      <c r="D154" s="182"/>
-      <c r="E154" s="184" t="s">
+      <c r="C154" s="182"/>
+      <c r="D154" s="180"/>
+      <c r="E154" s="182" t="s">
         <v>388</v>
       </c>
-      <c r="F154" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G154" s="184" t="s">
+      <c r="F154" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G154" s="182" t="s">
         <v>96</v>
       </c>
-      <c r="H154" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I154" s="177" t="s">
+      <c r="H154" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I154" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="J154" s="182" t="s">
+      <c r="J154" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K154" s="85" t="str">
@@ -8965,34 +9043,34 @@
       </c>
     </row>
     <row r="155" spans="1:13" ht="18" customHeight="1">
-      <c r="A155" s="177" t="s">
+      <c r="A155" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="B155" s="182" t="s">
+      <c r="B155" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C155" s="184" t="s">
+      <c r="C155" s="182" t="s">
+        <v>458</v>
+      </c>
+      <c r="D155" s="180" t="s">
+        <v>429</v>
+      </c>
+      <c r="E155" s="182" t="s">
         <v>459</v>
       </c>
-      <c r="D155" s="182" t="s">
-        <v>430</v>
-      </c>
-      <c r="E155" s="184" t="s">
-        <v>460</v>
-      </c>
-      <c r="F155" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G155" s="186" t="s">
-        <v>460</v>
-      </c>
-      <c r="H155" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I155" s="177" t="s">
+      <c r="F155" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G155" s="184" t="s">
+        <v>459</v>
+      </c>
+      <c r="H155" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I155" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="J155" s="182" t="s">
+      <c r="J155" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K155" s="85" t="str">
@@ -9009,22 +9087,22 @@
       </c>
     </row>
     <row r="156" spans="1:13" ht="18" customHeight="1">
-      <c r="A156" s="177" t="s">
+      <c r="A156" s="175" t="s">
         <v>14</v>
       </c>
-      <c r="B156" s="182" t="s">
+      <c r="B156" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C156" s="184"/>
-      <c r="D156" s="182"/>
-      <c r="E156" s="184"/>
-      <c r="F156" s="185"/>
-      <c r="G156" s="184"/>
-      <c r="H156" s="182"/>
-      <c r="I156" s="177" t="s">
+      <c r="C156" s="182"/>
+      <c r="D156" s="180"/>
+      <c r="E156" s="182"/>
+      <c r="F156" s="183"/>
+      <c r="G156" s="182"/>
+      <c r="H156" s="180"/>
+      <c r="I156" s="175" t="s">
         <v>14</v>
       </c>
-      <c r="J156" s="182" t="s">
+      <c r="J156" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K156" s="85" t="str">
@@ -9041,30 +9119,30 @@
       </c>
     </row>
     <row r="157" spans="1:13" ht="18" customHeight="1">
-      <c r="A157" s="177" t="s">
+      <c r="A157" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="B157" s="182" t="s">
+      <c r="B157" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C157" s="184"/>
-      <c r="D157" s="182"/>
-      <c r="E157" s="184" t="s">
+      <c r="C157" s="182"/>
+      <c r="D157" s="180"/>
+      <c r="E157" s="182" t="s">
+        <v>460</v>
+      </c>
+      <c r="F157" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G157" s="182" t="s">
         <v>461</v>
       </c>
-      <c r="F157" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G157" s="184" t="s">
-        <v>462</v>
-      </c>
-      <c r="H157" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I157" s="177" t="s">
+      <c r="H157" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I157" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="J157" s="182" t="s">
+      <c r="J157" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K157" s="85" t="str">
@@ -9081,30 +9159,30 @@
       </c>
     </row>
     <row r="158" spans="1:13" ht="18" customHeight="1">
-      <c r="A158" s="177" t="s">
+      <c r="A158" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="B158" s="182" t="s">
+      <c r="B158" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C158" s="184"/>
-      <c r="D158" s="182"/>
-      <c r="E158" s="184" t="s">
-        <v>463</v>
-      </c>
-      <c r="F158" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G158" s="184" t="s">
+      <c r="C158" s="182"/>
+      <c r="D158" s="180"/>
+      <c r="E158" s="182" t="s">
+        <v>462</v>
+      </c>
+      <c r="F158" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G158" s="182" t="s">
         <v>392</v>
       </c>
-      <c r="H158" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I158" s="177" t="s">
+      <c r="H158" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I158" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="J158" s="182" t="s">
+      <c r="J158" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K158" s="85" t="str">
@@ -9121,26 +9199,26 @@
       </c>
     </row>
     <row r="159" spans="1:13" ht="18" customHeight="1">
-      <c r="A159" s="177" t="s">
+      <c r="A159" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="B159" s="182" t="s">
+      <c r="B159" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C159" s="184" t="s">
-        <v>464</v>
-      </c>
-      <c r="D159" s="182" t="s">
-        <v>427</v>
-      </c>
-      <c r="E159" s="183"/>
-      <c r="F159" s="185"/>
-      <c r="G159" s="184"/>
-      <c r="H159" s="182"/>
-      <c r="I159" s="177" t="s">
+      <c r="C159" s="182" t="s">
+        <v>463</v>
+      </c>
+      <c r="D159" s="180" t="s">
+        <v>426</v>
+      </c>
+      <c r="E159" s="181"/>
+      <c r="F159" s="183"/>
+      <c r="G159" s="182"/>
+      <c r="H159" s="180"/>
+      <c r="I159" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="J159" s="182" t="s">
+      <c r="J159" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K159" s="85" t="str">
@@ -9157,30 +9235,30 @@
       </c>
     </row>
     <row r="160" spans="1:13" ht="18" customHeight="1">
-      <c r="A160" s="177" t="s">
+      <c r="A160" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="B160" s="182" t="s">
+      <c r="B160" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C160" s="184"/>
-      <c r="D160" s="182"/>
-      <c r="E160" s="184" t="s">
+      <c r="C160" s="182"/>
+      <c r="D160" s="180"/>
+      <c r="E160" s="182" t="s">
+        <v>464</v>
+      </c>
+      <c r="F160" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G160" s="182" t="s">
         <v>465</v>
       </c>
-      <c r="F160" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G160" s="184" t="s">
-        <v>466</v>
-      </c>
-      <c r="H160" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I160" s="177" t="s">
+      <c r="H160" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I160" s="175" t="s">
         <v>10</v>
       </c>
-      <c r="J160" s="182" t="s">
+      <c r="J160" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K160" s="85" t="str">
@@ -9197,30 +9275,30 @@
       </c>
     </row>
     <row r="161" spans="1:13" ht="18" customHeight="1">
-      <c r="A161" s="177" t="s">
+      <c r="A161" s="175" t="s">
         <v>9</v>
       </c>
-      <c r="B161" s="182" t="s">
+      <c r="B161" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C161" s="184"/>
-      <c r="D161" s="182"/>
-      <c r="E161" s="184" t="s">
+      <c r="C161" s="182"/>
+      <c r="D161" s="180"/>
+      <c r="E161" s="182" t="s">
+        <v>466</v>
+      </c>
+      <c r="F161" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G161" s="184" t="s">
         <v>467</v>
       </c>
-      <c r="F161" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G161" s="186" t="s">
-        <v>468</v>
-      </c>
-      <c r="H161" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I161" s="177" t="s">
+      <c r="H161" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I161" s="175" t="s">
         <v>9</v>
       </c>
-      <c r="J161" s="182" t="s">
+      <c r="J161" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K161" s="85" t="str">
@@ -9237,26 +9315,26 @@
       </c>
     </row>
     <row r="162" spans="1:13" ht="18" customHeight="1">
-      <c r="A162" s="177" t="s">
+      <c r="A162" s="175" t="s">
         <v>8</v>
       </c>
-      <c r="B162" s="182" t="s">
+      <c r="B162" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C162" s="184" t="s">
-        <v>469</v>
-      </c>
-      <c r="D162" s="182" t="s">
-        <v>412</v>
-      </c>
-      <c r="E162" s="184"/>
-      <c r="F162" s="185"/>
-      <c r="G162" s="184"/>
-      <c r="H162" s="182"/>
-      <c r="I162" s="177" t="s">
+      <c r="C162" s="182" t="s">
+        <v>468</v>
+      </c>
+      <c r="D162" s="180" t="s">
+        <v>411</v>
+      </c>
+      <c r="E162" s="182"/>
+      <c r="F162" s="183"/>
+      <c r="G162" s="182"/>
+      <c r="H162" s="180"/>
+      <c r="I162" s="175" t="s">
         <v>8</v>
       </c>
-      <c r="J162" s="182" t="s">
+      <c r="J162" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K162" s="85" t="str">
@@ -9273,30 +9351,30 @@
       </c>
     </row>
     <row r="163" spans="1:13" ht="18" customHeight="1">
-      <c r="A163" s="177" t="s">
+      <c r="A163" s="175" t="s">
         <v>7</v>
       </c>
-      <c r="B163" s="182" t="s">
+      <c r="B163" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C163" s="184"/>
-      <c r="D163" s="182"/>
-      <c r="E163" s="184" t="s">
+      <c r="C163" s="182"/>
+      <c r="D163" s="180"/>
+      <c r="E163" s="182" t="s">
+        <v>469</v>
+      </c>
+      <c r="F163" s="183" t="s">
+        <v>418</v>
+      </c>
+      <c r="G163" s="182" t="s">
         <v>470</v>
       </c>
-      <c r="F163" s="185" t="s">
-        <v>419</v>
-      </c>
-      <c r="G163" s="184" t="s">
-        <v>471</v>
-      </c>
-      <c r="H163" s="182" t="s">
-        <v>421</v>
-      </c>
-      <c r="I163" s="177" t="s">
+      <c r="H163" s="180" t="s">
+        <v>420</v>
+      </c>
+      <c r="I163" s="175" t="s">
         <v>7</v>
       </c>
-      <c r="J163" s="182" t="s">
+      <c r="J163" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K163" s="85" t="str">
@@ -9313,30 +9391,30 @@
       </c>
     </row>
     <row r="164" spans="1:13" ht="18" customHeight="1">
-      <c r="A164" s="177" t="s">
+      <c r="A164" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="B164" s="182" t="s">
+      <c r="B164" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C164" s="184"/>
-      <c r="D164" s="182"/>
-      <c r="E164" s="184" t="s">
+      <c r="C164" s="182"/>
+      <c r="D164" s="180"/>
+      <c r="E164" s="182" t="s">
         <v>342</v>
       </c>
-      <c r="F164" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G164" s="184" t="s">
-        <v>472</v>
-      </c>
-      <c r="H164" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I164" s="177" t="s">
+      <c r="F164" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G164" s="182" t="s">
+        <v>471</v>
+      </c>
+      <c r="H164" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I164" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="J164" s="182" t="s">
+      <c r="J164" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K164" s="85" t="str">
@@ -9353,26 +9431,26 @@
       </c>
     </row>
     <row r="165" spans="1:13" ht="18" customHeight="1">
-      <c r="A165" s="177" t="s">
+      <c r="A165" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="B165" s="182" t="s">
+      <c r="B165" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C165" s="184" t="s">
-        <v>473</v>
-      </c>
-      <c r="D165" s="182" t="s">
-        <v>428</v>
-      </c>
-      <c r="E165" s="184"/>
-      <c r="F165" s="185"/>
-      <c r="G165" s="184"/>
-      <c r="H165" s="182"/>
-      <c r="I165" s="177" t="s">
+      <c r="C165" s="182" t="s">
+        <v>472</v>
+      </c>
+      <c r="D165" s="180" t="s">
+        <v>427</v>
+      </c>
+      <c r="E165" s="182"/>
+      <c r="F165" s="183"/>
+      <c r="G165" s="182"/>
+      <c r="H165" s="180"/>
+      <c r="I165" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="J165" s="182" t="s">
+      <c r="J165" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K165" s="85" t="str">
@@ -9389,30 +9467,30 @@
       </c>
     </row>
     <row r="166" spans="1:13" ht="18" customHeight="1">
-      <c r="A166" s="177" t="s">
+      <c r="A166" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="B166" s="182" t="s">
+      <c r="B166" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C166" s="187"/>
-      <c r="D166" s="182"/>
-      <c r="E166" s="184" t="s">
+      <c r="C166" s="185"/>
+      <c r="D166" s="180"/>
+      <c r="E166" s="182" t="s">
+        <v>473</v>
+      </c>
+      <c r="F166" s="183" t="s">
+        <v>418</v>
+      </c>
+      <c r="G166" s="182" t="s">
         <v>474</v>
       </c>
-      <c r="F166" s="185" t="s">
-        <v>419</v>
-      </c>
-      <c r="G166" s="184" t="s">
-        <v>475</v>
-      </c>
-      <c r="H166" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I166" s="177" t="s">
+      <c r="H166" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I166" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="J166" s="182" t="s">
+      <c r="J166" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K166" s="85" t="str">
@@ -9429,30 +9507,30 @@
       </c>
     </row>
     <row r="167" spans="1:13" ht="18" customHeight="1">
-      <c r="A167" s="177" t="s">
+      <c r="A167" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="B167" s="182" t="s">
+      <c r="B167" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C167" s="184"/>
-      <c r="D167" s="182"/>
-      <c r="E167" s="184" t="s">
-        <v>477</v>
-      </c>
-      <c r="F167" s="185" t="s">
-        <v>420</v>
-      </c>
-      <c r="G167" s="184" t="s">
-        <v>477</v>
-      </c>
-      <c r="H167" s="182" t="s">
-        <v>423</v>
-      </c>
-      <c r="I167" s="177" t="s">
+      <c r="C167" s="182"/>
+      <c r="D167" s="180"/>
+      <c r="E167" s="182" t="s">
+        <v>476</v>
+      </c>
+      <c r="F167" s="183" t="s">
+        <v>419</v>
+      </c>
+      <c r="G167" s="182" t="s">
+        <v>476</v>
+      </c>
+      <c r="H167" s="180" t="s">
+        <v>422</v>
+      </c>
+      <c r="I167" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="J167" s="182" t="s">
+      <c r="J167" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K167" s="85" t="str">
@@ -9469,22 +9547,22 @@
       </c>
     </row>
     <row r="168" spans="1:13" ht="18" customHeight="1">
-      <c r="A168" s="177" t="s">
+      <c r="A168" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="B168" s="182" t="s">
+      <c r="B168" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C168" s="184"/>
-      <c r="D168" s="182"/>
-      <c r="E168" s="184"/>
-      <c r="F168" s="185"/>
-      <c r="G168" s="184"/>
-      <c r="H168" s="182"/>
-      <c r="I168" s="177" t="s">
+      <c r="C168" s="182"/>
+      <c r="D168" s="180"/>
+      <c r="E168" s="182"/>
+      <c r="F168" s="183"/>
+      <c r="G168" s="182"/>
+      <c r="H168" s="180"/>
+      <c r="I168" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="J168" s="182" t="s">
+      <c r="J168" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K168" s="85" t="str">
@@ -9501,34 +9579,34 @@
       </c>
     </row>
     <row r="169" spans="1:13" ht="18" customHeight="1">
-      <c r="A169" s="177" t="s">
+      <c r="A169" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="B169" s="182" t="s">
+      <c r="B169" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C169" s="184" t="s">
+      <c r="C169" s="182" t="s">
+        <v>487</v>
+      </c>
+      <c r="D169" s="180" t="s">
         <v>488</v>
       </c>
-      <c r="D169" s="182" t="s">
-        <v>489</v>
-      </c>
-      <c r="E169" s="184" t="s">
-        <v>478</v>
-      </c>
-      <c r="F169" s="191" t="s">
-        <v>561</v>
-      </c>
-      <c r="G169" s="184" t="s">
-        <v>478</v>
-      </c>
-      <c r="H169" s="182" t="s">
-        <v>424</v>
-      </c>
-      <c r="I169" s="177" t="s">
+      <c r="E169" s="182" t="s">
+        <v>477</v>
+      </c>
+      <c r="F169" s="189" t="s">
+        <v>553</v>
+      </c>
+      <c r="G169" s="182" t="s">
+        <v>477</v>
+      </c>
+      <c r="H169" s="180" t="s">
+        <v>423</v>
+      </c>
+      <c r="I169" s="175" t="s">
         <v>1</v>
       </c>
-      <c r="J169" s="182" t="s">
+      <c r="J169" s="180" t="s">
         <v>0</v>
       </c>
       <c r="K169" s="85" t="str">
@@ -9552,7 +9630,7 @@
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H119 D71:D1048576 G77 H121:H1048576 E159">
+  <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 D71:D1048576 G77 H121:H1048576 E159 H13:H119">
     <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3ABFB72-1BBF-494E-B9FE-501A2A7C97B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026B3D9E-3013-4979-9430-F107B6DA726E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10125" yWindow="3570" windowWidth="16140" windowHeight="11235" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10545" yWindow="720" windowWidth="16140" windowHeight="11235" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="581">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1987,6 +1987,18 @@
   </si>
   <si>
     <t>12:59</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:18</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>灰狼村 / 豬豬海岸</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:31</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2199,7 +2211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2780,6 +2792,9 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -5263,12 +5278,20 @@
       <c r="B64" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C64" s="117"/>
-      <c r="D64" s="116"/>
+      <c r="C64" s="117" t="s">
+        <v>578</v>
+      </c>
+      <c r="D64" s="194" t="s">
+        <v>579</v>
+      </c>
       <c r="E64" s="117"/>
       <c r="F64" s="118"/>
-      <c r="G64" s="117"/>
-      <c r="H64" s="116"/>
+      <c r="G64" s="117" t="s">
+        <v>580</v>
+      </c>
+      <c r="H64" s="116" t="s">
+        <v>422</v>
+      </c>
       <c r="I64" s="112" t="s">
         <v>10</v>
       </c>
@@ -5277,7 +5300,7 @@
       </c>
       <c r="K64" s="85" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>14:18</v>
       </c>
       <c r="L64" s="85" t="str">
         <f t="shared" si="1"/>
@@ -5285,7 +5308,7 @@
       </c>
       <c r="M64" s="85" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>14:31</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="18" customHeight="1">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE2B6C7-A986-4FB3-9A85-134E98CFA540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3936B1B-19B1-4A2D-BBE7-A6A622FF14E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13785" yWindow="105" windowWidth="15075" windowHeight="15240" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4473" uniqueCount="824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3837" uniqueCount="824">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -2700,10 +2700,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>02:25_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>01:0×</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2873,6 +2869,10 @@
   </si>
   <si>
     <t>10:48_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02:25</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3150,7 +3150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3728,189 +3728,179 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -3956,7 +3946,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF9999"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4258,23 +4248,23 @@
   <dimension ref="A1:J1055"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.25" style="225" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="225" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="225" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5" style="225" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="225" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="225" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="225" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="225" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.25" style="225" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.125" style="225" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.625" style="225" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="14.25" style="225"/>
+    <col min="1" max="1" width="4.25" style="187" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="187" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="187" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5" style="187" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="187" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="187" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="187" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.375" style="187" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.25" style="187" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3.125" style="187" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.625" style="187" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="14.25" style="187"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="234" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="232"/>
-      <c r="B1" s="233" t="s">
+    <row r="1" spans="1:10" s="233" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="231"/>
+      <c r="B1" s="232" t="s">
         <v>573</v>
       </c>
       <c r="C1" s="193" t="s">
@@ -4295,8 +4285,8 @@
       <c r="H1" s="193" t="s">
         <v>325</v>
       </c>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="194" t="s">
@@ -4336,13 +4326,13 @@
       </c>
       <c r="D3" s="194"/>
       <c r="E3" s="195" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F3" s="194" t="s">
         <v>609</v>
       </c>
       <c r="G3" s="195" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H3" s="194" t="s">
         <v>421</v>
@@ -4368,15 +4358,15 @@
         <v>412</v>
       </c>
       <c r="E4" s="195" t="s">
-        <v>805</v>
-      </c>
-      <c r="F4" s="235" t="s">
+        <v>804</v>
+      </c>
+      <c r="F4" s="234" t="s">
         <v>539</v>
       </c>
       <c r="G4" s="195" t="s">
         <v>615</v>
       </c>
-      <c r="H4" s="235" t="s">
+      <c r="H4" s="234" t="s">
         <v>623</v>
       </c>
       <c r="I4" s="194" t="s">
@@ -4424,15 +4414,15 @@
       </c>
       <c r="D6" s="194"/>
       <c r="E6" s="195" t="s">
-        <v>806</v>
-      </c>
-      <c r="F6" s="235" t="s">
+        <v>805</v>
+      </c>
+      <c r="F6" s="234" t="s">
         <v>549</v>
       </c>
       <c r="G6" s="195" t="s">
         <v>616</v>
       </c>
-      <c r="H6" s="236" t="s">
+      <c r="H6" s="235" t="s">
         <v>420</v>
       </c>
       <c r="I6" s="194" t="s">
@@ -4462,7 +4452,7 @@
       <c r="G7" s="195" t="s">
         <v>617</v>
       </c>
-      <c r="H7" s="236" t="s">
+      <c r="H7" s="235" t="s">
         <v>538</v>
       </c>
       <c r="I7" s="194" t="s">
@@ -4484,9 +4474,9 @@
       </c>
       <c r="D8" s="194"/>
       <c r="E8" s="195" t="s">
-        <v>807</v>
-      </c>
-      <c r="F8" s="235" t="s">
+        <v>806</v>
+      </c>
+      <c r="F8" s="234" t="s">
         <v>549</v>
       </c>
       <c r="G8" s="194" t="s">
@@ -4512,15 +4502,15 @@
       </c>
       <c r="D9" s="194"/>
       <c r="E9" s="195" t="s">
-        <v>808</v>
-      </c>
-      <c r="F9" s="235" t="s">
+        <v>807</v>
+      </c>
+      <c r="F9" s="234" t="s">
         <v>539</v>
       </c>
       <c r="G9" s="195" t="s">
         <v>618</v>
       </c>
-      <c r="H9" s="236" t="s">
+      <c r="H9" s="235" t="s">
         <v>538</v>
       </c>
       <c r="I9" s="194" t="s">
@@ -4550,7 +4540,7 @@
       <c r="G10" s="195" t="s">
         <v>619</v>
       </c>
-      <c r="H10" s="235" t="s">
+      <c r="H10" s="234" t="s">
         <v>516</v>
       </c>
       <c r="I10" s="194" t="s">
@@ -4572,7 +4562,7 @@
       </c>
       <c r="D11" s="194"/>
       <c r="E11" s="195" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F11" s="194" t="s">
         <v>608</v>
@@ -4600,15 +4590,15 @@
       </c>
       <c r="D12" s="194"/>
       <c r="E12" s="195" t="s">
-        <v>810</v>
-      </c>
-      <c r="F12" s="235" t="s">
+        <v>809</v>
+      </c>
+      <c r="F12" s="234" t="s">
         <v>549</v>
       </c>
       <c r="G12" s="195" t="s">
         <v>668</v>
       </c>
-      <c r="H12" s="236" t="s">
+      <c r="H12" s="235" t="s">
         <v>610</v>
       </c>
       <c r="I12" s="194" t="s">
@@ -4630,15 +4620,15 @@
       </c>
       <c r="D13" s="194"/>
       <c r="E13" s="195" t="s">
-        <v>811</v>
-      </c>
-      <c r="F13" s="235" t="s">
+        <v>810</v>
+      </c>
+      <c r="F13" s="234" t="s">
         <v>539</v>
       </c>
       <c r="G13" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="236" t="s">
+      <c r="H13" s="235" t="s">
         <v>610</v>
       </c>
       <c r="I13" s="194" t="s">
@@ -4696,7 +4686,7 @@
       <c r="G15" s="195" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="236" t="s">
+      <c r="H15" s="235" t="s">
         <v>610</v>
       </c>
       <c r="I15" s="194" t="s">
@@ -4718,15 +4708,15 @@
       </c>
       <c r="D16" s="194"/>
       <c r="E16" s="195" t="s">
-        <v>812</v>
-      </c>
-      <c r="F16" s="235" t="s">
+        <v>811</v>
+      </c>
+      <c r="F16" s="234" t="s">
         <v>549</v>
       </c>
       <c r="G16" s="195" t="s">
         <v>669</v>
       </c>
-      <c r="H16" s="235" t="s">
+      <c r="H16" s="234" t="s">
         <v>516</v>
       </c>
       <c r="I16" s="194" t="s">
@@ -4774,15 +4764,15 @@
       </c>
       <c r="D18" s="194"/>
       <c r="E18" s="195" t="s">
-        <v>813</v>
-      </c>
-      <c r="F18" s="235" t="s">
+        <v>812</v>
+      </c>
+      <c r="F18" s="234" t="s">
         <v>549</v>
       </c>
       <c r="G18" s="195" t="s">
         <v>620</v>
       </c>
-      <c r="H18" s="236" t="s">
+      <c r="H18" s="235" t="s">
         <v>610</v>
       </c>
       <c r="I18" s="194" t="s">
@@ -4810,7 +4800,7 @@
       <c r="G19" s="195" t="s">
         <v>621</v>
       </c>
-      <c r="H19" s="235" t="s">
+      <c r="H19" s="234" t="s">
         <v>516</v>
       </c>
       <c r="I19" s="194" t="s">
@@ -4892,7 +4882,7 @@
       <c r="G22" s="195" t="s">
         <v>622</v>
       </c>
-      <c r="H22" s="236" t="s">
+      <c r="H22" s="235" t="s">
         <v>610</v>
       </c>
       <c r="I22" s="194" t="s">
@@ -4992,7 +4982,7 @@
       </c>
       <c r="D26" s="197"/>
       <c r="E26" s="198" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F26" s="197" t="s">
         <v>609</v>
@@ -5000,7 +4990,7 @@
       <c r="G26" s="198" t="s">
         <v>624</v>
       </c>
-      <c r="H26" s="237" t="s">
+      <c r="H26" s="236" t="s">
         <v>516</v>
       </c>
       <c r="I26" s="197" t="s">
@@ -5106,7 +5096,7 @@
       <c r="G30" s="200" t="s">
         <v>670</v>
       </c>
-      <c r="H30" s="238" t="s">
+      <c r="H30" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I30" s="199" t="s">
@@ -5160,7 +5150,7 @@
       <c r="G32" s="200" t="s">
         <v>625</v>
       </c>
-      <c r="H32" s="239" t="s">
+      <c r="H32" s="238" t="s">
         <v>612</v>
       </c>
       <c r="I32" s="199" t="s">
@@ -5182,7 +5172,7 @@
       </c>
       <c r="D33" s="199"/>
       <c r="E33" s="200" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F33" s="199" t="s">
         <v>608</v>
@@ -5190,7 +5180,7 @@
       <c r="G33" s="200" t="s">
         <v>626</v>
       </c>
-      <c r="H33" s="239" t="s">
+      <c r="H33" s="238" t="s">
         <v>612</v>
       </c>
       <c r="I33" s="199" t="s">
@@ -5212,7 +5202,7 @@
       </c>
       <c r="D34" s="199"/>
       <c r="E34" s="200" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F34" s="199" t="s">
         <v>608</v>
@@ -5220,7 +5210,7 @@
       <c r="G34" s="200" t="s">
         <v>627</v>
       </c>
-      <c r="H34" s="238" t="s">
+      <c r="H34" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I34" s="199" t="s">
@@ -5268,7 +5258,7 @@
       </c>
       <c r="D36" s="199"/>
       <c r="E36" s="200" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F36" s="199" t="s">
         <v>609</v>
@@ -5276,7 +5266,7 @@
       <c r="G36" s="200" t="s">
         <v>628</v>
       </c>
-      <c r="H36" s="238" t="s">
+      <c r="H36" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I36" s="199" t="s">
@@ -5304,7 +5294,7 @@
       <c r="G37" s="200" t="s">
         <v>629</v>
       </c>
-      <c r="H37" s="239" t="s">
+      <c r="H37" s="238" t="s">
         <v>612</v>
       </c>
       <c r="I37" s="199" t="s">
@@ -5352,7 +5342,7 @@
       </c>
       <c r="D39" s="199"/>
       <c r="E39" s="200" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F39" s="199" t="s">
         <v>608</v>
@@ -5360,7 +5350,7 @@
       <c r="G39" s="200" t="s">
         <v>630</v>
       </c>
-      <c r="H39" s="238" t="s">
+      <c r="H39" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I39" s="199" t="s">
@@ -5388,7 +5378,7 @@
       <c r="G40" s="200" t="s">
         <v>631</v>
       </c>
-      <c r="H40" s="239" t="s">
+      <c r="H40" s="238" t="s">
         <v>612</v>
       </c>
       <c r="I40" s="199" t="s">
@@ -5442,7 +5432,7 @@
       <c r="G42" s="200" t="s">
         <v>632</v>
       </c>
-      <c r="H42" s="238" t="s">
+      <c r="H42" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I42" s="199" t="s">
@@ -5518,7 +5508,7 @@
         <v>607</v>
       </c>
       <c r="E45" s="200" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F45" s="199" t="s">
         <v>609</v>
@@ -5526,7 +5516,7 @@
       <c r="G45" s="200" t="s">
         <v>633</v>
       </c>
-      <c r="H45" s="238" t="s">
+      <c r="H45" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I45" s="199" t="s">
@@ -5554,7 +5544,7 @@
       <c r="G46" s="200" t="s">
         <v>634</v>
       </c>
-      <c r="H46" s="239" t="s">
+      <c r="H46" s="238" t="s">
         <v>612</v>
       </c>
       <c r="I46" s="199" t="s">
@@ -5576,7 +5566,7 @@
       </c>
       <c r="D47" s="199"/>
       <c r="E47" s="200" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F47" s="199" t="s">
         <v>608</v>
@@ -5610,7 +5600,7 @@
       <c r="G48" s="200" t="s">
         <v>635</v>
       </c>
-      <c r="H48" s="238" t="s">
+      <c r="H48" s="237" t="s">
         <v>516</v>
       </c>
       <c r="I48" s="199" t="s">
@@ -5684,7 +5674,7 @@
       </c>
       <c r="D51" s="203"/>
       <c r="E51" s="204" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F51" s="203" t="s">
         <v>608</v>
@@ -5770,7 +5760,7 @@
       <c r="G54" s="204" t="s">
         <v>636</v>
       </c>
-      <c r="H54" s="240" t="s">
+      <c r="H54" s="239" t="s">
         <v>623</v>
       </c>
       <c r="I54" s="203" t="s">
@@ -5798,7 +5788,7 @@
       <c r="G55" s="204" t="s">
         <v>671</v>
       </c>
-      <c r="H55" s="241" t="s">
+      <c r="H55" s="240" t="s">
         <v>610</v>
       </c>
       <c r="I55" s="203" t="s">
@@ -5846,7 +5836,7 @@
       </c>
       <c r="D57" s="203"/>
       <c r="E57" s="204" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F57" s="203" t="s">
         <v>609</v>
@@ -5854,7 +5844,7 @@
       <c r="G57" s="204" t="s">
         <v>637</v>
       </c>
-      <c r="H57" s="240" t="s">
+      <c r="H57" s="239" t="s">
         <v>516</v>
       </c>
       <c r="I57" s="203" t="s">
@@ -5882,7 +5872,7 @@
       <c r="G58" s="204" t="s">
         <v>638</v>
       </c>
-      <c r="H58" s="241" t="s">
+      <c r="H58" s="240" t="s">
         <v>612</v>
       </c>
       <c r="I58" s="203" t="s">
@@ -5910,7 +5900,7 @@
       <c r="G59" s="204" t="s">
         <v>639</v>
       </c>
-      <c r="H59" s="241" t="s">
+      <c r="H59" s="240" t="s">
         <v>610</v>
       </c>
       <c r="I59" s="203" t="s">
@@ -5932,7 +5922,7 @@
       </c>
       <c r="D60" s="203"/>
       <c r="E60" s="204" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F60" s="203" t="s">
         <v>609</v>
@@ -6295,7 +6285,7 @@
       <c r="B73" s="205" t="s">
         <v>576</v>
       </c>
-      <c r="C73" s="226" t="s">
+      <c r="C73" s="225" t="s">
         <v>712</v>
       </c>
       <c r="D73" s="205" t="s">
@@ -6303,7 +6293,7 @@
       </c>
       <c r="E73" s="205"/>
       <c r="F73" s="205"/>
-      <c r="G73" s="226" t="s">
+      <c r="G73" s="225" t="s">
         <v>738</v>
       </c>
       <c r="H73" s="205" t="s">
@@ -6327,13 +6317,13 @@
         <v>688</v>
       </c>
       <c r="D74" s="206"/>
-      <c r="E74" s="227" t="s">
+      <c r="E74" s="226" t="s">
         <v>726</v>
       </c>
       <c r="F74" s="206" t="s">
         <v>417</v>
       </c>
-      <c r="G74" s="227" t="s">
+      <c r="G74" s="226" t="s">
         <v>739</v>
       </c>
       <c r="H74" s="206" t="s">
@@ -6977,13 +6967,13 @@
         <v>688</v>
       </c>
       <c r="D97" s="209"/>
-      <c r="E97" s="228" t="s">
+      <c r="E97" s="227" t="s">
         <v>712</v>
       </c>
       <c r="F97" s="209" t="s">
         <v>418</v>
       </c>
-      <c r="G97" s="228" t="s">
+      <c r="G97" s="227" t="s">
         <v>751</v>
       </c>
       <c r="H97" s="209" t="s">
@@ -7234,7 +7224,7 @@
       </c>
       <c r="D106" s="212"/>
       <c r="E106" s="213" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F106" s="212" t="s">
         <v>418</v>
@@ -7634,8 +7624,8 @@
       <c r="E120" s="213" t="s">
         <v>737</v>
       </c>
-      <c r="F120" s="242" t="s">
-        <v>783</v>
+      <c r="F120" s="241" t="s">
+        <v>782</v>
       </c>
       <c r="G120" s="213" t="s">
         <v>672</v>
@@ -7662,10 +7652,10 @@
       </c>
       <c r="D121" s="214"/>
       <c r="E121" s="215" t="s">
-        <v>782</v>
-      </c>
-      <c r="F121" s="243" t="s">
-        <v>784</v>
+        <v>781</v>
+      </c>
+      <c r="F121" s="242" t="s">
+        <v>783</v>
       </c>
       <c r="G121" s="215" t="s">
         <v>135</v>
@@ -7694,13 +7684,13 @@
       <c r="E122" s="217" t="s">
         <v>739</v>
       </c>
-      <c r="F122" s="244" t="s">
-        <v>783</v>
+      <c r="F122" s="243" t="s">
+        <v>782</v>
       </c>
       <c r="G122" s="217" t="s">
         <v>690</v>
       </c>
-      <c r="H122" s="244" t="s">
+      <c r="H122" s="243" t="s">
         <v>516</v>
       </c>
       <c r="I122" s="216" t="s">
@@ -7750,7 +7740,7 @@
       <c r="E124" s="219"/>
       <c r="F124" s="219"/>
       <c r="G124" s="218" t="s">
-        <v>780</v>
+        <v>823</v>
       </c>
       <c r="H124" s="219" t="s">
         <v>610</v>
@@ -7774,10 +7764,10 @@
       </c>
       <c r="D125" s="219"/>
       <c r="E125" s="218" t="s">
-        <v>786</v>
-      </c>
-      <c r="F125" s="245" t="s">
-        <v>783</v>
+        <v>785</v>
+      </c>
+      <c r="F125" s="244" t="s">
+        <v>782</v>
       </c>
       <c r="G125" s="218" t="s">
         <v>673</v>
@@ -7804,7 +7794,7 @@
       </c>
       <c r="D126" s="219"/>
       <c r="E126" s="219"/>
-      <c r="F126" s="245"/>
+      <c r="F126" s="244"/>
       <c r="G126" s="219" t="s">
         <v>688</v>
       </c>
@@ -7830,15 +7820,15 @@
         <v>601</v>
       </c>
       <c r="E127" s="218" t="s">
-        <v>787</v>
-      </c>
-      <c r="F127" s="245" t="s">
-        <v>784</v>
+        <v>786</v>
+      </c>
+      <c r="F127" s="244" t="s">
+        <v>783</v>
       </c>
       <c r="G127" s="218" t="s">
         <v>691</v>
       </c>
-      <c r="H127" s="246" t="s">
+      <c r="H127" s="245" t="s">
         <v>538</v>
       </c>
       <c r="I127" s="219" t="s">
@@ -7860,10 +7850,10 @@
       </c>
       <c r="D128" s="219"/>
       <c r="E128" s="218" t="s">
-        <v>788</v>
-      </c>
-      <c r="F128" s="245" t="s">
-        <v>783</v>
+        <v>787</v>
+      </c>
+      <c r="F128" s="244" t="s">
+        <v>782</v>
       </c>
       <c r="G128" s="218" t="s">
         <v>674</v>
@@ -7916,10 +7906,10 @@
         <v>602</v>
       </c>
       <c r="E130" s="218" t="s">
-        <v>789</v>
-      </c>
-      <c r="F130" s="245" t="s">
-        <v>784</v>
+        <v>788</v>
+      </c>
+      <c r="F130" s="244" t="s">
+        <v>783</v>
       </c>
       <c r="G130" s="218" t="s">
         <v>675</v>
@@ -7974,7 +7964,7 @@
       </c>
       <c r="D132" s="219"/>
       <c r="E132" s="218" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F132" s="219" t="s">
         <v>609</v>
@@ -8034,10 +8024,10 @@
       </c>
       <c r="D134" s="219"/>
       <c r="E134" s="218" t="s">
-        <v>791</v>
-      </c>
-      <c r="F134" s="245" t="s">
-        <v>784</v>
+        <v>790</v>
+      </c>
+      <c r="F134" s="244" t="s">
+        <v>783</v>
       </c>
       <c r="G134" s="218" t="s">
         <v>678</v>
@@ -8122,10 +8112,10 @@
       </c>
       <c r="D137" s="219"/>
       <c r="E137" s="218" t="s">
-        <v>792</v>
-      </c>
-      <c r="F137" s="245" t="s">
-        <v>783</v>
+        <v>791</v>
+      </c>
+      <c r="F137" s="244" t="s">
+        <v>782</v>
       </c>
       <c r="G137" s="218" t="s">
         <v>679</v>
@@ -8180,10 +8170,10 @@
         <v>603</v>
       </c>
       <c r="E139" s="218" t="s">
-        <v>793</v>
-      </c>
-      <c r="F139" s="245" t="s">
-        <v>783</v>
+        <v>792</v>
+      </c>
+      <c r="F139" s="244" t="s">
+        <v>782</v>
       </c>
       <c r="G139" s="218" t="s">
         <v>680</v>
@@ -8236,10 +8226,10 @@
       </c>
       <c r="D141" s="219"/>
       <c r="E141" s="218" t="s">
-        <v>794</v>
-      </c>
-      <c r="F141" s="245" t="s">
-        <v>783</v>
+        <v>793</v>
+      </c>
+      <c r="F141" s="244" t="s">
+        <v>782</v>
       </c>
       <c r="G141" s="219" t="s">
         <v>688</v>
@@ -8296,10 +8286,10 @@
         <v>599</v>
       </c>
       <c r="E143" s="218" t="s">
-        <v>795</v>
-      </c>
-      <c r="F143" s="245" t="s">
-        <v>784</v>
+        <v>794</v>
+      </c>
+      <c r="F143" s="244" t="s">
+        <v>783</v>
       </c>
       <c r="G143" s="218" t="s">
         <v>683</v>
@@ -8353,11 +8343,11 @@
         <v>688</v>
       </c>
       <c r="D145" s="220"/>
-      <c r="E145" s="229" t="s">
-        <v>796</v>
-      </c>
-      <c r="F145" s="247" t="s">
-        <v>784</v>
+      <c r="E145" s="228" t="s">
+        <v>795</v>
+      </c>
+      <c r="F145" s="246" t="s">
+        <v>783</v>
       </c>
       <c r="G145" s="220" t="s">
         <v>688</v>
@@ -8381,11 +8371,11 @@
         <v>688</v>
       </c>
       <c r="D146" s="221"/>
-      <c r="E146" s="230" t="s">
-        <v>797</v>
-      </c>
-      <c r="F146" s="248" t="s">
-        <v>783</v>
+      <c r="E146" s="229" t="s">
+        <v>796</v>
+      </c>
+      <c r="F146" s="247" t="s">
+        <v>782</v>
       </c>
       <c r="G146" s="221" t="s">
         <v>688</v>
@@ -8438,10 +8428,10 @@
       </c>
       <c r="D148" s="222"/>
       <c r="E148" s="223" t="s">
-        <v>798</v>
-      </c>
-      <c r="F148" s="231" t="s">
-        <v>784</v>
+        <v>797</v>
+      </c>
+      <c r="F148" s="230" t="s">
+        <v>783</v>
       </c>
       <c r="G148" s="223" t="s">
         <v>684</v>
@@ -8472,8 +8462,8 @@
       <c r="E149" s="223" t="s">
         <v>740</v>
       </c>
-      <c r="F149" s="231" t="s">
-        <v>784</v>
+      <c r="F149" s="230" t="s">
+        <v>783</v>
       </c>
       <c r="G149" s="222" t="s">
         <v>688</v>
@@ -8526,15 +8516,15 @@
       </c>
       <c r="D151" s="222"/>
       <c r="E151" s="223" t="s">
-        <v>799</v>
-      </c>
-      <c r="F151" s="231" t="s">
-        <v>783</v>
+        <v>798</v>
+      </c>
+      <c r="F151" s="230" t="s">
+        <v>782</v>
       </c>
       <c r="G151" s="223" t="s">
         <v>696</v>
       </c>
-      <c r="H151" s="249" t="s">
+      <c r="H151" s="248" t="s">
         <v>697</v>
       </c>
       <c r="I151" s="222" t="s">
@@ -8614,10 +8604,10 @@
       </c>
       <c r="D154" s="222"/>
       <c r="E154" s="223" t="s">
-        <v>800</v>
-      </c>
-      <c r="F154" s="231" t="s">
-        <v>784</v>
+        <v>799</v>
+      </c>
+      <c r="F154" s="230" t="s">
+        <v>783</v>
       </c>
       <c r="G154" s="223" t="s">
         <v>387</v>
@@ -8644,10 +8634,10 @@
       </c>
       <c r="D155" s="222"/>
       <c r="E155" s="223" t="s">
-        <v>801</v>
-      </c>
-      <c r="F155" s="231" t="s">
-        <v>784</v>
+        <v>800</v>
+      </c>
+      <c r="F155" s="230" t="s">
+        <v>783</v>
       </c>
       <c r="G155" s="222" t="s">
         <v>688</v>
@@ -8730,10 +8720,10 @@
       </c>
       <c r="D158" s="222"/>
       <c r="E158" s="223" t="s">
-        <v>802</v>
-      </c>
-      <c r="F158" s="231" t="s">
-        <v>783</v>
+        <v>801</v>
+      </c>
+      <c r="F158" s="230" t="s">
+        <v>782</v>
       </c>
       <c r="G158" s="223" t="s">
         <v>699</v>
@@ -8788,7 +8778,7 @@
       </c>
       <c r="D160" s="222"/>
       <c r="E160" s="223" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F160" s="222" t="s">
         <v>608</v>
@@ -8824,7 +8814,7 @@
       <c r="G161" s="223" t="s">
         <v>700</v>
       </c>
-      <c r="H161" s="249" t="s">
+      <c r="H161" s="248" t="s">
         <v>697</v>
       </c>
       <c r="I161" s="222" t="s">
@@ -11710,12 +11700,12 @@
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18277,12 +18267,12 @@
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G1:G76 E1:E158 C1:C1048576 H12 D70 G78:G1048576 H120 E160:E1048576">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H119 D71:D1048576 G77 H121:H1048576 E159">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24824,22 +24814,22 @@
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D2 H1:H44 F1:F1048576 D4:D150 H46:H1048576 D152:D1048576">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="定期メンテナンス中">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="定期メンテナンス中">
       <formula>NOT(ISERROR(SEARCH("定期メンテナンス中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45 D151">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D45)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBEAA5F-4849-4D5C-8FEE-B34D49BA8BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C774EF99-E12A-46BA-B02F-E7DCE84ED68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7170" yWindow="675" windowWidth="21240" windowHeight="12960" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7335" yWindow="210" windowWidth="21600" windowHeight="11295" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3494" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="683">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1952,24 +1952,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>05:00</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>04:30</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>0430-1100 例行維護中</t>
-  </si>
-  <si>
-    <t>0430-1100 例行維護中</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>'11:54</t>
   </si>
   <si>
@@ -2071,104 +2053,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>'11:21</t>
-  </si>
-  <si>
-    <t>'12:52</t>
-  </si>
-  <si>
-    <t>'14:26</t>
-  </si>
-  <si>
-    <t>'17:20</t>
-  </si>
-  <si>
-    <t>'18:46</t>
-  </si>
-  <si>
-    <t>'20:11</t>
-  </si>
-  <si>
-    <t>'21:44</t>
-  </si>
-  <si>
-    <t>'23:11</t>
-  </si>
-  <si>
-    <t>11:10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>知性森林</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>'01:31</t>
-  </si>
-  <si>
-    <t>'02:58</t>
-  </si>
-  <si>
-    <t>'04:24</t>
-  </si>
-  <si>
-    <t>'05:59</t>
-  </si>
-  <si>
-    <t>'07:26</t>
-  </si>
-  <si>
-    <t>'09:01</t>
-  </si>
-  <si>
-    <t>'10:26</t>
-  </si>
-  <si>
-    <t>'11:53</t>
-  </si>
-  <si>
-    <t>'13:27</t>
-  </si>
-  <si>
-    <t>'15:02</t>
-  </si>
-  <si>
-    <t>'16:28</t>
-  </si>
-  <si>
-    <t>'17:58</t>
-  </si>
-  <si>
     <t>'19:23</t>
   </si>
   <si>
-    <t>'20:48</t>
-  </si>
-  <si>
-    <t>'22:22</t>
-  </si>
-  <si>
-    <t>'23:56</t>
-  </si>
-  <si>
-    <t>'00:59</t>
-  </si>
-  <si>
     <t>'02:28</t>
   </si>
   <si>
-    <t>'03:54</t>
-  </si>
-  <si>
-    <t>'05:19</t>
-  </si>
-  <si>
-    <t>'06:49</t>
-  </si>
-  <si>
-    <t>'08:16</t>
-  </si>
-  <si>
     <t>14:21</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2218,6 +2108,244 @@
   </si>
   <si>
     <t xml:space="preserve"> / 雪原(叛軍駐地)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>'12:42</t>
+  </si>
+  <si>
+    <t>'15:50</t>
+  </si>
+  <si>
+    <t>'18:43</t>
+  </si>
+  <si>
+    <t>'21:46</t>
+  </si>
+  <si>
+    <t>09:42_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:10_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:17</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:16</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>'01:33</t>
+  </si>
+  <si>
+    <t>'03:05</t>
+  </si>
+  <si>
+    <t>'04:40</t>
+  </si>
+  <si>
+    <t>'06:05</t>
+  </si>
+  <si>
+    <t>'07:33</t>
+  </si>
+  <si>
+    <t>'09:00</t>
+  </si>
+  <si>
+    <t>'10:27</t>
+  </si>
+  <si>
+    <t>'11:55</t>
+  </si>
+  <si>
+    <t>'16:23</t>
+  </si>
+  <si>
+    <t>'17:57</t>
+  </si>
+  <si>
+    <t>'20:55</t>
+  </si>
+  <si>
+    <t>'22:20</t>
+  </si>
+  <si>
+    <t>'23:55</t>
+  </si>
+  <si>
+    <t>'01:01</t>
+  </si>
+  <si>
+    <t>'04:03</t>
+  </si>
+  <si>
+    <t>'05:38</t>
+  </si>
+  <si>
+    <t>'07:06</t>
+  </si>
+  <si>
+    <t>'11:29</t>
+  </si>
+  <si>
+    <t>'12:57</t>
+  </si>
+  <si>
+    <t>'14:30</t>
+  </si>
+  <si>
+    <t>'16:02</t>
+  </si>
+  <si>
+    <t>'17:31</t>
+  </si>
+  <si>
+    <t>'19:03</t>
+  </si>
+  <si>
+    <t>'20:36</t>
+  </si>
+  <si>
+    <t>'22:02</t>
+  </si>
+  <si>
+    <t>'23:29</t>
+  </si>
+  <si>
+    <t>'08:36_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:03_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>03:02</t>
+  </si>
+  <si>
+    <t>04:29</t>
+  </si>
+  <si>
+    <t>10:24</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>14:57</t>
+  </si>
+  <si>
+    <t>16:24</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>00:02</t>
+  </si>
+  <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>12:52</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>20:11</t>
+  </si>
+  <si>
+    <t>23:11</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:53_?</t>
+  </si>
+  <si>
+    <t>15:02</t>
+  </si>
+  <si>
+    <t>20:48</t>
+  </si>
+  <si>
+    <t>00:59</t>
+  </si>
+  <si>
+    <t>03:54</t>
+  </si>
+  <si>
+    <t>06:49</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>01:27</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>19:31</t>
+  </si>
+  <si>
+    <t>21:04</t>
+  </si>
+  <si>
+    <t>22:33</t>
+  </si>
+  <si>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>18:46</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>13:27</t>
+  </si>
+  <si>
+    <t>16:28</t>
+  </si>
+  <si>
+    <t>06-11 例行維護中</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3388,6 +3516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEAFB3C-24F9-4C3B-92E1-88934B2FA9FC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J1055"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -3442,8 +3571,12 @@
       <c r="D2" s="118"/>
       <c r="E2" s="118"/>
       <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
+      <c r="G2" s="119" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="118" t="s">
+        <v>177</v>
+      </c>
       <c r="I2" s="118" t="s">
         <v>31</v>
       </c>
@@ -3462,8 +3595,12 @@
       <c r="D3" s="118"/>
       <c r="E3" s="119"/>
       <c r="F3" s="118"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="118"/>
+      <c r="G3" s="119" t="s">
+        <v>669</v>
+      </c>
+      <c r="H3" s="118" t="s">
+        <v>178</v>
+      </c>
       <c r="I3" s="118" t="s">
         <v>23</v>
       </c>
@@ -3502,8 +3639,12 @@
       <c r="D5" s="118"/>
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
+      <c r="G5" s="119" t="s">
+        <v>646</v>
+      </c>
+      <c r="H5" s="118" t="s">
+        <v>178</v>
+      </c>
       <c r="I5" s="118" t="s">
         <v>21</v>
       </c>
@@ -3522,8 +3663,12 @@
       <c r="D6" s="118"/>
       <c r="E6" s="119"/>
       <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="118"/>
+      <c r="G6" s="119" t="s">
+        <v>647</v>
+      </c>
+      <c r="H6" s="118" t="s">
+        <v>177</v>
+      </c>
       <c r="I6" s="118" t="s">
         <v>20</v>
       </c>
@@ -3562,8 +3707,12 @@
       <c r="D8" s="118"/>
       <c r="E8" s="119"/>
       <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
+      <c r="G8" s="119" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I8" s="118" t="s">
         <v>18</v>
       </c>
@@ -3582,8 +3731,12 @@
       <c r="D9" s="118"/>
       <c r="E9" s="119"/>
       <c r="F9" s="118"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="118"/>
+      <c r="G9" s="119" t="s">
+        <v>670</v>
+      </c>
+      <c r="H9" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I9" s="118" t="s">
         <v>17</v>
       </c>
@@ -3602,8 +3755,12 @@
       <c r="D10" s="118"/>
       <c r="E10" s="118"/>
       <c r="F10" s="118"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="118"/>
+      <c r="G10" s="119" t="s">
+        <v>671</v>
+      </c>
+      <c r="H10" s="118" t="s">
+        <v>177</v>
+      </c>
       <c r="I10" s="118" t="s">
         <v>16</v>
       </c>
@@ -3642,8 +3799,12 @@
       <c r="D12" s="118"/>
       <c r="E12" s="119"/>
       <c r="F12" s="118"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="118"/>
+      <c r="G12" s="119" t="s">
+        <v>648</v>
+      </c>
+      <c r="H12" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I12" s="118" t="s">
         <v>14</v>
       </c>
@@ -3662,8 +3823,12 @@
       <c r="D13" s="118"/>
       <c r="E13" s="119"/>
       <c r="F13" s="118"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="118"/>
+      <c r="G13" s="119" t="s">
+        <v>649</v>
+      </c>
+      <c r="H13" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I13" s="118" t="s">
         <v>13</v>
       </c>
@@ -3702,8 +3867,12 @@
       <c r="D15" s="118"/>
       <c r="E15" s="119"/>
       <c r="F15" s="118"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="118"/>
+      <c r="G15" s="119" t="s">
+        <v>650</v>
+      </c>
+      <c r="H15" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I15" s="118" t="s">
         <v>11</v>
       </c>
@@ -3722,8 +3891,12 @@
       <c r="D16" s="118"/>
       <c r="E16" s="119"/>
       <c r="F16" s="118"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="118"/>
+      <c r="G16" s="119" t="s">
+        <v>651</v>
+      </c>
+      <c r="H16" s="118" t="s">
+        <v>177</v>
+      </c>
       <c r="I16" s="118" t="s">
         <v>10</v>
       </c>
@@ -3762,8 +3935,12 @@
       <c r="D18" s="118"/>
       <c r="E18" s="119"/>
       <c r="F18" s="118"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="118"/>
+      <c r="G18" s="119" t="s">
+        <v>652</v>
+      </c>
+      <c r="H18" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I18" s="118" t="s">
         <v>8</v>
       </c>
@@ -3782,8 +3959,12 @@
       <c r="D19" s="118"/>
       <c r="E19" s="118"/>
       <c r="F19" s="118"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="118"/>
+      <c r="G19" s="119" t="s">
+        <v>653</v>
+      </c>
+      <c r="H19" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I19" s="118" t="s">
         <v>7</v>
       </c>
@@ -3822,8 +4003,12 @@
       <c r="D21" s="118"/>
       <c r="E21" s="118"/>
       <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
+      <c r="G21" s="118" t="s">
+        <v>672</v>
+      </c>
+      <c r="H21" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I21" s="118" t="s">
         <v>5</v>
       </c>
@@ -3862,8 +4047,12 @@
       <c r="D23" s="118"/>
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
+      <c r="G23" s="118" t="s">
+        <v>673</v>
+      </c>
+      <c r="H23" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I23" s="118" t="s">
         <v>3</v>
       </c>
@@ -3882,8 +4071,12 @@
       <c r="D24" s="118"/>
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
+      <c r="G24" s="118" t="s">
+        <v>674</v>
+      </c>
+      <c r="H24" s="118" t="s">
+        <v>175</v>
+      </c>
       <c r="I24" s="118" t="s">
         <v>2</v>
       </c>
@@ -3922,8 +4115,12 @@
       <c r="D26" s="121"/>
       <c r="E26" s="122"/>
       <c r="F26" s="121"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="121"/>
+      <c r="G26" s="122" t="s">
+        <v>654</v>
+      </c>
+      <c r="H26" s="121" t="s">
+        <v>178</v>
+      </c>
       <c r="I26" s="121" t="s">
         <v>24</v>
       </c>
@@ -3942,8 +4139,12 @@
       <c r="D27" s="123"/>
       <c r="E27" s="123"/>
       <c r="F27" s="123"/>
-      <c r="G27" s="123"/>
-      <c r="H27" s="123"/>
+      <c r="G27" s="123" t="s">
+        <v>675</v>
+      </c>
+      <c r="H27" s="123" t="s">
+        <v>175</v>
+      </c>
       <c r="I27" s="123" t="s">
         <v>23</v>
       </c>
@@ -3982,8 +4183,12 @@
       <c r="D29" s="123"/>
       <c r="E29" s="123"/>
       <c r="F29" s="123"/>
-      <c r="G29" s="123"/>
-      <c r="H29" s="123"/>
+      <c r="G29" s="123" t="s">
+        <v>668</v>
+      </c>
+      <c r="H29" s="123" t="s">
+        <v>175</v>
+      </c>
       <c r="I29" s="123" t="s">
         <v>21</v>
       </c>
@@ -4002,8 +4207,12 @@
       <c r="D30" s="123"/>
       <c r="E30" s="123"/>
       <c r="F30" s="123"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="123"/>
+      <c r="G30" s="124" t="s">
+        <v>111</v>
+      </c>
+      <c r="H30" s="123" t="s">
+        <v>178</v>
+      </c>
       <c r="I30" s="123" t="s">
         <v>20</v>
       </c>
@@ -4042,8 +4251,12 @@
       <c r="D32" s="123"/>
       <c r="E32" s="123"/>
       <c r="F32" s="123"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="123"/>
+      <c r="G32" s="124" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="123" t="s">
+        <v>175</v>
+      </c>
       <c r="I32" s="123" t="s">
         <v>18</v>
       </c>
@@ -4062,8 +4275,12 @@
       <c r="D33" s="123"/>
       <c r="E33" s="124"/>
       <c r="F33" s="123"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="123"/>
+      <c r="G33" s="124" t="s">
+        <v>655</v>
+      </c>
+      <c r="H33" s="123" t="s">
+        <v>178</v>
+      </c>
       <c r="I33" s="123" t="s">
         <v>17</v>
       </c>
@@ -4266,9 +4483,7 @@
         <v>435</v>
       </c>
       <c r="F43" s="123"/>
-      <c r="G43" s="123" t="s">
-        <v>435</v>
-      </c>
+      <c r="G43" s="123"/>
       <c r="H43" s="123"/>
       <c r="I43" s="123" t="s">
         <v>7</v>
@@ -4292,9 +4507,7 @@
         <v>435</v>
       </c>
       <c r="F44" s="123"/>
-      <c r="G44" s="123" t="s">
-        <v>435</v>
-      </c>
+      <c r="G44" s="123"/>
       <c r="H44" s="123"/>
       <c r="I44" s="123" t="s">
         <v>6</v>
@@ -4422,9 +4635,7 @@
       <c r="D50" s="126"/>
       <c r="E50" s="126"/>
       <c r="F50" s="126"/>
-      <c r="G50" s="126" t="s">
-        <v>435</v>
-      </c>
+      <c r="G50" s="126"/>
       <c r="H50" s="126"/>
       <c r="I50" s="126" t="s">
         <v>24</v>
@@ -4446,9 +4657,7 @@
       <c r="D51" s="127"/>
       <c r="E51" s="128"/>
       <c r="F51" s="127"/>
-      <c r="G51" s="127" t="s">
-        <v>435</v>
-      </c>
+      <c r="G51" s="127"/>
       <c r="H51" s="127"/>
       <c r="I51" s="127" t="s">
         <v>23</v>
@@ -4470,9 +4679,7 @@
       <c r="D52" s="127"/>
       <c r="E52" s="127"/>
       <c r="F52" s="127"/>
-      <c r="G52" s="127" t="s">
-        <v>435</v>
-      </c>
+      <c r="G52" s="127"/>
       <c r="H52" s="127"/>
       <c r="I52" s="127" t="s">
         <v>22</v>
@@ -4496,9 +4703,7 @@
         <v>435</v>
       </c>
       <c r="F53" s="127"/>
-      <c r="G53" s="127" t="s">
-        <v>435</v>
-      </c>
+      <c r="G53" s="127"/>
       <c r="H53" s="127"/>
       <c r="I53" s="127" t="s">
         <v>21</v>
@@ -4514,24 +4719,12 @@
       <c r="B54" s="181" t="s">
         <v>329</v>
       </c>
-      <c r="C54" s="128" t="s">
-        <v>561</v>
-      </c>
-      <c r="D54" s="127" t="s">
-        <v>562</v>
-      </c>
-      <c r="E54" s="127" t="s">
-        <v>46</v>
-      </c>
-      <c r="F54" s="127" t="s">
-        <v>562</v>
-      </c>
-      <c r="G54" s="128" t="s">
-        <v>46</v>
-      </c>
-      <c r="H54" s="127" t="s">
-        <v>562</v>
-      </c>
+      <c r="C54" s="128"/>
+      <c r="D54" s="127"/>
+      <c r="E54" s="127"/>
+      <c r="F54" s="127"/>
+      <c r="G54" s="128"/>
+      <c r="H54" s="127"/>
       <c r="I54" s="127" t="s">
         <v>20</v>
       </c>
@@ -4546,24 +4739,12 @@
       <c r="B55" s="181" t="s">
         <v>329</v>
       </c>
-      <c r="C55" s="128" t="s">
-        <v>560</v>
-      </c>
-      <c r="D55" s="127" t="s">
-        <v>562</v>
-      </c>
-      <c r="E55" s="127" t="s">
-        <v>559</v>
-      </c>
-      <c r="F55" s="127" t="s">
-        <v>562</v>
-      </c>
-      <c r="G55" s="128" t="s">
-        <v>559</v>
-      </c>
-      <c r="H55" s="127" t="s">
-        <v>562</v>
-      </c>
+      <c r="C55" s="128"/>
+      <c r="D55" s="127"/>
+      <c r="E55" s="127"/>
+      <c r="F55" s="127"/>
+      <c r="G55" s="128"/>
+      <c r="H55" s="127"/>
       <c r="I55" s="127" t="s">
         <v>19</v>
       </c>
@@ -4582,19 +4763,19 @@
         <v>554</v>
       </c>
       <c r="D56" s="127" t="s">
-        <v>563</v>
+        <v>682</v>
       </c>
       <c r="E56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="F56" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="G56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="H56" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="I56" s="127" t="s">
         <v>18</v>
@@ -4614,19 +4795,19 @@
         <v>555</v>
       </c>
       <c r="D57" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="E57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="F57" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="G57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="H57" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="I57" s="127" t="s">
         <v>17</v>
@@ -4646,19 +4827,19 @@
         <v>556</v>
       </c>
       <c r="D58" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="E58" s="127" t="s">
         <v>37</v>
       </c>
       <c r="F58" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="G58" s="128" t="s">
         <v>37</v>
       </c>
       <c r="H58" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="I58" s="127" t="s">
         <v>16</v>
@@ -4678,19 +4859,19 @@
         <v>557</v>
       </c>
       <c r="D59" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="E59" s="127" t="s">
         <v>38</v>
       </c>
       <c r="F59" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="G59" s="128" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="I59" s="127" t="s">
         <v>15</v>
@@ -4710,19 +4891,19 @@
         <v>558</v>
       </c>
       <c r="D60" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="E60" s="128" t="s">
         <v>228</v>
       </c>
       <c r="F60" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="G60" s="127" t="s">
         <v>228</v>
       </c>
       <c r="H60" s="127" t="s">
-        <v>562</v>
+        <v>682</v>
       </c>
       <c r="I60" s="127" t="s">
         <v>14</v>
@@ -4741,13 +4922,13 @@
       <c r="C61" s="127"/>
       <c r="D61" s="127"/>
       <c r="E61" s="127" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="F61" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G61" s="128" t="s">
-        <v>597</v>
+        <v>656</v>
       </c>
       <c r="H61" s="127" t="s">
         <v>178</v>
@@ -4771,7 +4952,7 @@
       <c r="E62" s="128"/>
       <c r="F62" s="127"/>
       <c r="G62" s="128" t="s">
-        <v>598</v>
+        <v>657</v>
       </c>
       <c r="H62" s="127" t="s">
         <v>178</v>
@@ -4793,7 +4974,7 @@
       <c r="C63" s="127"/>
       <c r="D63" s="127"/>
       <c r="E63" s="128" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F63" s="127" t="s">
         <v>173</v>
@@ -4815,19 +4996,19 @@
         <v>329</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>629</v>
+        <v>594</v>
       </c>
       <c r="D64" s="163" t="s">
-        <v>632</v>
+        <v>597</v>
       </c>
       <c r="E64" s="127" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="F64" s="127" t="s">
         <v>174</v>
       </c>
       <c r="G64" s="128" t="s">
-        <v>599</v>
+        <v>433</v>
       </c>
       <c r="H64" s="127" t="s">
         <v>175</v>
@@ -4851,7 +5032,7 @@
       <c r="E65" s="128"/>
       <c r="F65" s="127"/>
       <c r="G65" s="127" t="s">
-        <v>583</v>
+        <v>676</v>
       </c>
       <c r="H65" s="127" t="s">
         <v>178</v>
@@ -4873,7 +5054,7 @@
       <c r="C66" s="127"/>
       <c r="D66" s="127"/>
       <c r="E66" s="128" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="F66" s="127" t="s">
         <v>174</v>
@@ -4897,13 +5078,13 @@
       <c r="C67" s="128"/>
       <c r="D67" s="127"/>
       <c r="E67" s="127" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="F67" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G67" s="128" t="s">
-        <v>600</v>
+        <v>658</v>
       </c>
       <c r="H67" s="127" t="s">
         <v>177</v>
@@ -4923,15 +5104,15 @@
         <v>329</v>
       </c>
       <c r="C68" s="128" t="s">
-        <v>630</v>
+        <v>595</v>
       </c>
       <c r="D68" s="164" t="s">
-        <v>633</v>
+        <v>598</v>
       </c>
       <c r="E68" s="128"/>
       <c r="F68" s="127"/>
       <c r="G68" s="127" t="s">
-        <v>601</v>
+        <v>677</v>
       </c>
       <c r="H68" s="127" t="s">
         <v>178</v>
@@ -4953,7 +5134,7 @@
       <c r="C69" s="127"/>
       <c r="D69" s="127"/>
       <c r="E69" s="128" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="F69" s="127" t="s">
         <v>174</v>
@@ -4977,13 +5158,13 @@
       <c r="C70" s="127"/>
       <c r="D70" s="127"/>
       <c r="E70" s="127" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="F70" s="127" t="s">
         <v>174</v>
       </c>
       <c r="G70" s="128" t="s">
-        <v>602</v>
+        <v>659</v>
       </c>
       <c r="H70" s="127" t="s">
         <v>177</v>
@@ -5003,15 +5184,15 @@
         <v>329</v>
       </c>
       <c r="C71" s="128" t="s">
-        <v>631</v>
+        <v>596</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>634</v>
+        <v>599</v>
       </c>
       <c r="E71" s="128"/>
       <c r="F71" s="127"/>
       <c r="G71" s="127" t="s">
-        <v>603</v>
+        <v>290</v>
       </c>
       <c r="H71" s="127" t="s">
         <v>175</v>
@@ -5033,7 +5214,7 @@
       <c r="C72" s="127"/>
       <c r="D72" s="127"/>
       <c r="E72" s="128" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="F72" s="127" t="s">
         <v>174</v>
@@ -5057,13 +5238,13 @@
       <c r="C73" s="149"/>
       <c r="D73" s="129"/>
       <c r="E73" s="129" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="F73" s="129" t="s">
         <v>173</v>
       </c>
       <c r="G73" s="149" t="s">
-        <v>604</v>
+        <v>660</v>
       </c>
       <c r="H73" s="129" t="s">
         <v>175</v>
@@ -5087,7 +5268,7 @@
       <c r="E74" s="150"/>
       <c r="F74" s="130"/>
       <c r="G74" s="150" t="s">
-        <v>589</v>
+        <v>45</v>
       </c>
       <c r="H74" s="130" t="s">
         <v>177</v>
@@ -5109,13 +5290,13 @@
       <c r="C75" s="131"/>
       <c r="D75" s="131"/>
       <c r="E75" s="132" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="F75" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G75" s="131" t="s">
-        <v>607</v>
+        <v>107</v>
       </c>
       <c r="H75" s="131" t="s">
         <v>175</v>
@@ -5137,13 +5318,13 @@
       <c r="C76" s="132"/>
       <c r="D76" s="131"/>
       <c r="E76" s="131" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F76" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G76" s="132" t="s">
-        <v>608</v>
+        <v>187</v>
       </c>
       <c r="H76" s="131" t="s">
         <v>175</v>
@@ -5185,13 +5366,13 @@
       <c r="C78" s="132"/>
       <c r="D78" s="131"/>
       <c r="E78" s="132" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F78" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G78" s="131" t="s">
-        <v>609</v>
+        <v>678</v>
       </c>
       <c r="H78" s="131" t="s">
         <v>175</v>
@@ -5213,13 +5394,13 @@
       <c r="C79" s="131"/>
       <c r="D79" s="131"/>
       <c r="E79" s="131" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="F79" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G79" s="132" t="s">
-        <v>610</v>
+        <v>114</v>
       </c>
       <c r="H79" s="131" t="s">
         <v>177</v>
@@ -5261,13 +5442,13 @@
       <c r="C81" s="132"/>
       <c r="D81" s="131"/>
       <c r="E81" s="132" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="F81" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G81" s="132" t="s">
-        <v>611</v>
+        <v>70</v>
       </c>
       <c r="H81" s="131" t="s">
         <v>178</v>
@@ -5289,7 +5470,7 @@
       <c r="C82" s="132"/>
       <c r="D82" s="131"/>
       <c r="E82" s="131" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="F82" s="131" t="s">
         <v>173</v>
@@ -5311,15 +5492,15 @@
         <v>330</v>
       </c>
       <c r="C83" s="132" t="s">
-        <v>635</v>
+        <v>600</v>
       </c>
       <c r="D83" s="196" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="E83" s="132"/>
       <c r="F83" s="131"/>
       <c r="G83" s="132" t="s">
-        <v>612</v>
+        <v>661</v>
       </c>
       <c r="H83" s="131" t="s">
         <v>177</v>
@@ -5341,13 +5522,13 @@
       <c r="C84" s="131"/>
       <c r="D84" s="131"/>
       <c r="E84" s="132" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F84" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G84" s="131" t="s">
-        <v>613</v>
+        <v>679</v>
       </c>
       <c r="H84" s="131" t="s">
         <v>175</v>
@@ -5369,13 +5550,13 @@
       <c r="C85" s="132"/>
       <c r="D85" s="131"/>
       <c r="E85" s="131" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="F85" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G85" s="132" t="s">
-        <v>614</v>
+        <v>662</v>
       </c>
       <c r="H85" s="131" t="s">
         <v>177</v>
@@ -5395,10 +5576,10 @@
         <v>330</v>
       </c>
       <c r="C86" s="132" t="s">
-        <v>636</v>
+        <v>601</v>
       </c>
       <c r="D86" s="196" t="s">
-        <v>640</v>
+        <v>605</v>
       </c>
       <c r="E86" s="132"/>
       <c r="F86" s="131"/>
@@ -5421,13 +5602,13 @@
       <c r="C87" s="131"/>
       <c r="D87" s="131"/>
       <c r="E87" s="132" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="F87" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G87" s="131" t="s">
-        <v>615</v>
+        <v>680</v>
       </c>
       <c r="H87" s="131" t="s">
         <v>177</v>
@@ -5449,7 +5630,7 @@
       <c r="C88" s="131"/>
       <c r="D88" s="131"/>
       <c r="E88" s="132" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="F88" s="131" t="s">
         <v>174</v>
@@ -5471,19 +5652,19 @@
         <v>330</v>
       </c>
       <c r="C89" s="132" t="s">
-        <v>637</v>
+        <v>602</v>
       </c>
       <c r="D89" s="131" t="s">
-        <v>641</v>
+        <v>606</v>
       </c>
       <c r="E89" s="131" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F89" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G89" s="132" t="s">
-        <v>616</v>
+        <v>663</v>
       </c>
       <c r="H89" s="131" t="s">
         <v>178</v>
@@ -5507,7 +5688,7 @@
       <c r="E90" s="132"/>
       <c r="F90" s="131"/>
       <c r="G90" s="131" t="s">
-        <v>617</v>
+        <v>681</v>
       </c>
       <c r="H90" s="131" t="s">
         <v>175</v>
@@ -5529,13 +5710,13 @@
       <c r="C91" s="131"/>
       <c r="D91" s="131"/>
       <c r="E91" s="132" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F91" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G91" s="132" t="s">
-        <v>618</v>
+        <v>653</v>
       </c>
       <c r="H91" s="131" t="s">
         <v>178</v>
@@ -5577,13 +5758,13 @@
       <c r="C93" s="131"/>
       <c r="D93" s="131"/>
       <c r="E93" s="132" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F93" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G93" s="131" t="s">
-        <v>619</v>
+        <v>281</v>
       </c>
       <c r="H93" s="131" t="s">
         <v>177</v>
@@ -5605,13 +5786,13 @@
       <c r="C94" s="132"/>
       <c r="D94" s="131"/>
       <c r="E94" s="132" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F94" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G94" s="132" t="s">
-        <v>620</v>
+        <v>664</v>
       </c>
       <c r="H94" s="131" t="s">
         <v>177</v>
@@ -5651,19 +5832,19 @@
         <v>330</v>
       </c>
       <c r="C96" s="132" t="s">
-        <v>638</v>
+        <v>603</v>
       </c>
       <c r="D96" s="195" t="s">
-        <v>639</v>
+        <v>604</v>
       </c>
       <c r="E96" s="132" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F96" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G96" s="131" t="s">
-        <v>621</v>
+        <v>419</v>
       </c>
       <c r="H96" s="131" t="s">
         <v>175</v>
@@ -5685,13 +5866,13 @@
       <c r="C97" s="133"/>
       <c r="D97" s="133"/>
       <c r="E97" s="151" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="F97" s="133" t="s">
         <v>174</v>
       </c>
       <c r="G97" s="151" t="s">
-        <v>622</v>
+        <v>135</v>
       </c>
       <c r="H97" s="133" t="s">
         <v>177</v>
@@ -5713,13 +5894,13 @@
       <c r="C98" s="134"/>
       <c r="D98" s="135"/>
       <c r="E98" s="134" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="F98" s="135" t="s">
         <v>174</v>
       </c>
       <c r="G98" s="134" t="s">
-        <v>623</v>
+        <v>665</v>
       </c>
       <c r="H98" s="135" t="s">
         <v>178</v>
@@ -5741,7 +5922,7 @@
       <c r="C99" s="136"/>
       <c r="D99" s="136"/>
       <c r="E99" s="136" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="F99" s="136" t="s">
         <v>174</v>
@@ -5765,13 +5946,13 @@
       <c r="C100" s="137"/>
       <c r="D100" s="136"/>
       <c r="E100" s="137" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="F100" s="136" t="s">
         <v>173</v>
       </c>
       <c r="G100" s="136" t="s">
-        <v>624</v>
+        <v>206</v>
       </c>
       <c r="H100" s="136" t="s">
         <v>177</v>
@@ -5795,7 +5976,7 @@
       <c r="E101" s="137"/>
       <c r="F101" s="136"/>
       <c r="G101" s="137" t="s">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="H101" s="136" t="s">
         <v>175</v>
@@ -5817,7 +5998,7 @@
       <c r="C102" s="136"/>
       <c r="D102" s="136"/>
       <c r="E102" s="136" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F102" s="136" t="s">
         <v>173</v>
@@ -5841,13 +6022,13 @@
       <c r="C103" s="137"/>
       <c r="D103" s="136"/>
       <c r="E103" s="137" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="F103" s="136" t="s">
         <v>173</v>
       </c>
       <c r="G103" s="136" t="s">
-        <v>626</v>
+        <v>140</v>
       </c>
       <c r="H103" s="136" t="s">
         <v>175</v>
@@ -5871,7 +6052,7 @@
       <c r="E104" s="136"/>
       <c r="F104" s="136"/>
       <c r="G104" s="137" t="s">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="H104" s="136" t="s">
         <v>175</v>
@@ -5893,7 +6074,7 @@
       <c r="C105" s="136"/>
       <c r="D105" s="136"/>
       <c r="E105" s="137" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F105" s="136" t="s">
         <v>173</v>
@@ -5919,7 +6100,7 @@
       <c r="E106" s="137"/>
       <c r="F106" s="136"/>
       <c r="G106" s="137" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="H106" s="136" t="s">
         <v>175</v>
@@ -5942,8 +6123,12 @@
       <c r="D107" s="136"/>
       <c r="E107" s="136"/>
       <c r="F107" s="136"/>
-      <c r="G107" s="136"/>
-      <c r="H107" s="136"/>
+      <c r="G107" s="137" t="s">
+        <v>611</v>
+      </c>
+      <c r="H107" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I107" s="136" t="s">
         <v>15</v>
       </c>
@@ -5961,10 +6146,10 @@
       <c r="C108" s="136"/>
       <c r="D108" s="136"/>
       <c r="E108" s="137" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="F108" s="165" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G108" s="137"/>
       <c r="H108" s="173"/>
@@ -5987,10 +6172,10 @@
       <c r="E109" s="137"/>
       <c r="F109" s="136"/>
       <c r="G109" s="137" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="H109" s="173" t="s">
-        <v>606</v>
+        <v>175</v>
       </c>
       <c r="I109" s="136" t="s">
         <v>13</v>
@@ -6010,8 +6195,12 @@
       <c r="D110" s="136"/>
       <c r="E110" s="136"/>
       <c r="F110" s="136"/>
-      <c r="G110" s="136"/>
-      <c r="H110" s="136"/>
+      <c r="G110" s="136" t="s">
+        <v>607</v>
+      </c>
+      <c r="H110" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I110" s="136" t="s">
         <v>12</v>
       </c>
@@ -6050,8 +6239,12 @@
       <c r="D112" s="136"/>
       <c r="E112" s="137"/>
       <c r="F112" s="136"/>
-      <c r="G112" s="137"/>
-      <c r="H112" s="136"/>
+      <c r="G112" s="137" t="s">
+        <v>613</v>
+      </c>
+      <c r="H112" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I112" s="136" t="s">
         <v>10</v>
       </c>
@@ -6070,8 +6263,12 @@
       <c r="D113" s="136"/>
       <c r="E113" s="136"/>
       <c r="F113" s="136"/>
-      <c r="G113" s="136"/>
-      <c r="H113" s="136"/>
+      <c r="G113" s="136" t="s">
+        <v>608</v>
+      </c>
+      <c r="H113" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I113" s="136" t="s">
         <v>9</v>
       </c>
@@ -6110,8 +6307,12 @@
       <c r="D115" s="136"/>
       <c r="E115" s="137"/>
       <c r="F115" s="136"/>
-      <c r="G115" s="137"/>
-      <c r="H115" s="136"/>
+      <c r="G115" s="137" t="s">
+        <v>614</v>
+      </c>
+      <c r="H115" s="136" t="s">
+        <v>175</v>
+      </c>
       <c r="I115" s="136" t="s">
         <v>7</v>
       </c>
@@ -6130,8 +6331,12 @@
       <c r="D116" s="136"/>
       <c r="E116" s="136"/>
       <c r="F116" s="136"/>
-      <c r="G116" s="136"/>
-      <c r="H116" s="136"/>
+      <c r="G116" s="136" t="s">
+        <v>609</v>
+      </c>
+      <c r="H116" s="136" t="s">
+        <v>175</v>
+      </c>
       <c r="I116" s="136" t="s">
         <v>6</v>
       </c>
@@ -6170,8 +6375,12 @@
       <c r="D118" s="136"/>
       <c r="E118" s="137"/>
       <c r="F118" s="136"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="136"/>
+      <c r="G118" s="137" t="s">
+        <v>615</v>
+      </c>
+      <c r="H118" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I118" s="136" t="s">
         <v>4</v>
       </c>
@@ -6190,8 +6399,12 @@
       <c r="D119" s="136"/>
       <c r="E119" s="136"/>
       <c r="F119" s="136"/>
-      <c r="G119" s="136"/>
-      <c r="H119" s="136"/>
+      <c r="G119" s="136" t="s">
+        <v>610</v>
+      </c>
+      <c r="H119" s="136" t="s">
+        <v>178</v>
+      </c>
       <c r="I119" s="136" t="s">
         <v>3</v>
       </c>
@@ -6230,8 +6443,12 @@
       <c r="D121" s="138"/>
       <c r="E121" s="139"/>
       <c r="F121" s="138"/>
-      <c r="G121" s="139"/>
-      <c r="H121" s="138"/>
+      <c r="G121" s="139" t="s">
+        <v>616</v>
+      </c>
+      <c r="H121" s="138" t="s">
+        <v>177</v>
+      </c>
       <c r="I121" s="138" t="s">
         <v>1</v>
       </c>
@@ -6250,8 +6467,12 @@
       <c r="D122" s="140"/>
       <c r="E122" s="141"/>
       <c r="F122" s="140"/>
-      <c r="G122" s="141"/>
-      <c r="H122" s="140"/>
+      <c r="G122" s="141" t="s">
+        <v>584</v>
+      </c>
+      <c r="H122" s="140" t="s">
+        <v>177</v>
+      </c>
       <c r="I122" s="140" t="s">
         <v>24</v>
       </c>
@@ -6270,8 +6491,12 @@
       <c r="D123" s="143"/>
       <c r="E123" s="143"/>
       <c r="F123" s="143"/>
-      <c r="G123" s="143"/>
-      <c r="H123" s="143"/>
+      <c r="G123" s="143" t="s">
+        <v>618</v>
+      </c>
+      <c r="H123" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I123" s="143" t="s">
         <v>23</v>
       </c>
@@ -6310,8 +6535,12 @@
       <c r="D125" s="143"/>
       <c r="E125" s="142"/>
       <c r="F125" s="143"/>
-      <c r="G125" s="142"/>
-      <c r="H125" s="143"/>
+      <c r="G125" s="142" t="s">
+        <v>619</v>
+      </c>
+      <c r="H125" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I125" s="143" t="s">
         <v>21</v>
       </c>
@@ -6330,8 +6559,12 @@
       <c r="D126" s="143"/>
       <c r="E126" s="143"/>
       <c r="F126" s="143"/>
-      <c r="G126" s="143"/>
-      <c r="H126" s="143"/>
+      <c r="G126" s="143" t="s">
+        <v>620</v>
+      </c>
+      <c r="H126" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I126" s="143" t="s">
         <v>20</v>
       </c>
@@ -6370,8 +6603,12 @@
       <c r="D128" s="143"/>
       <c r="E128" s="142"/>
       <c r="F128" s="143"/>
-      <c r="G128" s="142"/>
-      <c r="H128" s="143"/>
+      <c r="G128" s="142" t="s">
+        <v>621</v>
+      </c>
+      <c r="H128" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I128" s="143" t="s">
         <v>18</v>
       </c>
@@ -6390,8 +6627,12 @@
       <c r="D129" s="143"/>
       <c r="E129" s="142"/>
       <c r="F129" s="143"/>
-      <c r="G129" s="143"/>
-      <c r="H129" s="143"/>
+      <c r="G129" s="143" t="s">
+        <v>622</v>
+      </c>
+      <c r="H129" s="143" t="s">
+        <v>175</v>
+      </c>
       <c r="I129" s="143" t="s">
         <v>17</v>
       </c>
@@ -6430,8 +6671,12 @@
       <c r="D131" s="143"/>
       <c r="E131" s="143"/>
       <c r="F131" s="143"/>
-      <c r="G131" s="142"/>
-      <c r="H131" s="143"/>
+      <c r="G131" s="142" t="s">
+        <v>623</v>
+      </c>
+      <c r="H131" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I131" s="143" t="s">
         <v>15</v>
       </c>
@@ -6450,8 +6695,12 @@
       <c r="D132" s="143"/>
       <c r="E132" s="142"/>
       <c r="F132" s="143"/>
-      <c r="G132" s="143"/>
-      <c r="H132" s="143"/>
+      <c r="G132" s="143" t="s">
+        <v>624</v>
+      </c>
+      <c r="H132" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I132" s="143" t="s">
         <v>14</v>
       </c>
@@ -6470,8 +6719,12 @@
       <c r="D133" s="143"/>
       <c r="E133" s="142"/>
       <c r="F133" s="143"/>
-      <c r="G133" s="142"/>
-      <c r="H133" s="143"/>
+      <c r="G133" s="142" t="s">
+        <v>625</v>
+      </c>
+      <c r="H133" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I133" s="143" t="s">
         <v>13</v>
       </c>
@@ -6510,8 +6763,12 @@
       <c r="D135" s="143"/>
       <c r="E135" s="143"/>
       <c r="F135" s="143"/>
-      <c r="G135" s="143"/>
-      <c r="H135" s="143"/>
+      <c r="G135" s="143" t="s">
+        <v>560</v>
+      </c>
+      <c r="H135" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I135" s="143" t="s">
         <v>11</v>
       </c>
@@ -6530,8 +6787,12 @@
       <c r="D136" s="143"/>
       <c r="E136" s="142"/>
       <c r="F136" s="143"/>
-      <c r="G136" s="142"/>
-      <c r="H136" s="143"/>
+      <c r="G136" s="142" t="s">
+        <v>561</v>
+      </c>
+      <c r="H136" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I136" s="143" t="s">
         <v>10</v>
       </c>
@@ -6570,8 +6831,12 @@
       <c r="D138" s="143"/>
       <c r="E138" s="143"/>
       <c r="F138" s="143"/>
-      <c r="G138" s="143"/>
-      <c r="H138" s="143"/>
+      <c r="G138" s="143" t="s">
+        <v>626</v>
+      </c>
+      <c r="H138" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I138" s="143">
         <v>16</v>
       </c>
@@ -6590,8 +6855,12 @@
       <c r="D139" s="143"/>
       <c r="E139" s="142"/>
       <c r="F139" s="143"/>
-      <c r="G139" s="142"/>
-      <c r="H139" s="143"/>
+      <c r="G139" s="142" t="s">
+        <v>627</v>
+      </c>
+      <c r="H139" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I139" s="143" t="s">
         <v>7</v>
       </c>
@@ -6630,8 +6899,12 @@
       <c r="D141" s="143"/>
       <c r="E141" s="142"/>
       <c r="F141" s="143"/>
-      <c r="G141" s="143"/>
-      <c r="H141" s="143"/>
+      <c r="G141" s="143" t="s">
+        <v>592</v>
+      </c>
+      <c r="H141" s="143" t="s">
+        <v>177</v>
+      </c>
       <c r="I141" s="143" t="s">
         <v>5</v>
       </c>
@@ -6650,8 +6923,12 @@
       <c r="D142" s="143"/>
       <c r="E142" s="142"/>
       <c r="F142" s="143"/>
-      <c r="G142" s="142"/>
-      <c r="H142" s="143"/>
+      <c r="G142" s="142" t="s">
+        <v>628</v>
+      </c>
+      <c r="H142" s="143" t="s">
+        <v>175</v>
+      </c>
       <c r="I142" s="143" t="s">
         <v>4</v>
       </c>
@@ -6690,8 +6967,12 @@
       <c r="D144" s="143"/>
       <c r="E144" s="143"/>
       <c r="F144" s="143"/>
-      <c r="G144" s="142"/>
-      <c r="H144" s="143"/>
+      <c r="G144" s="142" t="s">
+        <v>629</v>
+      </c>
+      <c r="H144" s="143" t="s">
+        <v>178</v>
+      </c>
       <c r="I144" s="143" t="s">
         <v>2</v>
       </c>
@@ -6710,8 +6991,12 @@
       <c r="D145" s="144"/>
       <c r="E145" s="152"/>
       <c r="F145" s="144"/>
-      <c r="G145" s="144"/>
-      <c r="H145" s="144"/>
+      <c r="G145" s="144" t="s">
+        <v>630</v>
+      </c>
+      <c r="H145" s="144" t="s">
+        <v>175</v>
+      </c>
       <c r="I145" s="144" t="s">
         <v>1</v>
       </c>
@@ -6750,8 +7035,12 @@
       <c r="D147" s="146"/>
       <c r="E147" s="146"/>
       <c r="F147" s="146"/>
-      <c r="G147" s="147"/>
-      <c r="H147" s="146"/>
+      <c r="G147" s="147" t="s">
+        <v>631</v>
+      </c>
+      <c r="H147" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I147" s="146" t="s">
         <v>23</v>
       </c>
@@ -6770,8 +7059,12 @@
       <c r="D148" s="146"/>
       <c r="E148" s="147"/>
       <c r="F148" s="146"/>
-      <c r="G148" s="147"/>
-      <c r="H148" s="146"/>
+      <c r="G148" s="147" t="s">
+        <v>593</v>
+      </c>
+      <c r="H148" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I148" s="146" t="s">
         <v>22</v>
       </c>
@@ -6810,8 +7103,12 @@
       <c r="D150" s="146"/>
       <c r="E150" s="146"/>
       <c r="F150" s="146"/>
-      <c r="G150" s="147"/>
-      <c r="H150" s="146"/>
+      <c r="G150" s="147" t="s">
+        <v>632</v>
+      </c>
+      <c r="H150" s="146" t="s">
+        <v>175</v>
+      </c>
       <c r="I150" s="146" t="s">
         <v>20</v>
       </c>
@@ -6830,8 +7127,12 @@
       <c r="D151" s="146"/>
       <c r="E151" s="147"/>
       <c r="F151" s="146"/>
-      <c r="G151" s="147"/>
-      <c r="H151" s="146"/>
+      <c r="G151" s="147" t="s">
+        <v>633</v>
+      </c>
+      <c r="H151" s="146" t="s">
+        <v>175</v>
+      </c>
       <c r="I151" s="146" t="s">
         <v>19</v>
       </c>
@@ -6870,8 +7171,12 @@
       <c r="D153" s="146"/>
       <c r="E153" s="146"/>
       <c r="F153" s="146"/>
-      <c r="G153" s="147"/>
-      <c r="H153" s="146"/>
+      <c r="G153" s="147" t="s">
+        <v>634</v>
+      </c>
+      <c r="H153" s="146" t="s">
+        <v>175</v>
+      </c>
       <c r="I153" s="146" t="s">
         <v>17</v>
       </c>
@@ -6890,8 +7195,12 @@
       <c r="D154" s="146"/>
       <c r="E154" s="147"/>
       <c r="F154" s="146"/>
-      <c r="G154" s="147"/>
-      <c r="H154" s="146"/>
+      <c r="G154" s="147" t="s">
+        <v>644</v>
+      </c>
+      <c r="H154" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I154" s="146" t="s">
         <v>16</v>
       </c>
@@ -6930,8 +7239,12 @@
       <c r="D156" s="146"/>
       <c r="E156" s="146"/>
       <c r="F156" s="146"/>
-      <c r="G156" s="147"/>
-      <c r="H156" s="146"/>
+      <c r="G156" s="147" t="s">
+        <v>645</v>
+      </c>
+      <c r="H156" s="146" t="s">
+        <v>175</v>
+      </c>
       <c r="I156" s="146" t="s">
         <v>14</v>
       </c>
@@ -6950,8 +7263,12 @@
       <c r="D157" s="146"/>
       <c r="E157" s="146"/>
       <c r="F157" s="146"/>
-      <c r="G157" s="147"/>
-      <c r="H157" s="146"/>
+      <c r="G157" s="147" t="s">
+        <v>635</v>
+      </c>
+      <c r="H157" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I157" s="146" t="s">
         <v>13</v>
       </c>
@@ -6970,8 +7287,12 @@
       <c r="D158" s="146"/>
       <c r="E158" s="147"/>
       <c r="F158" s="146"/>
-      <c r="G158" s="147"/>
-      <c r="H158" s="146"/>
+      <c r="G158" s="147" t="s">
+        <v>636</v>
+      </c>
+      <c r="H158" s="146" t="s">
+        <v>178</v>
+      </c>
       <c r="I158" s="146" t="s">
         <v>12</v>
       </c>
@@ -7010,8 +7331,12 @@
       <c r="D160" s="146"/>
       <c r="E160" s="147"/>
       <c r="F160" s="146"/>
-      <c r="G160" s="147"/>
-      <c r="H160" s="146"/>
+      <c r="G160" s="147" t="s">
+        <v>637</v>
+      </c>
+      <c r="H160" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I160" s="146" t="s">
         <v>10</v>
       </c>
@@ -7050,8 +7375,12 @@
       <c r="D162" s="146"/>
       <c r="E162" s="146"/>
       <c r="F162" s="146"/>
-      <c r="G162" s="146"/>
-      <c r="H162" s="146"/>
+      <c r="G162" s="146" t="s">
+        <v>638</v>
+      </c>
+      <c r="H162" s="146" t="s">
+        <v>178</v>
+      </c>
       <c r="I162" s="146" t="s">
         <v>8</v>
       </c>
@@ -7070,8 +7399,12 @@
       <c r="D163" s="146"/>
       <c r="E163" s="146"/>
       <c r="F163" s="146"/>
-      <c r="G163" s="146"/>
-      <c r="H163" s="146"/>
+      <c r="G163" s="146" t="s">
+        <v>639</v>
+      </c>
+      <c r="H163" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I163" s="146" t="s">
         <v>7</v>
       </c>
@@ -7110,8 +7443,12 @@
       <c r="D165" s="146"/>
       <c r="E165" s="146"/>
       <c r="F165" s="146"/>
-      <c r="G165" s="147"/>
-      <c r="H165" s="146"/>
+      <c r="G165" s="147" t="s">
+        <v>640</v>
+      </c>
+      <c r="H165" s="146" t="s">
+        <v>178</v>
+      </c>
       <c r="I165" s="146" t="s">
         <v>5</v>
       </c>
@@ -7130,8 +7467,12 @@
       <c r="D166" s="146"/>
       <c r="E166" s="146"/>
       <c r="F166" s="146"/>
-      <c r="G166" s="147"/>
-      <c r="H166" s="146"/>
+      <c r="G166" s="147" t="s">
+        <v>641</v>
+      </c>
+      <c r="H166" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I166" s="146" t="s">
         <v>4</v>
       </c>
@@ -7170,8 +7511,12 @@
       <c r="D168" s="146"/>
       <c r="E168" s="146"/>
       <c r="F168" s="146"/>
-      <c r="G168" s="147"/>
-      <c r="H168" s="146"/>
+      <c r="G168" s="147" t="s">
+        <v>642</v>
+      </c>
+      <c r="H168" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I168" s="146" t="s">
         <v>2</v>
       </c>
@@ -7190,8 +7535,12 @@
       <c r="D169" s="146"/>
       <c r="E169" s="146"/>
       <c r="F169" s="146"/>
-      <c r="G169" s="146"/>
-      <c r="H169" s="146"/>
+      <c r="G169" s="146" t="s">
+        <v>643</v>
+      </c>
+      <c r="H169" s="146" t="s">
+        <v>177</v>
+      </c>
       <c r="I169" s="146" t="s">
         <v>1</v>
       </c>
@@ -9858,7 +10207,13 @@
       <c r="B1055" s="194"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
+  <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}">
+    <filterColumn colId="5">
+      <customFilters>
+        <customFilter operator="notEqual" val="*''*"/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
     <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="'">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C774EF99-E12A-46BA-B02F-E7DCE84ED68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF74DA0-7E50-4963-B003-EE816FB9A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7335" yWindow="210" windowWidth="21600" windowHeight="11295" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="timeList" sheetId="13" r:id="rId1"/>
+    <sheet name="timeList_ZH" sheetId="13" r:id="rId1"/>
     <sheet name="timeList0212-0225" sheetId="15" r:id="rId2"/>
     <sheet name="timeList0204-0211" sheetId="14" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">timeList!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">timeList_ZH!$B$1:$H$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'timeList0204-0211'!$B$1:$H$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'timeList0212-0225'!$B$1:$H$169</definedName>
   </definedNames>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF74DA0-7E50-4963-B003-EE816FB9A5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFECEC3-6E2C-456C-AE30-0A98CA838D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7335" yWindow="210" windowWidth="21600" windowHeight="11295" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="686">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1952,99 +1952,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>'11:54</t>
-  </si>
-  <si>
-    <t>'13:22</t>
-  </si>
-  <si>
-    <t>'14:51</t>
-  </si>
-  <si>
-    <t>'16:22</t>
-  </si>
-  <si>
-    <t>'17:49</t>
-  </si>
-  <si>
-    <t>'19:19</t>
-  </si>
-  <si>
-    <t>'20:40</t>
-  </si>
-  <si>
-    <t>'22:11</t>
-  </si>
-  <si>
-    <t>'23:45</t>
-  </si>
-  <si>
-    <t>'01:04</t>
-  </si>
-  <si>
-    <t>'02:37</t>
-  </si>
-  <si>
-    <t>'04:06</t>
-  </si>
-  <si>
-    <t>'05:32</t>
-  </si>
-  <si>
-    <t>'07:02</t>
-  </si>
-  <si>
-    <t>'08:30</t>
-  </si>
-  <si>
-    <t>'10:01</t>
-  </si>
-  <si>
-    <t>'11:32</t>
-  </si>
-  <si>
-    <t>'13:02</t>
-  </si>
-  <si>
-    <t>'14:27</t>
-  </si>
-  <si>
-    <t>'15:54</t>
-  </si>
-  <si>
-    <t>'17:29</t>
-  </si>
-  <si>
-    <t>'19:01</t>
-  </si>
-  <si>
-    <t>'20:32</t>
-  </si>
-  <si>
-    <t>'22:00</t>
-  </si>
-  <si>
-    <t>'23:25</t>
-  </si>
-  <si>
-    <t>'00:00</t>
-  </si>
-  <si>
-    <t>'01:28</t>
-  </si>
-  <si>
-    <t>'02:54</t>
-  </si>
-  <si>
-    <t>'04:20</t>
-  </si>
-  <si>
-    <t>'05:54</t>
-  </si>
-  <si>
-    <t>'07:19</t>
-  </si>
-  <si>
     <t>10:29</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2053,12 +1960,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>'19:23</t>
-  </si>
-  <si>
-    <t>'02:28</t>
-  </si>
-  <si>
     <t>14:21</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2111,18 +2012,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>'12:42</t>
-  </si>
-  <si>
-    <t>'15:50</t>
-  </si>
-  <si>
-    <t>'18:43</t>
-  </si>
-  <si>
-    <t>'21:46</t>
-  </si>
-  <si>
     <t>09:42_?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2151,88 +2040,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>'01:33</t>
-  </si>
-  <si>
-    <t>'03:05</t>
-  </si>
-  <si>
-    <t>'04:40</t>
-  </si>
-  <si>
-    <t>'06:05</t>
-  </si>
-  <si>
-    <t>'07:33</t>
-  </si>
-  <si>
-    <t>'09:00</t>
-  </si>
-  <si>
-    <t>'10:27</t>
-  </si>
-  <si>
-    <t>'11:55</t>
-  </si>
-  <si>
-    <t>'16:23</t>
-  </si>
-  <si>
-    <t>'17:57</t>
-  </si>
-  <si>
-    <t>'20:55</t>
-  </si>
-  <si>
-    <t>'22:20</t>
-  </si>
-  <si>
-    <t>'23:55</t>
-  </si>
-  <si>
-    <t>'01:01</t>
-  </si>
-  <si>
-    <t>'04:03</t>
-  </si>
-  <si>
-    <t>'05:38</t>
-  </si>
-  <si>
-    <t>'07:06</t>
-  </si>
-  <si>
-    <t>'11:29</t>
-  </si>
-  <si>
-    <t>'12:57</t>
-  </si>
-  <si>
-    <t>'14:30</t>
-  </si>
-  <si>
-    <t>'16:02</t>
-  </si>
-  <si>
-    <t>'17:31</t>
-  </si>
-  <si>
-    <t>'19:03</t>
-  </si>
-  <si>
-    <t>'20:36</t>
-  </si>
-  <si>
-    <t>'22:02</t>
-  </si>
-  <si>
-    <t>'23:29</t>
-  </si>
-  <si>
-    <t>'08:36_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>10:03_?</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2303,49 +2110,327 @@
     <t>06:49</t>
   </si>
   <si>
+    <t>01:27</t>
+  </si>
+  <si>
+    <t>07:31</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>06-11 例行維護中</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:51</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:49</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:45</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02:37</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15:54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12:42</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>15:50</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>18:43</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21:46</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:33</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:33</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13:22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16:23</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:23</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:55</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:29</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21:04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:33</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:36</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>03:05</t>
-  </si>
-  <si>
-    <t>01:27</t>
-  </si>
-  <si>
-    <t>07:31</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>19:31</t>
-  </si>
-  <si>
-    <t>21:04</t>
-  </si>
-  <si>
-    <t>22:33</t>
-  </si>
-  <si>
-    <t>01:36</t>
-  </si>
-  <si>
-    <t>15:54</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>18:46</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21:44</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:31</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>04:24</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>10:26</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>13:27</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>16:28</t>
-  </si>
-  <si>
-    <t>06-11 例行維護中</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02:28</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>00:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>06:05</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:55</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:57</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:55</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:38</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:36_?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:29</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>12:57</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:30</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:03</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:36</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>16:22</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:19</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:11</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>01:04</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>11:32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>13:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>14:27</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>17:29</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19:01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>20:32</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>22:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>02:54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:54</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:19</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2591,7 +2676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3181,6 +3266,9 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="7" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3596,7 +3684,7 @@
       <c r="E3" s="119"/>
       <c r="F3" s="118"/>
       <c r="G3" s="119" t="s">
-        <v>669</v>
+        <v>604</v>
       </c>
       <c r="H3" s="118" t="s">
         <v>178</v>
@@ -3640,7 +3728,7 @@
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
       <c r="G5" s="119" t="s">
-        <v>646</v>
+        <v>582</v>
       </c>
       <c r="H5" s="118" t="s">
         <v>178</v>
@@ -3664,7 +3752,7 @@
       <c r="E6" s="119"/>
       <c r="F6" s="118"/>
       <c r="G6" s="119" t="s">
-        <v>647</v>
+        <v>583</v>
       </c>
       <c r="H6" s="118" t="s">
         <v>177</v>
@@ -3732,7 +3820,7 @@
       <c r="E9" s="119"/>
       <c r="F9" s="118"/>
       <c r="G9" s="119" t="s">
-        <v>670</v>
+        <v>605</v>
       </c>
       <c r="H9" s="118" t="s">
         <v>175</v>
@@ -3756,7 +3844,7 @@
       <c r="E10" s="118"/>
       <c r="F10" s="118"/>
       <c r="G10" s="119" t="s">
-        <v>671</v>
+        <v>606</v>
       </c>
       <c r="H10" s="118" t="s">
         <v>177</v>
@@ -3800,7 +3888,7 @@
       <c r="E12" s="119"/>
       <c r="F12" s="118"/>
       <c r="G12" s="119" t="s">
-        <v>648</v>
+        <v>584</v>
       </c>
       <c r="H12" s="118" t="s">
         <v>175</v>
@@ -3824,7 +3912,7 @@
       <c r="E13" s="119"/>
       <c r="F13" s="118"/>
       <c r="G13" s="119" t="s">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="H13" s="118" t="s">
         <v>175</v>
@@ -3868,7 +3956,7 @@
       <c r="E15" s="119"/>
       <c r="F15" s="118"/>
       <c r="G15" s="119" t="s">
-        <v>650</v>
+        <v>586</v>
       </c>
       <c r="H15" s="118" t="s">
         <v>175</v>
@@ -3892,7 +3980,7 @@
       <c r="E16" s="119"/>
       <c r="F16" s="118"/>
       <c r="G16" s="119" t="s">
-        <v>651</v>
+        <v>587</v>
       </c>
       <c r="H16" s="118" t="s">
         <v>177</v>
@@ -3936,7 +4024,7 @@
       <c r="E18" s="119"/>
       <c r="F18" s="118"/>
       <c r="G18" s="119" t="s">
-        <v>652</v>
+        <v>588</v>
       </c>
       <c r="H18" s="118" t="s">
         <v>175</v>
@@ -3960,7 +4048,7 @@
       <c r="E19" s="118"/>
       <c r="F19" s="118"/>
       <c r="G19" s="119" t="s">
-        <v>653</v>
+        <v>589</v>
       </c>
       <c r="H19" s="118" t="s">
         <v>175</v>
@@ -4003,8 +4091,8 @@
       <c r="D21" s="118"/>
       <c r="E21" s="118"/>
       <c r="F21" s="118"/>
-      <c r="G21" s="118" t="s">
-        <v>672</v>
+      <c r="G21" s="119" t="s">
+        <v>635</v>
       </c>
       <c r="H21" s="118" t="s">
         <v>175</v>
@@ -4047,8 +4135,8 @@
       <c r="D23" s="118"/>
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
-      <c r="G23" s="118" t="s">
-        <v>673</v>
+      <c r="G23" s="119" t="s">
+        <v>636</v>
       </c>
       <c r="H23" s="118" t="s">
         <v>175</v>
@@ -4071,8 +4159,8 @@
       <c r="D24" s="118"/>
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
-      <c r="G24" s="118" t="s">
-        <v>674</v>
+      <c r="G24" s="119" t="s">
+        <v>637</v>
       </c>
       <c r="H24" s="118" t="s">
         <v>175</v>
@@ -4116,7 +4204,7 @@
       <c r="E26" s="122"/>
       <c r="F26" s="121"/>
       <c r="G26" s="122" t="s">
-        <v>654</v>
+        <v>590</v>
       </c>
       <c r="H26" s="121" t="s">
         <v>178</v>
@@ -4139,8 +4227,8 @@
       <c r="D27" s="123"/>
       <c r="E27" s="123"/>
       <c r="F27" s="123"/>
-      <c r="G27" s="123" t="s">
-        <v>675</v>
+      <c r="G27" s="124" t="s">
+        <v>638</v>
       </c>
       <c r="H27" s="123" t="s">
         <v>175</v>
@@ -4183,8 +4271,8 @@
       <c r="D29" s="123"/>
       <c r="E29" s="123"/>
       <c r="F29" s="123"/>
-      <c r="G29" s="123" t="s">
-        <v>668</v>
+      <c r="G29" s="124" t="s">
+        <v>639</v>
       </c>
       <c r="H29" s="123" t="s">
         <v>175</v>
@@ -4276,7 +4364,7 @@
       <c r="E33" s="124"/>
       <c r="F33" s="123"/>
       <c r="G33" s="124" t="s">
-        <v>655</v>
+        <v>591</v>
       </c>
       <c r="H33" s="123" t="s">
         <v>178</v>
@@ -4763,19 +4851,19 @@
         <v>554</v>
       </c>
       <c r="D56" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="E56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="F56" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="G56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="H56" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="I56" s="127" t="s">
         <v>18</v>
@@ -4795,19 +4883,19 @@
         <v>555</v>
       </c>
       <c r="D57" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="E57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="F57" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="G57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="H57" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="I57" s="127" t="s">
         <v>17</v>
@@ -4827,19 +4915,19 @@
         <v>556</v>
       </c>
       <c r="D58" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="E58" s="127" t="s">
         <v>37</v>
       </c>
       <c r="F58" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="G58" s="128" t="s">
         <v>37</v>
       </c>
       <c r="H58" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="I58" s="127" t="s">
         <v>16</v>
@@ -4859,19 +4947,19 @@
         <v>557</v>
       </c>
       <c r="D59" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="E59" s="127" t="s">
         <v>38</v>
       </c>
       <c r="F59" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="G59" s="128" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="I59" s="127" t="s">
         <v>15</v>
@@ -4891,19 +4979,19 @@
         <v>558</v>
       </c>
       <c r="D60" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="E60" s="128" t="s">
         <v>228</v>
       </c>
       <c r="F60" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="G60" s="127" t="s">
         <v>228</v>
       </c>
       <c r="H60" s="127" t="s">
-        <v>682</v>
+        <v>608</v>
       </c>
       <c r="I60" s="127" t="s">
         <v>14</v>
@@ -4921,14 +5009,14 @@
       </c>
       <c r="C61" s="127"/>
       <c r="D61" s="127"/>
-      <c r="E61" s="127" t="s">
-        <v>559</v>
+      <c r="E61" s="128" t="s">
+        <v>609</v>
       </c>
       <c r="F61" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G61" s="128" t="s">
-        <v>656</v>
+        <v>592</v>
       </c>
       <c r="H61" s="127" t="s">
         <v>178</v>
@@ -4952,7 +5040,7 @@
       <c r="E62" s="128"/>
       <c r="F62" s="127"/>
       <c r="G62" s="128" t="s">
-        <v>657</v>
+        <v>593</v>
       </c>
       <c r="H62" s="127" t="s">
         <v>178</v>
@@ -4974,7 +5062,7 @@
       <c r="C63" s="127"/>
       <c r="D63" s="127"/>
       <c r="E63" s="128" t="s">
-        <v>560</v>
+        <v>628</v>
       </c>
       <c r="F63" s="127" t="s">
         <v>173</v>
@@ -4996,13 +5084,13 @@
         <v>329</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>594</v>
+        <v>561</v>
       </c>
       <c r="D64" s="163" t="s">
-        <v>597</v>
-      </c>
-      <c r="E64" s="127" t="s">
-        <v>561</v>
+        <v>564</v>
+      </c>
+      <c r="E64" s="128" t="s">
+        <v>610</v>
       </c>
       <c r="F64" s="127" t="s">
         <v>174</v>
@@ -5032,7 +5120,7 @@
       <c r="E65" s="128"/>
       <c r="F65" s="127"/>
       <c r="G65" s="127" t="s">
-        <v>676</v>
+        <v>607</v>
       </c>
       <c r="H65" s="127" t="s">
         <v>178</v>
@@ -5054,7 +5142,7 @@
       <c r="C66" s="127"/>
       <c r="D66" s="127"/>
       <c r="E66" s="128" t="s">
-        <v>562</v>
+        <v>668</v>
       </c>
       <c r="F66" s="127" t="s">
         <v>174</v>
@@ -5077,14 +5165,14 @@
       </c>
       <c r="C67" s="128"/>
       <c r="D67" s="127"/>
-      <c r="E67" s="127" t="s">
-        <v>563</v>
+      <c r="E67" s="128" t="s">
+        <v>611</v>
       </c>
       <c r="F67" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G67" s="128" t="s">
-        <v>658</v>
+        <v>594</v>
       </c>
       <c r="H67" s="127" t="s">
         <v>177</v>
@@ -5104,15 +5192,15 @@
         <v>329</v>
       </c>
       <c r="C68" s="128" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="D68" s="164" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
       <c r="E68" s="128"/>
       <c r="F68" s="127"/>
-      <c r="G68" s="127" t="s">
-        <v>677</v>
+      <c r="G68" s="128" t="s">
+        <v>640</v>
       </c>
       <c r="H68" s="127" t="s">
         <v>178</v>
@@ -5134,7 +5222,7 @@
       <c r="C69" s="127"/>
       <c r="D69" s="127"/>
       <c r="E69" s="128" t="s">
-        <v>564</v>
+        <v>669</v>
       </c>
       <c r="F69" s="127" t="s">
         <v>174</v>
@@ -5157,14 +5245,14 @@
       </c>
       <c r="C70" s="127"/>
       <c r="D70" s="127"/>
-      <c r="E70" s="127" t="s">
-        <v>565</v>
+      <c r="E70" s="128" t="s">
+        <v>612</v>
       </c>
       <c r="F70" s="127" t="s">
         <v>174</v>
       </c>
       <c r="G70" s="128" t="s">
-        <v>659</v>
+        <v>595</v>
       </c>
       <c r="H70" s="127" t="s">
         <v>177</v>
@@ -5184,15 +5272,15 @@
         <v>329</v>
       </c>
       <c r="C71" s="128" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="D71" s="164" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
       <c r="E71" s="128"/>
       <c r="F71" s="127"/>
-      <c r="G71" s="127" t="s">
-        <v>290</v>
+      <c r="G71" s="128" t="s">
+        <v>641</v>
       </c>
       <c r="H71" s="127" t="s">
         <v>175</v>
@@ -5214,7 +5302,7 @@
       <c r="C72" s="127"/>
       <c r="D72" s="127"/>
       <c r="E72" s="128" t="s">
-        <v>566</v>
+        <v>670</v>
       </c>
       <c r="F72" s="127" t="s">
         <v>174</v>
@@ -5237,14 +5325,14 @@
       </c>
       <c r="C73" s="149"/>
       <c r="D73" s="129"/>
-      <c r="E73" s="129" t="s">
-        <v>567</v>
+      <c r="E73" s="149" t="s">
+        <v>613</v>
       </c>
       <c r="F73" s="129" t="s">
         <v>173</v>
       </c>
       <c r="G73" s="149" t="s">
-        <v>660</v>
+        <v>596</v>
       </c>
       <c r="H73" s="129" t="s">
         <v>175</v>
@@ -5290,13 +5378,13 @@
       <c r="C75" s="131"/>
       <c r="D75" s="131"/>
       <c r="E75" s="132" t="s">
-        <v>568</v>
+        <v>671</v>
       </c>
       <c r="F75" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G75" s="131" t="s">
-        <v>107</v>
+      <c r="G75" s="132" t="s">
+        <v>642</v>
       </c>
       <c r="H75" s="131" t="s">
         <v>175</v>
@@ -5317,8 +5405,8 @@
       </c>
       <c r="C76" s="132"/>
       <c r="D76" s="131"/>
-      <c r="E76" s="131" t="s">
-        <v>569</v>
+      <c r="E76" s="132" t="s">
+        <v>614</v>
       </c>
       <c r="F76" s="131" t="s">
         <v>174</v>
@@ -5366,13 +5454,13 @@
       <c r="C78" s="132"/>
       <c r="D78" s="131"/>
       <c r="E78" s="132" t="s">
-        <v>570</v>
+        <v>672</v>
       </c>
       <c r="F78" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G78" s="131" t="s">
-        <v>678</v>
+      <c r="G78" s="132" t="s">
+        <v>643</v>
       </c>
       <c r="H78" s="131" t="s">
         <v>175</v>
@@ -5393,8 +5481,8 @@
       </c>
       <c r="C79" s="131"/>
       <c r="D79" s="131"/>
-      <c r="E79" s="131" t="s">
-        <v>571</v>
+      <c r="E79" s="132" t="s">
+        <v>615</v>
       </c>
       <c r="F79" s="131" t="s">
         <v>174</v>
@@ -5442,7 +5530,7 @@
       <c r="C81" s="132"/>
       <c r="D81" s="131"/>
       <c r="E81" s="132" t="s">
-        <v>572</v>
+        <v>673</v>
       </c>
       <c r="F81" s="131" t="s">
         <v>173</v>
@@ -5469,8 +5557,8 @@
       </c>
       <c r="C82" s="132"/>
       <c r="D82" s="131"/>
-      <c r="E82" s="131" t="s">
-        <v>573</v>
+      <c r="E82" s="132" t="s">
+        <v>616</v>
       </c>
       <c r="F82" s="131" t="s">
         <v>173</v>
@@ -5492,15 +5580,15 @@
         <v>330</v>
       </c>
       <c r="C83" s="132" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
       <c r="D83" s="196" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="E83" s="132"/>
       <c r="F83" s="131"/>
       <c r="G83" s="132" t="s">
-        <v>661</v>
+        <v>597</v>
       </c>
       <c r="H83" s="131" t="s">
         <v>177</v>
@@ -5522,13 +5610,13 @@
       <c r="C84" s="131"/>
       <c r="D84" s="131"/>
       <c r="E84" s="132" t="s">
-        <v>574</v>
+        <v>674</v>
       </c>
       <c r="F84" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G84" s="131" t="s">
-        <v>679</v>
+      <c r="G84" s="132" t="s">
+        <v>644</v>
       </c>
       <c r="H84" s="131" t="s">
         <v>175</v>
@@ -5549,14 +5637,14 @@
       </c>
       <c r="C85" s="132"/>
       <c r="D85" s="131"/>
-      <c r="E85" s="131" t="s">
-        <v>575</v>
+      <c r="E85" s="197" t="s">
+        <v>675</v>
       </c>
       <c r="F85" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G85" s="132" t="s">
-        <v>662</v>
+        <v>598</v>
       </c>
       <c r="H85" s="131" t="s">
         <v>177</v>
@@ -5576,10 +5664,10 @@
         <v>330</v>
       </c>
       <c r="C86" s="132" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
       <c r="D86" s="196" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
       <c r="E86" s="132"/>
       <c r="F86" s="131"/>
@@ -5602,13 +5690,13 @@
       <c r="C87" s="131"/>
       <c r="D87" s="131"/>
       <c r="E87" s="132" t="s">
-        <v>576</v>
+        <v>676</v>
       </c>
       <c r="F87" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G87" s="131" t="s">
-        <v>680</v>
+      <c r="G87" s="132" t="s">
+        <v>645</v>
       </c>
       <c r="H87" s="131" t="s">
         <v>177</v>
@@ -5630,7 +5718,7 @@
       <c r="C88" s="131"/>
       <c r="D88" s="131"/>
       <c r="E88" s="132" t="s">
-        <v>577</v>
+        <v>677</v>
       </c>
       <c r="F88" s="131" t="s">
         <v>174</v>
@@ -5652,19 +5740,19 @@
         <v>330</v>
       </c>
       <c r="C89" s="132" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
       <c r="D89" s="131" t="s">
-        <v>606</v>
-      </c>
-      <c r="E89" s="131" t="s">
-        <v>578</v>
+        <v>573</v>
+      </c>
+      <c r="E89" s="132" t="s">
+        <v>617</v>
       </c>
       <c r="F89" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G89" s="132" t="s">
-        <v>663</v>
+        <v>599</v>
       </c>
       <c r="H89" s="131" t="s">
         <v>178</v>
@@ -5687,8 +5775,8 @@
       <c r="D90" s="131"/>
       <c r="E90" s="132"/>
       <c r="F90" s="131"/>
-      <c r="G90" s="131" t="s">
-        <v>681</v>
+      <c r="G90" s="132" t="s">
+        <v>646</v>
       </c>
       <c r="H90" s="131" t="s">
         <v>175</v>
@@ -5710,13 +5798,13 @@
       <c r="C91" s="131"/>
       <c r="D91" s="131"/>
       <c r="E91" s="132" t="s">
-        <v>579</v>
+        <v>678</v>
       </c>
       <c r="F91" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G91" s="132" t="s">
-        <v>653</v>
+        <v>589</v>
       </c>
       <c r="H91" s="131" t="s">
         <v>178</v>
@@ -5758,13 +5846,13 @@
       <c r="C93" s="131"/>
       <c r="D93" s="131"/>
       <c r="E93" s="132" t="s">
-        <v>580</v>
+        <v>679</v>
       </c>
       <c r="F93" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G93" s="131" t="s">
-        <v>281</v>
+      <c r="G93" s="132" t="s">
+        <v>630</v>
       </c>
       <c r="H93" s="131" t="s">
         <v>177</v>
@@ -5786,13 +5874,13 @@
       <c r="C94" s="132"/>
       <c r="D94" s="131"/>
       <c r="E94" s="132" t="s">
-        <v>581</v>
+        <v>680</v>
       </c>
       <c r="F94" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G94" s="132" t="s">
-        <v>664</v>
+        <v>600</v>
       </c>
       <c r="H94" s="131" t="s">
         <v>177</v>
@@ -5832,19 +5920,19 @@
         <v>330</v>
       </c>
       <c r="C96" s="132" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="D96" s="195" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
       <c r="E96" s="132" t="s">
-        <v>582</v>
+        <v>681</v>
       </c>
       <c r="F96" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G96" s="131" t="s">
-        <v>419</v>
+      <c r="G96" s="132" t="s">
+        <v>647</v>
       </c>
       <c r="H96" s="131" t="s">
         <v>175</v>
@@ -5866,7 +5954,7 @@
       <c r="C97" s="133"/>
       <c r="D97" s="133"/>
       <c r="E97" s="151" t="s">
-        <v>583</v>
+        <v>682</v>
       </c>
       <c r="F97" s="133" t="s">
         <v>174</v>
@@ -5894,13 +5982,13 @@
       <c r="C98" s="134"/>
       <c r="D98" s="135"/>
       <c r="E98" s="134" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="F98" s="135" t="s">
         <v>174</v>
       </c>
       <c r="G98" s="134" t="s">
-        <v>665</v>
+        <v>601</v>
       </c>
       <c r="H98" s="135" t="s">
         <v>178</v>
@@ -5921,8 +6009,8 @@
       </c>
       <c r="C99" s="136"/>
       <c r="D99" s="136"/>
-      <c r="E99" s="136" t="s">
-        <v>585</v>
+      <c r="E99" s="137" t="s">
+        <v>618</v>
       </c>
       <c r="F99" s="136" t="s">
         <v>174</v>
@@ -5946,13 +6034,13 @@
       <c r="C100" s="137"/>
       <c r="D100" s="136"/>
       <c r="E100" s="137" t="s">
-        <v>586</v>
+        <v>683</v>
       </c>
       <c r="F100" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G100" s="136" t="s">
-        <v>206</v>
+      <c r="G100" s="137" t="s">
+        <v>648</v>
       </c>
       <c r="H100" s="136" t="s">
         <v>177</v>
@@ -5976,7 +6064,7 @@
       <c r="E101" s="137"/>
       <c r="F101" s="136"/>
       <c r="G101" s="137" t="s">
-        <v>666</v>
+        <v>602</v>
       </c>
       <c r="H101" s="136" t="s">
         <v>175</v>
@@ -5997,8 +6085,8 @@
       </c>
       <c r="C102" s="136"/>
       <c r="D102" s="136"/>
-      <c r="E102" s="136" t="s">
-        <v>587</v>
+      <c r="E102" s="137" t="s">
+        <v>619</v>
       </c>
       <c r="F102" s="136" t="s">
         <v>173</v>
@@ -6022,13 +6110,13 @@
       <c r="C103" s="137"/>
       <c r="D103" s="136"/>
       <c r="E103" s="137" t="s">
-        <v>588</v>
+        <v>684</v>
       </c>
       <c r="F103" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G103" s="136" t="s">
-        <v>140</v>
+      <c r="G103" s="137" t="s">
+        <v>649</v>
       </c>
       <c r="H103" s="136" t="s">
         <v>175</v>
@@ -6052,7 +6140,7 @@
       <c r="E104" s="136"/>
       <c r="F104" s="136"/>
       <c r="G104" s="137" t="s">
-        <v>667</v>
+        <v>603</v>
       </c>
       <c r="H104" s="136" t="s">
         <v>175</v>
@@ -6074,7 +6162,7 @@
       <c r="C105" s="136"/>
       <c r="D105" s="136"/>
       <c r="E105" s="137" t="s">
-        <v>589</v>
+        <v>685</v>
       </c>
       <c r="F105" s="136" t="s">
         <v>173</v>
@@ -6100,7 +6188,7 @@
       <c r="E106" s="137"/>
       <c r="F106" s="136"/>
       <c r="G106" s="137" t="s">
-        <v>617</v>
+        <v>580</v>
       </c>
       <c r="H106" s="136" t="s">
         <v>175</v>
@@ -6124,7 +6212,7 @@
       <c r="E107" s="136"/>
       <c r="F107" s="136"/>
       <c r="G107" s="137" t="s">
-        <v>611</v>
+        <v>574</v>
       </c>
       <c r="H107" s="136" t="s">
         <v>178</v>
@@ -6146,10 +6234,10 @@
       <c r="C108" s="136"/>
       <c r="D108" s="136"/>
       <c r="E108" s="137" t="s">
-        <v>590</v>
+        <v>559</v>
       </c>
       <c r="F108" s="165" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="G108" s="137"/>
       <c r="H108" s="173"/>
@@ -6172,7 +6260,7 @@
       <c r="E109" s="137"/>
       <c r="F109" s="136"/>
       <c r="G109" s="137" t="s">
-        <v>612</v>
+        <v>575</v>
       </c>
       <c r="H109" s="173" t="s">
         <v>175</v>
@@ -6195,8 +6283,8 @@
       <c r="D110" s="136"/>
       <c r="E110" s="136"/>
       <c r="F110" s="136"/>
-      <c r="G110" s="136" t="s">
-        <v>607</v>
+      <c r="G110" s="137" t="s">
+        <v>620</v>
       </c>
       <c r="H110" s="136" t="s">
         <v>178</v>
@@ -6240,7 +6328,7 @@
       <c r="E112" s="137"/>
       <c r="F112" s="136"/>
       <c r="G112" s="137" t="s">
-        <v>613</v>
+        <v>576</v>
       </c>
       <c r="H112" s="136" t="s">
         <v>178</v>
@@ -6263,8 +6351,8 @@
       <c r="D113" s="136"/>
       <c r="E113" s="136"/>
       <c r="F113" s="136"/>
-      <c r="G113" s="136" t="s">
-        <v>608</v>
+      <c r="G113" s="137" t="s">
+        <v>621</v>
       </c>
       <c r="H113" s="136" t="s">
         <v>178</v>
@@ -6308,7 +6396,7 @@
       <c r="E115" s="137"/>
       <c r="F115" s="136"/>
       <c r="G115" s="137" t="s">
-        <v>614</v>
+        <v>577</v>
       </c>
       <c r="H115" s="136" t="s">
         <v>175</v>
@@ -6331,8 +6419,8 @@
       <c r="D116" s="136"/>
       <c r="E116" s="136"/>
       <c r="F116" s="136"/>
-      <c r="G116" s="136" t="s">
-        <v>609</v>
+      <c r="G116" s="137" t="s">
+        <v>622</v>
       </c>
       <c r="H116" s="136" t="s">
         <v>175</v>
@@ -6376,7 +6464,7 @@
       <c r="E118" s="137"/>
       <c r="F118" s="136"/>
       <c r="G118" s="137" t="s">
-        <v>615</v>
+        <v>578</v>
       </c>
       <c r="H118" s="136" t="s">
         <v>178</v>
@@ -6399,8 +6487,8 @@
       <c r="D119" s="136"/>
       <c r="E119" s="136"/>
       <c r="F119" s="136"/>
-      <c r="G119" s="136" t="s">
-        <v>610</v>
+      <c r="G119" s="137" t="s">
+        <v>623</v>
       </c>
       <c r="H119" s="136" t="s">
         <v>178</v>
@@ -6444,7 +6532,7 @@
       <c r="E121" s="139"/>
       <c r="F121" s="138"/>
       <c r="G121" s="139" t="s">
-        <v>616</v>
+        <v>579</v>
       </c>
       <c r="H121" s="138" t="s">
         <v>177</v>
@@ -6468,7 +6556,7 @@
       <c r="E122" s="141"/>
       <c r="F122" s="140"/>
       <c r="G122" s="141" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="H122" s="140" t="s">
         <v>177</v>
@@ -6491,8 +6579,8 @@
       <c r="D123" s="143"/>
       <c r="E123" s="143"/>
       <c r="F123" s="143"/>
-      <c r="G123" s="143" t="s">
-        <v>618</v>
+      <c r="G123" s="142" t="s">
+        <v>624</v>
       </c>
       <c r="H123" s="143" t="s">
         <v>177</v>
@@ -6536,7 +6624,7 @@
       <c r="E125" s="142"/>
       <c r="F125" s="143"/>
       <c r="G125" s="142" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="H125" s="143" t="s">
         <v>177</v>
@@ -6559,8 +6647,8 @@
       <c r="D126" s="143"/>
       <c r="E126" s="143"/>
       <c r="F126" s="143"/>
-      <c r="G126" s="143" t="s">
-        <v>620</v>
+      <c r="G126" s="142" t="s">
+        <v>625</v>
       </c>
       <c r="H126" s="143" t="s">
         <v>177</v>
@@ -6604,7 +6692,7 @@
       <c r="E128" s="142"/>
       <c r="F128" s="143"/>
       <c r="G128" s="142" t="s">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="H128" s="143" t="s">
         <v>177</v>
@@ -6627,8 +6715,8 @@
       <c r="D129" s="143"/>
       <c r="E129" s="142"/>
       <c r="F129" s="143"/>
-      <c r="G129" s="143" t="s">
-        <v>622</v>
+      <c r="G129" s="142" t="s">
+        <v>626</v>
       </c>
       <c r="H129" s="143" t="s">
         <v>175</v>
@@ -6672,7 +6760,7 @@
       <c r="E131" s="143"/>
       <c r="F131" s="143"/>
       <c r="G131" s="142" t="s">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="H131" s="143" t="s">
         <v>178</v>
@@ -6695,8 +6783,8 @@
       <c r="D132" s="143"/>
       <c r="E132" s="142"/>
       <c r="F132" s="143"/>
-      <c r="G132" s="143" t="s">
-        <v>624</v>
+      <c r="G132" s="142" t="s">
+        <v>627</v>
       </c>
       <c r="H132" s="143" t="s">
         <v>178</v>
@@ -6720,7 +6808,7 @@
       <c r="E133" s="142"/>
       <c r="F133" s="143"/>
       <c r="G133" s="142" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="H133" s="143" t="s">
         <v>177</v>
@@ -6763,8 +6851,8 @@
       <c r="D135" s="143"/>
       <c r="E135" s="143"/>
       <c r="F135" s="143"/>
-      <c r="G135" s="143" t="s">
-        <v>560</v>
+      <c r="G135" s="142" t="s">
+        <v>628</v>
       </c>
       <c r="H135" s="143" t="s">
         <v>178</v>
@@ -6788,7 +6876,7 @@
       <c r="E136" s="142"/>
       <c r="F136" s="143"/>
       <c r="G136" s="142" t="s">
-        <v>561</v>
+        <v>610</v>
       </c>
       <c r="H136" s="143" t="s">
         <v>178</v>
@@ -6831,8 +6919,8 @@
       <c r="D138" s="143"/>
       <c r="E138" s="143"/>
       <c r="F138" s="143"/>
-      <c r="G138" s="143" t="s">
-        <v>626</v>
+      <c r="G138" s="142" t="s">
+        <v>629</v>
       </c>
       <c r="H138" s="143" t="s">
         <v>177</v>
@@ -6856,7 +6944,7 @@
       <c r="E139" s="142"/>
       <c r="F139" s="143"/>
       <c r="G139" s="142" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="H139" s="143" t="s">
         <v>178</v>
@@ -6899,8 +6987,8 @@
       <c r="D141" s="143"/>
       <c r="E141" s="142"/>
       <c r="F141" s="143"/>
-      <c r="G141" s="143" t="s">
-        <v>592</v>
+      <c r="G141" s="142" t="s">
+        <v>630</v>
       </c>
       <c r="H141" s="143" t="s">
         <v>177</v>
@@ -6924,7 +7012,7 @@
       <c r="E142" s="142"/>
       <c r="F142" s="143"/>
       <c r="G142" s="142" t="s">
-        <v>628</v>
+        <v>655</v>
       </c>
       <c r="H142" s="143" t="s">
         <v>175</v>
@@ -6968,7 +7056,7 @@
       <c r="E144" s="143"/>
       <c r="F144" s="143"/>
       <c r="G144" s="142" t="s">
-        <v>629</v>
+        <v>656</v>
       </c>
       <c r="H144" s="143" t="s">
         <v>178</v>
@@ -6991,8 +7079,8 @@
       <c r="D145" s="144"/>
       <c r="E145" s="152"/>
       <c r="F145" s="144"/>
-      <c r="G145" s="144" t="s">
-        <v>630</v>
+      <c r="G145" s="152" t="s">
+        <v>631</v>
       </c>
       <c r="H145" s="144" t="s">
         <v>175</v>
@@ -7036,7 +7124,7 @@
       <c r="E147" s="146"/>
       <c r="F147" s="146"/>
       <c r="G147" s="147" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="H147" s="146" t="s">
         <v>177</v>
@@ -7060,7 +7148,7 @@
       <c r="E148" s="147"/>
       <c r="F148" s="146"/>
       <c r="G148" s="147" t="s">
-        <v>593</v>
+        <v>648</v>
       </c>
       <c r="H148" s="146" t="s">
         <v>177</v>
@@ -7104,7 +7192,7 @@
       <c r="E150" s="146"/>
       <c r="F150" s="146"/>
       <c r="G150" s="147" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="H150" s="146" t="s">
         <v>175</v>
@@ -7128,7 +7216,7 @@
       <c r="E151" s="147"/>
       <c r="F151" s="146"/>
       <c r="G151" s="147" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="H151" s="146" t="s">
         <v>175</v>
@@ -7172,7 +7260,7 @@
       <c r="E153" s="146"/>
       <c r="F153" s="146"/>
       <c r="G153" s="147" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="H153" s="146" t="s">
         <v>175</v>
@@ -7196,7 +7284,7 @@
       <c r="E154" s="147"/>
       <c r="F154" s="146"/>
       <c r="G154" s="147" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
       <c r="H154" s="146" t="s">
         <v>177</v>
@@ -7240,7 +7328,7 @@
       <c r="E156" s="146"/>
       <c r="F156" s="146"/>
       <c r="G156" s="147" t="s">
-        <v>645</v>
+        <v>581</v>
       </c>
       <c r="H156" s="146" t="s">
         <v>175</v>
@@ -7264,7 +7352,7 @@
       <c r="E157" s="146"/>
       <c r="F157" s="146"/>
       <c r="G157" s="147" t="s">
-        <v>635</v>
+        <v>662</v>
       </c>
       <c r="H157" s="146" t="s">
         <v>177</v>
@@ -7288,7 +7376,7 @@
       <c r="E158" s="147"/>
       <c r="F158" s="146"/>
       <c r="G158" s="147" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="H158" s="146" t="s">
         <v>178</v>
@@ -7332,7 +7420,7 @@
       <c r="E160" s="147"/>
       <c r="F160" s="146"/>
       <c r="G160" s="147" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
       <c r="H160" s="146" t="s">
         <v>177</v>
@@ -7375,8 +7463,8 @@
       <c r="D162" s="146"/>
       <c r="E162" s="146"/>
       <c r="F162" s="146"/>
-      <c r="G162" s="146" t="s">
-        <v>638</v>
+      <c r="G162" s="147" t="s">
+        <v>632</v>
       </c>
       <c r="H162" s="146" t="s">
         <v>178</v>
@@ -7399,8 +7487,8 @@
       <c r="D163" s="146"/>
       <c r="E163" s="146"/>
       <c r="F163" s="146"/>
-      <c r="G163" s="146" t="s">
-        <v>639</v>
+      <c r="G163" s="147" t="s">
+        <v>633</v>
       </c>
       <c r="H163" s="146" t="s">
         <v>177</v>
@@ -7444,7 +7532,7 @@
       <c r="E165" s="146"/>
       <c r="F165" s="146"/>
       <c r="G165" s="147" t="s">
-        <v>640</v>
+        <v>665</v>
       </c>
       <c r="H165" s="146" t="s">
         <v>178</v>
@@ -7468,7 +7556,7 @@
       <c r="E166" s="146"/>
       <c r="F166" s="146"/>
       <c r="G166" s="147" t="s">
-        <v>641</v>
+        <v>666</v>
       </c>
       <c r="H166" s="146" t="s">
         <v>177</v>
@@ -7512,7 +7600,7 @@
       <c r="E168" s="146"/>
       <c r="F168" s="146"/>
       <c r="G168" s="147" t="s">
-        <v>642</v>
+        <v>667</v>
       </c>
       <c r="H168" s="146" t="s">
         <v>177</v>
@@ -7535,8 +7623,8 @@
       <c r="D169" s="146"/>
       <c r="E169" s="146"/>
       <c r="F169" s="146"/>
-      <c r="G169" s="146" t="s">
-        <v>643</v>
+      <c r="G169" s="147" t="s">
+        <v>634</v>
       </c>
       <c r="H169" s="146" t="s">
         <v>177</v>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFECEC3-6E2C-456C-AE30-0A98CA838D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6725214E-0237-41D3-80BC-5240B1A6EBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7335" yWindow="210" windowWidth="21600" windowHeight="11295" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="1515" windowWidth="21600" windowHeight="11295" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="timeList_ZH" sheetId="13" r:id="rId1"/>
-    <sheet name="timeList0212-0225" sheetId="15" r:id="rId2"/>
+    <sheet name="timeList_0225" sheetId="13" r:id="rId1"/>
+    <sheet name="timeList_ZH" sheetId="15" r:id="rId2"/>
     <sheet name="timeList0204-0211" sheetId="14" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">timeList_ZH!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">timeList_0225!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">timeList_ZH!$B$1:$H$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'timeList0204-0211'!$B$1:$H$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'timeList0212-0225'!$B$1:$H$169</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10320,7 +10320,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4E323D-80FF-4C16-B902-C80C196F169E}">
-  <dimension ref="A1:J1055"/>
+  <dimension ref="A1:Q1055"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.25" style="111" bestFit="1" customWidth="1"/>
@@ -10328,13 +10328,19 @@
     <col min="3" max="3" width="15.5" style="111" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="111" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="111" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" style="111" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="111" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="111" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.375" style="111" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.875" style="111" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.25" style="111" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.125" style="111" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.625" style="111" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="14.25" style="111"/>
+    <col min="12" max="12" width="7.125" style="111" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.375" style="111" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" style="111" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.375" style="111" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.125" style="111" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.375" style="111" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="14.25" style="111"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="157" customFormat="1" ht="18" customHeight="1">
@@ -12127,7 +12133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="18" customHeight="1">
+    <row r="65" spans="1:17" ht="18" customHeight="1">
       <c r="A65" s="127" t="s">
         <v>9</v>
       </c>
@@ -12155,7 +12161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="18" customHeight="1">
+    <row r="66" spans="1:17" ht="18" customHeight="1">
       <c r="A66" s="127" t="s">
         <v>8</v>
       </c>
@@ -12185,7 +12191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="18" customHeight="1">
+    <row r="67" spans="1:17" ht="18" customHeight="1">
       <c r="A67" s="127" t="s">
         <v>7</v>
       </c>
@@ -12213,7 +12219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="18" customHeight="1">
+    <row r="68" spans="1:17" ht="18" customHeight="1">
       <c r="A68" s="127" t="s">
         <v>6</v>
       </c>
@@ -12239,7 +12245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="18" customHeight="1">
+    <row r="69" spans="1:17" ht="18" customHeight="1">
       <c r="A69" s="127" t="s">
         <v>5</v>
       </c>
@@ -12269,7 +12275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="18" customHeight="1">
+    <row r="70" spans="1:17" ht="18" customHeight="1">
       <c r="A70" s="127" t="s">
         <v>4</v>
       </c>
@@ -12295,7 +12301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="18" customHeight="1">
+    <row r="71" spans="1:17" ht="18" customHeight="1">
       <c r="A71" s="127" t="s">
         <v>3</v>
       </c>
@@ -12323,7 +12329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="18" customHeight="1">
+    <row r="72" spans="1:17" ht="18" customHeight="1">
       <c r="A72" s="127" t="s">
         <v>2</v>
       </c>
@@ -12353,7 +12359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="18" customHeight="1" thickBot="1">
+    <row r="73" spans="1:17" ht="18" customHeight="1" thickBot="1">
       <c r="A73" s="129" t="s">
         <v>1</v>
       </c>
@@ -12381,7 +12387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="18" customHeight="1">
+    <row r="74" spans="1:17" ht="18" customHeight="1">
       <c r="A74" s="130" t="s">
         <v>24</v>
       </c>
@@ -12411,7 +12417,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="18" customHeight="1">
+    <row r="75" spans="1:17" ht="18" customHeight="1">
       <c r="A75" s="131" t="s">
         <v>23</v>
       </c>
@@ -12437,7 +12443,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="18" customHeight="1">
+    <row r="76" spans="1:17" ht="18" customHeight="1">
       <c r="A76" s="131" t="s">
         <v>22</v>
       </c>
@@ -12465,7 +12471,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="18" customHeight="1">
+    <row r="77" spans="1:17" ht="18" customHeight="1">
       <c r="A77" s="131" t="s">
         <v>21</v>
       </c>
@@ -12495,7 +12501,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="18" customHeight="1">
+    <row r="78" spans="1:17" ht="18" customHeight="1">
       <c r="A78" s="131" t="s">
         <v>20</v>
       </c>
@@ -12523,7 +12529,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="18" customHeight="1">
+    <row r="79" spans="1:17" ht="18" customHeight="1">
       <c r="A79" s="131" t="s">
         <v>19</v>
       </c>
@@ -12549,71 +12555,71 @@
         <v>27</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="18" customHeight="1">
+    <row r="80" spans="1:17" ht="18" customHeight="1">
       <c r="A80" s="131" t="s">
         <v>18</v>
       </c>
       <c r="B80" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C80" s="132" t="s">
-        <v>451</v>
-      </c>
-      <c r="D80" s="131" t="s">
-        <v>361</v>
-      </c>
-      <c r="E80" s="132" t="s">
-        <v>471</v>
-      </c>
-      <c r="F80" s="131" t="s">
-        <v>336</v>
-      </c>
-      <c r="G80" s="132" t="s">
-        <v>84</v>
-      </c>
-      <c r="H80" s="131" t="s">
-        <v>336</v>
-      </c>
       <c r="I80" s="131" t="s">
         <v>18</v>
       </c>
       <c r="J80" s="131" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="18" customHeight="1">
+      <c r="L80" s="132" t="s">
+        <v>451</v>
+      </c>
+      <c r="M80" s="131" t="s">
+        <v>361</v>
+      </c>
+      <c r="N80" s="132" t="s">
+        <v>471</v>
+      </c>
+      <c r="O80" s="131" t="s">
+        <v>336</v>
+      </c>
+      <c r="P80" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q80" s="131" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="18" customHeight="1">
       <c r="A81" s="131" t="s">
         <v>17</v>
       </c>
       <c r="B81" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C81" s="132" t="s">
-        <v>452</v>
-      </c>
-      <c r="D81" s="131" t="s">
-        <v>361</v>
-      </c>
-      <c r="E81" s="132" t="s">
-        <v>472</v>
-      </c>
-      <c r="F81" s="131" t="s">
-        <v>336</v>
-      </c>
-      <c r="G81" s="132" t="s">
-        <v>452</v>
-      </c>
-      <c r="H81" s="131" t="s">
-        <v>336</v>
-      </c>
       <c r="I81" s="131" t="s">
         <v>17</v>
       </c>
       <c r="J81" s="131" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="18" customHeight="1">
+      <c r="L81" s="132" t="s">
+        <v>452</v>
+      </c>
+      <c r="M81" s="131" t="s">
+        <v>361</v>
+      </c>
+      <c r="N81" s="132" t="s">
+        <v>472</v>
+      </c>
+      <c r="O81" s="131" t="s">
+        <v>336</v>
+      </c>
+      <c r="P81" s="132" t="s">
+        <v>452</v>
+      </c>
+      <c r="Q81" s="131" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" ht="18" customHeight="1">
       <c r="A82" s="131" t="s">
         <v>16</v>
       </c>
@@ -12641,7 +12647,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="18" customHeight="1">
+    <row r="83" spans="1:17" ht="18" customHeight="1">
       <c r="A83" s="131" t="s">
         <v>15</v>
       </c>
@@ -12671,7 +12677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="18" customHeight="1">
+    <row r="84" spans="1:17" ht="18" customHeight="1">
       <c r="A84" s="131" t="s">
         <v>14</v>
       </c>
@@ -12697,7 +12703,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="18" customHeight="1">
+    <row r="85" spans="1:17" ht="18" customHeight="1">
       <c r="A85" s="131" t="s">
         <v>13</v>
       </c>
@@ -12725,7 +12731,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="18" customHeight="1">
+    <row r="86" spans="1:17" ht="18" customHeight="1">
       <c r="A86" s="131" t="s">
         <v>12</v>
       </c>
@@ -12755,7 +12761,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="18" customHeight="1">
+    <row r="87" spans="1:17" ht="18" customHeight="1">
       <c r="A87" s="131" t="s">
         <v>11</v>
       </c>
@@ -12781,7 +12787,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="18" customHeight="1">
+    <row r="88" spans="1:17" ht="18" customHeight="1">
       <c r="A88" s="131" t="s">
         <v>10</v>
       </c>
@@ -12811,7 +12817,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="18" customHeight="1">
+    <row r="89" spans="1:17" ht="18" customHeight="1">
       <c r="A89" s="131" t="s">
         <v>9</v>
       </c>
@@ -12839,7 +12845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="18" customHeight="1">
+    <row r="90" spans="1:17" ht="18" customHeight="1">
       <c r="A90" s="131" t="s">
         <v>8</v>
       </c>
@@ -12865,7 +12871,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="18" customHeight="1">
+    <row r="91" spans="1:17" ht="18" customHeight="1">
       <c r="A91" s="131" t="s">
         <v>7</v>
       </c>
@@ -12895,7 +12901,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="18" customHeight="1">
+    <row r="92" spans="1:17" ht="18" customHeight="1">
       <c r="A92" s="131" t="s">
         <v>6</v>
       </c>
@@ -12921,7 +12927,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="18" customHeight="1">
+    <row r="93" spans="1:17" ht="18" customHeight="1">
       <c r="A93" s="131" t="s">
         <v>5</v>
       </c>
@@ -12947,7 +12953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="18" customHeight="1">
+    <row r="94" spans="1:17" ht="18" customHeight="1">
       <c r="A94" s="131" t="s">
         <v>4</v>
       </c>
@@ -12979,7 +12985,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="18" customHeight="1">
+    <row r="95" spans="1:17" ht="18" customHeight="1">
       <c r="A95" s="131" t="s">
         <v>3</v>
       </c>
@@ -13005,7 +13011,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="18" customHeight="1">
+    <row r="96" spans="1:17" ht="18" customHeight="1">
       <c r="A96" s="131" t="s">
         <v>2</v>
       </c>
@@ -17774,12 +17780,12 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
+  <conditionalFormatting sqref="C1:C79 C82:C1048576 L80:L81 E1:E79 E82:E1048576 N80:N81 G1:G79 G82:G1048576 P80:P81">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
+  <conditionalFormatting sqref="D1:D79 D82:D1048576 M80:M81 F1:F79 F82:F1048576 O80:O81 H1:H79 H82:H1048576 Q80:Q81">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56A3E71-D6B6-4F07-AEE4-861192F8E995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677F96E2-90BC-40E1-B61A-3138A0DF5407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="0" windowWidth="14190" windowHeight="15600" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1230" yWindow="0" windowWidth="14190" windowHeight="15585" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList_0225" sheetId="13" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3677" uniqueCount="706">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -1176,19 +1176,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>黑森林 / 土門客棧</t>
-  </si>
-  <si>
-    <t>黑森林 / 土門客棧</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>黑森林 / 染坊</t>
-  </si>
-  <si>
-    <t>土門客棧 / 灰狼村</t>
-  </si>
-  <si>
     <t>悲鳴村 / 豬豬海岸</t>
   </si>
   <si>
@@ -1198,24 +1185,12 @@
     <t>巨岩海岸 / 染坊</t>
   </si>
   <si>
-    <t>黑森林 / 豬豬海岸</t>
-  </si>
-  <si>
-    <t>土門客棧 / 悲鳴村</t>
-  </si>
-  <si>
-    <t>黑森林 / 鬼都</t>
-  </si>
-  <si>
     <t>豬豬海岸 / 鬼都</t>
   </si>
   <si>
     <t>巨岩海岸 / 灰狼村</t>
   </si>
   <si>
-    <t>巨岩海岸 / 土門客棧</t>
-  </si>
-  <si>
     <t>鬼都 / 豬豬農場</t>
   </si>
   <si>
@@ -1243,12 +1218,6 @@
     <t>05:39</t>
   </si>
   <si>
-    <t>07:17_?</t>
-  </si>
-  <si>
-    <t>08:42_?</t>
-  </si>
-  <si>
     <t>16:19_?</t>
   </si>
   <si>
@@ -1744,10 +1713,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>01:0×</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>23:39</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2433,10 +2398,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>土門客棧 / 雪原(叛軍駐地)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鬼都 / 雪原(叛軍駐地)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2490,6 +2451,68 @@
   </si>
   <si>
     <t>09:06</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>21:40</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>白樺林</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:42</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:13</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>23:42</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>知性森林</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒森林 / 染坊</t>
+  </si>
+  <si>
+    <t>黒森林 / 孤村</t>
+  </si>
+  <si>
+    <t>黒森林 / 豬豬海岸</t>
+  </si>
+  <si>
+    <t>黒森林 / 鬼都</t>
+  </si>
+  <si>
+    <t>土門客桟 / 染坊</t>
+  </si>
+  <si>
+    <t>黒森林 / 土門客桟</t>
+  </si>
+  <si>
+    <t>土門客桟 / 雪原(叛軍駐地)</t>
+  </si>
+  <si>
+    <t>土門客桟 / 灰狼村</t>
+  </si>
+  <si>
+    <t>土門客桟 / 悲鳴村</t>
+  </si>
+  <si>
+    <t>巨岩海岸 / 土門客桟</t>
+  </si>
+  <si>
+    <t>16:55</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">灰狼村 / </t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2735,7 +2758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="225">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3301,112 +3324,7 @@
     <xf numFmtId="20" fontId="7" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3424,14 +3342,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF9999"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3824,7 +3742,7 @@
       <c r="E3" s="119"/>
       <c r="F3" s="118"/>
       <c r="G3" s="119" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="H3" s="118" t="s">
         <v>178</v>
@@ -3868,7 +3786,7 @@
       <c r="E5" s="118"/>
       <c r="F5" s="118"/>
       <c r="G5" s="119" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="H5" s="118" t="s">
         <v>178</v>
@@ -3892,7 +3810,7 @@
       <c r="E6" s="119"/>
       <c r="F6" s="118"/>
       <c r="G6" s="119" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="H6" s="118" t="s">
         <v>177</v>
@@ -3960,7 +3878,7 @@
       <c r="E9" s="119"/>
       <c r="F9" s="118"/>
       <c r="G9" s="119" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="H9" s="118" t="s">
         <v>175</v>
@@ -3984,7 +3902,7 @@
       <c r="E10" s="118"/>
       <c r="F10" s="118"/>
       <c r="G10" s="119" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="H10" s="118" t="s">
         <v>177</v>
@@ -4028,7 +3946,7 @@
       <c r="E12" s="119"/>
       <c r="F12" s="118"/>
       <c r="G12" s="119" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="H12" s="118" t="s">
         <v>175</v>
@@ -4052,7 +3970,7 @@
       <c r="E13" s="119"/>
       <c r="F13" s="118"/>
       <c r="G13" s="119" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="H13" s="118" t="s">
         <v>175</v>
@@ -4096,7 +4014,7 @@
       <c r="E15" s="119"/>
       <c r="F15" s="118"/>
       <c r="G15" s="119" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="H15" s="118" t="s">
         <v>175</v>
@@ -4120,7 +4038,7 @@
       <c r="E16" s="119"/>
       <c r="F16" s="118"/>
       <c r="G16" s="119" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="H16" s="118" t="s">
         <v>177</v>
@@ -4164,7 +4082,7 @@
       <c r="E18" s="119"/>
       <c r="F18" s="118"/>
       <c r="G18" s="119" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="H18" s="118" t="s">
         <v>175</v>
@@ -4188,7 +4106,7 @@
       <c r="E19" s="118"/>
       <c r="F19" s="118"/>
       <c r="G19" s="119" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="H19" s="118" t="s">
         <v>175</v>
@@ -4232,7 +4150,7 @@
       <c r="E21" s="118"/>
       <c r="F21" s="118"/>
       <c r="G21" s="119" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="H21" s="118" t="s">
         <v>175</v>
@@ -4276,7 +4194,7 @@
       <c r="E23" s="118"/>
       <c r="F23" s="118"/>
       <c r="G23" s="119" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="H23" s="118" t="s">
         <v>175</v>
@@ -4300,7 +4218,7 @@
       <c r="E24" s="118"/>
       <c r="F24" s="118"/>
       <c r="G24" s="119" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="H24" s="118" t="s">
         <v>175</v>
@@ -4344,7 +4262,7 @@
       <c r="E26" s="122"/>
       <c r="F26" s="121"/>
       <c r="G26" s="122" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="H26" s="121" t="s">
         <v>178</v>
@@ -4368,7 +4286,7 @@
       <c r="E27" s="123"/>
       <c r="F27" s="123"/>
       <c r="G27" s="124" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="H27" s="123" t="s">
         <v>175</v>
@@ -4412,7 +4330,7 @@
       <c r="E29" s="123"/>
       <c r="F29" s="123"/>
       <c r="G29" s="124" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="H29" s="123" t="s">
         <v>175</v>
@@ -4504,7 +4422,7 @@
       <c r="E33" s="124"/>
       <c r="F33" s="123"/>
       <c r="G33" s="124" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="H33" s="123" t="s">
         <v>178</v>
@@ -4704,11 +4622,11 @@
         <v>328</v>
       </c>
       <c r="C43" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D43" s="123"/>
       <c r="E43" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="F43" s="123"/>
       <c r="G43" s="123"/>
@@ -4728,11 +4646,11 @@
         <v>328</v>
       </c>
       <c r="C44" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D44" s="123"/>
       <c r="E44" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="F44" s="123"/>
       <c r="G44" s="123"/>
@@ -4792,7 +4710,7 @@
         <v>328</v>
       </c>
       <c r="C47" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D47" s="123"/>
       <c r="E47" s="124"/>
@@ -4814,7 +4732,7 @@
         <v>328</v>
       </c>
       <c r="C48" s="123" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D48" s="123"/>
       <c r="E48" s="123"/>
@@ -4836,7 +4754,7 @@
         <v>328</v>
       </c>
       <c r="C49" s="125" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D49" s="125"/>
       <c r="E49" s="125"/>
@@ -4858,7 +4776,7 @@
         <v>329</v>
       </c>
       <c r="C50" s="126" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D50" s="126"/>
       <c r="E50" s="126"/>
@@ -4880,7 +4798,7 @@
         <v>329</v>
       </c>
       <c r="C51" s="127" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D51" s="127"/>
       <c r="E51" s="128"/>
@@ -4902,7 +4820,7 @@
         <v>329</v>
       </c>
       <c r="C52" s="127" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D52" s="127"/>
       <c r="E52" s="127"/>
@@ -4924,11 +4842,11 @@
         <v>329</v>
       </c>
       <c r="C53" s="127" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D53" s="127"/>
       <c r="E53" s="127" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="F53" s="127"/>
       <c r="G53" s="127"/>
@@ -4988,22 +4906,22 @@
         <v>329</v>
       </c>
       <c r="C56" s="128" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="D56" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="F56" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G56" s="127" t="s">
         <v>36</v>
       </c>
       <c r="H56" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="I56" s="127" t="s">
         <v>18</v>
@@ -5020,22 +4938,22 @@
         <v>329</v>
       </c>
       <c r="C57" s="128" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="D57" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="F57" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G57" s="128" t="s">
         <v>39</v>
       </c>
       <c r="H57" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="I57" s="127" t="s">
         <v>17</v>
@@ -5052,22 +4970,22 @@
         <v>329</v>
       </c>
       <c r="C58" s="128" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="D58" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E58" s="127" t="s">
         <v>37</v>
       </c>
       <c r="F58" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G58" s="128" t="s">
         <v>37</v>
       </c>
       <c r="H58" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="I58" s="127" t="s">
         <v>16</v>
@@ -5084,22 +5002,22 @@
         <v>329</v>
       </c>
       <c r="C59" s="128" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D59" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E59" s="127" t="s">
         <v>38</v>
       </c>
       <c r="F59" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G59" s="128" t="s">
         <v>38</v>
       </c>
       <c r="H59" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="I59" s="127" t="s">
         <v>15</v>
@@ -5116,22 +5034,22 @@
         <v>329</v>
       </c>
       <c r="C60" s="128" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="D60" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E60" s="128" t="s">
         <v>228</v>
       </c>
       <c r="F60" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G60" s="127" t="s">
         <v>228</v>
       </c>
       <c r="H60" s="127" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="I60" s="127" t="s">
         <v>14</v>
@@ -5150,13 +5068,13 @@
       <c r="C61" s="127"/>
       <c r="D61" s="127"/>
       <c r="E61" s="128" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="F61" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G61" s="128" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="H61" s="127" t="s">
         <v>178</v>
@@ -5180,7 +5098,7 @@
       <c r="E62" s="128"/>
       <c r="F62" s="127"/>
       <c r="G62" s="128" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="H62" s="127" t="s">
         <v>178</v>
@@ -5202,7 +5120,7 @@
       <c r="C63" s="127"/>
       <c r="D63" s="127"/>
       <c r="E63" s="128" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="F63" s="127" t="s">
         <v>173</v>
@@ -5224,19 +5142,19 @@
         <v>329</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="D64" s="161" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="E64" s="128" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="F64" s="127" t="s">
         <v>174</v>
       </c>
       <c r="G64" s="128" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="H64" s="127" t="s">
         <v>175</v>
@@ -5260,7 +5178,7 @@
       <c r="E65" s="128"/>
       <c r="F65" s="127"/>
       <c r="G65" s="127" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="H65" s="127" t="s">
         <v>178</v>
@@ -5282,7 +5200,7 @@
       <c r="C66" s="127"/>
       <c r="D66" s="127"/>
       <c r="E66" s="128" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="F66" s="127" t="s">
         <v>174</v>
@@ -5306,13 +5224,13 @@
       <c r="C67" s="128"/>
       <c r="D67" s="127"/>
       <c r="E67" s="128" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="F67" s="127" t="s">
         <v>173</v>
       </c>
       <c r="G67" s="128" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="H67" s="127" t="s">
         <v>177</v>
@@ -5332,15 +5250,15 @@
         <v>329</v>
       </c>
       <c r="C68" s="128" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D68" s="162" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="E68" s="128"/>
       <c r="F68" s="127"/>
       <c r="G68" s="128" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="H68" s="127" t="s">
         <v>178</v>
@@ -5362,7 +5280,7 @@
       <c r="C69" s="127"/>
       <c r="D69" s="127"/>
       <c r="E69" s="128" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="F69" s="127" t="s">
         <v>174</v>
@@ -5386,13 +5304,13 @@
       <c r="C70" s="127"/>
       <c r="D70" s="127"/>
       <c r="E70" s="128" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="F70" s="127" t="s">
         <v>174</v>
       </c>
       <c r="G70" s="128" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="H70" s="127" t="s">
         <v>177</v>
@@ -5412,15 +5330,15 @@
         <v>329</v>
       </c>
       <c r="C71" s="128" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D71" s="162" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="E71" s="128"/>
       <c r="F71" s="127"/>
       <c r="G71" s="128" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="H71" s="127" t="s">
         <v>175</v>
@@ -5442,7 +5360,7 @@
       <c r="C72" s="127"/>
       <c r="D72" s="127"/>
       <c r="E72" s="128" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="F72" s="127" t="s">
         <v>174</v>
@@ -5466,13 +5384,13 @@
       <c r="C73" s="149"/>
       <c r="D73" s="129"/>
       <c r="E73" s="149" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="F73" s="129" t="s">
         <v>173</v>
       </c>
       <c r="G73" s="149" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="H73" s="129" t="s">
         <v>175</v>
@@ -5518,13 +5436,13 @@
       <c r="C75" s="131"/>
       <c r="D75" s="131"/>
       <c r="E75" s="132" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="F75" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G75" s="132" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="H75" s="131" t="s">
         <v>175</v>
@@ -5546,7 +5464,7 @@
       <c r="C76" s="132"/>
       <c r="D76" s="131"/>
       <c r="E76" s="132" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="F76" s="131" t="s">
         <v>174</v>
@@ -5594,13 +5512,13 @@
       <c r="C78" s="132"/>
       <c r="D78" s="131"/>
       <c r="E78" s="132" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="F78" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G78" s="132" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="H78" s="131" t="s">
         <v>175</v>
@@ -5622,7 +5540,7 @@
       <c r="C79" s="131"/>
       <c r="D79" s="131"/>
       <c r="E79" s="132" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="F79" s="131" t="s">
         <v>174</v>
@@ -5670,7 +5588,7 @@
       <c r="C81" s="132"/>
       <c r="D81" s="131"/>
       <c r="E81" s="132" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="F81" s="131" t="s">
         <v>173</v>
@@ -5698,7 +5616,7 @@
       <c r="C82" s="132"/>
       <c r="D82" s="131"/>
       <c r="E82" s="132" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="F82" s="131" t="s">
         <v>173</v>
@@ -5720,15 +5638,15 @@
         <v>330</v>
       </c>
       <c r="C83" s="132" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="D83" s="187" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="E83" s="132"/>
       <c r="F83" s="131"/>
       <c r="G83" s="132" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="H83" s="131" t="s">
         <v>177</v>
@@ -5750,13 +5668,13 @@
       <c r="C84" s="131"/>
       <c r="D84" s="131"/>
       <c r="E84" s="132" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="F84" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G84" s="132" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="H84" s="131" t="s">
         <v>175</v>
@@ -5778,13 +5696,13 @@
       <c r="C85" s="132"/>
       <c r="D85" s="131"/>
       <c r="E85" s="188" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="F85" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G85" s="132" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="H85" s="131" t="s">
         <v>177</v>
@@ -5804,10 +5722,10 @@
         <v>330</v>
       </c>
       <c r="C86" s="132" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="D86" s="187" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="E86" s="132"/>
       <c r="F86" s="131"/>
@@ -5830,13 +5748,13 @@
       <c r="C87" s="131"/>
       <c r="D87" s="131"/>
       <c r="E87" s="132" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="F87" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G87" s="132" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="H87" s="131" t="s">
         <v>177</v>
@@ -5858,7 +5776,7 @@
       <c r="C88" s="131"/>
       <c r="D88" s="131"/>
       <c r="E88" s="132" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="F88" s="131" t="s">
         <v>174</v>
@@ -5880,19 +5798,19 @@
         <v>330</v>
       </c>
       <c r="C89" s="132" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="D89" s="131" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="E89" s="132" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="F89" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G89" s="132" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="H89" s="131" t="s">
         <v>178</v>
@@ -5916,7 +5834,7 @@
       <c r="E90" s="132"/>
       <c r="F90" s="131"/>
       <c r="G90" s="132" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="H90" s="131" t="s">
         <v>175</v>
@@ -5938,13 +5856,13 @@
       <c r="C91" s="131"/>
       <c r="D91" s="131"/>
       <c r="E91" s="132" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="F91" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G91" s="132" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="H91" s="131" t="s">
         <v>178</v>
@@ -5986,13 +5904,13 @@
       <c r="C93" s="131"/>
       <c r="D93" s="131"/>
       <c r="E93" s="132" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="F93" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G93" s="132" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="H93" s="131" t="s">
         <v>177</v>
@@ -6014,13 +5932,13 @@
       <c r="C94" s="132"/>
       <c r="D94" s="131"/>
       <c r="E94" s="132" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="F94" s="131" t="s">
         <v>174</v>
       </c>
       <c r="G94" s="132" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="H94" s="131" t="s">
         <v>177</v>
@@ -6060,19 +5978,19 @@
         <v>330</v>
       </c>
       <c r="C96" s="132" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="D96" s="186" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="E96" s="132" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F96" s="131" t="s">
         <v>173</v>
       </c>
       <c r="G96" s="132" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="H96" s="131" t="s">
         <v>175</v>
@@ -6094,7 +6012,7 @@
       <c r="C97" s="133"/>
       <c r="D97" s="133"/>
       <c r="E97" s="151" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="F97" s="133" t="s">
         <v>174</v>
@@ -6122,13 +6040,13 @@
       <c r="C98" s="134"/>
       <c r="D98" s="135"/>
       <c r="E98" s="134" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="F98" s="135" t="s">
         <v>174</v>
       </c>
       <c r="G98" s="134" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="H98" s="135" t="s">
         <v>178</v>
@@ -6150,7 +6068,7 @@
       <c r="C99" s="136"/>
       <c r="D99" s="136"/>
       <c r="E99" s="137" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F99" s="136" t="s">
         <v>174</v>
@@ -6174,13 +6092,13 @@
       <c r="C100" s="137"/>
       <c r="D100" s="136"/>
       <c r="E100" s="137" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="F100" s="136" t="s">
         <v>173</v>
       </c>
       <c r="G100" s="137" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="H100" s="136" t="s">
         <v>177</v>
@@ -6204,7 +6122,7 @@
       <c r="E101" s="137"/>
       <c r="F101" s="136"/>
       <c r="G101" s="137" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="H101" s="136" t="s">
         <v>175</v>
@@ -6226,7 +6144,7 @@
       <c r="C102" s="136"/>
       <c r="D102" s="136"/>
       <c r="E102" s="137" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F102" s="136" t="s">
         <v>173</v>
@@ -6250,13 +6168,13 @@
       <c r="C103" s="137"/>
       <c r="D103" s="136"/>
       <c r="E103" s="137" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="F103" s="136" t="s">
         <v>173</v>
       </c>
       <c r="G103" s="137" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="H103" s="136" t="s">
         <v>175</v>
@@ -6280,7 +6198,7 @@
       <c r="E104" s="136"/>
       <c r="F104" s="136"/>
       <c r="G104" s="137" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="H104" s="136" t="s">
         <v>175</v>
@@ -6302,7 +6220,7 @@
       <c r="C105" s="136"/>
       <c r="D105" s="136"/>
       <c r="E105" s="137" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="F105" s="136" t="s">
         <v>173</v>
@@ -6328,7 +6246,7 @@
       <c r="E106" s="137"/>
       <c r="F106" s="136"/>
       <c r="G106" s="137" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="H106" s="136" t="s">
         <v>175</v>
@@ -6352,7 +6270,7 @@
       <c r="E107" s="136"/>
       <c r="F107" s="136"/>
       <c r="G107" s="137" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="H107" s="136" t="s">
         <v>178</v>
@@ -6374,10 +6292,10 @@
       <c r="C108" s="136"/>
       <c r="D108" s="136"/>
       <c r="E108" s="137" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="F108" s="163" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="G108" s="137"/>
       <c r="H108" s="164"/>
@@ -6400,7 +6318,7 @@
       <c r="E109" s="137"/>
       <c r="F109" s="136"/>
       <c r="G109" s="137" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="H109" s="164" t="s">
         <v>175</v>
@@ -6424,7 +6342,7 @@
       <c r="E110" s="136"/>
       <c r="F110" s="136"/>
       <c r="G110" s="137" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="H110" s="136" t="s">
         <v>178</v>
@@ -6468,7 +6386,7 @@
       <c r="E112" s="137"/>
       <c r="F112" s="136"/>
       <c r="G112" s="137" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="H112" s="136" t="s">
         <v>178</v>
@@ -6492,7 +6410,7 @@
       <c r="E113" s="136"/>
       <c r="F113" s="136"/>
       <c r="G113" s="137" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="H113" s="136" t="s">
         <v>178</v>
@@ -6536,7 +6454,7 @@
       <c r="E115" s="137"/>
       <c r="F115" s="136"/>
       <c r="G115" s="137" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="H115" s="136" t="s">
         <v>175</v>
@@ -6560,7 +6478,7 @@
       <c r="E116" s="136"/>
       <c r="F116" s="136"/>
       <c r="G116" s="137" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="H116" s="136" t="s">
         <v>175</v>
@@ -6604,7 +6522,7 @@
       <c r="E118" s="137"/>
       <c r="F118" s="136"/>
       <c r="G118" s="137" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="H118" s="136" t="s">
         <v>178</v>
@@ -6628,7 +6546,7 @@
       <c r="E119" s="136"/>
       <c r="F119" s="136"/>
       <c r="G119" s="137" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="H119" s="136" t="s">
         <v>178</v>
@@ -6672,7 +6590,7 @@
       <c r="E121" s="139"/>
       <c r="F121" s="138"/>
       <c r="G121" s="139" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="H121" s="138" t="s">
         <v>177</v>
@@ -6696,7 +6614,7 @@
       <c r="E122" s="141"/>
       <c r="F122" s="140"/>
       <c r="G122" s="141" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="H122" s="140" t="s">
         <v>177</v>
@@ -6720,7 +6638,7 @@
       <c r="E123" s="143"/>
       <c r="F123" s="143"/>
       <c r="G123" s="142" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="H123" s="143" t="s">
         <v>177</v>
@@ -6764,7 +6682,7 @@
       <c r="E125" s="142"/>
       <c r="F125" s="143"/>
       <c r="G125" s="142" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="H125" s="143" t="s">
         <v>177</v>
@@ -6788,7 +6706,7 @@
       <c r="E126" s="143"/>
       <c r="F126" s="143"/>
       <c r="G126" s="142" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="H126" s="143" t="s">
         <v>177</v>
@@ -6832,7 +6750,7 @@
       <c r="E128" s="142"/>
       <c r="F128" s="143"/>
       <c r="G128" s="142" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="H128" s="143" t="s">
         <v>177</v>
@@ -6856,7 +6774,7 @@
       <c r="E129" s="142"/>
       <c r="F129" s="143"/>
       <c r="G129" s="142" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="H129" s="143" t="s">
         <v>175</v>
@@ -6900,7 +6818,7 @@
       <c r="E131" s="143"/>
       <c r="F131" s="143"/>
       <c r="G131" s="142" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="H131" s="143" t="s">
         <v>178</v>
@@ -6924,7 +6842,7 @@
       <c r="E132" s="142"/>
       <c r="F132" s="143"/>
       <c r="G132" s="142" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="H132" s="143" t="s">
         <v>178</v>
@@ -6948,7 +6866,7 @@
       <c r="E133" s="142"/>
       <c r="F133" s="143"/>
       <c r="G133" s="142" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="H133" s="143" t="s">
         <v>177</v>
@@ -6992,7 +6910,7 @@
       <c r="E135" s="143"/>
       <c r="F135" s="143"/>
       <c r="G135" s="142" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="H135" s="143" t="s">
         <v>178</v>
@@ -7016,7 +6934,7 @@
       <c r="E136" s="142"/>
       <c r="F136" s="143"/>
       <c r="G136" s="142" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="H136" s="143" t="s">
         <v>178</v>
@@ -7060,7 +6978,7 @@
       <c r="E138" s="143"/>
       <c r="F138" s="143"/>
       <c r="G138" s="142" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="H138" s="143" t="s">
         <v>177</v>
@@ -7084,7 +7002,7 @@
       <c r="E139" s="142"/>
       <c r="F139" s="143"/>
       <c r="G139" s="142" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="H139" s="143" t="s">
         <v>178</v>
@@ -7128,7 +7046,7 @@
       <c r="E141" s="142"/>
       <c r="F141" s="143"/>
       <c r="G141" s="142" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="H141" s="143" t="s">
         <v>177</v>
@@ -7152,7 +7070,7 @@
       <c r="E142" s="142"/>
       <c r="F142" s="143"/>
       <c r="G142" s="142" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="H142" s="143" t="s">
         <v>175</v>
@@ -7196,7 +7114,7 @@
       <c r="E144" s="143"/>
       <c r="F144" s="143"/>
       <c r="G144" s="142" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="H144" s="143" t="s">
         <v>178</v>
@@ -7220,7 +7138,7 @@
       <c r="E145" s="152"/>
       <c r="F145" s="144"/>
       <c r="G145" s="152" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="H145" s="144" t="s">
         <v>175</v>
@@ -7264,7 +7182,7 @@
       <c r="E147" s="146"/>
       <c r="F147" s="146"/>
       <c r="G147" s="147" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="H147" s="146" t="s">
         <v>177</v>
@@ -7288,7 +7206,7 @@
       <c r="E148" s="147"/>
       <c r="F148" s="146"/>
       <c r="G148" s="147" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="H148" s="146" t="s">
         <v>177</v>
@@ -7332,7 +7250,7 @@
       <c r="E150" s="146"/>
       <c r="F150" s="146"/>
       <c r="G150" s="147" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="H150" s="146" t="s">
         <v>175</v>
@@ -7356,7 +7274,7 @@
       <c r="E151" s="147"/>
       <c r="F151" s="146"/>
       <c r="G151" s="147" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="H151" s="146" t="s">
         <v>175</v>
@@ -7400,7 +7318,7 @@
       <c r="E153" s="146"/>
       <c r="F153" s="146"/>
       <c r="G153" s="147" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="H153" s="146" t="s">
         <v>175</v>
@@ -7424,7 +7342,7 @@
       <c r="E154" s="147"/>
       <c r="F154" s="146"/>
       <c r="G154" s="147" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="H154" s="146" t="s">
         <v>177</v>
@@ -7468,7 +7386,7 @@
       <c r="E156" s="146"/>
       <c r="F156" s="146"/>
       <c r="G156" s="147" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="H156" s="146" t="s">
         <v>175</v>
@@ -7492,7 +7410,7 @@
       <c r="E157" s="146"/>
       <c r="F157" s="146"/>
       <c r="G157" s="147" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="H157" s="146" t="s">
         <v>177</v>
@@ -7516,7 +7434,7 @@
       <c r="E158" s="147"/>
       <c r="F158" s="146"/>
       <c r="G158" s="147" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="H158" s="146" t="s">
         <v>178</v>
@@ -7560,7 +7478,7 @@
       <c r="E160" s="147"/>
       <c r="F160" s="146"/>
       <c r="G160" s="147" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="H160" s="146" t="s">
         <v>177</v>
@@ -7604,7 +7522,7 @@
       <c r="E162" s="146"/>
       <c r="F162" s="146"/>
       <c r="G162" s="147" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="H162" s="146" t="s">
         <v>178</v>
@@ -7628,7 +7546,7 @@
       <c r="E163" s="146"/>
       <c r="F163" s="146"/>
       <c r="G163" s="147" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="H163" s="146" t="s">
         <v>177</v>
@@ -7672,7 +7590,7 @@
       <c r="E165" s="146"/>
       <c r="F165" s="146"/>
       <c r="G165" s="147" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="H165" s="146" t="s">
         <v>178</v>
@@ -7696,7 +7614,7 @@
       <c r="E166" s="146"/>
       <c r="F166" s="146"/>
       <c r="G166" s="147" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="H166" s="146" t="s">
         <v>177</v>
@@ -7740,7 +7658,7 @@
       <c r="E168" s="146"/>
       <c r="F168" s="146"/>
       <c r="G168" s="147" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="H168" s="146" t="s">
         <v>177</v>
@@ -7764,7 +7682,7 @@
       <c r="E169" s="146"/>
       <c r="F169" s="146"/>
       <c r="G169" s="147" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="H169" s="146" t="s">
         <v>177</v>
@@ -10465,11 +10383,11 @@
   <cols>
     <col min="1" max="1" width="4.25" style="111" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" style="111" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="216" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="111" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="111" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="216" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="111" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="111" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="216" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="111" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.875" style="111" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.25" style="111" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3.125" style="111" bestFit="1" customWidth="1"/>
@@ -10488,19 +10406,19 @@
       <c r="B1" s="156" t="s">
         <v>326</v>
       </c>
-      <c r="C1" s="189" t="s">
+      <c r="C1" s="117" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="189" t="s">
+      <c r="E1" s="117" t="s">
         <v>33</v>
       </c>
       <c r="F1" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="189" t="s">
+      <c r="G1" s="117" t="s">
         <v>85</v>
       </c>
       <c r="H1" s="117" t="s">
@@ -10516,16 +10434,16 @@
       <c r="B2" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C2" s="190" t="s">
-        <v>431</v>
+      <c r="C2" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D2" s="118"/>
-      <c r="E2" s="190" t="s">
-        <v>431</v>
+      <c r="E2" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F2" s="118"/>
-      <c r="G2" s="190" t="s">
-        <v>431</v>
+      <c r="G2" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H2" s="118"/>
       <c r="I2" s="118" t="s">
@@ -10542,18 +10460,18 @@
       <c r="B3" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C3" s="190" t="s">
-        <v>431</v>
+      <c r="C3" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D3" s="118"/>
-      <c r="E3" s="191" t="s">
-        <v>522</v>
+      <c r="E3" s="119" t="s">
+        <v>511</v>
       </c>
       <c r="F3" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G3" s="191" t="s">
-        <v>506</v>
+      <c r="G3" s="119" t="s">
+        <v>648</v>
       </c>
       <c r="H3" s="118" t="s">
         <v>177</v>
@@ -10572,23 +10490,23 @@
       <c r="B4" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C4" s="191" t="s">
-        <v>385</v>
+      <c r="C4" s="119" t="s">
+        <v>375</v>
       </c>
       <c r="D4" s="118" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="191" t="s">
-        <v>523</v>
+      <c r="E4" s="119" t="s">
+        <v>512</v>
       </c>
       <c r="F4" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="G4" s="191" t="s">
-        <v>361</v>
-      </c>
-      <c r="H4" s="118" t="s">
-        <v>272</v>
+      <c r="G4" s="119" t="s">
+        <v>353</v>
+      </c>
+      <c r="H4" s="159" t="s">
+        <v>176</v>
       </c>
       <c r="I4" s="118" t="s">
         <v>22</v>
@@ -10604,16 +10522,16 @@
       <c r="B5" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C5" s="190" t="s">
-        <v>431</v>
+      <c r="C5" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D5" s="118"/>
-      <c r="E5" s="190" t="s">
-        <v>431</v>
+      <c r="E5" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F5" s="118"/>
-      <c r="G5" s="190" t="s">
-        <v>431</v>
+      <c r="G5" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H5" s="118"/>
       <c r="I5" s="118" t="s">
@@ -10630,18 +10548,18 @@
       <c r="B6" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C6" s="190" t="s">
-        <v>431</v>
+      <c r="C6" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D6" s="118"/>
-      <c r="E6" s="191" t="s">
-        <v>524</v>
+      <c r="E6" s="119" t="s">
+        <v>513</v>
       </c>
       <c r="F6" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G6" s="191" t="s">
-        <v>362</v>
+      <c r="G6" s="119" t="s">
+        <v>354</v>
       </c>
       <c r="H6" s="118" t="s">
         <v>176</v>
@@ -10660,18 +10578,18 @@
       <c r="B7" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="191" t="s">
-        <v>386</v>
+      <c r="C7" s="119" t="s">
+        <v>376</v>
       </c>
       <c r="D7" s="118" t="s">
-        <v>356</v>
-      </c>
-      <c r="E7" s="190" t="s">
-        <v>431</v>
+        <v>348</v>
+      </c>
+      <c r="E7" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F7" s="118"/>
-      <c r="G7" s="191" t="s">
-        <v>363</v>
+      <c r="G7" s="119" t="s">
+        <v>355</v>
       </c>
       <c r="H7" s="118" t="s">
         <v>294</v>
@@ -10690,18 +10608,18 @@
       <c r="B8" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C8" s="190" t="s">
-        <v>431</v>
+      <c r="C8" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D8" s="118"/>
-      <c r="E8" s="191" t="s">
-        <v>525</v>
+      <c r="E8" s="119" t="s">
+        <v>514</v>
       </c>
       <c r="F8" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G8" s="190" t="s">
-        <v>431</v>
+      <c r="G8" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H8" s="118"/>
       <c r="I8" s="118" t="s">
@@ -10718,18 +10636,18 @@
       <c r="B9" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C9" s="190" t="s">
-        <v>431</v>
+      <c r="C9" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D9" s="118"/>
-      <c r="E9" s="191" t="s">
-        <v>526</v>
+      <c r="E9" s="119" t="s">
+        <v>515</v>
       </c>
       <c r="F9" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="G9" s="191" t="s">
-        <v>364</v>
+      <c r="G9" s="119" t="s">
+        <v>691</v>
       </c>
       <c r="H9" s="118" t="s">
         <v>294</v>
@@ -10748,18 +10666,18 @@
       <c r="B10" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C10" s="191" t="s">
+      <c r="C10" s="119" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="E10" s="190" t="s">
-        <v>431</v>
+        <v>349</v>
+      </c>
+      <c r="E10" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F10" s="118"/>
-      <c r="G10" s="191" t="s">
-        <v>365</v>
+      <c r="G10" s="119" t="s">
+        <v>690</v>
       </c>
       <c r="H10" s="118" t="s">
         <v>272</v>
@@ -10778,18 +10696,18 @@
       <c r="B11" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C11" s="190" t="s">
-        <v>431</v>
+      <c r="C11" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D11" s="118"/>
-      <c r="E11" s="191" t="s">
-        <v>527</v>
+      <c r="E11" s="119" t="s">
+        <v>516</v>
       </c>
       <c r="F11" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="G11" s="190" t="s">
-        <v>431</v>
+      <c r="G11" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H11" s="118"/>
       <c r="I11" s="118" t="s">
@@ -10806,18 +10724,18 @@
       <c r="B12" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C12" s="190" t="s">
-        <v>431</v>
+      <c r="C12" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D12" s="118"/>
-      <c r="E12" s="191" t="s">
+      <c r="E12" s="119" t="s">
         <v>296</v>
       </c>
       <c r="F12" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G12" s="191" t="s">
-        <v>413</v>
+      <c r="G12" s="119" t="s">
+        <v>403</v>
       </c>
       <c r="H12" s="118" t="s">
         <v>176</v>
@@ -10836,17 +10754,17 @@
       <c r="B13" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="190" t="s">
-        <v>431</v>
+      <c r="C13" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D13" s="118"/>
-      <c r="E13" s="191" t="s">
-        <v>528</v>
+      <c r="E13" s="119" t="s">
+        <v>517</v>
       </c>
       <c r="F13" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="G13" s="191" t="s">
+      <c r="G13" s="119" t="s">
         <v>43</v>
       </c>
       <c r="H13" s="118" t="s">
@@ -10866,18 +10784,18 @@
       <c r="B14" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C14" s="191" t="s">
-        <v>387</v>
+      <c r="C14" s="119" t="s">
+        <v>377</v>
       </c>
       <c r="D14" s="118" t="s">
-        <v>179</v>
-      </c>
-      <c r="E14" s="190" t="s">
-        <v>431</v>
+        <v>698</v>
+      </c>
+      <c r="E14" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F14" s="118"/>
-      <c r="G14" s="190" t="s">
-        <v>431</v>
+      <c r="G14" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H14" s="118"/>
       <c r="I14" s="118" t="s">
@@ -10894,17 +10812,17 @@
       <c r="B15" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="190" t="s">
-        <v>431</v>
+      <c r="C15" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D15" s="118"/>
-      <c r="E15" s="191" t="s">
-        <v>410</v>
+      <c r="E15" s="119" t="s">
+        <v>400</v>
       </c>
       <c r="F15" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G15" s="191" t="s">
+      <c r="G15" s="119" t="s">
         <v>41</v>
       </c>
       <c r="H15" s="118" t="s">
@@ -10924,18 +10842,18 @@
       <c r="B16" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C16" s="190" t="s">
-        <v>431</v>
+      <c r="C16" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D16" s="118"/>
-      <c r="E16" s="191" t="s">
-        <v>529</v>
+      <c r="E16" s="119" t="s">
+        <v>518</v>
       </c>
       <c r="F16" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G16" s="191" t="s">
-        <v>414</v>
+      <c r="G16" s="119" t="s">
+        <v>404</v>
       </c>
       <c r="H16" s="118" t="s">
         <v>272</v>
@@ -10954,16 +10872,16 @@
       <c r="B17" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="190" t="s">
-        <v>431</v>
+      <c r="C17" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D17" s="118"/>
-      <c r="E17" s="190" t="s">
-        <v>431</v>
+      <c r="E17" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F17" s="118"/>
-      <c r="G17" s="190" t="s">
-        <v>431</v>
+      <c r="G17" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H17" s="118"/>
       <c r="I17" s="118" t="s">
@@ -10980,18 +10898,20 @@
       <c r="B18" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C18" s="190" t="s">
-        <v>431</v>
-      </c>
-      <c r="D18" s="118"/>
-      <c r="E18" s="191" t="s">
-        <v>530</v>
+      <c r="C18" s="119" t="s">
+        <v>704</v>
+      </c>
+      <c r="D18" s="158" t="s">
+        <v>705</v>
+      </c>
+      <c r="E18" s="119" t="s">
+        <v>519</v>
       </c>
       <c r="F18" s="118" t="s">
         <v>305</v>
       </c>
-      <c r="G18" s="191" t="s">
-        <v>366</v>
+      <c r="G18" s="119" t="s">
+        <v>356</v>
       </c>
       <c r="H18" s="118" t="s">
         <v>176</v>
@@ -11010,16 +10930,16 @@
       <c r="B19" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="190" t="s">
-        <v>431</v>
+      <c r="C19" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D19" s="118"/>
-      <c r="E19" s="190" t="s">
-        <v>431</v>
+      <c r="E19" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F19" s="118"/>
-      <c r="G19" s="191" t="s">
-        <v>367</v>
+      <c r="G19" s="119" t="s">
+        <v>357</v>
       </c>
       <c r="H19" s="118" t="s">
         <v>272</v>
@@ -11038,16 +10958,16 @@
       <c r="B20" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C20" s="190" t="s">
-        <v>431</v>
+      <c r="C20" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D20" s="118"/>
-      <c r="E20" s="190" t="s">
-        <v>431</v>
+      <c r="E20" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F20" s="118"/>
-      <c r="G20" s="190" t="s">
-        <v>431</v>
+      <c r="G20" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H20" s="118"/>
       <c r="I20" s="118" t="s">
@@ -11064,16 +10984,16 @@
       <c r="B21" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="190" t="s">
-        <v>431</v>
+      <c r="C21" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D21" s="118"/>
-      <c r="E21" s="190" t="s">
-        <v>431</v>
+      <c r="E21" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F21" s="118"/>
-      <c r="G21" s="191" t="s">
-        <v>692</v>
+      <c r="G21" s="119" t="s">
+        <v>680</v>
       </c>
       <c r="H21" s="158" t="s">
         <v>272</v>
@@ -11092,18 +11012,18 @@
       <c r="B22" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C22" s="190" t="s">
-        <v>431</v>
+      <c r="C22" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D22" s="118"/>
-      <c r="E22" s="191" t="s">
+      <c r="E22" s="119" t="s">
         <v>69</v>
       </c>
       <c r="F22" s="118" t="s">
         <v>295</v>
       </c>
-      <c r="G22" s="191" t="s">
-        <v>368</v>
+      <c r="G22" s="119" t="s">
+        <v>358</v>
       </c>
       <c r="H22" s="118" t="s">
         <v>176</v>
@@ -11122,16 +11042,16 @@
       <c r="B23" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C23" s="190" t="s">
-        <v>431</v>
+      <c r="C23" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D23" s="118"/>
-      <c r="E23" s="190" t="s">
-        <v>431</v>
+      <c r="E23" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F23" s="118"/>
-      <c r="G23" s="190" t="s">
-        <v>431</v>
+      <c r="G23" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="H23" s="118"/>
       <c r="I23" s="118" t="s">
@@ -11148,16 +11068,16 @@
       <c r="B24" s="118" t="s">
         <v>327</v>
       </c>
-      <c r="C24" s="190" t="s">
-        <v>431</v>
+      <c r="C24" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="D24" s="118"/>
-      <c r="E24" s="190" t="s">
-        <v>431</v>
+      <c r="E24" s="118" t="s">
+        <v>421</v>
       </c>
       <c r="F24" s="118"/>
-      <c r="G24" s="191" t="s">
-        <v>693</v>
+      <c r="G24" s="119" t="s">
+        <v>681</v>
       </c>
       <c r="H24" s="159" t="s">
         <v>294</v>
@@ -11176,16 +11096,16 @@
       <c r="B25" s="120" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="192" t="s">
-        <v>431</v>
+      <c r="C25" s="120" t="s">
+        <v>421</v>
       </c>
       <c r="D25" s="120"/>
-      <c r="E25" s="192" t="s">
-        <v>431</v>
+      <c r="E25" s="120" t="s">
+        <v>421</v>
       </c>
       <c r="F25" s="120"/>
-      <c r="G25" s="192" t="s">
-        <v>431</v>
+      <c r="G25" s="120" t="s">
+        <v>421</v>
       </c>
       <c r="H25" s="120"/>
       <c r="I25" s="120" t="s">
@@ -11202,18 +11122,18 @@
       <c r="B26" s="121" t="s">
         <v>328</v>
       </c>
-      <c r="C26" s="193" t="s">
-        <v>431</v>
+      <c r="C26" s="121" t="s">
+        <v>421</v>
       </c>
       <c r="D26" s="121"/>
-      <c r="E26" s="217" t="s">
-        <v>531</v>
+      <c r="E26" s="122" t="s">
+        <v>520</v>
       </c>
       <c r="F26" s="121" t="s">
         <v>305</v>
       </c>
-      <c r="G26" s="217" t="s">
-        <v>369</v>
+      <c r="G26" s="122" t="s">
+        <v>359</v>
       </c>
       <c r="H26" s="121" t="s">
         <v>272</v>
@@ -11232,16 +11152,16 @@
       <c r="B27" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C27" s="194" t="s">
-        <v>431</v>
+      <c r="C27" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D27" s="123"/>
-      <c r="E27" s="194" t="s">
-        <v>431</v>
+      <c r="E27" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F27" s="123"/>
-      <c r="G27" s="195" t="s">
-        <v>694</v>
+      <c r="G27" s="124" t="s">
+        <v>682</v>
       </c>
       <c r="H27" s="160" t="s">
         <v>176</v>
@@ -11260,16 +11180,16 @@
       <c r="B28" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C28" s="194" t="s">
-        <v>431</v>
+      <c r="C28" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D28" s="123"/>
-      <c r="E28" s="194" t="s">
-        <v>431</v>
+      <c r="E28" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F28" s="123"/>
-      <c r="G28" s="194" t="s">
-        <v>431</v>
+      <c r="G28" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H28" s="123"/>
       <c r="I28" s="123" t="s">
@@ -11286,19 +11206,19 @@
       <c r="B29" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C29" s="194" t="s">
-        <v>431</v>
+      <c r="C29" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D29" s="123"/>
-      <c r="E29" s="194" t="s">
-        <v>431</v>
+      <c r="E29" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F29" s="123"/>
-      <c r="G29" s="195" t="s">
-        <v>627</v>
+      <c r="G29" s="124" t="s">
+        <v>616</v>
       </c>
       <c r="H29" s="160" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="I29" s="123" t="s">
         <v>21</v>
@@ -11314,16 +11234,16 @@
       <c r="B30" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C30" s="194" t="s">
-        <v>431</v>
+      <c r="C30" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D30" s="123"/>
-      <c r="E30" s="194" t="s">
-        <v>431</v>
+      <c r="E30" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F30" s="123"/>
-      <c r="G30" s="195" t="s">
-        <v>695</v>
+      <c r="G30" s="124" t="s">
+        <v>683</v>
       </c>
       <c r="H30" s="123" t="s">
         <v>272</v>
@@ -11342,16 +11262,16 @@
       <c r="B31" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C31" s="194" t="s">
-        <v>431</v>
+      <c r="C31" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D31" s="123"/>
-      <c r="E31" s="194" t="s">
-        <v>431</v>
+      <c r="E31" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F31" s="123"/>
-      <c r="G31" s="194" t="s">
-        <v>431</v>
+      <c r="G31" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H31" s="123"/>
       <c r="I31" s="123" t="s">
@@ -11368,16 +11288,16 @@
       <c r="B32" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C32" s="194" t="s">
-        <v>431</v>
+      <c r="C32" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D32" s="123"/>
-      <c r="E32" s="194" t="s">
-        <v>431</v>
+      <c r="E32" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F32" s="123"/>
-      <c r="G32" s="195" t="s">
-        <v>370</v>
+      <c r="G32" s="124" t="s">
+        <v>360</v>
       </c>
       <c r="H32" s="123" t="s">
         <v>294</v>
@@ -11396,18 +11316,18 @@
       <c r="B33" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C33" s="194" t="s">
-        <v>431</v>
+      <c r="C33" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D33" s="123"/>
-      <c r="E33" s="195" t="s">
-        <v>532</v>
+      <c r="E33" s="124" t="s">
+        <v>521</v>
       </c>
       <c r="F33" s="123" t="s">
         <v>295</v>
       </c>
-      <c r="G33" s="195" t="s">
-        <v>371</v>
+      <c r="G33" s="124" t="s">
+        <v>361</v>
       </c>
       <c r="H33" s="123" t="s">
         <v>294</v>
@@ -11426,18 +11346,18 @@
       <c r="B34" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C34" s="194" t="s">
-        <v>431</v>
+      <c r="C34" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D34" s="123"/>
-      <c r="E34" s="195" t="s">
-        <v>533</v>
+      <c r="E34" s="124" t="s">
+        <v>522</v>
       </c>
       <c r="F34" s="123" t="s">
         <v>295</v>
       </c>
-      <c r="G34" s="195" t="s">
-        <v>372</v>
+      <c r="G34" s="124" t="s">
+        <v>362</v>
       </c>
       <c r="H34" s="123" t="s">
         <v>272</v>
@@ -11456,16 +11376,16 @@
       <c r="B35" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C35" s="194" t="s">
-        <v>431</v>
+      <c r="C35" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D35" s="123"/>
-      <c r="E35" s="194" t="s">
-        <v>431</v>
+      <c r="E35" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F35" s="123"/>
-      <c r="G35" s="194" t="s">
-        <v>431</v>
+      <c r="G35" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H35" s="123"/>
       <c r="I35" s="123" t="s">
@@ -11482,18 +11402,18 @@
       <c r="B36" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C36" s="194" t="s">
-        <v>431</v>
+      <c r="C36" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D36" s="123"/>
-      <c r="E36" s="195" t="s">
-        <v>534</v>
+      <c r="E36" s="124" t="s">
+        <v>523</v>
       </c>
       <c r="F36" s="123" t="s">
         <v>305</v>
       </c>
-      <c r="G36" s="195" t="s">
-        <v>373</v>
+      <c r="G36" s="124" t="s">
+        <v>363</v>
       </c>
       <c r="H36" s="123" t="s">
         <v>272</v>
@@ -11512,16 +11432,16 @@
       <c r="B37" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C37" s="194" t="s">
-        <v>431</v>
+      <c r="C37" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D37" s="123"/>
-      <c r="E37" s="194" t="s">
-        <v>431</v>
+      <c r="E37" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F37" s="123"/>
-      <c r="G37" s="195" t="s">
-        <v>374</v>
+      <c r="G37" s="124" t="s">
+        <v>364</v>
       </c>
       <c r="H37" s="123" t="s">
         <v>294</v>
@@ -11540,16 +11460,16 @@
       <c r="B38" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C38" s="194" t="s">
-        <v>431</v>
+      <c r="C38" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D38" s="123"/>
-      <c r="E38" s="194" t="s">
-        <v>431</v>
+      <c r="E38" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F38" s="123"/>
-      <c r="G38" s="194" t="s">
-        <v>431</v>
+      <c r="G38" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H38" s="123"/>
       <c r="I38" s="123" t="s">
@@ -11566,18 +11486,18 @@
       <c r="B39" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C39" s="194" t="s">
-        <v>431</v>
+      <c r="C39" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D39" s="123"/>
-      <c r="E39" s="195" t="s">
-        <v>535</v>
+      <c r="E39" s="124" t="s">
+        <v>524</v>
       </c>
       <c r="F39" s="123" t="s">
         <v>295</v>
       </c>
-      <c r="G39" s="195" t="s">
-        <v>375</v>
+      <c r="G39" s="124" t="s">
+        <v>365</v>
       </c>
       <c r="H39" s="123" t="s">
         <v>272</v>
@@ -11596,16 +11516,16 @@
       <c r="B40" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C40" s="194" t="s">
-        <v>431</v>
+      <c r="C40" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D40" s="123"/>
-      <c r="E40" s="194" t="s">
-        <v>431</v>
+      <c r="E40" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F40" s="123"/>
-      <c r="G40" s="195" t="s">
-        <v>376</v>
+      <c r="G40" s="124" t="s">
+        <v>366</v>
       </c>
       <c r="H40" s="123" t="s">
         <v>294</v>
@@ -11624,16 +11544,16 @@
       <c r="B41" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="194" t="s">
-        <v>431</v>
+      <c r="C41" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D41" s="123"/>
-      <c r="E41" s="194" t="s">
-        <v>431</v>
+      <c r="E41" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F41" s="123"/>
-      <c r="G41" s="194" t="s">
-        <v>431</v>
+      <c r="G41" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H41" s="123"/>
       <c r="I41" s="123" t="s">
@@ -11650,16 +11570,16 @@
       <c r="B42" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C42" s="194" t="s">
-        <v>431</v>
+      <c r="C42" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D42" s="123"/>
-      <c r="E42" s="194" t="s">
-        <v>431</v>
+      <c r="E42" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F42" s="123"/>
-      <c r="G42" s="195" t="s">
-        <v>377</v>
+      <c r="G42" s="124" t="s">
+        <v>367</v>
       </c>
       <c r="H42" s="123" t="s">
         <v>272</v>
@@ -11678,16 +11598,16 @@
       <c r="B43" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C43" s="194" t="s">
-        <v>431</v>
+      <c r="C43" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D43" s="123"/>
-      <c r="E43" s="194" t="s">
-        <v>431</v>
+      <c r="E43" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F43" s="123"/>
-      <c r="G43" s="195" t="s">
-        <v>697</v>
+      <c r="G43" s="124" t="s">
+        <v>685</v>
       </c>
       <c r="H43" s="160" t="s">
         <v>294</v>
@@ -11706,16 +11626,16 @@
       <c r="B44" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C44" s="194" t="s">
-        <v>431</v>
+      <c r="C44" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D44" s="123"/>
-      <c r="E44" s="194" t="s">
-        <v>431</v>
+      <c r="E44" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F44" s="123"/>
-      <c r="G44" s="194" t="s">
-        <v>431</v>
+      <c r="G44" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H44" s="123"/>
       <c r="I44" s="123" t="s">
@@ -11732,20 +11652,20 @@
       <c r="B45" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C45" s="195" t="s">
-        <v>388</v>
+      <c r="C45" s="124" t="s">
+        <v>378</v>
       </c>
       <c r="D45" s="123" t="s">
-        <v>358</v>
-      </c>
-      <c r="E45" s="195" t="s">
-        <v>537</v>
+        <v>350</v>
+      </c>
+      <c r="E45" s="124" t="s">
+        <v>526</v>
       </c>
       <c r="F45" s="123" t="s">
         <v>305</v>
       </c>
-      <c r="G45" s="195" t="s">
-        <v>378</v>
+      <c r="G45" s="124" t="s">
+        <v>368</v>
       </c>
       <c r="H45" s="123" t="s">
         <v>272</v>
@@ -11764,16 +11684,16 @@
       <c r="B46" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C46" s="194" t="s">
-        <v>431</v>
+      <c r="C46" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D46" s="123"/>
-      <c r="E46" s="194" t="s">
-        <v>431</v>
+      <c r="E46" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F46" s="123"/>
-      <c r="G46" s="195" t="s">
-        <v>379</v>
+      <c r="G46" s="124" t="s">
+        <v>369</v>
       </c>
       <c r="H46" s="123" t="s">
         <v>294</v>
@@ -11792,18 +11712,18 @@
       <c r="B47" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C47" s="194" t="s">
-        <v>431</v>
+      <c r="C47" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D47" s="123"/>
-      <c r="E47" s="195" t="s">
-        <v>536</v>
+      <c r="E47" s="124" t="s">
+        <v>525</v>
       </c>
       <c r="F47" s="123" t="s">
         <v>295</v>
       </c>
-      <c r="G47" s="194" t="s">
-        <v>431</v>
+      <c r="G47" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="H47" s="123"/>
       <c r="I47" s="123" t="s">
@@ -11820,16 +11740,16 @@
       <c r="B48" s="123" t="s">
         <v>328</v>
       </c>
-      <c r="C48" s="194" t="s">
-        <v>431</v>
+      <c r="C48" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="D48" s="123"/>
-      <c r="E48" s="194" t="s">
-        <v>431</v>
+      <c r="E48" s="123" t="s">
+        <v>421</v>
       </c>
       <c r="F48" s="123"/>
-      <c r="G48" s="195" t="s">
-        <v>380</v>
+      <c r="G48" s="124" t="s">
+        <v>370</v>
       </c>
       <c r="H48" s="123" t="s">
         <v>272</v>
@@ -11848,16 +11768,16 @@
       <c r="B49" s="125" t="s">
         <v>328</v>
       </c>
-      <c r="C49" s="196" t="s">
-        <v>431</v>
+      <c r="C49" s="125" t="s">
+        <v>421</v>
       </c>
       <c r="D49" s="125"/>
-      <c r="E49" s="196" t="s">
-        <v>431</v>
+      <c r="E49" s="125" t="s">
+        <v>421</v>
       </c>
       <c r="F49" s="125"/>
-      <c r="G49" s="196" t="s">
-        <v>431</v>
+      <c r="G49" s="125" t="s">
+        <v>421</v>
       </c>
       <c r="H49" s="125"/>
       <c r="I49" s="125" t="s">
@@ -11874,16 +11794,16 @@
       <c r="B50" s="126" t="s">
         <v>329</v>
       </c>
-      <c r="C50" s="197" t="s">
-        <v>431</v>
+      <c r="C50" s="126" t="s">
+        <v>421</v>
       </c>
       <c r="D50" s="126"/>
-      <c r="E50" s="197" t="s">
-        <v>431</v>
+      <c r="E50" s="126" t="s">
+        <v>421</v>
       </c>
       <c r="F50" s="126"/>
-      <c r="G50" s="197" t="s">
-        <v>431</v>
+      <c r="G50" s="126" t="s">
+        <v>421</v>
       </c>
       <c r="H50" s="126"/>
       <c r="I50" s="126" t="s">
@@ -11900,18 +11820,18 @@
       <c r="B51" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C51" s="198" t="s">
-        <v>431</v>
+      <c r="C51" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D51" s="127"/>
-      <c r="E51" s="199" t="s">
-        <v>538</v>
+      <c r="E51" s="128" t="s">
+        <v>527</v>
       </c>
       <c r="F51" s="127" t="s">
         <v>295</v>
       </c>
-      <c r="G51" s="198" t="s">
-        <v>431</v>
+      <c r="G51" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H51" s="127"/>
       <c r="I51" s="127" t="s">
@@ -11928,16 +11848,16 @@
       <c r="B52" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C52" s="198" t="s">
-        <v>431</v>
+      <c r="C52" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D52" s="127"/>
-      <c r="E52" s="198" t="s">
-        <v>431</v>
+      <c r="E52" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F52" s="127"/>
-      <c r="G52" s="198" t="s">
-        <v>431</v>
+      <c r="G52" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H52" s="127"/>
       <c r="I52" s="127" t="s">
@@ -11954,16 +11874,16 @@
       <c r="B53" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C53" s="198" t="s">
-        <v>431</v>
+      <c r="C53" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D53" s="127"/>
-      <c r="E53" s="198" t="s">
-        <v>431</v>
+      <c r="E53" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F53" s="127"/>
-      <c r="G53" s="198" t="s">
-        <v>431</v>
+      <c r="G53" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H53" s="127"/>
       <c r="I53" s="127" t="s">
@@ -11980,16 +11900,16 @@
       <c r="B54" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C54" s="198" t="s">
-        <v>431</v>
+      <c r="C54" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D54" s="127"/>
-      <c r="E54" s="198" t="s">
-        <v>431</v>
+      <c r="E54" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F54" s="127"/>
-      <c r="G54" s="199" t="s">
-        <v>381</v>
+      <c r="G54" s="128" t="s">
+        <v>371</v>
       </c>
       <c r="H54" s="127" t="s">
         <v>272</v>
@@ -12008,16 +11928,16 @@
       <c r="B55" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C55" s="198" t="s">
-        <v>431</v>
+      <c r="C55" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D55" s="127"/>
-      <c r="E55" s="198" t="s">
-        <v>431</v>
+      <c r="E55" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F55" s="127"/>
-      <c r="G55" s="199" t="s">
-        <v>698</v>
+      <c r="G55" s="128" t="s">
+        <v>686</v>
       </c>
       <c r="H55" s="127" t="s">
         <v>176</v>
@@ -12036,18 +11956,18 @@
       <c r="B56" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C56" s="199" t="s">
-        <v>441</v>
+      <c r="C56" s="128" t="s">
+        <v>431</v>
       </c>
       <c r="D56" s="127" t="s">
-        <v>680</v>
-      </c>
-      <c r="E56" s="198" t="s">
-        <v>431</v>
+        <v>669</v>
+      </c>
+      <c r="E56" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F56" s="127"/>
-      <c r="G56" s="198" t="s">
-        <v>431</v>
+      <c r="G56" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H56" s="127"/>
       <c r="I56" s="127" t="s">
@@ -12064,20 +11984,20 @@
       <c r="B57" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C57" s="199" t="s">
-        <v>442</v>
+      <c r="C57" s="128" t="s">
+        <v>432</v>
       </c>
       <c r="D57" s="127" t="s">
-        <v>680</v>
-      </c>
-      <c r="E57" s="199" t="s">
-        <v>539</v>
+        <v>669</v>
+      </c>
+      <c r="E57" s="128" t="s">
+        <v>528</v>
       </c>
       <c r="F57" s="127" t="s">
         <v>305</v>
       </c>
-      <c r="G57" s="199" t="s">
-        <v>382</v>
+      <c r="G57" s="128" t="s">
+        <v>372</v>
       </c>
       <c r="H57" s="127" t="s">
         <v>272</v>
@@ -12096,18 +12016,18 @@
       <c r="B58" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C58" s="199" t="s">
+      <c r="C58" s="128" t="s">
         <v>337</v>
       </c>
       <c r="D58" s="127" t="s">
-        <v>596</v>
-      </c>
-      <c r="E58" s="198" t="s">
-        <v>431</v>
+        <v>585</v>
+      </c>
+      <c r="E58" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F58" s="127"/>
-      <c r="G58" s="199" t="s">
-        <v>383</v>
+      <c r="G58" s="128" t="s">
+        <v>373</v>
       </c>
       <c r="H58" s="127" t="s">
         <v>294</v>
@@ -12126,18 +12046,18 @@
       <c r="B59" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C59" s="199" t="s">
+      <c r="C59" s="128" t="s">
         <v>338</v>
       </c>
       <c r="D59" s="127" t="s">
-        <v>596</v>
-      </c>
-      <c r="E59" s="198" t="s">
-        <v>431</v>
+        <v>585</v>
+      </c>
+      <c r="E59" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F59" s="127"/>
-      <c r="G59" s="199" t="s">
-        <v>384</v>
+      <c r="G59" s="128" t="s">
+        <v>374</v>
       </c>
       <c r="H59" s="127" t="s">
         <v>176</v>
@@ -12156,20 +12076,20 @@
       <c r="B60" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C60" s="199" t="s">
+      <c r="C60" s="128" t="s">
         <v>87</v>
       </c>
       <c r="D60" s="127" t="s">
-        <v>596</v>
-      </c>
-      <c r="E60" s="199" t="s">
-        <v>540</v>
+        <v>585</v>
+      </c>
+      <c r="E60" s="128" t="s">
+        <v>529</v>
       </c>
       <c r="F60" s="127" t="s">
         <v>305</v>
       </c>
-      <c r="G60" s="198" t="s">
-        <v>431</v>
+      <c r="G60" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H60" s="127"/>
       <c r="I60" s="127" t="s">
@@ -12186,16 +12106,16 @@
       <c r="B61" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="198" t="s">
-        <v>431</v>
+      <c r="C61" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D61" s="127"/>
-      <c r="E61" s="198" t="s">
-        <v>431</v>
+      <c r="E61" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="F61" s="127"/>
-      <c r="G61" s="199" t="s">
-        <v>438</v>
+      <c r="G61" s="128" t="s">
+        <v>428</v>
       </c>
       <c r="H61" s="127" t="s">
         <v>178</v>
@@ -12214,18 +12134,18 @@
       <c r="B62" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C62" s="198" t="s">
-        <v>431</v>
+      <c r="C62" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D62" s="127"/>
-      <c r="E62" s="199" t="s">
-        <v>451</v>
+      <c r="E62" s="128" t="s">
+        <v>441</v>
       </c>
       <c r="F62" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="G62" s="199" t="s">
-        <v>439</v>
+      <c r="G62" s="128" t="s">
+        <v>429</v>
       </c>
       <c r="H62" s="127" t="s">
         <v>178</v>
@@ -12244,18 +12164,18 @@
       <c r="B63" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C63" s="198" t="s">
-        <v>431</v>
+      <c r="C63" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D63" s="127"/>
-      <c r="E63" s="199" t="s">
-        <v>452</v>
+      <c r="E63" s="128" t="s">
+        <v>442</v>
       </c>
       <c r="F63" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="G63" s="198" t="s">
-        <v>431</v>
+      <c r="G63" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H63" s="127"/>
       <c r="I63" s="127" t="s">
@@ -12272,16 +12192,16 @@
       <c r="B64" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C64" s="199" t="s">
-        <v>443</v>
+      <c r="C64" s="128" t="s">
+        <v>433</v>
       </c>
       <c r="D64" s="127" t="s">
         <v>342</v>
       </c>
-      <c r="E64" s="198"/>
+      <c r="E64" s="127"/>
       <c r="F64" s="127"/>
-      <c r="G64" s="199" t="s">
-        <v>440</v>
+      <c r="G64" s="128" t="s">
+        <v>430</v>
       </c>
       <c r="H64" s="127" t="s">
         <v>294</v>
@@ -12300,18 +12220,18 @@
       <c r="B65" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C65" s="198" t="s">
-        <v>431</v>
+      <c r="C65" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D65" s="127"/>
-      <c r="E65" s="199" t="s">
-        <v>453</v>
+      <c r="E65" s="128" t="s">
+        <v>443</v>
       </c>
       <c r="F65" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="G65" s="198" t="s">
-        <v>431</v>
+      <c r="G65" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="H65" s="127"/>
       <c r="I65" s="127" t="s">
@@ -12328,18 +12248,18 @@
       <c r="B66" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C66" s="198" t="s">
-        <v>431</v>
+      <c r="C66" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D66" s="127"/>
-      <c r="E66" s="199" t="s">
-        <v>454</v>
+      <c r="E66" s="128" t="s">
+        <v>444</v>
       </c>
       <c r="F66" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="G66" s="199" t="s">
-        <v>464</v>
+      <c r="G66" s="128" t="s">
+        <v>454</v>
       </c>
       <c r="H66" s="127" t="s">
         <v>272</v>
@@ -12358,16 +12278,16 @@
       <c r="B67" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C67" s="199" t="s">
+      <c r="C67" s="128" t="s">
         <v>307</v>
       </c>
       <c r="D67" s="127" t="s">
         <v>339</v>
       </c>
-      <c r="E67" s="198"/>
+      <c r="E67" s="127"/>
       <c r="F67" s="127"/>
-      <c r="G67" s="199" t="s">
-        <v>465</v>
+      <c r="G67" s="128" t="s">
+        <v>455</v>
       </c>
       <c r="H67" s="127" t="s">
         <v>178</v>
@@ -12386,17 +12306,17 @@
       <c r="B68" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C68" s="198" t="s">
-        <v>431</v>
+      <c r="C68" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D68" s="127"/>
-      <c r="E68" s="199" t="s">
-        <v>455</v>
+      <c r="E68" s="128" t="s">
+        <v>445</v>
       </c>
       <c r="F68" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="G68" s="198"/>
+      <c r="G68" s="127"/>
       <c r="H68" s="127"/>
       <c r="I68" s="127" t="s">
         <v>6</v>
@@ -12412,17 +12332,17 @@
       <c r="B69" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C69" s="198" t="s">
-        <v>431</v>
+      <c r="C69" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D69" s="127"/>
-      <c r="E69" s="199" t="s">
-        <v>456</v>
+      <c r="E69" s="128" t="s">
+        <v>446</v>
       </c>
       <c r="F69" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="G69" s="199" t="s">
+      <c r="G69" s="128" t="s">
         <v>304</v>
       </c>
       <c r="H69" s="127" t="s">
@@ -12442,14 +12362,14 @@
       <c r="B70" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C70" s="198" t="s">
-        <v>431</v>
+      <c r="C70" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D70" s="127"/>
-      <c r="E70" s="198"/>
+      <c r="E70" s="127"/>
       <c r="F70" s="127"/>
-      <c r="G70" s="199" t="s">
-        <v>466</v>
+      <c r="G70" s="128" t="s">
+        <v>456</v>
       </c>
       <c r="H70" s="127" t="s">
         <v>175</v>
@@ -12468,19 +12388,19 @@
       <c r="B71" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C71" s="199" t="s">
-        <v>444</v>
+      <c r="C71" s="128" t="s">
+        <v>434</v>
       </c>
       <c r="D71" s="127" t="s">
         <v>340</v>
       </c>
-      <c r="E71" s="199" t="s">
-        <v>463</v>
+      <c r="E71" s="128" t="s">
+        <v>453</v>
       </c>
       <c r="F71" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="G71" s="198"/>
+      <c r="G71" s="127"/>
       <c r="H71" s="127"/>
       <c r="I71" s="127" t="s">
         <v>3</v>
@@ -12496,18 +12416,18 @@
       <c r="B72" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="C72" s="198" t="s">
-        <v>431</v>
+      <c r="C72" s="127" t="s">
+        <v>421</v>
       </c>
       <c r="D72" s="127"/>
-      <c r="E72" s="199" t="s">
-        <v>457</v>
+      <c r="E72" s="128" t="s">
+        <v>447</v>
       </c>
       <c r="F72" s="127" t="s">
         <v>173</v>
       </c>
-      <c r="G72" s="199" t="s">
-        <v>467</v>
+      <c r="G72" s="128" t="s">
+        <v>457</v>
       </c>
       <c r="H72" s="127" t="s">
         <v>176</v>
@@ -12526,16 +12446,16 @@
       <c r="B73" s="129" t="s">
         <v>329</v>
       </c>
-      <c r="C73" s="200" t="s">
+      <c r="C73" s="149" t="s">
         <v>83</v>
       </c>
       <c r="D73" s="129" t="s">
         <v>341</v>
       </c>
-      <c r="E73" s="218"/>
+      <c r="E73" s="129"/>
       <c r="F73" s="129"/>
-      <c r="G73" s="200" t="s">
-        <v>468</v>
+      <c r="G73" s="149" t="s">
+        <v>458</v>
       </c>
       <c r="H73" s="129" t="s">
         <v>176</v>
@@ -12554,18 +12474,18 @@
       <c r="B74" s="130" t="s">
         <v>330</v>
       </c>
-      <c r="C74" s="201" t="s">
-        <v>431</v>
+      <c r="C74" s="130" t="s">
+        <v>421</v>
       </c>
       <c r="D74" s="130"/>
-      <c r="E74" s="219" t="s">
+      <c r="E74" s="150" t="s">
         <v>231</v>
       </c>
       <c r="F74" s="130" t="s">
         <v>173</v>
       </c>
-      <c r="G74" s="219" t="s">
-        <v>469</v>
+      <c r="G74" s="150" t="s">
+        <v>459</v>
       </c>
       <c r="H74" s="130" t="s">
         <v>294</v>
@@ -12584,17 +12504,17 @@
       <c r="B75" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C75" s="202" t="s">
-        <v>431</v>
+      <c r="C75" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D75" s="131"/>
-      <c r="E75" s="203" t="s">
-        <v>458</v>
+      <c r="E75" s="132" t="s">
+        <v>448</v>
       </c>
       <c r="F75" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G75" s="202"/>
+      <c r="G75" s="131"/>
       <c r="H75" s="131"/>
       <c r="I75" s="131" t="s">
         <v>23</v>
@@ -12610,16 +12530,16 @@
       <c r="B76" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C76" s="203" t="s">
-        <v>389</v>
+      <c r="C76" s="132" t="s">
+        <v>379</v>
       </c>
       <c r="D76" s="131" t="s">
         <v>340</v>
       </c>
-      <c r="E76" s="202"/>
+      <c r="E76" s="131"/>
       <c r="F76" s="131"/>
-      <c r="G76" s="203" t="s">
-        <v>430</v>
+      <c r="G76" s="132" t="s">
+        <v>420</v>
       </c>
       <c r="H76" s="131" t="s">
         <v>175</v>
@@ -12638,18 +12558,18 @@
       <c r="B77" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C77" s="202" t="s">
-        <v>431</v>
+      <c r="C77" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D77" s="131"/>
-      <c r="E77" s="203" t="s">
-        <v>459</v>
+      <c r="E77" s="132" t="s">
+        <v>449</v>
       </c>
       <c r="F77" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G77" s="203" t="s">
-        <v>470</v>
+      <c r="G77" s="132" t="s">
+        <v>460</v>
       </c>
       <c r="H77" s="131" t="s">
         <v>178</v>
@@ -12668,19 +12588,19 @@
       <c r="B78" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C78" s="203" t="s">
-        <v>390</v>
+      <c r="C78" s="132" t="s">
+        <v>380</v>
       </c>
       <c r="D78" s="131" t="s">
-        <v>344</v>
-      </c>
-      <c r="E78" s="203" t="s">
-        <v>460</v>
+        <v>699</v>
+      </c>
+      <c r="E78" s="132" t="s">
+        <v>450</v>
       </c>
       <c r="F78" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G78" s="202"/>
+      <c r="G78" s="131"/>
       <c r="H78" s="131"/>
       <c r="I78" s="131" t="s">
         <v>20</v>
@@ -12696,14 +12616,14 @@
       <c r="B79" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C79" s="202" t="s">
-        <v>431</v>
+      <c r="C79" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D79" s="131"/>
-      <c r="E79" s="202"/>
+      <c r="E79" s="131"/>
       <c r="F79" s="131"/>
-      <c r="G79" s="203" t="s">
-        <v>471</v>
+      <c r="G79" s="132" t="s">
+        <v>461</v>
       </c>
       <c r="H79" s="131" t="s">
         <v>272</v>
@@ -12722,19 +12642,19 @@
       <c r="B80" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C80" s="202"/>
+      <c r="C80" s="131"/>
       <c r="D80" s="131"/>
-      <c r="E80" s="203" t="s">
-        <v>461</v>
+      <c r="E80" s="132" t="s">
+        <v>451</v>
       </c>
       <c r="F80" s="186" t="s">
         <v>295</v>
       </c>
-      <c r="G80" s="203" t="s">
-        <v>674</v>
+      <c r="G80" s="132" t="s">
+        <v>663</v>
       </c>
       <c r="H80" s="131" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="I80" s="131" t="s">
         <v>18</v>
@@ -12743,13 +12663,13 @@
         <v>27</v>
       </c>
       <c r="L80" s="132" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="M80" s="131" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N80" s="132" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="O80" s="131" t="s">
         <v>336</v>
@@ -12768,15 +12688,15 @@
       <c r="B81" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C81" s="202"/>
+      <c r="C81" s="131"/>
       <c r="D81" s="131"/>
-      <c r="E81" s="203" t="s">
-        <v>462</v>
+      <c r="E81" s="132" t="s">
+        <v>452</v>
       </c>
       <c r="F81" s="186" t="s">
         <v>305</v>
       </c>
-      <c r="G81" s="203"/>
+      <c r="G81" s="132"/>
       <c r="H81" s="131"/>
       <c r="I81" s="131" t="s">
         <v>17</v>
@@ -12785,19 +12705,19 @@
         <v>27</v>
       </c>
       <c r="L81" s="132" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="M81" s="131" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N81" s="132" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="O81" s="131" t="s">
         <v>336</v>
       </c>
       <c r="P81" s="132" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="Q81" s="131" t="s">
         <v>336</v>
@@ -12810,16 +12730,16 @@
       <c r="B82" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C82" s="202" t="s">
-        <v>391</v>
+      <c r="C82" s="131" t="s">
+        <v>381</v>
       </c>
       <c r="D82" s="131" t="s">
-        <v>345</v>
-      </c>
-      <c r="E82" s="202"/>
+        <v>694</v>
+      </c>
+      <c r="E82" s="131"/>
       <c r="F82" s="131"/>
-      <c r="G82" s="203" t="s">
-        <v>472</v>
+      <c r="G82" s="132" t="s">
+        <v>462</v>
       </c>
       <c r="H82" s="131" t="s">
         <v>176</v>
@@ -12838,18 +12758,18 @@
       <c r="B83" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C83" s="202" t="s">
-        <v>431</v>
+      <c r="C83" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D83" s="131"/>
-      <c r="E83" s="203" t="s">
-        <v>699</v>
+      <c r="E83" s="132" t="s">
+        <v>687</v>
       </c>
       <c r="F83" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G83" s="203" t="s">
-        <v>473</v>
+      <c r="G83" s="132" t="s">
+        <v>463</v>
       </c>
       <c r="H83" s="131" t="s">
         <v>176</v>
@@ -12868,17 +12788,17 @@
       <c r="B84" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C84" s="202" t="s">
-        <v>431</v>
+      <c r="C84" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D84" s="131"/>
-      <c r="E84" s="203" t="s">
-        <v>487</v>
+      <c r="E84" s="132" t="s">
+        <v>477</v>
       </c>
       <c r="F84" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G84" s="202"/>
+      <c r="G84" s="131"/>
       <c r="H84" s="131"/>
       <c r="I84" s="131" t="s">
         <v>14</v>
@@ -12894,16 +12814,16 @@
       <c r="B85" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C85" s="203" t="s">
-        <v>392</v>
+      <c r="C85" s="132" t="s">
+        <v>382</v>
       </c>
       <c r="D85" s="131" t="s">
-        <v>685</v>
-      </c>
-      <c r="E85" s="202"/>
+        <v>700</v>
+      </c>
+      <c r="E85" s="131"/>
       <c r="F85" s="131"/>
-      <c r="G85" s="203" t="s">
-        <v>438</v>
+      <c r="G85" s="132" t="s">
+        <v>428</v>
       </c>
       <c r="H85" s="131" t="s">
         <v>177</v>
@@ -12922,18 +12842,18 @@
       <c r="B86" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C86" s="202" t="s">
-        <v>431</v>
+      <c r="C86" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D86" s="131"/>
-      <c r="E86" s="203" t="s">
-        <v>488</v>
+      <c r="E86" s="132" t="s">
+        <v>478</v>
       </c>
       <c r="F86" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G86" s="203" t="s">
-        <v>474</v>
+      <c r="G86" s="132" t="s">
+        <v>464</v>
       </c>
       <c r="H86" s="131" t="s">
         <v>175</v>
@@ -12952,17 +12872,17 @@
       <c r="B87" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C87" s="202" t="s">
-        <v>431</v>
+      <c r="C87" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D87" s="131"/>
-      <c r="E87" s="203" t="s">
-        <v>489</v>
+      <c r="E87" s="132" t="s">
+        <v>479</v>
       </c>
       <c r="F87" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G87" s="202"/>
+      <c r="G87" s="131"/>
       <c r="H87" s="131"/>
       <c r="I87" s="131" t="s">
         <v>11</v>
@@ -12978,18 +12898,18 @@
       <c r="B88" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C88" s="202" t="s">
-        <v>431</v>
+      <c r="C88" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D88" s="131"/>
-      <c r="E88" s="203" t="s">
-        <v>490</v>
+      <c r="E88" s="132" t="s">
+        <v>480</v>
       </c>
       <c r="F88" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G88" s="203" t="s">
-        <v>475</v>
+      <c r="G88" s="132" t="s">
+        <v>465</v>
       </c>
       <c r="H88" s="131" t="s">
         <v>178</v>
@@ -13008,15 +12928,15 @@
       <c r="B89" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C89" s="203" t="s">
-        <v>393</v>
+      <c r="C89" s="132" t="s">
+        <v>383</v>
       </c>
       <c r="D89" s="131" t="s">
-        <v>686</v>
-      </c>
-      <c r="E89" s="202"/>
+        <v>674</v>
+      </c>
+      <c r="E89" s="131"/>
       <c r="F89" s="131"/>
-      <c r="G89" s="203" t="s">
+      <c r="G89" s="132" t="s">
         <v>324</v>
       </c>
       <c r="H89" s="131" t="s">
@@ -13036,17 +12956,17 @@
       <c r="B90" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C90" s="202" t="s">
-        <v>431</v>
+      <c r="C90" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D90" s="131"/>
-      <c r="E90" s="203" t="s">
-        <v>491</v>
+      <c r="E90" s="132" t="s">
+        <v>481</v>
       </c>
       <c r="F90" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G90" s="202"/>
+      <c r="G90" s="131"/>
       <c r="H90" s="131"/>
       <c r="I90" s="131" t="s">
         <v>8</v>
@@ -13062,18 +12982,18 @@
       <c r="B91" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C91" s="202" t="s">
-        <v>431</v>
+      <c r="C91" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D91" s="131"/>
-      <c r="E91" s="203" t="s">
-        <v>492</v>
+      <c r="E91" s="132" t="s">
+        <v>482</v>
       </c>
       <c r="F91" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G91" s="203" t="s">
-        <v>476</v>
+      <c r="G91" s="132" t="s">
+        <v>466</v>
       </c>
       <c r="H91" s="131" t="s">
         <v>178</v>
@@ -13092,14 +13012,14 @@
       <c r="B92" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C92" s="202" t="s">
-        <v>431</v>
+      <c r="C92" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D92" s="131"/>
-      <c r="E92" s="202"/>
+      <c r="E92" s="131"/>
       <c r="F92" s="131"/>
-      <c r="G92" s="203" t="s">
-        <v>477</v>
+      <c r="G92" s="132" t="s">
+        <v>467</v>
       </c>
       <c r="H92" s="131" t="s">
         <v>178</v>
@@ -13118,17 +13038,17 @@
       <c r="B93" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C93" s="202" t="s">
-        <v>431</v>
+      <c r="C93" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D93" s="131"/>
-      <c r="E93" s="203" t="s">
-        <v>493</v>
+      <c r="E93" s="132" t="s">
+        <v>483</v>
       </c>
       <c r="F93" s="131" t="s">
         <v>174</v>
       </c>
-      <c r="G93" s="202"/>
+      <c r="G93" s="131"/>
       <c r="H93" s="131"/>
       <c r="I93" s="131" t="s">
         <v>5</v>
@@ -13144,20 +13064,20 @@
       <c r="B94" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C94" s="203" t="s">
-        <v>394</v>
+      <c r="C94" s="132" t="s">
+        <v>384</v>
       </c>
       <c r="D94" s="131" t="s">
         <v>165</v>
       </c>
-      <c r="E94" s="203" t="s">
-        <v>494</v>
+      <c r="E94" s="132" t="s">
+        <v>484</v>
       </c>
       <c r="F94" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G94" s="203" t="s">
-        <v>478</v>
+      <c r="G94" s="132" t="s">
+        <v>468</v>
       </c>
       <c r="H94" s="131" t="s">
         <v>178</v>
@@ -13176,14 +13096,14 @@
       <c r="B95" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C95" s="202" t="s">
-        <v>431</v>
+      <c r="C95" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D95" s="131"/>
-      <c r="E95" s="202"/>
+      <c r="E95" s="131"/>
       <c r="F95" s="131"/>
-      <c r="G95" s="203" t="s">
-        <v>479</v>
+      <c r="G95" s="132" t="s">
+        <v>469</v>
       </c>
       <c r="H95" s="131" t="s">
         <v>177</v>
@@ -13202,17 +13122,17 @@
       <c r="B96" s="131" t="s">
         <v>330</v>
       </c>
-      <c r="C96" s="202" t="s">
-        <v>431</v>
+      <c r="C96" s="131" t="s">
+        <v>421</v>
       </c>
       <c r="D96" s="131"/>
-      <c r="E96" s="203" t="s">
-        <v>495</v>
+      <c r="E96" s="132" t="s">
+        <v>485</v>
       </c>
       <c r="F96" s="131" t="s">
         <v>173</v>
       </c>
-      <c r="G96" s="202"/>
+      <c r="G96" s="131"/>
       <c r="H96" s="131"/>
       <c r="I96" s="131" t="s">
         <v>2</v>
@@ -13228,18 +13148,18 @@
       <c r="B97" s="133" t="s">
         <v>330</v>
       </c>
-      <c r="C97" s="204" t="s">
-        <v>431</v>
+      <c r="C97" s="133" t="s">
+        <v>421</v>
       </c>
       <c r="D97" s="133"/>
-      <c r="E97" s="220" t="s">
+      <c r="E97" s="151" t="s">
         <v>83</v>
       </c>
       <c r="F97" s="133" t="s">
         <v>174</v>
       </c>
-      <c r="G97" s="220" t="s">
-        <v>480</v>
+      <c r="G97" s="151" t="s">
+        <v>470</v>
       </c>
       <c r="H97" s="133" t="s">
         <v>178</v>
@@ -13258,19 +13178,19 @@
       <c r="B98" s="135" t="s">
         <v>331</v>
       </c>
-      <c r="C98" s="205" t="s">
+      <c r="C98" s="134" t="s">
         <v>45</v>
       </c>
       <c r="D98" s="135" t="s">
-        <v>346</v>
-      </c>
-      <c r="E98" s="205" t="s">
-        <v>469</v>
+        <v>701</v>
+      </c>
+      <c r="E98" s="134" t="s">
+        <v>459</v>
       </c>
       <c r="F98" s="135" t="s">
         <v>173</v>
       </c>
-      <c r="G98" s="205" t="s">
+      <c r="G98" s="134" t="s">
         <v>231</v>
       </c>
       <c r="H98" s="135" t="s">
@@ -13290,14 +13210,14 @@
       <c r="B99" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C99" s="206" t="s">
-        <v>431</v>
+      <c r="C99" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D99" s="136"/>
-      <c r="E99" s="206"/>
+      <c r="E99" s="136"/>
       <c r="F99" s="136"/>
-      <c r="G99" s="207" t="s">
-        <v>481</v>
+      <c r="G99" s="137" t="s">
+        <v>471</v>
       </c>
       <c r="H99" s="136" t="s">
         <v>177</v>
@@ -13316,19 +13236,19 @@
       <c r="B100" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C100" s="207" t="s">
-        <v>395</v>
+      <c r="C100" s="137" t="s">
+        <v>385</v>
       </c>
       <c r="D100" s="136" t="s">
-        <v>347</v>
-      </c>
-      <c r="E100" s="207" t="s">
-        <v>496</v>
+        <v>343</v>
+      </c>
+      <c r="E100" s="137" t="s">
+        <v>486</v>
       </c>
       <c r="F100" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G100" s="206"/>
+      <c r="G100" s="136"/>
       <c r="H100" s="136"/>
       <c r="I100" s="136" t="s">
         <v>22</v>
@@ -13344,17 +13264,17 @@
       <c r="B101" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C101" s="206" t="s">
-        <v>431</v>
+      <c r="C101" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D101" s="136"/>
-      <c r="E101" s="207" t="s">
-        <v>497</v>
+      <c r="E101" s="137" t="s">
+        <v>487</v>
       </c>
       <c r="F101" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="G101" s="207" t="s">
+      <c r="G101" s="137" t="s">
         <v>233</v>
       </c>
       <c r="H101" s="136" t="s">
@@ -13374,14 +13294,14 @@
       <c r="B102" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C102" s="206" t="s">
-        <v>431</v>
+      <c r="C102" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D102" s="136"/>
-      <c r="E102" s="206"/>
+      <c r="E102" s="136"/>
       <c r="F102" s="136"/>
-      <c r="G102" s="207" t="s">
-        <v>482</v>
+      <c r="G102" s="137" t="s">
+        <v>472</v>
       </c>
       <c r="H102" s="136" t="s">
         <v>177</v>
@@ -13400,19 +13320,19 @@
       <c r="B103" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C103" s="207" t="s">
-        <v>396</v>
+      <c r="C103" s="137" t="s">
+        <v>386</v>
       </c>
       <c r="D103" s="136" t="s">
-        <v>348</v>
-      </c>
-      <c r="E103" s="207" t="s">
-        <v>498</v>
+        <v>344</v>
+      </c>
+      <c r="E103" s="137" t="s">
+        <v>488</v>
       </c>
       <c r="F103" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G103" s="206"/>
+      <c r="G103" s="136"/>
       <c r="H103" s="136"/>
       <c r="I103" s="136" t="s">
         <v>19</v>
@@ -13428,14 +13348,14 @@
       <c r="B104" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C104" s="206" t="s">
-        <v>431</v>
+      <c r="C104" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D104" s="136"/>
-      <c r="E104" s="206"/>
+      <c r="E104" s="136"/>
       <c r="F104" s="136"/>
-      <c r="G104" s="207" t="s">
-        <v>483</v>
+      <c r="G104" s="137" t="s">
+        <v>473</v>
       </c>
       <c r="H104" s="136" t="s">
         <v>175</v>
@@ -13454,18 +13374,18 @@
       <c r="B105" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C105" s="206" t="s">
-        <v>431</v>
+      <c r="C105" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D105" s="136"/>
-      <c r="E105" s="207" t="s">
-        <v>442</v>
+      <c r="E105" s="137" t="s">
+        <v>432</v>
       </c>
       <c r="F105" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G105" s="207" t="s">
-        <v>484</v>
+      <c r="G105" s="137" t="s">
+        <v>474</v>
       </c>
       <c r="H105" s="136" t="s">
         <v>177</v>
@@ -13484,18 +13404,18 @@
       <c r="B106" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C106" s="206" t="s">
-        <v>431</v>
+      <c r="C106" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D106" s="136"/>
-      <c r="E106" s="207" t="s">
-        <v>508</v>
+      <c r="E106" s="137" t="s">
+        <v>497</v>
       </c>
       <c r="F106" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="G106" s="207" t="s">
-        <v>485</v>
+      <c r="G106" s="137" t="s">
+        <v>475</v>
       </c>
       <c r="H106" s="136" t="s">
         <v>178</v>
@@ -13514,15 +13434,15 @@
       <c r="B107" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C107" s="207" t="s">
-        <v>397</v>
+      <c r="C107" s="137" t="s">
+        <v>387</v>
       </c>
       <c r="D107" s="136" t="s">
-        <v>360</v>
-      </c>
-      <c r="E107" s="206"/>
+        <v>352</v>
+      </c>
+      <c r="E107" s="136"/>
       <c r="F107" s="136"/>
-      <c r="G107" s="206"/>
+      <c r="G107" s="136"/>
       <c r="H107" s="136"/>
       <c r="I107" s="136" t="s">
         <v>15</v>
@@ -13538,17 +13458,17 @@
       <c r="B108" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C108" s="206" t="s">
-        <v>431</v>
+      <c r="C108" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D108" s="136"/>
-      <c r="E108" s="207" t="s">
-        <v>499</v>
+      <c r="E108" s="137" t="s">
+        <v>489</v>
       </c>
       <c r="F108" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G108" s="207" t="s">
+      <c r="G108" s="137" t="s">
         <v>318</v>
       </c>
       <c r="H108" s="136" t="s">
@@ -13568,20 +13488,20 @@
       <c r="B109" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C109" s="207" t="s">
+      <c r="C109" s="137" t="s">
         <v>54</v>
       </c>
       <c r="D109" s="136" t="s">
-        <v>687</v>
-      </c>
-      <c r="E109" s="207" t="s">
-        <v>500</v>
+        <v>675</v>
+      </c>
+      <c r="E109" s="137" t="s">
+        <v>490</v>
       </c>
       <c r="F109" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="G109" s="207" t="s">
-        <v>486</v>
+      <c r="G109" s="137" t="s">
+        <v>476</v>
       </c>
       <c r="H109" s="136" t="s">
         <v>178</v>
@@ -13600,14 +13520,14 @@
       <c r="B110" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C110" s="206" t="s">
-        <v>431</v>
+      <c r="C110" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D110" s="136"/>
-      <c r="E110" s="206"/>
+      <c r="E110" s="136"/>
       <c r="F110" s="136"/>
-      <c r="G110" s="206" t="s">
-        <v>431</v>
+      <c r="G110" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="H110" s="136"/>
       <c r="I110" s="136" t="s">
@@ -13624,18 +13544,18 @@
       <c r="B111" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C111" s="206" t="s">
-        <v>431</v>
+      <c r="C111" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D111" s="136"/>
-      <c r="E111" s="207" t="s">
-        <v>501</v>
+      <c r="E111" s="137" t="s">
+        <v>491</v>
       </c>
       <c r="F111" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="G111" s="207" t="s">
-        <v>445</v>
+      <c r="G111" s="137" t="s">
+        <v>435</v>
       </c>
       <c r="H111" s="136" t="s">
         <v>176</v>
@@ -13654,18 +13574,18 @@
       <c r="B112" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C112" s="206" t="s">
-        <v>431</v>
+      <c r="C112" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D112" s="136"/>
-      <c r="E112" s="207" t="s">
-        <v>502</v>
+      <c r="E112" s="137" t="s">
+        <v>492</v>
       </c>
       <c r="F112" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G112" s="207" t="s">
-        <v>446</v>
+      <c r="G112" s="137" t="s">
+        <v>436</v>
       </c>
       <c r="H112" s="136" t="s">
         <v>177</v>
@@ -13684,16 +13604,16 @@
       <c r="B113" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C113" s="207" t="s">
-        <v>398</v>
+      <c r="C113" s="137" t="s">
+        <v>388</v>
       </c>
       <c r="D113" s="136" t="s">
-        <v>181</v>
-      </c>
-      <c r="E113" s="206"/>
+        <v>695</v>
+      </c>
+      <c r="E113" s="136"/>
       <c r="F113" s="136"/>
-      <c r="G113" s="206" t="s">
-        <v>431</v>
+      <c r="G113" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="H113" s="136"/>
       <c r="I113" s="136" t="s">
@@ -13710,18 +13630,18 @@
       <c r="B114" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C114" s="206" t="s">
-        <v>431</v>
+      <c r="C114" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D114" s="136"/>
-      <c r="E114" s="207" t="s">
-        <v>503</v>
+      <c r="E114" s="137" t="s">
+        <v>493</v>
       </c>
       <c r="F114" s="136" t="s">
         <v>174</v>
       </c>
-      <c r="G114" s="207" t="s">
-        <v>447</v>
+      <c r="G114" s="137" t="s">
+        <v>437</v>
       </c>
       <c r="H114" s="136" t="s">
         <v>177</v>
@@ -13740,18 +13660,18 @@
       <c r="B115" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C115" s="206" t="s">
-        <v>431</v>
+      <c r="C115" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D115" s="136"/>
-      <c r="E115" s="207" t="s">
-        <v>504</v>
+      <c r="E115" s="137" t="s">
+        <v>494</v>
       </c>
       <c r="F115" s="136" t="s">
         <v>173</v>
       </c>
-      <c r="G115" s="207" t="s">
-        <v>448</v>
+      <c r="G115" s="137" t="s">
+        <v>438</v>
       </c>
       <c r="H115" s="136" t="s">
         <v>272</v>
@@ -13770,14 +13690,14 @@
       <c r="B116" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C116" s="206" t="s">
-        <v>431</v>
+      <c r="C116" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D116" s="136"/>
-      <c r="E116" s="206"/>
+      <c r="E116" s="136"/>
       <c r="F116" s="136"/>
-      <c r="G116" s="206" t="s">
-        <v>431</v>
+      <c r="G116" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="H116" s="136"/>
       <c r="I116" s="136" t="s">
@@ -13794,20 +13714,20 @@
       <c r="B117" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C117" s="207" t="s">
+      <c r="C117" s="137" t="s">
         <v>152</v>
       </c>
       <c r="D117" s="136" t="s">
-        <v>349</v>
-      </c>
-      <c r="E117" s="207" t="s">
+        <v>345</v>
+      </c>
+      <c r="E117" s="137" t="s">
         <v>304</v>
       </c>
       <c r="F117" s="136" t="s">
         <v>305</v>
       </c>
-      <c r="G117" s="207" t="s">
-        <v>449</v>
+      <c r="G117" s="137" t="s">
+        <v>439</v>
       </c>
       <c r="H117" s="136" t="s">
         <v>178</v>
@@ -13826,18 +13746,18 @@
       <c r="B118" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C118" s="206" t="s">
-        <v>431</v>
+      <c r="C118" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D118" s="136"/>
-      <c r="E118" s="207" t="s">
-        <v>505</v>
+      <c r="E118" s="137" t="s">
+        <v>495</v>
       </c>
       <c r="F118" s="136" t="s">
         <v>295</v>
       </c>
-      <c r="G118" s="207" t="s">
-        <v>450</v>
+      <c r="G118" s="137" t="s">
+        <v>440</v>
       </c>
       <c r="H118" s="136" t="s">
         <v>178</v>
@@ -13856,14 +13776,14 @@
       <c r="B119" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C119" s="206" t="s">
-        <v>431</v>
+      <c r="C119" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="D119" s="136"/>
-      <c r="E119" s="206"/>
+      <c r="E119" s="136"/>
       <c r="F119" s="136"/>
-      <c r="G119" s="206" t="s">
-        <v>431</v>
+      <c r="G119" s="136" t="s">
+        <v>421</v>
       </c>
       <c r="H119" s="136"/>
       <c r="I119" s="136" t="s">
@@ -13880,20 +13800,20 @@
       <c r="B120" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="C120" s="207" t="s">
-        <v>399</v>
+      <c r="C120" s="137" t="s">
+        <v>389</v>
       </c>
       <c r="D120" s="136" t="s">
-        <v>350</v>
-      </c>
-      <c r="E120" s="207" t="s">
-        <v>467</v>
+        <v>696</v>
+      </c>
+      <c r="E120" s="137" t="s">
+        <v>457</v>
       </c>
       <c r="F120" s="136" t="s">
         <v>305</v>
       </c>
-      <c r="G120" s="207" t="s">
-        <v>415</v>
+      <c r="G120" s="137" t="s">
+        <v>405</v>
       </c>
       <c r="H120" s="136" t="s">
         <v>176</v>
@@ -13912,17 +13832,17 @@
       <c r="B121" s="138" t="s">
         <v>331</v>
       </c>
-      <c r="C121" s="208" t="s">
-        <v>431</v>
+      <c r="C121" s="138" t="s">
+        <v>421</v>
       </c>
       <c r="D121" s="138"/>
-      <c r="E121" s="221" t="s">
-        <v>507</v>
+      <c r="E121" s="139" t="s">
+        <v>496</v>
       </c>
       <c r="F121" s="138" t="s">
         <v>295</v>
       </c>
-      <c r="G121" s="221" t="s">
+      <c r="G121" s="139" t="s">
         <v>64</v>
       </c>
       <c r="H121" s="138" t="s">
@@ -13942,18 +13862,18 @@
       <c r="B122" s="140" t="s">
         <v>332</v>
       </c>
-      <c r="C122" s="209" t="s">
-        <v>431</v>
+      <c r="C122" s="140" t="s">
+        <v>421</v>
       </c>
       <c r="D122" s="140"/>
-      <c r="E122" s="222" t="s">
-        <v>469</v>
+      <c r="E122" s="141" t="s">
+        <v>459</v>
       </c>
       <c r="F122" s="140" t="s">
         <v>305</v>
       </c>
-      <c r="G122" s="222" t="s">
-        <v>432</v>
+      <c r="G122" s="141" t="s">
+        <v>422</v>
       </c>
       <c r="H122" s="140" t="s">
         <v>272</v>
@@ -13972,16 +13892,16 @@
       <c r="B123" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C123" s="210" t="s">
-        <v>400</v>
+      <c r="C123" s="142" t="s">
+        <v>390</v>
       </c>
       <c r="D123" s="143" t="s">
-        <v>351</v>
-      </c>
-      <c r="E123" s="211"/>
+        <v>702</v>
+      </c>
+      <c r="E123" s="143"/>
       <c r="F123" s="143"/>
-      <c r="G123" s="211" t="s">
-        <v>431</v>
+      <c r="G123" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H123" s="143"/>
       <c r="I123" s="143" t="s">
@@ -13998,14 +13918,14 @@
       <c r="B124" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C124" s="211" t="s">
-        <v>431</v>
+      <c r="C124" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D124" s="143"/>
-      <c r="E124" s="211"/>
+      <c r="E124" s="143"/>
       <c r="F124" s="143"/>
-      <c r="G124" s="210" t="s">
-        <v>541</v>
+      <c r="G124" s="142" t="s">
+        <v>530</v>
       </c>
       <c r="H124" s="143" t="s">
         <v>176</v>
@@ -14024,18 +13944,18 @@
       <c r="B125" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C125" s="211" t="s">
-        <v>431</v>
+      <c r="C125" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D125" s="143"/>
-      <c r="E125" s="210" t="s">
-        <v>509</v>
+      <c r="E125" s="142" t="s">
+        <v>498</v>
       </c>
       <c r="F125" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G125" s="210" t="s">
-        <v>416</v>
+      <c r="G125" s="142" t="s">
+        <v>406</v>
       </c>
       <c r="H125" s="143" t="s">
         <v>272</v>
@@ -14054,14 +13974,14 @@
       <c r="B126" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C126" s="211" t="s">
-        <v>431</v>
+      <c r="C126" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D126" s="143"/>
-      <c r="E126" s="211"/>
+      <c r="E126" s="143"/>
       <c r="F126" s="143"/>
-      <c r="G126" s="211" t="s">
-        <v>431</v>
+      <c r="G126" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H126" s="143"/>
       <c r="I126" s="143" t="s">
@@ -14078,20 +13998,20 @@
       <c r="B127" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C127" s="210" t="s">
-        <v>401</v>
+      <c r="C127" s="142" t="s">
+        <v>391</v>
       </c>
       <c r="D127" s="143" t="s">
-        <v>352</v>
-      </c>
-      <c r="E127" s="210" t="s">
-        <v>510</v>
+        <v>697</v>
+      </c>
+      <c r="E127" s="142" t="s">
+        <v>499</v>
       </c>
       <c r="F127" s="143" t="s">
         <v>295</v>
       </c>
-      <c r="G127" s="210" t="s">
-        <v>433</v>
+      <c r="G127" s="142" t="s">
+        <v>423</v>
       </c>
       <c r="H127" s="143" t="s">
         <v>294</v>
@@ -14110,18 +14030,18 @@
       <c r="B128" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C128" s="211" t="s">
-        <v>431</v>
+      <c r="C128" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D128" s="143"/>
-      <c r="E128" s="210" t="s">
+      <c r="E128" s="142" t="s">
         <v>82</v>
       </c>
       <c r="F128" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G128" s="210" t="s">
-        <v>417</v>
+      <c r="G128" s="142" t="s">
+        <v>407</v>
       </c>
       <c r="H128" s="143" t="s">
         <v>176</v>
@@ -14140,14 +14060,14 @@
       <c r="B129" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C129" s="211" t="s">
-        <v>431</v>
+      <c r="C129" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D129" s="143"/>
-      <c r="E129" s="210"/>
+      <c r="E129" s="142"/>
       <c r="F129" s="143"/>
-      <c r="G129" s="211" t="s">
-        <v>431</v>
+      <c r="G129" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H129" s="143"/>
       <c r="I129" s="143" t="s">
@@ -14164,20 +14084,20 @@
       <c r="B130" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C130" s="210" t="s">
-        <v>402</v>
+      <c r="C130" s="142" t="s">
+        <v>392</v>
       </c>
       <c r="D130" s="143" t="s">
-        <v>353</v>
-      </c>
-      <c r="E130" s="210" t="s">
-        <v>511</v>
+        <v>346</v>
+      </c>
+      <c r="E130" s="142" t="s">
+        <v>500</v>
       </c>
       <c r="F130" s="143" t="s">
         <v>295</v>
       </c>
-      <c r="G130" s="210" t="s">
-        <v>418</v>
+      <c r="G130" s="142" t="s">
+        <v>408</v>
       </c>
       <c r="H130" s="143" t="s">
         <v>176</v>
@@ -14196,16 +14116,16 @@
       <c r="B131" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C131" s="211" t="s">
-        <v>431</v>
+      <c r="C131" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D131" s="143"/>
-      <c r="E131" s="211" t="s">
-        <v>431</v>
+      <c r="E131" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="F131" s="143"/>
-      <c r="G131" s="210" t="s">
-        <v>419</v>
+      <c r="G131" s="142" t="s">
+        <v>409</v>
       </c>
       <c r="H131" s="143" t="s">
         <v>294</v>
@@ -14224,18 +14144,18 @@
       <c r="B132" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C132" s="211" t="s">
-        <v>431</v>
+      <c r="C132" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D132" s="143"/>
-      <c r="E132" s="210" t="s">
+      <c r="E132" s="142" t="s">
         <v>87</v>
       </c>
       <c r="F132" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G132" s="211" t="s">
-        <v>431</v>
+      <c r="G132" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H132" s="143"/>
       <c r="I132" s="143" t="s">
@@ -14252,20 +14172,20 @@
       <c r="B133" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C133" s="210" t="s">
-        <v>403</v>
+      <c r="C133" s="142" t="s">
+        <v>393</v>
       </c>
       <c r="D133" s="143" t="s">
-        <v>352</v>
-      </c>
-      <c r="E133" s="210" t="s">
+        <v>697</v>
+      </c>
+      <c r="E133" s="142" t="s">
         <v>89</v>
       </c>
       <c r="F133" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G133" s="210" t="s">
-        <v>420</v>
+      <c r="G133" s="142" t="s">
+        <v>410</v>
       </c>
       <c r="H133" s="143" t="s">
         <v>272</v>
@@ -14284,18 +14204,18 @@
       <c r="B134" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C134" s="211" t="s">
-        <v>431</v>
+      <c r="C134" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D134" s="143"/>
-      <c r="E134" s="210" t="s">
-        <v>512</v>
+      <c r="E134" s="142" t="s">
+        <v>501</v>
       </c>
       <c r="F134" s="143" t="s">
         <v>295</v>
       </c>
-      <c r="G134" s="210" t="s">
-        <v>421</v>
+      <c r="G134" s="142" t="s">
+        <v>411</v>
       </c>
       <c r="H134" s="143" t="s">
         <v>272</v>
@@ -14314,16 +14234,16 @@
       <c r="B135" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C135" s="211" t="s">
-        <v>431</v>
+      <c r="C135" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D135" s="143"/>
-      <c r="E135" s="211" t="s">
-        <v>431</v>
+      <c r="E135" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="F135" s="143"/>
-      <c r="G135" s="211" t="s">
-        <v>431</v>
+      <c r="G135" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H135" s="143"/>
       <c r="I135" s="143" t="s">
@@ -14340,20 +14260,20 @@
       <c r="B136" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C136" s="210" t="s">
-        <v>404</v>
+      <c r="C136" s="142" t="s">
+        <v>394</v>
       </c>
       <c r="D136" s="143" t="s">
-        <v>346</v>
-      </c>
-      <c r="E136" s="210" t="s">
-        <v>411</v>
+        <v>701</v>
+      </c>
+      <c r="E136" s="142" t="s">
+        <v>401</v>
       </c>
       <c r="F136" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G136" s="210" t="s">
-        <v>434</v>
+      <c r="G136" s="142" t="s">
+        <v>424</v>
       </c>
       <c r="H136" s="143" t="s">
         <v>294</v>
@@ -14372,18 +14292,18 @@
       <c r="B137" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C137" s="211" t="s">
-        <v>431</v>
+      <c r="C137" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D137" s="143"/>
-      <c r="E137" s="210" t="s">
-        <v>513</v>
+      <c r="E137" s="142" t="s">
+        <v>502</v>
       </c>
       <c r="F137" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G137" s="210" t="s">
-        <v>422</v>
+      <c r="G137" s="142" t="s">
+        <v>412</v>
       </c>
       <c r="H137" s="143" t="s">
         <v>272</v>
@@ -14402,16 +14322,16 @@
       <c r="B138" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C138" s="211" t="s">
-        <v>431</v>
+      <c r="C138" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D138" s="143"/>
-      <c r="E138" s="211" t="s">
-        <v>431</v>
+      <c r="E138" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="F138" s="143"/>
-      <c r="G138" s="211" t="s">
-        <v>431</v>
+      <c r="G138" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H138" s="143"/>
       <c r="I138" s="143">
@@ -14428,20 +14348,20 @@
       <c r="B139" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C139" s="210" t="s">
-        <v>405</v>
+      <c r="C139" s="142" t="s">
+        <v>395</v>
       </c>
       <c r="D139" s="143" t="s">
-        <v>354</v>
-      </c>
-      <c r="E139" s="210" t="s">
-        <v>514</v>
+        <v>347</v>
+      </c>
+      <c r="E139" s="142" t="s">
+        <v>503</v>
       </c>
       <c r="F139" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G139" s="210" t="s">
-        <v>423</v>
+      <c r="G139" s="142" t="s">
+        <v>413</v>
       </c>
       <c r="H139" s="143" t="s">
         <v>176</v>
@@ -14460,14 +14380,14 @@
       <c r="B140" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C140" s="211" t="s">
-        <v>431</v>
+      <c r="C140" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D140" s="143"/>
-      <c r="E140" s="211"/>
+      <c r="E140" s="143"/>
       <c r="F140" s="143"/>
-      <c r="G140" s="210" t="s">
-        <v>424</v>
+      <c r="G140" s="142" t="s">
+        <v>414</v>
       </c>
       <c r="H140" s="143" t="s">
         <v>176</v>
@@ -14486,18 +14406,18 @@
       <c r="B141" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C141" s="211" t="s">
-        <v>431</v>
+      <c r="C141" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D141" s="143"/>
-      <c r="E141" s="210" t="s">
-        <v>515</v>
+      <c r="E141" s="142" t="s">
+        <v>504</v>
       </c>
       <c r="F141" s="143" t="s">
         <v>305</v>
       </c>
-      <c r="G141" s="211" t="s">
-        <v>431</v>
+      <c r="G141" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="H141" s="143"/>
       <c r="I141" s="143" t="s">
@@ -14514,18 +14434,18 @@
       <c r="B142" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C142" s="211" t="s">
-        <v>431</v>
+      <c r="C142" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D142" s="143"/>
-      <c r="E142" s="210" t="s">
+      <c r="E142" s="142" t="s">
         <v>325</v>
       </c>
       <c r="F142" s="143" t="s">
         <v>295</v>
       </c>
-      <c r="G142" s="210" t="s">
-        <v>425</v>
+      <c r="G142" s="142" t="s">
+        <v>415</v>
       </c>
       <c r="H142" s="143" t="s">
         <v>272</v>
@@ -14544,20 +14464,20 @@
       <c r="B143" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C143" s="210" t="s">
-        <v>406</v>
+      <c r="C143" s="142" t="s">
+        <v>396</v>
       </c>
       <c r="D143" s="143" t="s">
-        <v>350</v>
-      </c>
-      <c r="E143" s="210" t="s">
-        <v>516</v>
+        <v>696</v>
+      </c>
+      <c r="E143" s="142" t="s">
+        <v>505</v>
       </c>
       <c r="F143" s="143" t="s">
         <v>295</v>
       </c>
-      <c r="G143" s="210" t="s">
-        <v>426</v>
+      <c r="G143" s="142" t="s">
+        <v>416</v>
       </c>
       <c r="H143" s="143" t="s">
         <v>272</v>
@@ -14576,16 +14496,16 @@
       <c r="B144" s="143" t="s">
         <v>332</v>
       </c>
-      <c r="C144" s="211" t="s">
-        <v>431</v>
+      <c r="C144" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="D144" s="143"/>
-      <c r="E144" s="211" t="s">
-        <v>431</v>
+      <c r="E144" s="143" t="s">
+        <v>421</v>
       </c>
       <c r="F144" s="143"/>
-      <c r="G144" s="210" t="s">
-        <v>676</v>
+      <c r="G144" s="142" t="s">
+        <v>665</v>
       </c>
       <c r="H144" s="143" t="s">
         <v>294</v>
@@ -14604,18 +14524,18 @@
       <c r="B145" s="144" t="s">
         <v>332</v>
       </c>
-      <c r="C145" s="212" t="s">
-        <v>431</v>
+      <c r="C145" s="144" t="s">
+        <v>421</v>
       </c>
       <c r="D145" s="144"/>
-      <c r="E145" s="223" t="s">
-        <v>517</v>
+      <c r="E145" s="152" t="s">
+        <v>506</v>
       </c>
       <c r="F145" s="144" t="s">
         <v>295</v>
       </c>
-      <c r="G145" s="212" t="s">
-        <v>431</v>
+      <c r="G145" s="144" t="s">
+        <v>421</v>
       </c>
       <c r="H145" s="144"/>
       <c r="I145" s="144" t="s">
@@ -14632,18 +14552,18 @@
       <c r="B146" s="145" t="s">
         <v>333</v>
       </c>
-      <c r="C146" s="213" t="s">
-        <v>431</v>
+      <c r="C146" s="145" t="s">
+        <v>421</v>
       </c>
       <c r="D146" s="145"/>
-      <c r="E146" s="224" t="s">
-        <v>518</v>
+      <c r="E146" s="153" t="s">
+        <v>507</v>
       </c>
       <c r="F146" s="145" t="s">
         <v>305</v>
       </c>
-      <c r="G146" s="213" t="s">
-        <v>431</v>
+      <c r="G146" s="145" t="s">
+        <v>421</v>
       </c>
       <c r="H146" s="145"/>
       <c r="I146" s="145" t="s">
@@ -14660,16 +14580,16 @@
       <c r="B147" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C147" s="214" t="s">
-        <v>431</v>
+      <c r="C147" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D147" s="146"/>
-      <c r="E147" s="214" t="s">
-        <v>431</v>
+      <c r="E147" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F147" s="146"/>
-      <c r="G147" s="215" t="s">
-        <v>435</v>
+      <c r="G147" s="147" t="s">
+        <v>425</v>
       </c>
       <c r="H147" s="146" t="s">
         <v>272</v>
@@ -14688,18 +14608,18 @@
       <c r="B148" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C148" s="214" t="s">
-        <v>431</v>
+      <c r="C148" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D148" s="146"/>
-      <c r="E148" s="215" t="s">
-        <v>519</v>
+      <c r="E148" s="147" t="s">
+        <v>508</v>
       </c>
       <c r="F148" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G148" s="215" t="s">
-        <v>427</v>
+      <c r="G148" s="147" t="s">
+        <v>417</v>
       </c>
       <c r="H148" s="146" t="s">
         <v>294</v>
@@ -14718,20 +14638,20 @@
       <c r="B149" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C149" s="215" t="s">
-        <v>407</v>
+      <c r="C149" s="147" t="s">
+        <v>397</v>
       </c>
       <c r="D149" s="146" t="s">
-        <v>355</v>
-      </c>
-      <c r="E149" s="215" t="s">
-        <v>470</v>
+        <v>703</v>
+      </c>
+      <c r="E149" s="147" t="s">
+        <v>460</v>
       </c>
       <c r="F149" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G149" s="214" t="s">
-        <v>431</v>
+      <c r="G149" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H149" s="146"/>
       <c r="I149" s="146" t="s">
@@ -14748,15 +14668,15 @@
       <c r="B150" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C150" s="214" t="s">
-        <v>431</v>
+      <c r="C150" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D150" s="146"/>
-      <c r="E150" s="214" t="s">
-        <v>431</v>
+      <c r="E150" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F150" s="146"/>
-      <c r="G150" s="215" t="s">
+      <c r="G150" s="147" t="s">
         <v>51</v>
       </c>
       <c r="H150" s="146" t="s">
@@ -14776,18 +14696,18 @@
       <c r="B151" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C151" s="214" t="s">
-        <v>431</v>
+      <c r="C151" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D151" s="146"/>
-      <c r="E151" s="215" t="s">
+      <c r="E151" s="147" t="s">
         <v>301</v>
       </c>
       <c r="F151" s="146" t="s">
         <v>305</v>
       </c>
-      <c r="G151" s="215" t="s">
-        <v>436</v>
+      <c r="G151" s="147" t="s">
+        <v>426</v>
       </c>
       <c r="H151" s="146" t="s">
         <v>176</v>
@@ -14806,18 +14726,18 @@
       <c r="B152" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C152" s="214" t="s">
-        <v>431</v>
+      <c r="C152" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D152" s="146"/>
-      <c r="E152" s="215" t="s">
-        <v>412</v>
+      <c r="E152" s="147" t="s">
+        <v>402</v>
       </c>
       <c r="F152" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G152" s="214" t="s">
-        <v>431</v>
+      <c r="G152" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H152" s="146"/>
       <c r="I152" s="146" t="s">
@@ -14834,18 +14754,18 @@
       <c r="B153" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C153" s="215" t="s">
-        <v>408</v>
+      <c r="C153" s="147" t="s">
+        <v>398</v>
       </c>
       <c r="D153" s="146" t="s">
-        <v>351</v>
-      </c>
-      <c r="E153" s="214" t="s">
-        <v>431</v>
+        <v>702</v>
+      </c>
+      <c r="E153" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F153" s="146"/>
-      <c r="G153" s="215" t="s">
-        <v>428</v>
+      <c r="G153" s="147" t="s">
+        <v>418</v>
       </c>
       <c r="H153" s="146" t="s">
         <v>294</v>
@@ -14864,17 +14784,17 @@
       <c r="B154" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C154" s="214" t="s">
-        <v>431</v>
+      <c r="C154" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D154" s="146"/>
-      <c r="E154" s="215" t="s">
+      <c r="E154" s="147" t="s">
         <v>303</v>
       </c>
       <c r="F154" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G154" s="215" t="s">
+      <c r="G154" s="147" t="s">
         <v>143</v>
       </c>
       <c r="H154" s="146" t="s">
@@ -14894,18 +14814,18 @@
       <c r="B155" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C155" s="214" t="s">
-        <v>431</v>
+      <c r="C155" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D155" s="146"/>
-      <c r="E155" s="215" t="s">
-        <v>520</v>
+      <c r="E155" s="147" t="s">
+        <v>509</v>
       </c>
       <c r="F155" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G155" s="214" t="s">
-        <v>431</v>
+      <c r="G155" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H155" s="146"/>
       <c r="I155" s="146" t="s">
@@ -14922,18 +14842,18 @@
       <c r="B156" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C156" s="215" t="s">
-        <v>409</v>
+      <c r="C156" s="147" t="s">
+        <v>399</v>
       </c>
       <c r="D156" s="146" t="s">
-        <v>348</v>
-      </c>
-      <c r="E156" s="214" t="s">
-        <v>431</v>
+        <v>344</v>
+      </c>
+      <c r="E156" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F156" s="146"/>
-      <c r="G156" s="215" t="s">
-        <v>679</v>
+      <c r="G156" s="147" t="s">
+        <v>668</v>
       </c>
       <c r="H156" s="146" t="s">
         <v>294</v>
@@ -14952,16 +14872,16 @@
       <c r="B157" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C157" s="214" t="s">
-        <v>431</v>
+      <c r="C157" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D157" s="146"/>
-      <c r="E157" s="214" t="s">
-        <v>431</v>
+      <c r="E157" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F157" s="146"/>
-      <c r="G157" s="215" t="s">
-        <v>438</v>
+      <c r="G157" s="147" t="s">
+        <v>428</v>
       </c>
       <c r="H157" s="146" t="s">
         <v>272</v>
@@ -14980,18 +14900,18 @@
       <c r="B158" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C158" s="214" t="s">
-        <v>431</v>
+      <c r="C158" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D158" s="146"/>
-      <c r="E158" s="215" t="s">
-        <v>681</v>
+      <c r="E158" s="147" t="s">
+        <v>670</v>
       </c>
       <c r="F158" s="146" t="s">
         <v>305</v>
       </c>
-      <c r="G158" s="215" t="s">
-        <v>439</v>
+      <c r="G158" s="147" t="s">
+        <v>429</v>
       </c>
       <c r="H158" s="146" t="s">
         <v>176</v>
@@ -15010,17 +14930,17 @@
       <c r="B159" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C159" s="215" t="s">
+      <c r="C159" s="147" t="s">
         <v>124</v>
       </c>
       <c r="D159" s="146" t="s">
-        <v>343</v>
-      </c>
-      <c r="E159" s="214" t="s">
-        <v>431</v>
+        <v>699</v>
+      </c>
+      <c r="E159" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F159" s="146"/>
-      <c r="G159" s="214"/>
+      <c r="G159" s="146"/>
       <c r="H159" s="146"/>
       <c r="I159" s="146" t="s">
         <v>11</v>
@@ -15036,18 +14956,18 @@
       <c r="B160" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C160" s="214" t="s">
-        <v>431</v>
+      <c r="C160" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D160" s="146"/>
-      <c r="E160" s="215" t="s">
-        <v>521</v>
+      <c r="E160" s="147" t="s">
+        <v>510</v>
       </c>
       <c r="F160" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G160" s="215" t="s">
-        <v>429</v>
+      <c r="G160" s="147" t="s">
+        <v>419</v>
       </c>
       <c r="H160" s="146" t="s">
         <v>272</v>
@@ -15066,16 +14986,16 @@
       <c r="B161" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C161" s="214" t="s">
-        <v>431</v>
+      <c r="C161" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D161" s="146"/>
-      <c r="E161" s="214" t="s">
-        <v>431</v>
+      <c r="E161" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F161" s="146"/>
-      <c r="G161" s="215" t="s">
-        <v>437</v>
+      <c r="G161" s="147" t="s">
+        <v>427</v>
       </c>
       <c r="H161" s="146" t="s">
         <v>176</v>
@@ -15094,18 +15014,18 @@
       <c r="B162" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C162" s="215" t="s">
-        <v>683</v>
+      <c r="C162" s="147" t="s">
+        <v>672</v>
       </c>
       <c r="D162" s="146" t="s">
-        <v>688</v>
-      </c>
-      <c r="E162" s="214" t="s">
-        <v>431</v>
+        <v>676</v>
+      </c>
+      <c r="E162" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F162" s="146"/>
-      <c r="G162" s="214" t="s">
-        <v>431</v>
+      <c r="G162" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H162" s="146"/>
       <c r="I162" s="146" t="s">
@@ -15122,18 +15042,18 @@
       <c r="B163" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C163" s="214" t="s">
-        <v>431</v>
+      <c r="C163" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D163" s="146"/>
-      <c r="E163" s="215" t="s">
-        <v>689</v>
+      <c r="E163" s="147" t="s">
+        <v>677</v>
       </c>
       <c r="F163" s="146" t="s">
         <v>305</v>
       </c>
-      <c r="G163" s="215" t="s">
-        <v>465</v>
+      <c r="G163" s="147" t="s">
+        <v>455</v>
       </c>
       <c r="H163" s="154" t="s">
         <v>272</v>
@@ -15152,18 +15072,18 @@
       <c r="B164" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C164" s="214" t="s">
-        <v>431</v>
+      <c r="C164" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D164" s="146"/>
-      <c r="E164" s="215" t="s">
-        <v>690</v>
+      <c r="E164" s="147" t="s">
+        <v>678</v>
       </c>
       <c r="F164" s="146" t="s">
         <v>305</v>
       </c>
-      <c r="G164" s="214" t="s">
-        <v>431</v>
+      <c r="G164" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H164" s="146"/>
       <c r="I164" s="146" t="s">
@@ -15180,16 +15100,16 @@
       <c r="B165" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C165" s="214" t="s">
-        <v>431</v>
+      <c r="C165" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D165" s="146"/>
-      <c r="E165" s="214" t="s">
-        <v>431</v>
+      <c r="E165" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F165" s="146"/>
-      <c r="G165" s="215" t="s">
-        <v>678</v>
+      <c r="G165" s="147" t="s">
+        <v>667</v>
       </c>
       <c r="H165" s="146" t="s">
         <v>294</v>
@@ -15208,20 +15128,20 @@
       <c r="B166" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C166" s="215" t="s">
-        <v>684</v>
+      <c r="C166" s="147" t="s">
+        <v>673</v>
       </c>
       <c r="D166" s="146" t="s">
-        <v>685</v>
-      </c>
-      <c r="E166" s="215" t="s">
-        <v>691</v>
+        <v>700</v>
+      </c>
+      <c r="E166" s="147" t="s">
+        <v>679</v>
       </c>
       <c r="F166" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G166" s="215" t="s">
-        <v>600</v>
+      <c r="G166" s="147" t="s">
+        <v>589</v>
       </c>
       <c r="H166" s="146" t="s">
         <v>176</v>
@@ -15240,16 +15160,18 @@
       <c r="B167" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C167" s="214" t="s">
-        <v>431</v>
+      <c r="C167" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D167" s="146"/>
-      <c r="E167" s="214" t="s">
-        <v>431</v>
-      </c>
-      <c r="F167" s="146"/>
-      <c r="G167" s="214" t="s">
-        <v>431</v>
+      <c r="E167" s="147" t="s">
+        <v>688</v>
+      </c>
+      <c r="F167" s="154" t="s">
+        <v>689</v>
+      </c>
+      <c r="G167" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="H167" s="146"/>
       <c r="I167" s="146" t="s">
@@ -15266,16 +15188,16 @@
       <c r="B168" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C168" s="214" t="s">
-        <v>431</v>
+      <c r="C168" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D168" s="146"/>
-      <c r="E168" s="214" t="s">
-        <v>431</v>
+      <c r="E168" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="F168" s="146"/>
-      <c r="G168" s="215" t="s">
-        <v>677</v>
+      <c r="G168" s="147" t="s">
+        <v>666</v>
       </c>
       <c r="H168" s="146" t="s">
         <v>176</v>
@@ -15294,20 +15216,22 @@
       <c r="B169" s="146" t="s">
         <v>333</v>
       </c>
-      <c r="C169" s="214" t="s">
-        <v>431</v>
+      <c r="C169" s="146" t="s">
+        <v>421</v>
       </c>
       <c r="D169" s="146"/>
-      <c r="E169" s="215" t="s">
-        <v>682</v>
+      <c r="E169" s="147" t="s">
+        <v>671</v>
       </c>
       <c r="F169" s="146" t="s">
         <v>295</v>
       </c>
-      <c r="G169" s="214" t="s">
-        <v>431</v>
-      </c>
-      <c r="H169" s="146"/>
+      <c r="G169" s="147" t="s">
+        <v>692</v>
+      </c>
+      <c r="H169" s="189" t="s">
+        <v>693</v>
+      </c>
       <c r="I169" s="146" t="s">
         <v>1</v>
       </c>
@@ -17976,13 +17900,13 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="L80:L81 N80:N81 P80:P81 C1:C1048576 E1:E1048576 G1:G1048576">
+  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 L80:L81 N80:N81 P80:P81">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M80:M81 O80:O81 Q80:Q81 D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
+  <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576 M80:M81 O80:O81 Q80:Q81">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24544,12 +24468,12 @@
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="G1:G76 E1:E158 C1:C1048576 H12 D70 G78:G1048576 H120 E160:E1048576">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="'">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H11 D1:D69 F1:F1048576 H13:H119 D71:D1048576 G77 H121:H1048576 E159">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="例行維護中">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41B1AD8-8E0E-49A3-9A7C-1C35019F4B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6D2439-FC80-42CC-A8AA-9BE1FB5C3D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3735" yWindow="0" windowWidth="25065" windowHeight="15585" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" tabRatio="758" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="timeList" sheetId="16" r:id="rId1"/>
-    <sheet name="timeList_0225" sheetId="13" r:id="rId2"/>
-    <sheet name="timeList_0211-0224" sheetId="15" r:id="rId3"/>
-    <sheet name="timeList0204-0210" sheetId="14" r:id="rId4"/>
+    <sheet name="timeList_0225" sheetId="13" r:id="rId1"/>
+    <sheet name="timeList" sheetId="15" r:id="rId2"/>
+    <sheet name="timeList0204-0210" sheetId="14" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'timeList_0211-0224'!$B$1:$H$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">timeList_0225!$B$1:$H$169</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'timeList0204-0210'!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">timeList!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">timeList_0225!$B$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'timeList0204-0210'!$B$1:$H$169</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4489" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3652" uniqueCount="714">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -2557,6 +2556,12 @@
       <t>例行維護中</t>
     </r>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>05:3×</t>
+  </si>
+  <si>
+    <t>07:47_?</t>
   </si>
 </sst>
 </file>
@@ -3377,35 +3382,7 @@
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -3749,6189 +3726,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D35C763-89CA-436A-9C42-49C29E0C467A}">
-  <dimension ref="A1:J1055"/>
-  <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="4.25" style="111" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.625" style="111" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="111" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.75" style="111" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="111" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.75" style="111" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="111" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="111" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.25" style="111" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.125" style="111" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.625" style="111" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="14.25" style="111"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="157" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="155"/>
-      <c r="B1" s="156" t="s">
-        <v>326</v>
-      </c>
-      <c r="C1" s="117" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="117" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="117" t="s">
-        <v>85</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>86</v>
-      </c>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="118" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C4" s="119"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="119"/>
-      <c r="H4" s="159"/>
-      <c r="I4" s="118" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="18" customHeight="1">
-      <c r="A5" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1">
-      <c r="A6" s="118" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1">
-      <c r="A7" s="118" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="119"/>
-      <c r="H7" s="118"/>
-      <c r="I7" s="118" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1">
-      <c r="A8" s="118" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="118" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1">
-      <c r="A9" s="118" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="119"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="118" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1">
-      <c r="A10" s="118" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C10" s="119"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="118" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1">
-      <c r="A11" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1">
-      <c r="A12" s="118" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="118"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1">
-      <c r="A13" s="118" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="119"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118" t="s">
-        <v>13</v>
-      </c>
-      <c r="J13" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="18" customHeight="1">
-      <c r="A14" s="118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C14" s="119"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="18" customHeight="1">
-      <c r="A15" s="118" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C15" s="118"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="118" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="18" customHeight="1">
-      <c r="A16" s="118" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="18" customHeight="1">
-      <c r="A17" s="118" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="118" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="18" customHeight="1">
-      <c r="A18" s="118" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="119"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="18" customHeight="1">
-      <c r="A19" s="118" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="119"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="18" customHeight="1">
-      <c r="A20" s="118" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118" t="s">
-        <v>6</v>
-      </c>
-      <c r="J20" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1">
-      <c r="A21" s="118" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="119"/>
-      <c r="H21" s="158"/>
-      <c r="I21" s="118" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1">
-      <c r="A22" s="118" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="18" customHeight="1">
-      <c r="A23" s="118" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1">
-      <c r="A24" s="118" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="159"/>
-      <c r="I24" s="118" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="118" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A25" s="120" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="120" t="s">
-        <v>327</v>
-      </c>
-      <c r="C25" s="120"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="120"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="120"/>
-      <c r="H25" s="120"/>
-      <c r="I25" s="120" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="120" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1">
-      <c r="A26" s="121" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="121" t="s">
-        <v>328</v>
-      </c>
-      <c r="C26" s="121"/>
-      <c r="D26" s="121"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="122"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="121" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="121" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1">
-      <c r="A27" s="123" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="160"/>
-      <c r="I27" s="123" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1">
-      <c r="A28" s="123" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" s="123"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="123"/>
-      <c r="G28" s="123"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="123" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1">
-      <c r="A29" s="123" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C29" s="123"/>
-      <c r="D29" s="123"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="123"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="160"/>
-      <c r="I29" s="123" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1">
-      <c r="A30" s="123" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="123"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="123"/>
-      <c r="I30" s="123" t="s">
-        <v>20</v>
-      </c>
-      <c r="J30" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1">
-      <c r="A31" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C31" s="123"/>
-      <c r="D31" s="123"/>
-      <c r="E31" s="123"/>
-      <c r="F31" s="123"/>
-      <c r="G31" s="123"/>
-      <c r="H31" s="123"/>
-      <c r="I31" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1">
-      <c r="A32" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="B32" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C32" s="123"/>
-      <c r="D32" s="123"/>
-      <c r="E32" s="123"/>
-      <c r="F32" s="123"/>
-      <c r="G32" s="124"/>
-      <c r="H32" s="123"/>
-      <c r="I32" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1">
-      <c r="A33" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C33" s="123"/>
-      <c r="D33" s="123"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="123"/>
-      <c r="G33" s="124"/>
-      <c r="H33" s="123"/>
-      <c r="I33" s="123" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1">
-      <c r="A34" s="123" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C34" s="124"/>
-      <c r="D34" s="190"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="123"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="123"/>
-      <c r="I34" s="123" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1">
-      <c r="A35" s="123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C35" s="123"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="123"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="123"/>
-      <c r="I35" s="123" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1">
-      <c r="A36" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C36" s="123"/>
-      <c r="D36" s="123"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="123"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="123"/>
-      <c r="I36" s="123" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1">
-      <c r="A37" s="123" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C37" s="123"/>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="123"/>
-      <c r="I37" s="123" t="s">
-        <v>13</v>
-      </c>
-      <c r="J37" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1">
-      <c r="A38" s="123" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="190"/>
-      <c r="E38" s="123"/>
-      <c r="F38" s="123"/>
-      <c r="G38" s="123"/>
-      <c r="H38" s="123"/>
-      <c r="I38" s="123" t="s">
-        <v>12</v>
-      </c>
-      <c r="J38" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" customHeight="1">
-      <c r="A39" s="123" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C39" s="123"/>
-      <c r="D39" s="123"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="123"/>
-      <c r="G39" s="124"/>
-      <c r="H39" s="123"/>
-      <c r="I39" s="123" t="s">
-        <v>11</v>
-      </c>
-      <c r="J39" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="18" customHeight="1">
-      <c r="A40" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C40" s="123"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="123"/>
-      <c r="F40" s="123"/>
-      <c r="G40" s="124"/>
-      <c r="H40" s="123"/>
-      <c r="I40" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="J40" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="18" customHeight="1">
-      <c r="A41" s="123" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C41" s="123"/>
-      <c r="D41" s="123"/>
-      <c r="E41" s="123"/>
-      <c r="F41" s="123"/>
-      <c r="G41" s="123"/>
-      <c r="H41" s="123"/>
-      <c r="I41" s="123" t="s">
-        <v>9</v>
-      </c>
-      <c r="J41" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="18" customHeight="1">
-      <c r="A42" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C42" s="123"/>
-      <c r="D42" s="123"/>
-      <c r="E42" s="123"/>
-      <c r="F42" s="123"/>
-      <c r="G42" s="124"/>
-      <c r="H42" s="123"/>
-      <c r="I42" s="123" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="18" customHeight="1">
-      <c r="A43" s="123" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C43" s="123"/>
-      <c r="D43" s="123"/>
-      <c r="E43" s="123"/>
-      <c r="F43" s="123"/>
-      <c r="G43" s="124"/>
-      <c r="H43" s="160"/>
-      <c r="I43" s="123" t="s">
-        <v>7</v>
-      </c>
-      <c r="J43" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1">
-      <c r="A44" s="123" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C44" s="123"/>
-      <c r="D44" s="123"/>
-      <c r="E44" s="123"/>
-      <c r="F44" s="123"/>
-      <c r="G44" s="123"/>
-      <c r="H44" s="123"/>
-      <c r="I44" s="123" t="s">
-        <v>6</v>
-      </c>
-      <c r="J44" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="18" customHeight="1">
-      <c r="A45" s="123" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C45" s="124"/>
-      <c r="D45" s="123"/>
-      <c r="E45" s="124"/>
-      <c r="F45" s="123"/>
-      <c r="G45" s="124"/>
-      <c r="H45" s="123"/>
-      <c r="I45" s="123" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="18" customHeight="1">
-      <c r="A46" s="123" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C46" s="123"/>
-      <c r="D46" s="123"/>
-      <c r="E46" s="123"/>
-      <c r="F46" s="123"/>
-      <c r="G46" s="124"/>
-      <c r="H46" s="123"/>
-      <c r="I46" s="123" t="s">
-        <v>4</v>
-      </c>
-      <c r="J46" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="18" customHeight="1">
-      <c r="A47" s="123" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C47" s="123"/>
-      <c r="D47" s="123"/>
-      <c r="E47" s="124"/>
-      <c r="F47" s="123"/>
-      <c r="G47" s="123"/>
-      <c r="H47" s="123"/>
-      <c r="I47" s="123" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="18" customHeight="1">
-      <c r="A48" s="123" t="s">
-        <v>2</v>
-      </c>
-      <c r="B48" s="123" t="s">
-        <v>328</v>
-      </c>
-      <c r="C48" s="123"/>
-      <c r="D48" s="123"/>
-      <c r="E48" s="123"/>
-      <c r="F48" s="123"/>
-      <c r="G48" s="124"/>
-      <c r="H48" s="123"/>
-      <c r="I48" s="123" t="s">
-        <v>2</v>
-      </c>
-      <c r="J48" s="123" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A49" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="B49" s="125" t="s">
-        <v>328</v>
-      </c>
-      <c r="C49" s="125"/>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="125"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="125"/>
-      <c r="I49" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="J49" s="125" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="18" customHeight="1">
-      <c r="A50" s="126" t="s">
-        <v>24</v>
-      </c>
-      <c r="B50" s="126" t="s">
-        <v>329</v>
-      </c>
-      <c r="C50" s="126" t="s">
-        <v>416</v>
-      </c>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126" t="s">
-        <v>416</v>
-      </c>
-      <c r="F50" s="126"/>
-      <c r="G50" s="126" t="s">
-        <v>416</v>
-      </c>
-      <c r="H50" s="126"/>
-      <c r="I50" s="126" t="s">
-        <v>24</v>
-      </c>
-      <c r="J50" s="126" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="18" customHeight="1">
-      <c r="A51" s="127" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C51" s="127" t="s">
-        <v>416</v>
-      </c>
-      <c r="D51" s="127"/>
-      <c r="E51" s="128" t="s">
-        <v>522</v>
-      </c>
-      <c r="F51" s="127" t="s">
-        <v>295</v>
-      </c>
-      <c r="G51" s="127" t="s">
-        <v>416</v>
-      </c>
-      <c r="H51" s="127"/>
-      <c r="I51" s="127" t="s">
-        <v>23</v>
-      </c>
-      <c r="J51" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="18" customHeight="1">
-      <c r="A52" s="127" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C52" s="127" t="s">
-        <v>416</v>
-      </c>
-      <c r="D52" s="127"/>
-      <c r="E52" s="127" t="s">
-        <v>416</v>
-      </c>
-      <c r="F52" s="127"/>
-      <c r="G52" s="127" t="s">
-        <v>416</v>
-      </c>
-      <c r="H52" s="127"/>
-      <c r="I52" s="127" t="s">
-        <v>22</v>
-      </c>
-      <c r="J52" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="18" customHeight="1">
-      <c r="A53" s="127" t="s">
-        <v>21</v>
-      </c>
-      <c r="B53" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C53" s="128" t="s">
-        <v>708</v>
-      </c>
-      <c r="D53" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E53" s="128" t="s">
-        <v>708</v>
-      </c>
-      <c r="F53" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G53" s="128" t="s">
-        <v>708</v>
-      </c>
-      <c r="H53" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I53" s="127" t="s">
-        <v>21</v>
-      </c>
-      <c r="J53" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="18" customHeight="1">
-      <c r="A54" s="127" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C54" s="128" t="s">
-        <v>709</v>
-      </c>
-      <c r="D54" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E54" s="128" t="s">
-        <v>709</v>
-      </c>
-      <c r="F54" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G54" s="128" t="s">
-        <v>709</v>
-      </c>
-      <c r="H54" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I54" s="127" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="18" customHeight="1">
-      <c r="A55" s="127" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C55" s="128" t="s">
-        <v>710</v>
-      </c>
-      <c r="D55" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E55" s="128" t="s">
-        <v>710</v>
-      </c>
-      <c r="F55" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G55" s="128" t="s">
-        <v>710</v>
-      </c>
-      <c r="H55" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I55" s="127" t="s">
-        <v>19</v>
-      </c>
-      <c r="J55" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="18" customHeight="1">
-      <c r="A56" s="127" t="s">
-        <v>18</v>
-      </c>
-      <c r="B56" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C56" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="D56" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E56" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="F56" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G56" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="H56" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I56" s="127" t="s">
-        <v>18</v>
-      </c>
-      <c r="J56" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="18" customHeight="1">
-      <c r="A57" s="127" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C57" s="128" t="s">
-        <v>427</v>
-      </c>
-      <c r="D57" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E57" s="128" t="s">
-        <v>427</v>
-      </c>
-      <c r="F57" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G57" s="128" t="s">
-        <v>427</v>
-      </c>
-      <c r="H57" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I57" s="127" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="18" customHeight="1">
-      <c r="A58" s="127" t="s">
-        <v>16</v>
-      </c>
-      <c r="B58" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C58" s="128" t="s">
-        <v>337</v>
-      </c>
-      <c r="D58" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E58" s="128" t="s">
-        <v>337</v>
-      </c>
-      <c r="F58" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G58" s="128" t="s">
-        <v>337</v>
-      </c>
-      <c r="H58" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I58" s="127" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="18" customHeight="1">
-      <c r="A59" s="127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C59" s="128" t="s">
-        <v>338</v>
-      </c>
-      <c r="D59" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="E59" s="128" t="s">
-        <v>338</v>
-      </c>
-      <c r="F59" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="G59" s="128" t="s">
-        <v>338</v>
-      </c>
-      <c r="H59" s="127" t="s">
-        <v>711</v>
-      </c>
-      <c r="I59" s="127" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="18" customHeight="1">
-      <c r="A60" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C60" s="128"/>
-      <c r="D60" s="127"/>
-      <c r="E60" s="128"/>
-      <c r="F60" s="127"/>
-      <c r="G60" s="127"/>
-      <c r="H60" s="127"/>
-      <c r="I60" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="18" customHeight="1">
-      <c r="A61" s="127" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C61" s="127"/>
-      <c r="D61" s="127"/>
-      <c r="E61" s="127"/>
-      <c r="F61" s="127"/>
-      <c r="G61" s="128"/>
-      <c r="H61" s="127"/>
-      <c r="I61" s="127" t="s">
-        <v>13</v>
-      </c>
-      <c r="J61" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="18" customHeight="1">
-      <c r="A62" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="B62" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C62" s="127"/>
-      <c r="D62" s="127"/>
-      <c r="E62" s="128"/>
-      <c r="F62" s="127"/>
-      <c r="G62" s="128"/>
-      <c r="H62" s="127"/>
-      <c r="I62" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="J62" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="18" customHeight="1">
-      <c r="A63" s="127" t="s">
-        <v>11</v>
-      </c>
-      <c r="B63" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C63" s="127"/>
-      <c r="D63" s="127"/>
-      <c r="E63" s="128"/>
-      <c r="F63" s="127"/>
-      <c r="G63" s="127"/>
-      <c r="H63" s="127"/>
-      <c r="I63" s="127" t="s">
-        <v>11</v>
-      </c>
-      <c r="J63" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="18" customHeight="1">
-      <c r="A64" s="127" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C64" s="128"/>
-      <c r="D64" s="127"/>
-      <c r="E64" s="127"/>
-      <c r="F64" s="127"/>
-      <c r="G64" s="128"/>
-      <c r="H64" s="127"/>
-      <c r="I64" s="127" t="s">
-        <v>10</v>
-      </c>
-      <c r="J64" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="18" customHeight="1">
-      <c r="A65" s="127" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C65" s="127"/>
-      <c r="D65" s="127"/>
-      <c r="E65" s="128"/>
-      <c r="F65" s="127"/>
-      <c r="G65" s="127"/>
-      <c r="H65" s="127"/>
-      <c r="I65" s="127" t="s">
-        <v>9</v>
-      </c>
-      <c r="J65" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="18" customHeight="1">
-      <c r="A66" s="127" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C66" s="127"/>
-      <c r="D66" s="127"/>
-      <c r="E66" s="128"/>
-      <c r="F66" s="127"/>
-      <c r="G66" s="128"/>
-      <c r="H66" s="127"/>
-      <c r="I66" s="127" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="18" customHeight="1">
-      <c r="A67" s="127" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C67" s="128"/>
-      <c r="D67" s="127"/>
-      <c r="E67" s="127"/>
-      <c r="F67" s="127"/>
-      <c r="G67" s="128"/>
-      <c r="H67" s="127"/>
-      <c r="I67" s="127" t="s">
-        <v>7</v>
-      </c>
-      <c r="J67" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="18" customHeight="1">
-      <c r="A68" s="127" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C68" s="127"/>
-      <c r="D68" s="127"/>
-      <c r="E68" s="128"/>
-      <c r="F68" s="127"/>
-      <c r="G68" s="127"/>
-      <c r="H68" s="127"/>
-      <c r="I68" s="127" t="s">
-        <v>6</v>
-      </c>
-      <c r="J68" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="18" customHeight="1">
-      <c r="A69" s="127" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C69" s="127"/>
-      <c r="D69" s="127"/>
-      <c r="E69" s="128"/>
-      <c r="F69" s="127"/>
-      <c r="G69" s="128"/>
-      <c r="H69" s="127"/>
-      <c r="I69" s="127" t="s">
-        <v>5</v>
-      </c>
-      <c r="J69" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="18" customHeight="1">
-      <c r="A70" s="127" t="s">
-        <v>4</v>
-      </c>
-      <c r="B70" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C70" s="127"/>
-      <c r="D70" s="127"/>
-      <c r="E70" s="127"/>
-      <c r="F70" s="127"/>
-      <c r="G70" s="128"/>
-      <c r="H70" s="127"/>
-      <c r="I70" s="127" t="s">
-        <v>4</v>
-      </c>
-      <c r="J70" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="18" customHeight="1">
-      <c r="A71" s="127" t="s">
-        <v>3</v>
-      </c>
-      <c r="B71" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C71" s="128"/>
-      <c r="D71" s="127"/>
-      <c r="E71" s="128"/>
-      <c r="F71" s="127"/>
-      <c r="G71" s="127"/>
-      <c r="H71" s="127"/>
-      <c r="I71" s="127" t="s">
-        <v>3</v>
-      </c>
-      <c r="J71" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="18" customHeight="1">
-      <c r="A72" s="127" t="s">
-        <v>2</v>
-      </c>
-      <c r="B72" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="C72" s="127"/>
-      <c r="D72" s="127"/>
-      <c r="E72" s="128"/>
-      <c r="F72" s="127"/>
-      <c r="G72" s="128"/>
-      <c r="H72" s="127"/>
-      <c r="I72" s="127" t="s">
-        <v>2</v>
-      </c>
-      <c r="J72" s="127" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="B73" s="129" t="s">
-        <v>329</v>
-      </c>
-      <c r="C73" s="149"/>
-      <c r="D73" s="129"/>
-      <c r="E73" s="129"/>
-      <c r="F73" s="129"/>
-      <c r="G73" s="149"/>
-      <c r="H73" s="129"/>
-      <c r="I73" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="J73" s="129" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="18" customHeight="1">
-      <c r="A74" s="130" t="s">
-        <v>24</v>
-      </c>
-      <c r="B74" s="130" t="s">
-        <v>330</v>
-      </c>
-      <c r="C74" s="130"/>
-      <c r="D74" s="130"/>
-      <c r="E74" s="150"/>
-      <c r="F74" s="130"/>
-      <c r="G74" s="150"/>
-      <c r="H74" s="130"/>
-      <c r="I74" s="130" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="18" customHeight="1">
-      <c r="A75" s="131" t="s">
-        <v>23</v>
-      </c>
-      <c r="B75" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C75" s="131"/>
-      <c r="D75" s="131"/>
-      <c r="E75" s="132"/>
-      <c r="F75" s="131"/>
-      <c r="G75" s="131"/>
-      <c r="H75" s="131"/>
-      <c r="I75" s="131" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="18" customHeight="1">
-      <c r="A76" s="131" t="s">
-        <v>22</v>
-      </c>
-      <c r="B76" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="132"/>
-      <c r="D76" s="131"/>
-      <c r="E76" s="131"/>
-      <c r="F76" s="131"/>
-      <c r="G76" s="132"/>
-      <c r="H76" s="131"/>
-      <c r="I76" s="131" t="s">
-        <v>22</v>
-      </c>
-      <c r="J76" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="18" customHeight="1">
-      <c r="A77" s="131" t="s">
-        <v>21</v>
-      </c>
-      <c r="B77" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C77" s="131"/>
-      <c r="D77" s="131"/>
-      <c r="E77" s="132"/>
-      <c r="F77" s="131"/>
-      <c r="G77" s="132"/>
-      <c r="H77" s="131"/>
-      <c r="I77" s="131" t="s">
-        <v>21</v>
-      </c>
-      <c r="J77" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="18" customHeight="1">
-      <c r="A78" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="B78" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C78" s="132"/>
-      <c r="D78" s="131"/>
-      <c r="E78" s="132"/>
-      <c r="F78" s="131"/>
-      <c r="G78" s="131"/>
-      <c r="H78" s="131"/>
-      <c r="I78" s="131" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="18" customHeight="1">
-      <c r="A79" s="131" t="s">
-        <v>19</v>
-      </c>
-      <c r="B79" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C79" s="131"/>
-      <c r="D79" s="131"/>
-      <c r="E79" s="131"/>
-      <c r="F79" s="131"/>
-      <c r="G79" s="132"/>
-      <c r="H79" s="131"/>
-      <c r="I79" s="131" t="s">
-        <v>19</v>
-      </c>
-      <c r="J79" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="18" customHeight="1">
-      <c r="A80" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="B80" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C80" s="131"/>
-      <c r="D80" s="131"/>
-      <c r="E80" s="132"/>
-      <c r="F80" s="186"/>
-      <c r="G80" s="132"/>
-      <c r="H80" s="131"/>
-      <c r="I80" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J80" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="18" customHeight="1">
-      <c r="A81" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="B81" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C81" s="131"/>
-      <c r="D81" s="131"/>
-      <c r="E81" s="132"/>
-      <c r="F81" s="186"/>
-      <c r="G81" s="132"/>
-      <c r="H81" s="131"/>
-      <c r="I81" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="18" customHeight="1">
-      <c r="A82" s="131" t="s">
-        <v>16</v>
-      </c>
-      <c r="B82" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C82" s="131"/>
-      <c r="D82" s="131"/>
-      <c r="E82" s="131"/>
-      <c r="F82" s="131"/>
-      <c r="G82" s="132"/>
-      <c r="H82" s="131"/>
-      <c r="I82" s="131" t="s">
-        <v>16</v>
-      </c>
-      <c r="J82" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="18" customHeight="1">
-      <c r="A83" s="131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C83" s="131"/>
-      <c r="D83" s="131"/>
-      <c r="E83" s="132"/>
-      <c r="F83" s="131"/>
-      <c r="G83" s="132"/>
-      <c r="H83" s="131"/>
-      <c r="I83" s="131" t="s">
-        <v>15</v>
-      </c>
-      <c r="J83" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="18" customHeight="1">
-      <c r="A84" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C84" s="131"/>
-      <c r="D84" s="131"/>
-      <c r="E84" s="132"/>
-      <c r="F84" s="131"/>
-      <c r="G84" s="131"/>
-      <c r="H84" s="131"/>
-      <c r="I84" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="J84" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="18" customHeight="1">
-      <c r="A85" s="131" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C85" s="132"/>
-      <c r="D85" s="131"/>
-      <c r="E85" s="131"/>
-      <c r="F85" s="131"/>
-      <c r="G85" s="132"/>
-      <c r="H85" s="131"/>
-      <c r="I85" s="131" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="18" customHeight="1">
-      <c r="A86" s="131" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C86" s="131"/>
-      <c r="D86" s="131"/>
-      <c r="E86" s="132"/>
-      <c r="F86" s="131"/>
-      <c r="G86" s="132"/>
-      <c r="H86" s="131"/>
-      <c r="I86" s="131" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="18" customHeight="1">
-      <c r="A87" s="131" t="s">
-        <v>11</v>
-      </c>
-      <c r="B87" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C87" s="131"/>
-      <c r="D87" s="131"/>
-      <c r="E87" s="132"/>
-      <c r="F87" s="131"/>
-      <c r="G87" s="131"/>
-      <c r="H87" s="131"/>
-      <c r="I87" s="131" t="s">
-        <v>11</v>
-      </c>
-      <c r="J87" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="18" customHeight="1">
-      <c r="A88" s="131" t="s">
-        <v>10</v>
-      </c>
-      <c r="B88" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C88" s="131"/>
-      <c r="D88" s="131"/>
-      <c r="E88" s="132"/>
-      <c r="F88" s="131"/>
-      <c r="G88" s="132"/>
-      <c r="H88" s="131"/>
-      <c r="I88" s="131" t="s">
-        <v>10</v>
-      </c>
-      <c r="J88" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="18" customHeight="1">
-      <c r="A89" s="131" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C89" s="132"/>
-      <c r="D89" s="131"/>
-      <c r="E89" s="131"/>
-      <c r="F89" s="131"/>
-      <c r="G89" s="132"/>
-      <c r="H89" s="131"/>
-      <c r="I89" s="131" t="s">
-        <v>9</v>
-      </c>
-      <c r="J89" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="18" customHeight="1">
-      <c r="A90" s="131" t="s">
-        <v>8</v>
-      </c>
-      <c r="B90" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C90" s="131"/>
-      <c r="D90" s="131"/>
-      <c r="E90" s="132"/>
-      <c r="F90" s="131"/>
-      <c r="G90" s="131"/>
-      <c r="H90" s="131"/>
-      <c r="I90" s="131" t="s">
-        <v>8</v>
-      </c>
-      <c r="J90" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="18" customHeight="1">
-      <c r="A91" s="131" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C91" s="131"/>
-      <c r="D91" s="131"/>
-      <c r="E91" s="132"/>
-      <c r="F91" s="131"/>
-      <c r="G91" s="132"/>
-      <c r="H91" s="131"/>
-      <c r="I91" s="131" t="s">
-        <v>7</v>
-      </c>
-      <c r="J91" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="18" customHeight="1">
-      <c r="A92" s="131" t="s">
-        <v>6</v>
-      </c>
-      <c r="B92" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C92" s="131"/>
-      <c r="D92" s="131"/>
-      <c r="E92" s="131"/>
-      <c r="F92" s="131"/>
-      <c r="G92" s="132"/>
-      <c r="H92" s="131"/>
-      <c r="I92" s="131" t="s">
-        <v>6</v>
-      </c>
-      <c r="J92" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" ht="18" customHeight="1">
-      <c r="A93" s="131" t="s">
-        <v>5</v>
-      </c>
-      <c r="B93" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C93" s="131"/>
-      <c r="D93" s="131"/>
-      <c r="E93" s="132"/>
-      <c r="F93" s="131"/>
-      <c r="G93" s="131"/>
-      <c r="H93" s="131"/>
-      <c r="I93" s="131" t="s">
-        <v>5</v>
-      </c>
-      <c r="J93" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" ht="18" customHeight="1">
-      <c r="A94" s="131" t="s">
-        <v>4</v>
-      </c>
-      <c r="B94" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C94" s="132"/>
-      <c r="D94" s="131"/>
-      <c r="E94" s="132"/>
-      <c r="F94" s="131"/>
-      <c r="G94" s="132"/>
-      <c r="H94" s="131"/>
-      <c r="I94" s="131" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" ht="18" customHeight="1">
-      <c r="A95" s="131" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C95" s="131"/>
-      <c r="D95" s="131"/>
-      <c r="E95" s="131"/>
-      <c r="F95" s="131"/>
-      <c r="G95" s="132"/>
-      <c r="H95" s="131"/>
-      <c r="I95" s="131" t="s">
-        <v>3</v>
-      </c>
-      <c r="J95" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="18" customHeight="1">
-      <c r="A96" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="B96" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="C96" s="131"/>
-      <c r="D96" s="131"/>
-      <c r="E96" s="132"/>
-      <c r="F96" s="131"/>
-      <c r="G96" s="131"/>
-      <c r="H96" s="131"/>
-      <c r="I96" s="131" t="s">
-        <v>2</v>
-      </c>
-      <c r="J96" s="131" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A97" s="133" t="s">
-        <v>1</v>
-      </c>
-      <c r="B97" s="133" t="s">
-        <v>330</v>
-      </c>
-      <c r="C97" s="133"/>
-      <c r="D97" s="133"/>
-      <c r="E97" s="151"/>
-      <c r="F97" s="133"/>
-      <c r="G97" s="151"/>
-      <c r="H97" s="133"/>
-      <c r="I97" s="133" t="s">
-        <v>1</v>
-      </c>
-      <c r="J97" s="133" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" ht="18" customHeight="1">
-      <c r="A98" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="B98" s="135" t="s">
-        <v>331</v>
-      </c>
-      <c r="C98" s="134"/>
-      <c r="D98" s="135"/>
-      <c r="E98" s="134"/>
-      <c r="F98" s="135"/>
-      <c r="G98" s="134"/>
-      <c r="H98" s="135"/>
-      <c r="I98" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J98" s="135" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" ht="18" customHeight="1">
-      <c r="A99" s="136" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C99" s="136"/>
-      <c r="D99" s="136"/>
-      <c r="E99" s="136"/>
-      <c r="F99" s="136"/>
-      <c r="G99" s="137"/>
-      <c r="H99" s="136"/>
-      <c r="I99" s="136" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" ht="18" customHeight="1">
-      <c r="A100" s="136" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C100" s="137"/>
-      <c r="D100" s="136"/>
-      <c r="E100" s="137"/>
-      <c r="F100" s="136"/>
-      <c r="G100" s="136"/>
-      <c r="H100" s="136"/>
-      <c r="I100" s="136" t="s">
-        <v>22</v>
-      </c>
-      <c r="J100" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" ht="18" customHeight="1">
-      <c r="A101" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="B101" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C101" s="136"/>
-      <c r="D101" s="136"/>
-      <c r="E101" s="137"/>
-      <c r="F101" s="136"/>
-      <c r="G101" s="137"/>
-      <c r="H101" s="136"/>
-      <c r="I101" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="J101" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" ht="18" customHeight="1">
-      <c r="A102" s="136" t="s">
-        <v>20</v>
-      </c>
-      <c r="B102" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C102" s="136"/>
-      <c r="D102" s="136"/>
-      <c r="E102" s="136"/>
-      <c r="F102" s="136"/>
-      <c r="G102" s="137"/>
-      <c r="H102" s="136"/>
-      <c r="I102" s="136" t="s">
-        <v>20</v>
-      </c>
-      <c r="J102" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" ht="18" customHeight="1">
-      <c r="A103" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="B103" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C103" s="137"/>
-      <c r="D103" s="136"/>
-      <c r="E103" s="137"/>
-      <c r="F103" s="136"/>
-      <c r="G103" s="136"/>
-      <c r="H103" s="136"/>
-      <c r="I103" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="J103" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" ht="18" customHeight="1">
-      <c r="A104" s="136" t="s">
-        <v>18</v>
-      </c>
-      <c r="B104" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C104" s="136"/>
-      <c r="D104" s="136"/>
-      <c r="E104" s="136"/>
-      <c r="F104" s="136"/>
-      <c r="G104" s="137"/>
-      <c r="H104" s="136"/>
-      <c r="I104" s="136" t="s">
-        <v>18</v>
-      </c>
-      <c r="J104" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" ht="18" customHeight="1">
-      <c r="A105" s="136" t="s">
-        <v>17</v>
-      </c>
-      <c r="B105" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C105" s="136"/>
-      <c r="D105" s="136"/>
-      <c r="E105" s="137"/>
-      <c r="F105" s="136"/>
-      <c r="G105" s="137"/>
-      <c r="H105" s="136"/>
-      <c r="I105" s="136" t="s">
-        <v>17</v>
-      </c>
-      <c r="J105" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" ht="18" customHeight="1">
-      <c r="A106" s="136" t="s">
-        <v>16</v>
-      </c>
-      <c r="B106" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C106" s="136"/>
-      <c r="D106" s="136"/>
-      <c r="E106" s="137"/>
-      <c r="F106" s="136"/>
-      <c r="G106" s="137"/>
-      <c r="H106" s="136"/>
-      <c r="I106" s="136" t="s">
-        <v>16</v>
-      </c>
-      <c r="J106" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" ht="18" customHeight="1">
-      <c r="A107" s="136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C107" s="137"/>
-      <c r="D107" s="136"/>
-      <c r="E107" s="136"/>
-      <c r="F107" s="136"/>
-      <c r="G107" s="136"/>
-      <c r="H107" s="136"/>
-      <c r="I107" s="136" t="s">
-        <v>15</v>
-      </c>
-      <c r="J107" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" ht="18" customHeight="1">
-      <c r="A108" s="136" t="s">
-        <v>14</v>
-      </c>
-      <c r="B108" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C108" s="136"/>
-      <c r="D108" s="136"/>
-      <c r="E108" s="137"/>
-      <c r="F108" s="136"/>
-      <c r="G108" s="137"/>
-      <c r="H108" s="136"/>
-      <c r="I108" s="136" t="s">
-        <v>14</v>
-      </c>
-      <c r="J108" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" ht="18" customHeight="1">
-      <c r="A109" s="136" t="s">
-        <v>13</v>
-      </c>
-      <c r="B109" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C109" s="137"/>
-      <c r="D109" s="136"/>
-      <c r="E109" s="137"/>
-      <c r="F109" s="136"/>
-      <c r="G109" s="137"/>
-      <c r="H109" s="136"/>
-      <c r="I109" s="136" t="s">
-        <v>13</v>
-      </c>
-      <c r="J109" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="18" customHeight="1">
-      <c r="A110" s="136" t="s">
-        <v>12</v>
-      </c>
-      <c r="B110" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C110" s="136"/>
-      <c r="D110" s="136"/>
-      <c r="E110" s="136"/>
-      <c r="F110" s="136"/>
-      <c r="G110" s="136"/>
-      <c r="H110" s="136"/>
-      <c r="I110" s="136" t="s">
-        <v>12</v>
-      </c>
-      <c r="J110" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" ht="18" customHeight="1">
-      <c r="A111" s="136" t="s">
-        <v>11</v>
-      </c>
-      <c r="B111" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C111" s="136"/>
-      <c r="D111" s="136"/>
-      <c r="E111" s="137"/>
-      <c r="F111" s="136"/>
-      <c r="G111" s="137"/>
-      <c r="H111" s="136"/>
-      <c r="I111" s="136" t="s">
-        <v>11</v>
-      </c>
-      <c r="J111" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="18" customHeight="1">
-      <c r="A112" s="136" t="s">
-        <v>10</v>
-      </c>
-      <c r="B112" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C112" s="136"/>
-      <c r="D112" s="136"/>
-      <c r="E112" s="137"/>
-      <c r="F112" s="136"/>
-      <c r="G112" s="137"/>
-      <c r="H112" s="136"/>
-      <c r="I112" s="136" t="s">
-        <v>10</v>
-      </c>
-      <c r="J112" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" ht="18" customHeight="1">
-      <c r="A113" s="136" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C113" s="137"/>
-      <c r="D113" s="136"/>
-      <c r="E113" s="136"/>
-      <c r="F113" s="136"/>
-      <c r="G113" s="136"/>
-      <c r="H113" s="136"/>
-      <c r="I113" s="136" t="s">
-        <v>9</v>
-      </c>
-      <c r="J113" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="18" customHeight="1">
-      <c r="A114" s="136" t="s">
-        <v>8</v>
-      </c>
-      <c r="B114" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C114" s="136"/>
-      <c r="D114" s="136"/>
-      <c r="E114" s="137"/>
-      <c r="F114" s="136"/>
-      <c r="G114" s="137"/>
-      <c r="H114" s="136"/>
-      <c r="I114" s="136" t="s">
-        <v>8</v>
-      </c>
-      <c r="J114" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" ht="18" customHeight="1">
-      <c r="A115" s="136" t="s">
-        <v>7</v>
-      </c>
-      <c r="B115" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C115" s="136"/>
-      <c r="D115" s="136"/>
-      <c r="E115" s="137"/>
-      <c r="F115" s="136"/>
-      <c r="G115" s="137"/>
-      <c r="H115" s="136"/>
-      <c r="I115" s="136" t="s">
-        <v>7</v>
-      </c>
-      <c r="J115" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="18" customHeight="1">
-      <c r="A116" s="136" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C116" s="136"/>
-      <c r="D116" s="136"/>
-      <c r="E116" s="136"/>
-      <c r="F116" s="136"/>
-      <c r="G116" s="136"/>
-      <c r="H116" s="136"/>
-      <c r="I116" s="136" t="s">
-        <v>6</v>
-      </c>
-      <c r="J116" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="18" customHeight="1">
-      <c r="A117" s="136" t="s">
-        <v>5</v>
-      </c>
-      <c r="B117" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C117" s="137"/>
-      <c r="D117" s="136"/>
-      <c r="E117" s="137"/>
-      <c r="F117" s="136"/>
-      <c r="G117" s="137"/>
-      <c r="H117" s="136"/>
-      <c r="I117" s="136" t="s">
-        <v>5</v>
-      </c>
-      <c r="J117" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="18" customHeight="1">
-      <c r="A118" s="136" t="s">
-        <v>4</v>
-      </c>
-      <c r="B118" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C118" s="136"/>
-      <c r="D118" s="136"/>
-      <c r="E118" s="137"/>
-      <c r="F118" s="136"/>
-      <c r="G118" s="137"/>
-      <c r="H118" s="136"/>
-      <c r="I118" s="136" t="s">
-        <v>4</v>
-      </c>
-      <c r="J118" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="18" customHeight="1">
-      <c r="A119" s="136" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C119" s="136"/>
-      <c r="D119" s="136"/>
-      <c r="E119" s="136"/>
-      <c r="F119" s="136"/>
-      <c r="G119" s="136"/>
-      <c r="H119" s="136"/>
-      <c r="I119" s="136" t="s">
-        <v>3</v>
-      </c>
-      <c r="J119" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" ht="18" customHeight="1">
-      <c r="A120" s="136" t="s">
-        <v>2</v>
-      </c>
-      <c r="B120" s="136" t="s">
-        <v>331</v>
-      </c>
-      <c r="C120" s="137"/>
-      <c r="D120" s="136"/>
-      <c r="E120" s="137"/>
-      <c r="F120" s="136"/>
-      <c r="G120" s="137"/>
-      <c r="H120" s="136"/>
-      <c r="I120" s="136" t="s">
-        <v>2</v>
-      </c>
-      <c r="J120" s="136" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A121" s="138" t="s">
-        <v>1</v>
-      </c>
-      <c r="B121" s="138" t="s">
-        <v>331</v>
-      </c>
-      <c r="C121" s="138"/>
-      <c r="D121" s="138"/>
-      <c r="E121" s="139"/>
-      <c r="F121" s="138"/>
-      <c r="G121" s="139"/>
-      <c r="H121" s="138"/>
-      <c r="I121" s="138" t="s">
-        <v>1</v>
-      </c>
-      <c r="J121" s="138" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="18" customHeight="1">
-      <c r="A122" s="140" t="s">
-        <v>24</v>
-      </c>
-      <c r="B122" s="140" t="s">
-        <v>332</v>
-      </c>
-      <c r="C122" s="140"/>
-      <c r="D122" s="140"/>
-      <c r="E122" s="141"/>
-      <c r="F122" s="140"/>
-      <c r="G122" s="141"/>
-      <c r="H122" s="140"/>
-      <c r="I122" s="140" t="s">
-        <v>24</v>
-      </c>
-      <c r="J122" s="140" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" ht="18" customHeight="1">
-      <c r="A123" s="143" t="s">
-        <v>23</v>
-      </c>
-      <c r="B123" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C123" s="142"/>
-      <c r="D123" s="143"/>
-      <c r="E123" s="143"/>
-      <c r="F123" s="143"/>
-      <c r="G123" s="143"/>
-      <c r="H123" s="143"/>
-      <c r="I123" s="143" t="s">
-        <v>23</v>
-      </c>
-      <c r="J123" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" ht="18" customHeight="1">
-      <c r="A124" s="143" t="s">
-        <v>22</v>
-      </c>
-      <c r="B124" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C124" s="143"/>
-      <c r="D124" s="143"/>
-      <c r="E124" s="143"/>
-      <c r="F124" s="143"/>
-      <c r="G124" s="142"/>
-      <c r="H124" s="143"/>
-      <c r="I124" s="143" t="s">
-        <v>22</v>
-      </c>
-      <c r="J124" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="18" customHeight="1">
-      <c r="A125" s="143" t="s">
-        <v>21</v>
-      </c>
-      <c r="B125" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C125" s="143"/>
-      <c r="D125" s="143"/>
-      <c r="E125" s="142"/>
-      <c r="F125" s="143"/>
-      <c r="G125" s="142"/>
-      <c r="H125" s="143"/>
-      <c r="I125" s="143" t="s">
-        <v>21</v>
-      </c>
-      <c r="J125" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="18" customHeight="1">
-      <c r="A126" s="143" t="s">
-        <v>20</v>
-      </c>
-      <c r="B126" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C126" s="143"/>
-      <c r="D126" s="143"/>
-      <c r="E126" s="143"/>
-      <c r="F126" s="143"/>
-      <c r="G126" s="143"/>
-      <c r="H126" s="143"/>
-      <c r="I126" s="143" t="s">
-        <v>20</v>
-      </c>
-      <c r="J126" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="18" customHeight="1">
-      <c r="A127" s="143" t="s">
-        <v>19</v>
-      </c>
-      <c r="B127" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C127" s="142"/>
-      <c r="D127" s="143"/>
-      <c r="E127" s="142"/>
-      <c r="F127" s="143"/>
-      <c r="G127" s="142"/>
-      <c r="H127" s="143"/>
-      <c r="I127" s="143" t="s">
-        <v>19</v>
-      </c>
-      <c r="J127" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" ht="18" customHeight="1">
-      <c r="A128" s="143" t="s">
-        <v>18</v>
-      </c>
-      <c r="B128" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C128" s="143"/>
-      <c r="D128" s="143"/>
-      <c r="E128" s="142"/>
-      <c r="F128" s="143"/>
-      <c r="G128" s="142"/>
-      <c r="H128" s="143"/>
-      <c r="I128" s="143" t="s">
-        <v>18</v>
-      </c>
-      <c r="J128" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" ht="18" customHeight="1">
-      <c r="A129" s="143" t="s">
-        <v>17</v>
-      </c>
-      <c r="B129" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C129" s="143"/>
-      <c r="D129" s="143"/>
-      <c r="E129" s="142"/>
-      <c r="F129" s="143"/>
-      <c r="G129" s="143"/>
-      <c r="H129" s="143"/>
-      <c r="I129" s="143" t="s">
-        <v>17</v>
-      </c>
-      <c r="J129" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" ht="18" customHeight="1">
-      <c r="A130" s="143" t="s">
-        <v>16</v>
-      </c>
-      <c r="B130" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C130" s="142"/>
-      <c r="D130" s="143"/>
-      <c r="E130" s="142"/>
-      <c r="F130" s="143"/>
-      <c r="G130" s="142"/>
-      <c r="H130" s="143"/>
-      <c r="I130" s="143" t="s">
-        <v>16</v>
-      </c>
-      <c r="J130" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="18" customHeight="1">
-      <c r="A131" s="143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C131" s="143"/>
-      <c r="D131" s="143"/>
-      <c r="E131" s="143"/>
-      <c r="F131" s="143"/>
-      <c r="G131" s="142"/>
-      <c r="H131" s="143"/>
-      <c r="I131" s="143" t="s">
-        <v>15</v>
-      </c>
-      <c r="J131" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="18" customHeight="1">
-      <c r="A132" s="143" t="s">
-        <v>14</v>
-      </c>
-      <c r="B132" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C132" s="143"/>
-      <c r="D132" s="143"/>
-      <c r="E132" s="142"/>
-      <c r="F132" s="143"/>
-      <c r="G132" s="143"/>
-      <c r="H132" s="143"/>
-      <c r="I132" s="143" t="s">
-        <v>14</v>
-      </c>
-      <c r="J132" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="18" customHeight="1">
-      <c r="A133" s="143" t="s">
-        <v>13</v>
-      </c>
-      <c r="B133" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C133" s="142"/>
-      <c r="D133" s="143"/>
-      <c r="E133" s="142"/>
-      <c r="F133" s="143"/>
-      <c r="G133" s="142"/>
-      <c r="H133" s="143"/>
-      <c r="I133" s="143" t="s">
-        <v>13</v>
-      </c>
-      <c r="J133" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="18" customHeight="1">
-      <c r="A134" s="143" t="s">
-        <v>12</v>
-      </c>
-      <c r="B134" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C134" s="143"/>
-      <c r="D134" s="143"/>
-      <c r="E134" s="142"/>
-      <c r="F134" s="143"/>
-      <c r="G134" s="142"/>
-      <c r="H134" s="143"/>
-      <c r="I134" s="143" t="s">
-        <v>12</v>
-      </c>
-      <c r="J134" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="18" customHeight="1">
-      <c r="A135" s="143" t="s">
-        <v>11</v>
-      </c>
-      <c r="B135" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C135" s="143"/>
-      <c r="D135" s="143"/>
-      <c r="E135" s="143"/>
-      <c r="F135" s="143"/>
-      <c r="G135" s="143"/>
-      <c r="H135" s="143"/>
-      <c r="I135" s="143" t="s">
-        <v>11</v>
-      </c>
-      <c r="J135" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="18" customHeight="1">
-      <c r="A136" s="143" t="s">
-        <v>10</v>
-      </c>
-      <c r="B136" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C136" s="142"/>
-      <c r="D136" s="143"/>
-      <c r="E136" s="142"/>
-      <c r="F136" s="143"/>
-      <c r="G136" s="142"/>
-      <c r="H136" s="143"/>
-      <c r="I136" s="143" t="s">
-        <v>10</v>
-      </c>
-      <c r="J136" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="18" customHeight="1">
-      <c r="A137" s="143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B137" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C137" s="143"/>
-      <c r="D137" s="143"/>
-      <c r="E137" s="142"/>
-      <c r="F137" s="143"/>
-      <c r="G137" s="142"/>
-      <c r="H137" s="143"/>
-      <c r="I137" s="143" t="s">
-        <v>9</v>
-      </c>
-      <c r="J137" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="18" customHeight="1">
-      <c r="A138" s="143" t="s">
-        <v>8</v>
-      </c>
-      <c r="B138" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C138" s="143"/>
-      <c r="D138" s="143"/>
-      <c r="E138" s="143"/>
-      <c r="F138" s="143"/>
-      <c r="G138" s="143"/>
-      <c r="H138" s="143"/>
-      <c r="I138" s="143">
-        <v>16</v>
-      </c>
-      <c r="J138" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="18" customHeight="1">
-      <c r="A139" s="143" t="s">
-        <v>7</v>
-      </c>
-      <c r="B139" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C139" s="142"/>
-      <c r="D139" s="143"/>
-      <c r="E139" s="142"/>
-      <c r="F139" s="143"/>
-      <c r="G139" s="142"/>
-      <c r="H139" s="143"/>
-      <c r="I139" s="143" t="s">
-        <v>7</v>
-      </c>
-      <c r="J139" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="18" customHeight="1">
-      <c r="A140" s="143" t="s">
-        <v>6</v>
-      </c>
-      <c r="B140" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C140" s="143"/>
-      <c r="D140" s="143"/>
-      <c r="E140" s="143"/>
-      <c r="F140" s="143"/>
-      <c r="G140" s="142"/>
-      <c r="H140" s="143"/>
-      <c r="I140" s="143" t="s">
-        <v>6</v>
-      </c>
-      <c r="J140" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="18" customHeight="1">
-      <c r="A141" s="143" t="s">
-        <v>5</v>
-      </c>
-      <c r="B141" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C141" s="143"/>
-      <c r="D141" s="143"/>
-      <c r="E141" s="142"/>
-      <c r="F141" s="143"/>
-      <c r="G141" s="143"/>
-      <c r="H141" s="143"/>
-      <c r="I141" s="143" t="s">
-        <v>5</v>
-      </c>
-      <c r="J141" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="18" customHeight="1">
-      <c r="A142" s="143" t="s">
-        <v>4</v>
-      </c>
-      <c r="B142" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C142" s="143"/>
-      <c r="D142" s="143"/>
-      <c r="E142" s="142"/>
-      <c r="F142" s="143"/>
-      <c r="G142" s="142"/>
-      <c r="H142" s="143"/>
-      <c r="I142" s="143" t="s">
-        <v>4</v>
-      </c>
-      <c r="J142" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="18" customHeight="1">
-      <c r="A143" s="143" t="s">
-        <v>3</v>
-      </c>
-      <c r="B143" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C143" s="142"/>
-      <c r="D143" s="143"/>
-      <c r="E143" s="142"/>
-      <c r="F143" s="143"/>
-      <c r="G143" s="142"/>
-      <c r="H143" s="143"/>
-      <c r="I143" s="143" t="s">
-        <v>3</v>
-      </c>
-      <c r="J143" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="18" customHeight="1">
-      <c r="A144" s="143" t="s">
-        <v>2</v>
-      </c>
-      <c r="B144" s="143" t="s">
-        <v>332</v>
-      </c>
-      <c r="C144" s="143"/>
-      <c r="D144" s="143"/>
-      <c r="E144" s="143"/>
-      <c r="F144" s="143"/>
-      <c r="G144" s="142"/>
-      <c r="H144" s="143"/>
-      <c r="I144" s="143" t="s">
-        <v>2</v>
-      </c>
-      <c r="J144" s="143" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A145" s="144" t="s">
-        <v>1</v>
-      </c>
-      <c r="B145" s="144" t="s">
-        <v>332</v>
-      </c>
-      <c r="C145" s="144"/>
-      <c r="D145" s="144"/>
-      <c r="E145" s="152"/>
-      <c r="F145" s="144"/>
-      <c r="G145" s="144"/>
-      <c r="H145" s="144"/>
-      <c r="I145" s="144" t="s">
-        <v>1</v>
-      </c>
-      <c r="J145" s="144" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="18" customHeight="1">
-      <c r="A146" s="145" t="s">
-        <v>24</v>
-      </c>
-      <c r="B146" s="145" t="s">
-        <v>333</v>
-      </c>
-      <c r="C146" s="145"/>
-      <c r="D146" s="145"/>
-      <c r="E146" s="153"/>
-      <c r="F146" s="145"/>
-      <c r="G146" s="145"/>
-      <c r="H146" s="145"/>
-      <c r="I146" s="145" t="s">
-        <v>24</v>
-      </c>
-      <c r="J146" s="145" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="18" customHeight="1">
-      <c r="A147" s="146" t="s">
-        <v>23</v>
-      </c>
-      <c r="B147" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C147" s="146"/>
-      <c r="D147" s="146"/>
-      <c r="E147" s="146"/>
-      <c r="F147" s="146"/>
-      <c r="G147" s="147"/>
-      <c r="H147" s="146"/>
-      <c r="I147" s="146" t="s">
-        <v>23</v>
-      </c>
-      <c r="J147" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="18" customHeight="1">
-      <c r="A148" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="B148" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C148" s="146"/>
-      <c r="D148" s="146"/>
-      <c r="E148" s="147"/>
-      <c r="F148" s="146"/>
-      <c r="G148" s="147"/>
-      <c r="H148" s="146"/>
-      <c r="I148" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="J148" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="18" customHeight="1">
-      <c r="A149" s="146" t="s">
-        <v>21</v>
-      </c>
-      <c r="B149" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C149" s="147"/>
-      <c r="D149" s="146"/>
-      <c r="E149" s="147"/>
-      <c r="F149" s="146"/>
-      <c r="G149" s="146"/>
-      <c r="H149" s="146"/>
-      <c r="I149" s="146" t="s">
-        <v>21</v>
-      </c>
-      <c r="J149" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="18" customHeight="1">
-      <c r="A150" s="146" t="s">
-        <v>20</v>
-      </c>
-      <c r="B150" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C150" s="146"/>
-      <c r="D150" s="146"/>
-      <c r="E150" s="146"/>
-      <c r="F150" s="146"/>
-      <c r="G150" s="147"/>
-      <c r="H150" s="146"/>
-      <c r="I150" s="146" t="s">
-        <v>20</v>
-      </c>
-      <c r="J150" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="18" customHeight="1">
-      <c r="A151" s="146" t="s">
-        <v>19</v>
-      </c>
-      <c r="B151" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C151" s="146"/>
-      <c r="D151" s="146"/>
-      <c r="E151" s="147"/>
-      <c r="F151" s="146"/>
-      <c r="G151" s="147"/>
-      <c r="H151" s="146"/>
-      <c r="I151" s="146" t="s">
-        <v>19</v>
-      </c>
-      <c r="J151" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="18" customHeight="1">
-      <c r="A152" s="146" t="s">
-        <v>18</v>
-      </c>
-      <c r="B152" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C152" s="146"/>
-      <c r="D152" s="146"/>
-      <c r="E152" s="147"/>
-      <c r="F152" s="146"/>
-      <c r="G152" s="146"/>
-      <c r="H152" s="146"/>
-      <c r="I152" s="146" t="s">
-        <v>18</v>
-      </c>
-      <c r="J152" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="18" customHeight="1">
-      <c r="A153" s="146" t="s">
-        <v>17</v>
-      </c>
-      <c r="B153" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C153" s="147"/>
-      <c r="D153" s="146"/>
-      <c r="E153" s="146"/>
-      <c r="F153" s="146"/>
-      <c r="G153" s="147"/>
-      <c r="H153" s="146"/>
-      <c r="I153" s="146" t="s">
-        <v>17</v>
-      </c>
-      <c r="J153" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="18" customHeight="1">
-      <c r="A154" s="146" t="s">
-        <v>16</v>
-      </c>
-      <c r="B154" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C154" s="146"/>
-      <c r="D154" s="146"/>
-      <c r="E154" s="147"/>
-      <c r="F154" s="146"/>
-      <c r="G154" s="147"/>
-      <c r="H154" s="146"/>
-      <c r="I154" s="146" t="s">
-        <v>16</v>
-      </c>
-      <c r="J154" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="18" customHeight="1">
-      <c r="A155" s="146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C155" s="146"/>
-      <c r="D155" s="146"/>
-      <c r="E155" s="147"/>
-      <c r="F155" s="146"/>
-      <c r="G155" s="146"/>
-      <c r="H155" s="146"/>
-      <c r="I155" s="146" t="s">
-        <v>15</v>
-      </c>
-      <c r="J155" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="18" customHeight="1">
-      <c r="A156" s="146" t="s">
-        <v>14</v>
-      </c>
-      <c r="B156" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C156" s="147"/>
-      <c r="D156" s="146"/>
-      <c r="E156" s="146"/>
-      <c r="F156" s="146"/>
-      <c r="G156" s="147"/>
-      <c r="H156" s="146"/>
-      <c r="I156" s="146" t="s">
-        <v>14</v>
-      </c>
-      <c r="J156" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="18" customHeight="1">
-      <c r="A157" s="146" t="s">
-        <v>13</v>
-      </c>
-      <c r="B157" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C157" s="146"/>
-      <c r="D157" s="146"/>
-      <c r="E157" s="146"/>
-      <c r="F157" s="146"/>
-      <c r="G157" s="147"/>
-      <c r="H157" s="146"/>
-      <c r="I157" s="146" t="s">
-        <v>13</v>
-      </c>
-      <c r="J157" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="18" customHeight="1">
-      <c r="A158" s="146" t="s">
-        <v>12</v>
-      </c>
-      <c r="B158" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C158" s="146"/>
-      <c r="D158" s="146"/>
-      <c r="E158" s="147"/>
-      <c r="F158" s="146"/>
-      <c r="G158" s="147"/>
-      <c r="H158" s="146"/>
-      <c r="I158" s="146" t="s">
-        <v>12</v>
-      </c>
-      <c r="J158" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="18" customHeight="1">
-      <c r="A159" s="146" t="s">
-        <v>11</v>
-      </c>
-      <c r="B159" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C159" s="147"/>
-      <c r="D159" s="146"/>
-      <c r="E159" s="146"/>
-      <c r="F159" s="146"/>
-      <c r="G159" s="146"/>
-      <c r="H159" s="146"/>
-      <c r="I159" s="146" t="s">
-        <v>11</v>
-      </c>
-      <c r="J159" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="18" customHeight="1">
-      <c r="A160" s="146" t="s">
-        <v>10</v>
-      </c>
-      <c r="B160" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C160" s="146"/>
-      <c r="D160" s="146"/>
-      <c r="E160" s="147"/>
-      <c r="F160" s="146"/>
-      <c r="G160" s="147"/>
-      <c r="H160" s="146"/>
-      <c r="I160" s="146" t="s">
-        <v>10</v>
-      </c>
-      <c r="J160" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10" ht="18" customHeight="1">
-      <c r="A161" s="146" t="s">
-        <v>9</v>
-      </c>
-      <c r="B161" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C161" s="146"/>
-      <c r="D161" s="146"/>
-      <c r="E161" s="146"/>
-      <c r="F161" s="146"/>
-      <c r="G161" s="147"/>
-      <c r="H161" s="146"/>
-      <c r="I161" s="146" t="s">
-        <v>9</v>
-      </c>
-      <c r="J161" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="18" customHeight="1">
-      <c r="A162" s="146" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C162" s="147"/>
-      <c r="D162" s="146"/>
-      <c r="E162" s="146"/>
-      <c r="F162" s="146"/>
-      <c r="G162" s="146"/>
-      <c r="H162" s="146"/>
-      <c r="I162" s="146" t="s">
-        <v>8</v>
-      </c>
-      <c r="J162" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="18" customHeight="1">
-      <c r="A163" s="146" t="s">
-        <v>7</v>
-      </c>
-      <c r="B163" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C163" s="146"/>
-      <c r="D163" s="146"/>
-      <c r="E163" s="147"/>
-      <c r="F163" s="146"/>
-      <c r="G163" s="147"/>
-      <c r="H163" s="154"/>
-      <c r="I163" s="146" t="s">
-        <v>7</v>
-      </c>
-      <c r="J163" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10" ht="18" customHeight="1">
-      <c r="A164" s="146" t="s">
-        <v>6</v>
-      </c>
-      <c r="B164" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C164" s="146"/>
-      <c r="D164" s="146"/>
-      <c r="E164" s="147"/>
-      <c r="F164" s="146"/>
-      <c r="G164" s="146"/>
-      <c r="H164" s="146"/>
-      <c r="I164" s="146" t="s">
-        <v>6</v>
-      </c>
-      <c r="J164" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10" ht="18" customHeight="1">
-      <c r="A165" s="146" t="s">
-        <v>5</v>
-      </c>
-      <c r="B165" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C165" s="146"/>
-      <c r="D165" s="146"/>
-      <c r="E165" s="146"/>
-      <c r="F165" s="146"/>
-      <c r="G165" s="147"/>
-      <c r="H165" s="146"/>
-      <c r="I165" s="146" t="s">
-        <v>5</v>
-      </c>
-      <c r="J165" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10" ht="18" customHeight="1">
-      <c r="A166" s="146" t="s">
-        <v>4</v>
-      </c>
-      <c r="B166" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C166" s="147"/>
-      <c r="D166" s="146"/>
-      <c r="E166" s="147"/>
-      <c r="F166" s="146"/>
-      <c r="G166" s="147"/>
-      <c r="H166" s="146"/>
-      <c r="I166" s="146" t="s">
-        <v>4</v>
-      </c>
-      <c r="J166" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10" ht="18" customHeight="1">
-      <c r="A167" s="146" t="s">
-        <v>3</v>
-      </c>
-      <c r="B167" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C167" s="146"/>
-      <c r="D167" s="146"/>
-      <c r="E167" s="147"/>
-      <c r="F167" s="154"/>
-      <c r="G167" s="146"/>
-      <c r="H167" s="146"/>
-      <c r="I167" s="146" t="s">
-        <v>3</v>
-      </c>
-      <c r="J167" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10" ht="18" customHeight="1">
-      <c r="A168" s="146" t="s">
-        <v>2</v>
-      </c>
-      <c r="B168" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C168" s="146"/>
-      <c r="D168" s="146"/>
-      <c r="E168" s="146"/>
-      <c r="F168" s="146"/>
-      <c r="G168" s="147"/>
-      <c r="H168" s="146"/>
-      <c r="I168" s="146" t="s">
-        <v>2</v>
-      </c>
-      <c r="J168" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10" ht="18" customHeight="1">
-      <c r="A169" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="B169" s="146" t="s">
-        <v>333</v>
-      </c>
-      <c r="C169" s="146"/>
-      <c r="D169" s="146"/>
-      <c r="E169" s="147"/>
-      <c r="F169" s="146"/>
-      <c r="G169" s="147"/>
-      <c r="H169" s="189"/>
-      <c r="I169" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="J169" s="146" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" ht="18" customHeight="1">
-      <c r="B170" s="148"/>
-    </row>
-    <row r="171" spans="1:10" ht="18" customHeight="1">
-      <c r="B171" s="148"/>
-    </row>
-    <row r="172" spans="1:10" ht="18" customHeight="1">
-      <c r="B172" s="148"/>
-    </row>
-    <row r="173" spans="1:10" ht="18" customHeight="1">
-      <c r="B173" s="148"/>
-    </row>
-    <row r="174" spans="1:10" ht="18" customHeight="1">
-      <c r="B174" s="148"/>
-    </row>
-    <row r="175" spans="1:10" ht="18" customHeight="1">
-      <c r="B175" s="148"/>
-    </row>
-    <row r="176" spans="1:10" ht="18" customHeight="1">
-      <c r="B176" s="148"/>
-    </row>
-    <row r="177" spans="2:2" ht="18" customHeight="1">
-      <c r="B177" s="148"/>
-    </row>
-    <row r="178" spans="2:2" ht="18" customHeight="1">
-      <c r="B178" s="148"/>
-    </row>
-    <row r="179" spans="2:2" ht="18" customHeight="1">
-      <c r="B179" s="148"/>
-    </row>
-    <row r="180" spans="2:2" ht="18" customHeight="1">
-      <c r="B180" s="148"/>
-    </row>
-    <row r="181" spans="2:2" ht="18" customHeight="1">
-      <c r="B181" s="148"/>
-    </row>
-    <row r="182" spans="2:2" ht="18" customHeight="1">
-      <c r="B182" s="148"/>
-    </row>
-    <row r="183" spans="2:2" ht="18" customHeight="1">
-      <c r="B183" s="148"/>
-    </row>
-    <row r="184" spans="2:2" ht="18" customHeight="1">
-      <c r="B184" s="148"/>
-    </row>
-    <row r="185" spans="2:2" ht="18" customHeight="1">
-      <c r="B185" s="148"/>
-    </row>
-    <row r="186" spans="2:2" ht="18" customHeight="1">
-      <c r="B186" s="148"/>
-    </row>
-    <row r="187" spans="2:2" ht="18" customHeight="1">
-      <c r="B187" s="148"/>
-    </row>
-    <row r="188" spans="2:2" ht="18" customHeight="1">
-      <c r="B188" s="148"/>
-    </row>
-    <row r="189" spans="2:2" ht="18" customHeight="1">
-      <c r="B189" s="148"/>
-    </row>
-    <row r="190" spans="2:2" ht="18" customHeight="1">
-      <c r="B190" s="148"/>
-    </row>
-    <row r="191" spans="2:2" ht="18" customHeight="1">
-      <c r="B191" s="148"/>
-    </row>
-    <row r="192" spans="2:2" ht="18" customHeight="1">
-      <c r="B192" s="148"/>
-    </row>
-    <row r="193" spans="2:2" ht="18" customHeight="1">
-      <c r="B193" s="148"/>
-    </row>
-    <row r="194" spans="2:2" ht="18" customHeight="1">
-      <c r="B194" s="148"/>
-    </row>
-    <row r="195" spans="2:2" ht="18" customHeight="1">
-      <c r="B195" s="148"/>
-    </row>
-    <row r="196" spans="2:2" ht="18" customHeight="1">
-      <c r="B196" s="148"/>
-    </row>
-    <row r="197" spans="2:2" ht="18" customHeight="1">
-      <c r="B197" s="148"/>
-    </row>
-    <row r="198" spans="2:2" ht="18" customHeight="1">
-      <c r="B198" s="148"/>
-    </row>
-    <row r="199" spans="2:2" ht="18" customHeight="1">
-      <c r="B199" s="148"/>
-    </row>
-    <row r="200" spans="2:2" ht="18" customHeight="1">
-      <c r="B200" s="148"/>
-    </row>
-    <row r="201" spans="2:2" ht="18" customHeight="1">
-      <c r="B201" s="148"/>
-    </row>
-    <row r="202" spans="2:2" ht="18" customHeight="1">
-      <c r="B202" s="148"/>
-    </row>
-    <row r="203" spans="2:2" ht="18" customHeight="1">
-      <c r="B203" s="148"/>
-    </row>
-    <row r="204" spans="2:2" ht="18" customHeight="1">
-      <c r="B204" s="148"/>
-    </row>
-    <row r="205" spans="2:2" ht="18" customHeight="1">
-      <c r="B205" s="148"/>
-    </row>
-    <row r="206" spans="2:2" ht="18" customHeight="1">
-      <c r="B206" s="148"/>
-    </row>
-    <row r="207" spans="2:2" ht="18" customHeight="1">
-      <c r="B207" s="148"/>
-    </row>
-    <row r="208" spans="2:2" ht="18" customHeight="1">
-      <c r="B208" s="148"/>
-    </row>
-    <row r="209" spans="2:2" ht="18" customHeight="1">
-      <c r="B209" s="148"/>
-    </row>
-    <row r="210" spans="2:2" ht="18" customHeight="1">
-      <c r="B210" s="148"/>
-    </row>
-    <row r="211" spans="2:2" ht="18" customHeight="1">
-      <c r="B211" s="148"/>
-    </row>
-    <row r="212" spans="2:2" ht="18" customHeight="1">
-      <c r="B212" s="148"/>
-    </row>
-    <row r="213" spans="2:2" ht="18" customHeight="1">
-      <c r="B213" s="148"/>
-    </row>
-    <row r="214" spans="2:2" ht="18" customHeight="1">
-      <c r="B214" s="148"/>
-    </row>
-    <row r="215" spans="2:2" ht="18" customHeight="1">
-      <c r="B215" s="148"/>
-    </row>
-    <row r="216" spans="2:2" ht="18" customHeight="1">
-      <c r="B216" s="148"/>
-    </row>
-    <row r="217" spans="2:2" ht="18" customHeight="1">
-      <c r="B217" s="148"/>
-    </row>
-    <row r="218" spans="2:2" ht="18" customHeight="1">
-      <c r="B218" s="148"/>
-    </row>
-    <row r="219" spans="2:2" ht="18" customHeight="1">
-      <c r="B219" s="148"/>
-    </row>
-    <row r="220" spans="2:2" ht="18" customHeight="1">
-      <c r="B220" s="148"/>
-    </row>
-    <row r="221" spans="2:2" ht="18" customHeight="1">
-      <c r="B221" s="148"/>
-    </row>
-    <row r="222" spans="2:2" ht="18" customHeight="1">
-      <c r="B222" s="148"/>
-    </row>
-    <row r="223" spans="2:2" ht="18" customHeight="1">
-      <c r="B223" s="148"/>
-    </row>
-    <row r="224" spans="2:2" ht="18" customHeight="1">
-      <c r="B224" s="148"/>
-    </row>
-    <row r="225" spans="2:2" ht="18" customHeight="1">
-      <c r="B225" s="148"/>
-    </row>
-    <row r="226" spans="2:2" ht="18" customHeight="1">
-      <c r="B226" s="148"/>
-    </row>
-    <row r="227" spans="2:2" ht="18" customHeight="1">
-      <c r="B227" s="148"/>
-    </row>
-    <row r="228" spans="2:2" ht="18" customHeight="1">
-      <c r="B228" s="148"/>
-    </row>
-    <row r="229" spans="2:2" ht="18" customHeight="1">
-      <c r="B229" s="148"/>
-    </row>
-    <row r="230" spans="2:2" ht="18" customHeight="1">
-      <c r="B230" s="148"/>
-    </row>
-    <row r="231" spans="2:2" ht="18" customHeight="1">
-      <c r="B231" s="148"/>
-    </row>
-    <row r="232" spans="2:2" ht="18" customHeight="1">
-      <c r="B232" s="148"/>
-    </row>
-    <row r="233" spans="2:2" ht="18" customHeight="1">
-      <c r="B233" s="148"/>
-    </row>
-    <row r="234" spans="2:2" ht="18" customHeight="1">
-      <c r="B234" s="148"/>
-    </row>
-    <row r="235" spans="2:2" ht="18" customHeight="1">
-      <c r="B235" s="148"/>
-    </row>
-    <row r="236" spans="2:2" ht="18" customHeight="1">
-      <c r="B236" s="148"/>
-    </row>
-    <row r="237" spans="2:2" ht="18" customHeight="1">
-      <c r="B237" s="148"/>
-    </row>
-    <row r="238" spans="2:2" ht="18" customHeight="1">
-      <c r="B238" s="148"/>
-    </row>
-    <row r="239" spans="2:2" ht="18" customHeight="1">
-      <c r="B239" s="148"/>
-    </row>
-    <row r="240" spans="2:2" ht="18" customHeight="1">
-      <c r="B240" s="148"/>
-    </row>
-    <row r="241" spans="2:2" ht="18" customHeight="1">
-      <c r="B241" s="148"/>
-    </row>
-    <row r="242" spans="2:2" ht="18" customHeight="1">
-      <c r="B242" s="148"/>
-    </row>
-    <row r="243" spans="2:2" ht="18" customHeight="1">
-      <c r="B243" s="148"/>
-    </row>
-    <row r="244" spans="2:2" ht="18" customHeight="1">
-      <c r="B244" s="148"/>
-    </row>
-    <row r="245" spans="2:2" ht="18" customHeight="1">
-      <c r="B245" s="148"/>
-    </row>
-    <row r="246" spans="2:2" ht="18" customHeight="1">
-      <c r="B246" s="148"/>
-    </row>
-    <row r="247" spans="2:2" ht="18" customHeight="1">
-      <c r="B247" s="148"/>
-    </row>
-    <row r="248" spans="2:2" ht="18" customHeight="1">
-      <c r="B248" s="148"/>
-    </row>
-    <row r="249" spans="2:2" ht="18" customHeight="1">
-      <c r="B249" s="148"/>
-    </row>
-    <row r="250" spans="2:2" ht="18" customHeight="1">
-      <c r="B250" s="148"/>
-    </row>
-    <row r="251" spans="2:2" ht="18" customHeight="1">
-      <c r="B251" s="148"/>
-    </row>
-    <row r="252" spans="2:2" ht="18" customHeight="1">
-      <c r="B252" s="148"/>
-    </row>
-    <row r="253" spans="2:2" ht="18" customHeight="1">
-      <c r="B253" s="148"/>
-    </row>
-    <row r="254" spans="2:2" ht="18" customHeight="1">
-      <c r="B254" s="148"/>
-    </row>
-    <row r="255" spans="2:2" ht="18" customHeight="1">
-      <c r="B255" s="148"/>
-    </row>
-    <row r="256" spans="2:2" ht="18" customHeight="1">
-      <c r="B256" s="148"/>
-    </row>
-    <row r="257" spans="2:2" ht="18" customHeight="1">
-      <c r="B257" s="148"/>
-    </row>
-    <row r="258" spans="2:2" ht="18" customHeight="1">
-      <c r="B258" s="148"/>
-    </row>
-    <row r="259" spans="2:2" ht="18" customHeight="1">
-      <c r="B259" s="148"/>
-    </row>
-    <row r="260" spans="2:2" ht="18" customHeight="1">
-      <c r="B260" s="148"/>
-    </row>
-    <row r="261" spans="2:2" ht="18" customHeight="1">
-      <c r="B261" s="148"/>
-    </row>
-    <row r="262" spans="2:2" ht="18" customHeight="1">
-      <c r="B262" s="148"/>
-    </row>
-    <row r="263" spans="2:2" ht="18" customHeight="1">
-      <c r="B263" s="148"/>
-    </row>
-    <row r="264" spans="2:2" ht="18" customHeight="1">
-      <c r="B264" s="148"/>
-    </row>
-    <row r="265" spans="2:2" ht="18" customHeight="1">
-      <c r="B265" s="148"/>
-    </row>
-    <row r="266" spans="2:2" ht="18" customHeight="1">
-      <c r="B266" s="148"/>
-    </row>
-    <row r="267" spans="2:2" ht="18" customHeight="1">
-      <c r="B267" s="148"/>
-    </row>
-    <row r="268" spans="2:2" ht="18" customHeight="1">
-      <c r="B268" s="148"/>
-    </row>
-    <row r="269" spans="2:2" ht="18" customHeight="1">
-      <c r="B269" s="148"/>
-    </row>
-    <row r="270" spans="2:2" ht="18" customHeight="1">
-      <c r="B270" s="148"/>
-    </row>
-    <row r="271" spans="2:2" ht="18" customHeight="1">
-      <c r="B271" s="148"/>
-    </row>
-    <row r="272" spans="2:2" ht="18" customHeight="1">
-      <c r="B272" s="148"/>
-    </row>
-    <row r="273" spans="2:2" ht="18" customHeight="1">
-      <c r="B273" s="148"/>
-    </row>
-    <row r="274" spans="2:2" ht="18" customHeight="1">
-      <c r="B274" s="148"/>
-    </row>
-    <row r="275" spans="2:2" ht="18" customHeight="1">
-      <c r="B275" s="148"/>
-    </row>
-    <row r="276" spans="2:2" ht="18" customHeight="1">
-      <c r="B276" s="148"/>
-    </row>
-    <row r="277" spans="2:2" ht="18" customHeight="1">
-      <c r="B277" s="148"/>
-    </row>
-    <row r="278" spans="2:2" ht="18" customHeight="1">
-      <c r="B278" s="148"/>
-    </row>
-    <row r="279" spans="2:2" ht="18" customHeight="1">
-      <c r="B279" s="148"/>
-    </row>
-    <row r="280" spans="2:2" ht="18" customHeight="1">
-      <c r="B280" s="148"/>
-    </row>
-    <row r="281" spans="2:2" ht="18" customHeight="1">
-      <c r="B281" s="148"/>
-    </row>
-    <row r="282" spans="2:2" ht="18" customHeight="1">
-      <c r="B282" s="148"/>
-    </row>
-    <row r="283" spans="2:2" ht="18" customHeight="1">
-      <c r="B283" s="148"/>
-    </row>
-    <row r="284" spans="2:2" ht="18" customHeight="1">
-      <c r="B284" s="148"/>
-    </row>
-    <row r="285" spans="2:2" ht="18" customHeight="1">
-      <c r="B285" s="148"/>
-    </row>
-    <row r="286" spans="2:2" ht="18" customHeight="1">
-      <c r="B286" s="148"/>
-    </row>
-    <row r="287" spans="2:2" ht="18" customHeight="1">
-      <c r="B287" s="148"/>
-    </row>
-    <row r="288" spans="2:2" ht="18" customHeight="1">
-      <c r="B288" s="148"/>
-    </row>
-    <row r="289" spans="2:2" ht="18" customHeight="1">
-      <c r="B289" s="148"/>
-    </row>
-    <row r="290" spans="2:2" ht="18" customHeight="1">
-      <c r="B290" s="148"/>
-    </row>
-    <row r="291" spans="2:2" ht="18" customHeight="1">
-      <c r="B291" s="148"/>
-    </row>
-    <row r="292" spans="2:2" ht="18" customHeight="1">
-      <c r="B292" s="148"/>
-    </row>
-    <row r="293" spans="2:2" ht="18" customHeight="1">
-      <c r="B293" s="148"/>
-    </row>
-    <row r="294" spans="2:2" ht="18" customHeight="1">
-      <c r="B294" s="148"/>
-    </row>
-    <row r="295" spans="2:2" ht="18" customHeight="1">
-      <c r="B295" s="148"/>
-    </row>
-    <row r="296" spans="2:2" ht="18" customHeight="1">
-      <c r="B296" s="148"/>
-    </row>
-    <row r="297" spans="2:2" ht="18" customHeight="1">
-      <c r="B297" s="148"/>
-    </row>
-    <row r="298" spans="2:2" ht="18" customHeight="1">
-      <c r="B298" s="148"/>
-    </row>
-    <row r="299" spans="2:2" ht="18" customHeight="1">
-      <c r="B299" s="148"/>
-    </row>
-    <row r="300" spans="2:2" ht="18" customHeight="1">
-      <c r="B300" s="148"/>
-    </row>
-    <row r="301" spans="2:2" ht="18" customHeight="1">
-      <c r="B301" s="148"/>
-    </row>
-    <row r="302" spans="2:2" ht="18" customHeight="1">
-      <c r="B302" s="148"/>
-    </row>
-    <row r="303" spans="2:2" ht="18" customHeight="1">
-      <c r="B303" s="148"/>
-    </row>
-    <row r="304" spans="2:2" ht="18" customHeight="1">
-      <c r="B304" s="148"/>
-    </row>
-    <row r="305" spans="2:2" ht="18" customHeight="1">
-      <c r="B305" s="148"/>
-    </row>
-    <row r="306" spans="2:2" ht="18" customHeight="1">
-      <c r="B306" s="148"/>
-    </row>
-    <row r="307" spans="2:2" ht="18" customHeight="1">
-      <c r="B307" s="148"/>
-    </row>
-    <row r="308" spans="2:2" ht="18" customHeight="1">
-      <c r="B308" s="148"/>
-    </row>
-    <row r="309" spans="2:2" ht="18" customHeight="1">
-      <c r="B309" s="148"/>
-    </row>
-    <row r="310" spans="2:2" ht="18" customHeight="1">
-      <c r="B310" s="148"/>
-    </row>
-    <row r="311" spans="2:2" ht="18" customHeight="1">
-      <c r="B311" s="148"/>
-    </row>
-    <row r="312" spans="2:2" ht="18" customHeight="1">
-      <c r="B312" s="148"/>
-    </row>
-    <row r="313" spans="2:2" ht="18" customHeight="1">
-      <c r="B313" s="148"/>
-    </row>
-    <row r="314" spans="2:2" ht="18" customHeight="1">
-      <c r="B314" s="148"/>
-    </row>
-    <row r="315" spans="2:2" ht="18" customHeight="1">
-      <c r="B315" s="148"/>
-    </row>
-    <row r="316" spans="2:2" ht="18" customHeight="1">
-      <c r="B316" s="148"/>
-    </row>
-    <row r="317" spans="2:2" ht="18" customHeight="1">
-      <c r="B317" s="148"/>
-    </row>
-    <row r="318" spans="2:2" ht="18" customHeight="1">
-      <c r="B318" s="148"/>
-    </row>
-    <row r="319" spans="2:2" ht="18" customHeight="1">
-      <c r="B319" s="148"/>
-    </row>
-    <row r="320" spans="2:2" ht="18" customHeight="1">
-      <c r="B320" s="148"/>
-    </row>
-    <row r="321" spans="2:2" ht="18" customHeight="1">
-      <c r="B321" s="148"/>
-    </row>
-    <row r="322" spans="2:2" ht="18" customHeight="1">
-      <c r="B322" s="148"/>
-    </row>
-    <row r="323" spans="2:2" ht="18" customHeight="1">
-      <c r="B323" s="148"/>
-    </row>
-    <row r="324" spans="2:2" ht="18" customHeight="1">
-      <c r="B324" s="148"/>
-    </row>
-    <row r="325" spans="2:2" ht="18" customHeight="1">
-      <c r="B325" s="148"/>
-    </row>
-    <row r="326" spans="2:2" ht="18" customHeight="1">
-      <c r="B326" s="148"/>
-    </row>
-    <row r="327" spans="2:2" ht="18" customHeight="1">
-      <c r="B327" s="148"/>
-    </row>
-    <row r="328" spans="2:2" ht="18" customHeight="1">
-      <c r="B328" s="148"/>
-    </row>
-    <row r="329" spans="2:2" ht="18" customHeight="1">
-      <c r="B329" s="148"/>
-    </row>
-    <row r="330" spans="2:2" ht="18" customHeight="1">
-      <c r="B330" s="148"/>
-    </row>
-    <row r="331" spans="2:2" ht="18" customHeight="1">
-      <c r="B331" s="148"/>
-    </row>
-    <row r="332" spans="2:2" ht="18" customHeight="1">
-      <c r="B332" s="148"/>
-    </row>
-    <row r="333" spans="2:2" ht="18" customHeight="1">
-      <c r="B333" s="148"/>
-    </row>
-    <row r="334" spans="2:2" ht="18" customHeight="1">
-      <c r="B334" s="148"/>
-    </row>
-    <row r="335" spans="2:2" ht="18" customHeight="1">
-      <c r="B335" s="148"/>
-    </row>
-    <row r="336" spans="2:2" ht="18" customHeight="1">
-      <c r="B336" s="148"/>
-    </row>
-    <row r="337" spans="2:2" ht="18" customHeight="1">
-      <c r="B337" s="148"/>
-    </row>
-    <row r="338" spans="2:2" ht="18" customHeight="1">
-      <c r="B338" s="148"/>
-    </row>
-    <row r="339" spans="2:2" ht="18" customHeight="1">
-      <c r="B339" s="148"/>
-    </row>
-    <row r="340" spans="2:2" ht="18" customHeight="1">
-      <c r="B340" s="148"/>
-    </row>
-    <row r="341" spans="2:2" ht="18" customHeight="1">
-      <c r="B341" s="148"/>
-    </row>
-    <row r="342" spans="2:2" ht="18" customHeight="1">
-      <c r="B342" s="148"/>
-    </row>
-    <row r="343" spans="2:2" ht="18" customHeight="1">
-      <c r="B343" s="148"/>
-    </row>
-    <row r="344" spans="2:2" ht="18" customHeight="1">
-      <c r="B344" s="148"/>
-    </row>
-    <row r="345" spans="2:2" ht="18" customHeight="1">
-      <c r="B345" s="148"/>
-    </row>
-    <row r="346" spans="2:2" ht="18" customHeight="1">
-      <c r="B346" s="148"/>
-    </row>
-    <row r="347" spans="2:2" ht="18" customHeight="1">
-      <c r="B347" s="148"/>
-    </row>
-    <row r="348" spans="2:2" ht="18" customHeight="1">
-      <c r="B348" s="148"/>
-    </row>
-    <row r="349" spans="2:2" ht="18" customHeight="1">
-      <c r="B349" s="148"/>
-    </row>
-    <row r="350" spans="2:2" ht="18" customHeight="1">
-      <c r="B350" s="148"/>
-    </row>
-    <row r="351" spans="2:2" ht="18" customHeight="1">
-      <c r="B351" s="148"/>
-    </row>
-    <row r="352" spans="2:2" ht="18" customHeight="1">
-      <c r="B352" s="148"/>
-    </row>
-    <row r="353" spans="2:2" ht="18" customHeight="1">
-      <c r="B353" s="148"/>
-    </row>
-    <row r="354" spans="2:2" ht="18" customHeight="1">
-      <c r="B354" s="148"/>
-    </row>
-    <row r="355" spans="2:2" ht="18" customHeight="1">
-      <c r="B355" s="148"/>
-    </row>
-    <row r="356" spans="2:2" ht="18" customHeight="1">
-      <c r="B356" s="148"/>
-    </row>
-    <row r="357" spans="2:2" ht="18" customHeight="1">
-      <c r="B357" s="148"/>
-    </row>
-    <row r="358" spans="2:2" ht="18" customHeight="1">
-      <c r="B358" s="148"/>
-    </row>
-    <row r="359" spans="2:2" ht="18" customHeight="1">
-      <c r="B359" s="148"/>
-    </row>
-    <row r="360" spans="2:2" ht="18" customHeight="1">
-      <c r="B360" s="148"/>
-    </row>
-    <row r="361" spans="2:2" ht="18" customHeight="1">
-      <c r="B361" s="148"/>
-    </row>
-    <row r="362" spans="2:2" ht="18" customHeight="1">
-      <c r="B362" s="148"/>
-    </row>
-    <row r="363" spans="2:2" ht="18" customHeight="1">
-      <c r="B363" s="148"/>
-    </row>
-    <row r="364" spans="2:2" ht="18" customHeight="1">
-      <c r="B364" s="148"/>
-    </row>
-    <row r="365" spans="2:2" ht="18" customHeight="1">
-      <c r="B365" s="148"/>
-    </row>
-    <row r="366" spans="2:2" ht="18" customHeight="1">
-      <c r="B366" s="148"/>
-    </row>
-    <row r="367" spans="2:2" ht="18" customHeight="1">
-      <c r="B367" s="148"/>
-    </row>
-    <row r="368" spans="2:2" ht="18" customHeight="1">
-      <c r="B368" s="148"/>
-    </row>
-    <row r="369" spans="2:2" ht="18" customHeight="1">
-      <c r="B369" s="148"/>
-    </row>
-    <row r="370" spans="2:2" ht="18" customHeight="1">
-      <c r="B370" s="148"/>
-    </row>
-    <row r="371" spans="2:2" ht="18" customHeight="1">
-      <c r="B371" s="148"/>
-    </row>
-    <row r="372" spans="2:2" ht="18" customHeight="1">
-      <c r="B372" s="148"/>
-    </row>
-    <row r="373" spans="2:2" ht="18" customHeight="1">
-      <c r="B373" s="148"/>
-    </row>
-    <row r="374" spans="2:2" ht="18" customHeight="1">
-      <c r="B374" s="148"/>
-    </row>
-    <row r="375" spans="2:2" ht="18" customHeight="1">
-      <c r="B375" s="148"/>
-    </row>
-    <row r="376" spans="2:2" ht="18" customHeight="1">
-      <c r="B376" s="148"/>
-    </row>
-    <row r="377" spans="2:2" ht="18" customHeight="1">
-      <c r="B377" s="148"/>
-    </row>
-    <row r="378" spans="2:2" ht="18" customHeight="1">
-      <c r="B378" s="148"/>
-    </row>
-    <row r="379" spans="2:2" ht="18" customHeight="1">
-      <c r="B379" s="148"/>
-    </row>
-    <row r="380" spans="2:2" ht="18" customHeight="1">
-      <c r="B380" s="148"/>
-    </row>
-    <row r="381" spans="2:2" ht="18" customHeight="1">
-      <c r="B381" s="148"/>
-    </row>
-    <row r="382" spans="2:2" ht="18" customHeight="1">
-      <c r="B382" s="148"/>
-    </row>
-    <row r="383" spans="2:2" ht="18" customHeight="1">
-      <c r="B383" s="148"/>
-    </row>
-    <row r="384" spans="2:2" ht="18" customHeight="1">
-      <c r="B384" s="148"/>
-    </row>
-    <row r="385" spans="2:2" ht="18" customHeight="1">
-      <c r="B385" s="148"/>
-    </row>
-    <row r="386" spans="2:2" ht="18" customHeight="1">
-      <c r="B386" s="148"/>
-    </row>
-    <row r="387" spans="2:2" ht="18" customHeight="1">
-      <c r="B387" s="148"/>
-    </row>
-    <row r="388" spans="2:2" ht="18" customHeight="1">
-      <c r="B388" s="148"/>
-    </row>
-    <row r="389" spans="2:2" ht="18" customHeight="1">
-      <c r="B389" s="148"/>
-    </row>
-    <row r="390" spans="2:2" ht="18" customHeight="1">
-      <c r="B390" s="148"/>
-    </row>
-    <row r="391" spans="2:2" ht="18" customHeight="1">
-      <c r="B391" s="148"/>
-    </row>
-    <row r="392" spans="2:2" ht="18" customHeight="1">
-      <c r="B392" s="148"/>
-    </row>
-    <row r="393" spans="2:2" ht="18" customHeight="1">
-      <c r="B393" s="148"/>
-    </row>
-    <row r="394" spans="2:2" ht="18" customHeight="1">
-      <c r="B394" s="148"/>
-    </row>
-    <row r="395" spans="2:2" ht="18" customHeight="1">
-      <c r="B395" s="148"/>
-    </row>
-    <row r="396" spans="2:2" ht="18" customHeight="1">
-      <c r="B396" s="148"/>
-    </row>
-    <row r="397" spans="2:2" ht="18" customHeight="1">
-      <c r="B397" s="148"/>
-    </row>
-    <row r="398" spans="2:2" ht="18" customHeight="1">
-      <c r="B398" s="148"/>
-    </row>
-    <row r="399" spans="2:2" ht="18" customHeight="1">
-      <c r="B399" s="148"/>
-    </row>
-    <row r="400" spans="2:2" ht="18" customHeight="1">
-      <c r="B400" s="148"/>
-    </row>
-    <row r="401" spans="2:2" ht="18" customHeight="1">
-      <c r="B401" s="148"/>
-    </row>
-    <row r="402" spans="2:2" ht="18" customHeight="1">
-      <c r="B402" s="148"/>
-    </row>
-    <row r="403" spans="2:2" ht="18" customHeight="1">
-      <c r="B403" s="148"/>
-    </row>
-    <row r="404" spans="2:2" ht="18" customHeight="1">
-      <c r="B404" s="148"/>
-    </row>
-    <row r="405" spans="2:2" ht="18" customHeight="1">
-      <c r="B405" s="148"/>
-    </row>
-    <row r="406" spans="2:2" ht="18" customHeight="1">
-      <c r="B406" s="148"/>
-    </row>
-    <row r="407" spans="2:2" ht="18" customHeight="1">
-      <c r="B407" s="148"/>
-    </row>
-    <row r="408" spans="2:2" ht="18" customHeight="1">
-      <c r="B408" s="148"/>
-    </row>
-    <row r="409" spans="2:2" ht="18" customHeight="1">
-      <c r="B409" s="148"/>
-    </row>
-    <row r="410" spans="2:2" ht="18" customHeight="1">
-      <c r="B410" s="148"/>
-    </row>
-    <row r="411" spans="2:2" ht="18" customHeight="1">
-      <c r="B411" s="148"/>
-    </row>
-    <row r="412" spans="2:2" ht="18" customHeight="1">
-      <c r="B412" s="148"/>
-    </row>
-    <row r="413" spans="2:2" ht="18" customHeight="1">
-      <c r="B413" s="148"/>
-    </row>
-    <row r="414" spans="2:2" ht="18" customHeight="1">
-      <c r="B414" s="148"/>
-    </row>
-    <row r="415" spans="2:2" ht="18" customHeight="1">
-      <c r="B415" s="148"/>
-    </row>
-    <row r="416" spans="2:2" ht="18" customHeight="1">
-      <c r="B416" s="148"/>
-    </row>
-    <row r="417" spans="2:2" ht="18" customHeight="1">
-      <c r="B417" s="148"/>
-    </row>
-    <row r="418" spans="2:2" ht="18" customHeight="1">
-      <c r="B418" s="148"/>
-    </row>
-    <row r="419" spans="2:2" ht="18" customHeight="1">
-      <c r="B419" s="148"/>
-    </row>
-    <row r="420" spans="2:2" ht="18" customHeight="1">
-      <c r="B420" s="148"/>
-    </row>
-    <row r="421" spans="2:2" ht="18" customHeight="1">
-      <c r="B421" s="148"/>
-    </row>
-    <row r="422" spans="2:2" ht="18" customHeight="1">
-      <c r="B422" s="148"/>
-    </row>
-    <row r="423" spans="2:2" ht="18" customHeight="1">
-      <c r="B423" s="148"/>
-    </row>
-    <row r="424" spans="2:2" ht="18" customHeight="1">
-      <c r="B424" s="148"/>
-    </row>
-    <row r="425" spans="2:2" ht="18" customHeight="1">
-      <c r="B425" s="148"/>
-    </row>
-    <row r="426" spans="2:2" ht="18" customHeight="1">
-      <c r="B426" s="148"/>
-    </row>
-    <row r="427" spans="2:2" ht="18" customHeight="1">
-      <c r="B427" s="148"/>
-    </row>
-    <row r="428" spans="2:2" ht="18" customHeight="1">
-      <c r="B428" s="148"/>
-    </row>
-    <row r="429" spans="2:2" ht="18" customHeight="1">
-      <c r="B429" s="148"/>
-    </row>
-    <row r="430" spans="2:2" ht="18" customHeight="1">
-      <c r="B430" s="148"/>
-    </row>
-    <row r="431" spans="2:2" ht="18" customHeight="1">
-      <c r="B431" s="148"/>
-    </row>
-    <row r="432" spans="2:2" ht="18" customHeight="1">
-      <c r="B432" s="148"/>
-    </row>
-    <row r="433" spans="2:2" ht="18" customHeight="1">
-      <c r="B433" s="148"/>
-    </row>
-    <row r="434" spans="2:2" ht="18" customHeight="1">
-      <c r="B434" s="148"/>
-    </row>
-    <row r="435" spans="2:2" ht="18" customHeight="1">
-      <c r="B435" s="148"/>
-    </row>
-    <row r="436" spans="2:2" ht="18" customHeight="1">
-      <c r="B436" s="148"/>
-    </row>
-    <row r="437" spans="2:2" ht="18" customHeight="1">
-      <c r="B437" s="148"/>
-    </row>
-    <row r="438" spans="2:2" ht="18" customHeight="1">
-      <c r="B438" s="148"/>
-    </row>
-    <row r="439" spans="2:2" ht="18" customHeight="1">
-      <c r="B439" s="148"/>
-    </row>
-    <row r="440" spans="2:2" ht="18" customHeight="1">
-      <c r="B440" s="148"/>
-    </row>
-    <row r="441" spans="2:2" ht="18" customHeight="1">
-      <c r="B441" s="148"/>
-    </row>
-    <row r="442" spans="2:2" ht="18" customHeight="1">
-      <c r="B442" s="148"/>
-    </row>
-    <row r="443" spans="2:2" ht="18" customHeight="1">
-      <c r="B443" s="148"/>
-    </row>
-    <row r="444" spans="2:2" ht="18" customHeight="1">
-      <c r="B444" s="148"/>
-    </row>
-    <row r="445" spans="2:2" ht="18" customHeight="1">
-      <c r="B445" s="148"/>
-    </row>
-    <row r="446" spans="2:2" ht="18" customHeight="1">
-      <c r="B446" s="148"/>
-    </row>
-    <row r="447" spans="2:2" ht="18" customHeight="1">
-      <c r="B447" s="148"/>
-    </row>
-    <row r="448" spans="2:2" ht="18" customHeight="1">
-      <c r="B448" s="148"/>
-    </row>
-    <row r="449" spans="2:2" ht="18" customHeight="1">
-      <c r="B449" s="148"/>
-    </row>
-    <row r="450" spans="2:2" ht="18" customHeight="1">
-      <c r="B450" s="148"/>
-    </row>
-    <row r="451" spans="2:2" ht="18" customHeight="1">
-      <c r="B451" s="148"/>
-    </row>
-    <row r="452" spans="2:2" ht="18" customHeight="1">
-      <c r="B452" s="148"/>
-    </row>
-    <row r="453" spans="2:2" ht="18" customHeight="1">
-      <c r="B453" s="148"/>
-    </row>
-    <row r="454" spans="2:2" ht="18" customHeight="1">
-      <c r="B454" s="148"/>
-    </row>
-    <row r="455" spans="2:2" ht="18" customHeight="1">
-      <c r="B455" s="148"/>
-    </row>
-    <row r="456" spans="2:2" ht="18" customHeight="1">
-      <c r="B456" s="148"/>
-    </row>
-    <row r="457" spans="2:2" ht="18" customHeight="1">
-      <c r="B457" s="148"/>
-    </row>
-    <row r="458" spans="2:2" ht="18" customHeight="1">
-      <c r="B458" s="148"/>
-    </row>
-    <row r="459" spans="2:2" ht="18" customHeight="1">
-      <c r="B459" s="148"/>
-    </row>
-    <row r="460" spans="2:2" ht="18" customHeight="1">
-      <c r="B460" s="148"/>
-    </row>
-    <row r="461" spans="2:2" ht="18" customHeight="1">
-      <c r="B461" s="148"/>
-    </row>
-    <row r="462" spans="2:2" ht="18" customHeight="1">
-      <c r="B462" s="148"/>
-    </row>
-    <row r="463" spans="2:2" ht="18" customHeight="1">
-      <c r="B463" s="148"/>
-    </row>
-    <row r="464" spans="2:2" ht="18" customHeight="1">
-      <c r="B464" s="148"/>
-    </row>
-    <row r="465" spans="2:2" ht="18" customHeight="1">
-      <c r="B465" s="148"/>
-    </row>
-    <row r="466" spans="2:2" ht="18" customHeight="1">
-      <c r="B466" s="148"/>
-    </row>
-    <row r="467" spans="2:2" ht="18" customHeight="1">
-      <c r="B467" s="148"/>
-    </row>
-    <row r="468" spans="2:2" ht="18" customHeight="1">
-      <c r="B468" s="148"/>
-    </row>
-    <row r="469" spans="2:2" ht="18" customHeight="1">
-      <c r="B469" s="148"/>
-    </row>
-    <row r="470" spans="2:2" ht="18" customHeight="1">
-      <c r="B470" s="148"/>
-    </row>
-    <row r="471" spans="2:2" ht="18" customHeight="1">
-      <c r="B471" s="148"/>
-    </row>
-    <row r="472" spans="2:2" ht="18" customHeight="1">
-      <c r="B472" s="148"/>
-    </row>
-    <row r="473" spans="2:2" ht="18" customHeight="1">
-      <c r="B473" s="148"/>
-    </row>
-    <row r="474" spans="2:2" ht="18" customHeight="1">
-      <c r="B474" s="148"/>
-    </row>
-    <row r="475" spans="2:2" ht="18" customHeight="1">
-      <c r="B475" s="148"/>
-    </row>
-    <row r="476" spans="2:2" ht="18" customHeight="1">
-      <c r="B476" s="148"/>
-    </row>
-    <row r="477" spans="2:2" ht="18" customHeight="1">
-      <c r="B477" s="148"/>
-    </row>
-    <row r="478" spans="2:2" ht="18" customHeight="1">
-      <c r="B478" s="148"/>
-    </row>
-    <row r="479" spans="2:2" ht="18" customHeight="1">
-      <c r="B479" s="148"/>
-    </row>
-    <row r="480" spans="2:2" ht="18" customHeight="1">
-      <c r="B480" s="148"/>
-    </row>
-    <row r="481" spans="2:2" ht="18" customHeight="1">
-      <c r="B481" s="148"/>
-    </row>
-    <row r="482" spans="2:2" ht="18" customHeight="1">
-      <c r="B482" s="148"/>
-    </row>
-    <row r="483" spans="2:2" ht="18" customHeight="1">
-      <c r="B483" s="148"/>
-    </row>
-    <row r="484" spans="2:2" ht="18" customHeight="1">
-      <c r="B484" s="148"/>
-    </row>
-    <row r="485" spans="2:2" ht="18" customHeight="1">
-      <c r="B485" s="148"/>
-    </row>
-    <row r="486" spans="2:2" ht="18" customHeight="1">
-      <c r="B486" s="148"/>
-    </row>
-    <row r="487" spans="2:2" ht="18" customHeight="1">
-      <c r="B487" s="148"/>
-    </row>
-    <row r="488" spans="2:2" ht="18" customHeight="1">
-      <c r="B488" s="148"/>
-    </row>
-    <row r="489" spans="2:2" ht="18" customHeight="1">
-      <c r="B489" s="148"/>
-    </row>
-    <row r="490" spans="2:2" ht="18" customHeight="1">
-      <c r="B490" s="148"/>
-    </row>
-    <row r="491" spans="2:2" ht="18" customHeight="1">
-      <c r="B491" s="148"/>
-    </row>
-    <row r="492" spans="2:2" ht="18" customHeight="1">
-      <c r="B492" s="148"/>
-    </row>
-    <row r="493" spans="2:2" ht="18" customHeight="1">
-      <c r="B493" s="148"/>
-    </row>
-    <row r="494" spans="2:2" ht="18" customHeight="1">
-      <c r="B494" s="148"/>
-    </row>
-    <row r="495" spans="2:2" ht="18" customHeight="1">
-      <c r="B495" s="148"/>
-    </row>
-    <row r="496" spans="2:2" ht="18" customHeight="1">
-      <c r="B496" s="148"/>
-    </row>
-    <row r="497" spans="2:2" ht="18" customHeight="1">
-      <c r="B497" s="148"/>
-    </row>
-    <row r="498" spans="2:2" ht="18" customHeight="1">
-      <c r="B498" s="148"/>
-    </row>
-    <row r="499" spans="2:2" ht="18" customHeight="1">
-      <c r="B499" s="148"/>
-    </row>
-    <row r="500" spans="2:2" ht="18" customHeight="1">
-      <c r="B500" s="148"/>
-    </row>
-    <row r="501" spans="2:2" ht="18" customHeight="1">
-      <c r="B501" s="148"/>
-    </row>
-    <row r="502" spans="2:2" ht="18" customHeight="1">
-      <c r="B502" s="148"/>
-    </row>
-    <row r="503" spans="2:2" ht="18" customHeight="1">
-      <c r="B503" s="148"/>
-    </row>
-    <row r="504" spans="2:2" ht="18" customHeight="1">
-      <c r="B504" s="148"/>
-    </row>
-    <row r="505" spans="2:2" ht="18" customHeight="1">
-      <c r="B505" s="148"/>
-    </row>
-    <row r="506" spans="2:2" ht="18" customHeight="1">
-      <c r="B506" s="148"/>
-    </row>
-    <row r="507" spans="2:2" ht="18" customHeight="1">
-      <c r="B507" s="148"/>
-    </row>
-    <row r="508" spans="2:2" ht="18" customHeight="1">
-      <c r="B508" s="148"/>
-    </row>
-    <row r="509" spans="2:2" ht="18" customHeight="1">
-      <c r="B509" s="148"/>
-    </row>
-    <row r="510" spans="2:2" ht="18" customHeight="1">
-      <c r="B510" s="148"/>
-    </row>
-    <row r="511" spans="2:2" ht="18" customHeight="1">
-      <c r="B511" s="148"/>
-    </row>
-    <row r="512" spans="2:2" ht="18" customHeight="1">
-      <c r="B512" s="148"/>
-    </row>
-    <row r="513" spans="2:2" ht="18" customHeight="1">
-      <c r="B513" s="148"/>
-    </row>
-    <row r="514" spans="2:2" ht="18" customHeight="1">
-      <c r="B514" s="148"/>
-    </row>
-    <row r="515" spans="2:2" ht="18" customHeight="1">
-      <c r="B515" s="148"/>
-    </row>
-    <row r="516" spans="2:2" ht="18" customHeight="1">
-      <c r="B516" s="148"/>
-    </row>
-    <row r="517" spans="2:2" ht="18" customHeight="1">
-      <c r="B517" s="148"/>
-    </row>
-    <row r="518" spans="2:2" ht="18" customHeight="1">
-      <c r="B518" s="148"/>
-    </row>
-    <row r="519" spans="2:2" ht="18" customHeight="1">
-      <c r="B519" s="148"/>
-    </row>
-    <row r="520" spans="2:2" ht="18" customHeight="1">
-      <c r="B520" s="148"/>
-    </row>
-    <row r="521" spans="2:2" ht="18" customHeight="1">
-      <c r="B521" s="148"/>
-    </row>
-    <row r="522" spans="2:2" ht="18" customHeight="1">
-      <c r="B522" s="148"/>
-    </row>
-    <row r="523" spans="2:2" ht="18" customHeight="1">
-      <c r="B523" s="148"/>
-    </row>
-    <row r="524" spans="2:2" ht="18" customHeight="1">
-      <c r="B524" s="148"/>
-    </row>
-    <row r="525" spans="2:2" ht="18" customHeight="1">
-      <c r="B525" s="148"/>
-    </row>
-    <row r="526" spans="2:2" ht="18" customHeight="1">
-      <c r="B526" s="148"/>
-    </row>
-    <row r="527" spans="2:2" ht="18" customHeight="1">
-      <c r="B527" s="148"/>
-    </row>
-    <row r="528" spans="2:2" ht="18" customHeight="1">
-      <c r="B528" s="148"/>
-    </row>
-    <row r="529" spans="2:2" ht="18" customHeight="1">
-      <c r="B529" s="148"/>
-    </row>
-    <row r="530" spans="2:2" ht="18" customHeight="1">
-      <c r="B530" s="148"/>
-    </row>
-    <row r="531" spans="2:2" ht="18" customHeight="1">
-      <c r="B531" s="148"/>
-    </row>
-    <row r="532" spans="2:2" ht="18" customHeight="1">
-      <c r="B532" s="148"/>
-    </row>
-    <row r="533" spans="2:2" ht="18" customHeight="1">
-      <c r="B533" s="148"/>
-    </row>
-    <row r="534" spans="2:2" ht="18" customHeight="1">
-      <c r="B534" s="148"/>
-    </row>
-    <row r="535" spans="2:2" ht="18" customHeight="1">
-      <c r="B535" s="148"/>
-    </row>
-    <row r="536" spans="2:2" ht="18" customHeight="1">
-      <c r="B536" s="148"/>
-    </row>
-    <row r="537" spans="2:2" ht="18" customHeight="1">
-      <c r="B537" s="148"/>
-    </row>
-    <row r="538" spans="2:2" ht="18" customHeight="1">
-      <c r="B538" s="148"/>
-    </row>
-    <row r="539" spans="2:2" ht="18" customHeight="1">
-      <c r="B539" s="148"/>
-    </row>
-    <row r="540" spans="2:2" ht="18" customHeight="1">
-      <c r="B540" s="148"/>
-    </row>
-    <row r="541" spans="2:2" ht="18" customHeight="1">
-      <c r="B541" s="148"/>
-    </row>
-    <row r="542" spans="2:2" ht="18" customHeight="1">
-      <c r="B542" s="148"/>
-    </row>
-    <row r="543" spans="2:2" ht="18" customHeight="1">
-      <c r="B543" s="148"/>
-    </row>
-    <row r="544" spans="2:2" ht="18" customHeight="1">
-      <c r="B544" s="148"/>
-    </row>
-    <row r="545" spans="2:2" ht="18" customHeight="1">
-      <c r="B545" s="148"/>
-    </row>
-    <row r="546" spans="2:2" ht="18" customHeight="1">
-      <c r="B546" s="148"/>
-    </row>
-    <row r="547" spans="2:2" ht="18" customHeight="1">
-      <c r="B547" s="148"/>
-    </row>
-    <row r="548" spans="2:2" ht="18" customHeight="1">
-      <c r="B548" s="148"/>
-    </row>
-    <row r="549" spans="2:2" ht="18" customHeight="1">
-      <c r="B549" s="148"/>
-    </row>
-    <row r="550" spans="2:2" ht="18" customHeight="1">
-      <c r="B550" s="148"/>
-    </row>
-    <row r="551" spans="2:2" ht="18" customHeight="1">
-      <c r="B551" s="148"/>
-    </row>
-    <row r="552" spans="2:2" ht="18" customHeight="1">
-      <c r="B552" s="148"/>
-    </row>
-    <row r="553" spans="2:2" ht="18" customHeight="1">
-      <c r="B553" s="148"/>
-    </row>
-    <row r="554" spans="2:2" ht="18" customHeight="1">
-      <c r="B554" s="148"/>
-    </row>
-    <row r="555" spans="2:2" ht="18" customHeight="1">
-      <c r="B555" s="148"/>
-    </row>
-    <row r="556" spans="2:2" ht="18" customHeight="1">
-      <c r="B556" s="148"/>
-    </row>
-    <row r="557" spans="2:2" ht="18" customHeight="1">
-      <c r="B557" s="148"/>
-    </row>
-    <row r="558" spans="2:2" ht="18" customHeight="1">
-      <c r="B558" s="148"/>
-    </row>
-    <row r="559" spans="2:2" ht="18" customHeight="1">
-      <c r="B559" s="148"/>
-    </row>
-    <row r="560" spans="2:2" ht="18" customHeight="1">
-      <c r="B560" s="148"/>
-    </row>
-    <row r="561" spans="2:2" ht="18" customHeight="1">
-      <c r="B561" s="148"/>
-    </row>
-    <row r="562" spans="2:2" ht="18" customHeight="1">
-      <c r="B562" s="148"/>
-    </row>
-    <row r="563" spans="2:2" ht="18" customHeight="1">
-      <c r="B563" s="148"/>
-    </row>
-    <row r="564" spans="2:2" ht="18" customHeight="1">
-      <c r="B564" s="148"/>
-    </row>
-    <row r="565" spans="2:2" ht="18" customHeight="1">
-      <c r="B565" s="148"/>
-    </row>
-    <row r="566" spans="2:2" ht="18" customHeight="1">
-      <c r="B566" s="148"/>
-    </row>
-    <row r="567" spans="2:2" ht="18" customHeight="1">
-      <c r="B567" s="148"/>
-    </row>
-    <row r="568" spans="2:2" ht="18" customHeight="1">
-      <c r="B568" s="148"/>
-    </row>
-    <row r="569" spans="2:2" ht="18" customHeight="1">
-      <c r="B569" s="148"/>
-    </row>
-    <row r="570" spans="2:2" ht="18" customHeight="1">
-      <c r="B570" s="148"/>
-    </row>
-    <row r="571" spans="2:2" ht="18" customHeight="1">
-      <c r="B571" s="148"/>
-    </row>
-    <row r="572" spans="2:2" ht="18" customHeight="1">
-      <c r="B572" s="148"/>
-    </row>
-    <row r="573" spans="2:2" ht="18" customHeight="1">
-      <c r="B573" s="148"/>
-    </row>
-    <row r="574" spans="2:2" ht="18" customHeight="1">
-      <c r="B574" s="148"/>
-    </row>
-    <row r="575" spans="2:2" ht="18" customHeight="1">
-      <c r="B575" s="148"/>
-    </row>
-    <row r="576" spans="2:2" ht="18" customHeight="1">
-      <c r="B576" s="148"/>
-    </row>
-    <row r="577" spans="2:2" ht="18" customHeight="1">
-      <c r="B577" s="148"/>
-    </row>
-    <row r="578" spans="2:2" ht="18" customHeight="1">
-      <c r="B578" s="148"/>
-    </row>
-    <row r="579" spans="2:2" ht="18" customHeight="1">
-      <c r="B579" s="148"/>
-    </row>
-    <row r="580" spans="2:2" ht="18" customHeight="1">
-      <c r="B580" s="148"/>
-    </row>
-    <row r="581" spans="2:2" ht="18" customHeight="1">
-      <c r="B581" s="148"/>
-    </row>
-    <row r="582" spans="2:2" ht="18" customHeight="1">
-      <c r="B582" s="148"/>
-    </row>
-    <row r="583" spans="2:2" ht="18" customHeight="1">
-      <c r="B583" s="148"/>
-    </row>
-    <row r="584" spans="2:2" ht="18" customHeight="1">
-      <c r="B584" s="148"/>
-    </row>
-    <row r="585" spans="2:2" ht="18" customHeight="1">
-      <c r="B585" s="148"/>
-    </row>
-    <row r="586" spans="2:2" ht="18" customHeight="1">
-      <c r="B586" s="148"/>
-    </row>
-    <row r="587" spans="2:2" ht="18" customHeight="1">
-      <c r="B587" s="148"/>
-    </row>
-    <row r="588" spans="2:2" ht="18" customHeight="1">
-      <c r="B588" s="148"/>
-    </row>
-    <row r="589" spans="2:2" ht="18" customHeight="1">
-      <c r="B589" s="148"/>
-    </row>
-    <row r="590" spans="2:2" ht="18" customHeight="1">
-      <c r="B590" s="148"/>
-    </row>
-    <row r="591" spans="2:2" ht="18" customHeight="1">
-      <c r="B591" s="148"/>
-    </row>
-    <row r="592" spans="2:2" ht="18" customHeight="1">
-      <c r="B592" s="148"/>
-    </row>
-    <row r="593" spans="2:2" ht="18" customHeight="1">
-      <c r="B593" s="148"/>
-    </row>
-    <row r="594" spans="2:2" ht="18" customHeight="1">
-      <c r="B594" s="148"/>
-    </row>
-    <row r="595" spans="2:2" ht="18" customHeight="1">
-      <c r="B595" s="148"/>
-    </row>
-    <row r="596" spans="2:2" ht="18" customHeight="1">
-      <c r="B596" s="148"/>
-    </row>
-    <row r="597" spans="2:2" ht="18" customHeight="1">
-      <c r="B597" s="148"/>
-    </row>
-    <row r="598" spans="2:2" ht="18" customHeight="1">
-      <c r="B598" s="148"/>
-    </row>
-    <row r="599" spans="2:2" ht="18" customHeight="1">
-      <c r="B599" s="148"/>
-    </row>
-    <row r="600" spans="2:2" ht="18" customHeight="1">
-      <c r="B600" s="148"/>
-    </row>
-    <row r="601" spans="2:2" ht="18" customHeight="1">
-      <c r="B601" s="148"/>
-    </row>
-    <row r="602" spans="2:2" ht="18" customHeight="1">
-      <c r="B602" s="148"/>
-    </row>
-    <row r="603" spans="2:2" ht="18" customHeight="1">
-      <c r="B603" s="148"/>
-    </row>
-    <row r="604" spans="2:2" ht="18" customHeight="1">
-      <c r="B604" s="148"/>
-    </row>
-    <row r="605" spans="2:2" ht="18" customHeight="1">
-      <c r="B605" s="148"/>
-    </row>
-    <row r="606" spans="2:2" ht="18" customHeight="1">
-      <c r="B606" s="148"/>
-    </row>
-    <row r="607" spans="2:2" ht="18" customHeight="1">
-      <c r="B607" s="148"/>
-    </row>
-    <row r="608" spans="2:2" ht="18" customHeight="1">
-      <c r="B608" s="148"/>
-    </row>
-    <row r="609" spans="2:2" ht="18" customHeight="1">
-      <c r="B609" s="148"/>
-    </row>
-    <row r="610" spans="2:2" ht="18" customHeight="1">
-      <c r="B610" s="148"/>
-    </row>
-    <row r="611" spans="2:2" ht="18" customHeight="1">
-      <c r="B611" s="148"/>
-    </row>
-    <row r="612" spans="2:2" ht="18" customHeight="1">
-      <c r="B612" s="148"/>
-    </row>
-    <row r="613" spans="2:2" ht="18" customHeight="1">
-      <c r="B613" s="148"/>
-    </row>
-    <row r="614" spans="2:2" ht="18" customHeight="1">
-      <c r="B614" s="148"/>
-    </row>
-    <row r="615" spans="2:2" ht="18" customHeight="1">
-      <c r="B615" s="148"/>
-    </row>
-    <row r="616" spans="2:2" ht="18" customHeight="1">
-      <c r="B616" s="148"/>
-    </row>
-    <row r="617" spans="2:2" ht="18" customHeight="1">
-      <c r="B617" s="148"/>
-    </row>
-    <row r="618" spans="2:2" ht="18" customHeight="1">
-      <c r="B618" s="148"/>
-    </row>
-    <row r="619" spans="2:2" ht="18" customHeight="1">
-      <c r="B619" s="148"/>
-    </row>
-    <row r="620" spans="2:2" ht="18" customHeight="1">
-      <c r="B620" s="148"/>
-    </row>
-    <row r="621" spans="2:2" ht="18" customHeight="1">
-      <c r="B621" s="148"/>
-    </row>
-    <row r="622" spans="2:2" ht="18" customHeight="1">
-      <c r="B622" s="148"/>
-    </row>
-    <row r="623" spans="2:2" ht="18" customHeight="1">
-      <c r="B623" s="148"/>
-    </row>
-    <row r="624" spans="2:2" ht="18" customHeight="1">
-      <c r="B624" s="148"/>
-    </row>
-    <row r="625" spans="2:2" ht="18" customHeight="1">
-      <c r="B625" s="148"/>
-    </row>
-    <row r="626" spans="2:2" ht="18" customHeight="1">
-      <c r="B626" s="148"/>
-    </row>
-    <row r="627" spans="2:2" ht="18" customHeight="1">
-      <c r="B627" s="148"/>
-    </row>
-    <row r="628" spans="2:2" ht="18" customHeight="1">
-      <c r="B628" s="148"/>
-    </row>
-    <row r="629" spans="2:2" ht="18" customHeight="1">
-      <c r="B629" s="148"/>
-    </row>
-    <row r="630" spans="2:2" ht="18" customHeight="1">
-      <c r="B630" s="148"/>
-    </row>
-    <row r="631" spans="2:2" ht="18" customHeight="1">
-      <c r="B631" s="148"/>
-    </row>
-    <row r="632" spans="2:2" ht="18" customHeight="1">
-      <c r="B632" s="148"/>
-    </row>
-    <row r="633" spans="2:2" ht="18" customHeight="1">
-      <c r="B633" s="148"/>
-    </row>
-    <row r="634" spans="2:2" ht="18" customHeight="1">
-      <c r="B634" s="148"/>
-    </row>
-    <row r="635" spans="2:2" ht="18" customHeight="1">
-      <c r="B635" s="148"/>
-    </row>
-    <row r="636" spans="2:2" ht="18" customHeight="1">
-      <c r="B636" s="148"/>
-    </row>
-    <row r="637" spans="2:2" ht="18" customHeight="1">
-      <c r="B637" s="148"/>
-    </row>
-    <row r="638" spans="2:2" ht="18" customHeight="1">
-      <c r="B638" s="148"/>
-    </row>
-    <row r="639" spans="2:2" ht="18" customHeight="1">
-      <c r="B639" s="148"/>
-    </row>
-    <row r="640" spans="2:2" ht="18" customHeight="1">
-      <c r="B640" s="148"/>
-    </row>
-    <row r="641" spans="2:2" ht="18" customHeight="1">
-      <c r="B641" s="148"/>
-    </row>
-    <row r="642" spans="2:2" ht="18" customHeight="1">
-      <c r="B642" s="148"/>
-    </row>
-    <row r="643" spans="2:2" ht="18" customHeight="1">
-      <c r="B643" s="148"/>
-    </row>
-    <row r="644" spans="2:2" ht="18" customHeight="1">
-      <c r="B644" s="148"/>
-    </row>
-    <row r="645" spans="2:2" ht="18" customHeight="1">
-      <c r="B645" s="148"/>
-    </row>
-    <row r="646" spans="2:2" ht="18" customHeight="1">
-      <c r="B646" s="148"/>
-    </row>
-    <row r="647" spans="2:2" ht="18" customHeight="1">
-      <c r="B647" s="148"/>
-    </row>
-    <row r="648" spans="2:2" ht="18" customHeight="1">
-      <c r="B648" s="148"/>
-    </row>
-    <row r="649" spans="2:2" ht="18" customHeight="1">
-      <c r="B649" s="148"/>
-    </row>
-    <row r="650" spans="2:2" ht="18" customHeight="1">
-      <c r="B650" s="148"/>
-    </row>
-    <row r="651" spans="2:2" ht="18" customHeight="1">
-      <c r="B651" s="148"/>
-    </row>
-    <row r="652" spans="2:2" ht="18" customHeight="1">
-      <c r="B652" s="148"/>
-    </row>
-    <row r="653" spans="2:2" ht="18" customHeight="1">
-      <c r="B653" s="148"/>
-    </row>
-    <row r="654" spans="2:2" ht="18" customHeight="1">
-      <c r="B654" s="148"/>
-    </row>
-    <row r="655" spans="2:2" ht="18" customHeight="1">
-      <c r="B655" s="148"/>
-    </row>
-    <row r="656" spans="2:2" ht="18" customHeight="1">
-      <c r="B656" s="148"/>
-    </row>
-    <row r="657" spans="2:2" ht="18" customHeight="1">
-      <c r="B657" s="148"/>
-    </row>
-    <row r="658" spans="2:2" ht="18" customHeight="1">
-      <c r="B658" s="148"/>
-    </row>
-    <row r="659" spans="2:2" ht="18" customHeight="1">
-      <c r="B659" s="148"/>
-    </row>
-    <row r="660" spans="2:2" ht="18" customHeight="1">
-      <c r="B660" s="148"/>
-    </row>
-    <row r="661" spans="2:2" ht="18" customHeight="1">
-      <c r="B661" s="148"/>
-    </row>
-    <row r="662" spans="2:2" ht="18" customHeight="1">
-      <c r="B662" s="148"/>
-    </row>
-    <row r="663" spans="2:2" ht="18" customHeight="1">
-      <c r="B663" s="148"/>
-    </row>
-    <row r="664" spans="2:2" ht="18" customHeight="1">
-      <c r="B664" s="148"/>
-    </row>
-    <row r="665" spans="2:2" ht="18" customHeight="1">
-      <c r="B665" s="148"/>
-    </row>
-    <row r="666" spans="2:2" ht="18" customHeight="1">
-      <c r="B666" s="148"/>
-    </row>
-    <row r="667" spans="2:2" ht="18" customHeight="1">
-      <c r="B667" s="148"/>
-    </row>
-    <row r="668" spans="2:2" ht="18" customHeight="1">
-      <c r="B668" s="148"/>
-    </row>
-    <row r="669" spans="2:2" ht="18" customHeight="1">
-      <c r="B669" s="148"/>
-    </row>
-    <row r="670" spans="2:2" ht="18" customHeight="1">
-      <c r="B670" s="148"/>
-    </row>
-    <row r="671" spans="2:2" ht="18" customHeight="1">
-      <c r="B671" s="148"/>
-    </row>
-    <row r="672" spans="2:2" ht="18" customHeight="1">
-      <c r="B672" s="148"/>
-    </row>
-    <row r="673" spans="2:2" ht="18" customHeight="1">
-      <c r="B673" s="148"/>
-    </row>
-    <row r="674" spans="2:2" ht="18" customHeight="1">
-      <c r="B674" s="148"/>
-    </row>
-    <row r="675" spans="2:2" ht="18" customHeight="1">
-      <c r="B675" s="148"/>
-    </row>
-    <row r="676" spans="2:2" ht="18" customHeight="1">
-      <c r="B676" s="148"/>
-    </row>
-    <row r="677" spans="2:2" ht="18" customHeight="1">
-      <c r="B677" s="148"/>
-    </row>
-    <row r="678" spans="2:2" ht="18" customHeight="1">
-      <c r="B678" s="148"/>
-    </row>
-    <row r="679" spans="2:2" ht="18" customHeight="1">
-      <c r="B679" s="148"/>
-    </row>
-    <row r="680" spans="2:2" ht="18" customHeight="1">
-      <c r="B680" s="148"/>
-    </row>
-    <row r="681" spans="2:2" ht="18" customHeight="1">
-      <c r="B681" s="148"/>
-    </row>
-    <row r="682" spans="2:2" ht="18" customHeight="1">
-      <c r="B682" s="148"/>
-    </row>
-    <row r="683" spans="2:2" ht="18" customHeight="1">
-      <c r="B683" s="148"/>
-    </row>
-    <row r="684" spans="2:2" ht="18" customHeight="1">
-      <c r="B684" s="148"/>
-    </row>
-    <row r="685" spans="2:2" ht="18" customHeight="1">
-      <c r="B685" s="148"/>
-    </row>
-    <row r="686" spans="2:2" ht="18" customHeight="1">
-      <c r="B686" s="148"/>
-    </row>
-    <row r="687" spans="2:2" ht="18" customHeight="1">
-      <c r="B687" s="148"/>
-    </row>
-    <row r="688" spans="2:2" ht="18" customHeight="1">
-      <c r="B688" s="148"/>
-    </row>
-    <row r="689" spans="2:2" ht="18" customHeight="1">
-      <c r="B689" s="148"/>
-    </row>
-    <row r="690" spans="2:2" ht="18" customHeight="1">
-      <c r="B690" s="148"/>
-    </row>
-    <row r="691" spans="2:2" ht="18" customHeight="1">
-      <c r="B691" s="148"/>
-    </row>
-    <row r="692" spans="2:2" ht="18" customHeight="1">
-      <c r="B692" s="148"/>
-    </row>
-    <row r="693" spans="2:2" ht="18" customHeight="1">
-      <c r="B693" s="148"/>
-    </row>
-    <row r="694" spans="2:2" ht="18" customHeight="1">
-      <c r="B694" s="148"/>
-    </row>
-    <row r="695" spans="2:2" ht="18" customHeight="1">
-      <c r="B695" s="148"/>
-    </row>
-    <row r="696" spans="2:2" ht="18" customHeight="1">
-      <c r="B696" s="148"/>
-    </row>
-    <row r="697" spans="2:2" ht="18" customHeight="1">
-      <c r="B697" s="148"/>
-    </row>
-    <row r="698" spans="2:2" ht="18" customHeight="1">
-      <c r="B698" s="148"/>
-    </row>
-    <row r="699" spans="2:2" ht="18" customHeight="1">
-      <c r="B699" s="148"/>
-    </row>
-    <row r="700" spans="2:2" ht="18" customHeight="1">
-      <c r="B700" s="148"/>
-    </row>
-    <row r="701" spans="2:2" ht="18" customHeight="1">
-      <c r="B701" s="148"/>
-    </row>
-    <row r="702" spans="2:2" ht="18" customHeight="1">
-      <c r="B702" s="148"/>
-    </row>
-    <row r="703" spans="2:2" ht="18" customHeight="1">
-      <c r="B703" s="148"/>
-    </row>
-    <row r="704" spans="2:2" ht="18" customHeight="1">
-      <c r="B704" s="148"/>
-    </row>
-    <row r="705" spans="2:2" ht="18" customHeight="1">
-      <c r="B705" s="148"/>
-    </row>
-    <row r="706" spans="2:2" ht="18" customHeight="1">
-      <c r="B706" s="148"/>
-    </row>
-    <row r="707" spans="2:2" ht="18" customHeight="1">
-      <c r="B707" s="148"/>
-    </row>
-    <row r="708" spans="2:2" ht="18" customHeight="1">
-      <c r="B708" s="148"/>
-    </row>
-    <row r="709" spans="2:2" ht="18" customHeight="1">
-      <c r="B709" s="148"/>
-    </row>
-    <row r="710" spans="2:2" ht="18" customHeight="1">
-      <c r="B710" s="148"/>
-    </row>
-    <row r="711" spans="2:2" ht="18" customHeight="1">
-      <c r="B711" s="148"/>
-    </row>
-    <row r="712" spans="2:2" ht="18" customHeight="1">
-      <c r="B712" s="148"/>
-    </row>
-    <row r="713" spans="2:2" ht="18" customHeight="1">
-      <c r="B713" s="148"/>
-    </row>
-    <row r="714" spans="2:2" ht="18" customHeight="1">
-      <c r="B714" s="148"/>
-    </row>
-    <row r="715" spans="2:2" ht="18" customHeight="1">
-      <c r="B715" s="148"/>
-    </row>
-    <row r="716" spans="2:2" ht="18" customHeight="1">
-      <c r="B716" s="148"/>
-    </row>
-    <row r="717" spans="2:2" ht="18" customHeight="1">
-      <c r="B717" s="148"/>
-    </row>
-    <row r="718" spans="2:2" ht="18" customHeight="1">
-      <c r="B718" s="148"/>
-    </row>
-    <row r="719" spans="2:2" ht="18" customHeight="1">
-      <c r="B719" s="148"/>
-    </row>
-    <row r="720" spans="2:2" ht="18" customHeight="1">
-      <c r="B720" s="148"/>
-    </row>
-    <row r="721" spans="2:2" ht="18" customHeight="1">
-      <c r="B721" s="148"/>
-    </row>
-    <row r="722" spans="2:2" ht="18" customHeight="1">
-      <c r="B722" s="148"/>
-    </row>
-    <row r="723" spans="2:2" ht="18" customHeight="1">
-      <c r="B723" s="148"/>
-    </row>
-    <row r="724" spans="2:2" ht="18" customHeight="1">
-      <c r="B724" s="148"/>
-    </row>
-    <row r="725" spans="2:2" ht="18" customHeight="1">
-      <c r="B725" s="148"/>
-    </row>
-    <row r="726" spans="2:2" ht="18" customHeight="1">
-      <c r="B726" s="148"/>
-    </row>
-    <row r="727" spans="2:2" ht="18" customHeight="1">
-      <c r="B727" s="148"/>
-    </row>
-    <row r="728" spans="2:2" ht="18" customHeight="1">
-      <c r="B728" s="148"/>
-    </row>
-    <row r="729" spans="2:2" ht="18" customHeight="1">
-      <c r="B729" s="148"/>
-    </row>
-    <row r="730" spans="2:2" ht="18" customHeight="1">
-      <c r="B730" s="148"/>
-    </row>
-    <row r="731" spans="2:2" ht="18" customHeight="1">
-      <c r="B731" s="148"/>
-    </row>
-    <row r="732" spans="2:2" ht="18" customHeight="1">
-      <c r="B732" s="148"/>
-    </row>
-    <row r="733" spans="2:2" ht="18" customHeight="1">
-      <c r="B733" s="148"/>
-    </row>
-    <row r="734" spans="2:2" ht="18" customHeight="1">
-      <c r="B734" s="148"/>
-    </row>
-    <row r="735" spans="2:2" ht="18" customHeight="1">
-      <c r="B735" s="148"/>
-    </row>
-    <row r="736" spans="2:2" ht="18" customHeight="1">
-      <c r="B736" s="148"/>
-    </row>
-    <row r="737" spans="2:2" ht="18" customHeight="1">
-      <c r="B737" s="148"/>
-    </row>
-    <row r="738" spans="2:2" ht="18" customHeight="1">
-      <c r="B738" s="148"/>
-    </row>
-    <row r="739" spans="2:2" ht="18" customHeight="1">
-      <c r="B739" s="148"/>
-    </row>
-    <row r="740" spans="2:2" ht="18" customHeight="1">
-      <c r="B740" s="148"/>
-    </row>
-    <row r="741" spans="2:2" ht="18" customHeight="1">
-      <c r="B741" s="148"/>
-    </row>
-    <row r="742" spans="2:2" ht="18" customHeight="1">
-      <c r="B742" s="148"/>
-    </row>
-    <row r="743" spans="2:2" ht="18" customHeight="1">
-      <c r="B743" s="148"/>
-    </row>
-    <row r="744" spans="2:2" ht="18" customHeight="1">
-      <c r="B744" s="148"/>
-    </row>
-    <row r="745" spans="2:2" ht="18" customHeight="1">
-      <c r="B745" s="148"/>
-    </row>
-    <row r="746" spans="2:2" ht="18" customHeight="1">
-      <c r="B746" s="148"/>
-    </row>
-    <row r="747" spans="2:2" ht="18" customHeight="1">
-      <c r="B747" s="148"/>
-    </row>
-    <row r="748" spans="2:2" ht="18" customHeight="1">
-      <c r="B748" s="148"/>
-    </row>
-    <row r="749" spans="2:2" ht="18" customHeight="1">
-      <c r="B749" s="148"/>
-    </row>
-    <row r="750" spans="2:2" ht="18" customHeight="1">
-      <c r="B750" s="148"/>
-    </row>
-    <row r="751" spans="2:2" ht="18" customHeight="1">
-      <c r="B751" s="148"/>
-    </row>
-    <row r="752" spans="2:2" ht="18" customHeight="1">
-      <c r="B752" s="148"/>
-    </row>
-    <row r="753" spans="2:2" ht="18" customHeight="1">
-      <c r="B753" s="148"/>
-    </row>
-    <row r="754" spans="2:2" ht="18" customHeight="1">
-      <c r="B754" s="148"/>
-    </row>
-    <row r="755" spans="2:2" ht="18" customHeight="1">
-      <c r="B755" s="148"/>
-    </row>
-    <row r="756" spans="2:2" ht="18" customHeight="1">
-      <c r="B756" s="148"/>
-    </row>
-    <row r="757" spans="2:2" ht="18" customHeight="1">
-      <c r="B757" s="148"/>
-    </row>
-    <row r="758" spans="2:2" ht="18" customHeight="1">
-      <c r="B758" s="148"/>
-    </row>
-    <row r="759" spans="2:2" ht="18" customHeight="1">
-      <c r="B759" s="148"/>
-    </row>
-    <row r="760" spans="2:2" ht="18" customHeight="1">
-      <c r="B760" s="148"/>
-    </row>
-    <row r="761" spans="2:2" ht="18" customHeight="1">
-      <c r="B761" s="148"/>
-    </row>
-    <row r="762" spans="2:2" ht="18" customHeight="1">
-      <c r="B762" s="148"/>
-    </row>
-    <row r="763" spans="2:2" ht="18" customHeight="1">
-      <c r="B763" s="148"/>
-    </row>
-    <row r="764" spans="2:2" ht="18" customHeight="1">
-      <c r="B764" s="148"/>
-    </row>
-    <row r="765" spans="2:2" ht="18" customHeight="1">
-      <c r="B765" s="148"/>
-    </row>
-    <row r="766" spans="2:2" ht="18" customHeight="1">
-      <c r="B766" s="148"/>
-    </row>
-    <row r="767" spans="2:2" ht="18" customHeight="1">
-      <c r="B767" s="148"/>
-    </row>
-    <row r="768" spans="2:2" ht="18" customHeight="1">
-      <c r="B768" s="148"/>
-    </row>
-    <row r="769" spans="2:2" ht="18" customHeight="1">
-      <c r="B769" s="148"/>
-    </row>
-    <row r="770" spans="2:2" ht="18" customHeight="1">
-      <c r="B770" s="148"/>
-    </row>
-    <row r="771" spans="2:2" ht="18" customHeight="1">
-      <c r="B771" s="148"/>
-    </row>
-    <row r="772" spans="2:2" ht="18" customHeight="1">
-      <c r="B772" s="148"/>
-    </row>
-    <row r="773" spans="2:2" ht="18" customHeight="1">
-      <c r="B773" s="148"/>
-    </row>
-    <row r="774" spans="2:2" ht="18" customHeight="1">
-      <c r="B774" s="148"/>
-    </row>
-    <row r="775" spans="2:2" ht="18" customHeight="1">
-      <c r="B775" s="148"/>
-    </row>
-    <row r="776" spans="2:2" ht="18" customHeight="1">
-      <c r="B776" s="148"/>
-    </row>
-    <row r="777" spans="2:2" ht="18" customHeight="1">
-      <c r="B777" s="148"/>
-    </row>
-    <row r="778" spans="2:2" ht="18" customHeight="1">
-      <c r="B778" s="148"/>
-    </row>
-    <row r="779" spans="2:2" ht="18" customHeight="1">
-      <c r="B779" s="148"/>
-    </row>
-    <row r="780" spans="2:2" ht="18" customHeight="1">
-      <c r="B780" s="148"/>
-    </row>
-    <row r="781" spans="2:2" ht="18" customHeight="1">
-      <c r="B781" s="148"/>
-    </row>
-    <row r="782" spans="2:2" ht="18" customHeight="1">
-      <c r="B782" s="148"/>
-    </row>
-    <row r="783" spans="2:2" ht="18" customHeight="1">
-      <c r="B783" s="148"/>
-    </row>
-    <row r="784" spans="2:2" ht="18" customHeight="1">
-      <c r="B784" s="148"/>
-    </row>
-    <row r="785" spans="2:2" ht="18" customHeight="1">
-      <c r="B785" s="148"/>
-    </row>
-    <row r="786" spans="2:2" ht="18" customHeight="1">
-      <c r="B786" s="148"/>
-    </row>
-    <row r="787" spans="2:2" ht="18" customHeight="1">
-      <c r="B787" s="148"/>
-    </row>
-    <row r="788" spans="2:2" ht="18" customHeight="1">
-      <c r="B788" s="148"/>
-    </row>
-    <row r="789" spans="2:2" ht="18" customHeight="1">
-      <c r="B789" s="148"/>
-    </row>
-    <row r="790" spans="2:2" ht="18" customHeight="1">
-      <c r="B790" s="148"/>
-    </row>
-    <row r="791" spans="2:2" ht="18" customHeight="1">
-      <c r="B791" s="148"/>
-    </row>
-    <row r="792" spans="2:2" ht="18" customHeight="1">
-      <c r="B792" s="148"/>
-    </row>
-    <row r="793" spans="2:2" ht="18" customHeight="1">
-      <c r="B793" s="148"/>
-    </row>
-    <row r="794" spans="2:2" ht="18" customHeight="1">
-      <c r="B794" s="148"/>
-    </row>
-    <row r="795" spans="2:2" ht="18" customHeight="1">
-      <c r="B795" s="148"/>
-    </row>
-    <row r="796" spans="2:2" ht="18" customHeight="1">
-      <c r="B796" s="148"/>
-    </row>
-    <row r="797" spans="2:2" ht="18" customHeight="1">
-      <c r="B797" s="148"/>
-    </row>
-    <row r="798" spans="2:2" ht="18" customHeight="1">
-      <c r="B798" s="148"/>
-    </row>
-    <row r="799" spans="2:2" ht="18" customHeight="1">
-      <c r="B799" s="148"/>
-    </row>
-    <row r="800" spans="2:2" ht="18" customHeight="1">
-      <c r="B800" s="148"/>
-    </row>
-    <row r="801" spans="2:2" ht="18" customHeight="1">
-      <c r="B801" s="148"/>
-    </row>
-    <row r="802" spans="2:2" ht="18" customHeight="1">
-      <c r="B802" s="148"/>
-    </row>
-    <row r="803" spans="2:2" ht="18" customHeight="1">
-      <c r="B803" s="148"/>
-    </row>
-    <row r="804" spans="2:2" ht="18" customHeight="1">
-      <c r="B804" s="148"/>
-    </row>
-    <row r="805" spans="2:2" ht="18" customHeight="1">
-      <c r="B805" s="148"/>
-    </row>
-    <row r="806" spans="2:2" ht="18" customHeight="1">
-      <c r="B806" s="148"/>
-    </row>
-    <row r="807" spans="2:2" ht="18" customHeight="1">
-      <c r="B807" s="148"/>
-    </row>
-    <row r="808" spans="2:2" ht="18" customHeight="1">
-      <c r="B808" s="148"/>
-    </row>
-    <row r="809" spans="2:2" ht="18" customHeight="1">
-      <c r="B809" s="148"/>
-    </row>
-    <row r="810" spans="2:2" ht="18" customHeight="1">
-      <c r="B810" s="148"/>
-    </row>
-    <row r="811" spans="2:2" ht="18" customHeight="1">
-      <c r="B811" s="148"/>
-    </row>
-    <row r="812" spans="2:2" ht="18" customHeight="1">
-      <c r="B812" s="148"/>
-    </row>
-    <row r="813" spans="2:2" ht="18" customHeight="1">
-      <c r="B813" s="148"/>
-    </row>
-    <row r="814" spans="2:2" ht="18" customHeight="1">
-      <c r="B814" s="148"/>
-    </row>
-    <row r="815" spans="2:2" ht="18" customHeight="1">
-      <c r="B815" s="148"/>
-    </row>
-    <row r="816" spans="2:2" ht="18" customHeight="1">
-      <c r="B816" s="148"/>
-    </row>
-    <row r="817" spans="2:2" ht="18" customHeight="1">
-      <c r="B817" s="148"/>
-    </row>
-    <row r="818" spans="2:2" ht="18" customHeight="1">
-      <c r="B818" s="148"/>
-    </row>
-    <row r="819" spans="2:2" ht="18" customHeight="1">
-      <c r="B819" s="148"/>
-    </row>
-    <row r="820" spans="2:2" ht="18" customHeight="1">
-      <c r="B820" s="148"/>
-    </row>
-    <row r="821" spans="2:2" ht="18" customHeight="1">
-      <c r="B821" s="148"/>
-    </row>
-    <row r="822" spans="2:2" ht="18" customHeight="1">
-      <c r="B822" s="148"/>
-    </row>
-    <row r="823" spans="2:2" ht="18" customHeight="1">
-      <c r="B823" s="148"/>
-    </row>
-    <row r="824" spans="2:2" ht="18" customHeight="1">
-      <c r="B824" s="148"/>
-    </row>
-    <row r="825" spans="2:2" ht="18" customHeight="1">
-      <c r="B825" s="148"/>
-    </row>
-    <row r="826" spans="2:2" ht="18" customHeight="1">
-      <c r="B826" s="148"/>
-    </row>
-    <row r="827" spans="2:2" ht="18" customHeight="1">
-      <c r="B827" s="148"/>
-    </row>
-    <row r="828" spans="2:2" ht="18" customHeight="1">
-      <c r="B828" s="148"/>
-    </row>
-    <row r="829" spans="2:2" ht="18" customHeight="1">
-      <c r="B829" s="148"/>
-    </row>
-    <row r="830" spans="2:2" ht="18" customHeight="1">
-      <c r="B830" s="148"/>
-    </row>
-    <row r="831" spans="2:2" ht="18" customHeight="1">
-      <c r="B831" s="148"/>
-    </row>
-    <row r="832" spans="2:2" ht="18" customHeight="1">
-      <c r="B832" s="148"/>
-    </row>
-    <row r="833" spans="2:2" ht="18" customHeight="1">
-      <c r="B833" s="148"/>
-    </row>
-    <row r="834" spans="2:2" ht="18" customHeight="1">
-      <c r="B834" s="148"/>
-    </row>
-    <row r="835" spans="2:2" ht="18" customHeight="1">
-      <c r="B835" s="148"/>
-    </row>
-    <row r="836" spans="2:2" ht="18" customHeight="1">
-      <c r="B836" s="148"/>
-    </row>
-    <row r="837" spans="2:2" ht="18" customHeight="1">
-      <c r="B837" s="148"/>
-    </row>
-    <row r="838" spans="2:2" ht="18" customHeight="1">
-      <c r="B838" s="148"/>
-    </row>
-    <row r="839" spans="2:2" ht="18" customHeight="1">
-      <c r="B839" s="148"/>
-    </row>
-    <row r="840" spans="2:2" ht="18" customHeight="1">
-      <c r="B840" s="148"/>
-    </row>
-    <row r="841" spans="2:2" ht="18" customHeight="1">
-      <c r="B841" s="148"/>
-    </row>
-    <row r="842" spans="2:2" ht="18" customHeight="1">
-      <c r="B842" s="148"/>
-    </row>
-    <row r="843" spans="2:2" ht="18" customHeight="1">
-      <c r="B843" s="148"/>
-    </row>
-    <row r="844" spans="2:2" ht="18" customHeight="1">
-      <c r="B844" s="148"/>
-    </row>
-    <row r="845" spans="2:2" ht="18" customHeight="1">
-      <c r="B845" s="148"/>
-    </row>
-    <row r="846" spans="2:2" ht="18" customHeight="1">
-      <c r="B846" s="148"/>
-    </row>
-    <row r="847" spans="2:2" ht="18" customHeight="1">
-      <c r="B847" s="148"/>
-    </row>
-    <row r="848" spans="2:2" ht="18" customHeight="1">
-      <c r="B848" s="148"/>
-    </row>
-    <row r="849" spans="2:2" ht="18" customHeight="1">
-      <c r="B849" s="148"/>
-    </row>
-    <row r="850" spans="2:2" ht="18" customHeight="1">
-      <c r="B850" s="148"/>
-    </row>
-    <row r="851" spans="2:2" ht="18" customHeight="1">
-      <c r="B851" s="148"/>
-    </row>
-    <row r="852" spans="2:2" ht="18" customHeight="1">
-      <c r="B852" s="148"/>
-    </row>
-    <row r="853" spans="2:2" ht="18" customHeight="1">
-      <c r="B853" s="148"/>
-    </row>
-    <row r="854" spans="2:2" ht="18" customHeight="1">
-      <c r="B854" s="148"/>
-    </row>
-    <row r="855" spans="2:2" ht="18" customHeight="1">
-      <c r="B855" s="148"/>
-    </row>
-    <row r="856" spans="2:2" ht="18" customHeight="1">
-      <c r="B856" s="148"/>
-    </row>
-    <row r="857" spans="2:2" ht="18" customHeight="1">
-      <c r="B857" s="148"/>
-    </row>
-    <row r="858" spans="2:2" ht="18" customHeight="1">
-      <c r="B858" s="148"/>
-    </row>
-    <row r="859" spans="2:2" ht="18" customHeight="1">
-      <c r="B859" s="148"/>
-    </row>
-    <row r="860" spans="2:2" ht="18" customHeight="1">
-      <c r="B860" s="148"/>
-    </row>
-    <row r="861" spans="2:2" ht="18" customHeight="1">
-      <c r="B861" s="148"/>
-    </row>
-    <row r="862" spans="2:2" ht="18" customHeight="1">
-      <c r="B862" s="148"/>
-    </row>
-    <row r="863" spans="2:2" ht="18" customHeight="1">
-      <c r="B863" s="148"/>
-    </row>
-    <row r="864" spans="2:2" ht="18" customHeight="1">
-      <c r="B864" s="148"/>
-    </row>
-    <row r="865" spans="2:2" ht="18" customHeight="1">
-      <c r="B865" s="148"/>
-    </row>
-    <row r="866" spans="2:2" ht="18" customHeight="1">
-      <c r="B866" s="148"/>
-    </row>
-    <row r="867" spans="2:2" ht="18" customHeight="1">
-      <c r="B867" s="148"/>
-    </row>
-    <row r="868" spans="2:2" ht="18" customHeight="1">
-      <c r="B868" s="148"/>
-    </row>
-    <row r="869" spans="2:2" ht="18" customHeight="1">
-      <c r="B869" s="148"/>
-    </row>
-    <row r="870" spans="2:2" ht="18" customHeight="1">
-      <c r="B870" s="148"/>
-    </row>
-    <row r="871" spans="2:2" ht="18" customHeight="1">
-      <c r="B871" s="148"/>
-    </row>
-    <row r="872" spans="2:2" ht="18" customHeight="1">
-      <c r="B872" s="148"/>
-    </row>
-    <row r="873" spans="2:2" ht="18" customHeight="1">
-      <c r="B873" s="148"/>
-    </row>
-    <row r="874" spans="2:2" ht="18" customHeight="1">
-      <c r="B874" s="148"/>
-    </row>
-    <row r="875" spans="2:2" ht="18" customHeight="1">
-      <c r="B875" s="148"/>
-    </row>
-    <row r="876" spans="2:2" ht="18" customHeight="1">
-      <c r="B876" s="148"/>
-    </row>
-    <row r="877" spans="2:2" ht="18" customHeight="1">
-      <c r="B877" s="148"/>
-    </row>
-    <row r="878" spans="2:2" ht="18" customHeight="1">
-      <c r="B878" s="148"/>
-    </row>
-    <row r="879" spans="2:2" ht="18" customHeight="1">
-      <c r="B879" s="148"/>
-    </row>
-    <row r="880" spans="2:2" ht="18" customHeight="1">
-      <c r="B880" s="148"/>
-    </row>
-    <row r="881" spans="2:2" ht="18" customHeight="1">
-      <c r="B881" s="148"/>
-    </row>
-    <row r="882" spans="2:2" ht="18" customHeight="1">
-      <c r="B882" s="148"/>
-    </row>
-    <row r="883" spans="2:2" ht="18" customHeight="1">
-      <c r="B883" s="148"/>
-    </row>
-    <row r="884" spans="2:2" ht="18" customHeight="1">
-      <c r="B884" s="148"/>
-    </row>
-    <row r="885" spans="2:2" ht="18" customHeight="1">
-      <c r="B885" s="148"/>
-    </row>
-    <row r="886" spans="2:2" ht="18" customHeight="1">
-      <c r="B886" s="148"/>
-    </row>
-    <row r="887" spans="2:2" ht="18" customHeight="1">
-      <c r="B887" s="148"/>
-    </row>
-    <row r="888" spans="2:2" ht="18" customHeight="1">
-      <c r="B888" s="148"/>
-    </row>
-    <row r="889" spans="2:2" ht="18" customHeight="1">
-      <c r="B889" s="148"/>
-    </row>
-    <row r="890" spans="2:2" ht="18" customHeight="1">
-      <c r="B890" s="148"/>
-    </row>
-    <row r="891" spans="2:2" ht="18" customHeight="1">
-      <c r="B891" s="148"/>
-    </row>
-    <row r="892" spans="2:2" ht="18" customHeight="1">
-      <c r="B892" s="148"/>
-    </row>
-    <row r="893" spans="2:2" ht="18" customHeight="1">
-      <c r="B893" s="148"/>
-    </row>
-    <row r="894" spans="2:2" ht="18" customHeight="1">
-      <c r="B894" s="148"/>
-    </row>
-    <row r="895" spans="2:2" ht="18" customHeight="1">
-      <c r="B895" s="148"/>
-    </row>
-    <row r="896" spans="2:2" ht="18" customHeight="1">
-      <c r="B896" s="148"/>
-    </row>
-    <row r="897" spans="2:2" ht="18" customHeight="1">
-      <c r="B897" s="148"/>
-    </row>
-    <row r="898" spans="2:2" ht="18" customHeight="1">
-      <c r="B898" s="148"/>
-    </row>
-    <row r="899" spans="2:2" ht="18" customHeight="1">
-      <c r="B899" s="148"/>
-    </row>
-    <row r="900" spans="2:2" ht="18" customHeight="1">
-      <c r="B900" s="148"/>
-    </row>
-    <row r="901" spans="2:2" ht="18" customHeight="1">
-      <c r="B901" s="148"/>
-    </row>
-    <row r="902" spans="2:2" ht="18" customHeight="1">
-      <c r="B902" s="148"/>
-    </row>
-    <row r="903" spans="2:2" ht="18" customHeight="1">
-      <c r="B903" s="148"/>
-    </row>
-    <row r="904" spans="2:2" ht="18" customHeight="1">
-      <c r="B904" s="148"/>
-    </row>
-    <row r="905" spans="2:2" ht="18" customHeight="1">
-      <c r="B905" s="148"/>
-    </row>
-    <row r="906" spans="2:2" ht="18" customHeight="1">
-      <c r="B906" s="148"/>
-    </row>
-    <row r="907" spans="2:2" ht="18" customHeight="1">
-      <c r="B907" s="148"/>
-    </row>
-    <row r="908" spans="2:2" ht="18" customHeight="1">
-      <c r="B908" s="148"/>
-    </row>
-    <row r="909" spans="2:2" ht="18" customHeight="1">
-      <c r="B909" s="148"/>
-    </row>
-    <row r="910" spans="2:2" ht="18" customHeight="1">
-      <c r="B910" s="148"/>
-    </row>
-    <row r="911" spans="2:2" ht="18" customHeight="1">
-      <c r="B911" s="148"/>
-    </row>
-    <row r="912" spans="2:2" ht="18" customHeight="1">
-      <c r="B912" s="148"/>
-    </row>
-    <row r="913" spans="2:2" ht="18" customHeight="1">
-      <c r="B913" s="148"/>
-    </row>
-    <row r="914" spans="2:2" ht="18" customHeight="1">
-      <c r="B914" s="148"/>
-    </row>
-    <row r="915" spans="2:2" ht="18" customHeight="1">
-      <c r="B915" s="148"/>
-    </row>
-    <row r="916" spans="2:2" ht="18" customHeight="1">
-      <c r="B916" s="148"/>
-    </row>
-    <row r="917" spans="2:2" ht="18" customHeight="1">
-      <c r="B917" s="148"/>
-    </row>
-    <row r="918" spans="2:2" ht="18" customHeight="1">
-      <c r="B918" s="148"/>
-    </row>
-    <row r="919" spans="2:2" ht="18" customHeight="1">
-      <c r="B919" s="148"/>
-    </row>
-    <row r="920" spans="2:2" ht="18" customHeight="1">
-      <c r="B920" s="148"/>
-    </row>
-    <row r="921" spans="2:2" ht="18" customHeight="1">
-      <c r="B921" s="148"/>
-    </row>
-    <row r="922" spans="2:2" ht="18" customHeight="1">
-      <c r="B922" s="148"/>
-    </row>
-    <row r="923" spans="2:2" ht="18" customHeight="1">
-      <c r="B923" s="148"/>
-    </row>
-    <row r="924" spans="2:2" ht="18" customHeight="1">
-      <c r="B924" s="148"/>
-    </row>
-    <row r="925" spans="2:2" ht="18" customHeight="1">
-      <c r="B925" s="148"/>
-    </row>
-    <row r="926" spans="2:2" ht="18" customHeight="1">
-      <c r="B926" s="148"/>
-    </row>
-    <row r="927" spans="2:2" ht="18" customHeight="1">
-      <c r="B927" s="148"/>
-    </row>
-    <row r="928" spans="2:2" ht="18" customHeight="1">
-      <c r="B928" s="148"/>
-    </row>
-    <row r="929" spans="2:2" ht="18" customHeight="1">
-      <c r="B929" s="148"/>
-    </row>
-    <row r="930" spans="2:2" ht="18" customHeight="1">
-      <c r="B930" s="148"/>
-    </row>
-    <row r="931" spans="2:2" ht="18" customHeight="1">
-      <c r="B931" s="148"/>
-    </row>
-    <row r="932" spans="2:2" ht="18" customHeight="1">
-      <c r="B932" s="148"/>
-    </row>
-    <row r="933" spans="2:2" ht="18" customHeight="1">
-      <c r="B933" s="148"/>
-    </row>
-    <row r="934" spans="2:2" ht="18" customHeight="1">
-      <c r="B934" s="148"/>
-    </row>
-    <row r="935" spans="2:2" ht="18" customHeight="1">
-      <c r="B935" s="148"/>
-    </row>
-    <row r="936" spans="2:2" ht="18" customHeight="1">
-      <c r="B936" s="148"/>
-    </row>
-    <row r="937" spans="2:2" ht="18" customHeight="1">
-      <c r="B937" s="148"/>
-    </row>
-    <row r="938" spans="2:2" ht="18" customHeight="1">
-      <c r="B938" s="148"/>
-    </row>
-    <row r="939" spans="2:2" ht="18" customHeight="1">
-      <c r="B939" s="148"/>
-    </row>
-    <row r="940" spans="2:2" ht="18" customHeight="1">
-      <c r="B940" s="148"/>
-    </row>
-    <row r="941" spans="2:2" ht="18" customHeight="1">
-      <c r="B941" s="148"/>
-    </row>
-    <row r="942" spans="2:2" ht="18" customHeight="1">
-      <c r="B942" s="148"/>
-    </row>
-    <row r="943" spans="2:2" ht="18" customHeight="1">
-      <c r="B943" s="148"/>
-    </row>
-    <row r="944" spans="2:2" ht="18" customHeight="1">
-      <c r="B944" s="148"/>
-    </row>
-    <row r="945" spans="2:2" ht="18" customHeight="1">
-      <c r="B945" s="148"/>
-    </row>
-    <row r="946" spans="2:2" ht="18" customHeight="1">
-      <c r="B946" s="148"/>
-    </row>
-    <row r="947" spans="2:2" ht="18" customHeight="1">
-      <c r="B947" s="148"/>
-    </row>
-    <row r="948" spans="2:2" ht="18" customHeight="1">
-      <c r="B948" s="148"/>
-    </row>
-    <row r="949" spans="2:2" ht="18" customHeight="1">
-      <c r="B949" s="148"/>
-    </row>
-    <row r="950" spans="2:2" ht="18" customHeight="1">
-      <c r="B950" s="148"/>
-    </row>
-    <row r="951" spans="2:2" ht="18" customHeight="1">
-      <c r="B951" s="148"/>
-    </row>
-    <row r="952" spans="2:2" ht="18" customHeight="1">
-      <c r="B952" s="148"/>
-    </row>
-    <row r="953" spans="2:2" ht="18" customHeight="1">
-      <c r="B953" s="148"/>
-    </row>
-    <row r="954" spans="2:2" ht="18" customHeight="1">
-      <c r="B954" s="148"/>
-    </row>
-    <row r="955" spans="2:2" ht="18" customHeight="1">
-      <c r="B955" s="148"/>
-    </row>
-    <row r="956" spans="2:2" ht="18" customHeight="1">
-      <c r="B956" s="148"/>
-    </row>
-    <row r="957" spans="2:2" ht="18" customHeight="1">
-      <c r="B957" s="148"/>
-    </row>
-    <row r="958" spans="2:2" ht="18" customHeight="1">
-      <c r="B958" s="148"/>
-    </row>
-    <row r="959" spans="2:2" ht="18" customHeight="1">
-      <c r="B959" s="148"/>
-    </row>
-    <row r="960" spans="2:2" ht="18" customHeight="1">
-      <c r="B960" s="148"/>
-    </row>
-    <row r="961" spans="2:2" ht="18" customHeight="1">
-      <c r="B961" s="148"/>
-    </row>
-    <row r="962" spans="2:2" ht="18" customHeight="1">
-      <c r="B962" s="148"/>
-    </row>
-    <row r="963" spans="2:2" ht="18" customHeight="1">
-      <c r="B963" s="148"/>
-    </row>
-    <row r="964" spans="2:2" ht="18" customHeight="1">
-      <c r="B964" s="148"/>
-    </row>
-    <row r="965" spans="2:2" ht="18" customHeight="1">
-      <c r="B965" s="148"/>
-    </row>
-    <row r="966" spans="2:2" ht="18" customHeight="1">
-      <c r="B966" s="148"/>
-    </row>
-    <row r="967" spans="2:2" ht="18" customHeight="1">
-      <c r="B967" s="148"/>
-    </row>
-    <row r="968" spans="2:2" ht="18" customHeight="1">
-      <c r="B968" s="148"/>
-    </row>
-    <row r="969" spans="2:2" ht="18" customHeight="1">
-      <c r="B969" s="148"/>
-    </row>
-    <row r="970" spans="2:2" ht="18" customHeight="1">
-      <c r="B970" s="148"/>
-    </row>
-    <row r="971" spans="2:2" ht="18" customHeight="1">
-      <c r="B971" s="148"/>
-    </row>
-    <row r="972" spans="2:2" ht="18" customHeight="1">
-      <c r="B972" s="148"/>
-    </row>
-    <row r="973" spans="2:2" ht="18" customHeight="1">
-      <c r="B973" s="148"/>
-    </row>
-    <row r="974" spans="2:2" ht="18" customHeight="1">
-      <c r="B974" s="148"/>
-    </row>
-    <row r="975" spans="2:2" ht="18" customHeight="1">
-      <c r="B975" s="148"/>
-    </row>
-    <row r="976" spans="2:2" ht="18" customHeight="1">
-      <c r="B976" s="148"/>
-    </row>
-    <row r="977" spans="2:2" ht="18" customHeight="1">
-      <c r="B977" s="148"/>
-    </row>
-    <row r="978" spans="2:2" ht="18" customHeight="1">
-      <c r="B978" s="148"/>
-    </row>
-    <row r="979" spans="2:2" ht="18" customHeight="1">
-      <c r="B979" s="148"/>
-    </row>
-    <row r="980" spans="2:2" ht="18" customHeight="1">
-      <c r="B980" s="148"/>
-    </row>
-    <row r="981" spans="2:2" ht="18" customHeight="1">
-      <c r="B981" s="148"/>
-    </row>
-    <row r="982" spans="2:2" ht="18" customHeight="1">
-      <c r="B982" s="148"/>
-    </row>
-    <row r="983" spans="2:2" ht="18" customHeight="1">
-      <c r="B983" s="148"/>
-    </row>
-    <row r="984" spans="2:2" ht="18" customHeight="1">
-      <c r="B984" s="148"/>
-    </row>
-    <row r="985" spans="2:2" ht="18" customHeight="1">
-      <c r="B985" s="148"/>
-    </row>
-    <row r="986" spans="2:2" ht="18" customHeight="1">
-      <c r="B986" s="148"/>
-    </row>
-    <row r="987" spans="2:2" ht="18" customHeight="1">
-      <c r="B987" s="148"/>
-    </row>
-    <row r="988" spans="2:2" ht="18" customHeight="1">
-      <c r="B988" s="148"/>
-    </row>
-    <row r="989" spans="2:2" ht="18" customHeight="1">
-      <c r="B989" s="148"/>
-    </row>
-    <row r="990" spans="2:2" ht="18" customHeight="1">
-      <c r="B990" s="148"/>
-    </row>
-    <row r="991" spans="2:2" ht="18" customHeight="1">
-      <c r="B991" s="148"/>
-    </row>
-    <row r="992" spans="2:2" ht="18" customHeight="1">
-      <c r="B992" s="148"/>
-    </row>
-    <row r="993" spans="2:2" ht="18" customHeight="1">
-      <c r="B993" s="148"/>
-    </row>
-    <row r="994" spans="2:2" ht="18" customHeight="1">
-      <c r="B994" s="148"/>
-    </row>
-    <row r="995" spans="2:2" ht="18" customHeight="1">
-      <c r="B995" s="148"/>
-    </row>
-    <row r="996" spans="2:2" ht="18" customHeight="1">
-      <c r="B996" s="148"/>
-    </row>
-    <row r="997" spans="2:2" ht="18" customHeight="1">
-      <c r="B997" s="148"/>
-    </row>
-    <row r="998" spans="2:2" ht="18" customHeight="1">
-      <c r="B998" s="148"/>
-    </row>
-    <row r="999" spans="2:2" ht="18" customHeight="1">
-      <c r="B999" s="148"/>
-    </row>
-    <row r="1000" spans="2:2" ht="18" customHeight="1">
-      <c r="B1000" s="148"/>
-    </row>
-    <row r="1001" spans="2:2" ht="18" customHeight="1">
-      <c r="B1001" s="148"/>
-    </row>
-    <row r="1002" spans="2:2" ht="18" customHeight="1">
-      <c r="B1002" s="148"/>
-    </row>
-    <row r="1003" spans="2:2" ht="18" customHeight="1">
-      <c r="B1003" s="148"/>
-    </row>
-    <row r="1004" spans="2:2" ht="18" customHeight="1">
-      <c r="B1004" s="148"/>
-    </row>
-    <row r="1005" spans="2:2" ht="18" customHeight="1">
-      <c r="B1005" s="148"/>
-    </row>
-    <row r="1006" spans="2:2" ht="18" customHeight="1">
-      <c r="B1006" s="148"/>
-    </row>
-    <row r="1007" spans="2:2" ht="18" customHeight="1">
-      <c r="B1007" s="148"/>
-    </row>
-    <row r="1008" spans="2:2" ht="18" customHeight="1">
-      <c r="B1008" s="148"/>
-    </row>
-    <row r="1009" spans="2:2" ht="18" customHeight="1">
-      <c r="B1009" s="148"/>
-    </row>
-    <row r="1010" spans="2:2" ht="18" customHeight="1">
-      <c r="B1010" s="148"/>
-    </row>
-    <row r="1011" spans="2:2" ht="18" customHeight="1">
-      <c r="B1011" s="148"/>
-    </row>
-    <row r="1012" spans="2:2" ht="18" customHeight="1">
-      <c r="B1012" s="148"/>
-    </row>
-    <row r="1013" spans="2:2" ht="18" customHeight="1">
-      <c r="B1013" s="148"/>
-    </row>
-    <row r="1014" spans="2:2" ht="18" customHeight="1">
-      <c r="B1014" s="148"/>
-    </row>
-    <row r="1015" spans="2:2" ht="18" customHeight="1">
-      <c r="B1015" s="148"/>
-    </row>
-    <row r="1016" spans="2:2" ht="18" customHeight="1">
-      <c r="B1016" s="148"/>
-    </row>
-    <row r="1017" spans="2:2" ht="18" customHeight="1">
-      <c r="B1017" s="148"/>
-    </row>
-    <row r="1018" spans="2:2" ht="18" customHeight="1">
-      <c r="B1018" s="148"/>
-    </row>
-    <row r="1019" spans="2:2" ht="18" customHeight="1">
-      <c r="B1019" s="148"/>
-    </row>
-    <row r="1020" spans="2:2" ht="18" customHeight="1">
-      <c r="B1020" s="148"/>
-    </row>
-    <row r="1021" spans="2:2" ht="18" customHeight="1">
-      <c r="B1021" s="148"/>
-    </row>
-    <row r="1022" spans="2:2" ht="18" customHeight="1">
-      <c r="B1022" s="148"/>
-    </row>
-    <row r="1023" spans="2:2" ht="18" customHeight="1">
-      <c r="B1023" s="148"/>
-    </row>
-    <row r="1024" spans="2:2" ht="18" customHeight="1">
-      <c r="B1024" s="148"/>
-    </row>
-    <row r="1025" spans="2:2" ht="18" customHeight="1">
-      <c r="B1025" s="148"/>
-    </row>
-    <row r="1026" spans="2:2" ht="18" customHeight="1">
-      <c r="B1026" s="148"/>
-    </row>
-    <row r="1027" spans="2:2" ht="18" customHeight="1">
-      <c r="B1027" s="148"/>
-    </row>
-    <row r="1028" spans="2:2" ht="18" customHeight="1">
-      <c r="B1028" s="148"/>
-    </row>
-    <row r="1029" spans="2:2" ht="18" customHeight="1">
-      <c r="B1029" s="148"/>
-    </row>
-    <row r="1030" spans="2:2" ht="18" customHeight="1">
-      <c r="B1030" s="148"/>
-    </row>
-    <row r="1031" spans="2:2" ht="18" customHeight="1">
-      <c r="B1031" s="148"/>
-    </row>
-    <row r="1032" spans="2:2" ht="18" customHeight="1">
-      <c r="B1032" s="148"/>
-    </row>
-    <row r="1033" spans="2:2" ht="18" customHeight="1">
-      <c r="B1033" s="148"/>
-    </row>
-    <row r="1034" spans="2:2" ht="18" customHeight="1">
-      <c r="B1034" s="148"/>
-    </row>
-    <row r="1035" spans="2:2" ht="18" customHeight="1">
-      <c r="B1035" s="148"/>
-    </row>
-    <row r="1036" spans="2:2" ht="18" customHeight="1">
-      <c r="B1036" s="148"/>
-    </row>
-    <row r="1037" spans="2:2" ht="18" customHeight="1">
-      <c r="B1037" s="148"/>
-    </row>
-    <row r="1038" spans="2:2" ht="18" customHeight="1">
-      <c r="B1038" s="148"/>
-    </row>
-    <row r="1039" spans="2:2" ht="18" customHeight="1">
-      <c r="B1039" s="148"/>
-    </row>
-    <row r="1040" spans="2:2" ht="18" customHeight="1">
-      <c r="B1040" s="148"/>
-    </row>
-    <row r="1041" spans="2:2" ht="18" customHeight="1">
-      <c r="B1041" s="148"/>
-    </row>
-    <row r="1042" spans="2:2" ht="18" customHeight="1">
-      <c r="B1042" s="148"/>
-    </row>
-    <row r="1043" spans="2:2" ht="18" customHeight="1">
-      <c r="B1043" s="148"/>
-    </row>
-    <row r="1044" spans="2:2" ht="18" customHeight="1">
-      <c r="B1044" s="148"/>
-    </row>
-    <row r="1045" spans="2:2" ht="18" customHeight="1">
-      <c r="B1045" s="148"/>
-    </row>
-    <row r="1046" spans="2:2" ht="18" customHeight="1">
-      <c r="B1046" s="148"/>
-    </row>
-    <row r="1047" spans="2:2" ht="18" customHeight="1">
-      <c r="B1047" s="148"/>
-    </row>
-    <row r="1048" spans="2:2" ht="18" customHeight="1">
-      <c r="B1048" s="148"/>
-    </row>
-    <row r="1049" spans="2:2" ht="18" customHeight="1">
-      <c r="B1049" s="148"/>
-    </row>
-    <row r="1050" spans="2:2" ht="18" customHeight="1">
-      <c r="B1050" s="148"/>
-    </row>
-    <row r="1051" spans="2:2" ht="18" customHeight="1">
-      <c r="B1051" s="148"/>
-    </row>
-    <row r="1052" spans="2:2" ht="18" customHeight="1">
-      <c r="B1052" s="148"/>
-    </row>
-    <row r="1053" spans="2:2" ht="18" customHeight="1">
-      <c r="B1053" s="148"/>
-    </row>
-    <row r="1054" spans="2:2" ht="18" customHeight="1">
-      <c r="B1054" s="148"/>
-    </row>
-    <row r="1055" spans="2:2" ht="18" customHeight="1">
-      <c r="B1055" s="148"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEAFB3C-24F9-4C3B-92E1-88934B2FA9FC}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J1055"/>
@@ -16647,7 +10441,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4E323D-80FF-4C16-B902-C80C196F169E}">
   <dimension ref="A1:R1055"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
@@ -18156,17 +11950,13 @@
         <v>711</v>
       </c>
       <c r="E53" s="128" t="s">
-        <v>708</v>
-      </c>
-      <c r="F53" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F53" s="127"/>
       <c r="G53" s="128" t="s">
-        <v>708</v>
-      </c>
-      <c r="H53" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="H53" s="127"/>
       <c r="I53" s="127" t="s">
         <v>21</v>
       </c>
@@ -18196,16 +11986,14 @@
         <v>711</v>
       </c>
       <c r="E54" s="128" t="s">
-        <v>709</v>
-      </c>
-      <c r="F54" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F54" s="127"/>
       <c r="G54" s="128" t="s">
-        <v>709</v>
+        <v>366</v>
       </c>
       <c r="H54" s="127" t="s">
-        <v>711</v>
+        <v>177</v>
       </c>
       <c r="I54" s="127" t="s">
         <v>20</v>
@@ -18238,16 +12026,14 @@
         <v>711</v>
       </c>
       <c r="E55" s="128" t="s">
-        <v>710</v>
-      </c>
-      <c r="F55" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F55" s="127"/>
       <c r="G55" s="128" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H55" s="127" t="s">
-        <v>711</v>
+        <v>175</v>
       </c>
       <c r="I55" s="127" t="s">
         <v>19</v>
@@ -18280,17 +12066,13 @@
         <v>711</v>
       </c>
       <c r="E56" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="F56" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F56" s="127"/>
       <c r="G56" s="128" t="s">
-        <v>426</v>
-      </c>
-      <c r="H56" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="H56" s="127"/>
       <c r="I56" s="127" t="s">
         <v>18</v>
       </c>
@@ -18320,16 +12102,16 @@
         <v>711</v>
       </c>
       <c r="E57" s="128" t="s">
-        <v>427</v>
+        <v>713</v>
       </c>
       <c r="F57" s="127" t="s">
-        <v>711</v>
+        <v>173</v>
       </c>
       <c r="G57" s="128" t="s">
-        <v>427</v>
+        <v>367</v>
       </c>
       <c r="H57" s="127" t="s">
-        <v>711</v>
+        <v>177</v>
       </c>
       <c r="I57" s="127" t="s">
         <v>17</v>
@@ -18364,16 +12146,14 @@
         <v>711</v>
       </c>
       <c r="E58" s="128" t="s">
-        <v>337</v>
-      </c>
-      <c r="F58" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F58" s="127"/>
       <c r="G58" s="128" t="s">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="H58" s="127" t="s">
-        <v>711</v>
+        <v>178</v>
       </c>
       <c r="I58" s="127" t="s">
         <v>16</v>
@@ -18406,16 +12186,14 @@
         <v>711</v>
       </c>
       <c r="E59" s="128" t="s">
-        <v>338</v>
-      </c>
-      <c r="F59" s="127" t="s">
-        <v>711</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="F59" s="127"/>
       <c r="G59" s="128" t="s">
-        <v>338</v>
+        <v>369</v>
       </c>
       <c r="H59" s="127" t="s">
-        <v>711</v>
+        <v>175</v>
       </c>
       <c r="I59" s="127" t="s">
         <v>15</v>
@@ -24261,12 +18039,12 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C1048576 L80:L81 N80:N81 P80:P81 E1:E1048576 G1:G1048576">
+  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 L80:L81 N80:N81 P80:P81">
     <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M80:M81 O80:O81 Q80:Q81 D1:D1048576 F1:F1048576 H1:H1048576">
+  <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576 M80:M81 O80:O81 Q80:Q81">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
@@ -24286,7 +18064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5437107-BC19-4F06-8786-19B78F32A4F0}">
   <dimension ref="A1:M169"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60AD753-1507-4830-97D2-99680C6D8BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594A1B5D-C124-498B-AA1E-D8C3852E5366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="165" windowWidth="16425" windowHeight="15510" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="timeList" sheetId="15" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3678" uniqueCount="741">
   <si>
     <t>日</t>
     <phoneticPr fontId="1"/>
@@ -6973,7 +6973,7 @@
         <v>474</v>
       </c>
       <c r="F106" s="136" t="s">
-        <v>173</v>
+        <v>304</v>
       </c>
       <c r="G106" s="137" t="s">
         <v>660</v>
@@ -11471,12 +11471,12 @@
   </sheetData>
   <autoFilter ref="B1:H169" xr:uid="{43214550-866B-4296-AF4D-B97EB9C891BA}"/>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="C1:C1048576 L80:L81 N80:N81 P80:P81 E1:E1048576 G1:G1048576">
+  <conditionalFormatting sqref="C1:C1048576 E1:E1048576 G1:G1048576 L80:L81 N80:N81 P80:P81">
     <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="'">
       <formula>NOT(ISERROR(SEARCH("'",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576 M80:M81 O80:O81 Q80:Q81 F1:F1048576 H1:H1048576">
+  <conditionalFormatting sqref="D1:D1048576 F1:F1048576 H1:H1048576 M80:M81 O80:O81 Q80:Q81">
     <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="例行維護中">
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71067BA-13DE-4F0F-BB52-CBEC43E195CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E2E9F2-6879-4A23-A32A-60CA38CB91E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -380,15 +380,6 @@
     <t>04:00_?</t>
   </si>
   <si>
-    <t>07:02_?</t>
-  </si>
-  <si>
-    <t>08:33_?</t>
-  </si>
-  <si>
-    <t>09:59_?</t>
-  </si>
-  <si>
     <t>05:05</t>
   </si>
   <si>
@@ -885,10 +876,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>07:47_?</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>02:25</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1360,6 +1347,22 @@
   </si>
   <si>
     <t>10:00</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:02</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>08:33</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>09:59</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>07:47</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2049,15 +2052,15 @@
         <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
@@ -2075,17 +2078,17 @@
         <v>75</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>58</v>
@@ -2105,13 +2108,13 @@
         <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>64</v>
@@ -2137,15 +2140,15 @@
         <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
@@ -2163,11 +2166,11 @@
         <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
@@ -2193,13 +2196,13 @@
         <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>94</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="4" t="s">
@@ -2223,17 +2226,17 @@
         <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
@@ -2251,17 +2254,17 @@
         <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>63</v>
@@ -2287,11 +2290,11 @@
         <v>95</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="4" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>62</v>
@@ -2311,17 +2314,17 @@
         <v>75</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
@@ -2339,7 +2342,7 @@
         <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
@@ -2349,7 +2352,7 @@
         <v>69</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>57</v>
@@ -2369,11 +2372,11 @@
         <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>64</v>
@@ -2399,17 +2402,17 @@
         <v>75</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
@@ -2427,11 +2430,11 @@
         <v>75</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>69</v>
@@ -2457,17 +2460,17 @@
         <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>62</v>
@@ -2487,15 +2490,15 @@
         <v>75</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
@@ -2513,19 +2516,19 @@
         <v>75</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>57</v>
@@ -2545,17 +2548,17 @@
         <v>75</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>62</v>
@@ -2575,15 +2578,15 @@
         <v>75</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
@@ -2601,17 +2604,17 @@
         <v>75</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>62</v>
@@ -2631,10 +2634,10 @@
         <v>75</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>42</v>
@@ -2643,7 +2646,7 @@
         <v>64</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>57</v>
@@ -2663,15 +2666,15 @@
         <v>75</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
@@ -2689,17 +2692,17 @@
         <v>75</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>54</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>63</v>
@@ -2719,15 +2722,15 @@
         <v>75</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
@@ -2745,7 +2748,7 @@
         <v>76</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="7" t="s">
@@ -2755,7 +2758,7 @@
         <v>69</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>62</v>
@@ -2775,19 +2778,19 @@
         <v>76</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>57</v>
@@ -2807,15 +2810,15 @@
         <v>76</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8" t="s">
@@ -2833,15 +2836,15 @@
         <v>76</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F29" s="8"/>
       <c r="G29" s="9" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>63</v>
@@ -2861,15 +2864,15 @@
         <v>76</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="8"/>
       <c r="G30" s="9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>62</v>
@@ -2889,19 +2892,19 @@
         <v>76</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>55</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="s">
@@ -2919,15 +2922,15 @@
         <v>76</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F32" s="8"/>
       <c r="G32" s="9" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>63</v>
@@ -2947,17 +2950,17 @@
         <v>76</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="9" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>63</v>
@@ -2977,19 +2980,19 @@
         <v>76</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>62</v>
@@ -3009,15 +3012,15 @@
         <v>76</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F35" s="8"/>
       <c r="G35" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8" t="s">
@@ -3035,17 +3038,17 @@
         <v>76</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="9" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>62</v>
@@ -3065,17 +3068,17 @@
         <v>76</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="9" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H37" s="8" t="s">
         <v>63</v>
@@ -3095,17 +3098,17 @@
         <v>76</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H38" s="8"/>
       <c r="I38" s="8" t="s">
@@ -3123,17 +3126,17 @@
         <v>76</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="9" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H39" s="8" t="s">
         <v>62</v>
@@ -3153,17 +3156,17 @@
         <v>76</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="9" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H40" s="8" t="s">
         <v>63</v>
@@ -3183,15 +3186,15 @@
         <v>76</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H41" s="8"/>
       <c r="I41" s="8" t="s">
@@ -3209,19 +3212,19 @@
         <v>76</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H42" s="8" t="s">
         <v>62</v>
@@ -3241,17 +3244,17 @@
         <v>76</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="9" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H43" s="8" t="s">
         <v>63</v>
@@ -3271,15 +3274,15 @@
         <v>76</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H44" s="8"/>
       <c r="I44" s="8" t="s">
@@ -3297,19 +3300,19 @@
         <v>76</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>69</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="H45" s="8" t="s">
         <v>62</v>
@@ -3329,15 +3332,15 @@
         <v>76</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="9" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="H46" s="8" t="s">
         <v>63</v>
@@ -3357,17 +3360,17 @@
         <v>76</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="9" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>64</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H47" s="8"/>
       <c r="I47" s="8" t="s">
@@ -3385,17 +3388,17 @@
         <v>76</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H48" s="8" t="s">
         <v>62</v>
@@ -3415,20 +3418,20 @@
         <v>76</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="43" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>1</v>
@@ -3445,17 +3448,17 @@
         <v>77</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="44" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>55</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>57</v>
@@ -3475,17 +3478,17 @@
         <v>77</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="13" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F51" s="12" t="s">
         <v>64</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="12" t="s">
@@ -3503,17 +3506,17 @@
         <v>77</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>63</v>
@@ -3535,13 +3538,13 @@
       <c r="C53" s="13"/>
       <c r="D53" s="12"/>
       <c r="E53" s="13" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="12" t="s">
@@ -3551,11 +3554,11 @@
         <v>28</v>
       </c>
       <c r="O53" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P53" s="12"/>
       <c r="Q53" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="R53" s="12"/>
     </row>
@@ -3569,7 +3572,7 @@
       <c r="C54" s="13"/>
       <c r="D54" s="12"/>
       <c r="E54" s="13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="13" t="s">
@@ -3585,7 +3588,7 @@
         <v>28</v>
       </c>
       <c r="O54" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P54" s="12"/>
       <c r="Q54" s="13" t="s">
@@ -3605,11 +3608,11 @@
       <c r="C55" s="13"/>
       <c r="D55" s="12"/>
       <c r="E55" s="13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="13" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>56</v>
@@ -3621,11 +3624,11 @@
         <v>28</v>
       </c>
       <c r="O55" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P55" s="12"/>
       <c r="Q55" s="13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="R55" s="12" t="s">
         <v>57</v>
@@ -3639,22 +3642,22 @@
         <v>77</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>18</v>
@@ -3663,11 +3666,11 @@
         <v>28</v>
       </c>
       <c r="O56" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P56" s="12"/>
       <c r="Q56" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="R56" s="12"/>
     </row>
@@ -3679,22 +3682,22 @@
         <v>77</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I57" s="12" t="s">
         <v>17</v>
@@ -3703,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="O57" s="13" t="s">
-        <v>239</v>
+        <v>361</v>
       </c>
       <c r="P57" s="12" t="s">
         <v>69</v>
       </c>
       <c r="Q57" s="13" t="s">
-        <v>101</v>
+        <v>358</v>
       </c>
       <c r="R57" s="12" t="s">
         <v>62</v>
@@ -3726,19 +3729,19 @@
         <v>83</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>83</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I58" s="12" t="s">
         <v>16</v>
@@ -3747,11 +3750,11 @@
         <v>28</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P58" s="12"/>
       <c r="Q58" s="13" t="s">
-        <v>102</v>
+        <v>359</v>
       </c>
       <c r="R58" s="12" t="s">
         <v>63</v>
@@ -3768,19 +3771,19 @@
         <v>84</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>84</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>82</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I59" s="12" t="s">
         <v>15</v>
@@ -3789,11 +3792,11 @@
         <v>28</v>
       </c>
       <c r="O59" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P59" s="12"/>
       <c r="Q59" s="13" t="s">
-        <v>103</v>
+        <v>360</v>
       </c>
       <c r="R59" s="12" t="s">
         <v>57</v>
@@ -3807,22 +3810,22 @@
         <v>77</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="I60" s="12" t="s">
         <v>14</v>
@@ -3831,13 +3834,13 @@
         <v>28</v>
       </c>
       <c r="M60" s="13" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N60" s="12" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O60" s="13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="P60" s="12" t="s">
         <v>69</v>
@@ -3851,15 +3854,15 @@
         <v>77</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F61" s="12"/>
       <c r="G61" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H61" s="12" t="s">
         <v>59</v>
@@ -3879,17 +3882,17 @@
         <v>77</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F62" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>59</v>
@@ -3909,17 +3912,17 @@
         <v>77</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F63" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H63" s="12"/>
       <c r="I63" s="12" t="s">
@@ -3937,7 +3940,7 @@
         <v>77</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>88</v>
@@ -3945,7 +3948,7 @@
       <c r="E64" s="12"/>
       <c r="F64" s="12"/>
       <c r="G64" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H64" s="12" t="s">
         <v>63</v>
@@ -3965,17 +3968,17 @@
         <v>77</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>55</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H65" s="12"/>
       <c r="I65" s="12" t="s">
@@ -3993,17 +3996,17 @@
         <v>77</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="13" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F66" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H66" s="12" t="s">
         <v>62</v>
@@ -4031,7 +4034,7 @@
       <c r="E67" s="12"/>
       <c r="F67" s="12"/>
       <c r="G67" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>59</v>
@@ -4051,11 +4054,11 @@
         <v>77</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="13" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F68" s="12" t="s">
         <v>55</v>
@@ -4077,11 +4080,11 @@
         <v>77</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F69" s="12" t="s">
         <v>54</v>
@@ -4107,13 +4110,13 @@
         <v>77</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="12"/>
       <c r="G70" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H70" s="12" t="s">
         <v>56</v>
@@ -4133,13 +4136,13 @@
         <v>77</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D71" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F71" s="12" t="s">
         <v>54</v>
@@ -4161,17 +4164,17 @@
         <v>77</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F72" s="12" t="s">
         <v>54</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>57</v>
@@ -4199,7 +4202,7 @@
       <c r="E73" s="14"/>
       <c r="F73" s="14"/>
       <c r="G73" s="34" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>57</v>
@@ -4219,7 +4222,7 @@
         <v>78</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D74" s="15"/>
       <c r="E74" s="35" t="s">
@@ -4229,7 +4232,7 @@
         <v>54</v>
       </c>
       <c r="G74" s="35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H74" s="15" t="s">
         <v>63</v>
@@ -4249,11 +4252,11 @@
         <v>78</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D75" s="16"/>
       <c r="E75" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>55</v>
@@ -4275,7 +4278,7 @@
         <v>78</v>
       </c>
       <c r="C76" s="17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D76" s="16" t="s">
         <v>86</v>
@@ -4283,7 +4286,7 @@
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H76" s="16" t="s">
         <v>56</v>
@@ -4303,17 +4306,17 @@
         <v>78</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D77" s="16"/>
       <c r="E77" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="H77" s="16" t="s">
         <v>59</v>
@@ -4333,13 +4336,13 @@
         <v>78</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>54</v>
@@ -4361,13 +4364,13 @@
         <v>78</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D79" s="16"/>
       <c r="E79" s="16"/>
       <c r="F79" s="16"/>
       <c r="G79" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H79" s="16" t="s">
         <v>62</v>
@@ -4389,16 +4392,16 @@
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
       <c r="E80" s="17" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>64</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>18</v>
@@ -4417,7 +4420,7 @@
       <c r="C81" s="16"/>
       <c r="D81" s="16"/>
       <c r="E81" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>69</v>
@@ -4439,15 +4442,15 @@
         <v>78</v>
       </c>
       <c r="C82" s="42" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
       <c r="G82" s="17" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H82" s="16" t="s">
         <v>57</v>
@@ -4467,17 +4470,17 @@
         <v>78</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D83" s="16"/>
       <c r="E83" s="17" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>55</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H83" s="16" t="s">
         <v>57</v>
@@ -4497,11 +4500,11 @@
         <v>78</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D84" s="16"/>
       <c r="E84" s="17" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F84" s="16" t="s">
         <v>54</v>
@@ -4523,15 +4526,15 @@
         <v>78</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E85" s="16"/>
       <c r="F85" s="16"/>
       <c r="G85" s="17" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H85" s="16" t="s">
         <v>58</v>
@@ -4551,17 +4554,17 @@
         <v>78</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D86" s="16"/>
       <c r="E86" s="17" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F86" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H86" s="16" t="s">
         <v>56</v>
@@ -4581,11 +4584,11 @@
         <v>78</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D87" s="16"/>
       <c r="E87" s="17" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F87" s="16" t="s">
         <v>54</v>
@@ -4607,17 +4610,17 @@
         <v>78</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D88" s="16"/>
       <c r="E88" s="17" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F88" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H88" s="16" t="s">
         <v>59</v>
@@ -4637,10 +4640,10 @@
         <v>78</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E89" s="16"/>
       <c r="F89" s="16"/>
@@ -4665,11 +4668,11 @@
         <v>78</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D90" s="16"/>
       <c r="E90" s="17" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>55</v>
@@ -4691,17 +4694,17 @@
         <v>78</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D91" s="16"/>
       <c r="E91" s="17" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H91" s="16" t="s">
         <v>59</v>
@@ -4721,13 +4724,13 @@
         <v>78</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D92" s="16"/>
       <c r="E92" s="16"/>
       <c r="F92" s="16"/>
       <c r="G92" s="17" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H92" s="16" t="s">
         <v>59</v>
@@ -4747,11 +4750,11 @@
         <v>78</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D93" s="16"/>
       <c r="E93" s="17" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>55</v>
@@ -4773,19 +4776,19 @@
         <v>78</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D94" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H94" s="16" t="s">
         <v>59</v>
@@ -4805,13 +4808,13 @@
         <v>78</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D95" s="16"/>
       <c r="E95" s="16"/>
       <c r="F95" s="16"/>
       <c r="G95" s="17" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H95" s="16" t="s">
         <v>58</v>
@@ -4831,11 +4834,11 @@
         <v>78</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D96" s="16"/>
       <c r="E96" s="17" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>54</v>
@@ -4857,7 +4860,7 @@
         <v>78</v>
       </c>
       <c r="C97" s="18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D97" s="18"/>
       <c r="E97" s="36" t="s">
@@ -4867,7 +4870,7 @@
         <v>55</v>
       </c>
       <c r="G97" s="36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H97" s="18" t="s">
         <v>59</v>
@@ -4890,10 +4893,10 @@
         <v>38</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E98" s="19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F98" s="20" t="s">
         <v>54</v>
@@ -4919,13 +4922,13 @@
         <v>79</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D99" s="21"/>
       <c r="E99" s="21"/>
       <c r="F99" s="21"/>
       <c r="G99" s="22" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H99" s="21" t="s">
         <v>58</v>
@@ -4945,13 +4948,13 @@
         <v>79</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D100" s="21" t="s">
         <v>89</v>
       </c>
       <c r="E100" s="22" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F100" s="21" t="s">
         <v>54</v>
@@ -4973,11 +4976,11 @@
         <v>79</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D101" s="21"/>
       <c r="E101" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F101" s="21" t="s">
         <v>55</v>
@@ -5003,13 +5006,13 @@
         <v>79</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D102" s="21"/>
       <c r="E102" s="21"/>
       <c r="F102" s="21"/>
       <c r="G102" s="22" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H102" s="21" t="s">
         <v>58</v>
@@ -5029,13 +5032,13 @@
         <v>79</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D103" s="21" t="s">
         <v>90</v>
       </c>
       <c r="E103" s="22" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F103" s="21" t="s">
         <v>54</v>
@@ -5057,13 +5060,13 @@
         <v>79</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D104" s="21"/>
       <c r="E104" s="21"/>
       <c r="F104" s="21"/>
       <c r="G104" s="22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H104" s="21" t="s">
         <v>56</v>
@@ -5083,17 +5086,17 @@
         <v>79</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D105" s="21"/>
       <c r="E105" s="22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F105" s="21" t="s">
         <v>54</v>
       </c>
       <c r="G105" s="22" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H105" s="21" t="s">
         <v>58</v>
@@ -5113,17 +5116,17 @@
         <v>79</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D106" s="21"/>
       <c r="E106" s="22" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F106" s="21" t="s">
         <v>69</v>
       </c>
       <c r="G106" s="22" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H106" s="21" t="s">
         <v>59</v>
@@ -5143,10 +5146,10 @@
         <v>79</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E107" s="21"/>
       <c r="F107" s="21"/>
@@ -5167,11 +5170,11 @@
         <v>79</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D108" s="21"/>
       <c r="E108" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F108" s="21" t="s">
         <v>54</v>
@@ -5200,16 +5203,16 @@
         <v>41</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F109" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G109" s="22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H109" s="21" t="s">
         <v>59</v>
@@ -5229,13 +5232,13 @@
         <v>79</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D110" s="21"/>
       <c r="E110" s="21"/>
       <c r="F110" s="21"/>
       <c r="G110" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H110" s="21"/>
       <c r="I110" s="21" t="s">
@@ -5253,17 +5256,17 @@
         <v>79</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D111" s="21"/>
       <c r="E111" s="22" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F111" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G111" s="22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="H111" s="21" t="s">
         <v>57</v>
@@ -5283,17 +5286,17 @@
         <v>79</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D112" s="21"/>
       <c r="E112" s="22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F112" s="21" t="s">
         <v>54</v>
       </c>
       <c r="G112" s="22" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H112" s="21" t="s">
         <v>58</v>
@@ -5313,15 +5316,15 @@
         <v>79</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E113" s="21"/>
       <c r="F113" s="21"/>
       <c r="G113" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H113" s="21"/>
       <c r="I113" s="21" t="s">
@@ -5339,17 +5342,17 @@
         <v>79</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D114" s="21"/>
       <c r="E114" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F114" s="21" t="s">
         <v>55</v>
       </c>
       <c r="G114" s="22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H114" s="21" t="s">
         <v>58</v>
@@ -5369,17 +5372,17 @@
         <v>79</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D115" s="21"/>
       <c r="E115" s="22" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F115" s="21" t="s">
         <v>54</v>
       </c>
       <c r="G115" s="22" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H115" s="21" t="s">
         <v>62</v>
@@ -5399,13 +5402,13 @@
         <v>79</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D116" s="21"/>
       <c r="E116" s="21"/>
       <c r="F116" s="21"/>
       <c r="G116" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H116" s="21"/>
       <c r="I116" s="21" t="s">
@@ -5435,7 +5438,7 @@
         <v>69</v>
       </c>
       <c r="G117" s="22" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H117" s="21" t="s">
         <v>59</v>
@@ -5455,17 +5458,17 @@
         <v>79</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D118" s="21"/>
       <c r="E118" s="22" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F118" s="21" t="s">
         <v>64</v>
       </c>
       <c r="G118" s="22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H118" s="21" t="s">
         <v>59</v>
@@ -5485,13 +5488,13 @@
         <v>79</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D119" s="21"/>
       <c r="E119" s="21"/>
       <c r="F119" s="21"/>
       <c r="G119" s="21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H119" s="21"/>
       <c r="I119" s="21" t="s">
@@ -5509,19 +5512,19 @@
         <v>79</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E120" s="22" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F120" s="21" t="s">
         <v>69</v>
       </c>
       <c r="G120" s="22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H120" s="21" t="s">
         <v>57</v>
@@ -5541,17 +5544,17 @@
         <v>79</v>
       </c>
       <c r="C121" s="23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D121" s="23"/>
       <c r="E121" s="24" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F121" s="23" t="s">
         <v>64</v>
       </c>
       <c r="G121" s="24" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="H121" s="23" t="s">
         <v>56</v>
@@ -5571,17 +5574,17 @@
         <v>80</v>
       </c>
       <c r="C122" s="25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D122" s="25"/>
       <c r="E122" s="26" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F122" s="25" t="s">
         <v>69</v>
       </c>
       <c r="G122" s="26" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H122" s="25" t="s">
         <v>62</v>
@@ -5601,15 +5604,15 @@
         <v>80</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E123" s="28"/>
       <c r="F123" s="28"/>
       <c r="G123" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H123" s="28"/>
       <c r="I123" s="28" t="s">
@@ -5627,17 +5630,17 @@
         <v>80</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D124" s="28"/>
       <c r="E124" s="27" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F124" s="28" t="s">
         <v>54</v>
       </c>
       <c r="G124" s="27" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H124" s="28" t="s">
         <v>57</v>
@@ -5657,17 +5660,17 @@
         <v>80</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D125" s="28"/>
       <c r="E125" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F125" s="28" t="s">
         <v>69</v>
       </c>
       <c r="G125" s="27" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H125" s="28" t="s">
         <v>62</v>
@@ -5687,13 +5690,13 @@
         <v>80</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D126" s="28"/>
       <c r="E126" s="28"/>
       <c r="F126" s="28"/>
       <c r="G126" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H126" s="28"/>
       <c r="I126" s="28" t="s">
@@ -5711,19 +5714,19 @@
         <v>80</v>
       </c>
       <c r="C127" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E127" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F127" s="28" t="s">
         <v>64</v>
       </c>
       <c r="G127" s="27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H127" s="28" t="s">
         <v>63</v>
@@ -5743,7 +5746,7 @@
         <v>80</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D128" s="28"/>
       <c r="E128" s="27" t="s">
@@ -5753,7 +5756,7 @@
         <v>69</v>
       </c>
       <c r="G128" s="27" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H128" s="28" t="s">
         <v>57</v>
@@ -5773,13 +5776,13 @@
         <v>80</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D129" s="28"/>
       <c r="E129" s="27"/>
       <c r="F129" s="28"/>
       <c r="G129" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H129" s="28"/>
       <c r="I129" s="28" t="s">
@@ -5797,19 +5800,19 @@
         <v>80</v>
       </c>
       <c r="C130" s="27" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D130" s="28" t="s">
         <v>92</v>
       </c>
       <c r="E130" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F130" s="28" t="s">
         <v>64</v>
       </c>
       <c r="G130" s="27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H130" s="28" t="s">
         <v>57</v>
@@ -5829,15 +5832,15 @@
         <v>80</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D131" s="28"/>
       <c r="E131" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F131" s="28"/>
       <c r="G131" s="27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H131" s="28" t="s">
         <v>63</v>
@@ -5857,7 +5860,7 @@
         <v>80</v>
       </c>
       <c r="C132" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D132" s="28"/>
       <c r="E132" s="27" t="s">
@@ -5867,7 +5870,7 @@
         <v>69</v>
       </c>
       <c r="G132" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H132" s="28"/>
       <c r="I132" s="28" t="s">
@@ -5885,10 +5888,10 @@
         <v>80</v>
       </c>
       <c r="C133" s="27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>48</v>
@@ -5897,7 +5900,7 @@
         <v>69</v>
       </c>
       <c r="G133" s="27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H133" s="28" t="s">
         <v>62</v>
@@ -5917,17 +5920,17 @@
         <v>80</v>
       </c>
       <c r="C134" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D134" s="28"/>
       <c r="E134" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F134" s="28" t="s">
         <v>64</v>
       </c>
       <c r="G134" s="27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H134" s="28" t="s">
         <v>62</v>
@@ -5947,15 +5950,15 @@
         <v>80</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D135" s="28"/>
       <c r="E135" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F135" s="28"/>
       <c r="G135" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H135" s="28"/>
       <c r="I135" s="28" t="s">
@@ -5973,19 +5976,19 @@
         <v>80</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D136" s="28" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E136" s="27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F136" s="28" t="s">
         <v>69</v>
       </c>
       <c r="G136" s="27" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H136" s="28" t="s">
         <v>63</v>
@@ -6005,17 +6008,17 @@
         <v>80</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D137" s="28"/>
       <c r="E137" s="27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F137" s="28" t="s">
         <v>69</v>
       </c>
       <c r="G137" s="27" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H137" s="28" t="s">
         <v>62</v>
@@ -6035,15 +6038,15 @@
         <v>80</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D138" s="28"/>
       <c r="E138" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F138" s="28"/>
       <c r="G138" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H138" s="28"/>
       <c r="I138" s="28">
@@ -6061,19 +6064,19 @@
         <v>80</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D139" s="28" t="s">
         <v>93</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F139" s="28" t="s">
         <v>69</v>
       </c>
       <c r="G139" s="27" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H139" s="28" t="s">
         <v>57</v>
@@ -6093,13 +6096,13 @@
         <v>80</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D140" s="28"/>
       <c r="E140" s="28"/>
       <c r="F140" s="28"/>
       <c r="G140" s="27" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H140" s="28" t="s">
         <v>57</v>
@@ -6119,17 +6122,17 @@
         <v>80</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D141" s="28"/>
       <c r="E141" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F141" s="28" t="s">
         <v>69</v>
       </c>
       <c r="G141" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H141" s="28"/>
       <c r="I141" s="28" t="s">
@@ -6147,7 +6150,7 @@
         <v>80</v>
       </c>
       <c r="C142" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D142" s="28"/>
       <c r="E142" s="27" t="s">
@@ -6157,7 +6160,7 @@
         <v>64</v>
       </c>
       <c r="G142" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H142" s="28" t="s">
         <v>62</v>
@@ -6177,19 +6180,19 @@
         <v>80</v>
       </c>
       <c r="C143" s="27" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D143" s="28" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E143" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F143" s="28" t="s">
         <v>64</v>
       </c>
       <c r="G143" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H143" s="28" t="s">
         <v>62</v>
@@ -6209,15 +6212,15 @@
         <v>80</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D144" s="28"/>
       <c r="E144" s="28" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F144" s="28"/>
       <c r="G144" s="27" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H144" s="28" t="s">
         <v>63</v>
@@ -6237,17 +6240,17 @@
         <v>80</v>
       </c>
       <c r="C145" s="29" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D145" s="29"/>
       <c r="E145" s="37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F145" s="29" t="s">
         <v>64</v>
       </c>
       <c r="G145" s="29" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H145" s="29"/>
       <c r="I145" s="29" t="s">
@@ -6265,17 +6268,17 @@
         <v>81</v>
       </c>
       <c r="C146" s="30" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D146" s="30"/>
       <c r="E146" s="38" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F146" s="30" t="s">
         <v>69</v>
       </c>
       <c r="G146" s="30" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H146" s="30"/>
       <c r="I146" s="30" t="s">
@@ -6293,15 +6296,15 @@
         <v>81</v>
       </c>
       <c r="C147" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D147" s="31"/>
       <c r="E147" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F147" s="31"/>
       <c r="G147" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H147" s="31" t="s">
         <v>62</v>
@@ -6321,17 +6324,17 @@
         <v>81</v>
       </c>
       <c r="C148" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D148" s="31"/>
       <c r="E148" s="32" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F148" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G148" s="32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H148" s="31" t="s">
         <v>63</v>
@@ -6351,19 +6354,19 @@
         <v>81</v>
       </c>
       <c r="C149" s="32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D149" s="31" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E149" s="32" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F149" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G149" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H149" s="31"/>
       <c r="I149" s="31" t="s">
@@ -6381,11 +6384,11 @@
         <v>81</v>
       </c>
       <c r="C150" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D150" s="31"/>
       <c r="E150" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F150" s="31"/>
       <c r="G150" s="32" t="s">
@@ -6409,7 +6412,7 @@
         <v>81</v>
       </c>
       <c r="C151" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D151" s="31"/>
       <c r="E151" s="32" t="s">
@@ -6419,7 +6422,7 @@
         <v>69</v>
       </c>
       <c r="G151" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H151" s="31" t="s">
         <v>57</v>
@@ -6439,17 +6442,17 @@
         <v>81</v>
       </c>
       <c r="C152" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D152" s="31"/>
       <c r="E152" s="32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F152" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G152" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H152" s="31"/>
       <c r="I152" s="31" t="s">
@@ -6467,17 +6470,17 @@
         <v>81</v>
       </c>
       <c r="C153" s="32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D153" s="31" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E153" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F153" s="31"/>
       <c r="G153" s="32" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H153" s="31" t="s">
         <v>63</v>
@@ -6497,7 +6500,7 @@
         <v>81</v>
       </c>
       <c r="C154" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D154" s="31"/>
       <c r="E154" s="32" t="s">
@@ -6527,17 +6530,17 @@
         <v>81</v>
       </c>
       <c r="C155" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D155" s="31"/>
       <c r="E155" s="32" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F155" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G155" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H155" s="31"/>
       <c r="I155" s="31" t="s">
@@ -6555,17 +6558,17 @@
         <v>81</v>
       </c>
       <c r="C156" s="32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D156" s="31" t="s">
         <v>90</v>
       </c>
       <c r="E156" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="32" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H156" s="31" t="s">
         <v>63</v>
@@ -6585,17 +6588,17 @@
         <v>81</v>
       </c>
       <c r="C157" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D157" s="31"/>
       <c r="E157" s="32" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F157" s="31" t="s">
         <v>54</v>
       </c>
       <c r="G157" s="32" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H157" s="31" t="s">
         <v>62</v>
@@ -6615,17 +6618,17 @@
         <v>81</v>
       </c>
       <c r="C158" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D158" s="31"/>
       <c r="E158" s="32" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F158" s="31" t="s">
         <v>69</v>
       </c>
       <c r="G158" s="32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H158" s="31" t="s">
         <v>57</v>
@@ -6648,10 +6651,10 @@
         <v>49</v>
       </c>
       <c r="D159" s="31" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E159" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F159" s="31"/>
       <c r="G159" s="31"/>
@@ -6671,17 +6674,17 @@
         <v>81</v>
       </c>
       <c r="C160" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D160" s="31"/>
       <c r="E160" s="32" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F160" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G160" s="32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H160" s="31" t="s">
         <v>62</v>
@@ -6701,17 +6704,17 @@
         <v>81</v>
       </c>
       <c r="C161" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D161" s="31"/>
       <c r="E161" s="32" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F161" s="31" t="s">
         <v>55</v>
       </c>
       <c r="G161" s="32" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H161" s="31" t="s">
         <v>57</v>
@@ -6731,17 +6734,17 @@
         <v>81</v>
       </c>
       <c r="C162" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="D162" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="D162" s="31" t="s">
-        <v>260</v>
-      </c>
       <c r="E162" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F162" s="31"/>
       <c r="G162" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H162" s="31"/>
       <c r="I162" s="31" t="s">
@@ -6759,17 +6762,17 @@
         <v>81</v>
       </c>
       <c r="C163" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D163" s="31"/>
       <c r="E163" s="32" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F163" s="31" t="s">
         <v>69</v>
       </c>
       <c r="G163" s="32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H163" s="31" t="s">
         <v>62</v>
@@ -6789,17 +6792,17 @@
         <v>81</v>
       </c>
       <c r="C164" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D164" s="31"/>
       <c r="E164" s="32" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F164" s="31" t="s">
         <v>69</v>
       </c>
       <c r="G164" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H164" s="31"/>
       <c r="I164" s="31" t="s">
@@ -6817,15 +6820,15 @@
         <v>81</v>
       </c>
       <c r="C165" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D165" s="31"/>
       <c r="E165" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F165" s="31"/>
       <c r="G165" s="32" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H165" s="31" t="s">
         <v>63</v>
@@ -6845,19 +6848,19 @@
         <v>81</v>
       </c>
       <c r="C166" s="32" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D166" s="31" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E166" s="32" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F166" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G166" s="32" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H166" s="31" t="s">
         <v>57</v>
@@ -6877,17 +6880,17 @@
         <v>81</v>
       </c>
       <c r="C167" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D167" s="31"/>
       <c r="E167" s="32" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F167" s="31" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G167" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H167" s="31"/>
       <c r="I167" s="31" t="s">
@@ -6905,15 +6908,15 @@
         <v>81</v>
       </c>
       <c r="C168" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D168" s="31"/>
       <c r="E168" s="31" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F168" s="31"/>
       <c r="G168" s="32" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H168" s="31" t="s">
         <v>57</v>
@@ -6933,22 +6936,22 @@
         <v>81</v>
       </c>
       <c r="C169" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="D169" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="D169" s="31" t="s">
-        <v>304</v>
-      </c>
       <c r="E169" s="32" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F169" s="31" t="s">
         <v>64</v>
       </c>
       <c r="G169" s="32" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H169" s="31" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I169" s="31" t="s">
         <v>1</v>
@@ -9628,24 +9631,24 @@
       <formula>NOT(ISERROR(SEARCH("例行維護中",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O53:O59 Q53:Q59">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",O53)))</formula>
+  <conditionalFormatting sqref="O53:O60 M60">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="'">
+      <formula>NOT(ISERROR(SEARCH("'",M53)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P53:P59 R53:R59">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",P53)))</formula>
+  <conditionalFormatting sqref="P53:P60 N60">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",N53)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M60 O60">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="'">
-      <formula>NOT(ISERROR(SEARCH("'",M60)))</formula>
+  <conditionalFormatting sqref="Q53:Q59">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="'">
+      <formula>NOT(ISERROR(SEARCH("'",Q53)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N60 P60">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="例行維護中">
-      <formula>NOT(ISERROR(SEARCH("例行維護中",N60)))</formula>
+  <conditionalFormatting sqref="R53:R59">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="例行維護中">
+      <formula>NOT(ISERROR(SEARCH("例行維護中",R53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9195DD-78DD-4569-A0FD-6C6B55748614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6375836-B781-4D0F-A249-1BE58D422B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="53">
   <si>
     <t>23</t>
   </si>
@@ -148,30 +148,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>06:00</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>07:00</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Week</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>gishikiTime</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>shiraoTime</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sengenTime</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -227,12 +208,65 @@
   <si>
     <t>09:00</t>
   </si>
+  <si>
+    <r>
+      <t>Week-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>zh</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>gishiki</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>-t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ime</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>shirao-time</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sengen-time</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +322,22 @@
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="10">
@@ -922,28 +972,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="40" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="44" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B1" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
@@ -1696,22 +1746,22 @@
         <v>28</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="18" customHeight="1">
@@ -1722,22 +1772,22 @@
         <v>28</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="18" customHeight="1">
@@ -1748,22 +1798,22 @@
         <v>28</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="18" customHeight="1">
@@ -1777,19 +1827,19 @@
         <v>33</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="18" customHeight="1">
@@ -1803,19 +1853,19 @@
         <v>34</v>
       </c>
       <c r="D59" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E59" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E59" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="F59" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G59" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G59" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="H59" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="18" customHeight="1">
@@ -1829,19 +1879,19 @@
         <v>25</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="18" customHeight="1">

--- a/files/timeList.xlsx
+++ b/files/timeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mutsu\Pictures\BnSNEOtimeList\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6375836-B781-4D0F-A249-1BE58D422B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B5A3BE-13BA-4FAB-8CC1-AC597832D057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="758" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="55">
   <si>
     <t>23</t>
   </si>
@@ -210,23 +210,6 @@
   </si>
   <si>
     <r>
-      <t>Week-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>zh</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
       <t>gishiki</t>
     </r>
     <r>
@@ -261,12 +244,45 @@
     <t>sengen-time</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>AAAAAA</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>04:59</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>eek</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +352,21 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="136"/>
     </font>
@@ -451,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -567,9 +598,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -640,6 +668,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -952,14 +989,14 @@
   <dimension ref="A1:H1055"/>
   <sheetFormatPr defaultColWidth="14.25" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.25" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.375" style="1" bestFit="1" customWidth="1"/>
@@ -970,34 +1007,34 @@
     <col min="16" max="16384" width="14.25" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="40" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:8" s="39" customFormat="1" ht="18" customHeight="1">
+      <c r="A1" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="65" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1011,7 +1048,7 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="44" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1025,7 +1062,7 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="44" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1039,7 +1076,7 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="44" t="s">
         <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1053,7 +1090,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="44" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1067,7 +1104,7 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" ht="18" customHeight="1">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="44" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1081,7 +1118,7 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="44" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1095,7 +1132,7 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" ht="18" customHeight="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="44" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1109,7 +1146,7 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="44" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1123,7 +1160,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" ht="18" customHeight="1">
-      <c r="A11" s="45" t="s">
+      <c r="A11" s="44" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1137,7 +1174,7 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="18" customHeight="1">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="44" t="s">
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1151,7 +1188,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1">
-      <c r="A13" s="45" t="s">
+      <c r="A13" s="44" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1165,7 +1202,7 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="44" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1179,7 +1216,7 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1193,7 +1230,7 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="44" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1207,7 +1244,7 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="44" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1221,7 +1258,7 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" ht="18" customHeight="1">
-      <c r="A18" s="45" t="s">
+      <c r="A18" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1235,7 +1272,7 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" ht="18" customHeight="1">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1249,7 +1286,7 @@
       <c r="H19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="18" customHeight="1">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="44" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1263,7 +1300,7 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1">
-      <c r="A21" s="45" t="s">
+      <c r="A21" s="44" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1277,7 +1314,7 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="44" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1291,7 +1328,7 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="44" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1305,7 +1342,7 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1">
-      <c r="A24" s="45" t="s">
+      <c r="A24" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1319,7 +1356,7 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="45" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1333,7 +1370,7 @@
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1">
-      <c r="A26" s="47" t="s">
+      <c r="A26" s="46" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -1347,7 +1384,7 @@
       <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="47" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="8" t="s">
@@ -1361,7 +1398,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" ht="18" customHeight="1">
-      <c r="A28" s="48" t="s">
+      <c r="A28" s="47" t="s">
         <v>21</v>
       </c>
       <c r="B28" s="8" t="s">
@@ -1375,7 +1412,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" ht="18" customHeight="1">
-      <c r="A29" s="48" t="s">
+      <c r="A29" s="47" t="s">
         <v>20</v>
       </c>
       <c r="B29" s="8" t="s">
@@ -1389,7 +1426,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" ht="18" customHeight="1">
-      <c r="A30" s="48" t="s">
+      <c r="A30" s="47" t="s">
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
@@ -1403,7 +1440,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="18" customHeight="1">
-      <c r="A31" s="48" t="s">
+      <c r="A31" s="47" t="s">
         <v>18</v>
       </c>
       <c r="B31" s="8" t="s">
@@ -1417,7 +1454,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" ht="18" customHeight="1">
-      <c r="A32" s="48" t="s">
+      <c r="A32" s="47" t="s">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="s">
@@ -1431,7 +1468,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="18" customHeight="1">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="47" t="s">
         <v>16</v>
       </c>
       <c r="B33" s="8" t="s">
@@ -1445,7 +1482,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" ht="18" customHeight="1">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="47" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="8" t="s">
@@ -1459,7 +1496,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1">
-      <c r="A35" s="48" t="s">
+      <c r="A35" s="47" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
@@ -1473,7 +1510,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="47" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -1487,7 +1524,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" ht="18" customHeight="1">
-      <c r="A37" s="48" t="s">
+      <c r="A37" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B37" s="8" t="s">
@@ -1501,7 +1538,7 @@
       <c r="H37" s="8"/>
     </row>
     <row r="38" spans="1:8" ht="18" customHeight="1">
-      <c r="A38" s="48" t="s">
+      <c r="A38" s="47" t="s">
         <v>11</v>
       </c>
       <c r="B38" s="8" t="s">
@@ -1515,7 +1552,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" ht="18" customHeight="1">
-      <c r="A39" s="48" t="s">
+      <c r="A39" s="47" t="s">
         <v>10</v>
       </c>
       <c r="B39" s="8" t="s">
@@ -1529,7 +1566,7 @@
       <c r="H39" s="8"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1">
-      <c r="A40" s="48" t="s">
+      <c r="A40" s="47" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="8" t="s">
@@ -1543,7 +1580,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="18" customHeight="1">
-      <c r="A41" s="48" t="s">
+      <c r="A41" s="47" t="s">
         <v>8</v>
       </c>
       <c r="B41" s="8" t="s">
@@ -1557,7 +1594,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="18" customHeight="1">
-      <c r="A42" s="48" t="s">
+      <c r="A42" s="47" t="s">
         <v>7</v>
       </c>
       <c r="B42" s="8" t="s">
@@ -1571,7 +1608,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1">
-      <c r="A43" s="48" t="s">
+      <c r="A43" s="47" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="8" t="s">
@@ -1585,7 +1622,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" ht="18" customHeight="1">
-      <c r="A44" s="48" t="s">
+      <c r="A44" s="47" t="s">
         <v>5</v>
       </c>
       <c r="B44" s="8" t="s">
@@ -1599,7 +1636,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="18" customHeight="1">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="47" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="8" t="s">
@@ -1613,7 +1650,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" ht="18" customHeight="1">
-      <c r="A46" s="48" t="s">
+      <c r="A46" s="47" t="s">
         <v>3</v>
       </c>
       <c r="B46" s="8" t="s">
@@ -1627,7 +1664,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="18" customHeight="1">
-      <c r="A47" s="48" t="s">
+      <c r="A47" s="47" t="s">
         <v>2</v>
       </c>
       <c r="B47" s="8" t="s">
@@ -1641,7 +1678,7 @@
       <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:8" ht="18" customHeight="1">
-      <c r="A48" s="48" t="s">
+      <c r="A48" s="47" t="s">
         <v>1</v>
       </c>
       <c r="B48" s="8" t="s">
@@ -1655,21 +1692,21 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A49" s="49" t="s">
+      <c r="A49" s="48" t="s">
         <v>0</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C49" s="42"/>
+      <c r="C49" s="41"/>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
-      <c r="G49" s="42"/>
+      <c r="G49" s="41"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" ht="18" customHeight="1">
-      <c r="A50" s="50" t="s">
+      <c r="A50" s="49" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="11" t="s">
@@ -1677,13 +1714,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="43"/>
+      <c r="E50" s="42"/>
       <c r="F50" s="11"/>
-      <c r="G50" s="43"/>
+      <c r="G50" s="42"/>
       <c r="H50" s="11"/>
     </row>
     <row r="51" spans="1:8" ht="18" customHeight="1">
-      <c r="A51" s="51" t="s">
+      <c r="A51" s="50" t="s">
         <v>22</v>
       </c>
       <c r="B51" s="12" t="s">
@@ -1697,7 +1734,7 @@
       <c r="H51" s="12"/>
     </row>
     <row r="52" spans="1:8" ht="18" customHeight="1">
-      <c r="A52" s="51" t="s">
+      <c r="A52" s="50" t="s">
         <v>21</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -1711,7 +1748,7 @@
       <c r="H52" s="12"/>
     </row>
     <row r="53" spans="1:8" ht="18" customHeight="1">
-      <c r="A53" s="51" t="s">
+      <c r="A53" s="50" t="s">
         <v>20</v>
       </c>
       <c r="B53" s="12" t="s">
@@ -1725,21 +1762,25 @@
       <c r="H53" s="12"/>
     </row>
     <row r="54" spans="1:8" ht="18" customHeight="1">
-      <c r="A54" s="51" t="s">
+      <c r="A54" s="50" t="s">
         <v>19</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="12"/>
+      <c r="C54" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="64" t="s">
+        <v>52</v>
+      </c>
       <c r="E54" s="13"/>
       <c r="F54" s="12"/>
       <c r="G54" s="13"/>
       <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" ht="18" customHeight="1">
-      <c r="A55" s="51" t="s">
+      <c r="A55" s="50" t="s">
         <v>18</v>
       </c>
       <c r="B55" s="12" t="s">
@@ -1765,7 +1806,7 @@
       </c>
     </row>
     <row r="56" spans="1:8" ht="18" customHeight="1">
-      <c r="A56" s="51" t="s">
+      <c r="A56" s="50" t="s">
         <v>17</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -1791,7 +1832,7 @@
       </c>
     </row>
     <row r="57" spans="1:8" ht="18" customHeight="1">
-      <c r="A57" s="51" t="s">
+      <c r="A57" s="50" t="s">
         <v>16</v>
       </c>
       <c r="B57" s="12" t="s">
@@ -1817,7 +1858,7 @@
       </c>
     </row>
     <row r="58" spans="1:8" ht="18" customHeight="1">
-      <c r="A58" s="51" t="s">
+      <c r="A58" s="50" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="12" t="s">
@@ -1843,7 +1884,7 @@
       </c>
     </row>
     <row r="59" spans="1:8" ht="18" customHeight="1">
-      <c r="A59" s="51" t="s">
+      <c r="A59" s="50" t="s">
         <v>14</v>
       </c>
       <c r="B59" s="12" t="s">
@@ -1869,7 +1910,7 @@
       </c>
     </row>
     <row r="60" spans="1:8" ht="18" customHeight="1">
-      <c r="A60" s="51" t="s">
+      <c r="A60" s="50" t="s">
         <v>13</v>
       </c>
       <c r="B60" s="12" t="s">
@@ -1895,7 +1936,7 @@
       </c>
     </row>
     <row r="61" spans="1:8" ht="18" customHeight="1">
-      <c r="A61" s="51" t="s">
+      <c r="A61" s="50" t="s">
         <v>12</v>
       </c>
       <c r="B61" s="12" t="s">
@@ -1909,7 +1950,7 @@
       <c r="H61" s="12"/>
     </row>
     <row r="62" spans="1:8" ht="18" customHeight="1">
-      <c r="A62" s="51" t="s">
+      <c r="A62" s="50" t="s">
         <v>11</v>
       </c>
       <c r="B62" s="12" t="s">
@@ -1923,7 +1964,7 @@
       <c r="H62" s="12"/>
     </row>
     <row r="63" spans="1:8" ht="18" customHeight="1">
-      <c r="A63" s="51" t="s">
+      <c r="A63" s="50" t="s">
         <v>10</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -1937,7 +1978,7 @@
       <c r="H63" s="12"/>
     </row>
     <row r="64" spans="1:8" ht="18" customHeight="1">
-      <c r="A64" s="51" t="s">
+      <c r="A64" s="50" t="s">
         <v>9</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -1951,7 +1992,7 @@
       <c r="H64" s="12"/>
     </row>
     <row r="65" spans="1:8" ht="18" customHeight="1">
-      <c r="A65" s="51" t="s">
+      <c r="A65" s="50" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="12" t="s">
@@ -1965,7 +2006,7 @@
       <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:8" ht="18" customHeight="1">
-      <c r="A66" s="51" t="s">
+      <c r="A66" s="50" t="s">
         <v>7</v>
       </c>
       <c r="B66" s="12" t="s">
@@ -1979,7 +2020,7 @@
       <c r="H66" s="12"/>
     </row>
     <row r="67" spans="1:8" ht="18" customHeight="1">
-      <c r="A67" s="51" t="s">
+      <c r="A67" s="50" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="12" t="s">
@@ -1993,7 +2034,7 @@
       <c r="H67" s="12"/>
     </row>
     <row r="68" spans="1:8" ht="18" customHeight="1">
-      <c r="A68" s="51" t="s">
+      <c r="A68" s="50" t="s">
         <v>5</v>
       </c>
       <c r="B68" s="12" t="s">
@@ -2007,7 +2048,7 @@
       <c r="H68" s="12"/>
     </row>
     <row r="69" spans="1:8" ht="18" customHeight="1">
-      <c r="A69" s="51" t="s">
+      <c r="A69" s="50" t="s">
         <v>4</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -2021,7 +2062,7 @@
       <c r="H69" s="12"/>
     </row>
     <row r="70" spans="1:8" ht="18" customHeight="1">
-      <c r="A70" s="51" t="s">
+      <c r="A70" s="50" t="s">
         <v>3</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -2035,7 +2076,7 @@
       <c r="H70" s="12"/>
     </row>
     <row r="71" spans="1:8" ht="18" customHeight="1">
-      <c r="A71" s="51" t="s">
+      <c r="A71" s="50" t="s">
         <v>2</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -2049,7 +2090,7 @@
       <c r="H71" s="12"/>
     </row>
     <row r="72" spans="1:8" ht="18" customHeight="1">
-      <c r="A72" s="51" t="s">
+      <c r="A72" s="50" t="s">
         <v>1</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -2063,7 +2104,7 @@
       <c r="H72" s="12"/>
     </row>
     <row r="73" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="52" t="s">
+      <c r="A73" s="51" t="s">
         <v>0</v>
       </c>
       <c r="B73" s="14" t="s">
@@ -2077,7 +2118,7 @@
       <c r="H73" s="14"/>
     </row>
     <row r="74" spans="1:8" ht="18" customHeight="1">
-      <c r="A74" s="53" t="s">
+      <c r="A74" s="52" t="s">
         <v>23</v>
       </c>
       <c r="B74" s="15" t="s">
@@ -2091,7 +2132,7 @@
       <c r="H74" s="15"/>
     </row>
     <row r="75" spans="1:8" ht="18" customHeight="1">
-      <c r="A75" s="54" t="s">
+      <c r="A75" s="53" t="s">
         <v>22</v>
       </c>
       <c r="B75" s="16" t="s">
@@ -2105,7 +2146,7 @@
       <c r="H75" s="16"/>
     </row>
     <row r="76" spans="1:8" ht="18" customHeight="1">
-      <c r="A76" s="54" t="s">
+      <c r="A76" s="53" t="s">
         <v>21</v>
       </c>
       <c r="B76" s="16" t="s">
@@ -2119,7 +2160,7 @@
       <c r="H76" s="16"/>
     </row>
     <row r="77" spans="1:8" ht="18" customHeight="1">
-      <c r="A77" s="54" t="s">
+      <c r="A77" s="53" t="s">
         <v>20</v>
       </c>
       <c r="B77" s="16" t="s">
@@ -2133,7 +2174,7 @@
       <c r="H77" s="16"/>
     </row>
     <row r="78" spans="1:8" ht="18" customHeight="1">
-      <c r="A78" s="54" t="s">
+      <c r="A78" s="53" t="s">
         <v>19</v>
       </c>
       <c r="B78" s="16" t="s">
@@ -2147,7 +2188,7 @@
       <c r="H78" s="16"/>
     </row>
     <row r="79" spans="1:8" ht="18" customHeight="1">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="53" t="s">
         <v>18</v>
       </c>
       <c r="B79" s="16" t="s">
@@ -2161,7 +2202,7 @@
       <c r="H79" s="16"/>
     </row>
     <row r="80" spans="1:8" ht="18" customHeight="1">
-      <c r="A80" s="54" t="s">
+      <c r="A80" s="53" t="s">
         <v>17</v>
       </c>
       <c r="B80" s="16" t="s">
@@ -2175,7 +2216,7 @@
       <c r="H80" s="16"/>
     </row>
     <row r="81" spans="1:8" ht="18" customHeight="1">
-      <c r="A81" s="54" t="s">
+      <c r="A81" s="53" t="s">
         <v>16</v>
       </c>
       <c r="B81" s="16" t="s">
@@ -2189,13 +2230,13 @@
       <c r="H81" s="16"/>
     </row>
     <row r="82" spans="1:8" ht="18" customHeight="1">
-      <c r="A82" s="54" t="s">
+      <c r="A82" s="53" t="s">
         <v>15</v>
       </c>
       <c r="B82" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="41"/>
+      <c r="C82" s="40"/>
       <c r="D82" s="16"/>
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
@@ -2203,7 +2244,7 @@
       <c r="H82" s="16"/>
     </row>
     <row r="83" spans="1:8" ht="18" customHeight="1">
-      <c r="A83" s="54" t="s">
+      <c r="A83" s="53" t="s">
         <v>14</v>
       </c>
       <c r="B83" s="16" t="s">
@@ -2217,7 +2258,7 @@
       <c r="H83" s="16"/>
     </row>
     <row r="84" spans="1:8" ht="18" customHeight="1">
-      <c r="A84" s="54" t="s">
+      <c r="A84" s="53" t="s">
         <v>13</v>
       </c>
       <c r="B84" s="16" t="s">
@@ -2231,7 +2272,7 @@
       <c r="H84" s="16"/>
     </row>
     <row r="85" spans="1:8" ht="18" customHeight="1">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="53" t="s">
         <v>12</v>
       </c>
       <c r="B85" s="16" t="s">
@@ -2245,7 +2286,7 @@
       <c r="H85" s="16"/>
     </row>
     <row r="86" spans="1:8" ht="18" customHeight="1">
-      <c r="A86" s="54" t="s">
+      <c r="A86" s="53" t="s">
         <v>11</v>
       </c>
       <c r="B86" s="16" t="s">
@@ -2259,7 +2300,7 @@
       <c r="H86" s="16"/>
     </row>
     <row r="87" spans="1:8" ht="18" customHeight="1">
-      <c r="A87" s="54" t="s">
+      <c r="A87" s="53" t="s">
         <v>10</v>
       </c>
       <c r="B87" s="16" t="s">
@@ -2273,7 +2314,7 @@
       <c r="H87" s="16"/>
     </row>
     <row r="88" spans="1:8" ht="18" customHeight="1">
-      <c r="A88" s="54" t="s">
+      <c r="A88" s="53" t="s">
         <v>9</v>
       </c>
       <c r="B88" s="16" t="s">
@@ -2287,7 +2328,7 @@
       <c r="H88" s="16"/>
     </row>
     <row r="89" spans="1:8" ht="18" customHeight="1">
-      <c r="A89" s="54" t="s">
+      <c r="A89" s="53" t="s">
         <v>8</v>
       </c>
       <c r="B89" s="16" t="s">
@@ -2301,7 +2342,7 @@
       <c r="H89" s="16"/>
     </row>
     <row r="90" spans="1:8" ht="18" customHeight="1">
-      <c r="A90" s="54" t="s">
+      <c r="A90" s="53" t="s">
         <v>7</v>
       </c>
       <c r="B90" s="16" t="s">
@@ -2315,7 +2356,7 @@
       <c r="H90" s="16"/>
     </row>
     <row r="91" spans="1:8" ht="18" customHeight="1">
-      <c r="A91" s="54" t="s">
+      <c r="A91" s="53" t="s">
         <v>6</v>
       </c>
       <c r="B91" s="16" t="s">
@@ -2329,7 +2370,7 @@
       <c r="H91" s="16"/>
     </row>
     <row r="92" spans="1:8" ht="18" customHeight="1">
-      <c r="A92" s="54" t="s">
+      <c r="A92" s="53" t="s">
         <v>5</v>
       </c>
       <c r="B92" s="16" t="s">
@@ -2343,7 +2384,7 @@
       <c r="H92" s="16"/>
     </row>
     <row r="93" spans="1:8" ht="18" customHeight="1">
-      <c r="A93" s="54" t="s">
+      <c r="A93" s="53" t="s">
         <v>4</v>
       </c>
       <c r="B93" s="16" t="s">
@@ -2357,7 +2398,7 @@
       <c r="H93" s="16"/>
     </row>
     <row r="94" spans="1:8" ht="18" customHeight="1">
-      <c r="A94" s="54" t="s">
+      <c r="A94" s="53" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="16" t="s">
@@ -2371,7 +2412,7 @@
       <c r="H94" s="16"/>
     </row>
     <row r="95" spans="1:8" ht="18" customHeight="1">
-      <c r="A95" s="54" t="s">
+      <c r="A95" s="53" t="s">
         <v>2</v>
       </c>
       <c r="B95" s="16" t="s">
@@ -2385,7 +2426,7 @@
       <c r="H95" s="16"/>
     </row>
     <row r="96" spans="1:8" ht="18" customHeight="1">
-      <c r="A96" s="54" t="s">
+      <c r="A96" s="53" t="s">
         <v>1</v>
       </c>
       <c r="B96" s="16" t="s">
@@ -2399,7 +2440,7 @@
       <c r="H96" s="16"/>
     </row>
     <row r="97" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A97" s="55" t="s">
+      <c r="A97" s="54" t="s">
         <v>0</v>
       </c>
       <c r="B97" s="18" t="s">
@@ -2413,7 +2454,7 @@
       <c r="H97" s="18"/>
     </row>
     <row r="98" spans="1:8" ht="18" customHeight="1">
-      <c r="A98" s="56" t="s">
+      <c r="A98" s="55" t="s">
         <v>23</v>
       </c>
       <c r="B98" s="20" t="s">
@@ -2427,7 +2468,7 @@
       <c r="H98" s="20"/>
     </row>
     <row r="99" spans="1:8" ht="18" customHeight="1">
-      <c r="A99" s="57" t="s">
+      <c r="A99" s="56" t="s">
         <v>22</v>
       </c>
       <c r="B99" s="21" t="s">
@@ -2441,7 +2482,7 @@
       <c r="H99" s="21"/>
     </row>
     <row r="100" spans="1:8" ht="18" customHeight="1">
-      <c r="A100" s="57" t="s">
+      <c r="A100" s="56" t="s">
         <v>21</v>
       </c>
       <c r="B100" s="21" t="s">
@@ -2455,7 +2496,7 @@
       <c r="H100" s="21"/>
     </row>
     <row r="101" spans="1:8" ht="18" customHeight="1">
-      <c r="A101" s="57" t="s">
+      <c r="A101" s="56" t="s">
         <v>20</v>
       </c>
       <c r="B101" s="21" t="s">
@@ -2469,7 +2510,7 @@
       <c r="H101" s="21"/>
     </row>
     <row r="102" spans="1:8" ht="18" customHeight="1">
-      <c r="A102" s="57" t="s">
+      <c r="A102" s="56" t="s">
         <v>19</v>
       </c>
       <c r="B102" s="21" t="s">
@@ -2483,7 +2524,7 @@
       <c r="H102" s="21"/>
     </row>
     <row r="103" spans="1:8" ht="18" customHeight="1">
-      <c r="A103" s="57" t="s">
+      <c r="A103" s="56" t="s">
         <v>18</v>
       </c>
       <c r="B103" s="21" t="s">
@@ -2497,7 +2538,7 @@
       <c r="H103" s="21"/>
     </row>
     <row r="104" spans="1:8" ht="18" customHeight="1">
-      <c r="A104" s="57" t="s">
+      <c r="A104" s="56" t="s">
         <v>17</v>
       </c>
       <c r="B104" s="21" t="s">
@@ -2511,7 +2552,7 @@
       <c r="H104" s="21"/>
     </row>
     <row r="105" spans="1:8" ht="18" customHeight="1">
-      <c r="A105" s="57" t="s">
+      <c r="A105" s="56" t="s">
         <v>16</v>
       </c>
       <c r="B105" s="21" t="s">
@@ -2525,7 +2566,7 @@
       <c r="H105" s="21"/>
     </row>
     <row r="106" spans="1:8" ht="18" customHeight="1">
-      <c r="A106" s="57" t="s">
+      <c r="A106" s="56" t="s">
         <v>15</v>
       </c>
       <c r="B106" s="21" t="s">
@@ -2539,7 +2580,7 @@
       <c r="H106" s="21"/>
     </row>
     <row r="107" spans="1:8" ht="18" customHeight="1">
-      <c r="A107" s="57" t="s">
+      <c r="A107" s="56" t="s">
         <v>14</v>
       </c>
       <c r="B107" s="21" t="s">
@@ -2553,7 +2594,7 @@
       <c r="H107" s="21"/>
     </row>
     <row r="108" spans="1:8" ht="18" customHeight="1">
-      <c r="A108" s="57" t="s">
+      <c r="A108" s="56" t="s">
         <v>13</v>
       </c>
       <c r="B108" s="21" t="s">
@@ -2567,7 +2608,7 @@
       <c r="H108" s="21"/>
     </row>
     <row r="109" spans="1:8" ht="18" customHeight="1">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="56" t="s">
         <v>12</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -2581,7 +2622,7 @@
       <c r="H109" s="21"/>
     </row>
     <row r="110" spans="1:8" ht="18" customHeight="1">
-      <c r="A110" s="57" t="s">
+      <c r="A110" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B110" s="21" t="s">
@@ -2595,7 +2636,7 @@
       <c r="H110" s="21"/>
     </row>
     <row r="111" spans="1:8" ht="18" customHeight="1">
-      <c r="A111" s="57" t="s">
+      <c r="A111" s="56" t="s">
         <v>10</v>
       </c>
       <c r="B111" s="21" t="s">
@@ -2609,7 +2650,7 @@
       <c r="H111" s="21"/>
     </row>
     <row r="112" spans="1:8" ht="18" customHeight="1">
-      <c r="A112" s="57" t="s">
+      <c r="A112" s="56" t="s">
         <v>9</v>
       </c>
       <c r="B112" s="21" t="s">
@@ -2623,7 +2664,7 @@
       <c r="H112" s="21"/>
     </row>
     <row r="113" spans="1:8" ht="18" customHeight="1">
-      <c r="A113" s="57" t="s">
+      <c r="A113" s="56" t="s">
         <v>8</v>
       </c>
       <c r="B113" s="21" t="s">
@@ -2637,7 +2678,7 @@
       <c r="H113" s="21"/>
     </row>
     <row r="114" spans="1:8" ht="18" customHeight="1">
-      <c r="A114" s="57" t="s">
+      <c r="A114" s="56" t="s">
         <v>7</v>
       </c>
       <c r="B114" s="21" t="s">
@@ -2651,7 +2692,7 @@
       <c r="H114" s="21"/>
     </row>
     <row r="115" spans="1:8" ht="18" customHeight="1">
-      <c r="A115" s="57" t="s">
+      <c r="A115" s="56" t="s">
         <v>6</v>
       </c>
       <c r="B115" s="21" t="s">
@@ -2665,7 +2706,7 @@
       <c r="H115" s="21"/>
     </row>
     <row r="116" spans="1:8" ht="18" customHeight="1">
-      <c r="A116" s="57" t="s">
+      <c r="A116" s="56" t="s">
         <v>5</v>
       </c>
       <c r="B116" s="21" t="s">
@@ -2679,7 +2720,7 @@
       <c r="H116" s="21"/>
     </row>
     <row r="117" spans="1:8" ht="18" customHeight="1">
-      <c r="A117" s="57" t="s">
+      <c r="A117" s="56" t="s">
         <v>4</v>
       </c>
       <c r="B117" s="21" t="s">
@@ -2693,7 +2734,7 @@
       <c r="H117" s="21"/>
     </row>
     <row r="118" spans="1:8" ht="18" customHeight="1">
-      <c r="A118" s="57" t="s">
+      <c r="A118" s="56" t="s">
         <v>3</v>
       </c>
       <c r="B118" s="21" t="s">
@@ -2707,7 +2748,7 @@
       <c r="H118" s="21"/>
     </row>
     <row r="119" spans="1:8" ht="18" customHeight="1">
-      <c r="A119" s="57" t="s">
+      <c r="A119" s="56" t="s">
         <v>2</v>
       </c>
       <c r="B119" s="21" t="s">
@@ -2721,7 +2762,7 @@
       <c r="H119" s="21"/>
     </row>
     <row r="120" spans="1:8" ht="18" customHeight="1">
-      <c r="A120" s="57" t="s">
+      <c r="A120" s="56" t="s">
         <v>1</v>
       </c>
       <c r="B120" s="21" t="s">
@@ -2735,7 +2776,7 @@
       <c r="H120" s="21"/>
     </row>
     <row r="121" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A121" s="58" t="s">
+      <c r="A121" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B121" s="23" t="s">
@@ -2749,7 +2790,7 @@
       <c r="H121" s="23"/>
     </row>
     <row r="122" spans="1:8" ht="18" customHeight="1">
-      <c r="A122" s="59" t="s">
+      <c r="A122" s="58" t="s">
         <v>23</v>
       </c>
       <c r="B122" s="25" t="s">
@@ -2763,7 +2804,7 @@
       <c r="H122" s="25"/>
     </row>
     <row r="123" spans="1:8" ht="18" customHeight="1">
-      <c r="A123" s="60" t="s">
+      <c r="A123" s="59" t="s">
         <v>22</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -2777,7 +2818,7 @@
       <c r="H123" s="28"/>
     </row>
     <row r="124" spans="1:8" ht="18" customHeight="1">
-      <c r="A124" s="60" t="s">
+      <c r="A124" s="59" t="s">
         <v>21</v>
       </c>
       <c r="B124" s="28" t="s">
@@ -2791,7 +2832,7 @@
       <c r="H124" s="28"/>
     </row>
     <row r="125" spans="1:8" ht="18" customHeight="1">
-      <c r="A125" s="60" t="s">
+      <c r="A125" s="59" t="s">
         <v>20</v>
       </c>
       <c r="B125" s="28" t="s">
@@ -2805,7 +2846,7 @@
       <c r="H125" s="28"/>
     </row>
     <row r="126" spans="1:8" ht="18" customHeight="1">
-      <c r="A126" s="60" t="s">
+      <c r="A126" s="59" t="s">
         <v>19</v>
       </c>
       <c r="B126" s="28" t="s">
@@ -2819,7 +2860,7 @@
       <c r="H126" s="28"/>
     </row>
     <row r="127" spans="1:8" ht="18" customHeight="1">
-      <c r="A127" s="60" t="s">
+      <c r="A127" s="59" t="s">
         <v>18</v>
       </c>
       <c r="B127" s="28" t="s">
@@ -2833,7 +2874,7 @@
       <c r="H127" s="28"/>
     </row>
     <row r="128" spans="1:8" ht="18" customHeight="1">
-      <c r="A128" s="60" t="s">
+      <c r="A128" s="59" t="s">
         <v>17</v>
       </c>
       <c r="B128" s="28" t="s">
@@ -2847,7 +2888,7 @@
       <c r="H128" s="28"/>
     </row>
     <row r="129" spans="1:8" ht="18" customHeight="1">
-      <c r="A129" s="60" t="s">
+      <c r="A129" s="59" t="s">
         <v>16</v>
       </c>
       <c r="B129" s="28" t="s">
@@ -2861,7 +2902,7 @@
       <c r="H129" s="28"/>
     </row>
     <row r="130" spans="1:8" ht="18" customHeight="1">
-      <c r="A130" s="60" t="s">
+      <c r="A130" s="59" t="s">
         <v>15</v>
       </c>
       <c r="B130" s="28" t="s">
@@ -2875,7 +2916,7 @@
       <c r="H130" s="28"/>
     </row>
     <row r="131" spans="1:8" ht="18" customHeight="1">
-      <c r="A131" s="60" t="s">
+      <c r="A131" s="59" t="s">
         <v>14</v>
       </c>
       <c r="B131" s="28" t="s">
@@ -2889,7 +2930,7 @@
       <c r="H131" s="28"/>
     </row>
     <row r="132" spans="1:8" ht="18" customHeight="1">
-      <c r="A132" s="60" t="s">
+      <c r="A132" s="59" t="s">
         <v>13</v>
       </c>
       <c r="B132" s="28" t="s">
@@ -2903,7 +2944,7 @@
       <c r="H132" s="28"/>
     </row>
     <row r="133" spans="1:8" ht="18" customHeight="1">
-      <c r="A133" s="60" t="s">
+      <c r="A133" s="59" t="s">
         <v>12</v>
       </c>
       <c r="B133" s="28" t="s">
@@ -2917,7 +2958,7 @@
       <c r="H133" s="28"/>
     </row>
     <row r="134" spans="1:8" ht="18" customHeight="1">
-      <c r="A134" s="60" t="s">
+      <c r="A134" s="59" t="s">
         <v>11</v>
       </c>
       <c r="B134" s="28" t="s">
@@ -2931,7 +2972,7 @@
       <c r="H134" s="28"/>
     </row>
     <row r="135" spans="1:8" ht="18" customHeight="1">
-      <c r="A135" s="60" t="s">
+      <c r="A135" s="59" t="s">
         <v>10</v>
       </c>
       <c r="B135" s="28" t="s">
@@ -2945,7 +2986,7 @@
       <c r="H135" s="28"/>
     </row>
     <row r="136" spans="1:8" ht="18" customHeight="1">
-      <c r="A136" s="60" t="s">
+      <c r="A136" s="59" t="s">
         <v>9</v>
       </c>
       <c r="B136" s="28" t="s">
@@ -2959,7 +3000,7 @@
       <c r="H136" s="28"/>
     </row>
     <row r="137" spans="1:8" ht="18" customHeight="1">
-      <c r="A137" s="60" t="s">
+      <c r="A137" s="59" t="s">
         <v>8</v>
       </c>
       <c r="B137" s="28" t="s">
@@ -2973,7 +3014,7 @@
       <c r="H137" s="28"/>
     </row>
     <row r="138" spans="1:8" ht="18" customHeight="1">
-      <c r="A138" s="60" t="s">
+      <c r="A138" s="59" t="s">
         <v>7</v>
       </c>
       <c r="B138" s="28" t="s">
@@ -2987,7 +3028,7 @@
       <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8" ht="18" customHeight="1">
-      <c r="A139" s="60" t="s">
+      <c r="A139" s="59" t="s">
         <v>6</v>
       </c>
       <c r="B139" s="28" t="s">
@@ -3001,7 +3042,7 @@
       <c r="H139" s="28"/>
     </row>
     <row r="140" spans="1:8" ht="18" customHeight="1">
-      <c r="A140" s="60" t="s">
+      <c r="A140" s="59" t="s">
         <v>5</v>
       </c>
       <c r="B140" s="28" t="s">
@@ -3015,7 +3056,7 @@
       <c r="H140" s="28"/>
     </row>
     <row r="141" spans="1:8" ht="18" customHeight="1">
-      <c r="A141" s="60" t="s">
+      <c r="A141" s="59" t="s">
         <v>4</v>
       </c>
       <c r="B141" s="28" t="s">
@@ -3029,7 +3070,7 @@
       <c r="H141" s="28"/>
     </row>
     <row r="142" spans="1:8" ht="18" customHeight="1">
-      <c r="A142" s="60" t="s">
+      <c r="A142" s="59" t="s">
         <v>3</v>
       </c>
       <c r="B142" s="28" t="s">
@@ -3043,7 +3084,7 @@
       <c r="H142" s="28"/>
     </row>
     <row r="143" spans="1:8" ht="18" customHeight="1">
-      <c r="A143" s="60" t="s">
+      <c r="A143" s="59" t="s">
         <v>2</v>
       </c>
       <c r="B143" s="28" t="s">
@@ -3057,7 +3098,7 @@
       <c r="H143" s="28"/>
     </row>
     <row r="144" spans="1:8" ht="18" customHeight="1">
-      <c r="A144" s="60" t="s">
+      <c r="A144" s="59" t="s">
         <v>1</v>
       </c>
       <c r="B144" s="28" t="s">
@@ -3071,7 +3112,7 @@
       <c r="H144" s="28"/>
     </row>
     <row r="145" spans="1:8" ht="18" customHeight="1" thickBot="1">
-      <c r="A145" s="61" t="s">
+      <c r="A145" s="60" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="29" t="s">
@@ -3085,7 +3126,7 @@
       <c r="H145" s="29"/>
     </row>
     <row r="146" spans="1:8" ht="18" customHeight="1">
-      <c r="A146" s="62" t="s">
+      <c r="A146" s="61" t="s">
         <v>23</v>
       </c>
       <c r="B146" s="30" t="s">
@@ -3099,7 +3140,7 @@
       <c r="H146" s="30"/>
     </row>
     <row r="147" spans="1:8" ht="18" customHeight="1">
-      <c r="A147" s="63" t="s">
+      <c r="A147" s="62" t="s">
         <v>22</v>
       </c>
       <c r="B147" s="31" t="s">
@@ -3113,7 +3154,7 @@
       <c r="H147" s="31"/>
     </row>
     <row r="148" spans="1:8" ht="18" customHeight="1">
-      <c r="A148" s="63" t="s">
+      <c r="A148" s="62" t="s">
         <v>21</v>
       </c>
       <c r="B148" s="31" t="s">
@@ -3127,7 +3168,7 @@
       <c r="H148" s="31"/>
     </row>
     <row r="149" spans="1:8" ht="18" customHeight="1">
-      <c r="A149" s="63" t="s">
+      <c r="A149" s="62" t="s">
         <v>20</v>
       </c>
       <c r="B149" s="31" t="s">
@@ -3141,7 +3182,7 @@
       <c r="H149" s="31"/>
     </row>
     <row r="150" spans="1:8" ht="18" customHeight="1">
-      <c r="A150" s="63" t="s">
+      <c r="A150" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B150" s="31" t="s">
@@ -3155,7 +3196,7 @@
       <c r="H150" s="31"/>
     </row>
     <row r="151" spans="1:8" ht="18" customHeight="1">
-      <c r="A151" s="63" t="s">
+      <c r="A151" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B151" s="31" t="s">
@@ -3169,7 +3210,7 @@
       <c r="H151" s="31"/>
     </row>
     <row r="152" spans="1:8" ht="18" customHeight="1">
-      <c r="A152" s="63" t="s">
+      <c r="A152" s="62" t="s">
         <v>17</v>
       </c>
       <c r="B152" s="31" t="s">
@@ -3183,7 +3224,7 @@
       <c r="H152" s="31"/>
     </row>
     <row r="153" spans="1:8" ht="18" customHeight="1">
-      <c r="A153" s="63" t="s">
+      <c r="A153" s="62" t="s">
         <v>16</v>
       </c>
       <c r="B153" s="31" t="s">
@@ -3197,7 +3238,7 @@
       <c r="H153" s="31"/>
     </row>
     <row r="154" spans="1:8" ht="18" customHeight="1">
-      <c r="A154" s="63" t="s">
+      <c r="A154" s="62" t="s">
         <v>15</v>
       </c>
       <c r="B154" s="31" t="s">
@@ -3211,7 +3252,7 @@
       <c r="H154" s="31"/>
     </row>
     <row r="155" spans="1:8" ht="18" customHeight="1">
-      <c r="A155" s="63" t="s">
+      <c r="A155" s="62" t="s">
         <v>14</v>
       </c>
       <c r="B155" s="31" t="s">
@@ -3225,7 +3266,7 @@
       <c r="H155" s="31"/>
     </row>
     <row r="156" spans="1:8" ht="18" customHeight="1">
-      <c r="A156" s="63" t="s">
+      <c r="A156" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B156" s="31" t="s">
@@ -3239,7 +3280,7 @@
       <c r="H156" s="31"/>
     </row>
     <row r="157" spans="1:8" ht="18" customHeight="1">
-      <c r="A157" s="63" t="s">
+      <c r="A157" s="62" t="s">
         <v>12</v>
       </c>
       <c r="B157" s="31" t="s">
@@ -3253,7 +3294,7 @@
       <c r="H157" s="31"/>
     </row>
     <row r="158" spans="1:8" ht="18" customHeight="1">
-      <c r="A158" s="63" t="s">
+      <c r="A158" s="62" t="s">
         <v>11</v>
       </c>
       <c r="B158" s="31" t="s">
@@ -3267,7 +3308,7 @@
       <c r="H158" s="31"/>
     </row>
     <row r="159" spans="1:8" ht="18" customHeight="1">
-      <c r="A159" s="63" t="s">
+      <c r="A159" s="62" t="s">
         <v>10</v>
       </c>
       <c r="B159" s="31" t="s">
@@ -3281,7 +3322,7 @@
       <c r="H159" s="31"/>
     </row>
     <row r="160" spans="1:8" ht="18" customHeight="1">
-      <c r="A160" s="63" t="s">
+      <c r="A160" s="62" t="s">
         <v>9</v>
       </c>
       <c r="B160" s="31" t="s">
@@ -3295,7 +3336,7 @@
       <c r="H160" s="31"/>
     </row>
     <row r="161" spans="1:8" ht="18" customHeight="1">
-      <c r="A161" s="63" t="s">
+      <c r="A161" s="62" t="s">
         <v>8</v>
       </c>
       <c r="B161" s="31" t="s">
@@ -3309,7 +3350,7 @@
       <c r="H161" s="31"/>
     </row>
     <row r="162" spans="1:8" ht="18" customHeight="1">
-      <c r="A162" s="63" t="s">
+      <c r="A162" s="62" t="s">
         <v>7</v>
       </c>
       <c r="B162" s="31" t="s">
@@ -3323,7 +3364,7 @@
       <c r="H162" s="31"/>
     </row>
     <row r="163" spans="1:8" ht="18" customHeight="1">
-      <c r="A163" s="63" t="s">
+      <c r="A163" s="62" t="s">
         <v>6</v>
       </c>
       <c r="B163" s="31" t="s">
@@ -3337,7 +3378,7 @@
       <c r="H163" s="31"/>
     </row>
     <row r="164" spans="1:8" ht="18" customHeight="1">
-      <c r="A164" s="63" t="s">
+      <c r="A164" s="62" t="s">
         <v>5</v>
       </c>
       <c r="B164" s="31" t="s">
@@ -3351,7 +3392,7 @@
       <c r="H164" s="31"/>
     </row>
     <row r="165" spans="1:8" ht="18" customHeight="1">
-      <c r="A165" s="63" t="s">
+      <c r="A165" s="62" t="s">
         <v>4</v>
       </c>
       <c r="B165" s="31" t="s">
@@ -3365,7 +3406,7 @@
       <c r="H165" s="31"/>
     </row>
     <row r="166" spans="1:8" ht="18" customHeight="1">
-      <c r="A166" s="63" t="s">
+      <c r="A166" s="62" t="s">
         <v>3</v>
       </c>
       <c r="B166" s="31" t="s">
@@ -3379,7 +3420,7 @@
       <c r="H166" s="31"/>
     </row>
     <row r="167" spans="1:8" ht="18" customHeight="1">
-      <c r="A167" s="63" t="s">
+      <c r="A167" s="62" t="s">
         <v>2</v>
       </c>
       <c r="B167" s="31" t="s">
@@ -3393,7 +3434,7 @@
       <c r="H167" s="31"/>
     </row>
     <row r="168" spans="1:8" ht="18" customHeight="1">
-      <c r="A168" s="63" t="s">
+      <c r="A168" s="62" t="s">
         <v>1</v>
       </c>
       <c r="B168" s="31" t="s">
@@ -3407,7 +3448,7 @@
       <c r="H168" s="31"/>
     </row>
     <row r="169" spans="1:8" ht="18" customHeight="1">
-      <c r="A169" s="63" t="s">
+      <c r="A169" s="62" t="s">
         <v>0</v>
       </c>
       <c r="B169" s="31" t="s">
